--- a/questoes.xlsx
+++ b/questoes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J501"/>
+  <dimension ref="A1:K501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23711,6 +23711,11 @@
         </is>
       </c>
       <c r="J452" t="inlineStr"/>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -23760,6 +23765,11 @@
         </is>
       </c>
       <c r="J453" t="inlineStr"/>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -23811,6 +23821,11 @@
         </is>
       </c>
       <c r="J454" t="inlineStr"/>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -23861,6 +23876,11 @@
         </is>
       </c>
       <c r="J455" t="inlineStr"/>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -23910,6 +23930,11 @@
         </is>
       </c>
       <c r="J456" t="inlineStr"/>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -23958,6 +23983,11 @@
         </is>
       </c>
       <c r="J457" t="inlineStr"/>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -24006,6 +24036,11 @@
         </is>
       </c>
       <c r="J458" t="inlineStr"/>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -24055,6 +24090,11 @@
         </is>
       </c>
       <c r="J459" t="inlineStr"/>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -24110,6 +24150,11 @@
           <t>ph10_cie_09.jpg</t>
         </is>
       </c>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -24160,6 +24205,11 @@
         </is>
       </c>
       <c r="J461" t="inlineStr"/>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -24209,6 +24259,11 @@
         </is>
       </c>
       <c r="J462" t="inlineStr"/>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -24258,6 +24313,11 @@
         </is>
       </c>
       <c r="J463" t="inlineStr"/>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -24310,6 +24370,11 @@
         </is>
       </c>
       <c r="J464" t="inlineStr"/>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -24359,6 +24424,11 @@
         </is>
       </c>
       <c r="J465" t="inlineStr"/>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -24408,6 +24478,11 @@
         </is>
       </c>
       <c r="J466" t="inlineStr"/>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -24457,6 +24532,11 @@
         </is>
       </c>
       <c r="J467" t="inlineStr"/>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -24510,6 +24590,11 @@
           <t>ph10_geo_07.png</t>
         </is>
       </c>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -24558,6 +24643,11 @@
         </is>
       </c>
       <c r="J469" t="inlineStr"/>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -24611,6 +24701,11 @@
           <t>ph10_geo_09.jpg</t>
         </is>
       </c>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -24659,6 +24754,11 @@
         </is>
       </c>
       <c r="J471" t="inlineStr"/>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -24712,6 +24812,11 @@
         </is>
       </c>
       <c r="J472" t="inlineStr"/>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -24762,6 +24867,11 @@
         </is>
       </c>
       <c r="J473" t="inlineStr"/>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -24812,6 +24922,11 @@
         </is>
       </c>
       <c r="J474" t="inlineStr"/>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -24862,6 +24977,11 @@
         </is>
       </c>
       <c r="J475" t="inlineStr"/>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -24912,6 +25032,11 @@
         </is>
       </c>
       <c r="J476" t="inlineStr"/>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -24967,6 +25092,11 @@
         </is>
       </c>
       <c r="J477" t="inlineStr"/>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -25021,6 +25151,11 @@
           <t>ph10_his_07.png</t>
         </is>
       </c>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -25072,6 +25207,11 @@
       <c r="J479" t="inlineStr">
         <is>
           <t>ph10_his_08.png</t>
+        </is>
+      </c>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>7ano</t>
         </is>
       </c>
     </row>
@@ -25124,6 +25264,11 @@
         </is>
       </c>
       <c r="J480" t="inlineStr"/>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -25175,6 +25320,11 @@
         </is>
       </c>
       <c r="J481" t="inlineStr"/>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -25226,6 +25376,11 @@
         </is>
       </c>
       <c r="J482" t="inlineStr"/>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -25276,6 +25431,11 @@
         </is>
       </c>
       <c r="J483" t="inlineStr"/>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -25337,6 +25497,11 @@
         </is>
       </c>
       <c r="J484" t="inlineStr"/>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -25390,6 +25555,11 @@
         </is>
       </c>
       <c r="J485" t="inlineStr"/>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -25446,6 +25616,11 @@
         </is>
       </c>
       <c r="J486" t="inlineStr"/>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -25498,6 +25673,11 @@
         </is>
       </c>
       <c r="J487" t="inlineStr"/>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -25552,6 +25732,11 @@
         </is>
       </c>
       <c r="J488" t="inlineStr"/>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -25608,6 +25793,11 @@
         </is>
       </c>
       <c r="J489" t="inlineStr"/>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -25660,6 +25850,11 @@
       <c r="J490" t="inlineStr">
         <is>
           <t>ph10_por_09.png</t>
+        </is>
+      </c>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>7ano</t>
         </is>
       </c>
     </row>
@@ -25717,6 +25912,11 @@
         </is>
       </c>
       <c r="J491" t="inlineStr"/>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -25772,6 +25972,11 @@
         </is>
       </c>
       <c r="J492" t="inlineStr"/>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -25821,6 +26026,11 @@
         </is>
       </c>
       <c r="J493" t="inlineStr"/>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -25875,6 +26085,11 @@
         </is>
       </c>
       <c r="J494" t="inlineStr"/>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -25924,6 +26139,11 @@
         </is>
       </c>
       <c r="J495" t="inlineStr"/>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -25977,6 +26197,11 @@
           <t>ph10_mat_05.png</t>
         </is>
       </c>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -26031,6 +26256,11 @@
           <t>ph10_mat_06.png</t>
         </is>
       </c>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -26085,6 +26315,11 @@
           <t>ph10_mat_07.png</t>
         </is>
       </c>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -26138,6 +26373,11 @@
           <t>ph10_mat_08.png</t>
         </is>
       </c>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -26190,6 +26430,11 @@
       <c r="J500" t="inlineStr">
         <is>
           <t>ph10_mat_09.png</t>
+        </is>
+      </c>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>7ano</t>
         </is>
       </c>
     </row>
@@ -26246,6 +26491,11 @@
       <c r="J501" t="inlineStr">
         <is>
           <t>ph10_mat_10.png</t>
+        </is>
+      </c>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>7ano</t>
         </is>
       </c>
     </row>

--- a/questoes.xlsx
+++ b/questoes.xlsx
@@ -23975,7 +23975,7 @@
       <c r="J452" t="inlineStr"/>
       <c r="K452" t="inlineStr">
         <is>
-          <t>8ano</t>
+          <t>7ano</t>
         </is>
       </c>
     </row>
@@ -24029,7 +24029,7 @@
       <c r="J453" t="inlineStr"/>
       <c r="K453" t="inlineStr">
         <is>
-          <t>8ano</t>
+          <t>7ano</t>
         </is>
       </c>
     </row>
@@ -24083,7 +24083,7 @@
       <c r="J454" t="inlineStr"/>
       <c r="K454" t="inlineStr">
         <is>
-          <t>8ano</t>
+          <t>7ano</t>
         </is>
       </c>
     </row>
@@ -24137,7 +24137,7 @@
       <c r="J455" t="inlineStr"/>
       <c r="K455" t="inlineStr">
         <is>
-          <t>8ano</t>
+          <t>7ano</t>
         </is>
       </c>
     </row>
@@ -24191,7 +24191,7 @@
       <c r="J456" t="inlineStr"/>
       <c r="K456" t="inlineStr">
         <is>
-          <t>8ano</t>
+          <t>7ano</t>
         </is>
       </c>
     </row>
@@ -24244,12 +24244,12 @@
       </c>
       <c r="J457" t="inlineStr">
         <is>
-          <t>8a_ph01_cie_06.png</t>
+          <t>ph01_cie_06.png</t>
         </is>
       </c>
       <c r="K457" t="inlineStr">
         <is>
-          <t>8ano</t>
+          <t>7ano</t>
         </is>
       </c>
     </row>
@@ -24302,12 +24302,12 @@
       </c>
       <c r="J458" t="inlineStr">
         <is>
-          <t>8a_ph01_cie_07.png</t>
+          <t>ph01_cie_07.png</t>
         </is>
       </c>
       <c r="K458" t="inlineStr">
         <is>
-          <t>8ano</t>
+          <t>7ano</t>
         </is>
       </c>
     </row>
@@ -24360,7 +24360,7 @@
       <c r="J459" t="inlineStr"/>
       <c r="K459" t="inlineStr">
         <is>
-          <t>8ano</t>
+          <t>7ano</t>
         </is>
       </c>
     </row>
@@ -24416,7 +24416,7 @@
       <c r="J460" t="inlineStr"/>
       <c r="K460" t="inlineStr">
         <is>
-          <t>8ano</t>
+          <t>7ano</t>
         </is>
       </c>
     </row>
@@ -24469,7 +24469,7 @@
       <c r="J461" t="inlineStr"/>
       <c r="K461" t="inlineStr">
         <is>
-          <t>8ano</t>
+          <t>7ano</t>
         </is>
       </c>
     </row>
@@ -24522,7 +24522,7 @@
       <c r="J462" t="inlineStr"/>
       <c r="K462" t="inlineStr">
         <is>
-          <t>8ano</t>
+          <t>7ano</t>
         </is>
       </c>
     </row>
@@ -24576,7 +24576,7 @@
       <c r="J463" t="inlineStr"/>
       <c r="K463" t="inlineStr">
         <is>
-          <t>8ano</t>
+          <t>7ano</t>
         </is>
       </c>
     </row>
@@ -24630,7 +24630,7 @@
       <c r="J464" t="inlineStr"/>
       <c r="K464" t="inlineStr">
         <is>
-          <t>8ano</t>
+          <t>7ano</t>
         </is>
       </c>
     </row>
@@ -24684,7 +24684,7 @@
       <c r="J465" t="inlineStr"/>
       <c r="K465" t="inlineStr">
         <is>
-          <t>8ano</t>
+          <t>7ano</t>
         </is>
       </c>
     </row>
@@ -24738,7 +24738,7 @@
       <c r="J466" t="inlineStr"/>
       <c r="K466" t="inlineStr">
         <is>
-          <t>8ano</t>
+          <t>7ano</t>
         </is>
       </c>
     </row>
@@ -24799,7 +24799,7 @@
       <c r="J467" t="inlineStr"/>
       <c r="K467" t="inlineStr">
         <is>
-          <t>8ano</t>
+          <t>7ano</t>
         </is>
       </c>
     </row>
@@ -24851,12 +24851,12 @@
       </c>
       <c r="J468" t="inlineStr">
         <is>
-          <t>8a_ph01_geo_07.jpg</t>
+          <t>ph01_geo_07.jpg</t>
         </is>
       </c>
       <c r="K468" t="inlineStr">
         <is>
-          <t>8ano</t>
+          <t>7ano</t>
         </is>
       </c>
     </row>
@@ -24910,12 +24910,12 @@
       </c>
       <c r="J469" t="inlineStr">
         <is>
-          <t>8a_ph01_geo_08.png</t>
+          <t>ph01_geo_08.png</t>
         </is>
       </c>
       <c r="K469" t="inlineStr">
         <is>
-          <t>8ano</t>
+          <t>7ano</t>
         </is>
       </c>
     </row>
@@ -24974,12 +24974,12 @@
       </c>
       <c r="J470" t="inlineStr">
         <is>
-          <t>8a_ph01_geo_09.jpg</t>
+          <t>ph01_geo_09.jpg</t>
         </is>
       </c>
       <c r="K470" t="inlineStr">
         <is>
-          <t>8ano</t>
+          <t>7ano</t>
         </is>
       </c>
     </row>
@@ -25035,7 +25035,7 @@
       <c r="J471" t="inlineStr"/>
       <c r="K471" t="inlineStr">
         <is>
-          <t>8ano</t>
+          <t>7ano</t>
         </is>
       </c>
     </row>
@@ -25090,7 +25090,7 @@
       <c r="J472" t="inlineStr"/>
       <c r="K472" t="inlineStr">
         <is>
-          <t>8ano</t>
+          <t>7ano</t>
         </is>
       </c>
     </row>
@@ -25146,7 +25146,7 @@
       <c r="J473" t="inlineStr"/>
       <c r="K473" t="inlineStr">
         <is>
-          <t>8ano</t>
+          <t>7ano</t>
         </is>
       </c>
     </row>
@@ -25200,7 +25200,7 @@
       <c r="J474" t="inlineStr"/>
       <c r="K474" t="inlineStr">
         <is>
-          <t>8ano</t>
+          <t>7ano</t>
         </is>
       </c>
     </row>
@@ -25255,7 +25255,7 @@
       <c r="J475" t="inlineStr"/>
       <c r="K475" t="inlineStr">
         <is>
-          <t>8ano</t>
+          <t>7ano</t>
         </is>
       </c>
     </row>
@@ -25310,7 +25310,7 @@
       <c r="J476" t="inlineStr"/>
       <c r="K476" t="inlineStr">
         <is>
-          <t>8ano</t>
+          <t>7ano</t>
         </is>
       </c>
     </row>
@@ -25363,12 +25363,12 @@
       </c>
       <c r="J477" t="inlineStr">
         <is>
-          <t>8a_ph01_his_06.png</t>
+          <t>ph01_his_06.png</t>
         </is>
       </c>
       <c r="K477" t="inlineStr">
         <is>
-          <t>8ano</t>
+          <t>7ano</t>
         </is>
       </c>
     </row>
@@ -25421,12 +25421,12 @@
       </c>
       <c r="J478" t="inlineStr">
         <is>
-          <t>8a_ph01_his_07.png</t>
+          <t>ph01_his_07.png</t>
         </is>
       </c>
       <c r="K478" t="inlineStr">
         <is>
-          <t>8ano</t>
+          <t>7ano</t>
         </is>
       </c>
     </row>
@@ -25485,7 +25485,7 @@
       <c r="J479" t="inlineStr"/>
       <c r="K479" t="inlineStr">
         <is>
-          <t>8ano</t>
+          <t>7ano</t>
         </is>
       </c>
     </row>
@@ -25541,7 +25541,7 @@
       <c r="J480" t="inlineStr"/>
       <c r="K480" t="inlineStr">
         <is>
-          <t>8ano</t>
+          <t>7ano</t>
         </is>
       </c>
     </row>
@@ -25597,7 +25597,7 @@
       <c r="J481" t="inlineStr"/>
       <c r="K481" t="inlineStr">
         <is>
-          <t>8ano</t>
+          <t>7ano</t>
         </is>
       </c>
     </row>
@@ -25652,7 +25652,7 @@
       <c r="J482" t="inlineStr"/>
       <c r="K482" t="inlineStr">
         <is>
-          <t>8ano</t>
+          <t>7ano</t>
         </is>
       </c>
     </row>
@@ -25707,7 +25707,7 @@
       <c r="J483" t="inlineStr"/>
       <c r="K483" t="inlineStr">
         <is>
-          <t>8ano</t>
+          <t>7ano</t>
         </is>
       </c>
     </row>
@@ -25767,7 +25767,7 @@
       <c r="J484" t="inlineStr"/>
       <c r="K484" t="inlineStr">
         <is>
-          <t>8ano</t>
+          <t>7ano</t>
         </is>
       </c>
     </row>
@@ -25822,7 +25822,7 @@
       <c r="J485" t="inlineStr"/>
       <c r="K485" t="inlineStr">
         <is>
-          <t>8ano</t>
+          <t>7ano</t>
         </is>
       </c>
     </row>
@@ -25878,7 +25878,7 @@
       <c r="J486" t="inlineStr"/>
       <c r="K486" t="inlineStr">
         <is>
-          <t>8ano</t>
+          <t>7ano</t>
         </is>
       </c>
     </row>
@@ -25948,7 +25948,7 @@
       <c r="J487" t="inlineStr"/>
       <c r="K487" t="inlineStr">
         <is>
-          <t>8ano</t>
+          <t>7ano</t>
         </is>
       </c>
     </row>
@@ -26018,7 +26018,7 @@
       <c r="J488" t="inlineStr"/>
       <c r="K488" t="inlineStr">
         <is>
-          <t>8ano</t>
+          <t>7ano</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       <c r="J489" t="inlineStr"/>
       <c r="K489" t="inlineStr">
         <is>
-          <t>8ano</t>
+          <t>7ano</t>
         </is>
       </c>
     </row>
@@ -26132,7 +26132,7 @@
       <c r="J490" t="inlineStr"/>
       <c r="K490" t="inlineStr">
         <is>
-          <t>8ano</t>
+          <t>7ano</t>
         </is>
       </c>
     </row>
@@ -26188,7 +26188,7 @@
       <c r="J491" t="inlineStr"/>
       <c r="K491" t="inlineStr">
         <is>
-          <t>8ano</t>
+          <t>7ano</t>
         </is>
       </c>
     </row>
@@ -26245,7 +26245,7 @@
       <c r="J492" t="inlineStr"/>
       <c r="K492" t="inlineStr">
         <is>
-          <t>8ano</t>
+          <t>7ano</t>
         </is>
       </c>
     </row>
@@ -26299,12 +26299,12 @@
       </c>
       <c r="J493" t="inlineStr">
         <is>
-          <t>8a_ph01_mat_02.png</t>
+          <t>ph01_mat_02.png</t>
         </is>
       </c>
       <c r="K493" t="inlineStr">
         <is>
-          <t>8ano</t>
+          <t>7ano</t>
         </is>
       </c>
     </row>
@@ -26362,7 +26362,7 @@
       <c r="J494" t="inlineStr"/>
       <c r="K494" t="inlineStr">
         <is>
-          <t>8ano</t>
+          <t>7ano</t>
         </is>
       </c>
     </row>
@@ -26416,7 +26416,7 @@
       <c r="J495" t="inlineStr"/>
       <c r="K495" t="inlineStr">
         <is>
-          <t>8ano</t>
+          <t>7ano</t>
         </is>
       </c>
     </row>
@@ -26481,7 +26481,7 @@
       <c r="J496" t="inlineStr"/>
       <c r="K496" t="inlineStr">
         <is>
-          <t>8ano</t>
+          <t>7ano</t>
         </is>
       </c>
     </row>
@@ -26534,7 +26534,7 @@
       <c r="J497" t="inlineStr"/>
       <c r="K497" t="inlineStr">
         <is>
-          <t>8ano</t>
+          <t>7ano</t>
         </is>
       </c>
     </row>
@@ -26587,7 +26587,7 @@
       <c r="J498" t="inlineStr"/>
       <c r="K498" t="inlineStr">
         <is>
-          <t>8ano</t>
+          <t>7ano</t>
         </is>
       </c>
     </row>
@@ -26642,7 +26642,7 @@
       <c r="J499" t="inlineStr"/>
       <c r="K499" t="inlineStr">
         <is>
-          <t>8ano</t>
+          <t>7ano</t>
         </is>
       </c>
     </row>
@@ -26696,7 +26696,7 @@
       <c r="J500" t="inlineStr"/>
       <c r="K500" t="inlineStr">
         <is>
-          <t>8ano</t>
+          <t>7ano</t>
         </is>
       </c>
     </row>
@@ -26749,7 +26749,7 @@
       <c r="J501" t="inlineStr"/>
       <c r="K501" t="inlineStr">
         <is>
-          <t>8ano</t>
+          <t>7ano</t>
         </is>
       </c>
     </row>

--- a/questoes.xlsx
+++ b/questoes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K501"/>
+  <dimension ref="A1:K492"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23928,38 +23928,38 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Os fungos são organismos que podem ser unicelulares ou pluricelulares. Eles desempenham papéis importantes nos ecossistemas, como decompositores, e podem ser utilizados na produção de alimentos e medicamentos. Além disso, alguns fungos são patogênicos e podem causar doenças em plantas, animais e seres humanos.
-Qual das seguintes características é verdadeira para todos os fungos?</t>
+          <t>As fases da Lua são causadas pela posição relativa do Sol, da Terra e da Lua. Dependendo de como a luz solar incide sobre a Lua e de como a vemos da Terra, observamos diferentes fases.
+Qual fase da Lua ocorre quando a Lua está entre a Terra e o Sol?</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>São autotróficos.</t>
+          <t>Lua Cheia</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>São procariontes.</t>
+          <t>Lua Nova</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>São eucariontes.</t>
+          <t>Quarto Crescente</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>São fotossintetizantes.</t>
+          <t>Quarto Minguante</t>
         </is>
       </c>
       <c r="F452" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>Os fungos são organismos eucariontes, ou seja, possuem células com núcleo delimitado por membrana. Eles podem ser unicelulares ou pluricelulares, mas não são autotróficos nem procariontes.</t>
+          <t>A Lua Nova ocorre quando a Lua está entre a Terra e o Sol, fazendo com que a face iluminada da Lua fique voltada para o Sol e a face escura fique voltada para a Terra.</t>
         </is>
       </c>
       <c r="H452" t="inlineStr">
@@ -23975,45 +23975,46 @@
       <c r="J452" t="inlineStr"/>
       <c r="K452" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>As bactérias são organismos unicelulares e procariontes, presentes em diversos ambientes, como solo, água e até no corpo humano. Elas desempenham papéis fundamentais na natureza.
-Uma das principais funções ecológicas das bactérias decompositoras nos ecossistemas é a de</t>
+          <t>Os eclipses lunares ocorrem cerca de duas vezes por ano, uma vez que a órbita da Lua ao redor da Terra é inclinada em relação ao plano da órbita da Terra ao redor do Sol. Quando isso acontece, nosso planeta serve como anteparo para a luz solar, que deixa de iluminar a Lua.
+CHERMAN, Alexandre. Disponível em: https://cienciahoje.periodicos.capes.gov.br/storage/acervo/ch/ch_248.pdf#page=05. Acesso em: 17 Out 2024.(Adaptado)
+O fenômeno de eclipse lunar ocorre apenas em</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>transformar dióxido de carbono em substâncias orgânicas.</t>
+          <t>Lua nova.</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>transformar luz solar em energia química.</t>
+          <t>Lua cheia.</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>transformar matéria orgânica em substâncias inorgânicas.</t>
+          <t>Lua negra.</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>transformar oxigênio em gás carbônico.</t>
+          <t>Lua crescente.</t>
         </is>
       </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>As bactérias decompositoras têm a função crucial de transformar matéria orgânica, como restos de plantas e animais mortos, em substâncias inorgânicas, como água, dióxido de carbono e sais minerais. Esse processo é essencial para a reciclagem de nutrientes nos ecossistemas, permitindo que esses nutrientes sejam reutilizados por plantas e outros organismos autotróficos.</t>
+          <t>Os eclipses lunares só podem ocorrer durante a fase de Lua Cheia, quando a Terra se posiciona entre o Sol e a Lua, bloqueando a luz solar que normalmente seria refletida pela Lua. As outras fases lunares não permitem essa configuração geométrica necessária para um eclipse lunar.</t>
         </is>
       </c>
       <c r="H453" t="inlineStr">
@@ -24029,45 +24030,48 @@
       <c r="J453" t="inlineStr"/>
       <c r="K453" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>Os vírus são partículas acelulares constituídas por material genético (DNA ou RNA) envolto por uma cápsula proteica chamada capsídeo. Alguns vírus também possuem um envelope lipídico. No entanto para que possam sobreviver precisam de uma condição específica.
-Essa condição é a presença de um(a)</t>
+          <t>Leia o texto a seguir.
+De onde vem o brilho da Lua
+Ao contrário do Sol, que produz seu próprio brilho, a Lua não o faz. O brilho dela e o fato de o satélite natural poder ser visto da Terra devem-se à luz do Sol, que a ilumina e produz seu reflexo tanto de dia quanto de noite.
+Disponível em: https://www.nationalgeographicbrasil.com/espaco/2023/08/por-que-a-lua-pode-ser-vista-durante-o-dia. Acesso em: 8 out. 2024. (Adaptado).
+De acordo com o texto, a luz que observamos na Lua vem do Sol. Considerando esse fato, qual das afirmações a seguir está correta sobre a Lua cheia e a Lua nova?</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>ambiente com luz solar.</t>
+          <t>Na Lua cheia, a face iluminada é totalmente visível da Terra, enquanto na Lua nova não vemos a Lua porque a face iluminada está voltada para o Sol.</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>célula hospedeira.</t>
+          <t>Na Lua nova, a face iluminada é totalmente visível da Terra, enquanto na Lua cheia não vemos a Lua porque a face iluminada está voltada para o Sol.</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>fonte de energia externa.</t>
+          <t>A Lua cheia é o momento em que a Lua está mais próxima da Terra, enquanto a Lua nova é o momento em que a Lua está mais distante.</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>temperatura ideal para crescimento.</t>
+          <t>Tanto a Lua cheia quanto a Lua nova podem ser vistas da Terra durante o dia.</t>
         </is>
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>Os vírus são considerados parasitas intracelulares obrigatórios porque necessitam de uma célula hospedeira para se replicar. Fora das células hospedeiras, eles são inertes e incapazes de realizar qualquer atividade vital. Portanto, a presença de uma célula hospedeira é uma condição essencial para a sobrevivência e replicação dos vírus.</t>
+          <t>Na fase da Lua cheia, a Terra está posicionada entre a Lua e o Sol, permitindo que toda a face iluminada da Lua seja refletida e vista da Terra. Por outro lado, na Lua nova, a face da Lua que recebe luz solar está voltada para o Sol, o que resulta na ausência de visibilidade da Lua no céu.</t>
         </is>
       </c>
       <c r="H454" t="inlineStr">
@@ -24083,45 +24087,45 @@
       <c r="J454" t="inlineStr"/>
       <c r="K454" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>As algas são organismos eucariontes, autotróficos e fotossintetizantes. Elas podem ser unicelulares ou pluricelulares e são encontradas em ambientes aquáticos e terrestres úmidos. 
-Qual é a principal função ecológica das algas nos ecossistemas aquáticos?</t>
+          <t>Os solstícios marcam momentos importantes no calendário e têm relação direta com a incidência de luz solar em diferentes partes do planeta.
+Considerando isso, qual das afirmativas a seguir está correta sobre os solstícios de verão e inverno?</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Decomposição de matéria orgânica.</t>
+          <t>O solstício de verão ocorre quando o Sol está mais distante da Terra, resultando em dias mais curtos e noites mais longas.</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Produção de oxigênio.</t>
+          <t>O solstício de inverno ocorre quando o Sol atinge a sua maior posição no céu, proporcionando dias mais longos e temperaturas mais altas.</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>Fixação de nitrogênio.</t>
+          <t>Durante o solstício de verão, o Hemisfério Norte recebe a maior quantidade de luz solar, enquanto o Hemisfério Sul experimenta o solstício de inverno.</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>Parasitismo de outros organismos.</t>
+          <t>O solstício de inverno é marcado pela maior quantidade de luz solar recebida pelo Hemisfério Norte, enquanto o Hemisfério Sul vive o solstício de verão.</t>
         </is>
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>A principal função ecológica das algas nos ecossistemas aquáticos é a produção de oxigênio através da fotossíntese, além de servir como base das cadeias alimentares.</t>
+          <t>Durante o solstício de verão no Hemisfério Norte, este hemisfério está inclinado em direção ao Sol, resultando em um aumento da incidência de luz solar e, consequentemente, dias mais longos e temperaturas mais altas. Em contrapartida, o Hemisfério Sul, que está inclinado para longe do Sol, experimenta o solstício de inverno, resultando em dias mais curtos e temperaturas mais baixas.</t>
         </is>
       </c>
       <c r="H455" t="inlineStr">
@@ -24137,45 +24141,46 @@
       <c r="J455" t="inlineStr"/>
       <c r="K455" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>Os protozoários são organismos unicelulares e heterotróficos que podem ser encontrados em diversos tipos de ambiente, isolados ou em colônias. Podem ter vida livre ou associar-se a outros seres vivos. Algumas espécies são parasitas e podem causar doenças no ser humano, como a malária e a doença de Chagas.
-Quais dos seguintes organismos são exemplos de protozoários?</t>
+          <t>Observe a tabela que mostra os horários em algumas regiões do mundo.
+Perceba que enquanto no Brasil é dia, no Japão (Tóquio), já é noite.
+Assinale a alternativa que contém o fenômeno que explica a diferença de horários entre o Brasil e o Japão.</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Amebas e paramécios.</t>
+          <t>O movimento de translação do planeta Terra.</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Amebas e cogumelos.</t>
+          <t>A distância entre o planeta Terra e o Sol.</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>Bactérias e cianobactérias.</t>
+          <t>O movimento de rotação do planeta Terra.</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>Paramécios e bactérias.</t>
+          <t>O movimento de translação do Sol ao redor da Terra.</t>
         </is>
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>São exemplos de protozoários: as amebas e os paramécios. Eles podem ser encontrados em diversos ambientes e algumas espécies são parasitas que causam doenças em seres humanos. Fungos, algas, cianobactérias, plantas e animais não são classificados como protozoários.</t>
+          <t>A rotação é o movimento em que o planeta Terra gira em torno do seu próprio eixo. Devido a esse movimento, há variação entre os dias e as noites. Como o Brasil e o Japão estão em regiões opostas do globo terrestre, enquanto num país é dia, no outro será noite.</t>
         </is>
       </c>
       <c r="H456" t="inlineStr">
@@ -24188,38 +24193,42 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="J456" t="inlineStr"/>
+      <c r="J456" t="inlineStr">
+        <is>
+          <t>8a_ph01_cie_06.png</t>
+        </is>
+      </c>
       <c r="K456" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>Para um organismo ser considerado vivo, algumas características devem estar presentes. Observe a imagem a seguir.
-Assinale a alternativa que apresenta características do ser vivo apresentado na imagem, que o diferem de um ser não vivo.</t>
+          <t>A distribuição de energia solar pelas diferentes regiões do planeta Terra depende dos movimentos de rotação, da inclinação do eixo de rotação e do movimento de translação da Terra.
+Sobre a incidência de luz solar na superfície do planeta, é correto afirmar que</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Nada e nasce.</t>
+          <t>a quantidade de luz do Sol que chega até o planeta Terra é a mesma em todos os pontos de sua superfície.</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Possui casco duro e se alimenta.</t>
+          <t>nos polos Norte e Sul, as quatro estações do ano são bem definidas porque a incidência de luz solar quase não varia ao longo do ano.</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>Pode se reproduzir e morrer.</t>
+          <t>no outono ou na primavera, os hemisférios Sul e Norte são iluminados da mesma maneira pelo Sol.</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>Possui metabolismo e possui nadadeiras.</t>
+          <t>no solstício de verão, o dia é mais curto e a noite é mais longa; no solstício de inverno, a noite é mais curta e o dia é mais longo.</t>
         </is>
       </c>
       <c r="F457" t="inlineStr">
@@ -24229,7 +24238,7 @@
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>A tartaruga é caracterizada como um ser vivo, pois possui metabolismo, se alimenta, nasce, pode se reproduzir e morre.</t>
+          <t>A quantidade de luz do Sol que ilumina a Terra não é a mesma em todas as regiões do planeta, devido à sua forma esférica e à inclinação do seu eixo de rotação. Nos polos, geralmente é possível distinguir apenas o verão e o inverno. Cada estação tem duração de 6 meses. No solstício de verão, o dia é mais longo que a noite, enquanto no solstício de inverno, a noite é mais longa que o dia.</t>
         </is>
       </c>
       <c r="H457" t="inlineStr">
@@ -24242,52 +24251,55 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="J457" t="inlineStr">
-        <is>
-          <t>ph01_cie_06.png</t>
-        </is>
-      </c>
+      <c r="J457" t="inlineStr"/>
       <c r="K457" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Observe a imagem a seguir.
-Relacione o organismo autótrofo e o heterótrofo com os processos de fotossíntese e respiração celular, marcando a alternativa correta.</t>
+          <t>“Se olharmos para o céu numa noite clara sem lua, os objetos mais brilhantes que vemos são os planetas Vênus, Marte, Júpiter e Saturno. Também percebemos um número muito grande de estrelas que são exatamente iguais ao nosso Sol, embora muito distantes de nós. Algumas dessas estrelas parecem, de fato, mudar sutilmente suas posições com relação umas às outras, à medida que a Terra gira em torno do Sol.”
+(HAWKING, S. W. Uma breve história do tempo: do Big Bang aos Buracos Negros. Trad. de Maria Helena Torres. Rio de Janeiro: Rocco, 1988. p. 61.)
+A respeito do assunto, considere as seguintes afirmativas:
+I. O movimento da Terra ao qual o autor se refere é chamado de translação.
+II. O movimento da Terra em torno do Sol é responsável pela sucessão dos dias e das noites.
+III. A distribuição desigual das temperaturas, determinante da vida em distintos lugares da superfície terrestre, está relacionada, entre outros fatores, à forma esférica da Terra e ao ângulo de incidência dos raios solares.
+Assinale a alternativa correta.</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>A árvore é autotrófica e faz fotossíntese.</t>
+          <t>Somente a afirmativa I é verdadeira.</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>O javali é heterotrófico e faz fotossíntese.</t>
+          <t>Somente a afirmativa II é verdadeira.</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>O javali é autotrófico e não produz seu próprio alimento.</t>
+          <t>Somente as afirmativas II e III são verdadeiras.</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>A árvore é autotrófica e não produz seu próprio alimento.</t>
+          <t>Somente as afirmativas I e III são verdadeiras.</t>
         </is>
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>A árvore é autótrofa e produz seu próprio alimento por meio da fotossíntese; enquanto o javali é heterótrofo, pois depende de outros seres vivos para se alimentar e produzir energia por meio da respiração celular.</t>
+          <t>I. Correta.
+II. Incorreta. O movimento responsável pela sucessão dos dias e das noites é o de rotação.
+III. Correta.</t>
         </is>
       </c>
       <c r="H458" t="inlineStr">
@@ -24300,41 +24312,38 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="J458" t="inlineStr">
-        <is>
-          <t>ph01_cie_07.png</t>
-        </is>
-      </c>
+      <c r="J458" t="inlineStr"/>
       <c r="K458" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>Um pesquisador estava analisando uma lâmina ao microscópio e observou que as células eram muito simples e não possuíam núcleo individualizado. Com base nessas informações, marque a alternativa com o tipo de célula que estava presente na lâmina.</t>
+          <t>A tabela abaixo mostra a previsão de temperatura nas cidades de Toronto, no Canadá, e Rio de Janeiro, no Brasil, em dezembro de 2018.
+Assinale a alternativa que explica por que pode ocorrer de, no mesmo período, o Brasil apresentar temperaturas altas e o Canadá temperaturas baixas.</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Procariontes.</t>
+          <t>Isso ocorre devido ao movimento de translação e à inclinação do eixo de rotação da Terra.</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Eucariontes.</t>
+          <t>Isso ocorre devido ao movimento de rotação da Terra que faz com que a luz do Sol incida sobre o planeta de forma irregular.</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>Pluricelular.</t>
+          <t>Isso ocorre porque é inverno no Canadá e verão no Brasil, o que depende de a Terra estar mais longe ou mais perto do Sol.</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>Acelular.</t>
+          <t>Isso ocorre devido à diferença de estações entre as duas cidades determinadas pelas fases da Lua.</t>
         </is>
       </c>
       <c r="F459" t="inlineStr">
@@ -24344,7 +24353,7 @@
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>Na lâmina estavam presentes células procariontes, pois essas não possuem núcleo individualizado.</t>
+          <t>A diferença de estações nos hemisférios norte e sul está associada ao movimento de translação da Terra e à inclinação do eixo de rotação do planeta que, juntos, fazem com que a incidência de luz solar sobre os hemisférios seja diferente em algumas épocas do ano.</t>
         </is>
       </c>
       <c r="H459" t="inlineStr">
@@ -24357,50 +24366,51 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="J459" t="inlineStr"/>
+      <c r="J459" t="inlineStr">
+        <is>
+          <t>8a_ph01_cie_09.png</t>
+        </is>
+      </c>
       <c r="K459" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>Leia o texto a seguir e responda a questão.
-Seres chamados "piratas" biológicos invadem as células, saqueiam seus nutrientes e utilizam as reações químicas das mesmas para se reproduzir. Logo em seguida, os descendentes dos invasores transmitem-se a outras células, provocando danos devastadores. A estes danos, dá-se o nome de virose, como a gripe, herpes, dengue, AIDS, etc.
-(SCOTT, Andrew. Piratas da Célula. Adaptado.)
-Certos agentes infecciosos são formados apenas por material genético protegido por uma cápsula de proteína. Estes seres só conseguem se reproduzir quando invadem uma célula e utilizam suas estruturas, terminando por destruí-la. Estes agentes são</t>
+          <t>O planeta Terra realiza dois principais movimentos, que possuem um efeito direto mais notório em nossas vidas. O movimento caracterizado por ser um movimento giratório em torno de seu próprio eixo é a:</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>bactérias.</t>
+          <t>translação.</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>fungos.</t>
+          <t>rotação.</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>protozoários.</t>
+          <t>revolução.</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>vírus.</t>
+          <t>inclinação.</t>
         </is>
       </c>
       <c r="F460" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>Os vírus são parasitas intracelulares e, por isso, precisam invadir células para se reproduzir e são estruturas muito simples, formadas de cápsula e material genético.</t>
+          <t>O movimento que a Terra realiza em torno de seu próprio eixo se chama Rotação, e o movimento que a Terra realiza em torno do Sol se chama Translação.</t>
         </is>
       </c>
       <c r="H460" t="inlineStr">
@@ -24416,44 +24426,46 @@
       <c r="J460" t="inlineStr"/>
       <c r="K460" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>Os vírus são seres acelulares e possuem uma estrutura muito simples, eles são constituídos de:</t>
+          <t>As regionalizações representam retratos dos processos sociais e econômicos das épocas em que foram elaboradas. Elas refletem as dinâmicas específicas de cada período histórico, capturando as características e as relações sociais, econômicas e culturais que definem diferentes regiões. 
+Disponível em: https://sme.goiania.go.gov.br/conexaoescola/ensino_fundamental/geografia-o-conceito-de-regionalizacao-e-as-regionalizacoes-do-brasil/. Acesso em 18 de set de 2024.
+Qual é um dos critérios físicos utilizados para a regionalização do mundo?</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>membrana, citoplasma e núcleo.</t>
+          <t>Clima.</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>capsídeo e material genético.</t>
+          <t>Altitude.</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>célula e Material genético.</t>
+          <t>População.</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>capsídeo e núcleo.</t>
+          <t>Fuso horário.</t>
         </is>
       </c>
       <c r="F461" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>Os vírus são constituídos de capsídeo e material genético (DNA ou RNA).</t>
+          <t>O clima é um critério fundamental na regionalização do mundo, pois ele afeta diretamente as condições de vida, a agricultura e as atividades econômicas das regiões.</t>
         </is>
       </c>
       <c r="H461" t="inlineStr">
@@ -24463,50 +24475,53 @@
       </c>
       <c r="I461" t="inlineStr">
         <is>
-          <t>Ciências</t>
+          <t>Geografia</t>
         </is>
       </c>
       <c r="J461" t="inlineStr"/>
       <c r="K461" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>O Brasil é um dos maiores países em extensão territorial no mundo. Sabendo disso, qual das alternativas a seguir melhor explica como as características socioculturais estão distribuídas no território brasileiro?</t>
+          <t>A filosofia oriental é um campo pouco conhecido no Ocidente. No entanto, nas últimas décadas houve um boom no estudo dessas correntes filosóficas, dentro das quais existem diferentes teorias e costumes.
+De fato, poder-se-ia falar de filosofias orientais, no plural, pois há uma grande riqueza de conceitos de diversos países, com modos de vida particulares e pensamentos diversos.
+Disponível em: https://amenteemaravilhosa.com.br/uma-introducao-a-filosofia-oriental/. Acesso em 21 de set de 2024. 
+As principais bases filosóficas da civilização oriental são:</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>O território brasileiro é culturalmente uniforme, com as mesmas tradições e costumes em todas as regiões.</t>
+          <t>Taoísmo, confucionismo e budismo.</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Cada região brasileira possui paisagens e culturas distintas, influenciadas por fatores históricos, geográficos e climáticos.</t>
+          <t>Shintoísmo, hinduísmo e confucionismo.</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>O Brasil possui poucas variações culturais entre suas regiões, com pequenas diferenças na culinária e no idioma.</t>
+          <t>Budismo, cristianismo e taoísmo.</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>A diversidade sociocultural do Brasil não está ligada ao território, mas sim à economia global.</t>
+          <t>Hinduísmo, jainismo e taoísmo.</t>
         </is>
       </c>
       <c r="F462" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>O Brasil, devido à sua vasta extensão territorial, apresenta uma grande diversidade de paisagens e culturas. Cada região do país possui características únicas que são influenciadas por uma combinação de fatores históricos, geográficos e climáticos. Por exemplo, o Nordeste brasileiro tem tradições culturais e paisagens diferentes das encontradas no Sul do país. Essa diversidade é um reflexo da complexa formação histórica do Brasil e das variações ambientais que moldam os modos de vida das populações em diferentes partes do território.</t>
+          <t>As principais bases da filosofia oriental são o taoísmo, o confucionismo e o budismo. O taoísmo prega a harmonia com a natureza e o "Tao" (Caminho). O confucionismo foca na ética, nas relações sociais e na educação para construir uma sociedade justa. O budismo busca o desapego dos desejos materiais e a iluminação espiritual. Essas três correntes influenciam profundamente a cultura e o pensamento no Leste Asiático.</t>
         </is>
       </c>
       <c r="H462" t="inlineStr">
@@ -24522,45 +24537,46 @@
       <c r="J462" t="inlineStr"/>
       <c r="K462" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>O território brasileiro é organizado politicamente em três níveis de governo: federal, estadual e municipal. Cada um desses níveis possui competências específicas e atua de acordo com as necessidades da população em seu respectivo âmbito. A noção de território é fundamental para entender como as políticas públicas são implementadas e como o poder é distribuído entre as diferentes esferas de governo.
-Como a noção de território influencia a organização política do espaço brasileiro?</t>
+          <t>O Islã, uma das maiores religiões monoteístas do mundo, tem a Arábia Saudita como seu coração. Os seguidores do Islã, chamados de muçulmanos, acreditam em Deus – em árabe, Alá – e que Muhammad é Seu profeta (...)  Historicamente, a Arábia Saudita ocupou um lugar especial no mundo islâmico, pois é em direção a Meca e ao santuário mais sagrado do Islã, a Ka’abah, localizada na Mesquita Sagrada de lá, que os muçulmanos em todo o mundo se voltam devotamente em oração cinco vezes por dia .
+Disponível em: https://www.cicibas.org.br/islamismo/. Acesso em 21 de set de 2024.
+Quais são algumas características principais do Islamismo?</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>O território brasileiro é administrado exclusivamente pelo governo federal, sem a participação dos estados e municípios.</t>
+          <t>O Islã é uma religião politeísta que reverencia vários deuses.</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>A organização política do território brasileiro é centralizada, com todas as decisões sendo tomadas pela capital federal.</t>
+          <t>Os muçulmanos acreditam no Deus Alá, e que Muhammad é seu profeta.</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>O território brasileiro é dividido em diferentes níveis de governo, cada um com competências específicas para atender às necessidades locais.</t>
+          <t>A oração muçulmana ocorre apenas uma vez por semana, aos domingos.</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>A noção de território não tem impacto na organização política do Brasil, já que todas as regiões seguem as mesmas políticas públicas.</t>
+          <t>Os seguidores do Islã se voltam para Jerusalém durante suas orações diárias.</t>
         </is>
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t>A noção de território é essencial para a organização política do Brasil, que é dividido em três níveis de governo: federal, estadual e municipal. Cada nível tem competências específicas e atua de acordo com as necessidades da população em seu respectivo âmbito. O governo federal cuida de questões nacionais, os estados tratam de assuntos regionais e os municípios lidam com questões locais. Essa divisão permite uma administração mais eficiente e adaptada às particularidades de cada região.</t>
+          <t>Os seguidores do Islã acreditam em um único Deus, chamado Alá, e que Muhammad (Maomé) é o seu profeta, característica central do islamismo.</t>
         </is>
       </c>
       <c r="H463" t="inlineStr">
@@ -24576,45 +24592,47 @@
       <c r="J463" t="inlineStr"/>
       <c r="K463" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>A cultura de um povo é refletida de várias formas no espaço geográfico que ocupa. Ela não apenas molda o ambiente, mas também é moldada pelas interações entre os indivíduos e o espaço onde vivem.
-Como a cultura de um povo pode ser percebida no espaço geográfico?</t>
+          <t>Regionalizar é um processo de divisão de um determinado espaço, levando em conta suas características comuns, a fim de considerar as diversas realidades e, por conseguinte, criar regiões distintas. Ao elaborar uma regionalização mundial, busca-se agrupar países de acordo com suas características específicas.
+As regionalizações mundiais são divisões ou agrupamentos de países e regiões do mundo com base em critérios diversos, como geográficos, culturais, econômicos, políticos e históricos. Essas regionalizações oferecem uma perspectiva analítica que facilita a compreensão das relações internacionais, das dinâmicas globais e das interações entre países.
+Disponível em: https://sme.goiania.go.gov.br/conexaoescola/eaja/geografia-diferentes-regionalizacoes-mundiais/. Acesso em 18 de set de 2024.
+Qual dos tipos de regionalização foca nas semelhanças linguísticas, religiosas e tradicionais das populações?</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Pela ausência de construções e práticas festivas.</t>
+          <t>Regionalização por continentes.</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Pelo estilo das construções, modo de vestir e práticas festivas.</t>
+          <t>Regionalização histórico-geográfica.</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>Pela uniformidade de hábitos em todas as regiões.</t>
+          <t>Regionalização por grupos culturais.</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>Pela exclusão de influências externas.</t>
+          <t>Regionalização econômica.</t>
         </is>
       </c>
       <c r="F464" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>A cultura de um povo é percebida no espaço geográfico através de várias manifestações visíveis. O estilo das construções reflete não apenas as preferências estéticas, mas também as influências históricas, climáticas e funcionais da região. O modo de vestir expressa tradições e identidade cultural, frequentemente incorporando elementos que representam a história e os valores do povo. As práticas festivas, por sua vez, revelam as crenças e os costumes da comunidade, tornando-se um meio de celebração e de reafirmação da identidade cultural. Juntas, essas expressões mostram como a cultura molda e é moldada pelo espaço geográfico.</t>
+          <t>A regionalização por grupos culturais considera as semelhanças linguísticas, religiosas e tradicionais das populações.</t>
         </is>
       </c>
       <c r="H464" t="inlineStr">
@@ -24630,45 +24648,48 @@
       <c r="J464" t="inlineStr"/>
       <c r="K464" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>O Brasil possui uma grande diversidade de recursos naturais, como minerais, água e solos cultiváveis. No entanto, a gestão desses recursos é um desafio constante.
-Um dos principais desafios relacionados à grande diversidade de recursos naturais no Brasil é a</t>
+          <t>O sistema de castas divide os hindus em quatro categorias principais: Brahmins, Kshatriyas, Vaishyas e Shudras.
+Muitos acreditam que os grupos se originaram de Brahma, o deus hindu da criação.
+No topo da ordem hierárquica estavam os brâmanes, que eram principalmente professores e intelectuais; acredita-se que eram descendentes de Brahma. Então, vieram os Kshatriyas ou os guerreiros e governantes, supostamente de seus braços. Em terceiro, os Vaishyas, ou mercadores, que foram criados a partir de suas coxas. E, por último, os Shudras, que vieram dos pés de Brahma e faziam todos os trabalhos braçais.
+Disponível em: https://www.bbc.com/portuguese/internacional-55452675. Acesso em 18 de set de 2024.
+Qual é uma das principais características do sistema de castas indiano?</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>gestão sustentável desses recursos.</t>
+          <t>Mobilidade social entre castas.</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>necessidade de investir em tecnologias para a agricultura</t>
+          <t>Igualdade de oportunidades.</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>ausência de solos cultiváveis</t>
+          <t>Ausência de discriminação.</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>competição entre o uso agrícola e a preservação ambiental.</t>
+          <t>Hierarquia rígida e imutável.</t>
         </is>
       </c>
       <c r="F465" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>Um dos principais desafios relacionados à grande diversidade de recursos naturais no Brasil é a gestão sustentável desses recursos para garantir o desenvolvimento do país.</t>
+          <t>O sistema de castas indiano é caracterizado por uma hierarquia rígida e imutável, onde a posição social é determinada pelo nascimento e não pode ser alterada ao longo da vida.</t>
         </is>
       </c>
       <c r="H465" t="inlineStr">
@@ -24684,35 +24705,36 @@
       <c r="J465" t="inlineStr"/>
       <c r="K465" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>No Brasil, o sistema de governo é baseado na divisão dos Três Poderes, idealizada por Montesquieu no século XVIII, para garantir o equilíbrio e evitar abusos de poder. Esses poderes são independentes e harmônicos entre si, sendo responsáveis por diferentes funções no Estado. Essa estrutura busca assegurar a democracia e o funcionamento equilibrado das instituições.
-No sistema democrático brasileiro, os três poderes desempenham papéis fundamentais na organização do Estado. Qual alternativa descreve corretamente a função de cada um dos três poderes?</t>
+          <t>Os curdos formam uma população estimada entre 25 milhões e 35 milhões e habitam uma região montanhosa que se espalha pelos territórios de cinco países: Turquia, Iraque, Síria, Irã e Armênia. Eles compõem o quarto maior grupo étnico do Oriente Médio [...]
+Disponível em: &lt;https://www.bbc.com/portuguese/internacional-50012988&gt;. Acesso em: 04 dez. 2019.
+Dentre as categorias possíveis na geografia, qual pode ser aplicada aos curdos?</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>O Poder Executivo cria leis, o Poder Legislativo julga, e o Poder Judiciário executa as políticas públicas.</t>
+          <t>Governo.</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>O Poder Legislativo executa as leis, o Poder Executivo as interpreta, e o Poder Judiciário aprova as leis .</t>
+          <t>Estado.</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>O Poder Legislativo cria e aprova leis, o Poder Judiciário julga e aplica as leis, e o Poder Executivo administra e executa as políticas públicas.</t>
+          <t>Nação.</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>O Poder Executivo julga casos de violação de leis, o Poder Legislativo executa as políticas públicas, e o Poder Judiciário cria as leis.</t>
+          <t>Território.</t>
         </is>
       </c>
       <c r="F466" t="inlineStr">
@@ -24722,7 +24744,7 @@
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>A divisão dos três poderes no Brasil é clara: o Poder Legislativo tem a função de criar e aprovar leis; o Poder Judiciário julga e aplica essas leis, assegurando que sejam cumpridas; e o Poder Executivo administra o país e executa as políticas públicas.</t>
+          <t>Os curdos são a maior nação do mundo sem território. O conceito de nação corresponde a união de práticas, sociais, culturais e históricas que identificam um grupo.</t>
         </is>
       </c>
       <c r="H466" t="inlineStr">
@@ -24738,42 +24760,34 @@
       <c r="J466" t="inlineStr"/>
       <c r="K466" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>A Rússia é o país de maior área territorial do mundo. Ele ocupa quase metade da Europa e cerca de um terço da Ásia. São mais de 17 milhões de quilômetros quadrados! O idioma oficial é o russo, a moeda é o rublo e a capital é Moscou
-Disponível em:&lt;http://www.ebc.com.br/infantil/voce-sabia/2015/07/qual-e-o-maior-pais-do-mundo&gt;. Acesso em: 04 dez.2019.
-O Censo dos Estados Unidos estima que a população mundial no dia 1º de janeiro de 2018 seja de 7.444.443.881 habitantes.
-Veja a lista completa, feita pelo Censo dos Estados Unidos:
-1. China: 1.384.688.986 habitantes
-2. Índia: 1.296.834.042 habitantes
-3. Estados Unidos: 329.256.465 habitantes
-Disponível em:&lt;https://epocanegocios.globo.com/Mundo/noticia/2017/12/estes-serao-os-paises-mais-populosos-de-2018.html&gt;. Acesso em: 04 dez.2019.
-Utilizando o critério do primeiro texto, os países que ocupam posição superior ao Brasil são</t>
+          <t>Os elementos de culinária, música, expressão popular fazem parte da</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Canadá, Índia, México e China.</t>
+          <t>vivência cotidiana</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Rússia, China, Índia e Austrália.</t>
+          <t>multiculturalismo</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>Rússia, Canadá, China e Estados Unidos.</t>
+          <t>cultura</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>Estados Unidos, Canadá, África do Sul e Indonésia.</t>
+          <t>movimentos sociais</t>
         </is>
       </c>
       <c r="F467" t="inlineStr">
@@ -24783,7 +24797,7 @@
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>Os países que possuem maior área territorial que o Brasil, em ordem decrescente, são Rússia, Canadá, China e EUA.</t>
+          <t>A cultura popular do Brasil conta com a feijoada, com o samba, capoeira, carnaval como elementos constitutivos que aproximam a sociedade brasileira.</t>
         </is>
       </c>
       <c r="H467" t="inlineStr">
@@ -24796,47 +24810,54 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="J467" t="inlineStr"/>
+      <c r="J467" t="inlineStr">
+        <is>
+          <t>8a_ph01_geo_08.png</t>
+        </is>
+      </c>
       <c r="K467" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>Observando o mapa, os dois países da América do Sul que não se limitam com o Brasil são</t>
+          <t>"Houve uma crise institucional. Carlos 1º procurava tornar-se mais forte, ao estilo dos monarcas absolutistas de França e Espanha, mas se encontrava numa situação de fragilidade: não tinha dinheiro suficiente e dependia dos recursos de proprietários de terras, cuja renda não estava aumentando. Além disso, a inflação subia rapidamente porque havia uma burocracia cada vez maior para sustentar", explica Worden.
+"A Coroa dependia do Parlamento para arrecadar fundos e, quando o Parlamento não concordou, o monarca tentou aumentar os impostos sem o Parlamento, o que levou a uma crise política.".
+BERMÚDEZ. Ángel. Jubileu da rainha Elizabeth 2ª: a década em que o Reino Unido foi uma república em vez de monarquia. Disponível em: https://www.bbc.com/portuguese/internacional-61691288. Acesso em:. 17 out. 2024
+No século XVII, a Inglaterra passou por mudanças significativas em sua estrutura política e social, que fortaleceram as ideias de representação política e direitos dos cidadãos.  De acordo com o texto qual fator foi crucial para a emergência de um desejo por reformas políticas na Inglaterra do século XVII?</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Uruguai e Peru.</t>
+          <t>O controle absoluto da monarquia sobre o Parlamento.</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Chile e Equador.</t>
+          <t>O crescimento do comércio externo em detrimento do interno.</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>Argentina e Chile.</t>
+          <t>A tensão entre a Monarquia e o Parlamento.</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>Bolívia e Venezuela.</t>
+          <t>A influência das ideias absolutistas no governo.</t>
         </is>
       </c>
       <c r="F468" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>O Brasil divide fronteiras com a maior parte dos países da América do Sul; as exceções são Chile e Equador.</t>
+          <t>A tensão e as disputas entre os interesses da Monarquia e dos parlamentares foram cruciais para a emergência de um desejo por reformas políticas, refletindo a luta por representação e direitos na sociedade contra a tirania real.</t>
         </is>
       </c>
       <c r="H468" t="inlineStr">
@@ -24846,46 +24867,41 @@
       </c>
       <c r="I468" t="inlineStr">
         <is>
-          <t>Geografia</t>
-        </is>
-      </c>
-      <c r="J468" t="inlineStr">
-        <is>
-          <t>ph01_geo_07.jpg</t>
-        </is>
-      </c>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="J468" t="inlineStr"/>
       <c r="K468" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>Observe a representação abaixo: 
-Disponível em: https://escolakids.uol.com.br/upload/conteudo_legenda/eadce3825839373174aaefd6f7e89b52.png. Acesso em: 01 fev. 2019
-O ponto extremo mais ao Sul do Brasil é o (a)</t>
+          <t>A Revolução Gloriosa, ocorrida em 1688, foi um evento decisivo na história da Inglaterra. Este movimento resultou na deposição do rei Jaime II e na ascensão de Guilherme de Orange ao trono. Os conflitos entre o governo absolutista de Jaime II e a crescente oposição parlamentar resultaram em um novo modelo de governo que limitou os poderes da monarquia. 
+Qual foi a principal consequência da Revolução Gloriosa de 1688?</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Nascente do Rio Moa.</t>
+          <t>A independência das colônias americanas.</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Monte Caburaí.</t>
+          <t>A instituição da monarquia absoluta.</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>Ponta do Seixas.</t>
+          <t>A ascensão do absolutismo na Europa.</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>Arroio Chuí.</t>
+          <t>O fortalecimento do Parlamento.</t>
         </is>
       </c>
       <c r="F469" t="inlineStr">
@@ -24895,7 +24911,7 @@
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>O ponto mais ao sul do Brasil é o Arroio Chuí, no Rio Grande do Sul.</t>
+          <t>O fortalecimento do Parlamento foi a principal consequência da Revolução Gloriosa, por meio do estabelecimento de um governo que limitava os poderes da monarquia.</t>
         </is>
       </c>
       <c r="H469" t="inlineStr">
@@ -24905,50 +24921,42 @@
       </c>
       <c r="I469" t="inlineStr">
         <is>
-          <t>Geografia</t>
-        </is>
-      </c>
-      <c r="J469" t="inlineStr">
-        <is>
-          <t>ph01_geo_08.png</t>
-        </is>
-      </c>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="J469" t="inlineStr"/>
       <c r="K469" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Disponível em:&lt;http://www.educandusweb.com.br/ewbco/portal/upload/xinha/UNICENTRO20122FGEOG01.PNG&gt;. Acesso em: 04 dez.2019.
-Após observar o planisfério, considere as afirmações:
-I -  O Brasil situa-se a oeste do Meridiano de Greenwich.
-II -  O Brasil é cortado ao norte pela Linha do Equador.
-III -  Ao sul, é cortado pelo Trópico de Câncer.
-IV -  Ao sul, é cortado pelo Trópico de Capricórnio, apresentando grande parte do seu território na Zona Intertropical, entre os Trópicos de Câncer e de Capricórnio.
-Assinale a alternativa que apresenta apenas a(s) afirmação(ões) verdadeira(s).</t>
+          <t>A Revolução Industrial começou no Reino Unido na segunda metade do século 18 e substituiu a produção de manufaturas por produção de máquinas, alimentadas, principalmente, pela queima do carvão. Em poucas décadas, a revolução se espalhou para outros países europeus e para os Estados Unidos. 
+Emissões da Revolução Industrial ficaram marcadas no gelo do Himalaia. Disponível em: https://super.abril.com.br/historia/emissoes-da-revolucao-industrial-ficaram-marcadas-no-gelo-do-himalaia. Acesso em: 17 out. 2024
+A Inglaterra se tornou pioneira na Revolução Industrial devido à(ao)</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Apenas I é verdadeira.</t>
+          <t>falta de estabilidade política.</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Apenas III e IV são verdadeiras.</t>
+          <t>ausência de inovações tecnológicas.</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>Apenas I, II e IV são verdadeiras.</t>
+          <t>disponibilidade de recursos naturais.</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>Apenas I, II, e III são verdadeiras.</t>
+          <t>diminuição da demanda por produtos.</t>
         </is>
       </c>
       <c r="F470" t="inlineStr">
@@ -24958,8 +24966,7 @@
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>Letra C.
-O Brasil fica localizado no hemisfério ocidental, ou seja a oeste do meridiano de Greenwich. A maior parte do seu território é localizado no hemisfério Sul, na faixa intertropical, com uma pequena parte cortada pela linha do Equador, no norte do país.</t>
+          <t>A Inglaterra foi pioneira na Revolução Industrial, em grande parte, devido à sua abundante disponibilidade de recursos naturais, como carvão e minério de ferro, que eram essenciais para o desenvolvimento de tecnologias e para a operação das máquinas industriais. Esses recursos facilitaram a transição para uma economia baseada na indústria, além de impulsionar o desenvolvimento de novas tecnologias.</t>
         </is>
       </c>
       <c r="H470" t="inlineStr">
@@ -24969,57 +24976,51 @@
       </c>
       <c r="I470" t="inlineStr">
         <is>
-          <t>Geografia</t>
-        </is>
-      </c>
-      <c r="J470" t="inlineStr">
-        <is>
-          <t>ph01_geo_09.jpg</t>
-        </is>
-      </c>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="J470" t="inlineStr"/>
       <c r="K470" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>Juridicamente, território nacional é a área que compreende todo o espaço, terrestre, fluvial, marítimo (12 milhas) e aéreo (coluna atmosférica), onde o Estado brasileiro é soberano. Mas, esse território poderá ser estendido quando se tratar de embarcações ou aeronaves públicas ou a serviço do governo brasileiro onde quer que se encontre e as embarcações ou aeronaves estrangeiras privadas quando em território nacional.
-[...]
-Disponível em:&lt;https://lfg.jusbrasil.com.br/noticias/2086332/o-que-se-entende-por-territorio-nacional-lais-mamede-dias-leme&gt;.Acesso em&gt; 04 dez.2019.
-A partir do texto, pode-se afirmar que território nacional é</t>
+          <t>As consequências sociais da Revolução Industrial foram vastas e complexas. O deslocamento de pessoas para as cidades em busca de trabalho nas fábricas levou ao crescimento das áreas urbanas e à formação de novos bairros industriais. Essa rápida urbanização trouxe desafios como a superlotação, a falta de infraestrutura e ao mesmo tempo, provocou uma mudança na percepção dos direitos dos trabalhadores e a luta por melhores condições de vida.
+Qual foi uma das consequências sociais mais significativas da Revolução Industrial?</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>o limite fronteiriço do país.</t>
+          <t>O aumento da população rural.</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>o espaço contido dentro das fronteiras.</t>
+          <t>A formação de novas classes sociais.</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>a região natural de maior abrangência em um país.</t>
+          <t>A estagnação do crescimento urbano.</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>o espaço controlado pelas instituições políticas e militares de um país.</t>
+          <t>O fortalecimento das comunidades agrícolas.</t>
         </is>
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>O território nacional pode ser considerado o espaço controlado pelas instituições políticas e militares de um país, ou seja, uma embaixada brasileira localizada em Londres, é considerada território brasileiro.</t>
+          <t>A formação de novas classes sociais foi uma das consequências sociais mais significativas da Revolução Industrial, alterando a estrutura da sociedade com o surgimento do proletariado e a consolidação da burguesia como classe dominante.</t>
         </is>
       </c>
       <c r="H471" t="inlineStr">
@@ -25029,52 +25030,51 @@
       </c>
       <c r="I471" t="inlineStr">
         <is>
-          <t>Geografia</t>
+          <t>História</t>
         </is>
       </c>
       <c r="J471" t="inlineStr"/>
       <c r="K471" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>As cidades apresentavam, naturalmente, condições específicas, com uma grande população concentrada numa superfície pequena, enquanto o campo tinha uma densidade demográfica baixa. Mas, assim como os campos se diferenciavam pelo seu contexto geográfico, as cidades não eram iguais entre si. Uma grande sede feudal (como Troyes), a capital de um reino (caso de Londres), uma importante sé episcopal (Burgos, por exemplo), uma cidade dedicada ao comércio internacional (como Veneza ou Lübeck), uma cidade artesanal (como Ypres), um pequeno burgo rural (os mais comuns) não poderiam, por razões geográficas e profissionais, construir habitações e edifícios públicos da mesma forma.
-FRANCO JR., Hilário. A Idade Média: nascimento do ocidente. São Paulo: Brasiliense, 1995, pp. 181-182.
-Qual foi uma das principais razões para o crescimento das cidades na Baixa Idade Média?</t>
+          <t>As invenções tecnológicas foram fundamentais para o sucesso da Revolução Industrial. Dispositivos como a máquina a vapor, o tear mecânico e o motor de combustão interna revolucionaram os processos produtivos. Essas inovações não apenas aumentaram a eficiência das fábricas, mas também transformaram o cotidiano das pessoas, facilitando a produção em massa e permitindo a expansão do comércio. As invenções moldaram uma nova era de progresso e mudança social.
+Uma das contribuições das inovações tecnológicas durante a Revolução Industrial foi o(a)</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>A criação de novas rotas marítimas.</t>
+          <t>facilitação da produção em massa.</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>O​​​​​​​ desenvolvimento das técnicas agrícolas e do comércio.</t>
+          <t>retorno à produção artesanal.</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>A descoberta de novos continentes.</t>
+          <t>diminuição da eficiência produtiva.</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>A construção de grandes monumentos.</t>
+          <t>aumento do tempo de trabalho manual.</t>
         </is>
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>A melhoria das técnicas agrícolas possibilitou um aumento da produção e, consequentemente, um crescimento populacional e econômico. O crescimento populacional provocou uma superlotação dos feudos, o que acarretou na expulsão de camponeses pelos senhores feudais, enquanto o aumento da produção permitiu que os excedentes fossem comercializados em feiras. Esse cenário, de migração de grandes parcelas da população camponesa, e de concentração do comércio em feiras próximas a centros urbanos, contribuíram para o chamado Renascimento Urbano.</t>
+          <t>As inovações tecnológicas durante a Revolução Industrial, como a máquina a vapor e o tear mecânico, permitiram a produção em massa de bens. Isso aumentou significativamente a eficiência das fábricas e reduziu os custos de produção, tornando produtos mais acessíveis e disponíveis para um maior número de pessoas.</t>
         </is>
       </c>
       <c r="H472" t="inlineStr">
@@ -25090,47 +25090,45 @@
       <c r="J472" t="inlineStr"/>
       <c r="K472" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>Leia o texto a seguir.
-Entre 1095 e 1291 d.C., uma série de guerras religiosas foram organizadas por cristãos europeus em resposta ao expansionismo militar dos povos muçulmanos que estendiam suas posses por regiões do Oriente e do norte da África. 
-Disponível em: https://revistagalileu.globo.com/sociedade/historia/noticia/2019/10/dois-seculos-de-guerra-cristas-entenda-o-que-foram-cruzadas.ghtml. Acesso em: 2 out. 2024.
-O trecho acima refere-se às Cruzadas, que tinham como principal objetivo</t>
+          <t>J.R. Barfoot. Pessoas com cestos e sacos colhem algodão em uma plantação. Darnton, 1840. Disponível em: &lt;https://upload.wikimedia.org/wikipedia/commons/thumb/1/1c/People_with_baskets_and_sacks_pick_cotton_on_a_plantation._Coloured_lithograph_after_J.R._Barfoot.jpg&gt;. Acesso em 03 de Out. 2023.
+Entre as principais matérias-primas utilizadas durante o processo conhecido como Revolução Industrial, está o algodão, obtido, principalmente através</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>conquistar novos territórios para os reinos cristãos na Ásia.</t>
+          <t>do desenvolvimento da indústria.</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>abrir novas rotas de comércio entre a Europa e o Oriente Médio.</t>
+          <t>de plantações em colônias inglesas.</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>retomar Jerusalém e outros territórios sagrados que estavam sob controle muçulmano.</t>
+          <t>do comércio com nações plantadoras dessa matéria-prima.</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>impedir o avanço do Império Bizantino no Oriente Médio.</t>
+          <t>de relações comerciais estabelecidas entre artesãos e burgueses.</t>
         </is>
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>As Cruzadas foram expedições militares organizadas principalmente pela Igreja Católica com o intuito de reconquistar Jerusalém e outros territórios sagrados do controle muçulmano. Embora houvesse interesses secundários, como o estabelecimento de rotas comerciais ou a conversão religiosa, o objetivo central era a retomada da Terra Santa, justificada como uma missão espiritual de defesa do cristianismo.</t>
+          <t>A partir do desenvolvimento da indústria têxtil, o algodão se tornou matéria-prima fundamental durante a Revolução Industrial, sendo obtido, principalmente, através das colônias inglesas.</t>
         </is>
       </c>
       <c r="H473" t="inlineStr">
@@ -25143,48 +25141,56 @@
           <t>História</t>
         </is>
       </c>
-      <c r="J473" t="inlineStr"/>
+      <c r="J473" t="inlineStr">
+        <is>
+          <t>8a_ph01_his_06.png</t>
+        </is>
+      </c>
       <c r="K473" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>Eram eventos importantes para a economia das cidades. Permitiam a troca de produtos entre diferentes regiões, facilitando o comércio e a circulação de mercadorias e eram momentos de encontro social e cultural.
-O trecho trata das(dos)</t>
+          <t>Leia o texto a seguir.
+A indústria que se iniciava precisava de mão de obra, porém tal mão de obra deveria ter baixo custo. Isso possibilitou a contratação de mulheres e crianças na indústria têxtil inglesa, as quais se sujeitavam ao trabalho industrial como forma de complementar a renda familiar [...].
+RODRIGUES, P. J.; MILANI, D. R. C.; CASTRO, L. L. O.; CELESTE FILHO, M. O trabalho feminino durante a Revolução Industrial. Disponível
+em: &lt; https://www.marilia.unesp.br/Home/Eventos/2015/xiisemanadamulher11189/o-trabalho-feminino_paulo-jorge-rodrigues.pdf&gt;.
+Acesso em: 09 dez. 2019.
+As condições de trabalho nas fábricas oferecidas às mulheres e crianças eram</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Feiras medievais.</t>
+          <t>boas, existindo alas específicas para descanso desses dois grupos.</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Mercados urbanos.</t>
+          <t>ruins, já que elas não atendiam às demandas de produção das fábricas.</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>Festivais religiosos.</t>
+          <t>ruins, tendo em vista a ausência de direitos para as operárias e os riscos enfrentados pelas crianças.</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>Assembleias comerciais.</t>
+          <t>boas, tendo em vista que as fábricas foram seus primeiros espaços de inserção no mercado de trabalho.</t>
         </is>
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>As feiras medievais tinham como principal função facilitar a troca de produtos entre diferentes regiões, promovendo o comércio e a circulação de mercadorias e culturas.</t>
+          <t>A intensa exploração dos trabalhadores, durante a Revolução Industrial, pode ser observada através da utilização da mão de obra de mulheres e crianças sem nenhuma regulamentação. As mulheres não tinham direitos fundamentais garantidos, como a licença maternidade, e as crianças arriscavam suas vidas ao manipularem as máquinas.</t>
         </is>
       </c>
       <c r="H474" t="inlineStr">
@@ -25200,46 +25206,49 @@
       <c r="J474" t="inlineStr"/>
       <c r="K474" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>Sua origem remonta à Idade Média [...]. Os pedreiros ou construtores, com o conhecimento herdado das técnicas romanas e gregas, se organizavam em um desses grupos. E, por uma questão de sobrevivência frente a uma possível concorrência, eles guardavam os segredos da construção civil, temerosos de que as técnicas caíssem em domínio público.
-Disponível em: https://www.bbc.com/portuguese/geral-45457166. Acesso em: 14 out. 2024.
-Essas associações descritas pelo texto eram chamadas de</t>
+          <t>Leia o texto a seguir.
+Com a Inglaterra liderando o processo de industrialização, o país torna-se o grande responsável por parcela considerável da produção industrial global. Isso não foi resultado de um século de mudanças rápidas, mas de uma revolução mais lenta e gradual do que se esperava, e se costuma descrever.
+Lima, E. C. de, &amp; Oliveira Neto, C. R. de. Revolução Industrial: considerações sobre o pioneirismo industrial inglês. Revista Espaço
+Acadêmico, 17(194), p.104. Acesso em: &lt;http://www.periodicos.uem.br/ojs/index.php/EspacoAcademico/article/view/32912&gt;. Acesso
+em: 10 dez. 2019. (Adaptado)
+Iniciada na Inglaterra, a Revolução Industrial contou com o protagonismo da burguesia, uma vez que</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>grêmios comerciais.</t>
+          <t>os burgueses faziam oposição à aristocracia que os explorava nas fábricas.</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>associações de artesãos.</t>
+          <t>estes lideraram o Parlamento inglês na maior parte dos séculos XVIII e XIX.</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>ligas de produção.</t>
+          <t>foi a partir dela que houve o restabelecimento do absolutismo inglês.</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>corporações de ofício.</t>
+          <t>tal classe social, por meio dos sindicatos, tomou os meios de produção para si.</t>
         </is>
       </c>
       <c r="F475" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>As corporações de ofício foram associações fundamentais durante o Renascimento comercial, reunindo artesãos de uma mesma profissão com o objetivo de organizar e regulamentar a produção. Elas desempenhavam um papel crucial na garantia da qualidade dos produtos, estabelecendo padrões técnicos e controlando a concorrência. Além disso, as corporações protegiam os interesses econômicos e sociais de seus membros, oferecendo suporte e representando-os em questões legais e políticas, o que fortalecia a cooperação entre os artesãos.</t>
+          <t>Além de ser detentora dos meios de produção, a burguesia desempenhou também um papel protagonista na política inglesa, implementando políticas que favorecessem a liberdade econômica e, consequentemente, sua própria classe social.</t>
         </is>
       </c>
       <c r="H475" t="inlineStr">
@@ -25255,46 +25264,49 @@
       <c r="J475" t="inlineStr"/>
       <c r="K475" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>Nesse sentido, o século XI é marcado, por um lado, pela expansão da produção e crescimento urbano e, por outro, com o desenvolvimento da atividade comercial na cidade medieval. Nesses burgos, com o aumento de seus habitantes, as construções urbanas foram edificadas fora das muralhas, o que gerava a necessidade de proteção contra o banditismo senhorial e de organização política própria na defesa de seus interesses, pois seus moradores eram constituídos, basicamente, pelo clero, nobres, ricos comerciantes, artesãos, etc, sendo denominados de burgueses.
-AMBONI, V. As Comunas na Idade Média (Século XII): Lutas de Classes e Ontologia da Burguesia Medieval. In: CONGRESSO INTERNACIONAL DE HISTÓRIA, 5., 2011, Passo Fundo. Anais eletrônicos... Passo Fundo: UPF, 2011. Disponível em: http://www.cih.uem.br/anais/2011/trabalhos/79.pdf. Acesso em: 14 out. 2024.
-A formação dos primeiros burgos ocorreu devido a</t>
+          <t>Leia o texto a seguir.
+Propriedade
+Propriedade é a instituição fundamental do capitalismo, que permite vedar ao trabalhador acesso aos meios (terra, recursos naturais) e aos instrumentos (maquinário) de produção. [...] A transformação das terras comunais em propriedade – através do processo de cercamentos (enclosures) na Inglaterra que durou do século XVI ao século XVIII -- privou os trabalhadores da possibilidade de produzirem seus meios de subsistência obrigando-os a vender sua força de trabalho e assim transformou os servos e pequenos produtores independentes em assalariados, a relação de produção predominante no capitalismo.
+Propriedade. In: Glossário HISTEDBR UNICAMP. Disponível em:
+&lt;http://www.histedbr.fe.unicamp.br/navegando/glossario/verb_c_propriedade.htm&gt;. Acesso em: 10 dez. 2019.
+É sabido que o processo de cercamento dos campos na Inglaterra influenciou diversos aspectos da Revolução Industrial, dentre eles</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>expansão das rotas marítimas.</t>
+          <t>a ruralização da economia inglesa.</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>construção de catedrais góticas.</t>
+          <t>a expansão da mão de obra fabril.</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>necessidade de proteção e segurança.</t>
+          <t>o retorno da monarquia absolutista.</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>descoberta de novas terras.</t>
+          <t>a instauração de um regime republicano.</t>
         </is>
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>A formação dos primeiros burgos na Europa foi motivada pela necessidade de proteção e segurança, tendo em vista a grande instabilidade social que se espalhou pela Europa após o fim do Império Carolíngio. Os primeiros burgos cresceram muito com o tempo, o que acarretou no surgimento de novos burgos ao redor das muralhas e das fortificações dos primeiros.</t>
+          <t>Com o cercamento dos campos, houve um processo de êxodo rural devido à dificuldade de acesso à terra nas zonas rurais. A partir disso, os camponeses passaram a ir para as cidades em busca de oportunidades de trabalho, integrando assim a mão de obra fabril chamada de proletariado.</t>
         </is>
       </c>
       <c r="H476" t="inlineStr">
@@ -25310,45 +25322,44 @@
       <c r="J476" t="inlineStr"/>
       <c r="K476" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>Veja o quadro a seguir:
-O quadro acima demonstra o acelerado crescimento da população europeia entre os séculos XI e XIV. Um fator que possibilitou esse fenômeno foi</t>
+          <t>A imagem acima ilustra uma situação muito comum nas fábricas durante a Revolução Industrial, podendo ser observado(a)</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>o advento de máquinas movidas por combustíveis fósseis, causando um aumento da produção agrícola.</t>
+          <t>a forte regulamentação do trabalho exercida pelo Estado inglês.</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>as migrações de povos eslavos da Europa Oriental que estavam fugindo dos ataques de muçulmanos.</t>
+          <t>a substituição do uso de máquinas nas fábricas pelo trabalho infantil.</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>os avanços tecnológicos como o moinho hidráulico e o arado de ferro, que possibilitaram um aumento na produção de alimentos.</t>
+          <t>a ausência de desemprego na Inglaterra deste período.</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>a descoberta de novas vacinas, o que permitiu aos europeus superar doenças fatais como a peste negra.</t>
+          <t>a exploração do trabalho nas fábricas, que se utilizavam do trabalho infantil.</t>
         </is>
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>Os diversos avanços tecnológicos relacionados à prática da agricultura, foram fundamentais para o crescimento populacional na Europa devido ao aumento que proporcionou na produção de alimentos.</t>
+          <t>A Revolução Industrial tinha como uma de suas marcas a extrema exploração da classe trabalhadora, praticamente não havendo nenhuma regulamentação trabalhista, o que dava precedentes para o uso do trabalho infantil, demonstrando a precarização do proletariado em tal contexto.</t>
         </is>
       </c>
       <c r="H477" t="inlineStr">
@@ -25363,50 +25374,52 @@
       </c>
       <c r="J477" t="inlineStr">
         <is>
-          <t>ph01_his_06.png</t>
+          <t>8a_ph01_his_10.png</t>
         </is>
       </c>
       <c r="K477" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>Observe a imagem a seguir.
-A imagem acima é uma representação de uma cidade italiana a época do Renascimento Comercial e urbano. Este processo</t>
+          <t>Leia um trecho de uma resenha crítica sobre o filme Divertidamente.
+Divertida Mente é a perfeita união de originalidade com criatividade em um roteiro inteligente, em iguais medidas engraçado e emocionante que fará rir e derreterá corações de crianças e adultos igualmente. Some à isso personagens apaixonantes e a criação de um fantástico universo visual e o resultado é hipnotizante e arrebatador do começo ao fim, literalmente sem qualquer falha visível.
+Disponível em: https://www.planocritico.com/critica-divertidamente/#:~:text=Divertida%20Mente%20%C3%A9%20a%20perfeita%20uni%C3%A3o%20de. Acesso em: 4 out. 2024. (Fragmento)
+Na frase em destaque, a função do pronome "isso" é substituir o substantivo</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>representou uma reativação do comércio no continente europeu, que estava enfraquecido na Idade Média.</t>
+          <t>"personagens".</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>significou o surgimento do comércio na Europa, visto que antes nunca existiram rotas de comércio no continente.</t>
+          <t>"resultado".</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>foi possível graças a tomada de Jerusalém pelos exércitos da Igreja durante as Cruzadas.</t>
+          <t>"história".</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>iniciou-se no século XIII e não provocou significativas mudanças no sistema e nas relações feudais vigentes.</t>
+          <t>"roteiro".</t>
         </is>
       </c>
       <c r="F478" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>Como o nome sugere, o Renascimento Comercial consistiu na reativação do comércio no continente europeu. Esse processo foi possibilitado pela desagregação do feudalismo, pela comercialização dos excedentes produzidos nos campos, e pelo aumento do número de comerciantes. Assim, as relações comerciais, que já existiam anteriormente mas ficaram enfraquecidas durante o feudalismo, voltaram a ganhar espaço na vida econômica e social do período.</t>
+          <t>O pronome 'isso' substitui o substantivo 'roteiro', mencionado na frase anterior em "um roteiro inteligente". Ele exerce a função de retomar uma ideia já apresentada no texto, evitando a repetição do termo e contribuindo para a coesão textual.</t>
         </is>
       </c>
       <c r="H478" t="inlineStr">
@@ -25416,50 +25429,42 @@
       </c>
       <c r="I478" t="inlineStr">
         <is>
-          <t>História</t>
-        </is>
-      </c>
-      <c r="J478" t="inlineStr">
-        <is>
-          <t>ph01_his_07.png</t>
-        </is>
-      </c>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="J478" t="inlineStr"/>
       <c r="K478" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>Leia o texto a seguir.
-O anúncio em boletins e sites da Igreja Católica vem sendo saudado com entusiasmo por alguns e cautela por outros. Mas passou em branco para uma grande geração de católicos que não fazem ideia do que significa: "Bispo anuncia indulgências plenárias".
-[...]
-A volta das indulgências começou com o papa João Paulo 2º, que em 2000 autorizou os bispos a oferecê-las como parte das celebrações do terceiro milênio da igreja.
-CLARA, Allain (trad.). Indulgência volta à voga na Igreja Católica. Folha de São Paulo, 11 fev. 2009. Disponível em:
-&lt;https://www1.folha.uol.com.br/fsp/mundo/ft1102200915.htm&gt;. Acesso em: 02 dez. 2019.
-Ao contrário dos dias de hoje, durante o período de Cruzadas a indulgência foi comumente utilizada como</t>
+          <t>Disponível em: https://www.sonypictures.com.br/filmes/garfield-fora-de-casa. Acesso em 16 out. 2024
+Garfield, o mundialmente famoso gato de estimação que odeia segundas-feiras e ama lasanha, está prestes a ter uma aventura selvagem ao ar livre! Após um reencontro inesperado com seu pai há muito perdido, o maltrapilho gato de rua Vic, Garfield e seu amigo canino, Odie, são forçados a sair de suas vidas perfeitamente mimadas para se juntarem a Vic em um hilariante e arriscado assalto.
+Os pronomes “que”, “seu” e “suas” são, respectivamente,</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>modo de conversão dos infiéis ao cristianismo.</t>
+          <t>indefinido, demonstrativo, possessivo.</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>estratégia de negociação com os muçulmanos.</t>
+          <t>demonstrativo, possessivo, pessoal.</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>método de controle populacional em toda a Europa.</t>
+          <t>interrogativo, pessoal, indefinido.</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>forma de convencer os fiéis a participarem das expedições.</t>
+          <t>relativo, possessivo, possessivo.</t>
         </is>
       </c>
       <c r="F479" t="inlineStr">
@@ -25469,7 +25474,7 @@
       </c>
       <c r="G479" t="inlineStr">
         <is>
-          <t>Durante o período das Cruzadas, a indulgência, prática que perdoa todos os pecados dos fiéis cristãos, foi utilizada como incentivo para a participação dos cristãos nas expedições cruzadistas.</t>
+          <t>O termo 'que' é um pronome relativo, utilizado para introduzir orações que acrescentam informações sobre um substantivo. Por outro lado, 'seu' e 'suas' são pronomes possessivos, que indicam posse ou pertencimento.</t>
         </is>
       </c>
       <c r="H479" t="inlineStr">
@@ -25479,43 +25484,45 @@
       </c>
       <c r="I479" t="inlineStr">
         <is>
-          <t>História</t>
-        </is>
-      </c>
-      <c r="J479" t="inlineStr"/>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="J479" t="inlineStr">
+        <is>
+          <t>8a_ph01_por_04.png</t>
+        </is>
+      </c>
       <c r="K479" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Leia o texto a seguir.
-Enquanto por volta do ano 1000 talvez não existisse na Europa católica nenhuma cidade com uma população de 10.000 habitantes, no século XIII havia 55 cidades com um número de habitantes superior àquele. [...] Ainda que as cifras sejam sempre discutíveis, sem haver consenso entre os especialistas, Milão, Florença, Veneza e Gênova devem ter ultrapassado os 100.000 habitantes. No restante da Europa Ocidental, apenas Paris parece ter alcançado tal população.
-FRANCO JÚNIOR, Hilário. A Idade Média, nascimento do ocidente. São Paulo: Brasiliense, 2006, p.23-24.
-Um dos motivos de tal crescimento das grandes cidades europeias, como destacado no texto, foi</t>
+          <t>A resenha crítica e a sinopse são dois tipos de textos que, apesar de terem algumas semelhanças, possuem objetivos e estruturas diferentes.
+Assinale qual alternativa indica as características desses dois gêneros.</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>o rápido processo de industrialização que se iniciou nesse contexto.</t>
+          <t>A resenha crítica inclui apenas uma descrição geral da trama e dos personagens principais, e pode ser encontrada na contracapa de livros ou em descrições de filmes.  Já a sinopse inclui a análise de elementos como roteiro, direção, atuação e aspectos técnicos, e é geralmente escrita por críticos especializados.</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>o crescimento populacional que ocorreu no continente durante as Cruzadas.</t>
+          <t>A resenha crítica tem como objetivo principal informar o leitor sobre o enredo básico da obra, sem emitir juízo de valor. Já a sinopse informa e persuade o leitor sobre a qualidade da obra, analisando aspectos técnicos e emocionais.</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>a grande concentração de muçulmanos que chegaram à Europa nesse período.</t>
+          <t>A resenha crítica é geralmente curta e objetiva, fornecendo apenas as informações essenciais sobre a história. Já a sinopse pode ser mais longa e detalhada, oferecendo uma visão aprofundada da obra e suas nuances.</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>o processo de migração de comerciantes que viviam nos feudos para os burgos.</t>
+          <t>A resenha crítica apresenta uma opinião detalhada sobre a obra, incluindo pontos positivos e negativos, e pode conter spoilers. Já a sinopse fornece um resumo breve da história sem revelar detalhes importantes ou o final.</t>
         </is>
       </c>
       <c r="F480" t="inlineStr">
@@ -25525,7 +25532,7 @@
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>Juntamente ao Renascimento Comercial ocorreu também o Renascimento Urbano, no qual houve a migração de camponeses comerciantes que, enfrentando dificuldades comerciais dentro dos feudos, se mudaram para os burgos, aumentando, consequentemente, a população e o tamanho das cidades.</t>
+          <t>A resenha crítica tem como objetivo principal oferecer uma análise detalhada da obra, incluindo pontos positivos e negativos, e frequentemente contém spoilers para fundamentar a avaliação crítica. Ela aborda diversos aspectos da obra, como roteiro, direção, atuação e aspectos técnicos, permitindo ao leitor uma compreensão aprofundada e crítica. Por outro lado, a sinopse tem a função de fornecer um resumo breve e objetivo da história, sem revelar detalhes importantes ou o final, servindo como uma introdução à trama e aos personagens principais. Dessa forma, a sinopse ajuda o leitor a decidir se deseja explorar a obra mais a fundo, sem comprometer a experiência de descoberta.</t>
         </is>
       </c>
       <c r="H480" t="inlineStr">
@@ -25535,53 +25542,59 @@
       </c>
       <c r="I480" t="inlineStr">
         <is>
-          <t>História</t>
+          <t>Português</t>
         </is>
       </c>
       <c r="J480" t="inlineStr"/>
       <c r="K480" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>Leia o texto a seguir.
-As Corporações de Ofício medievais congregavam pessoas com um mesmo interesse econômico, político ou cultural. Tais pessoas agrupavam-se, criavam um estatuto para garantir os melhores preços e impedir a entrada de produtos ou de pessoas em seu meio. Cada membro da corporação deveria respeitar um estatuto próprio.
-Disponível em: &lt;http://www.histedbr.fe.unicamp.br/navegando/glossario/verb_c_universidades_medievais.htm&gt;. Acesso em: 02 dez. 2019.
-Conforme demonstra o texto, as Corporações de Ofício possuíam uma organização baseada no(a)</t>
+          <t>Cão no cinema
+Um indivíduo vai com o seu cão ao cinema. O homem da cadeira ao lado começa a ficar espantado ao ver que o cão ria e batia palmas, como se estivesse realmente a compreender o filme. Diz o homem para o dono do cão:
+- Estou admiradíssimo! O seu cão é muito inteligente, percebe o filme todo.
+Diz o dono do cão:
+- Ai, está admirado?! Mais admirado estou eu!
+- Então… mas por quê? – Pergunta intrigado o homem.
+Explica o dono do cão:
+- É que ele leu o livro e não gostou…
+  Disponível em: https://www.anedotadodia.net/anedotas/animais/cao-no-cinema. Acesso em: 27 fev. 2018.
+O pronome possessivo “seu” em “O seu cão é muito inteligente, percebe o filme todo” refere-se ao</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>modo de produção industrializado.</t>
+          <t>“cão”.</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>rejeição das atividades ligadas à agricultura.</t>
+          <t>“dono do cão”.</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>combate ao processo de urbanização medieval.</t>
+          <t>“indivíduo”.</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>monopólio de determinadas atividades econômicas.</t>
+          <t>“homem”.</t>
         </is>
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>Como destaca o texto-base, os membros das Corporações criavam seus estatutos internos com o intuito de “impedir a entrada de produtos ou de pessoas em seu meio”, algo que demonstra o caráter monopolista de tais organizações.</t>
+          <t>O uso do pronome concorda com a terceira pessoa discursiva (você), referindo-se ao interlocutor do diálogo, o dono do cão.</t>
         </is>
       </c>
       <c r="H481" t="inlineStr">
@@ -25591,52 +25604,59 @@
       </c>
       <c r="I481" t="inlineStr">
         <is>
-          <t>História</t>
+          <t>Português</t>
         </is>
       </c>
       <c r="J481" t="inlineStr"/>
       <c r="K481" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>Atena era uma importante deusa presente na religiosidade da Grécia Antiga. Ela era considerada a deusa da sabedoria, mas também tinha forte relação com ofícios e habilidades manuais. Era a deusa patrona de uma das cidades mais importantes da Grécia: Atenas. Era filha de Zeus e nasceu ao sair da cabeça de seu pai.
-Disponível em: https://www.historiadomundo.com.br/grega/atena.htm. Acesso em 11 de out. de 2024.
-Qual adjetivo melhor descreve a deusa grega Atena apresentada pelo texto?</t>
+          <t>Cão no cinema
+Um indivíduo vai com o seu cão ao cinema. O homem da cadeira ao lado começa a ficar espantado ao ver que o cão ria e batia palmas, como se estivesse realmente a compreender o filme. Diz o homem para o dono do cão:
+- Estou admiradíssimo! O seu cão é muito inteligente, percebe o filme todo.
+Diz o dono do cão:
+- Ai, está admirado?! Mais admirado estou eu!
+- Então… mas por quê? – Pergunta intrigado o homem.
+Explica o dono do cão:
+- É que ele leu o livro e não gostou…
+  Disponível em https://www.anedotadodia.net/anedotas/animais/cao-no-cinema. Acesso em: 27 fev. 2018.
+Os substantivos são classificados como biformes quando há duas palavras distintas para marcar o gênero, como em “homem” e “mulher”, “gato” e “gata”. É um substantivo biforme:</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>Prudente</t>
+          <t>cão.</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Ingênua</t>
+          <t>indivíduo.</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>Sábia</t>
+          <t>filme.</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>Frágil</t>
+          <t>cinema.</t>
         </is>
       </c>
       <c r="F482" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>Na mitologia grega, Atena é reconhecida por sua inteligência e habilidade em aconselhar os heróis, características que a diferenciam como uma figura justa e ponderada. Assim, "sábia" complementa perfeitamente sua representação, evidenciando seu papel como protetora e conselheira em batalhas.</t>
+          <t>O substantivo "cão" (forma masculina) possui também a forma "cadela" (forma feminina).</t>
         </is>
       </c>
       <c r="H482" t="inlineStr">
@@ -25652,46 +25672,54 @@
       <c r="J482" t="inlineStr"/>
       <c r="K482" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>Poseidon era o deus grego dos mares e rios e considerado um causador de catástrofes. Acredita-se que seu culto tenho se originado no período Pré-Homérico.
-Disponível em: https://www.historiadomundo.com.br/grega/poseidon.htm. Acesso em 11 de out. de 2024.
-Qual é a função do artigo "o" no trecho destacado?</t>
+          <t>Leia o texto abaixo para responder à questão.
+‘O Irlandês’: o arrebatador olhar de Martin Scorsese sobre a máfia
+Com seu estupendo domínio de cena, o diretor conta sua versão de uma história real — e impregna o filme feito para a Netflix com a angústia do esquecimento
+Mal de saúde e preso a uma cadeira de rodas em um asilo de idosos, Frank “o Irlandês” Sheeran (Robert De Niro) narra para o espectador como tudo se passou, desde o dia distante em que, dirigindo seu caminhão de entregas numa estrada próxima à cidade de Filadélfia, conheceu o chefão local Russell Bufalino (Joe Pesci, em uma atuação extraordinária) — e assim se aproximou da máfia e, por causa dela, acabou se envolvendo também com Jimmy Hoffa (Al Pacino). “Nos anos 50, Hoffa era maior do que Elvis Presley. E, nos anos 60, era maior do que os Beatles”, explica Sheeran a respeito do folclórico e poderosíssimo presidente do maior sindicato americano de caminhoneiros. Entre 1957 e 1971, Hoffa teve o transporte de cargas dos Estados Unidos nas mãos, dobrando aos seus interesses tanto governo como agências da lei e organizações criminosas — até desaparecer, ou ser desaparecido, em 30 de julho de 1975, quando tentava reconquistar o controle do sindicato.
+O crime suscitou uma das mais vastas e prolongadas investigações já conduzidas na história policial americana. Mas, até hoje, quem matou Hoffa e o que foi feito de seu corpo são perguntas sem resposta, no que virou uma obsessão para detetives amadores, teóricos da conspiração e americanos de certas gerações, entre as quais a do cineasta Martin Scorsese, de 77 anos. Depois de três horas e meia de filme, porém — e que filme —, Frank Sheeran põe o nome de Jimmy Hoffa na conversa com a enfermeira que cuida dele no asilo, e a moça dá de ombros; Jimmy quem?
+O Irlandês (The Irishman, Estados Unidos, 2019), que está em cartaz em algumas salas de cinema e estreia na Netflix nesta quarta-feira, 27, parece em tudo uma escolha natural para Martin Scorsese, um descendente de sicilianos que cresceu no Queens nova- -iorquino cercado por tipos como os que frequentemente retrata em seus filmes. Mas, à medida que a história transcorre, outros temas que soam bem mais íntimos começam a subir à superfície: velhice, obsolescência, reputação, a desconexão entre o passado e o presente. Scorsese não sublinha esses temas. Com seu estupendo domínio de cena, ele apenas os reitera de maneira que impregnem o filme, como se fossem um pensamento que nunca se articula completamente. Mas é nesse eco que está a razão de ser de O Irlandês.
+Se na trilogia O Poderoso Chefão Francis Ford Coppola mitologizou o alto escalão da máfia, Scorsese sempre se interessou mais pelos soldados e tenentes do crime organizado, aqueles homens que recebem ordens e prestam contas, e que às vezes, como Henry Hill, o personagem de Ray Liotta em Os Bons Companheiros (1990), se deixam intoxicar pelos maços de dinheiro presos com clipes, pela permissão fácil para a violência e pelos rapapés que donos de mercearias e garçons fazem a eles. Frank Sheeran é um típico soldado (“Pinto paredes”, ele diz — e pinta-as mesmo, com sangue). Pela lealdade, é promovido a sargento e, depois, a figura de proa do sindicalismo regional. Ao contrário do jovem e alucinado Henry Hill de Os Bons Companheiros ou do metódico e ambiciosíssimo Sam Roths-tein de Cassino (1995), também interpretado por De Niro, Sheeran é um personagem contido: menos dado a voos de imaginação, mais prestativo e obediente — e truculento. Mas, do mesmo modo, é alguém que confunde o medo que inspira com respeito, e o terror que é capaz de instaurar com poder (...).
+BOSCOV, Isabela. “‘O Irlandês’: o arrebatador olhar de Martin Scorsese sobre a máfia”. Veja. São paulo 22
+nov. 2019. Disponível em: https://veja.abril.com.br/blog/isabela-boscov/o-irlandes-o-arrebatador-olhar-de-
+martin-scorsese-sobre-a-mafia/
+Sobre o título de filme O Poderoso Chefão, citado no texto, é correto afirmar que</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>Generalizar Poseidon.</t>
+          <t>o emprego do adjetivo poderoso em nada contribui para a caracterização do substantivo chefão.</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Especificar Poseidon.</t>
+          <t>o uso do adjetivo poderoso é o único recurso utilizado para destacar a importância do chefão.</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>Descrever Poseidon.</t>
+          <t>o emprego do aumentativo em chefão tem valor irônico, pois o diretor do filme despreza os agentes da máfia, conforme se comenta no texto.</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>Nomear Poseidon.</t>
+          <t>o uso do aumentativo em chefão realça o poder do chefe, já adjetivado como poderoso.</t>
         </is>
       </c>
       <c r="F483" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G483" t="inlineStr">
         <is>
-          <t>O artigo "o" específica Poseidon como "o deus grego dos mares e rios", destacando sua posição única e suas características na mitologia grega.</t>
+          <t>Em O Poderoso Chefão, o chefe, ao qual se refere o título, tem seu poder sinalizado pelo uso do adjetivo poderoso e pelo aumentativo, chefão, que também ressalta sua importância.</t>
         </is>
       </c>
       <c r="H483" t="inlineStr">
@@ -25707,51 +25735,54 @@
       <c r="J483" t="inlineStr"/>
       <c r="K483" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>A origem do Sol
-Há muitos e muitos anos, houve uma festa na aldeia onde um lindo rapaz morava, a “festa da moça nova”, um ritual que celebra a passagem das meninas indígenas de crianças a “moças” ou “jovens mulheres”. Era dia de música, dança, bebida e comida à vontade. E todos, é claro, caprichariam nas pinturas do corpo com a tinta vermelha a base de urucum, fruto do urucuzeiro.
-Pois bem, o belo rapaz quis ajudar sua tia no preparo da tinta. Entrou na mata, trouxe madeira vermelha de muirapiranga, cortou a lenha e acendeu o fogo, no qual a velha senhora pôs a ferver o urucum para que todos pudessem se pintar. Mas a tia do moço não era uma pessoa muito feliz. Era maldosa e ranzinza. O rapaz se dedicava à tarefa de buscar mais e mais lenha para o fogo e, mesmo assim, ela não parava de reclamar.
-Admirado com o caldo vermelho borbulhando, ele perguntou à tia se poderia provar da tinta. A mulher impaciente disse que sim. Insistiu para ele beber uma grande quantidade, garantindo que o gosto era bom e que não lhe faria mal. No fundo, porém, ela queria que ele passasse mal, fosse embora logo e a deixasse sozinha.
-O rapaz bebeu e, conforme engolia a tinta quente, ia ficando vermelho, cada vez mais vermelho, extremamente vermelho, até que ficou em chamas! A tia, espantada, viu o sobrinho virar uma bola de fogo, subir ao céu e sumir entre as nuvens.
-E foi assim que um jovem indígena se tornou o Sol, que aquece e ilumina o mundo todo.
-Disponível em: https://chc.org.br/artigo/a-origem-do-sol/. Acesso em 21 nov. 2024.
-Qual é o substantivo plural no grau aumentativo da palavra em destaque?</t>
+          <t>Leia o texto abaixo para responder à questão.
+‘O Irlandês’: o arrebatador olhar de Martin Scorsese sobre a máfia
+Com seu estupendo domínio de cena, o diretor conta sua versão de uma história real — e impregna o filme feito para a Netflix com a angústia do esquecimento
+Mal de saúde e preso a uma cadeira de rodas em um asilo de idosos, Frank “o Irlandês” Sheeran (Robert De Niro) narra para o espectador como tudo se passou, desde o dia distante em que, dirigindo seu caminhão de entregas numa estrada próxima à cidade de Filadélfia, conheceu o chefão local Russell Bufalino (Joe Pesci, em uma atuação extraordinária) — e assim se aproximou da máfia e, por causa dela, acabou se envolvendo também com Jimmy Hoffa (Al Pacino). “Nos anos 50, Hoffa era maior do que Elvis Presley. E, nos anos 60, era maior do que os Beatles”, explica Sheeran a respeito do folclórico e poderosíssimo presidente do maior sindicato americano de caminhoneiros. Entre 1957 e 1971, Hoffa teve o transporte de cargas dos Estados Unidos nas mãos, dobrando aos seus interesses tanto governo como agências da lei e organizações criminosas — até desaparecer, ou ser desaparecido, em 30 de julho de 1975, quando tentava reconquistar o controle do sindicato.
+O crime suscitou uma das mais vastas e prolongadas investigações já conduzidas na história policial americana. Mas, até hoje, quem matou Hoffa e o que foi feito de seu corpo são perguntas sem resposta, no que virou uma obsessão para detetives amadores, teóricos da conspiração e americanos de certas gerações, entre as quais a do cineasta Martin Scorsese, de 77 anos. Depois de três horas e meia de filme, porém — e que filme —, Frank Sheeran põe o nome de Jimmy Hoffa na conversa com a enfermeira que cuida dele no asilo, e a moça dá de ombros; Jimmy quem?
+O Irlandês (The Irishman, Estados Unidos, 2019), que está em cartaz em algumas salas de cinema e estreia na Netflix nesta quarta-feira, 27, parece em tudo uma escolha natural para Martin Scorsese, um descendente de sicilianos que cresceu no Queens nova- -iorquino cercado por tipos como os que frequentemente retrata em seus filmes. Mas, à medida que a história transcorre, outros temas que soam bem mais íntimos começam a subir à superfície: velhice, obsolescência, reputação, a desconexão entre o passado e o presente. Scorsese não sublinha esses temas. Com seu estupendo domínio de cena, ele apenas os reitera de maneira que impregnem o filme, como se fossem um pensamento que nunca se articula completamente. Mas é nesse eco que está a razão de ser de O Irlandês.
+Se na trilogia O Poderoso Chefão Francis Ford Coppola mitologizou o alto escalão da máfia, Scorsese sempre se interessou mais pelos soldados e tenentes do crime organizado, aqueles homens que recebem ordens e prestam contas, e que às vezes, como Henry Hill, o personagem de Ray Liotta em Os Bons Companheiros (1990), se deixam intoxicar pelos maços de dinheiro presos com clipes, pela permissão fácil para a violência e pelos rapapés que donos de mercearias e garçons fazem a eles. Frank Sheeran é um típico soldado (“Pinto paredes”, ele diz — e pinta-as mesmo, com sangue). Pela lealdade, é promovido a sargento e, depois, a figura de proa do sindicalismo regional. Ao contrário do jovem e alucinado Henry Hill de Os Bons Companheiros ou do metódico e ambiciosíssimo Sam Roths-tein de Cassino (1995), também interpretado por De Niro, Sheeran é um personagem contido: menos dado a voos de imaginação, mais prestativo e obediente — e truculento. Mas, do mesmo modo, é alguém que confunde o medo que inspira com respeito, e o terror que é capaz de instaurar com poder (...).
+BOSCOV, Isabela. “‘O Irlandês’: o arrebatador olhar de Martin Scorsese sobre a máfia”. Veja. São paulo 22
+nov. 2019. Disponível em: https://veja.abril.com.br/blog/isabela-boscov/o-irlandes-o-arrebatador-olhar-de-
+martin-scorsese-sobre-a-mafia/
+No filme abordado pelo texto, a personagem de Robert De Niro, Frank, é conhecida pela alcunha “o Irlandês”. Sobre o emprego do artigo definido “o” nessa expressão é correto afirmar que este</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>Rapazãos</t>
+          <t>caracteriza a personagem Frank.</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Rapagões.</t>
+          <t>expressa desprezo por Frank.</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>Rapazotes.</t>
+          <t>singulariza a personagem de De Niro.</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>Rapazinhos.</t>
+          <t>atribui importância a Frank na história de Scorsese.</t>
         </is>
       </c>
       <c r="F484" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G484" t="inlineStr">
         <is>
-          <t>Na língua portuguesa, o aumentativo da palavra "rapaz" pode ser feito de duas maneiras: 1. com o acréscimo do sufixo -ão à raiz, formando "rapazão"; 2. com a substituição da letra /z/ por /g/ + acréscimo do sufixo -ão, formando "rapagão". Nos dois casos, a forma do aumentativo plural recebe o acréscimo do sufixo -ões, e não -ãos. Portanto, "rapagões" ou "rapazões".</t>
+          <t>O emprego do artigo definido “o” na alcunha “o Irlandês” singulariza Frank, personagem de Robert De Niro, uma vez que indica que este é uma pessoa específica. O mesmo não aconteceria se fosse empregado o artigo indefinido “um”, pois a expressão “um Irlandês” expressaria generalização.</t>
         </is>
       </c>
       <c r="H484" t="inlineStr">
@@ -25767,46 +25798,46 @@
       <c r="J484" t="inlineStr"/>
       <c r="K484" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>Um dos protagonistas do Monte Olimpo, Apolo é dos mais adorados entre os deuses gregos. Até por ser uma divindade multifunção: é o deus do Sol, da luz, da verdade, da profecia, da cura, da beleza masculina, do equilíbrio e da razão.
-Disponível em: https://super.abril.com.br/especiais/apolo-deus-da-perfeicao. Acesso em 14 de out. de 2024.
-O substantivo em destaque é classificado como</t>
+          <t>Na culinária é importante que as receitas possuam medições precisas. Muitas das receitas usam frações para indicar quantidades e ao cozinhar é preciso calcular ou utilizar instrumentos que possuem indicados a conversão em medidas decimais de modo a garantir a exatidão. Leia a receita a seguir.
+Disponível em: https://www.tudogostoso.com.br/receita/198422-cookies-simples.html. Acesso em: 07 out. 2024.
+Qual é a forma decimal da quantidade de açúcar pedida na receita?</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>Substantivo próprio, concreto.</t>
+          <t>0,304</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Substantivo comum, abstrato.</t>
+          <t>0,34</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>Substantivo próprio, abstrato.</t>
+          <t>0,705</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>Substantivo comum, concreto.</t>
+          <t>0,75</t>
         </is>
       </c>
       <c r="F485" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G485" t="inlineStr">
         <is>
-          <t>"Beleza" é um substantivo comum e abstrato, pois nomeia uma qualidade ou estado e não um objeto físico.</t>
+          <t>A quantidade de açúcar pedida na receita é de  e para converter essa fração em número decimal, é preciso dividir 3 por 4 que resulta em 0,75.</t>
         </is>
       </c>
       <c r="H485" t="inlineStr">
@@ -25816,53 +25847,58 @@
       </c>
       <c r="I485" t="inlineStr">
         <is>
-          <t>Português</t>
-        </is>
-      </c>
-      <c r="J485" t="inlineStr"/>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="J485" t="inlineStr">
+        <is>
+          <t>8a_ph01_mat_02.png</t>
+        </is>
+      </c>
       <c r="K485" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>Hélio tem a aparência de um deus jovem e radiante, com raios solares em volta da cabeça, e com cabelos loiros. Conduzindo uma carruagem dourada pelo céu, puxada por quatro cavalos alados, Pírois, Eoo, Éton e Flégon dotados de grande rapidez. 
-Ele atravessa o céu diariamente, iluminando a Terra com sua luz brilhante. Seu papel era crucial na criação do ciclo diário, trazendo a luz ao amanhecer do dia e a tarde chegava ao mar, onde banhava seus cavalos fadigados. 
-Disponível em: https://deusesgregos.com.br/helio-deus/. Acesso em 14 de out. de 2024.
-Qual é a forma plural do adjetivo em destaque quando concorda com o substantivo "luzes"?</t>
+          <t>Leia o texto a seguir.
+A massa de ar polar que atravessa parte do país desde o começo desta semana deixou as temperaturas negativas em ao menos dez cidades do país neste sábado (31), segundo o Instituto Nacional de Meteorologia (Inmet).
+A região do Parque Nacional do Itatiaia, na serra da Mantiqueira, entre Rio de Janeiro e Minas Gerais, foi a que apresentou a temperatura mínima média mais baixa do país, com -7 ºC.
+Disponível em: https://www.cnnbrasil.com.br/nacional/pais-registra-temperaturas-negativas-em-10-cidades-neste-sabado-veja-ranking/. Acesso em: 08 out. 2024.
+Qual é o módulo e o oposto da temperatura indicada no texto, respectivamente?</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>Brilhantíssimos</t>
+          <t>7 e 7</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Brilhantões</t>
+          <t>-7 e 7</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>Brilhantas</t>
+          <t>7 e -7</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>Brilhantes</t>
+          <t>31 e -31</t>
         </is>
       </c>
       <c r="F486" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>O adjetivo "brilhante" concorda em gênero e número com o substantivo "luzes", ficando "brilhantes" no plural feminino.</t>
+          <t>O módulo de -7 é 7 porque o módulo, ou valor absoluto, de um número representa a distância dele em relação ao zero na reta numérica, ignorando o sinal. Portanto, ao calcular |-7|, obtemos 7, que é a distância entre -7 e 0. Por outro lado, o oposto de -7 é 7, pois o oposto de um número é aquele que, quando somado ao original, resulta em zero. Assim, considerando o oposto de -7, obtemos 7 (ou seja, -7 + 7 = 0). Portanto, enquanto o módulo indica a magnitude sem levar em conta o sinal, o oposto inverte o sinal do número original.</t>
         </is>
       </c>
       <c r="H486" t="inlineStr">
@@ -25872,57 +25908,41 @@
       </c>
       <c r="I486" t="inlineStr">
         <is>
-          <t>Português</t>
+          <t>Matemática</t>
         </is>
       </c>
       <c r="J486" t="inlineStr"/>
       <c r="K486" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>Leia o texto a seguir para responder à questão:
-Num domingo, Onofre e Anésia dormiam, Antônio na sala roçando canivete na sola das botas, Maria, no quarto jogando talco nos vestidos da cômoda, deu um toque no pescoço. Nico passava café, Antônio sentiu o cheiro e foi sugerir um biscoito de polvilho, ele mesmo o faria se Maria deixasse.
-- Faz, mas deixa a cozinha arrumada e não usa a gordura toda que amanhã faço sabão.
-Antônio pegou na despensa os ovos, leite e polvilho azedo. No fogão a lenha a água borbulhava, Nico botou açúcar deixando-a leitosa, acrescentou o pó torrado pela manhã e levou a mistura até a pia onde a coaria no bule. Antônio usava a lateral da mesma pia, ficou em pé sobre o banco para alcançá-la, ia misturar os ingredientes numa bacia. Na frente deles uma janela dando para a represa, ouvia-se dali uma cachoeira ao longe, constante, úmida.
-Nico derramou a água fervente, o perfume subiu. Antônio interrompeu o biscoito para ver a fumaça se erguer. Nico apoiou a caneca de água na pia, Antônio fechou os olhos para fortalecer o aroma. Abriu-os e não viu mais o irmão, ele não estava mais na cozinha. Antônio se espichou para ver a água dentro do coador, ela desapareceu deixando uma pasta pelas beiradas, a caneca apoiada na pia, Maria fechando o armário lá dentro.
-- Maria? Vem ver, o Nico caiu no bule.
-Maria demorou a vir, pela impossibilidade do fato e nenhuma urgência naquela idiotia. Vendo Antônio olhar pela janela, foi até a despensa procurar Nico, no terreiro, chiqueiro, paiol, milharal.
-- Nico sair desse jeito? Sem falar nada?
-- Saiu não, Maria. Ele foi embora no coador.
-- Fala direito, Antônio.
-- Ele tava passando o pó, hora que botou a água, sumiu.
-- Daqui a pouco ele chega.
-- Não mexe no bule, deixa do jeito que tá para ele voltar.
-(...)
-FUEGO, Andrea del. Os Malaquias. Rio de Janeiro: Língua Geral, 2010.3
-No trecho do romance da escritora paulistana Andrea del Fuego, quando se dá conta de que Nico sumiu, Antônio fala:
-- Maria? Vem ver, o Nico caiu no bule.
-Com a análise atenta da fala de Antônio, podemos afirmar que não haveria mudança de sentido se o artigo definido “o” estivesse ausente da frase, pois o substantivo “Nico” é</t>
+          <t>Para a criação de um sistema de controle financeiro, um programador precisava criar um programa que encontrasse a fração exata correspondente ao valor de uma dízima periódica. 
+A fração tratada no trecho acima é chamada de</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>um substantivo próprio, o que cria uma especificação por si só.</t>
+          <t>geratriz.</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>um substantivo primitivo, pois não deriva de outra palavra.</t>
+          <t>decimal.</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>um substantivo simples, o que mostra seu caráter único.</t>
+          <t>periódica.</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>um substantivo concreto, pois indica o ser denominado.</t>
+          <t>racional.</t>
         </is>
       </c>
       <c r="F487" t="inlineStr">
@@ -25932,7 +25952,7 @@
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>“Nico” é um substantivo que, por si só, já indica uma especificação. Isso decorre do fato de ele ser um substantivo próprio. Portanto, o uso do artigo definido “o” seria mais uma escolha do próprio falante do que uma necessidade à compreensão do sentido.</t>
+          <t>A dízima periódica é um número decimal que possui uma sequência de dígitos que se repete indefinidamente, como 0,333... ou 0,636363... Para representar esse tipo de número de forma exata, utiliza-se uma fração especial chamada fração geratriz.</t>
         </is>
       </c>
       <c r="H487" t="inlineStr">
@@ -25942,67 +25962,59 @@
       </c>
       <c r="I487" t="inlineStr">
         <is>
-          <t>Português</t>
+          <t>Matemática</t>
         </is>
       </c>
       <c r="J487" t="inlineStr"/>
       <c r="K487" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>Leia o texto a seguir para responder à questão:
-Num domingo, Onofre e Anésia dormiam, Antônio na sala roçando canivete na sola das botas, Maria, no quarto jogando talco nos vestidos da cômoda, deu um toque no pescoço. Nico passava café, Antônio sentiu o cheiro e foi sugerir um biscoito de polvilho, ele mesmo o faria se Maria deixasse.
-- Faz, mas deixa a cozinha arrumada e não usa a gordura toda que amanhã faço sabão.
-Antônio pegou na despensa os ovos, leite e polvilho azedo. No fogão a lenha a água borbulhava, Nico botou açúcar deixando-a leitosa, acrescentou o pó torrado pela manhã e levou a mistura até a pia onde a coaria no bule. Antônio usava a lateral da mesma pia, ficou em pé sobre o banco para alcançá-la, ia misturar os ingredientes numa bacia. Na frente deles uma janela dando para a represa, ouvia-se dali uma cachoeira ao longe, constante, úmida.
-Nico derramou a água fervente, o perfume subiu. Antônio interrompeu o biscoito para ver a fumaça se erguer. Nico apoiou a caneca de água na pia, Antônio fechou os olhos para fortalecer o aroma. Abriu-os e não viu mais o irmão, ele não estava mais na cozinha. Antônio se espichou para ver a água dentro do coador, ela desapareceu deixando uma pasta pelas beiradas, a caneca apoiada na pia, Maria fechando o armário lá dentro.
-- Maria? Vem ver, o Nico caiu no bule.
-Maria demorou a vir, pela impossibilidade do fato e nenhuma urgência naquela idiotia. Vendo Antônio olhar pela janela, foi até a despensa procurar Nico, no terreiro, chiqueiro, paiol, milharal.
-- Nico sair desse jeito? Sem falar nada?
-- Saiu não, Maria. Ele foi embora no coador.
-- Fala direito, Antônio.
-- Ele tava passando o pó, hora que botou a água, sumiu.
-- Daqui a pouco ele chega.
-- Não mexe no bule, deixa do jeito que tá para ele voltar.
-(...)
-FUEGO, Andrea del. Os Malaquias. Rio de Janeiro: Língua Geral, 2010.
-Releia o trecho:
-Nico apoiou a caneca de água na pia, Antônio fechou os olhos para fortalecer o aroma.
-A construção destacada caracteriza-se como</t>
+          <t>Felipe decidiu escrever uma receita de bolo de chocolate para seu amigo. No entanto para desafiá-lo, utilizou diferentes representações numéricas. A receita ficou da seguinte maneira:
+Qual das seguintes afirmações é verdadeira sobre os conjuntos numéricos que representam as quantidades dos ingredientes na receita escrita por Felipe?</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>substantivo concreto, por se referir a uma entidade real.</t>
+          <t>Todos os números são irracionais, exceto a quantidade de ovos.</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>locução adjetiva, por caracterizar o substantivo “caneca”.</t>
+          <t>Todos os números são inteiros.</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>adjetivo impróprio, por caracterizar o substantivo “água”.</t>
+          <t>Todos os números são racionais, exceto a quantidade de fermento em pó.</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>sintagma verbal, por se referir à relação de posse entre a caneca e a água.</t>
+          <t>Todos os números são racionais, mas não inteiros.</t>
         </is>
       </c>
       <c r="F488" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>A construção preposicionada “de água” caracteriza o substantivo “a caneca”, especificando-o, constituindo, assim, uma locução adjetiva.</t>
+          <t>Vamos analisar cada quantidade de ingredientes:
+ xícaras de farinha de trigo: equivalente a 2,5, que é um número racional, pois pode ser escrito como a divisão de dois números inteiros.
+ xícaras de açúcar: dízima periódica equivalente a , que é um número racional, pois pode ser escrito como a divisão de dois números inteiros.
+ ovos: equivalente a 3, que é número inteiro e natural, e, portanto, racional.
+ xícaras de leite: equivalente a 4, que é um número inteiro e natural, e, portanto, racional.
+ xícara de óleo: número racional, pois pode ser escrito como a divisão de dois números inteiros.
+ xícara de chocolate em pó: número racional.
+ gramas de fermento em pó: número irracional, pois não pode ser escrito como a divisão de dois números inteiros.
+Portanto, todos os números são racionais, exceto a quantidade de fermento em pó, que é um número irracional.</t>
         </is>
       </c>
       <c r="H488" t="inlineStr">
@@ -26012,53 +26024,55 @@
       </c>
       <c r="I488" t="inlineStr">
         <is>
-          <t>Português</t>
-        </is>
-      </c>
-      <c r="J488" t="inlineStr"/>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="J488" t="inlineStr">
+        <is>
+          <t>8a_ph01_mat_05.png</t>
+        </is>
+      </c>
       <c r="K488" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>Posêidon estava sentado à sua escrivaninha e fazia contas. A administração de todas as águas dava-lhe um trabalho interminável. Poderia ter quantos auxiliares quisesse, possuía muitos, aliás; mas, uma vez que levava muito a sério seu ofício, revia mais uma vez tudo e sendo assim os auxiliares o ajudavam pouco. Não se pode dizer que o trabalho o alegrasse; na verdade ele o realizava só porque lhe fora imposto; já havia solicitado muitas vezes tarefas mais prazerosas, conforme se expressava; mas, sempre que lhe faziam propostas diferentes, era manifesto que nada o agradava tanto quanto o cargo que até então ocupara. Era muito difícil, além disso, encontrar outra coisa para ele. Com efeito, era impossível atribuir-lhe algo como um determinado mar; sem mencionar que, neste caso, o trabalho de calcular não seria apenas maior, mas também mesquinho, o grande Posêidon só podia receber um posto que fosse dominante. E, se lhe ofereciam um ofício fora da água, sentia-se mal só com a ideia: seu alento divino se descontrolava, o tórax de bronze oscilava. De resto, não levavam realmente a sério as queixas que fazia; quando um poderoso importuna, é preciso dar a impressão de tentar ceder mesmo nas questões mais sem perspectiva: ninguém pensava em remover de fato Posêidon do seu posto; desde o início mais remoto tinha sido destinado a ser o rei dos mares e assim devia permanecer.
-[...]
-KAFKA, Franz. Posêidon. In: Narrativas do Espólio. São Paulo: Companhia das Letras, 2002.
-Observe os vocábulos em destaque na narrativa do escritor tcheco Franz Kafka. Embora todos sejam adjetivos, os que estão associados diretamente a substantivos são</t>
+          <t>No conjunto dos números reais, existem os números racionais, que contêm os números naturais e inteiros. Mas dentro do conjunto dos números reais também encontramos o subconjunto dos irracionais.
+Os números irracionais têm a característica de</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>“diferentes”, “difícil” e “impossível”.</t>
+          <t>serem infinitos nas casas decimais.</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>“interminável”, “difícil” e “prazerosas”.</t>
+          <t>serem raízes quadradas.</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>“prazerosas”, “diferentes” e “impossível”</t>
+          <t>serem frações.</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>“interminável”, “prazerosas” e “diferentes”.</t>
+          <t>serem números entre 0 e 1.</t>
         </is>
       </c>
       <c r="F489" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t>"Interminável" está associado a "trabalho", "prazerosas" está associado a "tarefas" e "diferentes" está associado a "propostas". Todos esses adjetivos estão diretamente ligados a substantivos, descrevendo suas características de forma clara e direta. Já os adjetivos “difícil” e “impossível” não se ligam a substantivos expressos no texto.</t>
+          <t>Os números irracionais são aqueles que não podem ser expressos como frações de inteiros e possuem expansões decimais que se estendem infinitamente sem se repetirem. Isso significa que, ao serem representados na forma decimal, seus dígitos continuam indefinidamente sem formar um padrão regular.</t>
         </is>
       </c>
       <c r="H489" t="inlineStr">
@@ -26068,55 +26082,51 @@
       </c>
       <c r="I489" t="inlineStr">
         <is>
-          <t>Português</t>
+          <t>Matemática</t>
         </is>
       </c>
       <c r="J489" t="inlineStr"/>
       <c r="K489" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>Posêidon estava sentado à sua escrivaninha e fazia contas. A administração de todas as águas dava-lhe um trabalho interminável. Poderia ter quantos auxiliares quisesse, possuía muitos, aliás; mas, uma vez que levava muito a sério seu ofício, revia mais uma vez tudo e sendo assim os auxiliares o ajudavam pouco. Não se pode dizer que o trabalho o alegrasse; na verdade ele o realizava só porque lhe fora imposto; já havia solicitado muitas vezes tarefas mais prazerosas, conforme se expressava; mas, sempre que lhe faziam propostas diferentes, era manifesto que nada o agradava tanto quanto o cargo que até então ocupara. Era muito difícil, além disso, encontrar outra coisa para ele. Com efeito, era impossível atribuir-lhe algo como um determinado mar; sem mencionar que, neste caso, o trabalho de calcular não seria apenas maior, mas também mesquinho, o grande Posêidon só podia receber um posto que fosse dominante. E, se lhe ofereciam um ofício fora da água, sentia-se mal só com a ideia: seu alento divino se descontrolava, o tórax de bronze oscilava. De resto, não levavam realmente a sério as queixas que fazia; quando um poderoso importuna, é preciso dar a impressão de tentar ceder mesmo nas questões mais sem perspectiva: ninguém pensava em remover de fato Posêidon do seu posto; desde o início mais remoto tinha sido destinado a ser o rei dos mares e assim devia permanecer.
-[...]
-KAFKA, Franz. Posêidon. In: Narrativas do Espólio. São Paulo: Companhia das Letras, 2002.
-Releia:
-Posêidon estava sentado à sua escrivaninha e fazia contas.
-Quanto ao seu sentido, a flexão de grau do substantivo destacado</t>
+          <t>O número π é usado em cálculos que envolvem círculos e circunferências. Ele é a razão entre o comprimento de uma circunferência e seu diâmetro. 
+Pode-se afirmar que π é um número</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>indica a mudança de dimensão de um substantivo primitivo.</t>
+          <t>racional, com infinitas casas decimais.</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>sintetiza um modo afetuoso de se referir ao substantivo “escrivão”.</t>
+          <t>natural, cuja representação numérica mais utilizada é 3.</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>compõe uma maneira irônica de se referir ao substantivo “escrivão”.</t>
+          <t>irracional, com infinitas casas decimais, sendo as primeiras 3,14159...</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>é parte integral do substantivo e não se refere necessariamente à sua dimensão.</t>
+          <t>racional, com uma quantidade finita de casas decimais, sendo seu valor  3,14.</t>
         </is>
       </c>
       <c r="F490" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G490" t="inlineStr">
         <is>
-          <t>A flexão de grau do substantivo “escrivaninha” não se refere necessariamente a uma mudança de tamanho/dimensão do substantivo, mas é parte integral do seu significado de mesa apropriada para se escrever.</t>
+          <t>O número π é irracional, e, portanto, possui infinitas casas decimais.</t>
         </is>
       </c>
       <c r="H490" t="inlineStr">
@@ -26126,53 +26136,51 @@
       </c>
       <c r="I490" t="inlineStr">
         <is>
-          <t>Português</t>
+          <t>Matemática</t>
         </is>
       </c>
       <c r="J490" t="inlineStr"/>
       <c r="K490" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>Posêidon estava sentado à sua escrivaninha e fazia contas. A administração de todas as águas dava-lhe um trabalho interminável. Poderia ter quantos auxiliares quisesse, possuía muitos, aliás; mas, uma vez que levava muito a sério seu ofício, revia mais uma vez tudo e sendo assim os auxiliares o ajudavam pouco. Não se pode dizer que o trabalho o alegrasse; na verdade ele o realizava só porque lhe fora imposto; já havia solicitado muitas vezes tarefas mais prazerosas, conforme se expressava; mas, sempre que lhe faziam propostas diferentes, era manifesto que nada o agradava tanto quanto o cargo que até então ocupara. Era muito difícil, além disso, encontrar outra coisa para ele. Com efeito, era impossível atribuir-lhe algo como um determinado mar; sem mencionar que, neste caso, o trabalho de calcular não seria apenas maior, mas também mesquinho, o grande Posêidon só podia receber um posto que fosse dominante. E, se lhe ofereciam um ofício fora da água, sentia-se mal só com a ideia: seu alento divino se descontrolava, o tórax de bronze oscilava. De resto, não levavam realmente a sério as queixas que fazia; quando um poderoso importuna, é preciso dar a impressão de tentar ceder mesmo nas questões mais sem perspectiva: ninguém pensava em remover de fato Posêidon do seu posto; desde o início mais remoto tinha sido destinado a ser o rei dos mares e assim devia permanecer.
-[...]
-KAFKA, Franz. Posêidon. In: Narrativas do Espólio. São Paulo: Companhia das Letras, 2002.
-Observe o uso dos artigos em destaque em dois trechos finais do texto: “quando um poderoso importuna” e “destinado a ser o rei dos mares”. A utilização desses artigos trazem ao texto sentidos opostos. Tais sentidos são, respectivamente,</t>
+          <t>Durante a resolução de uma questão, Ana chega na seguinte subtração: .
+O resultado dessa subtração é um número</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>de especificação e generalização.</t>
+          <t>natural.</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>de figurativização e indefinição.</t>
+          <t>inteiro.</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>de generalização e especificação.</t>
+          <t>racional.</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>de definição e concretização.</t>
+          <t>irracional.</t>
         </is>
       </c>
       <c r="F491" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>O artigo indefinido “um” traz uma generalização: um poderoso dentre vários; já o artigo definido “o” traz uma especificação: o único rei dos mares, Posêidon.</t>
+          <t>é um número irracional, com infinitas casas decimais, que pode ser representado como 1,4142135624... Portanto, ao subtrairmos 1,414 de , temos 0,0002135624..., que ainda é um número irracional, pois não pode ser escrito como uma razão entre dois inteiros.</t>
         </is>
       </c>
       <c r="H491" t="inlineStr">
@@ -26182,54 +26190,56 @@
       </c>
       <c r="I491" t="inlineStr">
         <is>
-          <t>Português</t>
-        </is>
-      </c>
-      <c r="J491" t="inlineStr"/>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="J491" t="inlineStr">
+        <is>
+          <t>8a_ph01_mat_09.png</t>
+        </is>
+      </c>
       <c r="K491" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>Em um parque, duas fontes de água começam a jorrar ao mesmo tempo. A primeira fonte jorra água a cada 6 minutos, enquanto a segunda jorra a cada 8 minutos.
-Em quantos minutos as duas fontes jorrarão água simultaneamente novamente após começarem a jorrar água juntas?</t>
+          <t>Números que possuem a característica de ter raízes quadradas exatas desempenham um papel importante em diversas áreas da matemática, incluindo álgebra e geometria, ajudando na resolução de problemas relacionados a áreas e distâncias.
+Dessa forma, considerando os números   , é correto afirmar que</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>ambos são irracionais.</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>é irracional e  é racional.</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>é racional e  é irracional.</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>Ambos são racionais.</t>
         </is>
       </c>
       <c r="F492" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>Para calcular o tempo em que as fontes irão jorrar água simultaneamente, é preciso calcular o Mínimo Múltiplo Comum (MMC) de 6 minutos e 8 minutos. Para calcular o MMC, podemos listar os múltiplos:
-Múltiplos de 6: 6, 12, 18, 24, 30, ...
-Múltiplos de 8: 8, 16, 24, 32, ...
-O menor múltiplo que aparece em ambas as listas é 24. Portanto, as duas fontes jorrarão água simultaneamente novamente em 24 minutos.</t>
+          <t>é igual a = 0,5, que é um número racional, pois resulta da divisão de dois inteiros.
+, que é um número cuja parte decimal é infinita e não se repete, sendo irracional.</t>
         </is>
       </c>
       <c r="H492" t="inlineStr">
@@ -26242,514 +26252,14 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="J492" t="inlineStr"/>
+      <c r="J492" t="inlineStr">
+        <is>
+          <t>8a_ph01_mat_10.png</t>
+        </is>
+      </c>
       <c r="K492" t="inlineStr">
         <is>
-          <t>7ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="493">
-      <c r="A493" t="inlineStr">
-        <is>
-          <t>Em uma das etapas de uma competição matemática os participantes precisavam efetuar a soma dos valores que um atleta correu durante três percursos, sendo eles: 12 km na primeira volta, 15 km na segunda e 10 km na terceira. 
-Dois dos participantes estruturaram a soma da seguinte maneira:
-Qual dos participantes estruturou a expressão numérica corretamente?</t>
-        </is>
-      </c>
-      <c r="B493" t="inlineStr">
-        <is>
-          <t>Ambos, uma vez que pela propriedade associativa a ordem das parcelas não altera a soma.</t>
-        </is>
-      </c>
-      <c r="C493" t="inlineStr">
-        <is>
-          <t>Ambos, uma vez que pela propriedade comutativa a ordem dos números não altera a soma.</t>
-        </is>
-      </c>
-      <c r="D493" t="inlineStr">
-        <is>
-          <t>Apenas o participante 1, uma vez que a soma deve ser feita da esquerda para a direita.</t>
-        </is>
-      </c>
-      <c r="E493" t="inlineStr">
-        <is>
-          <t>Apenas o participante 2, uma vez que a soma deve ser feita da direita para a esquerda.</t>
-        </is>
-      </c>
-      <c r="F493" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G493" t="inlineStr">
-        <is>
-          <t>Ambos os participantes estruturaram a expressão corretamente. A propriedade associativa da adição afirma que a forma como os números são agrupados não altera a soma. Portanto, (12 + 10) + 15 e 12 + (10 + 15) resultarão no mesmo valor, que é 37 km.</t>
-        </is>
-      </c>
-      <c r="H493" t="inlineStr">
-        <is>
-          <t>PH01</t>
-        </is>
-      </c>
-      <c r="I493" t="inlineStr">
-        <is>
-          <t>Matemática</t>
-        </is>
-      </c>
-      <c r="J493" t="inlineStr">
-        <is>
-          <t>ph01_mat_02.png</t>
-        </is>
-      </c>
-      <c r="K493" t="inlineStr">
-        <is>
-          <t>7ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="494">
-      <c r="A494" t="inlineStr">
-        <is>
-          <t>Na multiplicação, existe um número que quando multiplicado por qualquer outro número, não altera o valor desse número. Na soma, também há um número que somado a qualquer outro não altera seu valor. Esses números são chamados de elemento neutro. 
-O elemento neutro na multiplicação e na soma, é respectivamente</t>
-        </is>
-      </c>
-      <c r="B494" t="inlineStr">
-        <is>
-          <t>1 e 0</t>
-        </is>
-      </c>
-      <c r="C494" t="inlineStr">
-        <is>
-          <t>0 e 0</t>
-        </is>
-      </c>
-      <c r="D494" t="inlineStr">
-        <is>
-          <t>1 e 1</t>
-        </is>
-      </c>
-      <c r="E494" t="inlineStr">
-        <is>
-          <t>0 e 1</t>
-        </is>
-      </c>
-      <c r="F494" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G494" t="inlineStr">
-        <is>
-          <t>Na multiplicação, o número que, quando multiplicado por qualquer outro número, não altera o valor desse número é o 1. Este número é conhecido como o elemento neutro da multiplicação. Por exemplo:
-5 × 1 = 5
-Na soma, o número que, quando somado a qualquer outro número, não altera o valor desse número é o 0. Este número é conhecido como o elemento neutro da soma. Por exemplo:
-7 + 0 = 7
-Portanto, os elementos neutros na multiplicação e na soma são, respectivamente, 1 e 0.</t>
-        </is>
-      </c>
-      <c r="H494" t="inlineStr">
-        <is>
-          <t>PH01</t>
-        </is>
-      </c>
-      <c r="I494" t="inlineStr">
-        <is>
-          <t>Matemática</t>
-        </is>
-      </c>
-      <c r="J494" t="inlineStr"/>
-      <c r="K494" t="inlineStr">
-        <is>
-          <t>7ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="495">
-      <c r="A495" t="inlineStr">
-        <is>
-          <t>Durante a preparação de uma grande festa, os organizadores precisavam organizar as cadeiras em várias filas. Eles tinham 4 filas, e em cada fila, colocaram 5 grupos de 6 cadeiras. Dois organizadores decidiram calcular o total de cadeiras de maneiras diferentes. O organizador A agrupou as cadeiras por fila primeiro e, em seguida, multiplicou pelo número de grupos de cadeiras. O organizador B fez o oposto, agrupando primeiro os grupos de cadeiras e depois multiplicando pelo número de filas. No final, ambos chegaram ao mesmo total de cadeiras.
-Qual propriedade da multiplicação justifica que ambos os organizadores obtiveram o mesmo resultado?</t>
-        </is>
-      </c>
-      <c r="B495" t="inlineStr">
-        <is>
-          <t>Propriedade Comutativa.</t>
-        </is>
-      </c>
-      <c r="C495" t="inlineStr">
-        <is>
-          <t>Propriedade Distributiva.</t>
-        </is>
-      </c>
-      <c r="D495" t="inlineStr">
-        <is>
-          <t>Propriedade Associativa.</t>
-        </is>
-      </c>
-      <c r="E495" t="inlineStr">
-        <is>
-          <t>Elemento Neutro.</t>
-        </is>
-      </c>
-      <c r="F495" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G495" t="inlineStr">
-        <is>
-          <t>A propriedade associativa da multiplicação afirma que, independentemente de como os números são agrupados, o produto permanece o mesmo. Nesse caso, tanto (4 × 5) × 6 quanto 4 × (5 × 6) resultam no mesmo total de cadeiras: 120.</t>
-        </is>
-      </c>
-      <c r="H495" t="inlineStr">
-        <is>
-          <t>PH01</t>
-        </is>
-      </c>
-      <c r="I495" t="inlineStr">
-        <is>
-          <t>Matemática</t>
-        </is>
-      </c>
-      <c r="J495" t="inlineStr"/>
-      <c r="K495" t="inlineStr">
-        <is>
-          <t>7ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="496">
-      <c r="A496" t="inlineStr">
-        <is>
-          <t>Pedro está organizando uma festa e comprou três pacotes de balões. O primeiro pacote contém 120 balões amarelos, o segundo contém 180 balões verdes e o terceiro contém 240 balões brancos. Ele quer dividir todos os balões em grupos de igual tamanho, utilizando o maior número possível de balões em cada grupo.
-Qual será o número de balões em cada grupo?</t>
-        </is>
-      </c>
-      <c r="B496" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="C496" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="D496" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="E496" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="F496" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G496" t="inlineStr">
-        <is>
-          <t>Para encontrar o maior número possível de balões em cada grupo, é preciso determinar o Máximo Divisor Comum (MDC) dos três números: 120, 180 e 240. 
-Primeiro, deve-se fatorar cada número em seus fatores primos:
-120 = 23 x 3 x 5
-180 = 22 x 32 x 5
-120 = 24 x 3 x 5
-O MDC é o produtos dos menores expoentes dos fatores comuns:
-Fator 2: menor expoente é 2
-Fator 3: menor expoente é 1
-Fator 5: menor expoente é 1
-Portanto, o MDC é: 
-22 x 3 x 5 = 4 x 3 x 5 = 60.
-Portanto, o número de balões em cada grupo será 60.</t>
-        </is>
-      </c>
-      <c r="H496" t="inlineStr">
-        <is>
-          <t>PH01</t>
-        </is>
-      </c>
-      <c r="I496" t="inlineStr">
-        <is>
-          <t>Matemática</t>
-        </is>
-      </c>
-      <c r="J496" t="inlineStr"/>
-      <c r="K496" t="inlineStr">
-        <is>
-          <t>7ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="497">
-      <c r="A497" t="inlineStr">
-        <is>
-          <t>Um colecionador possui 300 figurinhas ilustradas. Ao comprar doze pacotes, com dez figurinhas cada, ele percebe que cada pacote tinha uma figurinha repetida e, por serem repetidas, não poderiam ser contabilizadas em sua coleção. Sendo assim, sua coleção possou a ter:</t>
-        </is>
-      </c>
-      <c r="B497" t="inlineStr">
-        <is>
-          <t>310 figurinhas</t>
-        </is>
-      </c>
-      <c r="C497" t="inlineStr">
-        <is>
-          <t>312 figurinhas</t>
-        </is>
-      </c>
-      <c r="D497" t="inlineStr">
-        <is>
-          <t>408 figurinhas</t>
-        </is>
-      </c>
-      <c r="E497" t="inlineStr">
-        <is>
-          <t>420 figurinhas</t>
-        </is>
-      </c>
-      <c r="F497" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G497" t="inlineStr">
-        <is>
-          <t>300 + 12 x (10 - 1) = 300 + 12 x 9 = 300 + 108 = 408</t>
-        </is>
-      </c>
-      <c r="H497" t="inlineStr">
-        <is>
-          <t>PH01</t>
-        </is>
-      </c>
-      <c r="I497" t="inlineStr">
-        <is>
-          <t>Matemática</t>
-        </is>
-      </c>
-      <c r="J497" t="inlineStr"/>
-      <c r="K497" t="inlineStr">
-        <is>
-          <t>7ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="498">
-      <c r="A498" t="inlineStr">
-        <is>
-          <t>Em uma escola, a turma do 7º ano começou o ano com 35 alunos e durante o ano recebeu mais 5 alunos. Se no fim do ano 10 alunos ficaram de recuperação, a quantidade de alunos que foram aprovados direto, sem passar pela recuperação, foi:</t>
-        </is>
-      </c>
-      <c r="B498" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="C498" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="D498" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E498" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F498" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G498" t="inlineStr">
-        <is>
-          <t>(35 + 5) – 10 = 40 – 10 = 30</t>
-        </is>
-      </c>
-      <c r="H498" t="inlineStr">
-        <is>
-          <t>PH01</t>
-        </is>
-      </c>
-      <c r="I498" t="inlineStr">
-        <is>
-          <t>Matemática</t>
-        </is>
-      </c>
-      <c r="J498" t="inlineStr"/>
-      <c r="K498" t="inlineStr">
-        <is>
-          <t>7ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="499">
-      <c r="A499" t="inlineStr">
-        <is>
-          <t>Em uma campanha de doação de brinquedos, as quatro turmas do ensino fundamental de uma escola conseguiram arrecadar 345 bonecos. Se o 6º ano doou 65 bonecos, o 8º ano doou 95 e o 9º ano 83 bonecos, então o 7º ano doou:</t>
-        </is>
-      </c>
-      <c r="B499" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="C499" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="D499" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="E499" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="F499" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G499" t="inlineStr">
-        <is>
-          <t>Total da arrecadação (4 turmas)  → de 345 bonecos
-6° + 8° + 9° →  65 + 95 + 83 = 243 bonecos
-7° ano → 345 – 243 = 102 bonecos</t>
-        </is>
-      </c>
-      <c r="H499" t="inlineStr">
-        <is>
-          <t>PH01</t>
-        </is>
-      </c>
-      <c r="I499" t="inlineStr">
-        <is>
-          <t>Matemática</t>
-        </is>
-      </c>
-      <c r="J499" t="inlineStr"/>
-      <c r="K499" t="inlineStr">
-        <is>
-          <t>7ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="500">
-      <c r="A500" t="inlineStr">
-        <is>
-          <t>Ao passar pelo caixa de um supermercado, dona Maria percebe que suas compras totalizaram R$ 243,00 e, para pagar, usou três notas de R$ 100,00. Sendo assim, o troco que dona Maria receberá será de:</t>
-        </is>
-      </c>
-      <c r="B500" t="inlineStr">
-        <is>
-          <t>R$ 47,00</t>
-        </is>
-      </c>
-      <c r="C500" t="inlineStr">
-        <is>
-          <t>R$ 53,00</t>
-        </is>
-      </c>
-      <c r="D500" t="inlineStr">
-        <is>
-          <t>R$ 57,00</t>
-        </is>
-      </c>
-      <c r="E500" t="inlineStr">
-        <is>
-          <t>R$ 60,00</t>
-        </is>
-      </c>
-      <c r="F500" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G500" t="inlineStr">
-        <is>
-          <t>3 x 100 – 243
-300 – 243 = R$ 57,00</t>
-        </is>
-      </c>
-      <c r="H500" t="inlineStr">
-        <is>
-          <t>PH01</t>
-        </is>
-      </c>
-      <c r="I500" t="inlineStr">
-        <is>
-          <t>Matemática</t>
-        </is>
-      </c>
-      <c r="J500" t="inlineStr"/>
-      <c r="K500" t="inlineStr">
-        <is>
-          <t>7ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="501">
-      <c r="A501" t="inlineStr">
-        <is>
-          <t>Em uma determinada atividade em sala de aula, o professor de matemática pede que seus alunos reescrevam a seguinte expressão numérica, sem que alterem seu resultado:  (4+5) + 2 + 3x(1+7). Um aluno que conseguiu reescrever corretamente, mostrou a seguinte expressão ao professor:</t>
-        </is>
-      </c>
-      <c r="B501" t="inlineStr">
-        <is>
-          <t>2x(4+5) + 3+(1+7)</t>
-        </is>
-      </c>
-      <c r="C501" t="inlineStr">
-        <is>
-          <t>4 + (5+2) +  (3+1)x7</t>
-        </is>
-      </c>
-      <c r="D501" t="inlineStr">
-        <is>
-          <t>(4+5) + 5x(1+7)</t>
-        </is>
-      </c>
-      <c r="E501" t="inlineStr">
-        <is>
-          <t>4 + (5+2) + 3x1 + 3x7</t>
-        </is>
-      </c>
-      <c r="F501" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G501" t="inlineStr">
-        <is>
-          <t>Uma outra maneira de escrever esta expressão é 4 + (5+2) + 3x1 + 3x7.</t>
-        </is>
-      </c>
-      <c r="H501" t="inlineStr">
-        <is>
-          <t>PH01</t>
-        </is>
-      </c>
-      <c r="I501" t="inlineStr">
-        <is>
-          <t>Matemática</t>
-        </is>
-      </c>
-      <c r="J501" t="inlineStr"/>
-      <c r="K501" t="inlineStr">
-        <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>

--- a/questoes.xlsx
+++ b/questoes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L501"/>
+  <dimension ref="A1:L551"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23982,7 +23982,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K452" t="inlineStr"/>
       <c r="L452" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -24041,7 +24040,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K453" t="inlineStr"/>
       <c r="L453" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -24101,7 +24099,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K454" t="inlineStr"/>
       <c r="L454" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -24163,7 +24160,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K455" t="inlineStr"/>
       <c r="L455" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -24222,7 +24218,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K456" t="inlineStr"/>
       <c r="L456" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -24345,7 +24340,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K458" t="inlineStr"/>
       <c r="L458" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -24411,7 +24405,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K459" t="inlineStr"/>
       <c r="L459" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -24532,7 +24525,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K461" t="inlineStr"/>
       <c r="L461" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -24592,7 +24584,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K462" t="inlineStr"/>
       <c r="L462" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -24653,7 +24644,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K463" t="inlineStr"/>
       <c r="L463" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -24713,7 +24703,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K464" t="inlineStr"/>
       <c r="L464" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -24774,7 +24763,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K465" t="inlineStr"/>
       <c r="L465" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -24836,7 +24824,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K466" t="inlineStr"/>
       <c r="L466" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -24896,7 +24883,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K467" t="inlineStr"/>
       <c r="L467" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -25208,7 +25194,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K472" t="inlineStr"/>
       <c r="L472" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -25267,7 +25252,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K473" t="inlineStr"/>
       <c r="L473" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -25327,7 +25311,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K474" t="inlineStr"/>
       <c r="L474" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -25386,7 +25369,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K475" t="inlineStr"/>
       <c r="L475" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -25445,7 +25427,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K476" t="inlineStr"/>
       <c r="L476" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -25571,7 +25552,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K478" t="inlineStr"/>
       <c r="L478" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -25634,7 +25614,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K479" t="inlineStr"/>
       <c r="L479" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -25697,7 +25676,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K480" t="inlineStr"/>
       <c r="L480" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -25820,7 +25798,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K482" t="inlineStr"/>
       <c r="L482" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -25881,7 +25858,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K483" t="inlineStr"/>
       <c r="L483" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -25940,7 +25916,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K484" t="inlineStr"/>
       <c r="L484" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -26063,7 +26038,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K486" t="inlineStr"/>
       <c r="L486" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -26130,7 +26104,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K487" t="inlineStr"/>
       <c r="L487" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -26197,7 +26170,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K488" t="inlineStr"/>
       <c r="L488" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -26265,7 +26237,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K489" t="inlineStr"/>
       <c r="L489" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -26333,7 +26304,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K490" t="inlineStr"/>
       <c r="L490" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -26401,7 +26371,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K491" t="inlineStr"/>
       <c r="L491" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -26591,7 +26560,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K494" t="inlineStr"/>
       <c r="L494" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -26650,7 +26618,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K495" t="inlineStr"/>
       <c r="L495" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -26780,7 +26747,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K497" t="inlineStr"/>
       <c r="L497" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -26907,7 +26873,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K499" t="inlineStr"/>
       <c r="L499" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -27038,6 +27003,2884 @@
       <c r="L501" t="inlineStr">
         <is>
           <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>Os fungos são organismos que podem ser unicelulares ou pluricelulares. Eles desempenham papéis importantes nos ecossistemas, como decompositores, e podem ser utilizados na produção de alimentos e medicamentos. Além disso, alguns fungos são patogênicos e podem causar doenças em plantas, animais e seres humanos.
+Qual das seguintes características é verdadeira para todos os fungos?</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>São autotróficos.</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>São procariontes.</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>São eucariontes.</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>São fotossintetizantes.</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr"/>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>Os fungos são organismos eucariontes, ou seja, possuem células com núcleo delimitado por membrana. Eles podem ser unicelulares ou pluricelulares, mas não são autotróficos nem procariontes.</t>
+        </is>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>PH01</t>
+        </is>
+      </c>
+      <c r="J502" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K502" t="inlineStr"/>
+      <c r="L502" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>As bactérias são organismos unicelulares e procariontes, presentes em diversos ambientes, como solo, água e até no corpo humano. Elas desempenham papéis fundamentais na natureza.
+Uma das principais funções ecológicas das bactérias decompositoras nos ecossistemas é a de</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>transformar dióxido de carbono em substâncias orgânicas.</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>transformar luz solar em energia química.</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>transformar matéria orgânica em substâncias inorgânicas.</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>transformar oxigênio em gás carbônico.</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr"/>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>As bactérias decompositoras têm a função crucial de transformar matéria orgânica, como restos de plantas e animais mortos, em substâncias inorgânicas, como água, dióxido de carbono e sais minerais. Esse processo é essencial para a reciclagem de nutrientes nos ecossistemas, permitindo que esses nutrientes sejam reutilizados por plantas e outros organismos autotróficos.</t>
+        </is>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>PH01</t>
+        </is>
+      </c>
+      <c r="J503" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K503" t="inlineStr"/>
+      <c r="L503" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>Os vírus são partículas acelulares constituídas por material genético (DNA ou RNA) envolto por uma cápsula proteica chamada capsídeo. Alguns vírus também possuem um envelope lipídico. No entanto para que possam sobreviver precisam de uma condição específica.
+Essa condição é a presença de um(a)</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>ambiente com luz solar.</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>célula hospedeira.</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>fonte de energia externa.</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>temperatura ideal para crescimento.</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr"/>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>Os vírus são considerados parasitas intracelulares obrigatórios porque necessitam de uma célula hospedeira para se replicar. Fora das células hospedeiras, eles são inertes e incapazes de realizar qualquer atividade vital. Portanto, a presença de uma célula hospedeira é uma condição essencial para a sobrevivência e replicação dos vírus.</t>
+        </is>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>PH01</t>
+        </is>
+      </c>
+      <c r="J504" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K504" t="inlineStr"/>
+      <c r="L504" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>As algas são organismos eucariontes, autotróficos e fotossintetizantes. Elas podem ser unicelulares ou pluricelulares e são encontradas em ambientes aquáticos e terrestres úmidos. 
+Qual é a principal função ecológica das algas nos ecossistemas aquáticos?</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>Decomposição de matéria orgânica.</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>Produção de oxigênio.</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>Fixação de nitrogênio.</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>Parasitismo de outros organismos.</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr"/>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>A principal função ecológica das algas nos ecossistemas aquáticos é a produção de oxigênio através da fotossíntese, além de servir como base das cadeias alimentares.</t>
+        </is>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>PH01</t>
+        </is>
+      </c>
+      <c r="J505" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K505" t="inlineStr"/>
+      <c r="L505" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>Os protozoários são organismos unicelulares e heterotróficos que podem ser encontrados em diversos tipos de ambiente, isolados ou em colônias. Podem ter vida livre ou associar-se a outros seres vivos. Algumas espécies são parasitas e podem causar doenças no ser humano, como a malária e a doença de Chagas.
+Quais dos seguintes organismos são exemplos de protozoários?</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>Amebas e paramécios.</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>Amebas e cogumelos.</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>Bactérias e cianobactérias.</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>Paramécios e bactérias.</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr"/>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>São exemplos de protozoários: as amebas e os paramécios. Eles podem ser encontrados em diversos ambientes e algumas espécies são parasitas que causam doenças em seres humanos. Fungos, algas, cianobactérias, plantas e animais não são classificados como protozoários.</t>
+        </is>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>PH01</t>
+        </is>
+      </c>
+      <c r="J506" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K506" t="inlineStr"/>
+      <c r="L506" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>Para um organismo ser considerado vivo, algumas características devem estar presentes. Observe a imagem a seguir.
+Assinale a alternativa que apresenta características do ser vivo apresentado na imagem, que o diferem de um ser não vivo.</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>Nada e nasce.</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>Possui casco duro e se alimenta.</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>Pode se reproduzir e morrer.</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>Possui metabolismo e possui nadadeiras.</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr"/>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>A tartaruga é caracterizada como um ser vivo, pois possui metabolismo, se alimenta, nasce, pode se reproduzir e morre.</t>
+        </is>
+      </c>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>PH01</t>
+        </is>
+      </c>
+      <c r="J507" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>ph01_cie_06.png</t>
+        </is>
+      </c>
+      <c r="L507" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>Observe a imagem a seguir.
+Relacione o organismo autótrofo e o heterótrofo com os processos de fotossíntese e respiração celular, marcando a alternativa correta.</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>A árvore é autotrófica e faz fotossíntese.</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>O javali é heterotrófico e faz fotossíntese.</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>O javali é autotrófico e não produz seu próprio alimento.</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>A árvore é autotrófica e não produz seu próprio alimento.</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr"/>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>A árvore é autótrofa e produz seu próprio alimento por meio da fotossíntese; enquanto o javali é heterótrofo, pois depende de outros seres vivos para se alimentar e produzir energia por meio da respiração celular.</t>
+        </is>
+      </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>PH01</t>
+        </is>
+      </c>
+      <c r="J508" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>ph01_cie_07.png</t>
+        </is>
+      </c>
+      <c r="L508" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>Um pesquisador estava analisando uma lâmina ao microscópio e observou que as células eram muito simples e não possuíam núcleo individualizado. Com base nessas informações, marque a alternativa com o tipo de célula que estava presente na lâmina.</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>Procariontes.</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>Eucariontes.</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>Pluricelular.</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>Acelular.</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr"/>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>Na lâmina estavam presentes células procariontes, pois essas não possuem núcleo individualizado.</t>
+        </is>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>PH01</t>
+        </is>
+      </c>
+      <c r="J509" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K509" t="inlineStr"/>
+      <c r="L509" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>Leia o texto a seguir e responda a questão.
+Seres chamados "piratas" biológicos invadem as células, saqueiam seus nutrientes e utilizam as reações químicas das mesmas para se reproduzir. Logo em seguida, os descendentes dos invasores transmitem-se a outras células, provocando danos devastadores. A estes danos, dá-se o nome de virose, como a gripe, herpes, dengue, AIDS, etc.
+(SCOTT, Andrew. Piratas da Célula. Adaptado.)
+Certos agentes infecciosos são formados apenas por material genético protegido por uma cápsula de proteína. Estes seres só conseguem se reproduzir quando invadem uma célula e utilizam suas estruturas, terminando por destruí-la. Estes agentes são</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>bactérias.</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>fungos.</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>protozoários.</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>vírus.</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr"/>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>Os vírus são parasitas intracelulares e, por isso, precisam invadir células para se reproduzir e são estruturas muito simples, formadas de cápsula e material genético.</t>
+        </is>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>PH01</t>
+        </is>
+      </c>
+      <c r="J510" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K510" t="inlineStr"/>
+      <c r="L510" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>Os vírus são seres acelulares e possuem uma estrutura muito simples, eles são constituídos de:</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>membrana, citoplasma e núcleo.</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>capsídeo e material genético.</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>célula e Material genético.</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>capsídeo e núcleo.</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr"/>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>Os vírus são constituídos de capsídeo e material genético (DNA ou RNA).</t>
+        </is>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>PH01</t>
+        </is>
+      </c>
+      <c r="J511" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K511" t="inlineStr"/>
+      <c r="L511" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>O Brasil é um dos maiores países em extensão territorial no mundo. Sabendo disso, qual das alternativas a seguir melhor explica como as características socioculturais estão distribuídas no território brasileiro?</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>O território brasileiro é culturalmente uniforme, com as mesmas tradições e costumes em todas as regiões.</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>Cada região brasileira possui paisagens e culturas distintas, influenciadas por fatores históricos, geográficos e climáticos.</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>O Brasil possui poucas variações culturais entre suas regiões, com pequenas diferenças na culinária e no idioma.</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>A diversidade sociocultural do Brasil não está ligada ao território, mas sim à economia global.</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr"/>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>O Brasil, devido à sua vasta extensão territorial, apresenta uma grande diversidade de paisagens e culturas. Cada região do país possui características únicas que são influenciadas por uma combinação de fatores históricos, geográficos e climáticos. Por exemplo, o Nordeste brasileiro tem tradições culturais e paisagens diferentes das encontradas no Sul do país. Essa diversidade é um reflexo da complexa formação histórica do Brasil e das variações ambientais que moldam os modos de vida das populações em diferentes partes do território.</t>
+        </is>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>PH01</t>
+        </is>
+      </c>
+      <c r="J512" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K512" t="inlineStr"/>
+      <c r="L512" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>O território brasileiro é organizado politicamente em três níveis de governo: federal, estadual e municipal. Cada um desses níveis possui competências específicas e atua de acordo com as necessidades da população em seu respectivo âmbito. A noção de território é fundamental para entender como as políticas públicas são implementadas e como o poder é distribuído entre as diferentes esferas de governo.
+Como a noção de território influencia a organização política do espaço brasileiro?</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>O território brasileiro é administrado exclusivamente pelo governo federal, sem a participação dos estados e municípios.</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>A organização política do território brasileiro é centralizada, com todas as decisões sendo tomadas pela capital federal.</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>O território brasileiro é dividido em diferentes níveis de governo, cada um com competências específicas para atender às necessidades locais.</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>A noção de território não tem impacto na organização política do Brasil, já que todas as regiões seguem as mesmas políticas públicas.</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr"/>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>A noção de território é essencial para a organização política do Brasil, que é dividido em três níveis de governo: federal, estadual e municipal. Cada nível tem competências específicas e atua de acordo com as necessidades da população em seu respectivo âmbito. O governo federal cuida de questões nacionais, os estados tratam de assuntos regionais e os municípios lidam com questões locais. Essa divisão permite uma administração mais eficiente e adaptada às particularidades de cada região.</t>
+        </is>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>PH01</t>
+        </is>
+      </c>
+      <c r="J513" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K513" t="inlineStr"/>
+      <c r="L513" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>A cultura de um povo é refletida de várias formas no espaço geográfico que ocupa. Ela não apenas molda o ambiente, mas também é moldada pelas interações entre os indivíduos e o espaço onde vivem.
+Como a cultura de um povo pode ser percebida no espaço geográfico?</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>Pela ausência de construções e práticas festivas.</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>Pelo estilo das construções, modo de vestir e práticas festivas.</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>Pela uniformidade de hábitos em todas as regiões.</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>Pela exclusão de influências externas.</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr"/>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>A cultura de um povo é percebida no espaço geográfico através de várias manifestações visíveis. O estilo das construções reflete não apenas as preferências estéticas, mas também as influências históricas, climáticas e funcionais da região. O modo de vestir expressa tradições e identidade cultural, frequentemente incorporando elementos que representam a história e os valores do povo. As práticas festivas, por sua vez, revelam as crenças e os costumes da comunidade, tornando-se um meio de celebração e de reafirmação da identidade cultural. Juntas, essas expressões mostram como a cultura molda e é moldada pelo espaço geográfico.</t>
+        </is>
+      </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>PH01</t>
+        </is>
+      </c>
+      <c r="J514" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K514" t="inlineStr"/>
+      <c r="L514" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>O Brasil possui uma grande diversidade de recursos naturais, como minerais, água e solos cultiváveis. No entanto, a gestão desses recursos é um desafio constante.
+Um dos principais desafios relacionados à grande diversidade de recursos naturais no Brasil é a</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>gestão sustentável desses recursos.</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>necessidade de investir em tecnologias para a agricultura</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>ausência de solos cultiváveis</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>competição entre o uso agrícola e a preservação ambiental.</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr"/>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>Um dos principais desafios relacionados à grande diversidade de recursos naturais no Brasil é a gestão sustentável desses recursos para garantir o desenvolvimento do país.</t>
+        </is>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>PH01</t>
+        </is>
+      </c>
+      <c r="J515" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K515" t="inlineStr"/>
+      <c r="L515" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>No Brasil, o sistema de governo é baseado na divisão dos Três Poderes, idealizada por Montesquieu no século XVIII, para garantir o equilíbrio e evitar abusos de poder. Esses poderes são independentes e harmônicos entre si, sendo responsáveis por diferentes funções no Estado. Essa estrutura busca assegurar a democracia e o funcionamento equilibrado das instituições.
+No sistema democrático brasileiro, os três poderes desempenham papéis fundamentais na organização do Estado. Qual alternativa descreve corretamente a função de cada um dos três poderes?</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>O Poder Executivo cria leis, o Poder Legislativo julga, e o Poder Judiciário executa as políticas públicas.</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>O Poder Legislativo executa as leis, o Poder Executivo as interpreta, e o Poder Judiciário aprova as leis .</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>O Poder Legislativo cria e aprova leis, o Poder Judiciário julga e aplica as leis, e o Poder Executivo administra e executa as políticas públicas.</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>O Poder Executivo julga casos de violação de leis, o Poder Legislativo executa as políticas públicas, e o Poder Judiciário cria as leis.</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr"/>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>A divisão dos três poderes no Brasil é clara: o Poder Legislativo tem a função de criar e aprovar leis; o Poder Judiciário julga e aplica essas leis, assegurando que sejam cumpridas; e o Poder Executivo administra o país e executa as políticas públicas.</t>
+        </is>
+      </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>PH01</t>
+        </is>
+      </c>
+      <c r="J516" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K516" t="inlineStr"/>
+      <c r="L516" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>A Rússia é o país de maior área territorial do mundo. Ele ocupa quase metade da Europa e cerca de um terço da Ásia. São mais de 17 milhões de quilômetros quadrados! O idioma oficial é o russo, a moeda é o rublo e a capital é Moscou
+Disponível em:&lt;http://www.ebc.com.br/infantil/voce-sabia/2015/07/qual-e-o-maior-pais-do-mundo&gt;. Acesso em: 04 dez.2019.
+O Censo dos Estados Unidos estima que a população mundial no dia 1º de janeiro de 2018 seja de 7.444.443.881 habitantes.
+Veja a lista completa, feita pelo Censo dos Estados Unidos:
+1. China: 1.384.688.986 habitantes
+2. Índia: 1.296.834.042 habitantes
+3. Estados Unidos: 329.256.465 habitantes
+Disponível em:&lt;https://epocanegocios.globo.com/Mundo/noticia/2017/12/estes-serao-os-paises-mais-populosos-de-2018.html&gt;. Acesso em: 04 dez.2019.
+Utilizando o critério do primeiro texto, os países que ocupam posição superior ao Brasil são</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>Canadá, Índia, México e China.</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>Rússia, China, Índia e Austrália.</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>Rússia, Canadá, China e Estados Unidos.</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>Estados Unidos, Canadá, África do Sul e Indonésia.</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr"/>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>Os países que possuem maior área territorial que o Brasil, em ordem decrescente, são Rússia, Canadá, China e EUA.</t>
+        </is>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>PH01</t>
+        </is>
+      </c>
+      <c r="J517" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K517" t="inlineStr"/>
+      <c r="L517" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>Observando o mapa, os dois países da América do Sul que não se limitam com o Brasil são</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>Uruguai e Peru.</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>Chile e Equador.</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>Argentina e Chile.</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>Bolívia e Venezuela.</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr"/>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>O Brasil divide fronteiras com a maior parte dos países da América do Sul; as exceções são Chile e Equador.</t>
+        </is>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>PH01</t>
+        </is>
+      </c>
+      <c r="J518" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>ph01_geo_07.jpg</t>
+        </is>
+      </c>
+      <c r="L518" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>Observe a representação abaixo: 
+Disponível em: https://escolakids.uol.com.br/upload/conteudo_legenda/eadce3825839373174aaefd6f7e89b52.png. Acesso em: 01 fev. 2019
+O ponto extremo mais ao Sul do Brasil é o (a)</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>Nascente do Rio Moa.</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>Monte Caburaí.</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>Ponta do Seixas.</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>Arroio Chuí.</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr"/>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>O ponto mais ao sul do Brasil é o Arroio Chuí, no Rio Grande do Sul.</t>
+        </is>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>PH01</t>
+        </is>
+      </c>
+      <c r="J519" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>ph01_geo_08.png</t>
+        </is>
+      </c>
+      <c r="L519" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>Disponível em:&lt;http://www.educandusweb.com.br/ewbco/portal/upload/xinha/UNICENTRO20122FGEOG01.PNG&gt;. Acesso em: 04 dez.2019.
+Após observar o planisfério, considere as afirmações:
+I -  O Brasil situa-se a oeste do Meridiano de Greenwich.
+II -  O Brasil é cortado ao norte pela Linha do Equador.
+III -  Ao sul, é cortado pelo Trópico de Câncer.
+IV -  Ao sul, é cortado pelo Trópico de Capricórnio, apresentando grande parte do seu território na Zona Intertropical, entre os Trópicos de Câncer e de Capricórnio.
+Assinale a alternativa que apresenta apenas a(s) afirmação(ões) verdadeira(s).</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>Apenas I é verdadeira.</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>Apenas III e IV são verdadeiras.</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>Apenas I, II e IV são verdadeiras.</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>Apenas I, II, e III são verdadeiras.</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr"/>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>Letra C.
+O Brasil fica localizado no hemisfério ocidental, ou seja a oeste do meridiano de Greenwich. A maior parte do seu território é localizado no hemisfério Sul, na faixa intertropical, com uma pequena parte cortada pela linha do Equador, no norte do país.</t>
+        </is>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>PH01</t>
+        </is>
+      </c>
+      <c r="J520" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>ph01_geo_09.jpg</t>
+        </is>
+      </c>
+      <c r="L520" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>Juridicamente, território nacional é a área que compreende todo o espaço, terrestre, fluvial, marítimo (12 milhas) e aéreo (coluna atmosférica), onde o Estado brasileiro é soberano. Mas, esse território poderá ser estendido quando se tratar de embarcações ou aeronaves públicas ou a serviço do governo brasileiro onde quer que se encontre e as embarcações ou aeronaves estrangeiras privadas quando em território nacional.
+[...]
+Disponível em:&lt;https://lfg.jusbrasil.com.br/noticias/2086332/o-que-se-entende-por-territorio-nacional-lais-mamede-dias-leme&gt;.Acesso em&gt; 04 dez.2019.
+A partir do texto, pode-se afirmar que território nacional é</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>o limite fronteiriço do país.</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>o espaço contido dentro das fronteiras.</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>a região natural de maior abrangência em um país.</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>o espaço controlado pelas instituições políticas e militares de um país.</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr"/>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>O território nacional pode ser considerado o espaço controlado pelas instituições políticas e militares de um país, ou seja, uma embaixada brasileira localizada em Londres, é considerada território brasileiro.</t>
+        </is>
+      </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>PH01</t>
+        </is>
+      </c>
+      <c r="J521" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K521" t="inlineStr"/>
+      <c r="L521" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>As cidades apresentavam, naturalmente, condições específicas, com uma grande população concentrada numa superfície pequena, enquanto o campo tinha uma densidade demográfica baixa. Mas, assim como os campos se diferenciavam pelo seu contexto geográfico, as cidades não eram iguais entre si. Uma grande sede feudal (como Troyes), a capital de um reino (caso de Londres), uma importante sé episcopal (Burgos, por exemplo), uma cidade dedicada ao comércio internacional (como Veneza ou Lübeck), uma cidade artesanal (como Ypres), um pequeno burgo rural (os mais comuns) não poderiam, por razões geográficas e profissionais, construir habitações e edifícios públicos da mesma forma.
+FRANCO JR., Hilário. A Idade Média: nascimento do ocidente. São Paulo: Brasiliense, 1995, pp. 181-182.
+Qual foi uma das principais razões para o crescimento das cidades na Baixa Idade Média?</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>A criação de novas rotas marítimas.</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>O​​​​​​​ desenvolvimento das técnicas agrícolas e do comércio.</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>A descoberta de novos continentes.</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>A construção de grandes monumentos.</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr"/>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>A melhoria das técnicas agrícolas possibilitou um aumento da produção e, consequentemente, um crescimento populacional e econômico. O crescimento populacional provocou uma superlotação dos feudos, o que acarretou na expulsão de camponeses pelos senhores feudais, enquanto o aumento da produção permitiu que os excedentes fossem comercializados em feiras. Esse cenário, de migração de grandes parcelas da população camponesa, e de concentração do comércio em feiras próximas a centros urbanos, contribuíram para o chamado Renascimento Urbano.</t>
+        </is>
+      </c>
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>PH01</t>
+        </is>
+      </c>
+      <c r="J522" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K522" t="inlineStr"/>
+      <c r="L522" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>Leia o texto a seguir.
+Entre 1095 e 1291 d.C., uma série de guerras religiosas foram organizadas por cristãos europeus em resposta ao expansionismo militar dos povos muçulmanos que estendiam suas posses por regiões do Oriente e do norte da África. 
+Disponível em: https://revistagalileu.globo.com/sociedade/historia/noticia/2019/10/dois-seculos-de-guerra-cristas-entenda-o-que-foram-cruzadas.ghtml. Acesso em: 2 out. 2024.
+O trecho acima refere-se às Cruzadas, que tinham como principal objetivo</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>conquistar novos territórios para os reinos cristãos na Ásia.</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>abrir novas rotas de comércio entre a Europa e o Oriente Médio.</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>retomar Jerusalém e outros territórios sagrados que estavam sob controle muçulmano.</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>impedir o avanço do Império Bizantino no Oriente Médio.</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr"/>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>As Cruzadas foram expedições militares organizadas principalmente pela Igreja Católica com o intuito de reconquistar Jerusalém e outros territórios sagrados do controle muçulmano. Embora houvesse interesses secundários, como o estabelecimento de rotas comerciais ou a conversão religiosa, o objetivo central era a retomada da Terra Santa, justificada como uma missão espiritual de defesa do cristianismo.</t>
+        </is>
+      </c>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>PH01</t>
+        </is>
+      </c>
+      <c r="J523" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K523" t="inlineStr"/>
+      <c r="L523" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>Eram eventos importantes para a economia das cidades. Permitiam a troca de produtos entre diferentes regiões, facilitando o comércio e a circulação de mercadorias e eram momentos de encontro social e cultural.
+O trecho trata das(dos)</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>Feiras medievais.</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>Mercados urbanos.</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>Festivais religiosos.</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>Assembleias comerciais.</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr"/>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>As feiras medievais tinham como principal função facilitar a troca de produtos entre diferentes regiões, promovendo o comércio e a circulação de mercadorias e culturas.</t>
+        </is>
+      </c>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>PH01</t>
+        </is>
+      </c>
+      <c r="J524" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K524" t="inlineStr"/>
+      <c r="L524" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>Sua origem remonta à Idade Média [...]. Os pedreiros ou construtores, com o conhecimento herdado das técnicas romanas e gregas, se organizavam em um desses grupos. E, por uma questão de sobrevivência frente a uma possível concorrência, eles guardavam os segredos da construção civil, temerosos de que as técnicas caíssem em domínio público.
+Disponível em: https://www.bbc.com/portuguese/geral-45457166. Acesso em: 14 out. 2024.
+Essas associações descritas pelo texto eram chamadas de</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>grêmios comerciais.</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>associações de artesãos.</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>ligas de produção.</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>corporações de ofício.</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr"/>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>As corporações de ofício foram associações fundamentais durante o Renascimento comercial, reunindo artesãos de uma mesma profissão com o objetivo de organizar e regulamentar a produção. Elas desempenhavam um papel crucial na garantia da qualidade dos produtos, estabelecendo padrões técnicos e controlando a concorrência. Além disso, as corporações protegiam os interesses econômicos e sociais de seus membros, oferecendo suporte e representando-os em questões legais e políticas, o que fortalecia a cooperação entre os artesãos.</t>
+        </is>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>PH01</t>
+        </is>
+      </c>
+      <c r="J525" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K525" t="inlineStr"/>
+      <c r="L525" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>Nesse sentido, o século XI é marcado, por um lado, pela expansão da produção e crescimento urbano e, por outro, com o desenvolvimento da atividade comercial na cidade medieval. Nesses burgos, com o aumento de seus habitantes, as construções urbanas foram edificadas fora das muralhas, o que gerava a necessidade de proteção contra o banditismo senhorial e de organização política própria na defesa de seus interesses, pois seus moradores eram constituídos, basicamente, pelo clero, nobres, ricos comerciantes, artesãos, etc, sendo denominados de burgueses.
+AMBONI, V. As Comunas na Idade Média (Século XII): Lutas de Classes e Ontologia da Burguesia Medieval. In: CONGRESSO INTERNACIONAL DE HISTÓRIA, 5., 2011, Passo Fundo. Anais eletrônicos... Passo Fundo: UPF, 2011. Disponível em: http://www.cih.uem.br/anais/2011/trabalhos/79.pdf. Acesso em: 14 out. 2024.
+A formação dos primeiros burgos ocorreu devido a</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>expansão das rotas marítimas.</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>construção de catedrais góticas.</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>necessidade de proteção e segurança.</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>descoberta de novas terras.</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr"/>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>A formação dos primeiros burgos na Europa foi motivada pela necessidade de proteção e segurança, tendo em vista a grande instabilidade social que se espalhou pela Europa após o fim do Império Carolíngio. Os primeiros burgos cresceram muito com o tempo, o que acarretou no surgimento de novos burgos ao redor das muralhas e das fortificações dos primeiros.</t>
+        </is>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>PH01</t>
+        </is>
+      </c>
+      <c r="J526" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K526" t="inlineStr"/>
+      <c r="L526" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>Veja o quadro a seguir:
+O quadro acima demonstra o acelerado crescimento da população europeia entre os séculos XI e XIV. Um fator que possibilitou esse fenômeno foi</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>o advento de máquinas movidas por combustíveis fósseis, causando um aumento da produção agrícola.</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>as migrações de povos eslavos da Europa Oriental que estavam fugindo dos ataques de muçulmanos.</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>os avanços tecnológicos como o moinho hidráulico e o arado de ferro, que possibilitaram um aumento na produção de alimentos.</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>a descoberta de novas vacinas, o que permitiu aos europeus superar doenças fatais como a peste negra.</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr"/>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>Os diversos avanços tecnológicos relacionados à prática da agricultura, foram fundamentais para o crescimento populacional na Europa devido ao aumento que proporcionou na produção de alimentos.</t>
+        </is>
+      </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>PH01</t>
+        </is>
+      </c>
+      <c r="J527" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>ph01_his_06.png</t>
+        </is>
+      </c>
+      <c r="L527" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>Observe a imagem a seguir.
+A imagem acima é uma representação de uma cidade italiana a época do Renascimento Comercial e urbano. Este processo</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>representou uma reativação do comércio no continente europeu, que estava enfraquecido na Idade Média.</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>significou o surgimento do comércio na Europa, visto que antes nunca existiram rotas de comércio no continente.</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>foi possível graças a tomada de Jerusalém pelos exércitos da Igreja durante as Cruzadas.</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>iniciou-se no século XIII e não provocou significativas mudanças no sistema e nas relações feudais vigentes.</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr"/>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>Como o nome sugere, o Renascimento Comercial consistiu na reativação do comércio no continente europeu. Esse processo foi possibilitado pela desagregação do feudalismo, pela comercialização dos excedentes produzidos nos campos, e pelo aumento do número de comerciantes. Assim, as relações comerciais, que já existiam anteriormente mas ficaram enfraquecidas durante o feudalismo, voltaram a ganhar espaço na vida econômica e social do período.</t>
+        </is>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>PH01</t>
+        </is>
+      </c>
+      <c r="J528" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>ph01_his_07.png</t>
+        </is>
+      </c>
+      <c r="L528" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>Leia o texto a seguir.
+O anúncio em boletins e sites da Igreja Católica vem sendo saudado com entusiasmo por alguns e cautela por outros. Mas passou em branco para uma grande geração de católicos que não fazem ideia do que significa: "Bispo anuncia indulgências plenárias".
+[...]
+A volta das indulgências começou com o papa João Paulo 2º, que em 2000 autorizou os bispos a oferecê-las como parte das celebrações do terceiro milênio da igreja.
+CLARA, Allain (trad.). Indulgência volta à voga na Igreja Católica. Folha de São Paulo, 11 fev. 2009. Disponível em:
+&lt;https://www1.folha.uol.com.br/fsp/mundo/ft1102200915.htm&gt;. Acesso em: 02 dez. 2019.
+Ao contrário dos dias de hoje, durante o período de Cruzadas a indulgência foi comumente utilizada como</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>modo de conversão dos infiéis ao cristianismo.</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>estratégia de negociação com os muçulmanos.</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>método de controle populacional em toda a Europa.</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>forma de convencer os fiéis a participarem das expedições.</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr"/>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>Durante o período das Cruzadas, a indulgência, prática que perdoa todos os pecados dos fiéis cristãos, foi utilizada como incentivo para a participação dos cristãos nas expedições cruzadistas.</t>
+        </is>
+      </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>PH01</t>
+        </is>
+      </c>
+      <c r="J529" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K529" t="inlineStr"/>
+      <c r="L529" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>Leia o texto a seguir.
+Enquanto por volta do ano 1000 talvez não existisse na Europa católica nenhuma cidade com uma população de 10.000 habitantes, no século XIII havia 55 cidades com um número de habitantes superior àquele. [...] Ainda que as cifras sejam sempre discutíveis, sem haver consenso entre os especialistas, Milão, Florença, Veneza e Gênova devem ter ultrapassado os 100.000 habitantes. No restante da Europa Ocidental, apenas Paris parece ter alcançado tal população.
+FRANCO JÚNIOR, Hilário. A Idade Média, nascimento do ocidente. São Paulo: Brasiliense, 2006, p.23-24.
+Um dos motivos de tal crescimento das grandes cidades europeias, como destacado no texto, foi</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>o rápido processo de industrialização que se iniciou nesse contexto.</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>o crescimento populacional que ocorreu no continente durante as Cruzadas.</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>a grande concentração de muçulmanos que chegaram à Europa nesse período.</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>o processo de migração de comerciantes que viviam nos feudos para os burgos.</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr"/>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>Juntamente ao Renascimento Comercial ocorreu também o Renascimento Urbano, no qual houve a migração de camponeses comerciantes que, enfrentando dificuldades comerciais dentro dos feudos, se mudaram para os burgos, aumentando, consequentemente, a população e o tamanho das cidades.</t>
+        </is>
+      </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>PH01</t>
+        </is>
+      </c>
+      <c r="J530" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K530" t="inlineStr"/>
+      <c r="L530" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>Leia o texto a seguir.
+As Corporações de Ofício medievais congregavam pessoas com um mesmo interesse econômico, político ou cultural. Tais pessoas agrupavam-se, criavam um estatuto para garantir os melhores preços e impedir a entrada de produtos ou de pessoas em seu meio. Cada membro da corporação deveria respeitar um estatuto próprio.
+Disponível em: &lt;http://www.histedbr.fe.unicamp.br/navegando/glossario/verb_c_universidades_medievais.htm&gt;. Acesso em: 02 dez. 2019.
+Conforme demonstra o texto, as Corporações de Ofício possuíam uma organização baseada no(a)</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>modo de produção industrializado.</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>rejeição das atividades ligadas à agricultura.</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>combate ao processo de urbanização medieval.</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>monopólio de determinadas atividades econômicas.</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr"/>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>Como destaca o texto-base, os membros das Corporações criavam seus estatutos internos com o intuito de “impedir a entrada de produtos ou de pessoas em seu meio”, algo que demonstra o caráter monopolista de tais organizações.</t>
+        </is>
+      </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>PH01</t>
+        </is>
+      </c>
+      <c r="J531" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K531" t="inlineStr"/>
+      <c r="L531" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>Atena era uma importante deusa presente na religiosidade da Grécia Antiga. Ela era considerada a deusa da sabedoria, mas também tinha forte relação com ofícios e habilidades manuais. Era a deusa patrona de uma das cidades mais importantes da Grécia: Atenas. Era filha de Zeus e nasceu ao sair da cabeça de seu pai.
+Disponível em: https://www.historiadomundo.com.br/grega/atena.htm. Acesso em 11 de out. de 2024.
+Qual adjetivo melhor descreve a deusa grega Atena apresentada pelo texto?</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>Prudente</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>Ingênua</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>Sábia</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>Frágil</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr"/>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>Na mitologia grega, Atena é reconhecida por sua inteligência e habilidade em aconselhar os heróis, características que a diferenciam como uma figura justa e ponderada. Assim, "sábia" complementa perfeitamente sua representação, evidenciando seu papel como protetora e conselheira em batalhas.</t>
+        </is>
+      </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>PH01</t>
+        </is>
+      </c>
+      <c r="J532" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K532" t="inlineStr"/>
+      <c r="L532" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>Poseidon era o deus grego dos mares e rios e considerado um causador de catástrofes. Acredita-se que seu culto tenho se originado no período Pré-Homérico.
+Disponível em: https://www.historiadomundo.com.br/grega/poseidon.htm. Acesso em 11 de out. de 2024.
+Qual é a função do artigo "o" no trecho destacado?</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>Generalizar Poseidon.</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>Especificar Poseidon.</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>Descrever Poseidon.</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>Nomear Poseidon.</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr"/>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>O artigo "o" específica Poseidon como "o deus grego dos mares e rios", destacando sua posição única e suas características na mitologia grega.</t>
+        </is>
+      </c>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t>PH01</t>
+        </is>
+      </c>
+      <c r="J533" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K533" t="inlineStr"/>
+      <c r="L533" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>A origem do Sol
+Há muitos e muitos anos, houve uma festa na aldeia onde um lindo rapaz morava, a “festa da moça nova”, um ritual que celebra a passagem das meninas indígenas de crianças a “moças” ou “jovens mulheres”. Era dia de música, dança, bebida e comida à vontade. E todos, é claro, caprichariam nas pinturas do corpo com a tinta vermelha a base de urucum, fruto do urucuzeiro.
+Pois bem, o belo rapaz quis ajudar sua tia no preparo da tinta. Entrou na mata, trouxe madeira vermelha de muirapiranga, cortou a lenha e acendeu o fogo, no qual a velha senhora pôs a ferver o urucum para que todos pudessem se pintar. Mas a tia do moço não era uma pessoa muito feliz. Era maldosa e ranzinza. O rapaz se dedicava à tarefa de buscar mais e mais lenha para o fogo e, mesmo assim, ela não parava de reclamar.
+Admirado com o caldo vermelho borbulhando, ele perguntou à tia se poderia provar da tinta. A mulher impaciente disse que sim. Insistiu para ele beber uma grande quantidade, garantindo que o gosto era bom e que não lhe faria mal. No fundo, porém, ela queria que ele passasse mal, fosse embora logo e a deixasse sozinha.
+O rapaz bebeu e, conforme engolia a tinta quente, ia ficando vermelho, cada vez mais vermelho, extremamente vermelho, até que ficou em chamas! A tia, espantada, viu o sobrinho virar uma bola de fogo, subir ao céu e sumir entre as nuvens.
+E foi assim que um jovem indígena se tornou o Sol, que aquece e ilumina o mundo todo.
+Disponível em: https://chc.org.br/artigo/a-origem-do-sol/. Acesso em 21 nov. 2024.
+Qual é o substantivo plural no grau aumentativo da palavra em destaque?</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>Rapazãos</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>Rapagões.</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>Rapazotes.</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>Rapazinhos.</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr"/>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>Na língua portuguesa, o aumentativo da palavra "rapaz" pode ser feito de duas maneiras: 1. com o acréscimo do sufixo -ão à raiz, formando "rapazão"; 2. com a substituição da letra /z/ por /g/ + acréscimo do sufixo -ão, formando "rapagão". Nos dois casos, a forma do aumentativo plural recebe o acréscimo do sufixo -ões, e não -ãos. Portanto, "rapagões" ou "rapazões".</t>
+        </is>
+      </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>PH01</t>
+        </is>
+      </c>
+      <c r="J534" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K534" t="inlineStr"/>
+      <c r="L534" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>Um dos protagonistas do Monte Olimpo, Apolo é dos mais adorados entre os deuses gregos. Até por ser uma divindade multifunção: é o deus do Sol, da luz, da verdade, da profecia, da cura, da beleza masculina, do equilíbrio e da razão.
+Disponível em: https://super.abril.com.br/especiais/apolo-deus-da-perfeicao. Acesso em 14 de out. de 2024.
+O substantivo em destaque é classificado como</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>Substantivo próprio, concreto.</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>Substantivo comum, abstrato.</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>Substantivo próprio, abstrato.</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>Substantivo comum, concreto.</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr"/>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>"Beleza" é um substantivo comum e abstrato, pois nomeia uma qualidade ou estado e não um objeto físico.</t>
+        </is>
+      </c>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>PH01</t>
+        </is>
+      </c>
+      <c r="J535" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K535" t="inlineStr"/>
+      <c r="L535" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>Hélio tem a aparência de um deus jovem e radiante, com raios solares em volta da cabeça, e com cabelos loiros. Conduzindo uma carruagem dourada pelo céu, puxada por quatro cavalos alados, Pírois, Eoo, Éton e Flégon dotados de grande rapidez. 
+Ele atravessa o céu diariamente, iluminando a Terra com sua luz brilhante. Seu papel era crucial na criação do ciclo diário, trazendo a luz ao amanhecer do dia e a tarde chegava ao mar, onde banhava seus cavalos fadigados. 
+Disponível em: https://deusesgregos.com.br/helio-deus/. Acesso em 14 de out. de 2024.
+Qual é a forma plural do adjetivo em destaque quando concorda com o substantivo "luzes"?</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>Brilhantíssimos</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>Brilhantões</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>Brilhantas</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>Brilhantes</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr"/>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>O adjetivo "brilhante" concorda em gênero e número com o substantivo "luzes", ficando "brilhantes" no plural feminino.</t>
+        </is>
+      </c>
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>PH01</t>
+        </is>
+      </c>
+      <c r="J536" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K536" t="inlineStr"/>
+      <c r="L536" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>Leia o texto a seguir para responder à questão:
+Num domingo, Onofre e Anésia dormiam, Antônio na sala roçando canivete na sola das botas, Maria, no quarto jogando talco nos vestidos da cômoda, deu um toque no pescoço. Nico passava café, Antônio sentiu o cheiro e foi sugerir um biscoito de polvilho, ele mesmo o faria se Maria deixasse.
+- Faz, mas deixa a cozinha arrumada e não usa a gordura toda que amanhã faço sabão.
+Antônio pegou na despensa os ovos, leite e polvilho azedo. No fogão a lenha a água borbulhava, Nico botou açúcar deixando-a leitosa, acrescentou o pó torrado pela manhã e levou a mistura até a pia onde a coaria no bule. Antônio usava a lateral da mesma pia, ficou em pé sobre o banco para alcançá-la, ia misturar os ingredientes numa bacia. Na frente deles uma janela dando para a represa, ouvia-se dali uma cachoeira ao longe, constante, úmida.
+Nico derramou a água fervente, o perfume subiu. Antônio interrompeu o biscoito para ver a fumaça se erguer. Nico apoiou a caneca de água na pia, Antônio fechou os olhos para fortalecer o aroma. Abriu-os e não viu mais o irmão, ele não estava mais na cozinha. Antônio se espichou para ver a água dentro do coador, ela desapareceu deixando uma pasta pelas beiradas, a caneca apoiada na pia, Maria fechando o armário lá dentro.
+- Maria? Vem ver, o Nico caiu no bule.
+Maria demorou a vir, pela impossibilidade do fato e nenhuma urgência naquela idiotia. Vendo Antônio olhar pela janela, foi até a despensa procurar Nico, no terreiro, chiqueiro, paiol, milharal.
+- Nico sair desse jeito? Sem falar nada?
+- Saiu não, Maria. Ele foi embora no coador.
+- Fala direito, Antônio.
+- Ele tava passando o pó, hora que botou a água, sumiu.
+- Daqui a pouco ele chega.
+- Não mexe no bule, deixa do jeito que tá para ele voltar.
+(...)
+FUEGO, Andrea del. Os Malaquias. Rio de Janeiro: Língua Geral, 2010.3
+No trecho do romance da escritora paulistana Andrea del Fuego, quando se dá conta de que Nico sumiu, Antônio fala:
+- Maria? Vem ver, o Nico caiu no bule.
+Com a análise atenta da fala de Antônio, podemos afirmar que não haveria mudança de sentido se o artigo definido “o” estivesse ausente da frase, pois o substantivo “Nico” é</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>um substantivo próprio, o que cria uma especificação por si só.</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>um substantivo primitivo, pois não deriva de outra palavra.</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>um substantivo simples, o que mostra seu caráter único.</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>um substantivo concreto, pois indica o ser denominado.</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr"/>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>“Nico” é um substantivo que, por si só, já indica uma especificação. Isso decorre do fato de ele ser um substantivo próprio. Portanto, o uso do artigo definido “o” seria mais uma escolha do próprio falante do que uma necessidade à compreensão do sentido.</t>
+        </is>
+      </c>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>PH01</t>
+        </is>
+      </c>
+      <c r="J537" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K537" t="inlineStr"/>
+      <c r="L537" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>Leia o texto a seguir para responder à questão:
+Num domingo, Onofre e Anésia dormiam, Antônio na sala roçando canivete na sola das botas, Maria, no quarto jogando talco nos vestidos da cômoda, deu um toque no pescoço. Nico passava café, Antônio sentiu o cheiro e foi sugerir um biscoito de polvilho, ele mesmo o faria se Maria deixasse.
+- Faz, mas deixa a cozinha arrumada e não usa a gordura toda que amanhã faço sabão.
+Antônio pegou na despensa os ovos, leite e polvilho azedo. No fogão a lenha a água borbulhava, Nico botou açúcar deixando-a leitosa, acrescentou o pó torrado pela manhã e levou a mistura até a pia onde a coaria no bule. Antônio usava a lateral da mesma pia, ficou em pé sobre o banco para alcançá-la, ia misturar os ingredientes numa bacia. Na frente deles uma janela dando para a represa, ouvia-se dali uma cachoeira ao longe, constante, úmida.
+Nico derramou a água fervente, o perfume subiu. Antônio interrompeu o biscoito para ver a fumaça se erguer. Nico apoiou a caneca de água na pia, Antônio fechou os olhos para fortalecer o aroma. Abriu-os e não viu mais o irmão, ele não estava mais na cozinha. Antônio se espichou para ver a água dentro do coador, ela desapareceu deixando uma pasta pelas beiradas, a caneca apoiada na pia, Maria fechando o armário lá dentro.
+- Maria? Vem ver, o Nico caiu no bule.
+Maria demorou a vir, pela impossibilidade do fato e nenhuma urgência naquela idiotia. Vendo Antônio olhar pela janela, foi até a despensa procurar Nico, no terreiro, chiqueiro, paiol, milharal.
+- Nico sair desse jeito? Sem falar nada?
+- Saiu não, Maria. Ele foi embora no coador.
+- Fala direito, Antônio.
+- Ele tava passando o pó, hora que botou a água, sumiu.
+- Daqui a pouco ele chega.
+- Não mexe no bule, deixa do jeito que tá para ele voltar.
+(...)
+FUEGO, Andrea del. Os Malaquias. Rio de Janeiro: Língua Geral, 2010.
+Releia o trecho:
+Nico apoiou a caneca de água na pia, Antônio fechou os olhos para fortalecer o aroma.
+A construção destacada caracteriza-se como</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>substantivo concreto, por se referir a uma entidade real.</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>locução adjetiva, por caracterizar o substantivo “caneca”.</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>adjetivo impróprio, por caracterizar o substantivo “água”.</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>sintagma verbal, por se referir à relação de posse entre a caneca e a água.</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr"/>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>A construção preposicionada “de água” caracteriza o substantivo “a caneca”, especificando-o, constituindo, assim, uma locução adjetiva.</t>
+        </is>
+      </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>PH01</t>
+        </is>
+      </c>
+      <c r="J538" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K538" t="inlineStr"/>
+      <c r="L538" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>Posêidon estava sentado à sua escrivaninha e fazia contas. A administração de todas as águas dava-lhe um trabalho interminável. Poderia ter quantos auxiliares quisesse, possuía muitos, aliás; mas, uma vez que levava muito a sério seu ofício, revia mais uma vez tudo e sendo assim os auxiliares o ajudavam pouco. Não se pode dizer que o trabalho o alegrasse; na verdade ele o realizava só porque lhe fora imposto; já havia solicitado muitas vezes tarefas mais prazerosas, conforme se expressava; mas, sempre que lhe faziam propostas diferentes, era manifesto que nada o agradava tanto quanto o cargo que até então ocupara. Era muito difícil, além disso, encontrar outra coisa para ele. Com efeito, era impossível atribuir-lhe algo como um determinado mar; sem mencionar que, neste caso, o trabalho de calcular não seria apenas maior, mas também mesquinho, o grande Posêidon só podia receber um posto que fosse dominante. E, se lhe ofereciam um ofício fora da água, sentia-se mal só com a ideia: seu alento divino se descontrolava, o tórax de bronze oscilava. De resto, não levavam realmente a sério as queixas que fazia; quando um poderoso importuna, é preciso dar a impressão de tentar ceder mesmo nas questões mais sem perspectiva: ninguém pensava em remover de fato Posêidon do seu posto; desde o início mais remoto tinha sido destinado a ser o rei dos mares e assim devia permanecer.
+[...]
+KAFKA, Franz. Posêidon. In: Narrativas do Espólio. São Paulo: Companhia das Letras, 2002.
+Observe os vocábulos em destaque na narrativa do escritor tcheco Franz Kafka. Embora todos sejam adjetivos, os que estão associados diretamente a substantivos são</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>“diferentes”, “difícil” e “impossível”.</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>“interminável”, “difícil” e “prazerosas”.</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>“prazerosas”, “diferentes” e “impossível”</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>“interminável”, “prazerosas” e “diferentes”.</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr"/>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>"Interminável" está associado a "trabalho", "prazerosas" está associado a "tarefas" e "diferentes" está associado a "propostas". Todos esses adjetivos estão diretamente ligados a substantivos, descrevendo suas características de forma clara e direta. Já os adjetivos “difícil” e “impossível” não se ligam a substantivos expressos no texto.</t>
+        </is>
+      </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>PH01</t>
+        </is>
+      </c>
+      <c r="J539" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K539" t="inlineStr"/>
+      <c r="L539" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>Posêidon estava sentado à sua escrivaninha e fazia contas. A administração de todas as águas dava-lhe um trabalho interminável. Poderia ter quantos auxiliares quisesse, possuía muitos, aliás; mas, uma vez que levava muito a sério seu ofício, revia mais uma vez tudo e sendo assim os auxiliares o ajudavam pouco. Não se pode dizer que o trabalho o alegrasse; na verdade ele o realizava só porque lhe fora imposto; já havia solicitado muitas vezes tarefas mais prazerosas, conforme se expressava; mas, sempre que lhe faziam propostas diferentes, era manifesto que nada o agradava tanto quanto o cargo que até então ocupara. Era muito difícil, além disso, encontrar outra coisa para ele. Com efeito, era impossível atribuir-lhe algo como um determinado mar; sem mencionar que, neste caso, o trabalho de calcular não seria apenas maior, mas também mesquinho, o grande Posêidon só podia receber um posto que fosse dominante. E, se lhe ofereciam um ofício fora da água, sentia-se mal só com a ideia: seu alento divino se descontrolava, o tórax de bronze oscilava. De resto, não levavam realmente a sério as queixas que fazia; quando um poderoso importuna, é preciso dar a impressão de tentar ceder mesmo nas questões mais sem perspectiva: ninguém pensava em remover de fato Posêidon do seu posto; desde o início mais remoto tinha sido destinado a ser o rei dos mares e assim devia permanecer.
+[...]
+KAFKA, Franz. Posêidon. In: Narrativas do Espólio. São Paulo: Companhia das Letras, 2002.
+Releia:
+Posêidon estava sentado à sua escrivaninha e fazia contas.
+Quanto ao seu sentido, a flexão de grau do substantivo destacado</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>indica a mudança de dimensão de um substantivo primitivo.</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>sintetiza um modo afetuoso de se referir ao substantivo “escrivão”.</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>compõe uma maneira irônica de se referir ao substantivo “escrivão”.</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>é parte integral do substantivo e não se refere necessariamente à sua dimensão.</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr"/>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>A flexão de grau do substantivo “escrivaninha” não se refere necessariamente a uma mudança de tamanho/dimensão do substantivo, mas é parte integral do seu significado de mesa apropriada para se escrever.</t>
+        </is>
+      </c>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>PH01</t>
+        </is>
+      </c>
+      <c r="J540" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K540" t="inlineStr"/>
+      <c r="L540" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>Posêidon estava sentado à sua escrivaninha e fazia contas. A administração de todas as águas dava-lhe um trabalho interminável. Poderia ter quantos auxiliares quisesse, possuía muitos, aliás; mas, uma vez que levava muito a sério seu ofício, revia mais uma vez tudo e sendo assim os auxiliares o ajudavam pouco. Não se pode dizer que o trabalho o alegrasse; na verdade ele o realizava só porque lhe fora imposto; já havia solicitado muitas vezes tarefas mais prazerosas, conforme se expressava; mas, sempre que lhe faziam propostas diferentes, era manifesto que nada o agradava tanto quanto o cargo que até então ocupara. Era muito difícil, além disso, encontrar outra coisa para ele. Com efeito, era impossível atribuir-lhe algo como um determinado mar; sem mencionar que, neste caso, o trabalho de calcular não seria apenas maior, mas também mesquinho, o grande Posêidon só podia receber um posto que fosse dominante. E, se lhe ofereciam um ofício fora da água, sentia-se mal só com a ideia: seu alento divino se descontrolava, o tórax de bronze oscilava. De resto, não levavam realmente a sério as queixas que fazia; quando um poderoso importuna, é preciso dar a impressão de tentar ceder mesmo nas questões mais sem perspectiva: ninguém pensava em remover de fato Posêidon do seu posto; desde o início mais remoto tinha sido destinado a ser o rei dos mares e assim devia permanecer.
+[...]
+KAFKA, Franz. Posêidon. In: Narrativas do Espólio. São Paulo: Companhia das Letras, 2002.
+Observe o uso dos artigos em destaque em dois trechos finais do texto: “quando um poderoso importuna” e “destinado a ser o rei dos mares”. A utilização desses artigos trazem ao texto sentidos opostos. Tais sentidos são, respectivamente,</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>de especificação e generalização.</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>de figurativização e indefinição.</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>de generalização e especificação.</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>de definição e concretização.</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr"/>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>O artigo indefinido “um” traz uma generalização: um poderoso dentre vários; já o artigo definido “o” traz uma especificação: o único rei dos mares, Posêidon.</t>
+        </is>
+      </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>PH01</t>
+        </is>
+      </c>
+      <c r="J541" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K541" t="inlineStr"/>
+      <c r="L541" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>Em um parque, duas fontes de água começam a jorrar ao mesmo tempo. A primeira fonte jorra água a cada 6 minutos, enquanto a segunda jorra a cada 8 minutos.
+Em quantos minutos as duas fontes jorrarão água simultaneamente novamente após começarem a jorrar água juntas?</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr"/>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>Para calcular o tempo em que as fontes irão jorrar água simultaneamente, é preciso calcular o Mínimo Múltiplo Comum (MMC) de 6 minutos e 8 minutos. Para calcular o MMC, podemos listar os múltiplos:
+Múltiplos de 6: 6, 12, 18, 24, 30, ...
+Múltiplos de 8: 8, 16, 24, 32, ...
+O menor múltiplo que aparece em ambas as listas é 24. Portanto, as duas fontes jorrarão água simultaneamente novamente em 24 minutos.</t>
+        </is>
+      </c>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>PH01</t>
+        </is>
+      </c>
+      <c r="J542" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K542" t="inlineStr"/>
+      <c r="L542" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>Em uma das etapas de uma competição matemática os participantes precisavam efetuar a soma dos valores que um atleta correu durante três percursos, sendo eles: 12 km na primeira volta, 15 km na segunda e 10 km na terceira. 
+Dois dos participantes estruturaram a soma da seguinte maneira:
+Qual dos participantes estruturou a expressão numérica corretamente?</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>Ambos, uma vez que pela propriedade associativa a ordem das parcelas não altera a soma.</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>Ambos, uma vez que pela propriedade comutativa a ordem dos números não altera a soma.</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>Apenas o participante 1, uma vez que a soma deve ser feita da esquerda para a direita.</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>Apenas o participante 2, uma vez que a soma deve ser feita da direita para a esquerda.</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr"/>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>Ambos os participantes estruturaram a expressão corretamente. A propriedade associativa da adição afirma que a forma como os números são agrupados não altera a soma. Portanto, (12 + 10) + 15 e 12 + (10 + 15) resultarão no mesmo valor, que é 37 km.</t>
+        </is>
+      </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>PH01</t>
+        </is>
+      </c>
+      <c r="J543" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>ph01_mat_02.png</t>
+        </is>
+      </c>
+      <c r="L543" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>Na multiplicação, existe um número que quando multiplicado por qualquer outro número, não altera o valor desse número. Na soma, também há um número que somado a qualquer outro não altera seu valor. Esses números são chamados de elemento neutro. 
+O elemento neutro na multiplicação e na soma, é respectivamente</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>1 e 0</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>0 e 0</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>1 e 1</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>0 e 1</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr"/>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>Na multiplicação, o número que, quando multiplicado por qualquer outro número, não altera o valor desse número é o 1. Este número é conhecido como o elemento neutro da multiplicação. Por exemplo:
+5 × 1 = 5
+Na soma, o número que, quando somado a qualquer outro número, não altera o valor desse número é o 0. Este número é conhecido como o elemento neutro da soma. Por exemplo:
+7 + 0 = 7
+Portanto, os elementos neutros na multiplicação e na soma são, respectivamente, 1 e 0.</t>
+        </is>
+      </c>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>PH01</t>
+        </is>
+      </c>
+      <c r="J544" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K544" t="inlineStr"/>
+      <c r="L544" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>Durante a preparação de uma grande festa, os organizadores precisavam organizar as cadeiras em várias filas. Eles tinham 4 filas, e em cada fila, colocaram 5 grupos de 6 cadeiras. Dois organizadores decidiram calcular o total de cadeiras de maneiras diferentes. O organizador A agrupou as cadeiras por fila primeiro e, em seguida, multiplicou pelo número de grupos de cadeiras. O organizador B fez o oposto, agrupando primeiro os grupos de cadeiras e depois multiplicando pelo número de filas. No final, ambos chegaram ao mesmo total de cadeiras.
+Qual propriedade da multiplicação justifica que ambos os organizadores obtiveram o mesmo resultado?</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>Propriedade Comutativa.</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>Propriedade Distributiva.</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>Propriedade Associativa.</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>Elemento Neutro.</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr"/>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>A propriedade associativa da multiplicação afirma que, independentemente de como os números são agrupados, o produto permanece o mesmo. Nesse caso, tanto (4 × 5) × 6 quanto 4 × (5 × 6) resultam no mesmo total de cadeiras: 120.</t>
+        </is>
+      </c>
+      <c r="I545" t="inlineStr">
+        <is>
+          <t>PH01</t>
+        </is>
+      </c>
+      <c r="J545" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K545" t="inlineStr"/>
+      <c r="L545" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>Pedro está organizando uma festa e comprou três pacotes de balões. O primeiro pacote contém 120 balões amarelos, o segundo contém 180 balões verdes e o terceiro contém 240 balões brancos. Ele quer dividir todos os balões em grupos de igual tamanho, utilizando o maior número possível de balões em cada grupo.
+Qual será o número de balões em cada grupo?</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr"/>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>Para encontrar o maior número possível de balões em cada grupo, é preciso determinar o Máximo Divisor Comum (MDC) dos três números: 120, 180 e 240. 
+Primeiro, deve-se fatorar cada número em seus fatores primos:
+120 = 23 x 3 x 5
+180 = 22 x 32 x 5
+120 = 24 x 3 x 5
+O MDC é o produtos dos menores expoentes dos fatores comuns:
+Fator 2: menor expoente é 2
+Fator 3: menor expoente é 1
+Fator 5: menor expoente é 1
+Portanto, o MDC é: 
+22 x 3 x 5 = 4 x 3 x 5 = 60.
+Portanto, o número de balões em cada grupo será 60.</t>
+        </is>
+      </c>
+      <c r="I546" t="inlineStr">
+        <is>
+          <t>PH01</t>
+        </is>
+      </c>
+      <c r="J546" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K546" t="inlineStr"/>
+      <c r="L546" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>Um colecionador possui 300 figurinhas ilustradas. Ao comprar doze pacotes, com dez figurinhas cada, ele percebe que cada pacote tinha uma figurinha repetida e, por serem repetidas, não poderiam ser contabilizadas em sua coleção. Sendo assim, sua coleção possou a ter:</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>310 figurinhas</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>312 figurinhas</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>408 figurinhas</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>420 figurinhas</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr"/>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>300 + 12 x (10 - 1) = 300 + 12 x 9 = 300 + 108 = 408</t>
+        </is>
+      </c>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>PH01</t>
+        </is>
+      </c>
+      <c r="J547" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K547" t="inlineStr"/>
+      <c r="L547" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>Em uma escola, a turma do 7º ano começou o ano com 35 alunos e durante o ano recebeu mais 5 alunos. Se no fim do ano 10 alunos ficaram de recuperação, a quantidade de alunos que foram aprovados direto, sem passar pela recuperação, foi:</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr"/>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>(35 + 5) – 10 = 40 – 10 = 30</t>
+        </is>
+      </c>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>PH01</t>
+        </is>
+      </c>
+      <c r="J548" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K548" t="inlineStr"/>
+      <c r="L548" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>Em uma campanha de doação de brinquedos, as quatro turmas do ensino fundamental de uma escola conseguiram arrecadar 345 bonecos. Se o 6º ano doou 65 bonecos, o 8º ano doou 95 e o 9º ano 83 bonecos, então o 7º ano doou:</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr"/>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>Total da arrecadação (4 turmas)  → de 345 bonecos
+6° + 8° + 9° →  65 + 95 + 83 = 243 bonecos
+7° ano → 345 – 243 = 102 bonecos</t>
+        </is>
+      </c>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t>PH01</t>
+        </is>
+      </c>
+      <c r="J549" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K549" t="inlineStr"/>
+      <c r="L549" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>Ao passar pelo caixa de um supermercado, dona Maria percebe que suas compras totalizaram R$ 243,00 e, para pagar, usou três notas de R$ 100,00. Sendo assim, o troco que dona Maria receberá será de:</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>R$ 47,00</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>R$ 53,00</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>R$ 57,00</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>R$ 60,00</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr"/>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>3 x 100 – 243
+300 – 243 = R$ 57,00</t>
+        </is>
+      </c>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>PH01</t>
+        </is>
+      </c>
+      <c r="J550" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K550" t="inlineStr"/>
+      <c r="L550" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>Em uma determinada atividade em sala de aula, o professor de matemática pede que seus alunos reescrevam a seguinte expressão numérica, sem que alterem seu resultado:  (4+5) + 2 + 3x(1+7). Um aluno que conseguiu reescrever corretamente, mostrou a seguinte expressão ao professor:</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>2x(4+5) + 3+(1+7)</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>4 + (5+2) +  (3+1)x7</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>(4+5) + 5x(1+7)</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>4 + (5+2) + 3x1 + 3x7</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr"/>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>Uma outra maneira de escrever esta expressão é 4 + (5+2) + 3x1 + 3x7.</t>
+        </is>
+      </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>PH01</t>
+        </is>
+      </c>
+      <c r="J551" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K551" t="inlineStr"/>
+      <c r="L551" t="inlineStr">
+        <is>
+          <t>7ano</t>
         </is>
       </c>
     </row>

--- a/questoes.xlsx
+++ b/questoes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L551"/>
+  <dimension ref="A1:L601"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27033,7 +27033,6 @@
           <t>São fotossintetizantes.</t>
         </is>
       </c>
-      <c r="F502" t="inlineStr"/>
       <c r="G502" t="inlineStr">
         <is>
           <t>C</t>
@@ -27054,7 +27053,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K502" t="inlineStr"/>
       <c r="L502" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -27088,7 +27086,6 @@
           <t>transformar oxigênio em gás carbônico.</t>
         </is>
       </c>
-      <c r="F503" t="inlineStr"/>
       <c r="G503" t="inlineStr">
         <is>
           <t>C</t>
@@ -27109,7 +27106,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K503" t="inlineStr"/>
       <c r="L503" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -27143,7 +27139,6 @@
           <t>temperatura ideal para crescimento.</t>
         </is>
       </c>
-      <c r="F504" t="inlineStr"/>
       <c r="G504" t="inlineStr">
         <is>
           <t>B</t>
@@ -27164,7 +27159,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K504" t="inlineStr"/>
       <c r="L504" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -27198,7 +27192,6 @@
           <t>Parasitismo de outros organismos.</t>
         </is>
       </c>
-      <c r="F505" t="inlineStr"/>
       <c r="G505" t="inlineStr">
         <is>
           <t>B</t>
@@ -27219,7 +27212,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K505" t="inlineStr"/>
       <c r="L505" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -27253,7 +27245,6 @@
           <t>Paramécios e bactérias.</t>
         </is>
       </c>
-      <c r="F506" t="inlineStr"/>
       <c r="G506" t="inlineStr">
         <is>
           <t>A</t>
@@ -27274,7 +27265,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K506" t="inlineStr"/>
       <c r="L506" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -27308,7 +27298,6 @@
           <t>Possui metabolismo e possui nadadeiras.</t>
         </is>
       </c>
-      <c r="F507" t="inlineStr"/>
       <c r="G507" t="inlineStr">
         <is>
           <t>C</t>
@@ -27367,7 +27356,6 @@
           <t>A árvore é autotrófica e não produz seu próprio alimento.</t>
         </is>
       </c>
-      <c r="F508" t="inlineStr"/>
       <c r="G508" t="inlineStr">
         <is>
           <t>A</t>
@@ -27425,7 +27413,6 @@
           <t>Acelular.</t>
         </is>
       </c>
-      <c r="F509" t="inlineStr"/>
       <c r="G509" t="inlineStr">
         <is>
           <t>A</t>
@@ -27446,7 +27433,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K509" t="inlineStr"/>
       <c r="L509" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -27482,7 +27468,6 @@
           <t>vírus.</t>
         </is>
       </c>
-      <c r="F510" t="inlineStr"/>
       <c r="G510" t="inlineStr">
         <is>
           <t>D</t>
@@ -27503,7 +27488,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K510" t="inlineStr"/>
       <c r="L510" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -27536,7 +27520,6 @@
           <t>capsídeo e núcleo.</t>
         </is>
       </c>
-      <c r="F511" t="inlineStr"/>
       <c r="G511" t="inlineStr">
         <is>
           <t>B</t>
@@ -27557,7 +27540,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K511" t="inlineStr"/>
       <c r="L511" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -27590,7 +27572,6 @@
           <t>A diversidade sociocultural do Brasil não está ligada ao território, mas sim à economia global.</t>
         </is>
       </c>
-      <c r="F512" t="inlineStr"/>
       <c r="G512" t="inlineStr">
         <is>
           <t>B</t>
@@ -27611,7 +27592,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K512" t="inlineStr"/>
       <c r="L512" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -27645,7 +27625,6 @@
           <t>A noção de território não tem impacto na organização política do Brasil, já que todas as regiões seguem as mesmas políticas públicas.</t>
         </is>
       </c>
-      <c r="F513" t="inlineStr"/>
       <c r="G513" t="inlineStr">
         <is>
           <t>C</t>
@@ -27666,7 +27645,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K513" t="inlineStr"/>
       <c r="L513" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -27700,7 +27678,6 @@
           <t>Pela exclusão de influências externas.</t>
         </is>
       </c>
-      <c r="F514" t="inlineStr"/>
       <c r="G514" t="inlineStr">
         <is>
           <t>B</t>
@@ -27721,7 +27698,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K514" t="inlineStr"/>
       <c r="L514" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -27755,7 +27731,6 @@
           <t>competição entre o uso agrícola e a preservação ambiental.</t>
         </is>
       </c>
-      <c r="F515" t="inlineStr"/>
       <c r="G515" t="inlineStr">
         <is>
           <t>A</t>
@@ -27776,7 +27751,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K515" t="inlineStr"/>
       <c r="L515" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -27810,7 +27784,6 @@
           <t>O Poder Executivo julga casos de violação de leis, o Poder Legislativo executa as políticas públicas, e o Poder Judiciário cria as leis.</t>
         </is>
       </c>
-      <c r="F516" t="inlineStr"/>
       <c r="G516" t="inlineStr">
         <is>
           <t>C</t>
@@ -27831,7 +27804,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K516" t="inlineStr"/>
       <c r="L516" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -27872,7 +27844,6 @@
           <t>Estados Unidos, Canadá, África do Sul e Indonésia.</t>
         </is>
       </c>
-      <c r="F517" t="inlineStr"/>
       <c r="G517" t="inlineStr">
         <is>
           <t>C</t>
@@ -27893,7 +27864,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K517" t="inlineStr"/>
       <c r="L517" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -27926,7 +27896,6 @@
           <t>Bolívia e Venezuela.</t>
         </is>
       </c>
-      <c r="F518" t="inlineStr"/>
       <c r="G518" t="inlineStr">
         <is>
           <t>B</t>
@@ -27986,7 +27955,6 @@
           <t>Arroio Chuí.</t>
         </is>
       </c>
-      <c r="F519" t="inlineStr"/>
       <c r="G519" t="inlineStr">
         <is>
           <t>D</t>
@@ -28050,7 +28018,6 @@
           <t>Apenas I, II, e III são verdadeiras.</t>
         </is>
       </c>
-      <c r="F520" t="inlineStr"/>
       <c r="G520" t="inlineStr">
         <is>
           <t>C</t>
@@ -28112,7 +28079,6 @@
           <t>o espaço controlado pelas instituições políticas e militares de um país.</t>
         </is>
       </c>
-      <c r="F521" t="inlineStr"/>
       <c r="G521" t="inlineStr">
         <is>
           <t>D</t>
@@ -28133,7 +28099,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K521" t="inlineStr"/>
       <c r="L521" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -28168,7 +28133,6 @@
           <t>A construção de grandes monumentos.</t>
         </is>
       </c>
-      <c r="F522" t="inlineStr"/>
       <c r="G522" t="inlineStr">
         <is>
           <t>B</t>
@@ -28189,7 +28153,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K522" t="inlineStr"/>
       <c r="L522" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -28225,7 +28188,6 @@
           <t>impedir o avanço do Império Bizantino no Oriente Médio.</t>
         </is>
       </c>
-      <c r="F523" t="inlineStr"/>
       <c r="G523" t="inlineStr">
         <is>
           <t>C</t>
@@ -28246,7 +28208,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K523" t="inlineStr"/>
       <c r="L523" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -28280,7 +28241,6 @@
           <t>Assembleias comerciais.</t>
         </is>
       </c>
-      <c r="F524" t="inlineStr"/>
       <c r="G524" t="inlineStr">
         <is>
           <t>A</t>
@@ -28301,7 +28261,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K524" t="inlineStr"/>
       <c r="L524" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -28336,7 +28295,6 @@
           <t>corporações de ofício.</t>
         </is>
       </c>
-      <c r="F525" t="inlineStr"/>
       <c r="G525" t="inlineStr">
         <is>
           <t>D</t>
@@ -28357,7 +28315,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K525" t="inlineStr"/>
       <c r="L525" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -28392,7 +28349,6 @@
           <t>descoberta de novas terras.</t>
         </is>
       </c>
-      <c r="F526" t="inlineStr"/>
       <c r="G526" t="inlineStr">
         <is>
           <t>C</t>
@@ -28413,7 +28369,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K526" t="inlineStr"/>
       <c r="L526" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -28447,7 +28402,6 @@
           <t>a descoberta de novas vacinas, o que permitiu aos europeus superar doenças fatais como a peste negra.</t>
         </is>
       </c>
-      <c r="F527" t="inlineStr"/>
       <c r="G527" t="inlineStr">
         <is>
           <t>C</t>
@@ -28506,7 +28460,6 @@
           <t>iniciou-se no século XIII e não provocou significativas mudanças no sistema e nas relações feudais vigentes.</t>
         </is>
       </c>
-      <c r="F528" t="inlineStr"/>
       <c r="G528" t="inlineStr">
         <is>
           <t>A</t>
@@ -28570,7 +28523,6 @@
           <t>forma de convencer os fiéis a participarem das expedições.</t>
         </is>
       </c>
-      <c r="F529" t="inlineStr"/>
       <c r="G529" t="inlineStr">
         <is>
           <t>D</t>
@@ -28591,7 +28543,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K529" t="inlineStr"/>
       <c r="L529" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -28627,7 +28578,6 @@
           <t>o processo de migração de comerciantes que viviam nos feudos para os burgos.</t>
         </is>
       </c>
-      <c r="F530" t="inlineStr"/>
       <c r="G530" t="inlineStr">
         <is>
           <t>D</t>
@@ -28648,7 +28598,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K530" t="inlineStr"/>
       <c r="L530" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -28684,7 +28633,6 @@
           <t>monopólio de determinadas atividades econômicas.</t>
         </is>
       </c>
-      <c r="F531" t="inlineStr"/>
       <c r="G531" t="inlineStr">
         <is>
           <t>D</t>
@@ -28705,7 +28653,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K531" t="inlineStr"/>
       <c r="L531" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -28740,7 +28687,6 @@
           <t>Frágil</t>
         </is>
       </c>
-      <c r="F532" t="inlineStr"/>
       <c r="G532" t="inlineStr">
         <is>
           <t>C</t>
@@ -28761,7 +28707,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K532" t="inlineStr"/>
       <c r="L532" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -28796,7 +28741,6 @@
           <t>Nomear Poseidon.</t>
         </is>
       </c>
-      <c r="F533" t="inlineStr"/>
       <c r="G533" t="inlineStr">
         <is>
           <t>B</t>
@@ -28817,7 +28761,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K533" t="inlineStr"/>
       <c r="L533" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -28857,7 +28800,6 @@
           <t>Rapazinhos.</t>
         </is>
       </c>
-      <c r="F534" t="inlineStr"/>
       <c r="G534" t="inlineStr">
         <is>
           <t>B</t>
@@ -28878,7 +28820,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K534" t="inlineStr"/>
       <c r="L534" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -28913,7 +28854,6 @@
           <t>Substantivo comum, concreto.</t>
         </is>
       </c>
-      <c r="F535" t="inlineStr"/>
       <c r="G535" t="inlineStr">
         <is>
           <t>B</t>
@@ -28934,7 +28874,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K535" t="inlineStr"/>
       <c r="L535" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -28970,7 +28909,6 @@
           <t>Brilhantes</t>
         </is>
       </c>
-      <c r="F536" t="inlineStr"/>
       <c r="G536" t="inlineStr">
         <is>
           <t>D</t>
@@ -28991,7 +28929,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K536" t="inlineStr"/>
       <c r="L536" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -29041,7 +28978,6 @@
           <t>um substantivo concreto, pois indica o ser denominado.</t>
         </is>
       </c>
-      <c r="F537" t="inlineStr"/>
       <c r="G537" t="inlineStr">
         <is>
           <t>A</t>
@@ -29062,7 +28998,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K537" t="inlineStr"/>
       <c r="L537" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -29112,7 +29047,6 @@
           <t>sintagma verbal, por se referir à relação de posse entre a caneca e a água.</t>
         </is>
       </c>
-      <c r="F538" t="inlineStr"/>
       <c r="G538" t="inlineStr">
         <is>
           <t>B</t>
@@ -29133,7 +29067,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K538" t="inlineStr"/>
       <c r="L538" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -29169,7 +29102,6 @@
           <t>“interminável”, “prazerosas” e “diferentes”.</t>
         </is>
       </c>
-      <c r="F539" t="inlineStr"/>
       <c r="G539" t="inlineStr">
         <is>
           <t>D</t>
@@ -29190,7 +29122,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K539" t="inlineStr"/>
       <c r="L539" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -29228,7 +29159,6 @@
           <t>é parte integral do substantivo e não se refere necessariamente à sua dimensão.</t>
         </is>
       </c>
-      <c r="F540" t="inlineStr"/>
       <c r="G540" t="inlineStr">
         <is>
           <t>D</t>
@@ -29249,7 +29179,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K540" t="inlineStr"/>
       <c r="L540" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -29285,7 +29214,6 @@
           <t>de definição e concretização.</t>
         </is>
       </c>
-      <c r="F541" t="inlineStr"/>
       <c r="G541" t="inlineStr">
         <is>
           <t>C</t>
@@ -29306,7 +29234,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K541" t="inlineStr"/>
       <c r="L541" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -29340,7 +29267,6 @@
           <t>48</t>
         </is>
       </c>
-      <c r="F542" t="inlineStr"/>
       <c r="G542" t="inlineStr">
         <is>
           <t>B</t>
@@ -29364,7 +29290,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K542" t="inlineStr"/>
       <c r="L542" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -29399,7 +29324,6 @@
           <t>Apenas o participante 2, uma vez que a soma deve ser feita da direita para a esquerda.</t>
         </is>
       </c>
-      <c r="F543" t="inlineStr"/>
       <c r="G543" t="inlineStr">
         <is>
           <t>A</t>
@@ -29458,7 +29382,6 @@
           <t>0 e 1</t>
         </is>
       </c>
-      <c r="F544" t="inlineStr"/>
       <c r="G544" t="inlineStr">
         <is>
           <t>A</t>
@@ -29483,7 +29406,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K544" t="inlineStr"/>
       <c r="L544" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -29517,7 +29439,6 @@
           <t>Elemento Neutro.</t>
         </is>
       </c>
-      <c r="F545" t="inlineStr"/>
       <c r="G545" t="inlineStr">
         <is>
           <t>C</t>
@@ -29538,7 +29459,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K545" t="inlineStr"/>
       <c r="L545" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -29572,7 +29492,6 @@
           <t>60</t>
         </is>
       </c>
-      <c r="F546" t="inlineStr"/>
       <c r="G546" t="inlineStr">
         <is>
           <t>D</t>
@@ -29604,7 +29523,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K546" t="inlineStr"/>
       <c r="L546" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -29637,7 +29555,6 @@
           <t>420 figurinhas</t>
         </is>
       </c>
-      <c r="F547" t="inlineStr"/>
       <c r="G547" t="inlineStr">
         <is>
           <t>C</t>
@@ -29658,7 +29575,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K547" t="inlineStr"/>
       <c r="L547" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -29691,7 +29607,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="F548" t="inlineStr"/>
       <c r="G548" t="inlineStr">
         <is>
           <t>A</t>
@@ -29712,7 +29627,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K548" t="inlineStr"/>
       <c r="L548" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -29745,7 +29659,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="F549" t="inlineStr"/>
       <c r="G549" t="inlineStr">
         <is>
           <t>B</t>
@@ -29768,7 +29681,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K549" t="inlineStr"/>
       <c r="L549" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -29801,7 +29713,6 @@
           <t>R$ 60,00</t>
         </is>
       </c>
-      <c r="F550" t="inlineStr"/>
       <c r="G550" t="inlineStr">
         <is>
           <t>C</t>
@@ -29823,7 +29734,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K550" t="inlineStr"/>
       <c r="L550" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -29856,7 +29766,6 @@
           <t>4 + (5+2) + 3x1 + 3x7</t>
         </is>
       </c>
-      <c r="F551" t="inlineStr"/>
       <c r="G551" t="inlineStr">
         <is>
           <t>D</t>
@@ -29877,10 +29786,3109 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K551" t="inlineStr"/>
       <c r="L551" t="inlineStr">
         <is>
           <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>Durante um passeio pelo parque em um dia quente de verão, Pedro percebeu que ao sentar em um banco de madeira, uma leve brisa parecia refrescá-lo. Observou também que, ao se aproximar de um muro, sentia o calor vindo da superfície.
+O que explica a sensação de frescor ao sentir a brisa e o calor ao se aproximar do muro?</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>O ar em movimento (brisa) aquece a superfície do corpo, enquanto o muro libera calor para o ambiente.</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>O ar em movimento (brisa) ajuda a dissipar o calor do corpo, enquanto o muro absorve calor e o libera para o ambiente.</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>O ar em movimento (brisa) retém o calor próximo ao corpo, enquanto o muro resfria o ar ao seu redor.</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>O ar em movimento (brisa) absorve o calor do corpo, enquanto o muro retém calor e o absorve para si.</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>O ar em movimento (brisa) aumenta a temperatura do corpo, enquanto o muro cria uma corrente de ar quente.</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>A brisa aumenta a evaporação do suor e promove a perda de calor do corpo, gerando uma sensação de frescor. O muro, por sua vez, aquece ao absorver calor do sol e libera essa energia para o ambiente, causando a sensação de calor ao se aproximar.</t>
+        </is>
+      </c>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J552" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K552" t="inlineStr"/>
+      <c r="L552" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>As correntes oceânicas quentes, como a Corrente do Golfo, transportam calor das regiões equatoriais para latitudes mais altas, enquanto as correntes oceânicas frias, como a Corrente de Humboldt, levam águas mais frias das regiões polares para áreas próximas ao Equador. Esses movimentos influenciam a temperatura e a umidade do ar, afetando o clima de diversas regiões costeiras.
+Disponível em: https://www.todoestudo.com.br/geografia/corrente-de-humboldt.
+A circulação das correntes oceânicas, como a Corrente do Golfo e a Corrente de Humboldt, contribui para:</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>A redução da temperatura das regiões equatoriais, levando águas quentes para os polos.</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>A formação de ventos alísios nas regiões polares, que deslocam o calor para os trópicos.</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>A transferência de calor das regiões tropicais para as temperadas, regulando o clima local.</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>A retenção de calor nos oceanos, mantendo as temperaturas constantes ao longo do ano.</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>A criação de vórtices de ar quente nas zonas polares, aumentando as temperaturas locais.</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>As correntes oceânicas são responsáveis por transportar calor das regiões tropicais para as áreas temperadas, influenciando o clima e a temperatura das regiões costeiras ao longo de seu percurso.</t>
+        </is>
+      </c>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J553" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>8a_ph02_cie_02.jpg</t>
+        </is>
+      </c>
+      <c r="L553" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>Leia o texto a seguir.
+O vapor d’água proveniente da transpiração das plantas e da evaporação na floresta amazônica, transportado pelas massas de ar, pode ter impacto sobre as chuvas do país, incluindo as regiões Sudeste e Centro-Oeste. Essa é uma das conclusões do projeto ‘Rios voadores’, que vem estudando a importância da floresta amazônica no ciclo hidrológico brasileiro.
+HUCHE, Marcella. Ciência Hoje. Disponível em:  https://cienciahoje.periodicos.capes.gov.br/storage/acervo/ch/ch_260.pdf#page=60 . Acesso em: 21 out. 2024.
+Como as mudanças climáticas globais causadas por ações humanas podem impactar o transporte de vapor d'água na atmosfera e, consequentemente, a circulação das massas de ar e as chuvas nas regiões Sudeste e Centro-Oeste do Brasil?</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>Aumento na frequência de massas de ar frias, reduzindo as chuvas.</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>Diminuição na intensidade das massas de ar úmidas, reduzindo as chuvas.</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>Aumento na frequência de massas de ar secas, aumentando as chuvas.</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>Diminuição na intensidade das massas de ar quentes, aumentando as chuvas.</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>Aumento na frequência de massas de ar úmidas, sem alteração nas chuvas.</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>A diminuição na intensidade das massas de ar úmidas resultaria em menos vapor d'água sendo transportado, o que reduziria as chuvas. Sendo assim, as mudanças climáticas podem alterar os padrões de circulação atmosférica e reduzir a umidade transportada.</t>
+        </is>
+      </c>
+      <c r="I554" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J554" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K554" t="inlineStr"/>
+      <c r="L554" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>A circulação atmosférica é um processo dinâmico que envolve a movimentação de massas de ar entre áreas de diferentes pressões. Em regiões de alta pressão, o ar tende a descer e se espalhar horizontalmente, enquanto em regiões de baixa pressão, o ar tende a subir, criando correntes ascendentes. Essas movimentações influenciam diretamente o clima de uma região.
+A circulação atmosférica contribui para a formação de frentes climáticas, pois:</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>Mantém o ar estático em regiões de alta e baixa pressão.</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>Impede a movimentação de massas de ar entre regiões de diferentes pressões.</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>Mantém o ar em movimento horizontal constante em regiões de alta e baixa pressão.</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>Move o ar de regiões de alta pressão para baixa pressão, criando correntes ascendentes.</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>Move o ar de regiões de baixa pressão para alta pressão, criando correntes descendentes.</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>A circulação atmosférica move o ar de regiões de alta pressão para regiões de baixa pressão. Em regiões de baixa pressão, o ar tende a subir, criando correntes ascendentes que são essenciais para a formação de frentes climáticas.</t>
+        </is>
+      </c>
+      <c r="I555" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J555" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K555" t="inlineStr"/>
+      <c r="L555" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>Em regiões costeiras, a presença de grandes corpos d'água, como oceanos, influencia o comportamento do clima local. Durante o dia, a água do mar absorve calor de forma lenta, enquanto a terra aquece mais rapidamente. À noite, a água libera o calor acumulado de forma gradual, fazendo com que a temperatura nas regiões próximas ao mar seja mais amena em comparação com áreas mais afastadas.
+A diferença na absorção e liberação de calor entre a água do mar e a terra é causada principalmente por:</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>A água refletir a maior parte da radiação solar, enquanto a terra a absorve completamente.</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>A água evaporar rapidamente, o que aumenta a temperatura ao redor.</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>A terra liberar calor para a água, que o mantém retido por mais tempo.</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>A água ter uma maior capacidade de armazenar calor do que a terra.</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>A água aquecer e esfriar mais rapidamente que a terra.</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>A água possui um alto calor específico, o que significa que ela absorve e libera calor mais lentamente que a terra, resultando em uma moderação da temperatura em regiões costeiras.</t>
+        </is>
+      </c>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J556" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K556" t="inlineStr"/>
+      <c r="L556" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>Olhar para o céu durante o dia pode fornecer um indicativo de como estará o tempo daqui algumas horas. As nuvens podem ser um indicativo para a chuva. Nuvens são formadas por:</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>água no estado gasoso, oriunda do espaço.</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>água no estado gasoso, oriunda da atmosfera.</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>água no estado líquido, oriunda do espaço.</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>água do estado líquido, oriunda da condensação da água da atmosfera.</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>água no estado sólido, oriundo do mar, rio ou lago.</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>As nuvens são formadas por água no estado liquido, a qual entrou na atmosfera pela vaporização da água presente no planeta (rios, mares, etc.).</t>
+        </is>
+      </c>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J557" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K557" t="inlineStr"/>
+      <c r="L557" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>“ O tempo da região sul do Brasil ao longo de 30 anos, sempre foi seco e de temperaturas baixa”.
+A frase acima, quanto ao uso da palavra tempo está:</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>incorreta, pois as condições meteorológicas obtidas ao longo de anos se refere ao clima.</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>incorreta, pois o clima é que é caracterizado pelas condições atmosféricas momentâneas.</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>correta, pois as condições meteorológicas obtidas ao longo de anos se refere ao tempo.</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>correta, pois o clima é que é caracterizado pelas condições atmosféricas momentâneas.</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>correta, pois o tempo se refere aos 30 anos que se passaram.</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>A afirmação está incorreta, pois a média das condições atmosféricas mais frequentes em uma região ao longo de um certo intervalo de tempo é chamada de clima. Já o tempo considera as condições atmosféricas momentâneas de uma região.</t>
+        </is>
+      </c>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J558" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K558" t="inlineStr"/>
+      <c r="L558" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>O ciclo da água explica a formação das nuvens e a presença de umidade no ar. As chuvas são formadas pelo vapor de água na atmosfera. Portanto</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>quanto menor a umidade do ar, menor é quantidade vapor de água na atmosfera, logo maior será a probabilidade de chuvas.</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>quanto maior a umidade do ar, maior é quantidade vapor de água na atmosfera, logo maiores serão as chances de ocorrência de chuvas.</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>quanto maior a umidade do ar, maior é quantidade vapor de água na atmosfera, logo menores serão as chances de ocorrência de chuvas.</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>quanto menor a umidade do ar, maior é quantidade vapor de água na atmosfera, logo maior será a probabilidade de chuvas.</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>quanto maior a umidade do ar, menor é quantidade vapor de água na atmosfera, logo maior será a probabilidade de chuvas.</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>A umidade do ar está relacionada com a quantidade de vapor de água na atmosfera. Quanto maior a umidade, maior é a quantidade de vapor de água, logo maior será a probabilidade de chuvas.</t>
+        </is>
+      </c>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J559" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K559" t="inlineStr"/>
+      <c r="L559" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>Disponível em: &lt;http://wwweducacionalnet1.cdn.educacional.com.br/imagens/reportagens/aguas_abril/img_pg7b.jpg&gt;. Acesso em 2 set. 2018.
+A figura mostra a representação de um aparelho que mede a quantidade de chuva de uma região. Ele é chamado de:</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>barômetro.</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>pluviômetro.</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>termômetro.</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>anemômetro.</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>aquametro.</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>O pluviômetro é um cilindro graduado, no qual a água é recolhida e estimada.</t>
+        </is>
+      </c>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J560" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>8a_ph02_cie_09.jpg</t>
+        </is>
+      </c>
+      <c r="L560" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>Analise a ilustração a seguir.
+Disponível em: &lt;https://cursinhocucafresca.files.wordpress.com/2011/05/dinc3a2mica-climc3a1tica-e-formac3a7c3b5es-vegetais.pdf&gt;. Acesso em: 2 set. 2018.
+O movimento de ar representado indica a formação de uma frente:</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>fria, caracterizada pela chegada de uma massa de ar frio em uma região na qual existe uma massa de ar quente.</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>fria, caracterizada pela chegada de uma massa de ar quente em uma região na qual existe uma massa de ar frio.</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>quente, caracterizada pela chegada de uma massa de ar quente em uma região na qual existe uma massa de ar frio.</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>quente, caracterizada pela chegada de uma massa de ar frio em uma região na qual existe uma massa de ar quente.</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>normal, caracterizada pela chegada de uma massa de ar frio em uma região na qual existe uma massa de ar quente.</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>A ilustração mostra a chegada de uma massa de ar frio sobre uma região com uma massa de ar quente, caracterizando a chegada de uma frente fria.</t>
+        </is>
+      </c>
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J561" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>8a_ph02_cie_10.jpg</t>
+        </is>
+      </c>
+      <c r="L561" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>A população humana no planeta apresenta uma diversidade de rotas de dispersão, influenciadas por fatores físicos, naturais e históricos. No continente americano, a colonização, as migrações forçadas e as oportunidades econômicas moldaram os padrões populacionais. Fatores como clima, relevo e recursos naturais também desempenham papéis cruciais na distribuição da população.
+Assinale a alternativa que melhor descreve um fator que contribuiu para a dispersão da população no continente americano.</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>Clima frio na América do Sul.</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>Presença de grandes desertos no norte da América.</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>Disponibilidade de recursos hídricos e terras férteis.</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>Relevo montanhoso na costa oeste da América do Norte.</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>Densidade populacional uniforme em todo o continente.</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>A disponibilidade de recursos hídricos e terras férteis atraiu populações ao longo da história, favorecendo a agricultura e o desenvolvimento de comunidades.</t>
+        </is>
+      </c>
+      <c r="I562" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J562" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K562" t="inlineStr"/>
+      <c r="L562" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>A América Anglo-Saxônica, composta principalmente pelos Estados Unidos e Canadá, têm sistemas políticos democráticos e uma influência significativa na economia e na cultura global. Além disso, a América Anglo-Saxônica possui vastos recursos naturais, incluindo petróleo, madeira e terras agrícolas.
+Assinale a alternativa que melhor descreve uma característica da América Anglo-Saxônica:</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>Alta diversidade cultural e étnica.</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>Baixo desenvolvimento econômico.</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>Exclusão de influências imigratórias.</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>Predomínio de sistemas autoritários.</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>Riqueza de recursos naturais escassos.</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>A América Anglo-Saxônica é conhecida pela alta diversidade cultural e étnica, resultado de longos processos migratórios e coloniais.</t>
+        </is>
+      </c>
+      <c r="I563" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J563" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K563" t="inlineStr"/>
+      <c r="L563" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>A formação territorial da América Anglo-Saxônica está ligada vários processos históricos, dentre eles a "Marcha para o Oeste" nos Estados Unidos.
+Um aspecto da Marcha para o Oeste nos Estados Unidos foi o(a)</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>Estagnação econômica.</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>Redução das tensões sociais.</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>Aumento da população indígena.</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>Conquista de terras para colonização.</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>Integração pacífica com os povos nativos.</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>A Marcha para o Oeste foi marcada pela conquista de terras, visando a colonização e o assentamento, frequentemente em detrimento das populações indígenas.</t>
+        </is>
+      </c>
+      <c r="I564" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J564" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K564" t="inlineStr"/>
+      <c r="L564" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>A Guerra Civil Americana, ocorrida entre 1861 e 1865, foi um conflito interno nos Estados Unidos. O resultado da guerra teve um impacto significativo na formação territorial e na economia do país.
+Qual das seguintes causas foi um dos principais motivos da Guerra Civil Americana?</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>Disputa por territórios com o Canadá.</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>Conflito com populações indígenas.</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>Questão da escravidão.</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>Expansão para o oeste.</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>Revolução Industrial.</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>A questão da escravidão foi um dos principais motivos da Guerra Civil Americana, gerando divisões profundas entre os estados do norte e do sul.</t>
+        </is>
+      </c>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J565" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K565" t="inlineStr"/>
+      <c r="L565" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>A formação territorial do Canadá foi influenciada por diversos eventos históricos, incluindo o Tratado de Paris de 1763. Esse tratado encerrou a Guerra dos Sete Anos e foi crucial para a configuração territorial do Canadá moderno.
+Uma das consequências do Tratado de Paris de 1763 para a formação territorial do Canadá foi a:</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>independência do Canadá da Grã-Bretanha.</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>cessão de territórios franceses para os britânicos.</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>unificação das colônias britânicas na América do Norte.</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>criação da província de Quebec como uma colônia francesa.</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>assinatura de um acordo de livre comércio com os Estados Unidos.</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>O Tratado de Paris de 1763 resultou na cessão de vastos territórios franceses na América do Norte para os britânicos, o que foi crucial para a formação territorial do Canadá moderno.</t>
+        </is>
+      </c>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J566" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K566" t="inlineStr"/>
+      <c r="L566" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>Banco de imagens/Arquivo da editora.
+Sistema de ensino PH. EFII9. Caderno 1. Módulo 5.
+A menor ocupação  demográfica na parte norte da América anglo saxônica se deve</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>ao clima frio e polar.</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>ao relevo plano e fértil.</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>a presença de agricultura mecanizada.</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>a rede hidrográfica planáltica.</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>a formação vegetal temperada.</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>A região norte do continente americano é uma área anecúmena - ou seja, de difícil ocupação -, apresentando condições climáticas muito rigorosas. Assim, as características do clima frio e polar dificultam a ocupação dessa área do território anglo-saxônico.</t>
+        </is>
+      </c>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J567" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>8a_ph02_geo_06.jpg</t>
+        </is>
+      </c>
+      <c r="L567" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>Leia o texto a seguir.
+A história dos Estados Unidos da América, hoje conhecida por nós, inicia-se a partir do século XVI, quando exploradores europeus aportaram no lado norte do continente americano. Até então, apenas nativos habitavam no local, a partir dessa conexão com o continente europeu, os Estados Unidos passaram a ser colônia da Inglaterra. Inicialmente estes colonizaram a parte leste do país, o que corresponde ao litoral que é banhado pelo oceano Atlântico. Logo depois a parte central foi colonizada pela França e a parte sudeste e sudoeste pela Espanha.
+[...]
+Disponível em:&lt; https://www.infoescola.com/historia/colonizacao-dos-estados-unidos-da-america/&gt;. Acesso em: 16 mar.2020.
+A relação entre as várias etnias indígenas americanas e o colonizador foi</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>amigável.</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>industrial.</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>comercial.</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>conflituosa.</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>cooperativa.</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>Os colonizadores ingleses não respeitaram as territorialidades indígenas e promoveram o extermínio genocida das populações indígenas através de doenças e do conflito direto pela posse de território.</t>
+        </is>
+      </c>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J568" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K568" t="inlineStr"/>
+      <c r="L568" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>Observe o mapa físico de parte da América do Norte:
+Disponível em: &lt; https://www.infoescola.com/wp-content/uploads/2009/08/full-1-e795eccc0c.jpg&gt;. Acesso em: 13 mar 2020.
+O que o aspecto do relevo do oeste da América do Norte revela?</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>Áreas com tectonismo inativo.</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>Áreas com tectonismo ativo.</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>Áreas com baixo aproveitamento hídrico.</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>Áreas com alto aproveitamento hídrico.</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>Área de planícies inundáveis.</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>A costa oeste é reconhecida por cadeias montanhosas entre 1000 e 2000 metros de altitude, tendo origem tectônica.</t>
+        </is>
+      </c>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J569" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>8a_ph02_geo_08.png</t>
+        </is>
+      </c>
+      <c r="L569" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>Leia o texto a seguir.
+O dia 25 de junho de 1876 amanheceu com cheiro e gosto de glória para o general George Armstrong Custer e seus 647 homens da 7ª Cavalaria. Finalmente, a caça aos índios que haviam se rebelado contra o governo dos Estados Unidos tinha chegado ao fim. Ao longo do vale do rio Little Bighorn, no atual estado de Montana, repousava o maior acampamento indígena já visto naquelas bandas.
+[...]
+Só que o general foi cercado.
+[...]
+Custer também foi assassinado. Essa batalha, entretanto, estava longe de ser decisiva. E os sioux estavam bem perto de seu fim como povo. "Essa rebelião indígena tem relação direta com a colonização do Oeste. Até por volta de 1840, os sioux, líderes da revolta, desfrutavam de uma boa convivência com os homens brancos", diz o professor Michael Tate, especialista em nativos americanos, da Universidade de Nebraska, no Estados Unidos.
+ONÇA, Fabiano. SIOUX: VÍTIMAS DO MAIOR GENOCÍDIO DO SÉCULO 19. Disponível em:&lt;https://aventurasnahistoria.uol.com.br/noticias/reportagem/sioux-vitimas-genocidio.phtml&gt;. Acesso em: 13 mar. 2020.
+Os fatos mencionados integram o processo de ocupação do território estadunidense conhecido como:</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>Colonização francesa.</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>Guerra de secessão.</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>Marcha para o Oeste.</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>Destino manifesto.</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>Guerra de independência.</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>Na segunda metade do século XIX, iniciou-se um processo de expansão da costa leste em direção ao oeste dos Estados Unidos, num processo que ficou conhecido como marcha para o oeste, várias ações integraram tal processo e até mesmo uma doutrina religiosa (Destino manifesto).</t>
+        </is>
+      </c>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J570" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K570" t="inlineStr"/>
+      <c r="L570" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>Leia o texto a seguir.
+A Corrente do Golfo nunca esteve tão fraca. Segundo pesquisas recentes, a diminuição do volume de água é o menor dos últimos 1.600 anos. Cientistas alertam para a necessidade de reverter a situação para evitar consequências no clima do planeta. As informações foram publicadas pelo jornal The Guardian.
+A corrente do Golfo estaria sendo prejudicada pelo Aquecimento Global. O aumento da temperatura derrete o gelo do Ártico e injeta água doce e fria no Atlântico Norte e isso estaria alterando a circulação da corrente pela diferença de densidade.
+A corrente do Golfo faz parte do sistema chamado Circulação Meridional do Atlântico, um gigantesco fluxo de água no Oceano Atlântico e com impacto no clima. A água quente de áreas tropicais vai em direção ao hemisfério norte, esfria no polo e retorna em direção ao hemisfério sul. Desde 1950, já foi registrado uma redução de 15 % da intensidade desse fluxo.
+Disponível em:&lt; https://noticias.r7.com/tecnologia-e-ciencia/corrente-do-golfo-mais-fraca-compromete-clima-em-todo-planeta18042018&gt;. Acesso em: 17 mar. 2020.
+A corrente do Golfo influencia o clima no EUA na</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>Porção oeste.</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>Porção leste.</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>Porção sul.</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>Porção norte.</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>Porção oeste e sul.</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>A Corrente do Golfo é uma corrente quente que influencia o clima europeu, deixando-o com invernos menos rigorosos e também o clima norte-americano, no estado da Flórida, deixando-o mais úmido e quente.</t>
+        </is>
+      </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J571" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K571" t="inlineStr"/>
+      <c r="L571" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>Leia o texto a seguir.
+A Revolução Industrial iniciada na Inglaterra, em meados do século XVIII, com a transição da manufatura para a indústria mecânica, gerando o aumento da produção e a ascensão de novas tecnologias, alterou o modo de vida no planeta.
+POTT, C. M. &amp; ESTRELA, C. C. Histórico ambiental: desastres ambientais e o despertar de um novo pensamento. Disponível em: &lt; http://www.scielo.br/scielo.php?script=sci_arttext&amp;pid=S0103-40142017000100271&gt;. Acesso em: 15 jan. 2020.
+Além das tecnologias ligadas à produção, está entre as consequências do processo conhecido como Revolução Industrial, a(o)</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>invenção do relógio.</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>criação de leis de proteção ao trabalhador.</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>devastação ambiental e a emissão de gases.</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>regulamentação da mão de obra feminina e infantil.</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>expansão dos direitos políticos aos mais pobres.</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>Entre as consequências da Revolução Industrial, está o impacto ambiental causado pelas máquinas, alimentadas por carvão, e que demandavam a exploração de bosques e florestas, além da emissão de gases e fuligem por conta do uso de combustíveis.</t>
+        </is>
+      </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J572" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K572" t="inlineStr"/>
+      <c r="L572" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>Leia o texto a seguir.
+[...] é a força de trabalho, no seu uso durante a jornada de trabalho pré-determinada, que adianta ao capitalista, na forma de mais-valia, os recursos que colocam a produção em funcionamento. Isso quer dizer que o trabalhador só recebe salários ao fim da jornada de trabalho [...].
+GOMES, Fábio Guedes. Mobilidade do trabalho e controle social: Trabalho e organizações na era neoliberal. Revista de Sociologia e Política v. 17, n. 32. Curitiba: p. 45, 2009. Disponível em: &lt;https://revistas.ufpr.br/rsp/article/view/28213/18727&gt;. Acesso em: 09 jan. 2020.
+O conceito de mais-valia, citado no trecho, designa a(o)</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>acúmulo de capital do burguês.</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>acúmulo de meios de produção pelo burguês.</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>alienação do operário em relação ao salário recebido.</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>tática de aumento do lucro mediante o pagamento de baixas remunerações.</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>diferença entre valor gerado pelo trabalho e pagamento da mão-de-obra.</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>Ao pagarem salários mais baixos para seus empregados, os patrões conseguiam aumentar seus lucros. Sendo assim, a mais valia designa a diferença entre o valor produzido pelo trabalho e o pagamento feito pelo patrão aos funcionários.</t>
+        </is>
+      </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J573" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K573" t="inlineStr"/>
+      <c r="L573" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>Leia o texto a seguir.
+“Os operários não se contentam com dirigir os seus ataques contra as relações burguesas de produção, e dirigem-se contra os próprios instrumentos de produção: destroem as mercadorias estrangeiras que lhes fazem concorrência, quebram as máquinas, incendeiam as fábricas, tentam reconquistar pela força a posição perdida do artesão da Idade Média”.
+COGGIOLA, Osvaldo. O início das organizações dos trabalhadores. Revista Aurora, n. 6. Marília: UNESP, p. 17, 2010. Disponível em: &lt; http://www2.marilia.unesp.br/revistas/index.php/aurora/article/view/1227/1094&gt;. Acesso em: 16 jan. 2020. (Adaptado).
+Os operários descritos pelo autor estão relacionados ao movimento chamado</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>sindical.</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>ludismo.</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>cartismo.</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>revolucionário.</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>resistência operária.</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>O movimento chamado ludismo era caracterizado por ações de trabalhadores que quebravam máquinas, pois as consideravam culpadas pela substituição da mão de obra humana.</t>
+        </is>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J574" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K574" t="inlineStr"/>
+      <c r="L574" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>Leia o texto a seguir.
+A Revolução Industrial vai além da ideia de grande desenvolvimento dos mecanismos tecnológicos aplicados à produção, na medida em que: consolidou o capitalismo; aumentou de forma rapidíssima a produtividade do trabalho; originou novos comportamentos sociais, novas formas de acumulação de capital, novos modelos políticos e uma nova visão do mundo; e talvez o mais importante, contribuiu de maneira decisiva para dividir a imensa maioria das sociedades humanas em duas classes sociais opostas e antagônicas [...].
+CAVALCANTE, Zedequias Vieira; SILVA, Mauro Luis Siqueira da. A Importância da Revolução Industrial no Mundo da Tecnologia. In: Anais Eletrônico VII EPCC – Encontro Internacional de Produção Científica Cesumar, p.4. Disponível em: &lt; https://www.unicesumar.edu.br/epcc-2011/wp-content/uploads/sites/86/2016/07/zedequias_vieira_cavalcante2.pdf&gt;. Acesso em: 16 jan. 2020.
+As “duas classes sociais opostas e antagônicas” a qual o texto se refere correspondem a quais segmentos da sociedade?</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>Liberais e socialistas.</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>Burguesia e operariado.</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>Classe média e aristocracia.</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>Republicanos e monarquistas.</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>Progressistas e conservadores.</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>Com a Revolução Industrial, os modos de produção e consumo foram alterados drasticamente, acarretando uma nova organização social nas relações de trabalho. Tal processo desencadeou na criação de duas classes sociais elementares para tal organização: os exploradores, representados na burguesia, e os explorados, com o operariado.</t>
+        </is>
+      </c>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J575" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K575" t="inlineStr"/>
+      <c r="L575" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>Leia o texto a seguir.
+A Europa da segunda metade do século XVIII foi marcada por profundas mudanças econômicas e sociais. Ideais liberais na França e transformações técnicas e econômicas na Grã-Bretanha deram a “sensação” de ruptura com o passado. A ideia do novo, do progresso, se disseminava pela Europa, que buscava pôr em prática novas invenções que se adequassem ao ritmo do cotidiano alucinante imposto pela nova ordem do trabalho. O tempo tornou-se ainda mais valioso para aqueles que almejavam ganhar dinheiro, de modo que cada minuto deveria ser minuciosamente aproveitado. Nas fábricas, os trabalhadores foram obrigados a seguir o ritmo da máquina a vapor, a qual forneceu um grande impulso ao setor têxtil.
+OLIVEIRA, E. M.. Transformações no Mundo do Trabalho: Da Revolução Industrial aos nossos dias. Caminhos da Geografia (UFU. Online), Uberlândia., v. 11, 2004, p.84-85. (Adaptado).
+A partir do fragmento acima, nota-se como a Revolução Industrial impactou a vida do trabalhador inglês,</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>melhorando o bem-estar do operariado, uma vez que mais riqueza passava a ser gerada e distribuída.</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>alterando o ritmo de trabalho e, por consequência, as relações sociais do operariado que então se formava.</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>levando aos operários ideias revolucionárias advindas dos ideais liberais, o que acarretou diversas revoltas sindicais.</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>mantendo os hábitos e costumes do proletariado, visto que os antigos trabalhadores rurais não conseguiam se adaptar ao ritmo de trabalho fabril.</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>diminuindo a carga de trabalho dos operários, tendo em vista que o progresso técnico visava também a melhoria das condições de vida dos trabalhadores.</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>O texto-base descreve algumas das mudanças decorrentes da Revolução Industrial com a chegada de um novo “ritmo do cotidiano alucinante imposto pela nova ordem do trabalho”, fazendo com que os trabalhadores fossem “obrigados a seguir o ritmo da máquina a vapor”. A partir disso, é possível notar como o ritmo do trabalho industrial impactou a vida do operário inglês, mudando não somente sua forma de trabalhar, mas também de se relacionar.</t>
+        </is>
+      </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J576" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K576" t="inlineStr"/>
+      <c r="L576" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>A imagem retrata uma cidade industrial típica do século XIX, com uma paisagem marcada pela presença de numerosas chaminés de fábricas. Este cenário é um reflexo das profundas transformações econômicas e sociais ocorridas durante a Revolução Industrial.
+Cidade de Manchester, 1852. Aquarela de William Wyld. Paisagem dominada por chaminés. Royal Collection Trust, Londres, Inglaterra.
+Disponível em: https://acervocmsp.educacao.sp.gov.br/92756/494622.pdf. Acesso em: 17 out. 2024.
+Com base na imagem e no contexto histórico da Revolução Industrial, como esse período contribuiu para o crescimento urbano?</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>Aumentando a produção agrícola e migração para áreas rurais.</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>Concentrando fábricas em áreas urbanas e com êxodo rural.</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>Desenvolvendo novas tecnologias de transporte marítimo.</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>Reduzindo a população urbana devido à mecanização.</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>Estagnando a economia com o declínio das cidades.</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>A Revolução Industrial levou à criação de grandes fábricas nas áreas urbanas, atraindo trabalhadores rurais em busca de emprego, o que resultou no crescimento das cidades.</t>
+        </is>
+      </c>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J577" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>8a_ph02_his_06.png</t>
+        </is>
+      </c>
+      <c r="L577" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>Leia o texto a seguir.
+A Revolução Industrial Britânica (1760-1840) testemunhou um grande número de inovações técnicas, como as máquinas a vapor, que resultaram em novas práticas de trabalho, que por sua vez trouxeram muitas mudanças sociais. Mais mulheres e crianças trabalhavam do que antes; pela primeira vez, os habitantes de vilas e cidades superaram os do campo; as pessoas se casavam mais jovens e tinham mais filhos; e a dieta da população melhorou. A mão de obra tornou-se muito menos qualificada do que antes e as novas instalações fabris se transformaram em locais insalubres e perigosos. As cidades sofriam com a poluição, a falta de saneamento e a criminalidade.  
+As Mudanças Sociais na Revolução Industrial Britânica. Disponível em: https://www.worldhistory.org/trans/pt/2-2229/as-mudancas-sociais-na-revolucao-industrial-britan/#google_vignette. Acesso em: 25 out. 2024.
+Como a Revolução Industrial ampliou a divisão entre a burguesia e o proletariado?</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>Criando uma classe de proprietários de fábricas ricos em oposição à aristocracia decadente.</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>Intensificando a urbanização devido ao uso das terras dos camponeses para a produção de lã.</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>Aumentando a produção e a eficiência nas fábricas sem distribuir os lucros de forma equitativa.</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>Proporcionando oportunidades de emprego estável com remuneração elevada para mais pessoas.</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>Introduzindo novas tecnologias que aumentaram a produtividade e ofereceram mercadorias baratas a todos.</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>Revolução Industrial acentuou a divisão entre a burguesia e o proletariado pois a burguesia, proprietária dos meios de produção, detinha fábricas altamente produtivas e eficientes, mas que dependiam dos trabalhadores para funcionarem. Ao não distribuir as riquezas produzidas, as contradições entre burguesia e proletariado se intensificaram.</t>
+        </is>
+      </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J578" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K578" t="inlineStr"/>
+      <c r="L578" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>Leia o texto a seguir.
+[...] foi um dos desenvolvimentos mais significativos da Revolução Industrial (1760-1840) na Grã-Bretanha. Empregada inicialmente em bombas de drenagem na década de 1690, uma série de inventores aperfeiçoou seus mecanismos, criando equipamentos que se tornaram uma alternativa eficiente e poderosa à energia dos músculos, da água e do vento, com real viabilidade econômica. 
+Disponível em: https://www.worldhistory.org/trans/pt/2-2166/. Acesso em 25 out. 2024.
+Qual invenção foi crucial para o desenvolvimento da Revolução Industrial?</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>Telefone</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>Telégrafo</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>Computador</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>Máquina a vapor</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>Motor de combustão interna</t>
+        </is>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t>A máquina a vapor foi crucial para o desenvolvimento da Revolução Industrial, sendo amplamente utilizada nas fábricas e nos transportes.</t>
+        </is>
+      </c>
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J579" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K579" t="inlineStr"/>
+      <c r="L579" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>Leia o texto a seguir.
+[...] este é reconhecido com a elaboração da Carta do Povo, que exigia o direito de votar e ser votado. Esse movimento direcionou a luta pelo direito ao sufrágio universal, despertando no proletariado o desejo de acabar com a sua impotência política.
+A organização política da classe operária do século XIX. Disponível em: http://www.ubimuseum.ubi.pt/n02/docs/ubimuseum02/ubimuseum02.fernando-araujo-reivan-souza.pdf. Acesso em: 25 out. 2024.
+Qual foi o importante movimento de trabalhadores trabalhado no texto que surgiu com o desenvolvimento da Revolução Industrial?</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>Cartismo.</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>Sindicalismo.</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>Ludismo.</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>Socialismo.</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>Anarquismo.</t>
+        </is>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>O movimento cartista baseava-se na Carta do Povo, exigindo reformas econômicas e políticas, como a redução da jornada de trabalho e o sufrágio universal, em defesa dos trabalhadores.</t>
+        </is>
+      </c>
+      <c r="I580" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J580" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K580" t="inlineStr"/>
+      <c r="L580" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>Leia o texto a seguir.
+Fazer bicos para sustentar a família ou complementar a renda não é novidade. Mas a forma como esses bicos ocorrem hoje em dia se tornou tão mediada pela tecnologia que ganhou um termo próprio em inglês: gig economy. A gig economy se refere aos tipos de trabalho em que a pessoa faz tarefas sob demanda, geralmente por meio de uma plataforma, como Uber e iFood. Por isso, ela é traduzida por pesquisadores como “economia de bicos” e “economia sob demanda”. E está chegando a cada vez mais profissões no Brasil e no mundo, muito além de entregadores e motoristas.
+ 'Gig economy': o que é o trabalho que muda cada vez mais profissões no Brasil. Disponível em: https://www.otempo.com.br/economia/gig-economy-o-que-e-o-trabalho-que-muda-cada-vez-mais-profissoes-no-brasil-1.2881086. Acesso em: 25 out 2024.
+Uma das principais características da gig economy é a contratação de trabalhadores</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>independentes para tarefas específicas.</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>permanentes para tarefas específicas.</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>independentes para tarefas contínuas.</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>permanentes para tarefas contínuas.</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>temporários para tarefas contínuas.</t>
+        </is>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H581" t="inlineStr">
+        <is>
+          <t>A gig economy é caracterizada pela contratação de trabalhadores independentes para tarefas específicas, em vez de empregos permanentes e estáveis.</t>
+        </is>
+      </c>
+      <c r="I581" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J581" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K581" t="inlineStr"/>
+      <c r="L581" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>Vários bairros de São Paulo enfrentam apagão após forte chuva
+Toda a cidade está em estado de atenção para alagamentos
+Vários bairros de São Paulo enfrentam um apagão por causa da forte chuva que atingiu a capital paulista no início da noite de hoje.
+Toda a cidade está em estado de atenção para alagamentos. Segundo o Centro de Gerenciamento de Emergências da capital paulista, pelos menos dois bairros estão com alerta para iminência de transbordamento.
+CBN. Disponível em: https://cbn.globo.com/sao-paulo/noticia/2024/10/11/varios-bairros-de-sao-paulo-enfrentam-apagao-apos-forte-chuva.ghtml. Acesso em: 16 out. 2024.
+Assinale a alternativa que identifica corretamente a preposição presente no trecho destacado e seu respectivo valor semântico:</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>"da", indicando posse.</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>"da", indicando tempo.</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>"por", indicando causa.</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>"por", indicando finalidade.</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>"da", indicando companhia.</t>
+        </is>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H582" t="inlineStr">
+        <is>
+          <t>A preposição "por" na expressão "por causa da" está corretamente indicando a causa do apagão, que é a forte chuva.</t>
+        </is>
+      </c>
+      <c r="I582" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J582" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K582" t="inlineStr"/>
+      <c r="L582" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>Vários bairros de São Paulo enfrentam apagão após forte chuva
+Toda a cidade está em estado de atenção para alagamentos
+Vários bairros de São Paulo enfrentam um apagão por causa da forte chuva que atingiu a capital paulista no início da noite de hoje.
+Toda a cidade está em estado de atenção para alagamentos. Segundo o Centro de Gerenciamento de Emergências da capital paulista, pelos menos dois bairros estão com alerta para iminência de transbordamento.
+CBN. Disponível em: https://cbn.globo.com/sao-paulo/noticia/2024/10/11/varios-bairros-de-sao-paulo-enfrentam-apagao-apos-forte-chuva.ghtml. Acesso em: 16 out. 2024.
+O valor semântico do advérbio destacado indica</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>modo.</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>lugar.</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>tempo.</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>afirmação.</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>intensidade.</t>
+        </is>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H583" t="inlineStr">
+        <is>
+          <t>O advérbio hoje no trecho "início da noite de hoje" indica o tempo em que a forte chuva ocorreu, especificando que foi no mesmo dia em que o texto foi escrito.</t>
+        </is>
+      </c>
+      <c r="I583" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J583" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K583" t="inlineStr"/>
+      <c r="L583" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>Montanhas no fundo do mar?
+A maior parte do mar profundo é plana e fica a, aproximadamente, 6 mil metros de profundidade, e essas regiões se estendem por milhões de quilômetros quadrados. Porém, nos locais onde ocorrem os encontros das placas tectônicas – grandes placas de rocha que se encaixam recobrindo toda a superfície da Terra – são formadas fendas enormes, que podem descer até 11 mil metros de profundidade.
+Disponível em: https://www.jornaljoca.com.br/colecao-tarsila-do-amaral-a-pintora-do-brasil-edicao-impressa-222/ Acesso em: 23 out. 2024.  
+A conjunção "porém" é substituída na oração sem perda semântica em:</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>"E, nos locais onde ocorrem os encontros das placas tectônicas"</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>"Porque, nos locais onde ocorrem os encontros das placas tectônicas"</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>"Embora, nos locais onde ocorrem os encontros das placas tectônicas"</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>"Portanto, nos locais onde ocorrem os encontros das placas tectônicas"</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>"Entretanto, nos locais onde ocorrem os encontros das placas tectônicas"</t>
+        </is>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H584" t="inlineStr">
+        <is>
+          <t>A conjunção "entretanto" é adversativa, assim como "porém". Ambas são usadas para introduzir uma ideia que contrasta com a anterior. No contexto da frase original, "porém" está sendo usado para mostrar um contraste em relação à informação sobre a maior parte do mar profundo ser plana. Substituir "porém" por "entretanto" mantém o mesmo valor semântico e a estrutura da frase, preservando o sentido original do texto.</t>
+        </is>
+      </c>
+      <c r="I584" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J584" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K584" t="inlineStr"/>
+      <c r="L584" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>Leia este trecho de um artigo de opinião.
+Saúde mental nas escolas deve ser prioridade
+O tema da saúde mental no Brasil ganhou força no debate público nos últimos anos. Segundo o Observatório da Atenção Primária em Saúde, durante a pandemia de Covid-19 os casos de depressão aumentaram 41%. Quando o assunto é violência nas escolas, a Secretaria da Educação do Estado de São Paulo registrou 4.021 agressões físicas só nos dois primeiros meses do ano letivo de 2022— 48,5% a mais que no mesmo período de 2019, antes da crise sanitária.
+Mais do que delinear o cenário e diagnosticar os problemas, é preciso avançar em soluções propositivas para a saúde mental das(os) estudantes, seus responsáveis e educadoras(es), de forma estrutural. [..] A adolescência é uma fase propícia para ações de prevenção, cujos efeitos podem influenciar tanto o presente quanto o futuro.
+FREITAS, Rebeca; QUARTIERO, Maria Fernanda Resende; ALTENFELDER, Anna Helena. Saúde mental nas escolas deve ser prioridade. O Globo, 2 Jul 2022. Disponível em: https://oglobo.globo.com/opiniao/artigos/coluna/2022/07/saude-mental-nas-escolas-deve-ser-prioridade.ghtml. Acesso em: 16 out. 2024. (Adaptado). 
+No texto, os verbos em destaque estão no</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>pretérito perfeito e futuro do indicativo.</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>pretérito perfeito e presente do indicativo.</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>pretérito imperfeito e futuro do subjuntivo.</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>pretérito imperfeito e presente do indicativo.</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>pretérito mais que perfeito e futuro do indicativo.</t>
+        </is>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H585" t="inlineStr">
+        <is>
+          <t>Os verbos "ganhou", "aumentaram" e "registrou" estão no pretérito perfeito do indicativo, que indica uma ação concluída no passado. Já os verbos "é" e "podem" estão no presente do indicativo, que indica uma ação que ocorre no momento da fala.</t>
+        </is>
+      </c>
+      <c r="I585" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J585" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K585" t="inlineStr"/>
+      <c r="L585" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>As conjunções são palavras essenciais para a coesão e a fluidez de um texto. Elas podem ser classificadas em coordenativas e subordinativas. Exemplos de conjunções coordenativas incluem “e”, “mas” e “ou”, enquanto exemplos de conjunções subordinativas incluem “porque”, “quando” e “se”.
+Qual é a principal diferença entre conjunções coordenativas e subordinativas?</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>Conjunções coordenativas são usadas apenas no início de frases, enquanto conjunções subordinativas são usadas no meio das frases.</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>Conjunções coordenativas ligam orações independentes, enquanto conjunções subordinativas ligam orações dependentes.</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>Conjunções coordenativas sempre indicam causa, enquanto conjunções subordinativas sempre indicam consequência.</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>Conjunções coordenativas indicam tempo, enquanto conjunções subordinativas indicam lugar.</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>Conjunções coordenativas são invariáveis, enquanto conjunções subordinativas são variáveis.</t>
+        </is>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H586" t="inlineStr">
+        <is>
+          <t>Conjunções coordenativas são usadas para ligar orações ou termos que têm a mesma função sintática e são independentes entre si. Por exemplo, em "Eu gosto de maçãs e ele gosta de laranjas", as orações são independentes. Por outro lado, conjunções subordinativas ligam uma oração principal a uma oração subordinada, que depende da principal para ter sentido completo. Por exemplo, em "Eu saí porque estava chovendo", a oração "porque estava chovendo" depende da principal para fazer sentido.</t>
+        </is>
+      </c>
+      <c r="I586" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J586" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K586" t="inlineStr"/>
+      <c r="L586" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>Leia o trecho abaixo para responder à questão.
+Minha terra tem palmeiras,
+Onde canta o Sabiá;
+As aves, que aqui gorjeiam,
+Não gorjeiam como lá.
+[...]
+DIAS, Gonçalves. Disponível em: http://www.dominiopublico.gov.br/download/texto/bn000100.pdf . Acesso em 06 jan. 2020.
+Do ponto de vista das classes gramaticais, as palavras em destaque no poema são classificadas como</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>pronomes espaciais.</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>locuções adjetivas.</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>advérbios de lugar.</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>locuções adverbiais.</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>advérbios de modo.</t>
+        </is>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H587" t="inlineStr">
+        <is>
+          <t>As palavras "onde", "aqui" e "lá" são advérbios de lugar. Advérbios são palavras que modificam o verbo, o adjetivo ou outro advérbio, indicando circunstâncias como tempo, modo, lugar, intensidade, entre outras. No caso específico do poema, "onde" indica o local em que algo acontece, "aqui" refere-se a um lugar próximo ao falante, e "lá" refere-se a um lugar distante do falante. Portanto, todas essas palavras estão relacionadas à indicação de lugares, caracterizando-se assim como advérbios de lugar.</t>
+        </is>
+      </c>
+      <c r="I587" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J587" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K587" t="inlineStr"/>
+      <c r="L587" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>Leia o trecho a seguir.
+Minha terra tem palmeiras,
+Onde canta o Sabiá;
+As aves, que aqui gorjeiam,
+Não gorjeiam como lá.
+[...]
+DIAS, Gonçalves. Disponível em: http://www.dominiopublico.gov.br/download/texto/bn000100.pdf . Acesso em 06 jan. 2020.
+Nos versos destacados, a expressão “como” é um(a)</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>advérbio que estabelece uma relação de lugar.</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>advérbio que estabelece uma relação de modo.</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>conjunção que estabelece uma relação causal.</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>conjunção que estabelece uma relação comparativa.</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>conjunção que estabelece uma relação de adição.</t>
+        </is>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H588" t="inlineStr">
+        <is>
+          <t>No poema, a palavra "como" desempenha o papel de conjunção estabelecendo uma relação comparativa. Nesse contexto, "como" está sendo utilizada para comparar o modo de gorjeio das aves em dois lugares diferentes: o lugar onde o eu lírico está (aqui) e o lugar ao qual ele se com saudade (lá).</t>
+        </is>
+      </c>
+      <c r="I588" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J588" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K588" t="inlineStr"/>
+      <c r="L588" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>Em relação à tirinha, assinale a alternativa que aponta para, respectivamente, um advérbio, um verbo e um adjetivo:</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>“outros”, “humanidade” e “tão”.</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>“lá”, “acham” e “difícil”.</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>“onde”, “pra” e “claro”.</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>“minha”, “que” e “é”.</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>“humanidade”, “estou” e “a”.</t>
+        </is>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H589" t="inlineStr">
+        <is>
+          <t>O termo "lá" é um advérbio de lugar, pois indica a localização de algo ou alguém em um ponto distante do falante. A palavra "acham" é um verbo, pois expressa uma ação realizada pelos sujeitos da frase. Já "difícil" é um adjetivo, pois qualifica um substantivo ao descrever a característica de algo que apresenta complexidade ou que não é fácil de ser realizado.</t>
+        </is>
+      </c>
+      <c r="I589" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J589" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>8a_ph02_por_08.png</t>
+        </is>
+      </c>
+      <c r="L589" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>Releia esta passagem do primeiro quadrinho:
+“Você só pode estacionar se me der 50 centavos.”.
+Os termos em destaque indicam que Calvin</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>fez uma proposta.</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>realizou uma persuasão.</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>impôs uma condição.</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>fez uma promoção.</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>fez uma exclusão.</t>
+        </is>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H590" t="inlineStr">
+        <is>
+          <t>No enunciado, os termos "só" e "se" indicam que Calvin está estabelecendo uma condição para que a ação de estacionar seja permitida. A palavra "só" limita a permissão, enquanto "se" introduz a condição necessária para que essa permissão seja concedida.</t>
+        </is>
+      </c>
+      <c r="I590" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J590" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>8a_ph02_por_09.png</t>
+        </is>
+      </c>
+      <c r="L590" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>Leia o texto a seguir.
+A Educação Pela Pedra
+Uma educação pela pedra: por lições;
+para aprender da pedra, freqüentá-la;
+captar sua voz inenfática, impessoal
+(pela de dicção ela começa as aulas).
+A lição de moral, sua resistência fria
+ao que flui e a fluir, a ser maleada;
+a de poética, sua carnadura concreta;
+a de economia, seu adensar-se compacta:
+lições da pedra (de fora para dentro,
+cartilha muda), para quem soletrá-la.
+*
+Outra educação pela pedra: no Sertão
+(de dentro para fora, e pré-didática).
+No Sertão a pedra não sabe lecionar,
+e se lecionasse, não ensinaria nada;
+lá não se aprende a pedra: lá a pedra,
+uma pedra de nascença, entranha a alma.
+NETO, João Cabral de. A Educação Pela Pedra. Disponível em: http://www.academia.org.br/academicos/joao-cabral-de-melo-neto/textos-escolhidos. Acesso em: 15 jan. 2020.
+Observe os termos destacados no poema. Morfologicamente eles são classificados como</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>pronomes.</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>advérbios.</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>interjeições.</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>preposições.</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>adjetivos.</t>
+        </is>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H591" t="inlineStr">
+        <is>
+          <t>Morfologicamente os termos destacados são classificados como preposições, pois relacionam e conectam substantivos.</t>
+        </is>
+      </c>
+      <c r="I591" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J591" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K591" t="inlineStr"/>
+      <c r="L591" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>Manuela está jogando 2048, um jogo de quebra-cabeça onde o objetivo é combinar blocos com potências de 2 para formar blocos de maior valor. No tabuleiro, os blocos são sempre números que são potências de 2, como 2, 4, 8, 16 e assim por diante, conforme mostra a imagem.
+Disponível em: https://www.matematicagenial.com/2017/06/5-jogos-para-desenvolver-o-raciocinio-matematico.html.
+Para vencer, Manuela precisa combinar os blocos para formar o número 2048. Durante uma partida, ela fez uma série de movimentos e terminou com os blocos as potencias: 21 + 23+ 25 + 26 + 29. 
+Qual é a soma de todos os blocos do tabuleiro de Manuela em termos de potência de 2?</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>1024</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H592" t="inlineStr">
+        <is>
+          <t>A soma da potência 21 + 23+ 25 + 26 + 29 dos blocos é obtida por meio de:
+(2 × 1) + (2 × 2 × 2) + (2 × 2 × 2 × 2 × 2) + (2 × 2 × 2 × 2 × 2 × 2) + (2 × 2 × 2 × 2 × 2 × 2 × 2 × 2 × 2) = 618.</t>
+        </is>
+      </c>
+      <c r="I592" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J592" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>8a_ph02_mat_01.png</t>
+        </is>
+      </c>
+      <c r="L592" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>Um engenheiro está analisando a distância mínima entre a Terra e Júpiter para calcular a eficiência de painéis solares em uma estação espacial. A distância aproximada entre a Terra e Júpiter é de 591.000.000 km. Para simplificar os cálculos, ele precisa converter essa distância em notação científica.
+Qual é a forma correta dessa distância em notação científica?</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>59,1×108 km</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>59,1×105 km</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>59,1×106 km</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>5,91×108km</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>5,91×105 km</t>
+        </is>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H593" t="inlineStr">
+        <is>
+          <t>Para converter 591.000.000 em notação científica, desloca-se a vírgula 8 casas para a esquerda, mantendo como coeficiente apenas um algarismo, o que resulta em 5,91×108.</t>
+        </is>
+      </c>
+      <c r="I593" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J593" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K593" t="inlineStr"/>
+      <c r="L593" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>Um data center possui n racks de servidores, e cada rack contém n³ servidores. Sabendo que o total de servidores no data center é de 512, um engenheiro precisa determinar quantos racks de servidores o data center possui para planejar a expansão.
+Qual a quantidade de racks de servidores que possui o data center?</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H594" t="inlineStr">
+        <is>
+          <t>Se n é o número de racks, então n3  é o número de servidores por rack. O total de servidores é dado por n × n3. Portanto, n3 = 512. Calculando a ,3√ 512 temos que 
+Portanto, 512 = 23 · 23 · 23. Usando as propriedades da potenciação para escrever o radicando:</t>
+        </is>
+      </c>
+      <c r="I594" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J594" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K594" t="inlineStr"/>
+      <c r="L594" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>Em um estudo sobre o consumo de energia elétrica em uma cidade, os engenheiros precisam calcular a demanda total de energia de diferentes setores. A demanda de energia é representada pelas expressões 2,3 · 105 kWh para o setor residencial, 1,5 · 106 kWh para o setor comercial,  3,2 · 107 kWh para o setor industrial, e subtraída pela energia gerada por fontes renováveis, representada por  5 · 108 kWh. Eles precisam simplificar essa expressão para determinar a demanda total de energia.
+Qual é o resultado da expressão  ?</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>– 4,51 · 108</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>– 4,53 · 108</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>– 4,64 · 108</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>– 4,66  · 108</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>– 4,93 · 108</t>
+        </is>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H595" t="inlineStr">
+        <is>
+          <t>Somando e subtraindo as intensidades: 2,3 · 105 + 1,5 · 106  + 3,2 · 107  – 5 · 108 = (0,0023 + 0,015 + 0,32 – 5) · 108= – 4,66 · 108.</t>
+        </is>
+      </c>
+      <c r="I595" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J595" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>8a_ph02_mat_04.png</t>
+        </is>
+      </c>
+      <c r="L595" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>Em um estudo sobre crescimento populacional, os cientistas estão analisando a expressão para modelar a taxa de crescimento de uma população. Eles precisam simplificar essa expressão em forma de radical para entender melhor os dados.
+Qual é a forma simplificada da expressão ?</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>[img:8a_ph02_mat_05_a.png]</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>[img:8a_ph02_mat_05_b.png]</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>[img:8a_ph02_mat_05_c.png]</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>[img:8a_ph02_mat_05_d.png]</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>[img:8a_ph02_mat_05_e.png]</t>
+        </is>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H596" t="inlineStr">
+        <is>
+          <t>A expressão   pode ser simplificada como  , que é a forma correta em radical.</t>
+        </is>
+      </c>
+      <c r="I596" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J596" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t>8a_ph02_mat_05.png</t>
+        </is>
+      </c>
+      <c r="L596" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>O tamanho de um átomo de hidrogênio é bem pequeno para os nossos parâmetros do dia a dia. Se aproximássemos o átomo ao formato de uma esfera, seu raio seria igual a 120 milionésimos de milionésimos de metro. A cada vez que falamos milionésimos, devemos dividir o número pela potência de 10 correspondente a milhão.
+Qual é o valor desse raio, em metros, escrito usando notação científica?</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>1,2 . 10-4</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>1,2 . 10-6</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>1,2 . 10-8</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>1,2 . 10-9</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>1,2 . 10-10</t>
+        </is>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H597" t="inlineStr">
+        <is>
+          <t>Primeiro, devemos calcular o que seria o milionésimo de milionésimo de metro: 1 metro deve ser dividido duas vezes por 106, potência correspondente a um milhão. Mas dividir por uma potência é o mesmo que multiplicar por uma potência de mesma base, mas o expoente deverá ter o sinal contrário. Logo:
+(1 ÷ 106) ÷ 106 = 1 ∙ 10-6 ∙ 10-6 = 1 ∙ 10-6+(-6) = 1 ∙ 10-12.
+A medida desejada é: 120 ∙ 10-12 m. Colocando 120 em notação científica, obtêm-se:
+120 ∙ 10-12 = (1,2 ∙ 102) ∙ 10-12 = 1,2 ∙102+(-12) = 1,2 ∙ 10-10 m.</t>
+        </is>
+      </c>
+      <c r="I597" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J597" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K597" t="inlineStr"/>
+      <c r="L597" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>Para determinar se uma raiz quadrada de um número natural é um número racional, devemos analisar o número que está dentro da raiz: o radicando. Observe os exemplos:
+, aqui o radicando é 4 e, como 4 é quadrado perfeito,  é racional.
+, aqui o radicando é 5 e, como 5 não é quadrado perfeito, não é racional.
+Dessa forma, considere os números  .</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>Ambos são irracionais.</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>é irracional e  é racional</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>é racional e  é irracional.</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>Ambos são racionais.</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>Ambos são naturais.</t>
+        </is>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H598" t="inlineStr">
+        <is>
+          <t>é racional pois 36 é quadrado perfeito
+ é irracional pois 63 não é quadrado perfeito.</t>
+        </is>
+      </c>
+      <c r="I598" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J598" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>8a_ph02_mat_07.png</t>
+        </is>
+      </c>
+      <c r="L598" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>O PIB (produto interno bruto) do Brasil no 4º trimestre de 2016 foi de 1 630,6 Bilhões de reais. Como esse número ficará quando reescrito usando notação científica?</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>1,6306 . 103</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>1,6306 . 106</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>1,6306 . 109</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>1,6306 . 1012</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>1,6306 . 1015</t>
+        </is>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H599" t="inlineStr">
+        <is>
+          <t>A classe de bilhão corresponde a 109. Dessa forma, o número pode ser reescrito como:
+1 630,6 ∙ 109.
+Agora, colocando no formato de notação científica, será obtido: (1,6306 ∙ 103) ∙109.
+Usando as propriedades de potências: 1,6306 ∙10(3+9) = 1,6306 ∙ 1012.</t>
+        </is>
+      </c>
+      <c r="I599" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J599" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K599" t="inlineStr"/>
+      <c r="L599" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>Considere as 3 afirmações a seguir:
+I. 24 = (-2)4
+II. -35 = (-3)5;
+III. 43 = (-4)3.
+Quais das afirmações são verdadeiras?</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>Apenas I.</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>I e II.</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>I e III.</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>II e III.</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>Apenas III.</t>
+        </is>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H600" t="inlineStr">
+        <is>
+          <t>I. 24 = 2 ∙ 2 ∙ 2 ∙ 2 = 16 e (-2)4 = (-2) ∙ (-2) ∙ (-2) ∙ (-2) = 16 (verdadeira);
+II. -35 = -3 ∙ 3 ∙ 3 ∙ 3 ∙ 3 = -243 e (-3)5 = (-3) ∙ (-3) ∙ (-3) ∙ (-3) ∙ (-3) = -243 (verdadeira);
+III. 43 = 4 ∙ 4 ∙ 4 = 64 e (-4)3 = (-4) ∙ (-4) ∙ (-4) = -64  (Falsa).</t>
+        </is>
+      </c>
+      <c r="I600" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J600" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K600" t="inlineStr"/>
+      <c r="L600" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>Leia um trecho sobre a notícia da primeira detecção de ondas gravitacionais:
+“... A colisão de buracos negros registrada pelo projeto foi detectada em 14 de setembro. Cada um dos dois objetos pesava cerca de 30 vezes a massa do Sol, e o fenômeno ocorreu a 1,3 bilhão de anos-luz.”
+Disponível em: http://g1.globo.com/ciencia-e-saude/noticia/2016/02/experimento-ve-ondas-gravitacionais-fenomeno-previsto-por-einstein.html. Acesso em: 10/01/2018.
+Ano-luz é uma medida de distância, usualmente utilizada em medidas astronômicas.
+Qual o valor dessa distância, em anos-luz, utilizando notação científica?</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>1,3 . 103</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>1,3 . 106</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>1,3 . 109</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>1,3 . 1012</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>1,3 . 1015</t>
+        </is>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H601" t="inlineStr">
+        <is>
+          <t>A classe de bilhão corresponde a 109. Dessa forma, o número pode ser reescrito como: 1,3 . 109.</t>
+        </is>
+      </c>
+      <c r="I601" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J601" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K601" t="inlineStr"/>
+      <c r="L601" t="inlineStr">
+        <is>
+          <t>8ano</t>
         </is>
       </c>
     </row>

--- a/questoes.xlsx
+++ b/questoes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L601"/>
+  <dimension ref="A1:L651"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29844,7 +29844,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K552" t="inlineStr"/>
       <c r="L552" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -29969,7 +29968,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K554" t="inlineStr"/>
       <c r="L554" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -30028,7 +30026,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K555" t="inlineStr"/>
       <c r="L555" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -30087,7 +30084,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K556" t="inlineStr"/>
       <c r="L556" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -30145,7 +30141,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K557" t="inlineStr"/>
       <c r="L557" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -30204,7 +30199,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K558" t="inlineStr"/>
       <c r="L558" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -30262,7 +30256,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K559" t="inlineStr"/>
       <c r="L559" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -30448,7 +30441,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K562" t="inlineStr"/>
       <c r="L562" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -30507,7 +30499,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K563" t="inlineStr"/>
       <c r="L563" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -30566,7 +30557,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K564" t="inlineStr"/>
       <c r="L564" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -30625,7 +30615,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K565" t="inlineStr"/>
       <c r="L565" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -30684,7 +30673,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K566" t="inlineStr"/>
       <c r="L566" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -30810,7 +30798,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K568" t="inlineStr"/>
       <c r="L568" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -30939,7 +30926,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K570" t="inlineStr"/>
       <c r="L570" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -31002,7 +30988,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K571" t="inlineStr"/>
       <c r="L571" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -31063,7 +31048,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K572" t="inlineStr"/>
       <c r="L572" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -31124,7 +31108,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K573" t="inlineStr"/>
       <c r="L573" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -31185,7 +31168,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K574" t="inlineStr"/>
       <c r="L574" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -31246,7 +31228,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K575" t="inlineStr"/>
       <c r="L575" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -31307,7 +31288,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K576" t="inlineStr"/>
       <c r="L576" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -31433,7 +31413,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K578" t="inlineStr"/>
       <c r="L578" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -31494,7 +31473,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K579" t="inlineStr"/>
       <c r="L579" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -31555,7 +31533,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K580" t="inlineStr"/>
       <c r="L580" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -31616,7 +31593,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K581" t="inlineStr"/>
       <c r="L581" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -31679,7 +31655,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K582" t="inlineStr"/>
       <c r="L582" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -31742,7 +31717,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K583" t="inlineStr"/>
       <c r="L583" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -31803,7 +31777,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K584" t="inlineStr"/>
       <c r="L584" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -31866,7 +31839,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K585" t="inlineStr"/>
       <c r="L585" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -31925,7 +31897,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K586" t="inlineStr"/>
       <c r="L586" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -31990,7 +31961,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K587" t="inlineStr"/>
       <c r="L587" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -32055,7 +32025,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K588" t="inlineStr"/>
       <c r="L588" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -32259,7 +32228,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K591" t="inlineStr"/>
       <c r="L591" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -32384,7 +32352,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K593" t="inlineStr"/>
       <c r="L593" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -32444,7 +32411,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K594" t="inlineStr"/>
       <c r="L594" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -32632,7 +32598,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K597" t="inlineStr"/>
       <c r="L597" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -32759,7 +32724,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K599" t="inlineStr"/>
       <c r="L599" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -32823,7 +32787,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K600" t="inlineStr"/>
       <c r="L600" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -32885,8 +32848,3106 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K601" t="inlineStr"/>
       <c r="L601" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>O clima da região Nordeste é semiárido, o que significa que o ano é dividido em estações chuvosas e estações de estiagem. A seca ocorre quando não chove nos meses em que deveria chover, no caso há expectativa de chuva entre janeiro e junho e ausência de precipitação esperada entre julho e dezembro.
+Disponível em: https://cienciahoje.periodicos.capes.gov.br/storage/acervo/ch/ch_308.pdf#page=43. Acesso em: 21 out. 2024. (Adaptado).
+Qual corrente oceânica tem influência direta no clima semiárido do sertão nordestino?</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>Corrente do Golfo.</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>Corrente das Falklands.</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>Corrente do Brasil.</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>Corrente de Humboldt.</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>Corrente de Benguela.</t>
+        </is>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H602" t="inlineStr">
+        <is>
+          <t>A Corrente do Brasil é uma corrente quente que flui ao longo da costa leste do Brasil e influencia diretamente o clima da região Nordeste, contribuindo para a variabilidade das chuvas.</t>
+        </is>
+      </c>
+      <c r="I602" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J602" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K602" t="inlineStr"/>
+      <c r="L602" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>O encontro das correntes marinhas do Brasil e das Malvinas em região adjacente, o fenômeno da ressurgência (em que a água do fundo oceânico, fria e rica em plâncton, sobe à superfície) e a influência da pluma do rio da Prata permitem o aparecimento de peixes e crustáceos de ambientes tropicais e de pinguins e baleias-francas, de clima subtropical.
+Disponível em: https://cienciahoje.periodicos.capes.gov.br/storage/acervo/ch/ch_313.pdf#page=37. Acesso em: 21 out. 2024. (Adaptado).
+Qual é a principal consequência do fenômeno da ressurgência na costa brasileira?</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>Diminui a temperatura da água, tornando-a imprópria para a maioria das espécies comerciais.</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>Aumenta a concentração de nutrientes, favorecendo a proliferação de espécies marinhas.</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>Reduz a salinidade da água, afetando negativamente a reprodução de peixes.</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>Provoca a migração de espécies tropicais para águas mais profundas.</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>Causa a formação de zonas mortas, onde a vida marinha é escassa.</t>
+        </is>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H603" t="inlineStr">
+        <is>
+          <t>A ressurgência traz água rica em nutrientes para a superfície, o que favorece a proliferação de plâncton e, consequentemente, de outras espécies marinhas.</t>
+        </is>
+      </c>
+      <c r="I603" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J603" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K603" t="inlineStr"/>
+      <c r="L603" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>Mudanças climáticas afetam diretamente a biodiversidade de uma região, já que algumas espécies são bastante sensíveis à variação de temperatura. Os corais recifais, por exemplo, não se adaptam a águas muito geladas.
+Disponível em: https://cienciahoje.periodicos.capes.gov.br/storage/acervo/ch/ch_283.pdf#page=63. Acesso em: 21 out. 2024. (Adaptado).
+Como a Corrente do Brasil pode impactar os recifes de corais na costa brasileira?</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>Diminuindo a temperatura da água e protegendo os corais do branqueamento.</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>Aumentando a temperatura da água e elevando o branqueamento dos corais.</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>Diminuindo a acidez da água e exacerbando o branqueamento dos corais.</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>Reduzindo a salinidade da água e favorecendo a recuperação dos corais.</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>Aumentando a acidez da água e protegendo os corais.</t>
+        </is>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H604" t="inlineStr">
+        <is>
+          <t>A Corrente do Brasil é uma corrente quente que pode aumentar a temperatura da água, contribuindo para o branqueamento dos corais.</t>
+        </is>
+      </c>
+      <c r="I604" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J604" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K604" t="inlineStr"/>
+      <c r="L604" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>Um sapo está dentro de uma panela sobre o fogo. A água aquece lentamente e o animal não percebe o aumento da temperatura até não se mais capaz de sair da panela e se livrar da morte. A história foi usada no 1º Encontro do Painel Intergovernamental de Mudanças do Clima (IPCC) na América Latina para ilustrar o comportamento da humanidade em relação às mudanças climáticas.
+Disponível em: https://cienciahoje.periodicos.capes.gov.br/storage/acervo/ch/ch_244.pdf#page=48. Acesso em: 21 out. 2024. (Adaptado).
+Segundo a analogia proposta no texto, qual é a consequência das mudanças climáticas para a biodiversidade?</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>Aumento da diversidade de espécies de águas frias.</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>Proliferação de espécies exóticas.</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>Destruição de habitats e redução da biodiversidade.</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>Expansão de espécies de águas profundas.</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>Aumento da resistência das espécies às mudanças ambientais.</t>
+        </is>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H605" t="inlineStr">
+        <is>
+          <t>As mudanças climáticas levam à destruição de habitats naturais, resultando em uma redução da biodiversidade.</t>
+        </is>
+      </c>
+      <c r="I605" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J605" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K605" t="inlineStr"/>
+      <c r="L605" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>Nas últimas décadas, a poluição da atmosfera aumentou bastante por conta da queima de combustíveis das indústrias e dos automóveis. A derrubada de árvores para fabricação de papel, móveis e outros materiais também é muito prejudicial ao meio ambiente. Fatores como esses contribuem para um processo de mudanças climáticas globais, ou seja, um conjunto de alterações em determinadas características do clima do planeta.
+Disponível em: https://cienciahoje.periodicos.capes.gov.br/storage/acervo/chc/chc_214.pdf#page=06. Acesso em: 21 out. 2024.
+Qual dos seguintes eventos climáticos extremos recentes no Brasil pode ser diretamente associado a essas mudanças climáticas?</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>Aumento da biodiversidade na Amazônia.</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>Redução das áreas de desertificação no Nordeste.</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>Intensificação das chuvas e enchentes no Sudeste.</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>Diminuição das temperaturas médias no Sul.</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>Estabilização dos níveis dos rios no Centro-Oeste.</t>
+        </is>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H606" t="inlineStr">
+        <is>
+          <t>As mudanças climáticas podem levar a eventos climáticos extremos, como chuvas intensas e enchentes.</t>
+        </is>
+      </c>
+      <c r="I606" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J606" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K606" t="inlineStr"/>
+      <c r="L606" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>João comentou com seu amigo, José, que o clima desse fim de semana seria de muito sol e calor.
+Em relação aos conceitos de clima e tempo, a análise de João para o fim de semana está:</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>correto, pois clima se relaciona com as condições atmosféricas momentâneas.</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>correto, pois clima se relaciona com as condições atmosféricas ao longo de anos.</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>incorreto, pois clima se relaciona com as condições atmosféricas ao longo de anos.</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>incorreto, pois clima se relaciona com as condições atmosféricas momentâneas.</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>correto, pois clima e tempo são sinônimos e não há diferenças.</t>
+        </is>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H607" t="inlineStr">
+        <is>
+          <t>João está se referindo ao tempo, o qual se refere às condições atmosféricas momentâneas. O termo clima faz referência às condições atmosféricas de um local ao longo de anos.</t>
+        </is>
+      </c>
+      <c r="I607" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J607" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K607" t="inlineStr"/>
+      <c r="L607" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>Uma mudança climática, por exemplo, afeta diretamente a biodiversidade de uma região, já que algumas espécies são bastante sensíveis à variação de temperatura. Os corais recifais, por exemplo, não se adaptam a águas muito geladas.
+Disponível em: https://cienciahoje.periodicos.capes.gov.br/storage/acervo/ch/ch_283.pdf#page=63. Acesso em: 06 dez 2024.
+Com base no texto que afirma que "algumas espécies são bastante sensíveis à variação de temperatura", analise as alternativas abaixo e escolha aquela que melhor exemplifica um impacto direto do aumento da temperatura na biodiversidade.</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>aumento da temperatura pode favorecer a proliferação de espécies invasoras.</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>redução da temperatura pode aumentar a produtividade agrícola.</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>aumento da temperatura pode reduzir a incidência de doenças em plantas.</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>redução da temperatura pode aumentar a diversidade de espécies aquáticas.</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>aumento da temperatura pode diminuir a taxa de evaporação dos corpos d'água.</t>
+        </is>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H608" t="inlineStr">
+        <is>
+          <t>O aumento da temperatura pode favorecer a proliferação de espécies invasoras. Com a intensificação do aquecimento global, muitas espécies invasoras encontram condições ideais para se proliferar, o que pode desestabilizar ecossistemas locais e afetar a biodiversidade.</t>
+        </is>
+      </c>
+      <c r="I608" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J608" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K608" t="inlineStr"/>
+      <c r="L608" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>Ferramenta prevê influência do clima sobre agricultura em 2018
+Lançado em agosto de 2016 pela Escola Superior de Agricultura Luiz de Queiroz (Esalq) da USP em Piracicaba, o Sistema TempoCampo finalizou o ano de 2017 com projeções climáticas para 2018.
+Criado no Departamento de Engenharia de Biossistemas da Esalq, o Sistema TempoCampo é resultado da intersecção de diversos projetos de pesquisa na área de modelagem agrícola e agrometeorologia. Com um banco de dados climáticos para todos os Estados brasileiros, o sistema oferece aos produtores a possibilidade de antever os efeitos do clima sobre determinadas culturas ao longo das safras. É possível saber, assim, se elas serão favorecidas ou prejudicadas por fatores meteorológicos.(...)
+Disponível em: &lt;https://jornal.usp.br/universidade/ferramenta-preve-influencia-do-clima-sobre-agricultura-em-2018/&gt;. Acesso em: 2 set. 2018.
+O texto aborda um assunto de grande importância para os produtores agrícolas que é</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>a melhor semente a ser plantada para conseguir germinar em qualquer tipo de clima.</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>a melhor época do ano para se plantar determinadas espécies de legumes e verduras.</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>o estudo da meteorologia para prever as possíveis mudanças climáticas para auxiliar em possíveis mudanças prejudiciais para a agricultura.</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>a quantidade de água que a plantação terá acesso naquele ano para decidir o melhor tipo de alimento a ser plantado naquele ano.</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>o estudo da meteorologia para prever as possíveis mudanças no tempo para alertar os trabalhadores rurais.</t>
+        </is>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H609" t="inlineStr">
+        <is>
+          <t>A reportagem traz uma novidade tecnológica que é uma ferramenta que pode prever mudanças climáticas. Isso auxilia os agricultores a preparar suas lavouras e minimizar os impactos e perdas.</t>
+        </is>
+      </c>
+      <c r="I609" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J609" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K609" t="inlineStr"/>
+      <c r="L609" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>Os recifes de corais são ecossistemas extremamente importantes para a biodiversidade marinha, sendo fonte de alimento e abrigo para uma variedade de espécies. No Brasil, esses recifes estão principalmente no litoral nordestino, e o Parque Nacional Marinho dos Abrolhos é um exemplo de área protegida dedicada à conservação desse ecossistema. No entanto, os recifes brasileiros têm enfrentado grandes desafios, como o branqueamento dos corais, causado pelo aumento das temperaturas dos oceanos devido às mudanças climáticas.
+Considerando a função dos recifes de corais nos ecossistemas marinhos, qual é o impacto ecológico mais provável do branqueamento de corais na biodiversidade?</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>O branqueamento dos corais estimula a colonização de novas espécies, aumentando a diversidade.</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>A perda das algas simbióticas enfraquece os corais, reduzindo o alimento e abrigo para várias espécies.</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>O branqueamento diminui a diversidade temporariamente, mas aumenta o crescimento de algas.</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>O branqueamento protege os corais contra predadores, ajudando na recuperação dos recifes.</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>A perda de pigmentação do coral não interfere na biodiversidade, pois afeta apenas a cor do recife.</t>
+        </is>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H610" t="inlineStr">
+        <is>
+          <t>Sem as algas simbióticas, os corais enfraquecem, perdendo a capacidade de suportar uma alta biodiversidade.</t>
+        </is>
+      </c>
+      <c r="I610" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J610" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K610" t="inlineStr"/>
+      <c r="L610" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>O Pantanal, a maior planície alagável do mundo, é um dos biomas com a maior biodiversidade do planeta. Ele passa por um ciclo anual de cheias e secas, o que cria um ambiente fértil e variado que sustenta muitas espécies. No entanto, as atividades humanas, como a agricultura, a pecuária e o desmatamento, estão causando degradação ambiental no Pantanal, ameaçando o equilíbrio ecológico e a diversidade de espécies.
+Qual das alternativas abaixo descreve melhor como o ciclo natural de cheias e secas do Pantanal beneficia a biodiversidade local?</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>O ciclo de cheias e secas aumenta a salinidade do solo, favorecendo espécies adaptadas ao sal.</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>As cheias anuais distribuem nutrientes no solo, criando habitats variados que sustentam muitas espécies.</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>O período de seca elimina as espécies menos adaptadas, fortalecendo a biodiversidade.</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>As secas constantes reduzem a vegetação, permitindo a sobrevivência de espécies aquáticas.</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>O ciclo de cheias e secas é responsável por criar um solo infértil, limitando o crescimento da vegetação.</t>
+        </is>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H611" t="inlineStr">
+        <is>
+          <t>O ciclo natural de cheias e secas do Pantanal é fundamental para a manutenção da sua biodiversidade. Durante as cheias, os rios transbordam e inundam grandes áreas, depositando sedimentos ricos em nutrientes no solo. Esses nutrientes são essenciais para o crescimento de diversas plantas, que por sua vez sustentam uma ampla variedade de animais. Além disso, as cheias criam diferentes tipos de habitats, como áreas alagadas, lagoas temporárias e campos secos, que abrigam diferentes espécies de flora e fauna. Esse mosaico de habitats permite que muitas espécies coexistam, aumentando a biodiversidade do bioma.</t>
+        </is>
+      </c>
+      <c r="I611" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J611" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K611" t="inlineStr"/>
+      <c r="L611" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>Disponível em: https://images.populationpyramid.net/capture/?selector=%23pyramid-share-container&amp;url=https%3A%2F%2Fwww.populationpyramid.net%2Fpt%2Fcanad%25C3%25A1%2F2023%2F%3Fshare%3Dtrue. Acesso em: 24 set. 2024.
+A partir da pirâmide etária do Canadá em 2023, é possível destacar que este país possui como característica</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>uma possível redução de trabalhadores no futuro.</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>a existência de  muitos jovens e alta taxa de fecundidade.</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>uma menor parcela da população entre homens e mulheres.</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>a baixa expectativa de vida da população para o futuro.</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>uma predominância da população idosa.</t>
+        </is>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H612" t="inlineStr">
+        <is>
+          <t>A pirâmide etária do Canadá em 2023 mostra que a faixa etária "0-4 anos" possui a menor proporção da população. Isso indica que pode haver uma redução na quantidade de jovens entrando no mercado de trabalho no futuro, potencialmente resultando em uma escassez de trabalhadores.</t>
+        </is>
+      </c>
+      <c r="I612" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J612" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>8a_ph03_geo_01.jpg</t>
+        </is>
+      </c>
+      <c r="L612" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>Leia o texto a seguir.
+A Estátua da Liberdade, um dos grandes símbolos dos EUA, desde 1886 "guarda" a entrada de Nova York pelo mar. [...]  A obra voltou ao imaginário americano depois da publicação dos controversos planos do presidente Donald Trump para a imigração, em especial sua tentativa de vetar a entrada de indivíduos de sete países majoritariamente muçulmanos - que atribui a questões de segurança.
+Disponível em: https://www.bbc.com/portuguese/internacional-38919713#:~:text=Objeto%20de%20controv%C3%A9rsia&amp;text=%22E%20se%20uma%20imagem%20ocidental,o%20projeto%20ser%20rejeitado%20totalmente.%22&amp;text=Esta%20n%C3%A3o%20foi%20a%20%C3%BAnica,correntes%20quebradas%2C%20al%C3%A9m%20da%20tocha. Acesso em 24 de out de 2024.
+Qual é o simbolismo principal da Estátua da Liberdade, inaugurada em 1886 em Nova York, especialmente ressaltado pelo poema gravado em sua base?</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>Comemorar a vitória americana na Guerra Civil.</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>Marcar a aliança entre os Estados Unidos e a França.</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>Exprimir solidariedade e acolhimento a imigrantes e estrangeiros.</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>Representar a inovação em monumentos de obras arquitetônicas pelo globo.</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>Representar a maioridade política dos Estados Unidos no cenário internacional.</t>
+        </is>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H613" t="inlineStr">
+        <is>
+          <t>Inaugurada em 1886, a Estátua da Liberdade guarda a entrada de Nova York pelo mar e simboliza a promessa feita aos imigrantes na época: liberdades civis, iniciativa privada e oportunidades de trabalho. O poema na base da estátua exalta a solidariedade e o acolhimento aos imigrantes, um tema que voltou ao imaginário americano durante os controversos planos do presidente Donald Trump para a imigração.</t>
+        </is>
+      </c>
+      <c r="I613" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J613" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K613" t="inlineStr"/>
+      <c r="L613" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>Leia o texto a seguir.
+Ao longo do último meio século, o Canadá se transformou em uma nação multicultural. Com uma imensa área habitada por apenas 12 milhões de pessoas após a 2ª Guerra Mundial, o governo canadense promoveu políticas durante as décadas seguintes para atrair estrangeiros.
+Além de tornar o Canadá uma das sociedades mais multiculturais do mundo, a imigração tem sido um motor do crescimento.
+Disponível em: https://www.bbc.com/portuguese/articles/c4nx08pp0q1o. Acesso em: 24 out. 2024. 
+Qual é o principal motivo pelo qual o Canadá promove políticas de imigração?</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>Atrair trabalhadores para o mercado de trabalho e expandir a economia.</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>Promover a sua imagem internacional como um país acolhedor.</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>Fortalecer o sistema educacional com a diversidade cultural.</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>Criar alianças estratégicas com outros países.</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>Incrementar o setor turístico e cultural no país.</t>
+        </is>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H614" t="inlineStr">
+        <is>
+          <t>Ao longo do último meio século, o Canadá se tornou uma nação multicultural. Após a 2ª Guerra Mundial, com uma população de apenas 12 milhões de pessoas, o governo canadense implementou políticas para atrair estrangeiros com o objetivo de povoar o país e expandir sua economia. A imigração tem sido um motor do crescimento, trazendo talento e mão de obra para as empresas canadenses.</t>
+        </is>
+      </c>
+      <c r="I614" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J614" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K614" t="inlineStr"/>
+      <c r="L614" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>Disponível em: http://www.geografia.seed.pr.gov.br/modules/galeria/detalhe.php?foto=1529&amp;evento=5. Acesso em 25 de out de 2024.
+Quais países compõem a América Anglo-Saxônica?</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>Estados Unidos e Canadá.</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>México e Estados Unidos.</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>México e Guatemala.</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>Canadá e México.</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>Brasil e Argentina.</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H615" t="inlineStr">
+        <is>
+          <t>No mapa, a América Anglo-Saxônica está representada pela região em vermelho, que é composta pelos Estados Unidos e Canadá. Essa área é caracterizada pelo predomínio da língua inglesa e da cultura de origem britânica.</t>
+        </is>
+      </c>
+      <c r="I615" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J615" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>8a_ph03_geo_04.jpg</t>
+        </is>
+      </c>
+      <c r="L615" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>Leia o texto a seguir.
+Os colonizadores estabeleceram o conceito de raça com base em fenótipos e cor da pele para classificar os seres humanos. Eles se autodenominaram brancos e consideraram aqueles que não eram brancos como pertencentes a raças inferiores, passíveis, portanto, de serem subjugados, escravizados e/ou explorados. Os Estados Unidos da América foram construídos sobre a divisão racial, com quase 250 anos de nação sustentados pela hierarquia racial.
+Disponível em: https://www.opeu.org.br/2024/06/08/racismo-institucional-nos-eua-o-caso-raven-baxter-e-a-persistencia-da-discriminacao-racial/. Acesso em 24 de out de 2024.
+Qual foi o papel da hierarquia racial na formação dos Estados Unidos?</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>Permitiu a emancipação de diferentes grupos étnicos no país.</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>Teve influência insignificante na formação dos Estados Unidos.</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>Destinou-se para manter a segregação e a desigualdade entre as raças.</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>Contribuiu para fortalecer os pilares de igualdade e liberdade no país.</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>Caminhou para fortalecer os distintos laços entre diferentes culturas.</t>
+        </is>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H616" t="inlineStr">
+        <is>
+          <t>A hierarquia racial nos Estados Unidos moldou profundamente a estrutura social, econômica e política do país. Embora tenham sido feitos progressos significativos na luta contra a discriminação racial, os efeitos dessa hierarquia ainda são visíveis e continuam a influenciar a sociedade americana.</t>
+        </is>
+      </c>
+      <c r="I616" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J616" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K616" t="inlineStr"/>
+      <c r="L616" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>Leia o texto a seguir.
+Megalópole
+José Horta Nunes
+A nomeação megalópole significa a cidade pela sua grandeza e influência, e nessa direção, ela funciona como sinônimo de metrópole. A megalópole significa também um grande aglomerado de cidades, resultante do crescimento e da junção delas, ou seja, de uma conurbação. Com a fusão das cidades, o espaço rural fica bastante delimitado, ao pondo em alguns casos de a distinção urbano x rural não funcionar mais.
+Um caso típico, apontado por vários urbanistas, é o da megalópole de Boswash, que vai de Boston a Washinton, no Nordeste dos Estados Unidos. Inclui as metrópoles de Nova York, Filadélfia, Baltimore e Washington. No Brasil, está em formação uma megalópole que une as regiões metropolitanas do Rio de Janeiro e de São Paulo, estendo-se até a região metropolitana de Campinas.
+[...]
+Disponível em:&lt; https://www.labeurb.unicamp.br/endici/index.php?r=verbete%2Fview&amp;id=237&gt;. Acesso em: 18 mar. 2020.
+A região em que se localiza BosWash é conhecida como:</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>Grandes lagos.</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>Nordeste.</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>Costa sul.</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>Planícies centrais.</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>Montes apalaches.</t>
+        </is>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H617" t="inlineStr">
+        <is>
+          <t>Sendo uma das maiores megalópoles do mundo, BosWash está localizada nas áreas urbanas de maior desenvolvimento no Nordeste dos Estados Unidos.</t>
+        </is>
+      </c>
+      <c r="I617" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J617" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K617" t="inlineStr"/>
+      <c r="L617" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>Um homem atropelou várias pessoas neste sábado (12) em uma marcha de manifestantes antirracismo em Charlottesville, na Virgínia. A cidade está sendo palco de conflitos entre esses ativistas e manifestantes nacionalistas brancos, neonazistas e membros da Ku Klux Klans que se reuniram desde a noite de sexta-feira (11)[...] Segundo as autoridades, uma mulher de 32 anos morreu no atropelamento. Outras 19 pessoas ficaram feridas --cinco estão em estado crítico. Além dessa morte, um helicóptero da polícia caiu, deixando dois mortos --a polícia investiga as causas e se o caso tem relação direta com o conflito racial.
+[...]
+UOL SP. Suspeito é preso após atropelar multidão e matar manifestante em marcha antirracismo nos EUA. 12 ago.2017. Disponível
+em:https://noticias.uol.com.br/internacional/ultimas-noticias/2017/08/12/carro-atropela-manifestantes-durante-protesto-desupremacistas-brancos-nos-eua.htm. Acesso em: 16 mar.2020
+Atentados racistas podem ser explicados pela</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>diminuição do nacionalismo branco.</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>tentativas de se reimplantar a escravidão.</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>radicalismo cristão que prega a hierarquia social.</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>autossegregação dos negros em relação aos brancos.</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>permanência de políticas segregacionistas pós-escravidão.</t>
+        </is>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H618" t="inlineStr">
+        <is>
+          <t>Mesmo após o fim da escravidão, permaneceram práticas segregacionistas semelhantes ao apartheid da África do Sul, desta forma, o conflito e o ideal de superioridade étnica perduram até hoje nos EUA, tendo se intensificado nos últimos anos.</t>
+        </is>
+      </c>
+      <c r="I618" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J618" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K618" t="inlineStr"/>
+      <c r="L618" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>A porta-voz da Casa Branca, Sarah Sanders, defendeu nesta o presidente Donald Trump das acusações de que ele estimulou a violência contra uma deputada muçulmana, depois de tuitar um vídeo que alterna imagens da parlamentar e dos ataques de 11 de setembro de 2001.
+A declaração de Sanders veio logo depois de a presidente da Câmara dos Deputados, a democrata Nancy Pelosi, dizer que conversou com as autoridades sobre a segurança de sua colega e pedir a Trump que apagasse o tuíte.
+No post, o presidente americano compartilhou um vídeo em que a congressista Ilhan Omar fala sobre o 11 de setembro. A edição foi feita de forma que a declaração da deputada é repetida e alternada com cenas dos atentados.
+[...]
+REDAÇÃO. Revista Veja. Trump é acusado de estimular violência contra deputada muçulmana. 15 abr.2019. Disponível
+em:&lt;https://veja.abril.com.br/mundo/trump-e-acusado-de-estimular-violencia-contra-congressista-muculmana/.&gt; Acesso em: 17mar. 2020.
+Imigrantes residentes nos EUA de origem islâmica sofrem com um estereótipo relacionado</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>a prática de crimes.</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>a intolerância cultural.</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>a atentados terroristas.</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>ao baixo nível de instrução.</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>a falta de protagonismo feminino.</t>
+        </is>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H619" t="inlineStr">
+        <is>
+          <t>Em 2001 atentados terroristas provocados por grupos islâmicos mataram cerca de 3 mil pessoas nos EUA, desde então, pessoas e grupos de origem islâmica sofrem com o estereótipo de terroristas.</t>
+        </is>
+      </c>
+      <c r="I619" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J619" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K619" t="inlineStr"/>
+      <c r="L619" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>Considerando que os EUA estão na terceira fase de transição demográfica, é característica deste país nos tempos atuais:</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>As altas taxas de mortalidade infantil.</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>A farta disponibilidade de mão-de-obra.</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>O significativo incremento da imigração.</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>As altas taxas de crescimento demográfico.</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>O progressivo envelhecimento populacional.</t>
+        </is>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H620" t="inlineStr">
+        <is>
+          <t>A terceira fase da transição demográfica caracteriza-se por baixos valores de crescimento demográfico, onde a baixa natalidade e a melhoria das condições de saúde geram envelhecimento populacional.</t>
+        </is>
+      </c>
+      <c r="I620" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J620" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K620" t="inlineStr"/>
+      <c r="L620" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>Os jovens que uniram indígenas dos EUA contra oleoduto barrado por Obama e liberado por Trump
+A celebração pôs fim a uma das maiores mobilizações de indígenas americanos em várias décadas[...]
+[...]
+Mas quando começou, em abril, o movimento não passava de um "acampamento de reza" erguido por um punhado de jovens e adolescentes sioux à beira do rio Cannonball.
+[...]
+Defensores do projeto dizem que ele gerará empregos na indústria petrolífera, reduzirá a dependência dos EUA por importações de combustíveis e barateará a gasolina.
+[...]
+FELLETE, João. Os jovens que uniram indígenas dos EUA contra oleoduto barrado por Obama e liberado por Trump. Da BBC Brasil em
+Washington. Disponível em:&lt; https://www.bbc.com/portuguese/internacional-38926624&gt;. Acesso em: 18 mar.2020.
+O contexto dado assemelha-se ao ideal pós-colonial de ocupação do território estadunidense na medida em que</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>concebe ao território prioridade econômica.</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>sempre respeitam as decisões nacionais indígenas.</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>prioriza a intocabilidade ambiental.</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>busca efetivar a consolidação do estado-nacional.</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>oferta terras a imigrantes britânicos.</t>
+        </is>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H621" t="inlineStr">
+        <is>
+          <t>Ainda hoje a prioridade dada ao território é de cunho econômico, o que gera conflito com visões não predatórias típicas das comunidades indígenas. Fenômeno que se processa desde tempos coloniais.</t>
+        </is>
+      </c>
+      <c r="I621" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J621" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K621" t="inlineStr"/>
+      <c r="L621" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>A própria noção de Iluminismo, Ilustração, ou ainda Esclarecimento, como o termo é por vezes traduzido, indica, através da metáfora da luz e da claridade, uma oposição às trevas, ao obscurantismo, á ignorância, à superstição, ou seja, à existência de algo oculto, enfatizando, ao contrário, a necessidade de o real, em todos os seus aspectos, tornar-se transparente à razão. 
+MARCONDES, Danilo. Iniciação a História da Filosofia: Dos Pré-Socráticos a Wittgenstein. Rio de Janeiro: Jorge Zahar, 2018, p. 207.
+A metáfora da luz trazida pelo Iluminismo se dá em oposição às "trevas" da(do)</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>Idade Média, compreendida de forma negativa pelos Iluministas que rejeitavam o dogmatismo religioso característico desse período.</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>Democracia, percebida como uma estrutura de poder injusta e arbitrária pelos pensadores iluministas.</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>Revolução Científica, rejeitada pelos iluministas por ter incentivado o abandono das práticas do cristianismo.</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>Renascimento, visto como herege por ter deslocado o centro das artes da esfera religiosa para os aspectos humanos</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>Antigo Regime, entendido como a estrutura responsável por desestruturar o feudalismo defendido pelos iluministas.</t>
+        </is>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H622" t="inlineStr">
+        <is>
+          <t>Os iluministas frequentemente viam a Idade Média como uma época de trevas, dominada pela ignorância e pela superstição, em oposição às ideias de razão e esclarecimento do Iluminismo.</t>
+        </is>
+      </c>
+      <c r="I622" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J622" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K622" t="inlineStr"/>
+      <c r="L622" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>Conhecido como o século das Luzes ou do Iluminismo, o século XVIII foi marcado por um movimento do pensamento europeu (ocorrido mais especificamente na segunda metade do século XVIII) que abrangeu o pensamento filosófico e gerou uma grande revolução nas artes (principalmente na literatura), nas ciências, nos costumes, na teoria política e na doutrina jurídica. O Iluminismo também se distinguiu pela centralidade da ciência e da racionalidade crítica no questionamento filosófico.
+Disponível em: https://www.maxwell.vrac.puc-rio.br/15543/15543_3.PDF. Acesso em: 22 out. 2024
+O movimento mencionado no texto teve como principal característica a</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>rejeição completa da religião e a adoção do ateísmo como doutrina oficial das sociedades europeias.</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>promoção de revoluções exclusivamente políticas sem impacto em outras áreas do conhecimento.</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>centralidade da ciência e da racionalidade crítica no questionamento filosófico.</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>priorização do ensino religioso como forma de produção de conhecimento.</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>ênfase na manutenção das tradições e dogmas medievais.</t>
+        </is>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H623" t="inlineStr">
+        <is>
+          <t>O Iluminismo enfatizou o uso da razão e da ciência para questionar e reformar todas as áreas do conhecimento humano, incluindo a filosofia, as artes, as ciências, os costumes, a teoria política e a doutrina jurídica. Este movimento foi fundamental para o desenvolvimento do pensamento crítico e científico.</t>
+        </is>
+      </c>
+      <c r="I623" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J623" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K623" t="inlineStr"/>
+      <c r="L623" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>Galileu Galilei nasceu na cidade de Pisa em 1564, mesmo ano da morte do pintor e escultor Michelangelo e do nascimento do dramaturgo inglês William Shakespeare. Exatos 31 anos antes, o matemático e astrônomo polonês Nicolau Copérnico publicou sua obra maior – Das revoluções dos corpos celestes –, defendendo a teoria de que a Terra se move em torno do Sol, e não o contrário.
+Essa teoria seria defendida e desenvolvida por Galileu e seu contemporâneo Johannes Kepler, que primeiro descreveu a trajetória elíptica dos planetas. A síntese final desses trabalhos foi a Teoria da Gravitação Universal, formulada pelo físico e matemático inglês Isaac Newton que, por coincidência, nasceu em 1642, o mesmo ano em que Galileu morreu.
+CAVALCANTE, Pedro. Como Galileu inventou a ciência moderna. Disponível em: https://super.abril.com.br/historia/o-novo-mundo-de-galileu. Acesso em: 22 out. 2024.
+A teoria concebida por Copérnico e desenvolvida por Galileu e Kepler deu origem ao</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>humanismo.</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>heliocentrismo.</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>protestantismo.</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>iluminismo.</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>geocentrismo.</t>
+        </is>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H624" t="inlineStr">
+        <is>
+          <t>A teoria defendida por Copérnico, e depois desenvolvida por Galileu e Kepler, é conhecida como heliocentrismo. Ela propõe que a Terra e os outros planetas giram em torno do Sol, desafiando a visão geocêntrica tradicional que colocava a Terra no centro do universo.</t>
+        </is>
+      </c>
+      <c r="I624" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J624" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K624" t="inlineStr"/>
+      <c r="L624" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>A efervescência cultural da Renascença criara uma vaga que não cessava de afogar as velhas certezas da Filosofia e da ciência baseadas sobretudo nos escritos do grego Aristóteles e na autoridade da Bíblia. O prestígio do Estado e da Igreja estavam igualmente corroídos pela dissidência política e pela Reforma protestante. Um novo mundo nascia. Mesmo em retirada, porém, a velhas instituições permaneciam, no início do século XVII, robustas o suficiente para queimar na fogueira um certo número de pensadores atrevidos.
+Descartes: a razão acima de tudo. Disponível em: https://super.abril.com.br/comportamento/descartes-a-razao-acima-de-tudo?utm_source=google&amp;utm_medium=cpc&amp;utm_campaign=eda_super_audiencia_institucional-Performance-Max-nova&amp;gad_source=1&amp;gclid=Cj0KCQjwmt24BhDPARIsAJFYKk0YMLGXm1apAQs1wxRQ_szSQzKsgCJJ8I_RXCnww8Lb4_A6gF-HnO4aAgx2EALw_wcB. Acesso em: 22 out. 2024.
+Como a Revolução Científica desafiou as antigas instituições, e qual foi a consequência enfrentada pelos cientistas?</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>A Revolução Científica reafirmou as teorias de Aristóteles, resultando no apoio incondicional da igreja aos novos cientistas.</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>Os cientistas passaram a questionar explicações baseadas na religião, resultando em perseguições e punições severas promovidas pela igreja.</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>A Revolução Científica eliminou todas as tradições religiosas, levando a uma cooperação harmoniosa entre a igreja e os cientistas.</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>Os seus pensadores fixaram suas formulações na Bíblia e na tradição, levando ao desenvolvimento conjunto de cientistas e teólogos.</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>O Estado incentivou os cientistas a colaborarem com a igreja para desenvolver novas tecnologias, resultando na aceitação plena das descobertas científicas.</t>
+        </is>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H625" t="inlineStr">
+        <is>
+          <t>Durante a Revolução Científica, os estudiosos começaram a desafiar as explicações tradicionais apoiadas pela igreja, o que levou a muitos conflitos, perseguições e até execuções de cientistas, como uma forma de suprimir tais ideias que desafiavam a autoridade religiosa.</t>
+        </is>
+      </c>
+      <c r="I625" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J625" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K625" t="inlineStr"/>
+      <c r="L625" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>Seu maior legado, porém, não foi uma descoberta científica específica, e sim um jeito de pensar. Galileu insistiu que a linguagem adequada para a filosofia natural (o nome que se dava, na época, às ciências exatas e biológicas) era a matemática, e não a palavra. Que qualquer afirmação sobre a natureza deveria partir da observação da própria natureza. Que é preciso acumular dados e fazer experimentos. 
+CAVALCANTE, Pedro. Como Galileu inventou a ciência moderna. Disponível em: https://super.abril.com.br/historia/o-novo-mundo-de-galileu. Acesso em: 23 out. 2024.
+Qual foi o principal legado de Galileu Galilei para a filosofia natural, conforme descrito no texto?</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>Desenvolvimento de hipóteses filosóficas com base exclusivamente na tradição e nos textos sagrados.</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>Aplicação rigorosa do método científico, enfatizando a observação, a experimentação e o uso da matemática.</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>Rejeição do uso da matemática na filosofia natural, priorizando a linguagem poética e literária.</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>Defesa da supremacia das explicações teológicas sobre as científicas, seguindo os dogmas da igreja.</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>Promoção do pensamento especulativo sem a necessidade de experimentação ou acumulação de dados.</t>
+        </is>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H626" t="inlineStr">
+        <is>
+          <t>O principal legado de Galileu foi a defesa da abordagem científica baseada na observação direta da natureza, no acúmulo de dados e na experimentação, utilizando a matemática como linguagem para descrever os fenômenos naturais, elementos centrais do método científico.</t>
+        </is>
+      </c>
+      <c r="I626" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J626" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K626" t="inlineStr"/>
+      <c r="L626" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>O pensamento iluminista, baseado no racionalismo, individualismo e liberdade absoluta do homem, ao criticar todos os fundamentos em que se assentava o Antigo Regime, revelava as suas contradições e as tornava transparentes aos olhos de um número cada vez maior de pessoas.
+(Modesto Florenzano. As revoluções burguesas, 1982. Adaptado.)
+Entre as críticas ao Antigo Regime, mencionadas no texto, podemos citar a rejeição iluminista ao</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>princípio da igualdade jurídica.</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>livre comércio.</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>liberalismo econômico.</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>republicanismo.</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>absolutismo monárquico.</t>
+        </is>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H627" t="inlineStr">
+        <is>
+          <t>Os filósofos iluministas teciam críticas ao Absolutismo monárquico pois esse feria o direito natural, ou seja, a afirmação de que todos eram iguais perante à lei e o exercício do poder baseado em explicações racionais.</t>
+        </is>
+      </c>
+      <c r="I627" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J627" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K627" t="inlineStr"/>
+      <c r="L627" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>O povo que possui o poder soberano deve fazer por si mesmo tudo o que pode fazer bem; e o que não puder fazer bem, deve fazê-lo por meio de seus ministros.
+Seus ministros não são seus se ele não os nomeia; logo, é uma máxima fundamental deste governo que o povo nomeie seus ministros, isto é, seus magistrados.
+MONTESQUIEU. O Espírito das Leis, Livro Segundo (adaptado). Disponível em:
+http://www.dhnet.org.br/direitos/anthist/marcos/hdh_montesquieu_o_espirito_das_leis.pdf. Acesso em 11 fev. 2020.
+A partir do excerto retirado de O Espírito das Leis, de Montesquieu, é correto afirmar que o pensamento iluminista</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>justificou pela religião o poder dos reis.</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>buscou conceber um sistema político justo.</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>promoveu ideias de sociedade sem Estado.</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>rejeitou toda forma de descentralização do poder.</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>defendeu a intervenção do Estado na economia.</t>
+        </is>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H628" t="inlineStr">
+        <is>
+          <t>Montesquieu, n'O Espírito das Leis, apresenta a necessidade de que o povo eleja magistrados para que assim, e somente assim, estes possam ter alguma autoridade sobre o povo. Os magistrados, os ministros, seriam do povo e teriam que se submeter aos seus desejos, algo que ia na contramão do sistema absolutista. Essas reflexões do movimento iluminista buscavam conceber um sistema baseado na justiça e na soberania do povo.</t>
+        </is>
+      </c>
+      <c r="I628" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J628" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K628" t="inlineStr"/>
+      <c r="L628" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>Resolvi fazer de conta que todas as coisas que até então haviam entrado no meu espírito não eram mais verdadeiras que as ilusões de meus sonhos. Mas, logo em seguida, adverti que, enquanto eu queria assim pensar que tudo era falso, cumpria necessariamente que eu, que pensava, fosse alguma coisa. E, notando que esta verdade: eu penso, logo existo, era tão firme e tão certa que todas as mais extravagantes suposições (...).
+DESCARTES, René. Discurso do Método, Parte IV.. São Paulo, LP&amp;M, 2005.
+A máxima de Descartes: eu penso, logo existo pode ser considerada parte das bases do pensamento Iluminista por</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>valorizar a centralidade do “eu” em oposição às filosofias renascentistas.</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>reafirmar a importância do autoconhecimento em oposição ao mundo externo.</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>refletir acerca da relevância dos sonhos na produção do conhecimento filosófico.</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>unir interpretações das perspectivas católica e renascentista em uma teoria.</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>destacar o valor da razão para se alcançar respostas justas e verdadeiras.</t>
+        </is>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H629" t="inlineStr">
+        <is>
+          <t>O Iluminismo é caracterizado pela valorização da verdade racional em oposição ao divino. Como é possível observar no excerto, o autor questiona-se acerca da veracidade dos elementos ao seu redor e sobre si mesmo. Sua existência, por sua vez, só pode ser confirmada pela certeza do uso de sua razão.</t>
+        </is>
+      </c>
+      <c r="I629" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J629" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K629" t="inlineStr"/>
+      <c r="L629" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>São verdades incontestáveis para nós: todos os homens nascem iguais; o Criador lhes conferiu certos direitos inalienáveis, entre os quais os de vida, o de liberdade e o de buscar a felicidade; para assegurar esses direitos se constituíram homens-governo cujos poderes justos emanam do consentimento dos governados; sempre que qualquer forma de governo tenda a destruir esses fins, assiste ao povo o direito de mudá-la ou aboli-la, instituindo um novo governo cujos princípios básicos e organização de poderes obedeçam às normas que lhes pareçam mais próprias para promover a segurança e a felicidade gerais.
+Trecho da Declaração de Independência dos Estados Unidos da América. Disponível em: https://www.uel.br/pessoal/jneto/gradua/historia/recdida/declaraindepeEUAHISJNeto.pdf. Acesso em: 01 nov. 2024.
+A Declaração de Independência dos EUA tem inspiração iluminista na medida em que</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>hierarquiza os homens a partir das famílias as quais pertencem e de sua riqueza.</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>define a supremacia plena dos governantes para fazer o que bem entenderem.</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>submete a autoridade dos governantes aos interesses das pessoas e não de um indivíduo.</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>justifica a liberdade dos homens como uma determinação divina definitiva.</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>determina que um governo justo está ligado aos interesses da Igreja.</t>
+        </is>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H630" t="inlineStr">
+        <is>
+          <t>O Iluminismo defende que o poder é emanado do povo, logo, o povo deveria escolher e legitimar seus governantes. Se os governantes não corresponderem às expectativas do povo, os governantes poderiam ser retirados do poder pelo povo. É precisamente essa ideia que é trabalhada no trecho da Declaração de Independência dos EUA.</t>
+        </is>
+      </c>
+      <c r="I630" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J630" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K630" t="inlineStr"/>
+      <c r="L630" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>Disponível em: https://upload.wikimedia.org/wikipedia/commons/7/7b/Index_Librorum_Prohibitorum_1.jpg. Acesso em: 01 nov. 2024.
+Em 1559, a Igreja Católica divulgou uma lista de livros proibidos por serem considerados opositores da fé, o Index. Diversos filósofos, escritores e cientistas tiveram suas obras incluídas no índice. Esse é um exemplo de que</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>a religião e a ciência coexistiram de forma pacífica durante a modernidade.</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>embora a ciência discordasse da religião em alguns aspectos, isso não era um impedimento de relacionamento pacífico pela perspectiva da religião.</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>embora a religião discordasse da ciência em alguns aspectos, isso não era um impedimento de relacionamento pacífico pela perspectiva da ciência.</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>ciência e religião tiveram uma relação conflituosa, incluindo casos de condenação de cientistas pela Santa Inquisição.</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>a religião e a ciência não coexistiram durante o mesmo período.</t>
+        </is>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H631" t="inlineStr">
+        <is>
+          <t>Com o avanço da ciência, temas defendidos pela Igreja passaram a ser contestados, como o geocentrismo, resultando, assim, na perseguição e no julgamento de pessoas acusadas de práticas heréticas, como os cientistas.</t>
+        </is>
+      </c>
+      <c r="I631" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J631" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K631" t="inlineStr">
+        <is>
+          <t>8a_ph03_his_10.jpg</t>
+        </is>
+      </c>
+      <c r="L631" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>Naruto e Tartarugas Ninja fazem crossover em novo quadrinho da IDW
+Naruto e Tartarugas Ninja farão um crossover especial em nova edição de quadrinho da IDW, com lançamento em outubro nos EUA. As informações são do JBox.
+Foi divulgada uma primeira imagem do lançamento. No entanto, ressalta-se que ainda não se trata de uma versão final. Confira abaixo. 
+Disponível em: https://www.omelete.com.br/naruto/naruto-tartarugas-ninja-hq-crossover. Acesso em 11 de out de 2024.
+Qual o tipo de sujeito da frase em destaque no texto?</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>Sujeito determinado composto.</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>Sujeito determinado elíptico.</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>Sujeito indeterminado.</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>Sujeito inexistente.</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>Sujeito simples.</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H632" t="inlineStr">
+        <is>
+          <t>Em "No entanto, ressalta-se que ainda não se trata de uma versão final", o pronome "se" indica que a ação do verbo não é atribuída a um sujeito específico, tornando o sujeito indeterminado. Dessa forma, não é possível identificar quem realiza a ação de "ressaltar", caracterizando o sujeito como indeterminado.</t>
+        </is>
+      </c>
+      <c r="I632" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J632" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K632" t="inlineStr"/>
+      <c r="L632" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>Nobel de Literatura: relembre os vencedores dos dez últimos anos
+Han Kang, escritora sul-coreana, ganhou o Prêmio Nobel de Literatura 2024. O anúncio foi feito nesta quinta-feira (10), pela Academia Sueca, em Estocolmo.
+De acordo com a academia, o prêmio foi concedido “por sua intensa prosa poética que confronta traumas históricos e expõe a fragilidade da vida humana".
+Disponível em: https://g1.globo.com/pop-arte/noticia/2024/10/10/nobel-de-literatura-relembre-os-vencedores-dos-ultimos-anos.ghtml. Acesso em 11 de out de 2024.
+Qual é o sujeito do segundo parágrafo da notícia?</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>"Fragilidade da vida humana".</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>"Traumas históricos".</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>"Prosa poética".</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>"Academia".</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>"Prêmio".</t>
+        </is>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H633" t="inlineStr">
+        <is>
+          <t>"Prêmio" é o sujeito da frase porque é o elemento que recebe a ação do verbo "foi concedido". Na frase, "o prêmio" é o que está sendo concedido pela academia, portanto, é o sujeito que realiza a ação principal da oração.</t>
+        </is>
+      </c>
+      <c r="I633" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J633" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K633" t="inlineStr"/>
+      <c r="L633" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>Taylor Swift doa US$ 5 milhões para ajudar vítimas dos furacões Milton e Helene nos Estados Unidos
+Informação foi anunciada pela Feeding America, organização sem fins lucrativos que constitui uma rede nacional de mais de 200 bancos alimentares.
+Taylor Swift doou US$ 5 milhões (aproximadamente R$ 27,9 milhões, na cotação atual) para ajudar as vítimas dos furacões Helene e Milton nos Estados Unidos. A informação foi anunciada pela Feeding America, organização sem fins lucrativos que constitui uma rede nacional de mais de 200 bancos alimentares.
+"Esta contribuição vai ajudar comunidades a reconstruir e se recuperar, provendo comida essencial, água limpa e suprimentos para pessoas afetadas por estas tempestades devastadoras. Juntos, podemos causar um impacto real ajudando famílias enquanto elas navegam os desafios à frente. Obrigado, Taylor, por se juntar a nós no movimento para acabar com a fome e ajudar comunidades necessitadas", escreveu a organização.
+Os EUA estão atravessando um período de fortes tempestades, com os furacões Helene e Milton. No final de setembro, o furacão Helene atingiu seis estados americanos, deixando ao menos 200 mortos.
+Já a noite da última quarta (9), o furacão Milton chegou ao estado da Flórida. O fenômeno foi considerado uma das tempestades mais poderosas que se formaram no Atlântico Norte nos últimos anos. A chegada do furacão deixou milhões de pessoas sem luz e provocou inundações na costa oeste do estado.
+Disponível em: Taylor Swift doa US$ 5 milhões para ajudar vítimas dos furacões Milton e Helene nos Estados Unidos | Pop &amp; Arte | G1 (globo.com). Acesso em: 11 out. 2024
+O texto acima se caracteriza como notícia e não como reportagem, pois</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>explora detalhadamente o contexto histórico dos furacões Helene e Milton.</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>inclui entrevistas com diversas fontes e perspectivas sobre a doação de Taylor Swift.</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>apresenta opiniões e análises sobre a importância das doações em situações de desastre.</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>fornece um relato breve e direto do evento, focando na doação de Taylor Swift e nas informações essenciais.</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>descreve minuciosamente os impactos econômicos que os furacões Helene e Milton causaram na vida da cantora Taylor Swift, que perdeu 5 milhões.</t>
+        </is>
+      </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H634" t="inlineStr">
+        <is>
+          <t>O texto fornece um relato breve e direto do evento, focando na doação de Taylor Swift e nas informações essenciais, como o valor da doação, a organização beneficiada e os impactos dos furacões. Isso caracteriza o texto como uma notícia. Se houvesse um aprofundamento maior nas informações, o texto se caracterizaria como reportagem.</t>
+        </is>
+      </c>
+      <c r="I634" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J634" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K634" t="inlineStr"/>
+      <c r="L634" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>Brasil supera a marca de 50 medalhas nos Jogos Paraolímpicos
+Nove novos pódios entre atletismo, natação e halterofilismo marcam o dia de competições na França. Em todas as conquistas brasileiras, a marca do Bolsa Atleta do Governo Federal
+Com mais quatro dias de competições ainda no horizonte dos Jogos Paralímpicos até o próximo domingo, a delegação brasileira já superou nesta quarta a marca de 50 medalhas em Paris. O feito simbólico veio com o bronze de Lara Lima na categoria até 41 quilos do halterofilismo.
+Ao longo do dia, o país subiu ao pódio outras oito vezes, entre atletismo e natação, com destaque para o sexto ouro de Maria Carolina Santiago, a brasileira com maior número de títulos na história dos Jogos. Carol venceu os 100m livre da classe S12 e fechou o revezamento 4 x 100m do Brasil que repetiu na França a prata de Tóquio.
+Ao todo, o Brasil soma 15 ouros, 15 pratas e 27 bronzes, um total de 57 medalhas, na sexta posição geral. A liderança permanece com a China, com 60 ouros e 131 medalhas.
+Até hoje, a melhor campanha do Brasil foi registrada em Tóquio, em 2021. No Japão, o Brasil somou 72 medalhas, com 22 ouros, 20 pratas e 30 bronzes. 
+Disponível em: Brasil supera a marca de 50 medalhas nos Jogos Paralímpicos — Secretaria de Comunicação Social (www.gov.br). Acesso em 14 de out. de 2024.
+Os dois últimos parágrafos destacados da notícia são classificados como</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>o terceiro parágrafo contém um período simples e o quarto parágrafo contém um período simples.</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>o terceiro parágrafo contém um período simples e o quarto parágrafo contém um período composto.</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>o terceiro parágrafo contém dois períodos simples e o quarto parágrafo contém dois períodos simples.</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>o terceiro parágrafo contém dois períodos simples e o quarto parágrafo contém um período composto.</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>o terceiro parágrafo contém um período composto e o quarto parágrafo contém dois períodos simples.</t>
+        </is>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H635" t="inlineStr">
+        <is>
+          <t>O terceiro parágrafo contém dois períodos simples, pois há apenas duas orações, isto é, uma frase que contenha um verbo (ou locução verbal). O mesmo acontece no quarto parágrafo, que contém dois períodos simples.</t>
+        </is>
+      </c>
+      <c r="I635" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J635" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K635" t="inlineStr"/>
+      <c r="L635" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>Leia a notícia a seguir.
+Por que gatos gostam mais dos homens que das mulheres? Estudo explica o motivo
+Pesquisa realizada em universidade da Turquia analisou 31 felinos domésticos e revelou uma possível seletividade comunicativa por parte dos animais
+Um dos principais achados foi a diferença de vocalização entre os gêneros dos tutores. Segundo os dados coletados, os gatos emitiram uma média de 4,3 miados ao reencontrar homens, enquanto vocalizaram 1,8 vezes diante de mulheres. A hipótese dos cientistas é que os felinos intensificam os sinais vocais com homens por perceberem menor frequência de interações verbais por parte desse grupo.
+[...]
+Apesar dos resultados, os pesquisadores alertam que o estudo tem limitações. A amostragem restrita e a condução do experimento exclusivamente na Turquia indicam a necessidade de novas investigações para determinar se os padrões observados se aplicam a gatos de outras culturas e ambientes. 
+Disponível em: https://exame.com/ciencia/por-que-gatos-gostam-mais-dos-homens-que-das-mulheres-estudo-explica-o-motivo/. Acesso em: 05 dez. 2025.
+Na notícia, identifica-se um sujeito determinado composto em</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>“Pesquisa realizada em universidade da Turquia analisou 31 felinos domésticos.”</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>“Apesar dos resultados, os pesquisadores alertam que o estudo tem limitações.”</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>“Um dos principais achados foi a diferença de vocalização entre os gêneros dos tutores.”</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>“[...] os felinos intensificam os sinais vocais com homens por perceberem menor frequência de interações verbais”</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>“A amostragem restrita e a condução do experimento exclusivamente na Turquia indicam a necessidade de novas investigações”</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H636" t="inlineStr">
+        <is>
+          <t>Na frase, o sujeito determinado composto é formado por "a amostragem restrita" e "a condução do experimento exclusivamente na Turquia". Ambos os elementos estão ligados pela conjunção "e", demonstrando que juntos realizam a ação de "indicar a necessidade de novas investigações". Assim, apresenta dois núcleos que compõem o sujeito da oração, caracterizando-o como um sujeito composto.</t>
+        </is>
+      </c>
+      <c r="I636" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J636" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K636" t="inlineStr"/>
+      <c r="L636" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>A princesa da água
+Ela era filha de um casal encantado, o rei do céu e a rainha da Terra. Ficou conhecida como a princesa das águas, porque tinha poderes sobre rios, riachos, cachoeiras… Era linda e sua beleza atraía muitos interessados em casar-se com ela. Mas foi o filho do Sol que conquistou seu coração. O casamento foi muito bonito e alegre, foram sete dias e sete noites de festividades.
+Quando a festa acabou, os noivos partiram para a casa do Sol. Chegando lá. a princesa das águas disse ao marido que pretendia passar com ele o ano inteiro, exceto três meses que havia de passar com sua mãe. Assim, todos os anos, a princesa das águas passava uma temporada com sua mãe debaixo do mar, num rico palácio de ouro e de brilhantes.
+O tempo correu e a princesa teve um filho. O principezinho ficava com o pai, quando a moça ia visitar sua mãe. Certo ano, porém, a princesa foi para a sua temporada com a mãe, como sempre, mas não a encontrou no palácio. A princesa perguntou sobre sua mãe aos peixes dos rios, às areias do mar, às conchas das praias, mas ninguém lhe respondia. Muito mais do que meses e anos se passaram nessa busca sem sucesso. Cansada e muito triste, ela retornou ao reino do Sol.
+Chegando lá, uma surpresa: o rei Sol havia se casado com outra e seu filho, já crescido, estava muito maltratado e triste. A princesa das águas, com muita raiva, pegou seu filho e se mudou para o fundo do mar. Deu ordem para que a maré subisse, e tudo ficou coberto pelas águas. No fundo do mar, a princesa e seu filho ficaram para sempre.
+Dizem que quem se atreve a olhar fixamente para a água do mar, vê a princesa, é encantado, cai na água e some para sempre.
+Disponível em: &lt;http://chc.org.br/artigo/a-princesa-da-agua/&gt;. Acesso em: 31 jan. 2020.
+Qual das sentenças retiradas do texto constitui um período simples?</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>“O tempo correu e a princesa teve um filho.”</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>“Quando a festa acabou, os noivos partiram para a casa do Sol.”</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>"O principezinho ficava com o pai, quando a moça ia visitar sua mãe."</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>“Era linda e sua beleza atraía muitos interessados em casar-se com ela.”</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>“Assim, todos os anos, a princesa das águas passava uma temporada com sua mãe debaixo do mar, num rico palácio de ouro e de brilhantes.”</t>
+        </is>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H637" t="inlineStr">
+        <is>
+          <t>Um período simples é aquele que contém apenas uma oração, sendo caracterizado pela presença de um único verbo ou locução verbal, que forma uma única oração. Na sentença "Assim, todos os anos, a princesa das águas passava uma temporada com sua mãe debaixo do mar, num rico palácio de ouro e de brilhantes.", o verbo "passava" é o único verbo presente, indicando uma única ação realizada pelo sujeito "a princesa das águas". Não há outras orações subordinadas ou coordenadas na frase, o que confirma que se trata de um período simples.</t>
+        </is>
+      </c>
+      <c r="I637" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J637" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>8a_ph03_por_06.png</t>
+        </is>
+      </c>
+      <c r="L637" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>Ela era filha de um casal encantado, o rei do céu e a rainha da Terra. Ficou conhecida como a princesa das águas, porque tinha poderes sobre rios, riachos, cachoeiras… Era linda e sua beleza atraía muitos interessados em casar-se com ela. Mas foi o filho do Sol que conquistou seu coração. O casamento foi muito bonito e alegre, foram sete dias e sete noites de festividades.
+Quando a festa acabou, os noivos partiram para a casa do Sol. Chegando lá, a princesa das águas disse ao marido que pretendia passar com ele o ano inteiro, exceto três meses que havia de passar com sua mãe. Assim, todos os anos, a princesa das águas passava uma temporada com sua mãe debaixo do mar, num rico palácio de ouro e de brilhantes.
+O tempo correu e a princesa teve um filho. O principezinho ficava com o pai, quando a moça ia visitar sua mãe. Certo ano, porém, a princesa foi para a sua temporada com a mãe, como sempre, mas não a encontrou no palácio. A princesa perguntou sobre sua mãe aos peixes dos rios, às areias do mar, às conchas das praias, mas ninguém lhe respondia. Muito mais do que meses e anos se passaram nessa busca sem sucesso. Cansada e muito triste, ela retornou ao reino do Sol.
+Chegando lá, uma surpresa: o rei Sol havia se casado com outra e seu filho, já crescido, estava muito maltratado e triste. A princesa das águas, com muita raiva, pegou seu filho e se mudou para o fundo do mar. Deu ordem para que a maré subisse, e tudo ficou coberto pelas águas. No fundo do mar, a princesa e seu filho ficaram para sempre. Dizem que quem se atreve a olhar fixamente para a água do mar, vê a princesa, é encantado, cai na água e some para sempre.
+Disponível em: &lt;http://chc.org.br/artigo/a-princesa-da-agua/&gt;. Acesso em: 31 jan. 2020
+Releia: “Ela era filha de um casal encantado, o rei do céu e a rainha da Terra.” Qual o sujeito do período?</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>“Ela”.</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>"Rei".</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>“Filha”.</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>“Casal”.</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>“Rainha”.</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H638" t="inlineStr">
+        <is>
+          <t>O sujeito é o termo da oração que indica quem ou o que realiza a ação expressa pelo verbo ou de quem ou do que se declara algo. No caso desta sentença, o verbo "era" está se referindo a "Ela", que é a pessoa sobre a qual se está fazendo uma declaração, informando que ela é filha de um casal encantado. As demais palavras na frase ("filha", "casal", "rei", "rainha") não desempenham o papel de sujeito, mas sim de complementos ou especificações adicionais dentro da oração. Portanto, "Ela" é o termo que exerce a função de sujeito.</t>
+        </is>
+      </c>
+      <c r="I638" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J638" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>8a_ph03_por_07.png</t>
+        </is>
+      </c>
+      <c r="L638" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>Ela era filha de um casal encantado, o rei do céu e a rainha da Terra. Ficou conhecida como a princesa das águas, porque tinha poderes sobre rios, riachos, cachoeiras… Era linda e sua beleza atraía muitos interessados em casar-se com ela. Mas foi o filho do Sol que conquistou seu coração. O casamento foi muito bonito e alegre, foram sete dias e sete noites de festividades.
+Quando a festa acabou, os noivos partiram para a casa do Sol. Chegando lá, a princesa das águas disse ao marido que pretendia passar com ele o ano inteiro, exceto três meses que havia de passar com sua mãe. Assim, todos os anos, a princesa das águas passava uma temporada com sua mãe debaixo do mar, num rico palácio de ouro e de brilhantes.
+O tempo correu e a princesa teve um filho. O principezinho ficava com o pai, quando a moça ia visitar sua mãe. Certo ano, porém, a princesa foi para a sua temporada com a mãe, como sempre, mas não a encontrou no palácio. A princesa perguntou sobre sua mãe aos peixes dos rios, às areias do mar, às conchas das praias, mas ninguém lhe respondia. Muito mais do que meses e anos se passaram nessa busca sem sucesso. Cansada e muito triste, ela retornou ao reino do Sol.
+Chegando lá, uma surpresa: o rei Sol havia se casado com outra e seu filho, já crescido, estava muito maltratado e triste. A princesa das águas, com muita raiva, pegou seu filho e se mudou para o fundo do mar. Deu ordem para que a maré subisse, e tudo ficou coberto pelas águas. No fundo do mar, a princesa e seu filho ficaram para sempre. Dizem que quem se atreve a olhar fixamente para a água do mar, vê a princesa, é encantado, cai na água e some para sempre.
+Disponível em: &lt;http://chc.org.br/artigo/a-princesa-da-agua/&gt;. Acesso em: 31 jan. 2020
+É exemplo de oração com sujeito desinencial:</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>"A princesa das águas, com muita raiva, pegou seu filho e se mudou para o fundo do mar."</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>“Muito mais do que meses e anos se passaram nessa busca sem sucesso.”</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>“Deu ordem para que a maré subisse, e tudo ficou coberto pelas águas.”</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>“Quando a festa acabou, os noivos partiram para a casa do Sol.”</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>“Cansada e muito triste, ela retornou ao reino do Sol.”</t>
+        </is>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H639" t="inlineStr">
+        <is>
+          <t>Uma oração com sujeito desinencial é aquela em que o sujeito não está explicitamente mencionado na frase, mas pode ser identificado pela desinência verbal, ou seja, pela terminação do verbo. Na sentença “Deu ordem para que a maré subisse, e tudo ficou coberto pelas águas.”, o verbo "deu" não tem um sujeito explícito na oração. No entanto, pelo contexto e pela conjugação do verbo, entende-se que o sujeito é "ele" ou "ela", que está implícito. Esse tipo de sujeito é chamado de desinencial ou elíptico porque não aparece na frase, mas pode ser inferido pelo leitor ou ouvinte. As demais alternativas apresentam sujeitos explícitos, ou seja, claramente mencionados na oração, o que não caracteriza um sujeito desinencial.</t>
+        </is>
+      </c>
+      <c r="I639" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J639" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K639" t="inlineStr">
+        <is>
+          <t>8a_ph03_por_08.png</t>
+        </is>
+      </c>
+      <c r="L639" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>Considere as sentenças a seguir:
+I. Rafael sempre foi um ótimo aluno.
+II. O caderno e os livros de Bruno ficaram em sua casa.
+III. Chegamos atrasadas para a aula de Literatura.
+IV. Choverá muito amanhã.
+V. Não avisaram qual será a sala de Thiago.
+Os sujeitos são classificados como:</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>I. Composto; II. Composto; III. Simples; IV. Inexistente; V. Oculto.</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>I. Composto; II. Simples; III. Oculto; IV. Indeterminado; V. Inexistente.</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>I. Simples; II. Composto; III. Oculto; IV. Inexistente; V. Indeterminado.</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>I. Simples; II. Composto; III. Inexistente; IV. Simples; V. Indeterminado.</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>I. Composto; II. Simples; III. Inexistente; IV. Indeterminado; V. Inexistente.</t>
+        </is>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H640" t="inlineStr">
+        <is>
+          <t>Na sentença I, "Rafael sempre foi um ótimo aluno", o sujeito é "Rafael", que é um sujeito simples por se tratar de um único núcleo.
+Na sentença II, "O caderno e os livros de Bruno ficaram em sua casa", o sujeito é "O caderno e os livros de Bruno", que é um sujeito composto por possuir dois núcleos ("caderno" e "livros").
+Na sentença III, "Chegamos atrasadas para a aula de Literatura", o sujeito é oculto, pois está implícito na forma verbal "chegamos", indicando "nós".
+Na sentença IV, "Choverá muito amanhã", o sujeito é inexistente, pois o verbo "chover" é impessoal e não se refere a nenhum sujeito.
+Na sentença V, "Não avisaram qual será a sala de Thiago", o sujeito é indeterminado, pois a forma verbal "avisaram" não especifica quem realizou a ação, podendo ser qualquer pessoa ou grupo.</t>
+        </is>
+      </c>
+      <c r="I640" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J640" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K640" t="inlineStr"/>
+      <c r="L640" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>É DESSA FLORESTA QUE SAI O CHAPEUZINHO VERMELHO,
+JOÃO E MARIA, OS IRMÃOS KARAMAZOV,
+A DAMA DAS CAMÉLIAS E OS TRÊS MOSQUETEIROS.
+Revista Bolsa, 1986. In: CARRASCOZA, J. A. A evolução do texto
+publicitário: a associação de palavras como elemento de sedução
+na publicidade. São Paulo: Futura, 1999 (adaptado).
+Sobre a sentença “É dessa floresta que sai o Chapeuzinho Vermelho, João e Maria, os Irmãos Karamazov, a Dama das CamélIas e Os Três Mosqueteiros.”, é possível afirmar que se trata de</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>um período composto.</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>uma frase não-verbal.</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>um período simples.</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>uma frase nominal.</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>uma oração sem sujeito.</t>
+        </is>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H641" t="inlineStr">
+        <is>
+          <t>"É dessa floresta que sai o Chapeuzinho Vermelho, João e Maria, os Irmãos Karamazov, a Dama das Camélias e Os Três Mosqueteiros." contém dois verbos: "é" e "sai". A presença desses dois verbos indica que a sentença é composta por duas orações: "É dessa floresta" e "que sai o Chapeuzinho Vermelho, João e Maria, os Irmãos Karamazov, a Dama das Camélias e Os Três Mosqueteiros." Quando uma sentença possui mais de uma oração, ela é classificada como um período composto.</t>
+        </is>
+      </c>
+      <c r="I641" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J641" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K641" t="inlineStr">
+        <is>
+          <t>8a_ph03_por_10.jpg</t>
+        </is>
+      </c>
+      <c r="L641" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>Um grupo de amigos resolveu comprar ingressos para ir ao show de sua banda favorita. Eles compraram 4 ingressos e também pagaram uma taxa de serviço no valor de R$ 10,00.
+Qual das expressões a seguir calcula corretamente o valor gasto pelo grupo de amigos?</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>[img:8a_ph03_mat_01_a.png]</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>[img:8a_ph03_mat_01_b.png]</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>[img:8a_ph03_mat_01_c.png]</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>[img:8a_ph03_mat_01_d.png]</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>[img:8a_ph03_mat_01_e.png]</t>
+        </is>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H642" t="inlineStr">
+        <is>
+          <t>A expressão correta é  pois eles compraram 4 ingressos a x reais cada e pagaram uma taxa de 10 reais.</t>
+        </is>
+      </c>
+      <c r="I642" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J642" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K642" t="inlineStr"/>
+      <c r="L642" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>Um grupo de amigos está organizando uma viagem de carro e calculou os custos totais da viagem, incluindo combustível, pedágios e alimentação. Eles expressaram o custo total da viagem na seguinte forma:
+onde y representa o custo por quilômetro rodado. Eles desejam simplificar essa expressão para entender melhor os custos totais da viagem.
+Qual é a expressão simplificada que o grupo deve usar?</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>[img:8a_ph03_mat_02_a.png]</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>[img:8a_ph03_mat_02_b.png]</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>[img:8a_ph03_mat_02_c.png]</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>[img:8a_ph03_mat_02_d.png]</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>[img:8a_ph03_mat_02_e.png]</t>
+        </is>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H643" t="inlineStr">
+        <is>
+          <t>Simplificando a expressão, tem-se:</t>
+        </is>
+      </c>
+      <c r="I643" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J643" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>8a_ph03_mat_02.png</t>
+        </is>
+      </c>
+      <c r="L643" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>Um garoto está ajudando seu pai a planejar a reforma do quintal da casa. Ele precisa calcular a área do terreno que será coberto por grama. O terreno tem o formato de um retângulo, medindo 12 metros de comprimento por 4 metros de largura. No entanto, no centro desse terreno, há uma piscina retangular que mede 4 metros de comprimento por 3 metros de largura. Pedro precisa saber a área que será coberta por grama, excluindo a área da piscina.
+Qual é a área do terreno que será coberta por grama?</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>[img:8a_ph03_mat_03_a.png]</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>[img:8a_ph03_mat_03_b.png]</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>[img:8a_ph03_mat_03_c.png]</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>[img:8a_ph03_mat_03_d.png]</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>[img:8a_ph03_mat_03_e.png]</t>
+        </is>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H644" t="inlineStr">
+        <is>
+          <t>A área total do terreno é calculada multiplicando o comprimento pela altura: 
+Logo, a área coberta por grama será:</t>
+        </is>
+      </c>
+      <c r="I644" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J644" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K644" t="inlineStr"/>
+      <c r="L644" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>Um grupo de amigos foi ao supermercado com R$ 150,00 e decidiu comprar produtos para o churrasco do fim de semana. Eles compraram dois pacotes de carne, cada um custando   reais, onde x é o peso em quilos, e um pacote de carvão que custa  reais, onde x também é o peso do carvão em Kg.
+Sabendo que o grupo gastou R$ 95,00 no total, qual foi o valor de x, que representa o peso dos produtos em kg?</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>8,75 kg</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>9,38 kg</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>15,63 kg</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>16,00 kg</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>27,00 kg</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H645" t="inlineStr">
+        <is>
+          <t>O custo total dos dois pacotes de carne e do pacote de carvão é dado por:
+Simplificando a expressão, tem-se que:</t>
+        </is>
+      </c>
+      <c r="I645" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J645" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>8a_ph03_mat_04.png</t>
+        </is>
+      </c>
+      <c r="L645" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>Um funcionário está construindo uma caixa em forma de bloco retangular para armazenar ferramentas. A caixa tem comprimento de  metros, largura de  metros e altura de x metros.
+Qual é a expressão algébrica que representa o volume da caixa?</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>[img:8a_ph03_mat_05_a.png]</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>[img:8a_ph03_mat_05_b.png]</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>[img:8a_ph03_mat_05_c.png]</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>[img:8a_ph03_mat_05_d.png]</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>[img:8a_ph03_mat_05_e.png]</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H646" t="inlineStr">
+        <is>
+          <t>volume de um bloco retangular é dado por  Portanto, a expressão algébrica para o volume da caixa é:
+Primeiro, multiplicamos (2x + 1) por (x - 2):
+Em seguida, multiplicamos o resultado por x:</t>
+        </is>
+      </c>
+      <c r="I646" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J646" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>8a_ph03_mat_05.png</t>
+        </is>
+      </c>
+      <c r="L646" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>Gabriel deseja comprar ladrilhos para sua casa, que está em construção. Como ele ainda não decidiu o tamanho da sua sala, mas sabe que ela terá o formato de um quadrado, ele pode então considerar que o lado medirá x metros.
+Se o preço dos ladrilhos é de 625 reais por metro quadrado, qual expressão algébrica representa o valor a ser pago, em reais, para ladrilhar sua sala?</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>25x</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>125x</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>125x²</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>625x</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>625x²</t>
+        </is>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H647" t="inlineStr">
+        <is>
+          <t>A área de sua sala será de x.x = x² metros quadrados. Como cada metro quadrado de ladrilho custa 625 reais, ele pagará 625x² reais.</t>
+        </is>
+      </c>
+      <c r="I647" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J647" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K647" t="inlineStr"/>
+      <c r="L647" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>Uma caixa d’água de 6 000 L está com a metade de sua capacidade preenchida. Uma bomba abastece a caixa d’água com 10 L de água por minuto.
+Qual é a expressão algébrica que representa a quantidade de água na caixa, considerando que passaram m minutos depois que a bomba foi ligada?</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>3 000 + 10m</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>3 000 + 100m</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>3 000 + 3 000m</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>6 000 + 10m</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>6 000 + 100m</t>
+        </is>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H648" t="inlineStr">
+        <is>
+          <t>Como a caixa já está cheia pela metade, há 3 000 L ocupados. Após m minutos, foram acrescentados 10m L na caixa.
+Logo, a expressão é 3 000 + 10m.</t>
+        </is>
+      </c>
+      <c r="I648" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J648" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K648" t="inlineStr"/>
+      <c r="L648" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>O pai de três filhas, Ana, Bianca e Carolina, deseja presenteá-las com chocolate pelo seu desempenho em matemática. Cada uma das filhas ganha de chocolate, em gramas, dez vezes a nota que tirar em matemática.
+Chamando a nota de Ana de A, a nota de Bianca de B e a nota de Carolina de C, qual expressão algébrica representa a quantidade de chocolate que o pai terá que comprar para presentear as filhas?</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>A + B + C</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>2A + 2B + 2C</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>10A + B + C</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>10A + B + 10C</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>10A + 10B + 10C</t>
+        </is>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H649" t="inlineStr">
+        <is>
+          <t>Ana receberá 10A gramas de chocolate, Bianca receberá 10B gramas de chocolate e Carolina receberá 10C gramas de chocolate.
+Portanto, o pai terá que comprar 10A + 10B + 10C gramas de chocolate.</t>
+        </is>
+      </c>
+      <c r="I649" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J649" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K649" t="inlineStr"/>
+      <c r="L649" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>João precisa pagar uma conta de 100 reais. Como ele sabe que não conseguirá pagar no dia, será cobrado uma multa por pagá-la atrasada. Ao ler o boleto da conta com mais detalhe, descobriu que a multa é de 2 reais para cada dia de atraso.
+Qual expressão algébrica representa o valor pago por João, considerando que houve um atraso de x dias?</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>100x</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>100 + x</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>100 + 2x</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>100 + 100x</t>
+        </is>
+      </c>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H650" t="inlineStr">
+        <is>
+          <t>João deve pagar um valor fixo de 100 reais mais x vezes a multa diária: 2x. Logo, a expressão é: 100 + 2x.</t>
+        </is>
+      </c>
+      <c r="I650" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J650" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K650" t="inlineStr"/>
+      <c r="L650" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>Em uma cidade, foi disponibilizado um sistema de aluguel de bicicletas que funciona da seguinte forma: paga-se uma mensalidade (valor fixo por mês) de R$ 25,00 e para cada hora andada com a bicicleta, paga-se R$ 2,50.
+Chamando de T o total pago no mês e h a quantidade de horas andadas de bicicleta, qual a expressão algébrica que representa a situação descrita?</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>T = 27,50</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>T = 25 + 2,50h</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>h = 25 + 2,50T</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>T = 25 + 25h</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>h = 25 + 25T</t>
+        </is>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H651" t="inlineStr">
+        <is>
+          <t>Há um valor fixo a ser pago: R$ 25,00. Além disso, será pago h vezes R$ 2,50 por hora de uso da bicicleta: 2,50h.
+Logo, a expressão será: T = 25 + 2,50h.</t>
+        </is>
+      </c>
+      <c r="I651" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J651" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K651" t="inlineStr"/>
+      <c r="L651" t="inlineStr">
         <is>
           <t>8ano</t>
         </is>

--- a/questoes.xlsx
+++ b/questoes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L651"/>
+  <dimension ref="A1:L701"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32907,7 +32907,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K602" t="inlineStr"/>
       <c r="L602" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -32967,7 +32966,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K603" t="inlineStr"/>
       <c r="L603" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -33027,7 +33025,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K604" t="inlineStr"/>
       <c r="L604" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -33087,7 +33084,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K605" t="inlineStr"/>
       <c r="L605" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -33147,7 +33143,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K606" t="inlineStr"/>
       <c r="L606" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -33206,7 +33201,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K607" t="inlineStr"/>
       <c r="L607" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -33266,7 +33260,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K608" t="inlineStr"/>
       <c r="L608" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -33328,7 +33321,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K609" t="inlineStr"/>
       <c r="L609" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -33387,7 +33379,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K610" t="inlineStr"/>
       <c r="L610" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -33446,7 +33437,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K611" t="inlineStr"/>
       <c r="L611" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -33570,7 +33560,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K613" t="inlineStr"/>
       <c r="L613" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -33632,7 +33621,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K614" t="inlineStr"/>
       <c r="L614" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -33756,7 +33744,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K616" t="inlineStr"/>
       <c r="L616" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -33821,7 +33808,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K617" t="inlineStr"/>
       <c r="L617" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -33883,7 +33869,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K618" t="inlineStr"/>
       <c r="L618" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -33947,7 +33932,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K619" t="inlineStr"/>
       <c r="L619" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -34005,7 +33989,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K620" t="inlineStr"/>
       <c r="L620" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -34072,7 +34055,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K621" t="inlineStr"/>
       <c r="L621" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -34132,7 +34114,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K622" t="inlineStr"/>
       <c r="L622" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -34192,7 +34173,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K623" t="inlineStr"/>
       <c r="L623" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -34253,7 +34233,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K624" t="inlineStr"/>
       <c r="L624" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -34313,7 +34292,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K625" t="inlineStr"/>
       <c r="L625" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -34373,7 +34351,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K626" t="inlineStr"/>
       <c r="L626" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -34433,7 +34410,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K627" t="inlineStr"/>
       <c r="L627" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -34495,7 +34471,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K628" t="inlineStr"/>
       <c r="L628" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -34555,7 +34530,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K629" t="inlineStr"/>
       <c r="L629" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -34615,7 +34589,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K630" t="inlineStr"/>
       <c r="L630" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -34740,7 +34713,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K632" t="inlineStr"/>
       <c r="L632" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -34802,7 +34774,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K633" t="inlineStr"/>
       <c r="L633" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -34867,7 +34838,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K634" t="inlineStr"/>
       <c r="L634" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -34932,7 +34902,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K635" t="inlineStr"/>
       <c r="L635" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -34997,7 +34966,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K636" t="inlineStr"/>
       <c r="L636" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -35268,7 +35236,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K640" t="inlineStr"/>
       <c r="L640" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -35395,7 +35362,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K642" t="inlineStr"/>
       <c r="L642" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -35519,7 +35485,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K644" t="inlineStr"/>
       <c r="L644" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -35707,7 +35672,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K647" t="inlineStr"/>
       <c r="L647" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -35767,7 +35731,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K648" t="inlineStr"/>
       <c r="L648" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -35827,7 +35790,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K649" t="inlineStr"/>
       <c r="L649" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -35886,7 +35848,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K650" t="inlineStr"/>
       <c r="L650" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -35946,8 +35907,3118 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K651" t="inlineStr"/>
       <c r="L651" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>A previsão do tempo é uma atividade que utiliza dados meteorológicos coletados de várias fontes, como satélites, estações meteorológicas e balões atmosféricos. Esses dados são analisados por meteorologistas que utilizam modelos matemáticos para prever as condições atmosféricas futuras.
+Qual das seguintes variáveis é fundamental para a previsão do tempo?</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>Densidade populacional.</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>Temperatura do solo.</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>Pressão atmosférica.</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>Nível de poluição.</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>Velocidade do som.</t>
+        </is>
+      </c>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H652" t="inlineStr">
+        <is>
+          <t>A pressão atmosférica é uma variável fundamental na previsão do tempo. Ela influencia a formação de sistemas de alta e baixa pressão, que são determinantes para o desenvolvimento de fenômenos meteorológicos como frentes frias, tempestades e ventos. Meteorologistas monitoram constantemente a pressão atmosférica para prever mudanças nas condições climáticas.</t>
+        </is>
+      </c>
+      <c r="I652" t="inlineStr">
+        <is>
+          <t>PH04</t>
+        </is>
+      </c>
+      <c r="J652" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K652" t="inlineStr"/>
+      <c r="L652" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>A pressão atmosférica é a força exercida pelo peso do ar sobre a superfície da Terra. Ela varia com a altitude e a temperatura e é uma variável crucial na previsão de frentes frias e quentes.
+Qual evento meteorológico é diretamente associado a mudanças na pressão atmosférica?</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>Formação de neblina.</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>Ocorrência de terremotos.</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>Passagem de frentes frias.</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>Intensidade da radiação solar.</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>Movimento das nuvens.</t>
+        </is>
+      </c>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H653" t="inlineStr">
+        <is>
+          <t>A passagem de frentes frias está diretamente associada a mudanças na pressão atmosférica. Quando uma frente fria se aproxima, a pressão atmosférica geralmente cai, e quando ela passa, a pressão tende a subir. Esse fenômeno é essencial para a previsão do tempo, pois frentes frias podem trazer mudanças significativas nas condições meteorológicas, como queda de temperatura e precipitação.</t>
+        </is>
+      </c>
+      <c r="I653" t="inlineStr">
+        <is>
+          <t>PH04</t>
+        </is>
+      </c>
+      <c r="J653" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K653" t="inlineStr"/>
+      <c r="L653" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>A umidade relativa do ar é uma medida da quantidade de vapor de água presente na atmosfera em relação à quantidade máxima que o ar pode conter a uma determinada temperatura. Ela é uma variável importante na previsão de chuva e neblina.
+Qual fenômeno meteorológico é diretamente influenciado pela umidade relativa do ar?</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>Formação de geada.</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>Ocorrência de relâmpagos.</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>Intensidade dos ventos.</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>Precipitação de chuva.</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>Movimento das marés.</t>
+        </is>
+      </c>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H654" t="inlineStr">
+        <is>
+          <t>A umidade relativa do ar é crucial para a formação de chuva. Quando o ar está saturado de vapor de água (umidade relativa de 100%), a água se condensa e precipita na forma de chuva. Portanto, a umidade relativa do ar é um indicador importante para prever a ocorrência de precipitação.</t>
+        </is>
+      </c>
+      <c r="I654" t="inlineStr">
+        <is>
+          <t>PH04</t>
+        </is>
+      </c>
+      <c r="J654" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K654" t="inlineStr"/>
+      <c r="L654" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>A precipitação é a quantidade de água que cai sobre a superfície da Terra na forma de chuva, neve, granizo ou orvalho. Ela é uma variável crucial na previsão de enchentes e secas.
+Qual instrumento é utilizado para medir a precipitação?</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>Higrômetro.</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>Barômetro.</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>Anemômetro.</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>Pluviômetro.</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>Termômetro.</t>
+        </is>
+      </c>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H655" t="inlineStr">
+        <is>
+          <t>O pluviômetro é um instrumento utilizado para medir a quantidade de precipitação que cai sobre uma determinada área. Ele coleta e mede a água da chuva, neve, granizo ou orvalho, sendo crucial para monitorar e prever enchentes e secas.</t>
+        </is>
+      </c>
+      <c r="I655" t="inlineStr">
+        <is>
+          <t>PH04</t>
+        </is>
+      </c>
+      <c r="J655" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K655" t="inlineStr"/>
+      <c r="L655" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>Os ventos de oeste, transportam massas de ar de regiões oceânicas para os continentes, influenciando o clima das zonas temperadas.
+Qual efeito climático é causado pelos ventos de oeste em regiões costeiras?</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>Redução da umidade.</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>Moderação das temperaturas.</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>Intensificação da radiação solar.</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>Diminuição da precipitação.</t>
+        </is>
+      </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>Aumento da aridez.</t>
+        </is>
+      </c>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H656" t="inlineStr">
+        <is>
+          <t>Os ventos de oeste transportam ar marítimo, que tem uma temperatura mais moderada em comparação com o ar continental. Isso tende a suavizar as temperaturas extremas, tanto no verão quanto no inverno, nas regiões costeiras, resultando em um clima mais ameno.</t>
+        </is>
+      </c>
+      <c r="I656" t="inlineStr">
+        <is>
+          <t>PH04</t>
+        </is>
+      </c>
+      <c r="J656" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K656" t="inlineStr"/>
+      <c r="L656" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>No Brasil, as massas de ar influenciam significativamente o clima e a previsão do tempo. Uma das massas mais importantes é a Massa Polar Atlântica, que frequentemente provoca quedas de temperatura no inverno, especialmente nas regiões Sul e Sudeste. Dependendo da interação entre diferentes massas de ar, podem ocorrer frentes frias ou ondas de calor.
+Com base no impacto das massas de ar no Brasil, qual das seguintes afirmações sobre a Massa Polar Atlântica é correta?</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>Provoca aumento nas temperaturas durante o inverno nas regiões Norte e Nordeste.</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>Atua principalmente no verão, aumentando a umidade relativa do ar no Sul do Brasil.</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>Causa queda de temperatura nas regiões Sul e Sudeste, especialmente durante o inverno.</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>É responsável por longos períodos de seca na região Amazônica.</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>Gera aquecimento intenso na região do Pantanal durante o inverno.</t>
+        </is>
+      </c>
+      <c r="G657" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H657" t="inlineStr">
+        <is>
+          <t>A Massa Polar Atlântica provoca quedas de temperatura, principalmente no Sul e Sudeste.</t>
+        </is>
+      </c>
+      <c r="I657" t="inlineStr">
+        <is>
+          <t>PH04</t>
+        </is>
+      </c>
+      <c r="J657" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K657" t="inlineStr"/>
+      <c r="L657" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>Os mapas meteorológicos são importantes ferramentas utilizadas para prever o tempo. Neles, podem ser identificadas áreas de alta e baixa pressão, frentes frias, e zonas de convergência. Essas informações auxiliam meteorologistas a prever condições climáticas como tempestades, ondas de calor e chuvas intensas.
+Em um mapa meteorológico, uma área com isóbaras muito próximas indica:</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>Baixa variação de temperatura entre o dia e a noite.</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>Uma região com clima estável e sem vento.</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>Alta velocidade dos ventos devido à grande diferença de pressão.</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>A presença de uma frente quente que se desloca lentamente.</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>Um sistema de alta pressão trazendo chuvas fortes.</t>
+        </is>
+      </c>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H658" t="inlineStr">
+        <is>
+          <t>Isóbaras próximas indicam um gradiente de pressão elevado, gerando ventos fortes.</t>
+        </is>
+      </c>
+      <c r="I658" t="inlineStr">
+        <is>
+          <t>PH04</t>
+        </is>
+      </c>
+      <c r="J658" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K658" t="inlineStr"/>
+      <c r="L658" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>El Niño e La Niña são fenômenos climáticos que alteram o padrão de circulação atmosférica e afetam o clima global. O El Niño está associado ao aquecimento anômalo das águas do Oceano Pacífico, enquanto o La Niña envolve um resfriamento anômalo. No Brasil, o El Niño tende a trazer secas para a região Amazônica e chuvas intensas para o Sul, enquanto o La Niña pode intensificar a seca no Nordeste e aumentar as chuvas no Norte.
+Considerando os efeitos do El Niño e do La Niña no Brasil, qual das seguintes afirmações é correta?</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>O El Niño provoca chuvas intensas e contínuas na Amazônia..</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>Durante o La Niña, há um aumento significativo das chuvas no Nordeste brasileiro.</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>O El Niño pode intensificar a seca na Amazônia e trazer mais chuvas ao Sul do Brasil.</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>O La Niña reduz as chuvas no Sul e aumenta a temperatura no Norte.Ambos os fenômenos não têm influência significativa no Brasil.</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>Ambos os fenômenos não têm influência significativa no Brasil.</t>
+        </is>
+      </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H659" t="inlineStr">
+        <is>
+          <t>O El Niño causa um aquecimento anômalo nas águas do Pacífico, que interfere no regime de chuvas do Brasil. Ele reduz a umidade na Amazônia, resultando em secas, e aumenta a ocorrência de chuvas intensas no Sul do país, devido ao fortalecimento das frentes frias e maior convergência de umidade nessa região.</t>
+        </is>
+      </c>
+      <c r="I659" t="inlineStr">
+        <is>
+          <t>PH04</t>
+        </is>
+      </c>
+      <c r="J659" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K659" t="inlineStr"/>
+      <c r="L659" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>A ideia surgiu quando o físico Henrikki Mertaniemi observava o comportamento do orvalho sobre as folhas do jardim de sua mãe. O pesquisador percebeu que as gotículas de água nem sempre se juntavam formando uma maior ao colidir entre si. Por vezes elas se chocavam e se repeliam como bolas de bilhar.
+Disponível em: https://cienciahoje.periodicos.capes.gov.br/storage/acervo/ch/ch_298.pdf#page=71. Acesso em: 06 dez 2024.
+Através da observação de um fenômeno, o físico idealizou a utilização de gotas d’água como bits em operações simples de informática, o fenômeno citado consiste na</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>formação de cristais de gelo a partir da sublimação direta do vapor d'água.</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>condensação do vapor d'água em superfícies frias, formando gotículas que podem se unir ou se repelir.</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>evaporação rápida de água líquida em superfícies quentes, gerando vapor que se dispersa no ar.</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>solidificação da água líquida em superfícies frias, formando uma camada de gelo uniforme.</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>absorção de umidade do ar por superfícies porosas, resultando na formação de uma película de água.</t>
+        </is>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H660" t="inlineStr">
+        <is>
+          <t>A condensação do vapor d'água em superfícies frias resulta na formação de gotículas. Essas gotículas podem se unir ou se repelir, conforme observado pelo físico Henrikki Mertaniemi. Este fenômeno é fundamental para a ideia de usar gotas d'água como bits em operações de informática.</t>
+        </is>
+      </c>
+      <c r="I660" t="inlineStr">
+        <is>
+          <t>PH04</t>
+        </is>
+      </c>
+      <c r="J660" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K660" t="inlineStr"/>
+      <c r="L660" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>Na Índia, no verão, há mais radiação solar sobre o continente do que sobre o oceano Índico Sul. O ar sobre o continente aquece-se mais do que o ar sobre o oceano e, mais leve, tende a subir. Desse modo, o ar relativamente mais frio e pesado sobre o oceano invade o continente. Quando o vento sopra do oceano para o continente, traz bastante umidade, que se condensa e precipita na forma de chuva. Durante o inverno, o oceano Índico Sul recebe mais radiação do que o continente e forma-se uma circulação oposta.
+Disponível em: https://cienciahoje.periodicos.capes.gov.br/storage/acervo/ch/ch_259.pdf#page=06. Acesso em: 06 dez 2024.
+O fenômeno de circulação oposta citado resulta na</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>formação de nuvens densas sobre o continente, levando a chuvas intensas.</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>elevação da temperatura do ar sobre o oceano, causando tempestades marítimas.</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>inibição da formação de nuvens sobre o continente, resultando em períodos secos.</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>intensificação dos ventos sobre o continente, provocando tempestades de areia.</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>diminuição da umidade sobre o oceano, gerando nevoeiros densos.</t>
+        </is>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H661" t="inlineStr">
+        <is>
+          <t>Durante o inverno, o ar sobre o continente é relativamente mais frio e pesado, enquanto o ar sobre o oceano é mais quente. Isso faz com que o vento sopre do continente para o oceano, inibindo a formação de nuvens sobre o continente e resultando em períodos secos.</t>
+        </is>
+      </c>
+      <c r="I661" t="inlineStr">
+        <is>
+          <t>PH04</t>
+        </is>
+      </c>
+      <c r="J661" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K661" t="inlineStr"/>
+      <c r="L661" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>“A floresta boreal do Canadá armazena carbono, purifica o ar e a água, regula o clima. Como uma grande parte da zona boreal do planeta (28% ou 552 milhões de hectares) fica no Canadá, a floresta boreal deste país afeta a saúde do meio ambiente em todo o mundo. A zona boreal é crucial para a economia devido à disponibilidade de produtos madeireiros e não-madeireiros, recursos minerais e energéticos e potencial hidrelétrico dos rios regionais; fornece alimentos e matérias-primas renováveis ​​para os canadenses. As florestas boreais são cultural e economicamente significativas para os povos aborígenes do Canadá”.  É a declaração do governo canadense no website oficial.
+Disponível em: https://dralumadorea.com.br/zelar-por-uma-floresta-e-possivel-prova-o-canada/. Acesso em 28 de out de 2024.
+A floresta boreal do Canadá desempenha um papel fundamental no equilíbrio ambiental e na economia do país. A floresta boreal do Canadá:</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>é a principal fonte de petróleo do país, sendo crucial para a economia canadense.</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>não possui relevância cultural para os povos aborígenes, sendo utilizada para fins econômicos</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>é utilizada na produção de celulose e papel, além de armazenar carbono e purificar o ar e a água</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>é composta principalmente por florestas tropicais, que são fonte de madeira para a produção de papel</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>não possui impactos significativos no clima global, uma vez que são relevantes apenas para a economia local</t>
+        </is>
+      </c>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H662" t="inlineStr">
+        <is>
+          <t>A floresta boreal do Canadá é crucial para a produção de celulose e papel, além de desempenhar funções ambientais importantes como o armazenamento de carbono e a purificação do ar e da água.</t>
+        </is>
+      </c>
+      <c r="I662" t="inlineStr">
+        <is>
+          <t>PH04</t>
+        </is>
+      </c>
+      <c r="J662" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K662" t="inlineStr"/>
+      <c r="L662" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>Um complexo agroindustrial (CAI) consiste de um conjunto de processos agrícolas, de processamentos industriais e comerciais, sequenciais e interdependentes, aplicados a uma determinada matéria-prima agrícola base, por exemplo, centeio, trigo, milho ou leite, que resultam em diferentes produtos destinados ao consumidor.
+Disponível em: http://www.cnpt.embrapa.br/biblio/do/p_do142_6.htm#:~:text=Um%20complexo%20agroindustrial%20(CAI)%20consiste,diferentes%20produtos%20destinados%20ao%20consumidor. Acesso em 28 de out de 2024.
+A terceirização e a financeirização são práticas cada vez mais comuns nas atividades agroindustriais da América Anglo-Saxônica. Sobre essas práticas:</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>A terceirização nas atividades agroindustriais da América Anglo-Saxônica tem como principal objetivo reduzir a dependência de tecnologia avançada.</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>A financeirização nas atividades agroindustriais da América Anglo-Saxônica implica a substituição de processos agrícolas tradicionais por investimentos em mercados financeiros</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>A terceirização permite que empresas agroindustriais da América Anglo-Saxônica se concentrem em suas competências principais, transferindo atividades secundárias para outras empresas especializadas</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>A financeirização nas atividades agroindustriais da América Anglo-Saxônica reduz a interdependência entre os processos agrícolas, industriais e comerciais</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>A terceirização nas atividades agroindustriais da América Anglo-Saxônica elimina a necessidade de integração entre os diferentes processos do complexo agroindustrial.</t>
+        </is>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H663" t="inlineStr">
+        <is>
+          <t>A terceirização permite que empresas agroindustriais se concentrem em suas competências principais, transferindo atividades secundárias para outras empresas especializadas, o que pode aumentar a eficiência e reduzir custos.</t>
+        </is>
+      </c>
+      <c r="I663" t="inlineStr">
+        <is>
+          <t>PH04</t>
+        </is>
+      </c>
+      <c r="J663" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K663" t="inlineStr"/>
+      <c r="L663" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>Agricultores nos Estados Unidos estão adotando novas tecnologias para aumentar a produção de suas lavouras usando menos produtos químicos (fertilizantes, herbicidas e pesticidas). Sensores e imagens aéreas mapeiam áreas da cultura que precisam de mais nutrientes, permitindo uma aplicação mais criteriosa de fertilizantes, ao passo que pulverizadores e tratores equipados com câmeras e softwares de inteligência artificial (IA) identificam e eliminam espécies invasoras por meio do uso direcionado de herbicidas.
+Disponível em: https://www.ipea.gov.br/cts/pt/central-de-conteudo/noticias/noticias/350-novas-tecnologias-permitem-que-agricultores-nos-estados-unidos-produzam-mais-comida-usando-menos-produtos-quimicos. Acesso em 28 de out de 2024.
+O avanço da tecnologia agrícola nos Estados Unidos tem contribuído para o aumento da produção, mas também tem gerado consequências na estrutura fundiária do país. Sobre esse contexto:</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>A adoção de tecnologias avançadas na agricultura dos Estados Unidos tem democratizado o acesso à terra, permitindo que pequenos agricultores compitam em igualdade de condições com grandes produtores.</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>O uso de sensores, imagens aéreas e inteligência artificial na agricultura dos Estados Unidos tem reduzido a necessidade de mão de obra, resultando em uma maior distribuição de terras entre pequenos agricultores.</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>A tecnologia agrícola nos Estados Unidos tem eliminado a necessidade de fertilizantes e herbicidas, tornando a produção mais sustentável e acessível para pequenos agricultores.</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>A implementação de tecnologias agrícolas avançadas nos Estados Unidos tem levado a uma maior concentração fundiária, favorecendo grandes produtores que possuem recursos para investir.</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>O avanço tecnológico na agricultura dos Estados Unidos tem promovido uma distribuição equitativa de terras, reduzindo a concentração fundiária e aumentando a competitividade entre pequenos e grandes produtores.</t>
+        </is>
+      </c>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H664" t="inlineStr">
+        <is>
+          <t>A implementação de tecnologias agrícolas avançadas tende a favorecer grandes produtores que possuem recursos para investir em equipamentos e inovações, levando a uma maior concentração fundiária.</t>
+        </is>
+      </c>
+      <c r="I664" t="inlineStr">
+        <is>
+          <t>PH04</t>
+        </is>
+      </c>
+      <c r="J664" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K664" t="inlineStr"/>
+      <c r="L664" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>A agricultura dos Estados Unidos é uma das mais modernas e produtivas do mundo tanto em área quanto em volume de produção. Grande produtor de grãos, carne e leite, a agricultura estadunidense se organiza (...) conforme as particularidades históricas do povoamento, as condições climáticas e os tipos de solos.
+Disponível em: https://digital.agrishow.com.br/tendencias/agricultura-pelo-mundo-saiba-como-funciona-agricultura-dos-eua. Acesso em 28 de out de 2024.
+A organização da agricultura nos Estados Unidos leva em consideração fatores históricos, climáticos e de solo. Essa organização é conhecida por:</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>Pequenas propriedades familiares espalhadas pelo país.</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>Grandes fazendas de monocultura em áreas isoladas.</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>Comunidades agrícolas autossustentáveis em regiões urbanas.</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>Faixas, zonas ou cinturões agrícolas denominados belts.</t>
+        </is>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>Plantios diversificados em áreas de preservação ambiental.</t>
+        </is>
+      </c>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H665" t="inlineStr">
+        <is>
+          <t>A agricultura nos Estados Unidos é organizada em grandes áreas chamadas "belts" (cinturões), que são regiões específicas onde se concentra a produção de determinados tipos de culturas. Exemplos incluem o "Corn Belt" (Cinturão do Milho), que abrange estados como Iowa, Illinois e Indiana, e o "Wheat Belt" (Cinturão do Trigo), que cobre partes de estados como Kansas, Oklahoma e Texas. Essa organização permite uma produção altamente eficiente e especializada, adaptada às condições climáticas e de solo de cada região.</t>
+        </is>
+      </c>
+      <c r="I665" t="inlineStr">
+        <is>
+          <t>PH04</t>
+        </is>
+      </c>
+      <c r="J665" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K665" t="inlineStr"/>
+      <c r="L665" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>“Marcha para o oeste” é o nome que dado ao processo de expansão territorial que aconteceu nos Estados Unidos da América (EUA) ao longo do século XIX. Esse processo foi marcado tanto pela expansão territorial como pelo estabelecimento de colonos/habitantes nessas novas terras. Durante esse processo, os Estados Unidos deixaram de ser um território recluso ao das antigas treze colônias, alcançou as planícies centrais e estendeu-se até a costa oeste (costa do Oceano Pacífico).
+Disponível em: https://www.historiadomundo.com.br/idade-contemporanea/marcha-para-oeste.htm. Acesso em 28 de out de 2024.
+A "Marcha para o Oeste" nos Estados Unidos, ocorrida ao longo do século XIX, foi caracterizada por:</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>A criação de novas colônias europeias no território americano</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>A ocupação de terras, com a morte de milhares de indígenas</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>A expansão territorial sem conflitos e de forma pacífica através de compras</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>A construção de ferrovias que ligavam o leste ao oeste sem ocupação territorial</t>
+        </is>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>A formação de novas cidades exclusivamente nas áreas costeiras do país</t>
+        </is>
+      </c>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H666" t="inlineStr">
+        <is>
+          <t>A "Marcha para o Oeste" foi um processo de expansão territorial que ocorreu nos Estados Unidos ao longo do século XIX. Esse movimento foi marcado pela ocupação de novas terras e pelo estabelecimento de colonos nessas áreas, transformando os Estados Unidos de um território restrito às treze colônias originais em uma nação que se estendia até a costa do Oceano Pacífico. A ocupação de terras que anteriormente eram habitadas por povos indígenas resultou em conflitos violentos e na morte de milhares de indígenas, além de sua remoção forçada de suas terras ancestrais.</t>
+        </is>
+      </c>
+      <c r="I666" t="inlineStr">
+        <is>
+          <t>PH04</t>
+        </is>
+      </c>
+      <c r="J666" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K666" t="inlineStr"/>
+      <c r="L666" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>"faixas de terras caracterizadas por um determinado tipo de cultivo ou produção onde se usam técnicas modernas e se consideram as particularidades paisagísticas (naturais)."
+No contexto agrícola estadunidense, a definição acima diz respeito aos:</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>Cinturões agrícolas localizados no sul do país, especializados na produção de trigo.</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>Zonas de indústrias de tecnologia da informação, instaladas na costa sul.</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>Regiões produtoras de álcool derivado do milho, localizadas no norte do país.</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>Áreas de agricultura de subsistência, cujas técnicas de plantio foram herdadas de povos indígenas.</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>Belts, extensões de áreas rurais em que há especialização produtiva agrícola ou pastoril.</t>
+        </is>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H667" t="inlineStr">
+        <is>
+          <t>Os cinturões agrícolas estadunidenses, regionalmente conhecidos como farm belts ou apenas belts, são grandes extensões de áreas rurais em que há especialização produtiva agrícola ou pastoril. Nesse sistema, o território é organizado em faixas e zonas onde se destaca um tipo de cultivo. A espacialização dos gêneros agrícolas se deve ao histórico de ocupação dos terrenos rurais e ao aproveitamento das condições climáticas, de relevo e dos tipos de solo.</t>
+        </is>
+      </c>
+      <c r="I667" t="inlineStr">
+        <is>
+          <t>PH04</t>
+        </is>
+      </c>
+      <c r="J667" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K667" t="inlineStr"/>
+      <c r="L667" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>O setor agrícola estadunidense recebe grandes subsídios por parte do Estado. Além disso, uma outra prática governamental que visa valorizar os produtos nacionais é</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>o incentivo às fazendas com produtos diversificados.</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>a política de protecionismo econômico.</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>a separação rígida entre os setores da economia.</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>a proteção contra a terceirização.</t>
+        </is>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>a produção restrita ao mercado interno.</t>
+        </is>
+      </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H668" t="inlineStr">
+        <is>
+          <t>O governo estadunidense pratica o protecionismo econômico, ou seja, cobra impostos altos sobre as importações de produtos, além da imposição de barreiras alfandegárias. O objetivo dessas práticas é a valorização dos produtos nacionais no mercado.</t>
+        </is>
+      </c>
+      <c r="I668" t="inlineStr">
+        <is>
+          <t>PH04</t>
+        </is>
+      </c>
+      <c r="J668" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K668" t="inlineStr"/>
+      <c r="L668" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>Fonte: DIERCKE, Drei. Universalatlas. Brunsvique: Westermann Gruppe, 2017. p. 212.
+As terras improdutivas ao norte se devem</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>Clima pouco favorável.</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>Solo pobre em nutrientes.</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>Área de cultivo de coníferas.</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>Presença indígena remanescente.</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>Baixos investimentos do estado.</t>
+        </is>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H669" t="inlineStr">
+        <is>
+          <t>O norte do Canadá apresenta clima pouco favorável para a agricultura em virtude das baixíssimas temperaturas.</t>
+        </is>
+      </c>
+      <c r="I669" t="inlineStr">
+        <is>
+          <t>PH04</t>
+        </is>
+      </c>
+      <c r="J669" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K669" t="inlineStr">
+        <is>
+          <t>8a_ph04_geo_08.png</t>
+        </is>
+      </c>
+      <c r="L669" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>Observe o mapa.
+Os cinturões da letra ‘A’ e ‘B’ correspondem a</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>Trigo e cevada; algodão</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>Pecuária leiteira; algodão.</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>Trigo e tabaco; amendoim.</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>Arroz e frutas; pecuária extensiva</t>
+        </is>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>Milho e soja; tabaco e amendoim.</t>
+        </is>
+      </c>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H670" t="inlineStr">
+        <is>
+          <t>.A área ''A''  corresponde a uma região conhecida como Cinturão de grãos, que planta produtos como trigo, cevada, aveia e arroz. Já a área ''B'' é conhecida como cultivos diversos, que em geral contém algodão, soja e arroz, como também rebanhos intensivos.</t>
+        </is>
+      </c>
+      <c r="I670" t="inlineStr">
+        <is>
+          <t>PH04</t>
+        </is>
+      </c>
+      <c r="J670" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>8a_ph04_geo_09.png</t>
+        </is>
+      </c>
+      <c r="L670" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>A formação territorial dos Estados Unidos é proveniente de uma ocupação marcada por ter sido iniciada pela área litorânea (costa Leste) e posteriormente expandida para o Oeste. Para que essa expansão fosse possível, houve uma série de medidas com o objetivo de atrair imigrantes para ocuparem as terras recém-conquistadas.
+Uma das medidas tomadas para que pudesse haver uma maior produção agrícola nesse território recém-conquistado foi:</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>A democratização do acesso a terra.</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>A implantação Lei de Terras.</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>Propriedade da terra 100% estatal.</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>Proibição da ocupação de terras por não americanos.</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>Trabalho compulsório.</t>
+        </is>
+      </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H671" t="inlineStr">
+        <is>
+          <t>A democratização do acesso a terra permitiu atrair imigrantes europeus e intensificar a conquista territorial em direção ao oeste. Para isso foram criadas leis de democratização do acesso a terra que concede propriedades rurais no século XIX nos Estados Unidos (Homestead Act, de 1862) e no Canadá (Domininion Lands Act, de 1872).</t>
+        </is>
+      </c>
+      <c r="I671" t="inlineStr">
+        <is>
+          <t>PH04</t>
+        </is>
+      </c>
+      <c r="J671" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K671" t="inlineStr"/>
+      <c r="L671" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>O acúmulo de saber e uma educação norteada pela razão deveriam fomentar a capacidade de raciocinar de modo autônomo e a responsabilidade própria. Essa imagem de mundo excluía tanto a superstição e o êxtase religioso como a repressão por um governante absolutista. Assim, a Enciclopédia foi uma obra-chave do Iluminismo, cujo projeto era libertar o ser humano da "dependência autoimposta", como formularia o filósofo alemão Immanuel Kant (1724-1804).
+Disponível em: https://www.dw.com/pt-br/enciclop%C3%A9dia-do-iluminismo-quis-substituir-f%C3%A9-pelo-conhecimento/a-4299793. Acesso em: 29 out. 2024.
+Ao desenvolver a Enciclopédia, Jean d'Alembert e Denis Diderot apresentaram uma concepção de mundo</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>atrasada em relação às descobertas científicas do período.</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>orientada ao auxílio de reis e nobres na administração do poder real.</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>complementar às explicações da Igreja sobre o funcionamento da vida.</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>desenvolvida pela razão e não por pressupostos religiosos e supersticiosos.</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>restrita aos filósofos que eram capazes de escapar da submissão das ideias.</t>
+        </is>
+      </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H672" t="inlineStr">
+        <is>
+          <t>A concepção de mundo apresentada por Jean d'Alembert e Denis Diderot na Enciclopédia foi desenvolvida pela razão e não por pressupostos religiosos e supersticiosos. O texto afirma que a obra excluía tanto a superstição e o êxtase religioso como a repressão por um governante absolutista, o que converge com a concepção iluminista.</t>
+        </is>
+      </c>
+      <c r="I672" t="inlineStr">
+        <is>
+          <t>PH04</t>
+        </is>
+      </c>
+      <c r="J672" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K672" t="inlineStr"/>
+      <c r="L672" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>O receio da indevida utilização do poder, em razão dos excessos perpetrados pelo regime absolutista, estimulou o francês Charles-Louis de Secondat, o Barão de Montesquieu, a engendrar um mecanismo para controlar as ações do soberano. O político-filósofo Montesquieu é considerado pai da “tripartição dos poderes”, cuja construção permite dividir a soberania no formato “quem legisla não executa e não julga, e vice-versa”. O julgador, desta feita, não cria as leis, não administraria o Estado, o ocorrendo com o gestor, que estaria sempre afastado das duas outras funções estatais. Montesquieu grafou em sua clássica obra De L’Esprit des Lois a crença de que todo aquele que exerce poder tende a dele abusar. Então, para coibir a tirania, propôs a divisão de atuação referida linhas atrás.
+RISTER, F.; VILLAS, O. Separação dos poderes e complexidade social - uma releitura sistêmica. Disponível em: https://www.scielo.br/j/rinc/a/R4B4GNDTY4VZYtVzWYgN9vL/. Acesso em: 29 out. 2024.
+O texto evidencia que uma das preocupações dos filósofos iluministas era</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>justificar os poderes dos reis visando a soberania nacional.</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>definir métodos eficientes de gestão de grandes empresas.</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>compreender e valorizar a estrutura clerical da Igreja.</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>governar seus países através do parlamentarismo.</t>
+        </is>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>estabelecer os princípios de um governo justo.</t>
+        </is>
+      </c>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H673" t="inlineStr">
+        <is>
+          <t>O texto evidencia que Montesquieu, um dos filósofos iluministas, estava preocupado em estabelecer os princípios de um governo justo. Ele propôs a tripartição dos poderes como um mecanismo para evitar a tirania e garantir que o poder não fosse concentrado nas mãos de um único governante ou grupo político.</t>
+        </is>
+      </c>
+      <c r="I673" t="inlineStr">
+        <is>
+          <t>PH04</t>
+        </is>
+      </c>
+      <c r="J673" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K673" t="inlineStr"/>
+      <c r="L673" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>Nesse sentido, as reformas pombalinas tentaram, a partir da perspectiva ideológica, recusar, eliminar ou modificar aquilo considerado ultrapassado, para a instalação de um novo projeto idealizado com base nos modelos experimentados pelo marquês. Assim, todos os esforços de Pombal vão denotar um anseio de promover um tipo desejado de homem e sociedade, os quais, antes de mais nada, necessitavam ser preparados.
+TELLES, T. O MARQUÊS DE POMBAL E O ILUMINISMO NA FORMAÇÃO DO ESTADO MODERNO PORTUGUÊS. Disponível em: https://encurtador.com.br/Vamse. Acesso em: 29 out 2024.
+Para promover o tipo de homem e sociedade que desejavam, como mencionado no texto, os déspotas esclarecidos promoveram a(o)</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>intensificação das práticas religiosas com apoio da Igreja.</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>fortalecimento do poder e dos privilégios da aristocracia.</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>construção de escolas, universidades e centros de saber.</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>aumento dos impostos sobre as atividade industriais.</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>direito de voto aos homens proprietários de terra.</t>
+        </is>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H674" t="inlineStr">
+        <is>
+          <t>Os déspotas esclarecidos, como o Marquês de Pombal, promoveram a construção de escolas, universidades e centros de saber. Essas instituições eram fundamentais para a formação de um novo tipo de homem e sociedade, alinhados com os ideais iluministas de racionalidade, progresso e educação.</t>
+        </is>
+      </c>
+      <c r="I674" t="inlineStr">
+        <is>
+          <t>PH04</t>
+        </is>
+      </c>
+      <c r="J674" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K674" t="inlineStr"/>
+      <c r="L674" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>Ela consiste em afirmar que a liberdade para que cada indivíduo busque seu interesse próprio não se contrapõe ao bem comum ou ao desenvolvimento da civilização. Neste sentido, Smith tenta conciliar o desenvolvimento do comércio com as virtudes cívicas e rompe com a visão predominante em sua época sobre uma oposição incontornável entre o impulso aquisitivo, próprio das economias mercantis, e os valores morais. Uma mão invisível concilia a busca do interesse individual com a manutenção da ordem e coesão social.
+CERQUEIRA, H.. Adam Smith e o surgimento do discurso econômico. Disponível em: https://www.scielo.br/j/rep/a/TCzJ99bQ6rKCXYzhdcXP8Tw/. Acesso em: 29 out 2024.
+Ao defender a atividade econômica nos marcos do que foi apresentado no texto, Adam Smith fazia uma crítica ao</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>luteranismo.</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>mercantilismo.</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>racionalismo.</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>colonialismo.</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>capitalismo.</t>
+        </is>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H675" t="inlineStr">
+        <is>
+          <t>Adam Smith fazia uma crítica ao mercantilismo, que era a prática econômica dominante na época. Ele defendia a liberdade econômica e a regulação do mercado pela "mão invisível", em oposição à intervenção estatal característica do mercantilismo. O texto apresenta a concepção de Smith acerca de como a atividade econômica autônoma, sem intervenção, tende a favorecer a todos, o que seria saudável à economia.</t>
+        </is>
+      </c>
+      <c r="I675" t="inlineStr">
+        <is>
+          <t>PH04</t>
+        </is>
+      </c>
+      <c r="J675" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K675" t="inlineStr"/>
+      <c r="L675" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>É mais correto chamarmos o “iluminismo” de ideologia revolucionária, apesar da cautela e moderação política de muitos de seus expoentes continentais, a maioria dos quais — até a década de 1780 — depositava sua fé no despotismo esclarecido. Pois o iluminismo implicava a abolição da ordem política e social vigente na maior parte da Europa.
+HOBSBAWM, E. A Era das Revoluções: 1789 - 1848. São Paulo, Paz e Terra, 2012.
+A abolição da ordem política e social, mencionada pelo texto e promovida pelos iluministas do século XVIII, envolvia a</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>livre interpretação da Bíblia e a crítica às indulgências.</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>defesa do sufrágio universal e de direitos aos trabalhadores.</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>conquista de direitos políticos e a limitação do poder absolutista.</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>concessão de privilégios à aristocracia e à burguesia ascendentes.</t>
+        </is>
+      </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>fragmentação do poder entre senhores de terra e o retorno da Inquisição.</t>
+        </is>
+      </c>
+      <c r="G676" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H676" t="inlineStr">
+        <is>
+          <t>A abolição da ordem política e social promovida pelos iluministas do século XVIII envolvia a conquista de direitos políticos e a limitação do poder absolutista. Os iluministas defendiam a separação dos poderes, o governo baseado em leis e a participação política, em oposição ao absolutismo monárquico.</t>
+        </is>
+      </c>
+      <c r="I676" t="inlineStr">
+        <is>
+          <t>PH04</t>
+        </is>
+      </c>
+      <c r="J676" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K676" t="inlineStr"/>
+      <c r="L676" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>O que é fé? É acreditar naquilo que é evidente? Não. É perfeitamente evidente na minha mente a existência necessária, eterna e suprema de uma inteligência criadora. Isso não é uma questão de fé, mas de razão. Acreditem em Deus, mas não acreditem nos padres.
+VOLTAIRE, François-Marie Arouet. Cartas Filosóficas. São Paulo: Martins Fontes, 2007. Adaptado.
+A frase de Voltaire expressa uma das suas mais reconhecidas posturas político-filosóficas que pode ser exemplificada através da crítica ao</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>mercantilismo e defesa do metalismo.</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>modelo cartesiano e defesa do teocentrismo.</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>liberalismo e defesa do absolutismo monárquico.</t>
+        </is>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>clericalismo e defesa da tolerância religiosa.</t>
+        </is>
+      </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>poder dos padres e defesa da censura absolutista.</t>
+        </is>
+      </c>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H677" t="inlineStr">
+        <is>
+          <t>A frase de Voltaire expressa uma postura crítica contra a Igreja Católica e sua atuação política e moral dentro da sociedade ocidental. Para combater o dogmatismo católico, Voltaire foi um ferrenho defensor da tolerância religiosa e política.</t>
+        </is>
+      </c>
+      <c r="I677" t="inlineStr">
+        <is>
+          <t>PH04</t>
+        </is>
+      </c>
+      <c r="J677" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K677" t="inlineStr"/>
+      <c r="L677" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>Mas o princípio de todos estes benefícios está na agricultura, que fornece a primeira necessidade material, que fornece as reservas para o Rei e para os proprietários, os dízimos ao clero e os lucros para os agricultores. Estas são riquezas sempre renovadas que suportam todos os outros estados do reino, que dão o esteio para todas as outras profissões, que estão florescendo no comércio que favorecem a população, que animam a indústria e que mantêm a prosperidade da nação.
+QUESNAY, François. Grains. Disponível em: &lt;http://ref.scielo.org/v7t7gz&gt;. Acesso em: 24 mar. 2020.
+O pensamento expresso no trecho escrito pelo pensador francês François Quesnay se liga à corrente dos economistas denominados</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>fisiocratas, que afirmavam que toda riqueza de uma sociedade era proveniente da terra e da agricultura.</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>fisiocratas, que afirmavam que toda a riqueza de uma sociedade era originada através das manufaturas.</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>fisiocratas, que afirmavam que toda a riqueza de uma sociedade provinha do poder do rei em organizar a produção agrícola.</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>mercantilistas, que afirmavam que a riqueza de uma sociedade dependia do número de colônias que um reino poderia formar.</t>
+        </is>
+      </c>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>mercantilistas, que afirmavam que a riqueza de uma sociedade era medida pela quantidade de metais preciosos em sua economia.</t>
+        </is>
+      </c>
+      <c r="G678" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H678" t="inlineStr">
+        <is>
+          <t>A fisiocracia, encabeçada pelo pensador e médico francês François Quenay, é uma teoria econômica que surgiu para se opor ao mercantilismo, se apresentando como fruto do Iluminismo. Essa teoria se baseia na afirmação de que toda a riqueza é proveniente da terra e da agricultura, pois considera que a produção agrícola proporciona grandes lucros e exige poucos investimentos; desse modo, é o melhor modo de gerar riquezas.</t>
+        </is>
+      </c>
+      <c r="I678" t="inlineStr">
+        <is>
+          <t>PH04</t>
+        </is>
+      </c>
+      <c r="J678" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K678" t="inlineStr"/>
+      <c r="L678" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>Nenhum homem recebeu da natureza o direito de comandar os outros. A liberdade é um presente do céu e cada indivíduo da mesma espécie tem o direito de gozar dela logo que goze da razão. Toda outra autoridade (que não a paterna) vem duma outra origem, que não é a da natureza. Examinando-a bem, sempre se fará remontar a uma destas duas fontes: ou a força e a violência daquele que dela se apoderou; ou o consentimento daqueles que lhe são submetidos, por um contrato celebrado ou suposto entre eles e aquele a quem deferiram a autoridade. O poder que se adquire pela violência não é mais que uma usurpação e não dura senão pelo tempo por que a força daquele que comanda prevalece sobre a daqueles que obedecem.
+DIDEROT, Denis. Jean Le Rond d'Alambert. Verbetes políticos da enciclopédia. Tradução de Maria das Graças Souza. São Paulo: Editora Unesp, 2006, p. 36-37. Adaptado.
+No trecho da Enciclopédia escrito por Diderot e D'Alambert, nota-se uma crítica dirigida a uma estrutura do Antigo Regime europeu, que era caracterizado pelo(a)</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>liberdade social.</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>liberalismo político.</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>socialismo mercantil.</t>
+        </is>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>sociedade igualitária.</t>
+        </is>
+      </c>
+      <c r="F679" t="inlineStr">
+        <is>
+          <t>absolutismo monárquico.</t>
+        </is>
+      </c>
+      <c r="G679" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H679" t="inlineStr">
+        <is>
+          <t>O denominado Antigo Regime europeu assentava-se em três estruturas fundamentais: politicamente, o absolutismo monárquico; economicamente o mercantilismo; e socialmente na sociedade estamental. O trecho escrito por Diderot e D'Alambert evidencia uma crítica contra a esfera política de sua época, no caso a existência de um poder absoluto concentrado excessivamente nas mãos do monarca, que mantinha seu poder não pelo consenso ou consentimento, mas pela tradição e pelo uso da força e da violência.</t>
+        </is>
+      </c>
+      <c r="I679" t="inlineStr">
+        <is>
+          <t>PH04</t>
+        </is>
+      </c>
+      <c r="J679" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K679" t="inlineStr"/>
+      <c r="L679" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>Encontrar uma forma de associação que defenda e proteja a pessoa e os bens de cada associado com toda a força comum, e pela qual cada um, unindo-se a todos, só obedece contudo a si mesmo, permanecendo assim tão livre quanto antes. Esse, o problema fundamental cuja solução o contrato social oferece. Cada um de nós põe em comum sua pessoa e todo o seu poder sob a direção suprema da vontade geral, e recebemos, enquanto corpo, cada membro como parte indivisível do todo.
+ROSSEAU, Jean-Jacques. Do contrato social, 1983. Adaptado.
+A partir do excerto é possível compreender que, no pensamento do filósofo iluminista Jean Jacques Rousseau, a ideia de um contrato social é importante porque</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>amplia as liberdades econômicas e não os direitos políticos.</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>exclui os incapazes de governarem a si mesmos e os outros.</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>estabelece uma elite esclarecida para governar a sociedade.</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>define regras claras para a atuação dos monarcas absolutistas.</t>
+        </is>
+      </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>pressupõe a participação política de todos os membros de uma sociedade.</t>
+        </is>
+      </c>
+      <c r="G680" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H680" t="inlineStr">
+        <is>
+          <t>A noção de contrato social proposta pelo pensador iluminista Jean Jacques Rousseau contribui para a inclusão de toda a sociedade dentro dos processos e etapas das decisões políticas.</t>
+        </is>
+      </c>
+      <c r="I680" t="inlineStr">
+        <is>
+          <t>PH04</t>
+        </is>
+      </c>
+      <c r="J680" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K680" t="inlineStr"/>
+      <c r="L680" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>Mais do que uma atitude mental, o Iluminismo foi um movimento de ideias, no sentido forte de um processo de constituição e acumulação sempre renovado e sempre capaz de ser modificado até nos fundamentos. Este é o significado da máxima latina com o qual [Immanuel] Kant definiu o Iluminismo na sua resposta à polêmica de 1784: sapere aude – ouse saber, isto é, 'ousa servir-te do teu próprio entendimento', sem imitar ou aceitar passivamente as ideias das autoridades reconhecidas e temidas. Mais do que um convite ao estudo, o lema é uma convocação à independência intelectual.
+GRESPAN, Jorge. Revolução Francesa e Iluminismo. São Paulo: Editora Contexto, 2003, p. 15-16.
+A partir da leitura do excerto, pode-se afirmar que o Iluminismo se caracteriza pelo (a)</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>mercantilismo colonial.</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>autoritarismo econômico.</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>liberdade de pensamento.</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>sujeição absoluta ao Estado.</t>
+        </is>
+      </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>submissão da emoção à razão.</t>
+        </is>
+      </c>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H681" t="inlineStr">
+        <is>
+          <t>Os filósofos iluministas construíram um conjunto de idéias que estabeleciam como lema principal a independência e a liberdade de livre pensar. Essas propostas iam na contra-mão da cultura da sociedade do Antigo Regime, ou seja, o Absolutismo, o Mercantilismo e a sociedade estamental.</t>
+        </is>
+      </c>
+      <c r="I681" t="inlineStr">
+        <is>
+          <t>PH04</t>
+        </is>
+      </c>
+      <c r="J681" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K681" t="inlineStr"/>
+      <c r="L681" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>Disponível em: https://www.tumblr.com/tirasarmandinho. Acesso em 22 de out. de 2024. 
+Qual verbo de ligação presente na tirinha?</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>Vi.</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>Ficou.</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>Agarrei.</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>Adivinha.</t>
+        </is>
+      </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>Arranhada.</t>
+        </is>
+      </c>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H682" t="inlineStr">
+        <is>
+          <t>O verbo "ficou" é um verbo de ligação, pois conecta o sujeito ("A chance") a um predicativo ("toda arranhada e mordida"), indicando um estado ou condição.</t>
+        </is>
+      </c>
+      <c r="I682" t="inlineStr">
+        <is>
+          <t>PH04</t>
+        </is>
+      </c>
+      <c r="J682" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K682" t="inlineStr">
+        <is>
+          <t>8a_ph04_por_01.jpg</t>
+        </is>
+      </c>
+      <c r="L682" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>O violão e o vilão
+Havia a viola da vila.
+A viola e o violão.
+Do vilão era a viola.
+E da Olívia o violão.
+O violão da Olívia dava
+vida à vila, à vila dela.
+O violão duvidava
+da vida, da viola e dela.
+Não vive Olívia na vila.
+Na vila nem na viola.
+O vilão levou-lhe a vida,
+levando o violão dela.
+No vale, a vila de Olívia
+vela a vida
+no seu violão vivida
+e por um vilão levada.
+Vida de Olívia — levada
+por um vilão violento.
+Violeta violada
+pela viola do vento.
+Cecília Meireles, no livro “Ou isto ou aquilo”. [ilustrações de Fernando Correia Dias]. Rio de Janeiro: Editora Nova Fronteira; FNDE/MEC, 1990.
+A figura de linguagem que predomina nesse poema é</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>assonância.</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>eufemismo.</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>aliteração.</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>antítese.</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>ironia.</t>
+        </is>
+      </c>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H683" t="inlineStr">
+        <is>
+          <t>A aliteração é a repetição de sons consonantais no início ou no interior das palavras. No poema, há uma predominância clara da repetição de sons consonantais, como em "violão", "vilão", "vida", "vila", "violada", entre outros, o que caracteriza a figura de linguagem predominante como aliteração.</t>
+        </is>
+      </c>
+      <c r="I683" t="inlineStr">
+        <is>
+          <t>PH04</t>
+        </is>
+      </c>
+      <c r="J683" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K683" t="inlineStr"/>
+      <c r="L683" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>Articulação divulga, nesta quarta, Dossiê Agro é Fogo.
+Disponível em: https://www.campanhacerrado.org.br/noticias/276-articulacao-divulga-nesta-quarta-dossie-agro-e-fogo-grilagem-desmatamento-e-incendios-na-amazonia-cerrado-e-pantanal. Acesso de 22 de out. de 2024.
+O nome do dossiê é considerado um predicado nominal, pois é formado por</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>um verbo de ligação e um predicativo que atribui uma característica ao sujeito.</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>um verbo intransitivo que não necessita de complemento.</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>um verbo transitivo indireto e um objeto indireto.</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>um verbo transitivo direto e um objeto direto.</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>um verbo de ação e um advérbio de modo.</t>
+        </is>
+      </c>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H684" t="inlineStr">
+        <is>
+          <t>Um predicado nominal é formado por um verbo de ligação ("é") e um predicativo do sujeito ("fogo"), que atribui uma característica ao sujeito ("agro").</t>
+        </is>
+      </c>
+      <c r="I684" t="inlineStr">
+        <is>
+          <t>PH04</t>
+        </is>
+      </c>
+      <c r="J684" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K684" t="inlineStr">
+        <is>
+          <t>8a_ph04_por_03.jpg</t>
+        </is>
+      </c>
+      <c r="L684" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>Tempo, tempo, tempo
+És um senhor tão bonito
+Quanto a cara do meu filho
+Tempo tempo tempo tempo
+Vou te fazer um pedido
+Tempo tempo tempo tempo
+Compositor de destinos
+Tambor de todos os ritmos
+Tempo tempo tempo tempo
+Entro num acordo contigo
+Tempo tempo tempo tempo
+Por seres tão inventivo
+E pareceres contínuo
+Tempo tempo tempo tempo
+És um dos deuses mais lindos
+[...]
+Disponível em: https://www.vagalume.com.br/maria-bethania/oracao-do-tempo-tempo-tempo-tempo.html. Acesso em 22 de out. de 2024.
+Qual dos versos da música de Maria Bethânia contém um predicado nominal?</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>"Tambor de todos os ritmos"</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>"Entro num acordo contigo"</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>"És um senhor tão bonito"</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>"Vou te fazer um pedido"</t>
+        </is>
+      </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>"Compositor de destinos"</t>
+        </is>
+      </c>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H685" t="inlineStr">
+        <is>
+          <t>"És um senhor tão bonito" contém um predicado nominal, pois o verbo "és" é um verbo de ligação e "um senhor tão bonito" é o predicativo do sujeito.</t>
+        </is>
+      </c>
+      <c r="I685" t="inlineStr">
+        <is>
+          <t>PH04</t>
+        </is>
+      </c>
+      <c r="J685" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K685" t="inlineStr"/>
+      <c r="L685" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>Soneto de Separação
+De repente do riso fez-se o pranto
+Silencioso e branco como a bruma
+E das bocas unidas fez-se a espuma
+E das mãos espalmadas fez-se o espanto
+De repente da calma fez-se o vento
+Que dos olhos desfez a última chama
+E da paixão fez-se o pressentimento
+E do momento imóvel fez-se o drama
+De repente, não mais que de repente
+Fez-se de triste o que se fez amante
+E de sozinho o que se fez contente
+Fez-se do amigo próximo, distante
+Fez-se da vida uma aventura errante
+De repente, não mais que de repente
+JOBIM, Tom. Disponível em: https://www.letras.mus.br/tom-jobim/86280/. Acesso em 23 de out. de 2024.
+Qual das figuras de linguagem abaixo está presente no poema e contribui para o efeito de sentido?</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>Ironia.</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>Antítese.</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>Aliteração.</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>Eufemismo.</t>
+        </is>
+      </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>Assonância.</t>
+        </is>
+      </c>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H686" t="inlineStr">
+        <is>
+          <t>A antítese é a figura de linguagem que coloca palavras ou ideias opostas em contraste. No poema, há várias antíteses, como "riso" e "pranto", "calma" e "vento", "triste" e "amante", "sozinho" e "contente", "próximo" e "distante".</t>
+        </is>
+      </c>
+      <c r="I686" t="inlineStr">
+        <is>
+          <t>PH04</t>
+        </is>
+      </c>
+      <c r="J686" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K686" t="inlineStr"/>
+      <c r="L686" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>Identifique a alternativa em que aparece um predicado verbo-nominal:</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>Os viajantes chegaram cedo ao destino.</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>Demitiram o secretário da instituição.</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>Nomearam as novas ruas da cidade.</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>Compareceram todos atrasados à reunião.</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>Estava irritado com as brincadeiras.</t>
+        </is>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H687" t="inlineStr">
+        <is>
+          <t>Na frase "Compareceram todos atrasados à reunião", existem dois núcleos no predicado, um núcleo verbal que é o verbo de ação “compareceram” e um núcleo nominal que é o predicativo do sujeito “atrasados”.</t>
+        </is>
+      </c>
+      <c r="I687" t="inlineStr">
+        <is>
+          <t>PH04</t>
+        </is>
+      </c>
+      <c r="J687" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K687" t="inlineStr"/>
+      <c r="L687" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>Serenata
+Permita que eu feche os meus olhos,
+pois é muito longe e tão tarde!
+Pensei que era apenas demora,
+e cantando pus-me a esperar-te.
+Permita que agora emudeça:
+que me conforme em ser sozinha.
+Há uma doce luz no silêncio, e a dor é de origem divina.
+Permita que eu volte o meu rosto para um céu maior que este mundo,
+e aprenda a ser dócil no sonho como as estrelas no seu rumo.
+Cecília Meirelles
+Os predicados dos versos destacados são, respectivamente,</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>nominal e verbonominal.</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>nominal e verbal.</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>verbal e nominal.</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>verbal e verbonominal.</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>nominal e nominal.</t>
+        </is>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H688" t="inlineStr">
+        <is>
+          <t>"pois é muito longe e tão tarde!" é uma oração cujo predicado é classificado como nominal, pois o verbo de ligação "é" não representa uma ação, e sim um estado; já no verso "Permita que agora emudeça" o núcleo do predicado é o verbo "emudeça", expressando uma ação, portanto, trata-se de um predicado verbal.</t>
+        </is>
+      </c>
+      <c r="I688" t="inlineStr">
+        <is>
+          <t>PH04</t>
+        </is>
+      </c>
+      <c r="J688" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K688" t="inlineStr"/>
+      <c r="L688" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>Soneto da separação​
+Vinicius de Moraes
+De repente do riso fez-se o pranto
+Silencioso e branco como a bruma
+E das bocas unidas fez-se a espuma
+E das mãos espalmadas fez-se o espanto
+De repente da calma fez-se o vento
+Que dos olhos desfez a última chama
+E da paixão fez-se o pressentimento
+E do momento imóvel fez-se o drama
+De repente não mais que de repente
+Fez-se de triste o que se fez amante
+E de sozinho o que se fez contente
+Fez-se do amigo próximo, distante
+Fez-se da vida uma aventura errante
+De repente, não mais que de repente
+Ao aproximar as palavras “triste” de “contente” e “próximo” de “distante”, o eu-lírico do poema lança mão de uma figura de linguagem conhecida como</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>eufemismo.</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>antítese.</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>ironia.</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>aliteração.</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>metáfora.</t>
+        </is>
+      </c>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H689" t="inlineStr">
+        <is>
+          <t>No "Soneto da Separação" de Vinicius de Moraes, o eu-lírico utiliza a antítese como figura de linguagem para criar um contraste entre sentimentos e situações opostas. Ao aproximar palavras como "triste" e "contente" e "próximo" e "distante", o poeta evidencia a transformação súbita e dramática dos estados emocionais e das relações humanas. A antítese realça a intensidade das mudanças descritas no poema, destacando a passagem abrupta de um estado positivo para um negativo, ou vice-versa, e reforçando o impacto emocional da separação.</t>
+        </is>
+      </c>
+      <c r="I689" t="inlineStr">
+        <is>
+          <t>PH04</t>
+        </is>
+      </c>
+      <c r="J689" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K689" t="inlineStr"/>
+      <c r="L689" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>Soneto da separação​
+Vinicius de Moraes
+De repente do riso fez-se o pranto
+Silencioso e branco como a bruma
+E das bocas unidas fez-se a espuma
+E das mãos espalmadas fez-se o espanto
+De repente da calma fez-se o vento
+Que dos olhos desfez a última chama
+E da paixão fez-se o pressentimento
+E do momento imóvel fez-se o drama
+De repente não mais que de repente
+Fez-se de triste o que se fez amante
+E de sozinho o que se fez contente
+Fez-se do amigo próximo, distante
+Fez-se da vida uma aventura errante
+De repente, não mais que de repente
+É possível afirmar que o eu-lírico no poema</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>declara o seu amor pelo ser amado.</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>lamenta por amar e não ser correspondido.</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>afirma que foi abandonado pelo ser amado.</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>divaga sobre o fim abrupto de seu relacionamento.</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>culpa o ser amado por não amá-lo da mesma forma.</t>
+        </is>
+      </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H690" t="inlineStr">
+        <is>
+          <t>O poema "Soneto da Separação" de Vinicius de Moraes descreve, de forma poética e melancólica, a súbita transformação de um relacionamento amoroso. O eu-lírico utiliza expressões como "De repente" e "não mais que de repente" para enfatizar a rapidez e a inesperada mudança de sentimentos e situações, passando do riso ao pranto, da calma ao vento, e do amor à solidão. Esses elementos indicam que o poema é uma reflexão sobre a ruptura inesperada e dolorosa de um relacionamento, capturando a essência do fim abrupto e suas consequências emocionais.</t>
+        </is>
+      </c>
+      <c r="I690" t="inlineStr">
+        <is>
+          <t>PH04</t>
+        </is>
+      </c>
+      <c r="J690" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K690" t="inlineStr"/>
+      <c r="L690" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>Palavras apenas fisicamente
+Clarice Lispector
+“Na Itália il miracolo é de pesca noturna. Mortalmente ferido pelo arpão, larga no mar sua tinta roxa. Quem o pesca desembarca antes de o sol nascer – sabendo com o rosto lívido e responsável que arrasta pelas areias o enorme peso da pesca milagrosa: il miracolo amore. Milagre é lágrima na folha, treme, desliza, tomba: eis milhares de milágrimas brilhando na relva.”
+Disponível em: http://notaterapia.com.br/2019/02/28/vender-alma-no-cotidiano-13-cronicas-curtas-de-clarice-lispector/. Acesso em
+18/02/2020.
+Considerando as características do gênero textual crônica, é possível afirmar que há no texto:</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>A aproximação a temas da vida cotidiana por meio de um tom descontraído que suscita diversas reflexões.</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>A expressão dos sentimentos de uma voz poética que utiliza diversas figuras de linguagem para expressar-se.</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>O tratamento sério de temas excepcionais que se distanciam de tópicos da vida cotidiana.</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>O desenvolvimento de uma longa história com participação ativa de diversos personagens.</t>
+        </is>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>A exposição de um ponto de vista com argumentos que visam convencer o leitor.</t>
+        </is>
+      </c>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H691" t="inlineStr">
+        <is>
+          <t>A crônica como gênero se aproxima de temas do cotidiano, partindo deles para, com humor e linguagem coloquial, aprofundar-se em questões complexas da existência. No texto de Clarice Lispector, a autora descreve um evento aparentemente simples, a pesca noturna, e o transforma em uma reflexão poética sobre o milagre e a beleza da vida. Utilizando uma linguagem rica em imagens e metáforas, Lispector aproxima o leitor de uma experiência comum, mas o faz enxergar a profundidade e a poesia presentes nas pequenas coisas do dia a dia. Esse tom descontraído e reflexivo é típico das crônicas, que buscam suscitar diversas reflexões a partir de situações corriqueiras.</t>
+        </is>
+      </c>
+      <c r="I691" t="inlineStr">
+        <is>
+          <t>PH04</t>
+        </is>
+      </c>
+      <c r="J691" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K691" t="inlineStr"/>
+      <c r="L691" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>Um jovem agricultor que está plantando árvores em sua fazenda, decide plantar árvores frutíferas em fileiras. Cada fileira tem um número de árvores que pode ser representado pelo monômio , onde x é o número de fileiras. Agora, o agricultor quer saber mais sobre esse monômio.
+Qual é o coeficiente, a parte literal e o grau desse monômio?</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>Coeficiente: 3, Parte literal: x², Grau: 2</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>Coeficiente: 2, Parte literal: 3x, Grau: 1</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>Coeficiente: 1, Parte literal: 3x², Grau: 3</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>Coeficiente: 3, Parte literal: x, Grau: 2</t>
+        </is>
+      </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>Coeficiente: 2, Parte literal: 3x², Grau: 3</t>
+        </is>
+      </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H692" t="inlineStr">
+        <is>
+          <t>O coeficiente é 3, a parte literal é x² e o grau é 2. O coeficiente é o número que multiplica a parte literal, que é x². O grau do monômio é o expoente da parte literal, que é 2.</t>
+        </is>
+      </c>
+      <c r="I692" t="inlineStr">
+        <is>
+          <t>PH04</t>
+        </is>
+      </c>
+      <c r="J692" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K692" t="inlineStr">
+        <is>
+          <t>8a_ph04_mat_01.png</t>
+        </is>
+      </c>
+      <c r="L692" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>Uma aluna está estudando como calcular o volume de prismas retos. Ela encontrou a seguinte expressão para o volume de um prisma específico:  
+Qual é a expressão simplificada para o volume desse prisma?</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>[img:8a_ph04_mat_02_a.png]</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>[img:8a_ph04_mat_02_b.png]</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>[img:8a_ph04_mat_02_c.png]</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>[img:8a_ph04_mat_02_d.png]</t>
+        </is>
+      </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>​​</t>
+        </is>
+      </c>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H693" t="inlineStr">
+        <is>
+          <t>Para encontrar a expressão simplificada para o volume desse prisma, realizamos a multiplicação dos coeficientes, e somamos os expoentes das partes literais, . Assim, obtemos .</t>
+        </is>
+      </c>
+      <c r="I693" t="inlineStr">
+        <is>
+          <t>PH04</t>
+        </is>
+      </c>
+      <c r="J693" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K693" t="inlineStr">
+        <is>
+          <t>8a_ph04_mat_02.png</t>
+        </is>
+      </c>
+      <c r="L693" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>Durante um festival, uma empresa está vendendo pipoca em embalagens de diferentes tamanhos. A relação entre o tamanho da embalagem e o preço em reais é dada pela função P(x) = 2x + 4, onde x é o tamanho da embalagem em litros.
+Se o cliente compra uma embalagem de 6 litros, qual será o preço da pipoca?</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H694" t="inlineStr">
+        <is>
+          <t>Para encontrar o preço da pipoca em uma embalagem de 6 litros, basta substituir x = 6 na equação: P(6) = 2*6 + 4 = 16 reais.</t>
+        </is>
+      </c>
+      <c r="I694" t="inlineStr">
+        <is>
+          <t>PH04</t>
+        </is>
+      </c>
+      <c r="J694" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K694" t="inlineStr"/>
+      <c r="L694" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>Uma empresa de tecnologia está desenvolvendo um novo sistema de distribuição de internet e a velocidade de transmissão é modelada pela expressão  . Para isso, na nova expressão, eles decidiram aplicar uma transformação matemática na expressão original, que envolve a raiz quadrada da expressão original e um fator de multiplicação.
+Sabendo que a equipe de engenharia deseja aumentar a velocidade em 50%, qual será a nova expressão para a velocidade de transmissão?</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>[img:8a_ph04_mat_04_a.png]</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>[img:8a_ph04_mat_04_b.png]</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>[img:8a_ph04_mat_04_c.png]</t>
+        </is>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>[img:8a_ph04_mat_04_d.png]</t>
+        </is>
+      </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>[img:8a_ph04_mat_04_e.png]</t>
+        </is>
+      </c>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H695" t="inlineStr">
+        <is>
+          <t>Para resolver essa questão, primeiro precisamos calcular a raiz quadrada da expressão original .
+A raiz quadrada  é 
+Agora, para aumentar a velocidade em 50%, multiplicamos a expressão obtida pela raiz quadrada por 1,5:
+Portanto, a nova expressão para a velocidade de transmissão é 4,5x².</t>
+        </is>
+      </c>
+      <c r="I695" t="inlineStr">
+        <is>
+          <t>PH04</t>
+        </is>
+      </c>
+      <c r="J695" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K695" t="inlineStr">
+        <is>
+          <t>8a_ph04_mat_04.png</t>
+        </is>
+      </c>
+      <c r="L695" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>Uma fábrica de peças metálicas e utiliza uma função para representar os custos de produção: C(x) = 2x³ + 4x² - 3x + 7, onde x é o número de peças produzidas em milhares.
+Classifique o polinômio de acordo com o número de termos e o grau.</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>Polinômio de 3 termos e grau 3.</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>Polinômio de 3 termos e grau 2.</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>Polinômio de 4 termos e grau 4.</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>Polinômio de 4 termos e grau 3.</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>Polinômio de 4 termos e grau 2.</t>
+        </is>
+      </c>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H696" t="inlineStr">
+        <is>
+          <t>O polinômio C(x) = 2x³ + 4x² - 3x + 7 tem grau 3, pois o maior expoente é 3, e tem quatro termos: 2x³, 4x², 3x e 7. Logo, trata-se de um polinômio de 4 termos e grau 3.</t>
+        </is>
+      </c>
+      <c r="I696" t="inlineStr">
+        <is>
+          <t>PH04</t>
+        </is>
+      </c>
+      <c r="J696" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K696" t="inlineStr"/>
+      <c r="L696" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>Laura é pintora e sua mais nova tela tem formato quadrado e área igual a 256x12y16z24 . Ela deseja comprar uma moldura para enquadrar a obra e apresentá-la em uma exposição.
+Qual deve ser a medida do lado da moldura para que caiba perfeitamente a tela de Laura?</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>16x6y8z12</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>256x6y8z12</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>16x12y16z24</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>64x3y4z6</t>
+        </is>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>(256x12y16z24)2</t>
+        </is>
+      </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H697" t="inlineStr">
+        <is>
+          <t>Como a tela tem o formato quadrado, a medida do lado da moldura deve ser igual a medida do lado da tela para que ela se encaixe perfeitamente:</t>
+        </is>
+      </c>
+      <c r="I697" t="inlineStr">
+        <is>
+          <t>PH04</t>
+        </is>
+      </c>
+      <c r="J697" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K697" t="inlineStr"/>
+      <c r="L697" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>O proprietário de uma casa deseja pintar sua fachada e, para estimar a quantidade de tinta a ser usada, necessita saber qual a área a ser pintada. A parte da frente dessa casa pode ser visualizada como a junção de um retângulo com um triângulo, conforme a imagem abaixo:
+Qual monômio representa a área da fachada da casa?</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>[img:8a_ph04_mat_07_a.png]</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>[img:8a_ph04_mat_07_b.png]</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>[img:8a_ph04_mat_07_c.png]</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>[img:8a_ph04_mat_07_d.png]</t>
+        </is>
+      </c>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>​​</t>
+        </is>
+      </c>
+      <c r="G698" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H698" t="inlineStr">
+        <is>
+          <t>Somando a área do retângulo com a área do triângulo, obtém-se:</t>
+        </is>
+      </c>
+      <c r="I698" t="inlineStr">
+        <is>
+          <t>PH04</t>
+        </is>
+      </c>
+      <c r="J698" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K698" t="inlineStr">
+        <is>
+          <t>8a_ph04_mat_07.png</t>
+        </is>
+      </c>
+      <c r="L698" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>Uma sala quadrada de lado  tem, em seu interior, uma coluna de base quadrada de lado . Observe a imagem abaixo, com as medidas de suas dimensões:
+Deseja-se colocar um rodapé nessa sala, ao redor de todo o cômodo e também da coluna. 
+Desconsiderando o espaço ocupado pelas entradas da sala, qual monômio representa a quantidade de rodapé necessária?</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>[img:8a_ph04_mat_08_a.png]</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>[img:8a_ph04_mat_08_b.png]</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>[img:8a_ph04_mat_08_c.png]</t>
+        </is>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>[img:8a_ph04_mat_08_d.png]</t>
+        </is>
+      </c>
+      <c r="F699" t="inlineStr">
+        <is>
+          <t>[img:8a_ph04_mat_08_e.png]</t>
+        </is>
+      </c>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H699" t="inlineStr">
+        <is>
+          <t>Somando o perímetro da sala com o perímetro da coluna, obtém-se:</t>
+        </is>
+      </c>
+      <c r="I699" t="inlineStr">
+        <is>
+          <t>PH04</t>
+        </is>
+      </c>
+      <c r="J699" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K699" t="inlineStr">
+        <is>
+          <t>8a_ph04_mat_08.png</t>
+        </is>
+      </c>
+      <c r="L699" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>Peças de lego têm um tamanho determinado: para cada círculo de encaixe, há um bloco cúbico que forma sua base. Considere que a figura abaixo foi construída com peças de lego:
+Se a medida do lado de cada bloco cúbico é x, qual o perímetro exterior da figura formada?</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>8x</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>16x</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>24x</t>
+        </is>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>32x</t>
+        </is>
+      </c>
+      <c r="F700" t="inlineStr">
+        <is>
+          <t>40x</t>
+        </is>
+      </c>
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H700" t="inlineStr">
+        <is>
+          <t>Como as peças têm medida padrão, a figura formada com as peças de lego é um quadrado com 8 círculos de encaixe em cada lado. Desta forma, o lado exterior do quadrado medirá: .
+Portanto, o perímetro da figura será: .</t>
+        </is>
+      </c>
+      <c r="I700" t="inlineStr">
+        <is>
+          <t>PH04</t>
+        </is>
+      </c>
+      <c r="J700" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K700" t="inlineStr">
+        <is>
+          <t>8a_ph04_mat_09.png</t>
+        </is>
+      </c>
+      <c r="L700" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>Considere o seguinte polinômio: .
+Qual a sua classificação?</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>monômio.</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>binômio.</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>trinômio.</t>
+        </is>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>quadrinômio.</t>
+        </is>
+      </c>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>pentanômio.</t>
+        </is>
+      </c>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H701" t="inlineStr">
+        <is>
+          <t>O polinômio  possui três termos, logo é classificado como trinômio.</t>
+        </is>
+      </c>
+      <c r="I701" t="inlineStr">
+        <is>
+          <t>PH04</t>
+        </is>
+      </c>
+      <c r="J701" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K701" t="inlineStr">
+        <is>
+          <t>8a_ph04_mat_10.png</t>
+        </is>
+      </c>
+      <c r="L701" t="inlineStr">
         <is>
           <t>8ano</t>
         </is>

--- a/questoes.xlsx
+++ b/questoes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L701"/>
+  <dimension ref="A1:L751"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35965,7 +35965,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K652" t="inlineStr"/>
       <c r="L652" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -36024,7 +36023,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K653" t="inlineStr"/>
       <c r="L653" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -36083,7 +36081,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K654" t="inlineStr"/>
       <c r="L654" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -36142,7 +36139,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K655" t="inlineStr"/>
       <c r="L655" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -36201,7 +36197,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K656" t="inlineStr"/>
       <c r="L656" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -36260,7 +36255,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K657" t="inlineStr"/>
       <c r="L657" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -36319,7 +36313,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K658" t="inlineStr"/>
       <c r="L658" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -36378,7 +36371,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K659" t="inlineStr"/>
       <c r="L659" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -36438,7 +36430,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K660" t="inlineStr"/>
       <c r="L660" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -36498,7 +36489,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K661" t="inlineStr"/>
       <c r="L661" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -36558,7 +36548,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K662" t="inlineStr"/>
       <c r="L662" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -36618,7 +36607,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K663" t="inlineStr"/>
       <c r="L663" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -36678,7 +36666,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K664" t="inlineStr"/>
       <c r="L664" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -36738,7 +36725,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K665" t="inlineStr"/>
       <c r="L665" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -36798,7 +36784,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K666" t="inlineStr"/>
       <c r="L666" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -36857,7 +36842,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K667" t="inlineStr"/>
       <c r="L667" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -36915,7 +36899,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K668" t="inlineStr"/>
       <c r="L668" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -37100,7 +37083,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K671" t="inlineStr"/>
       <c r="L671" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -37160,7 +37142,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K672" t="inlineStr"/>
       <c r="L672" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -37220,7 +37201,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K673" t="inlineStr"/>
       <c r="L673" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -37280,7 +37260,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K674" t="inlineStr"/>
       <c r="L674" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -37340,7 +37319,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K675" t="inlineStr"/>
       <c r="L675" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -37400,7 +37378,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K676" t="inlineStr"/>
       <c r="L676" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -37460,7 +37437,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K677" t="inlineStr"/>
       <c r="L677" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -37520,7 +37496,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K678" t="inlineStr"/>
       <c r="L678" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -37580,7 +37555,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K679" t="inlineStr"/>
       <c r="L679" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -37640,7 +37614,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K680" t="inlineStr"/>
       <c r="L680" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -37700,7 +37673,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K681" t="inlineStr"/>
       <c r="L681" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -37843,7 +37815,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K683" t="inlineStr"/>
       <c r="L683" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -37982,7 +37953,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K685" t="inlineStr"/>
       <c r="L685" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -38056,7 +38026,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K686" t="inlineStr"/>
       <c r="L686" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -38114,7 +38083,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K687" t="inlineStr"/>
       <c r="L687" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -38183,7 +38151,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K688" t="inlineStr"/>
       <c r="L688" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -38257,7 +38224,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K689" t="inlineStr"/>
       <c r="L689" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -38331,7 +38297,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K690" t="inlineStr"/>
       <c r="L690" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -38394,7 +38359,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K691" t="inlineStr"/>
       <c r="L691" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -38579,7 +38543,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K694" t="inlineStr"/>
       <c r="L694" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -38704,7 +38667,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K696" t="inlineStr"/>
       <c r="L696" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -38763,7 +38725,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K697" t="inlineStr"/>
       <c r="L697" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -39019,6 +38980,3081 @@
         </is>
       </c>
       <c r="L701" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>O desmatamento tem sido mais intenso nas áreas tropicais e, sobretudo, na mata atlântica, da qual restam míseros 7% da extensão original, segundo o Programa SOS Mata Atlântica. O desmatamento desenfreado transformou esse bioma, antes contínuo, em pequenos fragmentos espalhados pelas regiões Sul, Sudeste e Nordeste. Esse processo é conhecido como fragmentação.
+Disponível em: https://cienciahoje.periodicos.capes.gov.br/storage/acervo/ch/ch_258.pdf#page=37. Acesso em: 21 nov. 2024.
+Baseando-se na fragmentação da Mata Atlântica, qual das seguintes iniciativas poderia contribuir para a restauração desse bioma?</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>Construção de novas rodovias nas áreas remanescentes da Mata Atlântica.</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>Estabelecimento de corredores ecológicos para conectar fragmentos florestais.</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>Aumento da produção agrícola nas áreas desmatadas da Mata Atlântica.</t>
+        </is>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>Expansão urbana nas regiões de floresta remanescente.</t>
+        </is>
+      </c>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>Intensificação da mineração nas áreas de Mata Atlântica.</t>
+        </is>
+      </c>
+      <c r="G702" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H702" t="inlineStr">
+        <is>
+          <t>Corredores ecológicos conectam fragmentos florestais, permitindo o fluxo gênico e contribuindo para a restauração e conservação da biodiversidade.</t>
+        </is>
+      </c>
+      <c r="I702" t="inlineStr">
+        <is>
+          <t>PH05</t>
+        </is>
+      </c>
+      <c r="J702" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K702" t="inlineStr"/>
+      <c r="L702" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>As previsões mostram que, até 2099, dependendo do cenário, a temperatura média do planeta aumentará entre 1,8ºC e 4º C e o nível do mar subirá entre 18 e 59 cm.
+Disponível em: https://cienciahoje.periodicos.capes.gov.br/storage/acervo/ch/ch_238.pdf#page=44. Acesso em: 21 nov. 2024.
+Considerando o aumento previsto da temperatura média global até 2099, qual das seguintes ações seria mais eficaz para mitigar esse aumento?</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>Adoção de práticas agrícolas que utilizam pesticidas e fertilizantes químicos.</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>Incentivo à utilização de energias renováveis, como solar e eólica.</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>Expansão da frota de veículos movidos a combustíveis fósseis.</t>
+        </is>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>Construção de novas usinas termelétricas a carvão.</t>
+        </is>
+      </c>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>Desmatamento de áreas florestais para expansão urbana.</t>
+        </is>
+      </c>
+      <c r="G703" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H703" t="inlineStr">
+        <is>
+          <t>Energias renováveis reduzem a dependência de combustíveis fósseis e as emissões de gases de efeito estufa, mitigando o aumento da temperatura global.</t>
+        </is>
+      </c>
+      <c r="I703" t="inlineStr">
+        <is>
+          <t>PH05</t>
+        </is>
+      </c>
+      <c r="J703" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K703" t="inlineStr"/>
+      <c r="L703" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>O ser humano é atualmente um dos maiores responsáveis pelo desenvolvimento de fontes de estresse, entre elas o desmatamento, a poluição de corpos d’água e a queima de combustíveis fósseis.
+Disponível em: https://cienciahoje.periodicos.capes.gov.br/storage/acervo/ch/ch_247.pdf#page=27. Acesso em: 21 nov. 2024.
+Diante da poluição de corpos d'água, qual das seguintes iniciativas poderia contribuir para a melhoria da qualidade da água?</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>Despejo de resíduos industriais diretamente nos rios.</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>Implementação de sistemas de tratamento de esgoto.</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>Aumento do uso de fertilizantes químicos nas atividades agrícolas.</t>
+        </is>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>Construção de barragens para represamento de rios.</t>
+        </is>
+      </c>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>Expansão da mineração em áreas próximas a corpos d'água.</t>
+        </is>
+      </c>
+      <c r="G704" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H704" t="inlineStr">
+        <is>
+          <t>Sistemas de tratamento de esgoto reduzem a quantidade de poluentes lançados nos corpos d'água, melhorando a qualidade da água.</t>
+        </is>
+      </c>
+      <c r="I704" t="inlineStr">
+        <is>
+          <t>PH05</t>
+        </is>
+      </c>
+      <c r="J704" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K704" t="inlineStr"/>
+      <c r="L704" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>O monte Fuji, símbolo do Japão, está sem neve, algo nunca visto em 130 anos. Normalmente, o cume do vulcão começa a ficar coberto de neve por volta de 2 de outubro. Neste ano, porém, não houve nevasca devido às altas temperaturas, disse Yutaka Katsuta, meteorologista do serviço de Kofu, no centro do Japão.
+Disponível em: https://www1.folha.uol.com.br/ambiente/2024/10/monte-fuji-no-japao-esta-sem-neve-em-recorde-em-130-anos.shtml. Acesso em: 21 nov. 2024.
+Considerando a ausência de neve no Monte Fuji devido às altas temperaturas, qual das seguintes ações poderia ajudar a reduzir a emissão de gases de efeito estufa?</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>Aumento da produção de energia nuclear sem controle de resíduos.</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>Incentivo ao uso de biocombustíveis e tecnologias limpas.</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>Expansão da frota de veículos movidos a diesel.</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>Desmatamento de áreas florestais para agricultura.</t>
+        </is>
+      </c>
+      <c r="F705" t="inlineStr">
+        <is>
+          <t>Construção de novas usinas termelétricas a carvão.</t>
+        </is>
+      </c>
+      <c r="G705" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H705" t="inlineStr">
+        <is>
+          <t>Biocombustíveis e tecnologias limpas, como energia solar e eólica, emitem menos gases de efeito estufa em comparação com combustíveis fósseis. Incentivar o uso dessas tecnologias pode ajudar a reduzir as emissões de gases de efeito estufa.</t>
+        </is>
+      </c>
+      <c r="I705" t="inlineStr">
+        <is>
+          <t>PH05</t>
+        </is>
+      </c>
+      <c r="J705" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K705" t="inlineStr"/>
+      <c r="L705" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>A poluição do ar causada pela queima de combustíveis fósseis é um dos maiores desafios ambientais da atualidade. Essa poluição resulta na emissão de dióxido de carbono, óxidos de nitrogênio e partículas finas, que contribuem para o aquecimento global, a chuva ácida e problemas respiratórios na população. A transição para fontes de energia mais limpas e a adoção de tecnologias sustentáveis são essenciais para melhorar a qualidade do ar.
+Considerando a poluição do ar causada pela queima de combustíveis fósseis, qual das seguintes iniciativas poderia contribuir para a melhoria da qualidade do ar?</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>Aumento da produção de veículos a gasolina.</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>Incentivo ao uso de veículos elétricos e híbridos.</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>Construção de novas usinas a carvão.</t>
+        </is>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>Expansão da indústria petroquímica.</t>
+        </is>
+      </c>
+      <c r="F706" t="inlineStr">
+        <is>
+          <t>Desmatamento para construção de novas áreas industriais.</t>
+        </is>
+      </c>
+      <c r="G706" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H706" t="inlineStr">
+        <is>
+          <t>Veículos elétricos e híbridos reduzem a emissão de poluentes atmosféricos, melhorando a qualidade do ar.</t>
+        </is>
+      </c>
+      <c r="I706" t="inlineStr">
+        <is>
+          <t>PH05</t>
+        </is>
+      </c>
+      <c r="J706" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K706" t="inlineStr"/>
+      <c r="L706" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>No momento em que vivemos, de forte conscientização sobre a importância da sustentabilidade, a compostagem tem sido cada vez mais difundida. O processo de reaproveitamento de resíduos orgânicos vem se tornando uma opção mais acessível, iniciativas de apoio surgem na iniciativa pública e milhares de conteúdos sobre o tema são encontrados nas redes sociais.
+Disponível em: https://g1.globo.com/pr/parana/especial-publicitario/composta-mais/residuo-nao-e-lixo-e-oportunidade/noticia/2024/03/08/compostagem-saiba-tudo-sobre-como-os-organicos-podem-ser-reciclados.ghtml. Acesso em 14 nov. 2024
+Com base no trecho, a compostagem é um processo de</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>purificação da água potável, removendo impurezas e contaminantes.</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>reciclagem de materiais plásticos e metálicos, transformando-os em novos produtos.</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>tratamento de resíduos orgânicos e materiais biodegradáveis, os transformando em adubo.</t>
+        </is>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>despoluição do ar em áreas urbanas, reduzindo a quantidade de poluentes atmosféricos.</t>
+        </is>
+      </c>
+      <c r="F707" t="inlineStr">
+        <is>
+          <t>geração de energia elétrica a partir de resíduos sólidos, utilizando processos de combustão.</t>
+        </is>
+      </c>
+      <c r="G707" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H707" t="inlineStr">
+        <is>
+          <t>A compostagem é um processo biológico que envolve a decomposição de materiais orgânicos, como restos de alimentos, folhas, e outros resíduos biodegradáveis, por meio da ação de microrganismos. Este processo resulta na formação de um composto rico em nutrientes, conhecido como adubo ou húmus, que pode ser utilizado para melhorar a qualidade do solo em jardins, hortas e plantações.</t>
+        </is>
+      </c>
+      <c r="I707" t="inlineStr">
+        <is>
+          <t>PH05</t>
+        </is>
+      </c>
+      <c r="J707" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K707" t="inlineStr"/>
+      <c r="L707" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>As cadeias alimentares representam as relações de alimentação entre os organismos, enquanto as teias alimentares mostram essas relações de forma mais complexa, evidenciando como os diferentes organismos interagem em um ecossistema.
+Qual das alternativas melhor explica a diferença entre uma cadeia alimentar e uma teia alimentar?</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>Cadeias alimentares são formadas por produtores e consumidores, enquanto teias alimentares não têm produtores.</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>Teias alimentares são formadas por apenas uma sequência de organismos, enquanto cadeias alimentares mostram várias interações.</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>Cadeias alimentares representam uma sequência linear de consumo, enquanto teias alimentares mostram diversas cadeias interligadas.</t>
+        </is>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>Teias alimentares ocorrem apenas em ecossistemas aquáticos, enquanto cadeias alimentares ocorrem em ecossistemas terrestres.</t>
+        </is>
+      </c>
+      <c r="F708" t="inlineStr">
+        <is>
+          <t>Cadeias alimentares mostram interações entre predadores de um mesmo nível trófico.</t>
+        </is>
+      </c>
+      <c r="G708" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H708" t="inlineStr">
+        <is>
+          <t>A cadeia alimentar representa uma sequência linear, enquanto a teia alimentar mostra várias cadeias interligadas.</t>
+        </is>
+      </c>
+      <c r="I708" t="inlineStr">
+        <is>
+          <t>PH05</t>
+        </is>
+      </c>
+      <c r="J708" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K708" t="inlineStr"/>
+      <c r="L708" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>As ações humanas, como desmatamento e poluição, impactam significativamente os ecossistemas, alterando o equilíbrio ambiental e prejudicando a biodiversidade.
+Qual das ações humanas a seguir tem maior impacto na perda de biodiversidade?</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>Construção de parques eólicos.</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>Prática da agricultura sustentável.</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>Desmatamento de florestas nativas.</t>
+        </is>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>Instalação de sistemas de reaproveitamento de água.</t>
+        </is>
+      </c>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>Programas de reflorestamento.</t>
+        </is>
+      </c>
+      <c r="G709" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H709" t="inlineStr">
+        <is>
+          <t>O desmatamento de florestas nativas leva à perda de habitat e à redução da biodiversidade.</t>
+        </is>
+      </c>
+      <c r="I709" t="inlineStr">
+        <is>
+          <t>PH05</t>
+        </is>
+      </c>
+      <c r="J709" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K709" t="inlineStr"/>
+      <c r="L709" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>O ciclo do carbono é essencial para o equilíbrio ecológico, pois regula a quantidade de dióxido de carbono (CO₂) na atmosfera e envolve processos como a fotossíntese, respiração e decomposição.
+Qual processo do ciclo do carbono contribui diretamente para a remoção de CO₂ da atmosfera?</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>Respiração celular.</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>Combustão de combustíveis fósseis.</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>Fotossíntese.</t>
+        </is>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>Decomposição de matéria orgânica.</t>
+        </is>
+      </c>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>Erosão do solo.</t>
+        </is>
+      </c>
+      <c r="G710" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H710" t="inlineStr">
+        <is>
+          <t>A fotossíntese remove CO₂ da atmosfera ao ser usado pelas plantas para produzir glicose.</t>
+        </is>
+      </c>
+      <c r="I710" t="inlineStr">
+        <is>
+          <t>PH05</t>
+        </is>
+      </c>
+      <c r="J710" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K710" t="inlineStr"/>
+      <c r="L710" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>O aquecimento global, intensificado pelas atividades humanas, resulta em mudanças climáticas, como o derretimento das calotas polares, elevação do nível do mar e eventos climáticos extremos.
+Qual dos seguintes fenômenos não é uma consequência direta do aquecimento global?</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>Elevação do nível do mar.</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>Aumento na frequência de furacões e tempestades.</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>Redução das florestas tropicais devido à seca.</t>
+        </is>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>Aumento da biodiversidade em áreas polares.</t>
+        </is>
+      </c>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>Derretimento das geleiras.</t>
+        </is>
+      </c>
+      <c r="G711" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H711" t="inlineStr">
+        <is>
+          <t>O aumento da biodiversidade em áreas polares não é uma consequência direta do aquecimento global, que tende a reduzir a biodiversidade.</t>
+        </is>
+      </c>
+      <c r="I711" t="inlineStr">
+        <is>
+          <t>PH05</t>
+        </is>
+      </c>
+      <c r="J711" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K711" t="inlineStr"/>
+      <c r="L711" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>O Fordismo consiste em um sistema de produção industrial idealizado e difundido pelo empresário Henry Ford. Como fundador da Ford Motor Company, em 1914, Henry tinha o objetivo de atingir um nível produtivo em que a eficiência industrial atingisse seu ápice. Para isso, criou o método batizado de Fordismo, comprovando que a produção massificada, e padronizada, atingia uma capacidade de produção ímpar.
+Disponível em: https://fm2s.com.br/blog/taylorismo-e-fordismo. Acesso em: 4 nov. 2024.
+O sistema de produção conhecido como Fordismo trouxe diversas inovações para a indústria automobilística. Uma característica fundamental do Fordismo é:</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>Produção artesanal, com foco na individualização.</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>Produção em pequenas séries, com personalização.</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>Produção em massa, com padronização e linhas de montagem</t>
+        </is>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>Produção descentralizada, com várias pequenas fábricas</t>
+        </is>
+      </c>
+      <c r="F712" t="inlineStr">
+        <is>
+          <t>Produção sob demanda, fabricando após a compra.</t>
+        </is>
+      </c>
+      <c r="G712" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H712" t="inlineStr">
+        <is>
+          <t>O Fordismo é caracterizado pela produção em massa e padronização dos produtos, utilizando linhas de montagem para aumentar a eficiência industrial. Esse sistema foi idealizado por Henry Ford com o objetivo de alcançar uma alta capacidade produtiva, reduzindo custos e aumentando a velocidade de produção.</t>
+        </is>
+      </c>
+      <c r="I712" t="inlineStr">
+        <is>
+          <t>PH05</t>
+        </is>
+      </c>
+      <c r="J712" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K712" t="inlineStr"/>
+      <c r="L712" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>O sistema Toyota de produção ou Toyotismo, refere-se a um modelo de produção criado no Japão e instalado na fábrica da Toyota após o término da Segunda Guerra Mundial. Assim, vale ressaltar que esse novo modelo de produção surgiu em decorrência da necessidade das fábricas japonesas se reconstruírem, devido ao grande impacto da Grande Guerra no contexto social e econômico do país.
+Disponível em: https://pucconsultoriajr.com.br/o-que-e-o-toyotismo-e-qual-sua-importancia/. Acesso em 4 de nov de 2024.
+O Toyotismo é um modelo de produção desenvolvido no Japão após a Segunda Guerra Mundial. Uma característica fundamental do Toyotismo é a produção:</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>centralizada em grandes fábricas.</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>em massa com alta padronização</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>com foco na individualização artesanal</t>
+        </is>
+      </c>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>enxuta com redução de desperdícios e just-in-time</t>
+        </is>
+      </c>
+      <c r="F713" t="inlineStr">
+        <is>
+          <t>com grandes estoques para evitar falta de produtos.</t>
+        </is>
+      </c>
+      <c r="G713" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H713" t="inlineStr">
+        <is>
+          <t>O Toyotismo é caracterizado pela produção enxuta, que visa a redução de desperdícios e a implementação do sistema just-in-time, onde a produção é ajustada conforme a demanda, minimizando estoques e aumentando a eficiência. Esse modelo foi desenvolvido pela Toyota no Japão como uma resposta às necessidades de reconstrução pós-guerra.</t>
+        </is>
+      </c>
+      <c r="I713" t="inlineStr">
+        <is>
+          <t>PH05</t>
+        </is>
+      </c>
+      <c r="J713" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K713" t="inlineStr"/>
+      <c r="L713" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>A consequência da Grande Depressão foi a maior crise social do capitalismo com elevadas taxas de desemprego em todo o mundo. Pela primeira vez os fundamentos da teoria liberal foram colocados em xeque. Ou seja, questionava-se o princípio de que somente o mercado regulando a economia é capaz de promover a eficiência dos negócios e a prosperidade econômica. Para solucionar o problema começou a ser praticado pelos estados capitalistas o “New Deal”, implementado pelo presidente Franklin D. Roosevelt nos Estados Unidos entre 1933 e 1937.
+Disponível em: https://smabc.org.br/a-crise-de-1929-e-a-revolucao-russa/. Acesso em: 21 nov 2024. (Adaptado).
+Qual era a proposta do "New Deal" implementado pelo presidente Franklin D. Roosevelt nos Estados Unidos entre 1933 e 1937?</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>Adotar a intervenção de organizações internacionais para solucionar os problemas econômicos.</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>Incentivar a privatização de empresas públicas para aumentar a eficiência.</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>Reduzir a intervenção do Estado na economia para promover a eficiência dos negócios.</t>
+        </is>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>Implementar políticas de intervenção estatal para recuperar a economia e reduzir o desemprego.</t>
+        </is>
+      </c>
+      <c r="F714" t="inlineStr">
+        <is>
+          <t>Promover o livre comércio do mercado pelas grandes empresas para estimular o mercado competitivo.</t>
+        </is>
+      </c>
+      <c r="G714" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H714" t="inlineStr">
+        <is>
+          <t>O "New Deal" foi um conjunto de políticas econômicas e sociais implementadas pelo presidente Franklin D. Roosevelt com o objetivo de recuperar a economia dos Estados Unidos após a Grande Depressão. Essas políticas incluíam a intervenção estatal na economia, a criação de empregos, a regulamentação do mercado financeiro e a implementação de programas sociais para reduzir o desemprego e estimular a recuperação econômica.</t>
+        </is>
+      </c>
+      <c r="I714" t="inlineStr">
+        <is>
+          <t>PH05</t>
+        </is>
+      </c>
+      <c r="J714" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K714" t="inlineStr"/>
+      <c r="L714" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>Compreendendo cidades importantes, como Nova Iorque e Chicago, o Cinturão Fabril concentra indústrias tradicionais, típicas da Primeira e da Segunda Revolução Industrial. Atualmente, muitas indústrias tem migrado da região, em um processo de dispersão industrial, principalmente para estados do sul e do oeste. 
+Disponível em: https://cprepmauss.com.br/site/wp-content/uploads/2019/06/2-EUA-%E2%80%93-Manufacturing-Belt-e-Sun-Belt.pdf. Acesso em: 04 nov 2024.
+Qual é uma característica atual do Cinturão Fabril (Manufacturing Belt) nos Estados Unidos?</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>Predominância de indústrias agrícolas e pecuárias.</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>Áreas de industrialização moderna e pouco poluente.</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>Concentração de indústrias tradicionais, substituídas pelo terceiro setor.</t>
+        </is>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>Concentração de indústrias tradicionais do primeiro setor da economia.</t>
+        </is>
+      </c>
+      <c r="F715" t="inlineStr">
+        <is>
+          <t>Acumulo de indústrias de alta tecnologia, como biotecnologia e robótica.</t>
+        </is>
+      </c>
+      <c r="G715" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H715" t="inlineStr">
+        <is>
+          <t>O Cinturão Fabril tem uma concentração de indústrias tradicionais, e muitas dessas indústrias têm sido substituídas por atividades do terceiro setor (serviços).</t>
+        </is>
+      </c>
+      <c r="I715" t="inlineStr">
+        <is>
+          <t>PH05</t>
+        </is>
+      </c>
+      <c r="J715" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K715" t="inlineStr"/>
+      <c r="L715" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>[...] a criação de riqueza na economia digital está altamente concentrada nos Estados Unidos e na China. O resto do mundo, especialmente países da África e da América Latina, estão muito atrás. Estes dois países possuem 75% de todas as patentes relacionadas à tecnologia blockchain e 50% dos gastos na chamada Internet das Coisas, IoT, na sigla em inglês. 
+As duas economias também detêm mais de 75% do mercado de computação em nuvem e representam 90% da capitalização de mercado das 70 maiores empresas de plataformas digitais.
+Disponível em: https://news.un.org/pt/story/2019/09/1685712. Acesso em: 4 nov 2024.
+Qual é a principal característica da economia digital focada nos Estados Unidos e na China?</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>Elevada produção agrícola e pecuária.</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>Foco em indústrias tradicionais.</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>Concentração de indústrias tecnológicas.</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>Economia baseada em serviços.</t>
+        </is>
+      </c>
+      <c r="F716" t="inlineStr">
+        <is>
+          <t>Dependência da exportação de matérias-primas.</t>
+        </is>
+      </c>
+      <c r="G716" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H716" t="inlineStr">
+        <is>
+          <t>A economia digital está altamente concentrada nos Estados Unidos e na China, com grande domínio em setores tecnológicos, incluindo a maioria das patentes, investimentos, computação em nuvem e capitalização de mercado das principais empresas de plataformas digitais.</t>
+        </is>
+      </c>
+      <c r="I716" t="inlineStr">
+        <is>
+          <t>PH05</t>
+        </is>
+      </c>
+      <c r="J716" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K716" t="inlineStr"/>
+      <c r="L716" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>[...] Os Estados Unidos ainda são, de longe, os maiores investidores do mundo em P&amp;D. Em 1987, o investimento desse País foi quase o dobro do investimento do Japão e da Alemanha Ocidental juntos. No entanto, esses dois países são hoje os maiores concorrentes dos Estados Unidos em áreas de tecnologia de ponta. [...]
+Disponível em: &lt;http://www.scielo.br/scielo.php?script=sci_arttext&amp;pid=S0034-75901990000100006&gt;. Acesso em: 09 mar 2020
+A região dos Estados Unidos em que se desenvolve tecnologia de ponta é</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>Oeste, Sun belt.</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>Leste, Manufacturing belt.</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>Norte, Vale do Silício.</t>
+        </is>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>Sul, Manufacturing belt.</t>
+        </is>
+      </c>
+      <c r="F717" t="inlineStr">
+        <is>
+          <t>Oeste, Manufacturing belt.</t>
+        </is>
+      </c>
+      <c r="G717" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H717" t="inlineStr">
+        <is>
+          <t>A região na qual o EUA desenvolve tecnologia avançada ou ‘de ponta’ é a Oeste, onde localiza-se o Vale do Silício, polo de empresas como Youtube e Google, também conhecida como Sun belt.</t>
+        </is>
+      </c>
+      <c r="I717" t="inlineStr">
+        <is>
+          <t>PH05</t>
+        </is>
+      </c>
+      <c r="J717" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K717" t="inlineStr"/>
+      <c r="L717" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>[...] Os lotes vazios são uma das memórias mais dolorosas da classe média que prosperou em meio ao boom da indústria automobilística de Detroit.
+Isso antes das demissões, que culminaram em centenas de milhares de pessoas abandonando a cidade. Como resultado, bairros inteiros ficaram "às moscas".
+Foi um êxodo sem precedentes. Desde 1960, a população da cidade caiu de 2 milhões de habitantes para os atuais 700 mil. E, quando se imaginava que nada de pior pudesse mais acontecer, há um ano e meio, as autoridades de Detroit declararam a cidade falida. [...]
+Disponível em: &lt;https://www.bbc.com/portuguese/noticias/2015/02/150206_detroit_ressurreicao_lgb&gt;. Acesso em: 13 abr.2020.
+A região de Detroit sofreu essas consequências por que</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>os cinturões agropecuários se tornaram o motor econômico do país.</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>a região de Detroit foi transformada em área estritamente residencial.</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>os impostos ficaram muito altos e as indústrias se deslocaram para outras regiões.</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>com o desenvolvimento do Sun belt a indústria automobilística tinha menos relevância.</t>
+        </is>
+      </c>
+      <c r="F718" t="inlineStr">
+        <is>
+          <t>os custos de produção se tornaram altos demais levando à transferência das indústrias.</t>
+        </is>
+      </c>
+      <c r="G718" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H718" t="inlineStr">
+        <is>
+          <t>A partir de 1960, Detroit começa a declinar na produção industrial automobilística pela transferência das fábricas para outras regiões em virtude dos altos custos de produção, o que levou a cidade a ficar conhecida como rusty belt ou cinturão da ferrugem.</t>
+        </is>
+      </c>
+      <c r="I718" t="inlineStr">
+        <is>
+          <t>PH05</t>
+        </is>
+      </c>
+      <c r="J718" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K718" t="inlineStr"/>
+      <c r="L718" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>As siglas San-San, Bos-Wash e ChiPitts representam qual categoria da geografia urbana?</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>Megalópoles.</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>Conurbação.</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>Megacidades.</t>
+        </is>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>Metrópoles.</t>
+        </is>
+      </c>
+      <c r="F719" t="inlineStr">
+        <is>
+          <t>Cidades globais.</t>
+        </is>
+      </c>
+      <c r="G719" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H719" t="inlineStr">
+        <is>
+          <t>As siglas significam São Francisco e São Diego, Boston e Washington e Chicago e Pittsburg são megalópoles norte americanas, isso é espaços urbanos que vão se integrando.</t>
+        </is>
+      </c>
+      <c r="I719" t="inlineStr">
+        <is>
+          <t>PH05</t>
+        </is>
+      </c>
+      <c r="J719" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K719" t="inlineStr"/>
+      <c r="L719" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>As características da área onde se localiza o Vale do Silício são:</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>Localizada ao sul, desenvolve o setor agropecuário a partir de tecnologia de ponta.</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>Localizada na costa leste, desenvolve o setor de serviços com maquinário industrial de ponta.</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>Localizada no Nordeste, desenvolvimento automobilísticos e resquícios da Primeira e Segunda Revolução.</t>
+        </is>
+      </c>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>Localizada na costa oeste, alto desenvolvimento tecnológico e presença de grandes empresas do período da Terceira Revolução Industrial.</t>
+        </is>
+      </c>
+      <c r="F720" t="inlineStr">
+        <is>
+          <t>Localizada na costa oeste, com baixo grau de desenvolvimento tecnológico abriga as empresas de tecnologia do período pós Segunda Revolução Industrial.</t>
+        </is>
+      </c>
+      <c r="G720" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H720" t="inlineStr">
+        <is>
+          <t>O Vale do Silício é uma área próximo à cidade de São Francisco com foco em desenvolvimento tecnológico da informática e robótica, além de universidades e centros de pesquisa que em parceria formaram alguns tecnopolos.</t>
+        </is>
+      </c>
+      <c r="I720" t="inlineStr">
+        <is>
+          <t>PH05</t>
+        </is>
+      </c>
+      <c r="J720" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K720" t="inlineStr"/>
+      <c r="L720" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>Disponível em: https://admevolution.wordpress.com/2016/11/03/teoria-do-modelo-de-producao-fordista/. Acesso em: 16 abr. 2019.
+O sistema produtivo ilustrado na imagem tem como contexto a</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>Primeira Revolução Industrial.</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>Segunda Revolução Industrial.</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>Terceira Revolução Industrial.</t>
+        </is>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>Primeira Guerra Mundial.</t>
+        </is>
+      </c>
+      <c r="F721" t="inlineStr">
+        <is>
+          <t>Segunda Guerra Mundial.</t>
+        </is>
+      </c>
+      <c r="G721" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H721" t="inlineStr">
+        <is>
+          <t>O contexto histórico da elaboração e implantação do fordismo é a Segunda Revolução Industrial, já que nesse período se iniciou a utilização de petróleo, o motor a combustão, entre outras inovações. Foi nesse momento também que surgiu a indústria automobilística.</t>
+        </is>
+      </c>
+      <c r="I721" t="inlineStr">
+        <is>
+          <t>PH05</t>
+        </is>
+      </c>
+      <c r="J721" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K721" t="inlineStr">
+        <is>
+          <t>8a_ph05_geo_10.jpeg</t>
+        </is>
+      </c>
+      <c r="L721" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>As colônias do Sul, por sua vez, abrigaram uma economia diferente. Seu solo e clima eram mais propícios para uma colonização voltada aos interesses europeus.
+O produto que a economia sulina destacou desde cedo foi o tabaco. A planta implicou permanente expansão agrícola por ser exigente, esgotando rapidamente o solo e obrigando a novas áreas de cultivo. O fumo tomou-se um produto fundamental no Sul.
+A falta de braços para o tabaco em pouco tempo impôs o uso do escravo. Esse trabalho escravo cresceu lentamente, posto que, como vimos, a mão-de-obra branca servil era muito forte no século XVII.
+KARNAL, L. História dos Estados Unidos: Das origens ao século XXI. São Paulo, Contexto, 2007.
+Diferentemente das colônias britânicas na América localizadas na região sul, as colônias da região norte</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>evitaram o comércio externo para focar no povoamento.</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>tinham um clima mais quente e favorável às plantações.</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>priorizavam a plantação de algodão favorecida pelo clima seco.</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>desenvolveram um mercado interno e tinham mão-de-obra livre.</t>
+        </is>
+      </c>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t>sofriam maior fiscalização da Inglaterra por serem mais lucrativas.</t>
+        </is>
+      </c>
+      <c r="G722" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H722" t="inlineStr">
+        <is>
+          <t>As colônias do norte desenvolveram um mercado interno e tinham mão-de-obra livre. O clima frio e seco não favorecia grandes plantações para exportação, levando ao desenvolvimento de um comércio interno e à utilização de mão-de-obra livre.</t>
+        </is>
+      </c>
+      <c r="I722" t="inlineStr">
+        <is>
+          <t>PH05</t>
+        </is>
+      </c>
+      <c r="J722" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K722" t="inlineStr"/>
+      <c r="L722" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>O domínio britânico sobre as colônias que se tornariam os Estados Unidos teve um marco em 1763, quando teve fim a Guerra dos Sete Anos, que envolveu a maioria das grandes potências europeias da época e contrapôs França e Grã-Bretanha.
+Com a assinatura do Tratado de Paris entre França, Espanha e Grã-Bretanha em 1763, os franceses renunciaram às suas aspirações sobre as 13 colônias britânicas na América do Norte.
+Ainda que tenham saído vitoriosos, os britânicos emergiram do conflito em situação delicada, com as finanças públicas em frangalhos.
+Disponível em: https://www.bbc.com/portuguese/internacional-48876152. Acesso em 06 nov. 2024.
+ Para as 13 Colônias britânicas na América, a Guerra dos Sete Anos teve como consequência a(o)</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>abolição da escravidão no norte.</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>negligência salutar da metrópole.</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>independência política da Inglaterra.</t>
+        </is>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>domínio francês sobre seu território.</t>
+        </is>
+      </c>
+      <c r="F723" t="inlineStr">
+        <is>
+          <t>aumento de impostos vindos da metrópole.</t>
+        </is>
+      </c>
+      <c r="G723" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H723" t="inlineStr">
+        <is>
+          <t>A Guerra dos Sete Anos deixou a Inglaterra com um grande prejuízo financeiro, levando a metrópole a aumentar os impostos sobre as 13 Colônias para equilibrar sua economia.</t>
+        </is>
+      </c>
+      <c r="I723" t="inlineStr">
+        <is>
+          <t>PH05</t>
+        </is>
+      </c>
+      <c r="J723" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K723" t="inlineStr"/>
+      <c r="L723" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>Interessada em ajudar a companhia, a metrópole inglesa permitiu que ela deixasse de pagar taxas alfandegárias, em função das dificuldades financeiras em que se encontrava. Outros comerciantes das colônias temeram que a Companhia da Índia Oriental pudesse passar a monopolizar o mercado e opuseram-se então, por razões econômicas, à entrada desse chá no país.
+Um grupo de 50 a 100 homens, fantasiados de índios, foram até o porto de Boston, esvaziaram os navios e atiraram cerca de 45 toneladas de chá ao mar.
+O acontecimento ficou conhecido em todo o país sob o nome de Boston Tea Party (Festa do Chá de Boston). Os homens que lançaram o chá ao mar foram imitados em várias outras cidades do país e acabaram ficando conhecidos como os primeiros heróis do movimento pela independência dos Estados Unidos.
+Disponível em: https://www.dw.com/pt-br/1773-rebeli%C3%A3o-do-ch%C3%A1-em-boston/a-355171. Acesso em: 06 nov. 2024. Adaptado.
+A Festa do Chá de Boston foi um importante momento das tensões entre as 13 Colônias e a Inglaterra pois</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>representou o ódio à cultura inglesa de tomar chá.</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>mostrou que os colonos queriam produtos franceses.</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>foi uma revolta contra os privilégios ingleses na colônia.</t>
+        </is>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>ampliou as disputas religiosas entre colonos e ingleses.</t>
+        </is>
+      </c>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>indicou o apoio dos indígenas à independência da colônias.</t>
+        </is>
+      </c>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H724" t="inlineStr">
+        <is>
+          <t>A Festa do Chá de Boston foi uma revolta contra os privilégios ingleses na colônia, especialmente contra o monopólio do chá e a taxação imposta pela metrópole, que os colonos consideravam injusta.</t>
+        </is>
+      </c>
+      <c r="I724" t="inlineStr">
+        <is>
+          <t>PH05</t>
+        </is>
+      </c>
+      <c r="J724" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K724" t="inlineStr"/>
+      <c r="L724" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>Para o filósofo, a maioria tem o direito de fazer valer seu ponto de vista e, quando o Estado não cumpre seus objetivos e não assegura aos cidadãos a possibilidade de defender seus direitos naturais, os cidadãos podem e devem fazer uma revolução para depô-lo. [...]
+Tais princípios, expostos na obra de Locke, tornaram-se com o tempo parte da tradição política da Inglaterra. Muitos ingleses que emigraram para
+as colônias conheciam as idéias do filósofo.
+[...] A 2 de julho de 1776, o Congresso da Filadélfia acaba decidindo-se pela separação e encarrega uma comissão de redigir a Declaração da Independência. A Declaração fica pronta dois dias depois, em 4 de julho. O teor da Declaração de Independência é típico desse “pensamento ilustrado”, presente nas colônias no século XVIII. 
+KARNAL, L. História dos Estados Unidos: Das origens ao século XXI. São Paulo, Contexto, 2007.
+O texto evidencia que a Independência dos EUA foi inspirada em uma tradição política</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>iluminista e liberal.</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>absolutista e ilustrada.</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>protestante e humanista.</t>
+        </is>
+      </c>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>racionalista e republicana.</t>
+        </is>
+      </c>
+      <c r="F725" t="inlineStr">
+        <is>
+          <t>colonialista e mercantilista.</t>
+        </is>
+      </c>
+      <c r="G725" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H725" t="inlineStr">
+        <is>
+          <t>O texto evidencia que a Independência dos EUA foi inspirada em uma tradição política iluminista e liberal. Isso é demonstrado pela influência das ideias iluministas na Declaração de Independência e na Constituição dos Estados Unidos, que defendiam direitos individuais como vida, liberdade, propriedade privada e busca pela felicidade, além de promoverem uma república federalista e presidencialista.</t>
+        </is>
+      </c>
+      <c r="I725" t="inlineStr">
+        <is>
+          <t>PH05</t>
+        </is>
+      </c>
+      <c r="J725" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K725" t="inlineStr"/>
+      <c r="L725" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>A Declaração de Independência dos Estados Unidos da América e a promulgação da sua Constituição em 1787 trouxeram a conquista da cidadania liberal. Se, por um lado, esta representou importante avanço consolidado com a independência das colônias e a promulgação da Constituição Americana, por outro, a cidadania liberal era marcada pela exclusão da participação política de todos e do gozo dos direitos fundamentais. Por isso, o processo revolucionário representou para os indígenas norte-americanos a perda de direitos, mesmo sendo eles os americanos originários do continente. As mulheres e os homens brancos sem poder aquisitivo também não eram titulares de direitos políticos e por isso não votavam, ou seja, não participavam da vida política do Estado. Ademais, a escravidão perdurou até a Guerra de Secessão (1861-1865).
+ Declarações históricas de direitos humanos. Disponível em: https://enciclopediajuridica.pucsp.br/verbete/530/edicao-1/declaracoes-historicas-de-direitos-humanos. Acesso em: 06 nov. 2024.
+Ao debater os aspectos políticos dos EUA após a independência, o texto aponta uma contradição entre a(o)</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>liberdade religiosa e os argumentos religiosos para a independência.</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>livre mercado na economia nacional e a intervenção no estrangeiro.</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>autonomia externa do povo estadunidense e a exclusão interna.</t>
+        </is>
+      </c>
+      <c r="E726" t="inlineStr">
+        <is>
+          <t>abolição da escravidão e a continuidade do tráfico de escravos.</t>
+        </is>
+      </c>
+      <c r="F726" t="inlineStr">
+        <is>
+          <t>defesa da república e a instalação de um reinado no país.</t>
+        </is>
+      </c>
+      <c r="G726" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H726" t="inlineStr">
+        <is>
+          <t>O texto aponta uma contradição entre a autonomia externa do povo estadunidense, conquistada com a independência, e a exclusão interna de certos grupos, como indígenas, mulheres, homens brancos sem poder aquisitivo e afrodescendentes, da participação política e do gozo dos direitos fundamentais.</t>
+        </is>
+      </c>
+      <c r="I726" t="inlineStr">
+        <is>
+          <t>PH05</t>
+        </is>
+      </c>
+      <c r="J726" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K726" t="inlineStr"/>
+      <c r="L726" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>O desenho a seguir circulou na América do Norte em favor da unificação das Treze Colônias. Durante o século XVIII, os colonos da região viviam um crescente descontentamento com as políticas impostas pela Inglaterra. Observe: 
+Sobre a interpretação do desenho e as motivações para que ele fosse produzido, assinale a alternativa correta.</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>Os colonos viviam em um regime unificado das Trezes Colônias e resistiram à tentativa da Inglaterra de colonizar a região no século XVIII.</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>O desenho sugere a união de algumas das Treze Colônias para combater as políticas tarifárias da Inglaterra, como a Lei do Chá, do Açúcar e do Selo.</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>Os colonizadores eram contra a unificação das Treze Colônias porque isso poderia beneficiar os exércitos indígenas, que defendiam os interesses dos ingleses.</t>
+        </is>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>Os colonos foram estimulados por homens como Benjamin Franklin, autor do desenho, a se unificarem para resistir à divisão territorial da América do Norte entre Espanha e Inglaterra.</t>
+        </is>
+      </c>
+      <c r="F727" t="inlineStr">
+        <is>
+          <t>As colônias do sul se unificaram contra os colonos do norte, uma vez que estes defendiam a escravidão indígena e negra enquanto aqueles, juntos da Inglaterra, eram majoritariamente a favor da abolição.</t>
+        </is>
+      </c>
+      <c r="G727" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H727" t="inlineStr">
+        <is>
+          <t>O desenho de Benjamin Franklin representa algumas das treze colônias como partes de um mesmo animal, uma cobra. Com isso, Franklin defendia a unificação das colônias através de um objetivo comum: a independência frente à Inglaterra, que impunha cada vez mais impostos sobre as Treze Colônias.</t>
+        </is>
+      </c>
+      <c r="I727" t="inlineStr">
+        <is>
+          <t>PH05</t>
+        </is>
+      </c>
+      <c r="J727" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K727" t="inlineStr">
+        <is>
+          <t>8a_ph05_his_06.png</t>
+        </is>
+      </c>
+      <c r="L727" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>“cada colônia organizou-se por grupos distintos entre si, seja por orientação religiosa, interesse econômico ou formação social [...]. Esses fatores embrionários oferecerão os mecanismos para a criação de comércio triangular, em que mercadores da colônia fabricavam rum, que era trocado por escravos. Esses escravos, imprescindíveis para a agricultura, eram negociados no Caribe e nas colônias do Sul.”
+GEBARA, Gassen Zaki. O constitucionalismo nos Estados Unidos da América: das treze colônias à república federativa presidencialista.
+Revista Jurídica Unigran, v. 12, n. 23, p. 57 – 58. Disponível em: &lt;https://www.unigran.br/dourados/revista_juridica/ed_anteriores/23/artigos/artigo04.pdf&gt;. Acesso em: 16 mar. 2020.​
+Durante o período colonial da América do Norte, houve uma divisão entre colônias do sul e colônias do norte. Sobre esse tema, é correto afirmar que as colônias do</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>sul tinham sua economia em torno da produção industrial de materiais têxteis.</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>norte foram ocupadas por britânicos que fugiam dos conflitos religiosos da Europa.</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>norte instituíram a escravização de africanos para trabalhar em plantações de algodão.</t>
+        </is>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>sul foram um fracasso econômico para a Inglaterra, o que resultou em seu total abandono.</t>
+        </is>
+      </c>
+      <c r="F728" t="inlineStr">
+        <is>
+          <t>sul eram organizadas sob o trabalho servil, tendo os indígenas como servos dos colonizadores.</t>
+        </is>
+      </c>
+      <c r="G728" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H728" t="inlineStr">
+        <is>
+          <t>As colônias do Sul foram caracterizadas por seu plantio de algodão voltado à exportação utilizando mão de obra escrava africana. Já as colônias do Norte, pelo seu clima pouco propício a esse tipo de agricultura, tiveram menos atenção da Inglaterra e passou a ser ocupada por britânicos que fugiam das guerras religiosas que ocorriam na Europa durante aquele período.</t>
+        </is>
+      </c>
+      <c r="I728" t="inlineStr">
+        <is>
+          <t>PH05</t>
+        </is>
+      </c>
+      <c r="J728" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K728" t="inlineStr"/>
+      <c r="L728" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>O quadro a seguir retrata um momentos marcantes da história dos Estados Unidos.
+TRUMBULL, John. A morte do general Mercer na Batalha de Princeton, 3 de janeiro de 1777.
+Disponível em: https://pt.wikipedia.org/wiki/Ficheiro:The_Death_of_General_Mercer_at_the_Battle_of_Princeton_January_3_1777.jpeg. Acesso em: 06 mar. 2020
+O quadro tem como contexto a(o)</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>processo de independência dos Estados Unidos, que foi um conflito entre as colônias do sul e as colônias do norte.</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>presença inglesa nas colônias da América do Norte, que diminuiu ao longo do século XVIII, o que desagradou os colonos.</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>manifestação dos colonos do norte e do sul, que teve como estopim a abolição da escravatura no território americano.</t>
+        </is>
+      </c>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>conflito de independência das Treze Colônias, que teve como resultado a vitória dos colonos sobre os ingleses e a fundação dos Estados Unidos.</t>
+        </is>
+      </c>
+      <c r="F729" t="inlineStr">
+        <is>
+          <t>caráter pacífico da independência dos Estados Unidos, na qual ocorreram vários acordos de cooperação entre ingleses e colonos.</t>
+        </is>
+      </c>
+      <c r="G729" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H729" t="inlineStr">
+        <is>
+          <t>O quadro representa um conflito bélico durante a independência dos Estados Unidos (as Treze Colônias). Esse processo foi marcado pelas disputas entre os colonos e os ingleses, resultando na vitória dos primeiros. Os descontentamentos iniciais foram motivados por uma presença mais ostensiva da Inglaterra nas colônias e pelo aumento dos impostos metropolitanos.</t>
+        </is>
+      </c>
+      <c r="I729" t="inlineStr">
+        <is>
+          <t>PH05</t>
+        </is>
+      </c>
+      <c r="J729" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K729" t="inlineStr">
+        <is>
+          <t>8a_ph05_his_08.png</t>
+        </is>
+      </c>
+      <c r="L729" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>Thomas Jefferson foi um dos colonos que participou do processo de Independência das Treze Colônias no século XVIII, movimento norteado pelo Iluminismo.
+“Eu sou a favor da liberdade de religião [...]; sou a favor da liberdade de imprensa, e contra todas as violações que constituem silêncio pela força e não pela razão as reclamações e críticas, justas ou injustas [...]. E eu sou a favor do encorajamento do progresso da ciência em todos os seus ramos”
+The Works of Thomas Jefferson. Collected and Edited by Paul Leicester Ford. Vol. IX. New York/London: The Knickerbocker Press, 1905, p.
+18 – 19. Tradução livre.
+Sobre a relação entre Iluminismo e Independência das Treze Colônias, escolha a alternativa correta:</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>A ciência era entendida como um obstáculo para a plena harmonia das Treze Colônias.</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>A defesa da liberdade em diversos âmbitos da vida humana foi um preceito do Iluminismo adotado por Jefferson.</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>A percepção de Jefferson sobre o Iluminismo incluía o cerceamento da manifestação política em veículos de comunicação.</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>O governo monárquico era defendido tanto pelos Iluministas quanto pelos adeptos da Independência das Trezes Colônias, como Jefferson.</t>
+        </is>
+      </c>
+      <c r="F730" t="inlineStr">
+        <is>
+          <t>O Iluminismo se expressa em Jefferson pela sua posição acerca da religião, pois ele defendia a obrigatoriedade da prática do protestantismo nos Estados Unidos.</t>
+        </is>
+      </c>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H730" t="inlineStr">
+        <is>
+          <t>Conforme o texto de Jefferson, baseado nos preceitos do Iluminismo, seus ideais para o país recém-fundado incluíam a plena liberdade em âmbitos como a religião e a imprensa, assim como da manifestação política. Além disso, a defesa da ciência como um motor do desenvolvimento humano também foi um ideal do Iluminismo adotado por Jefferson.</t>
+        </is>
+      </c>
+      <c r="I730" t="inlineStr">
+        <is>
+          <t>PH05</t>
+        </is>
+      </c>
+      <c r="J730" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K730" t="inlineStr"/>
+      <c r="L730" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>“Em uma carta ao presidente Donald Trump na terça-feira, a prefeita de Washington, a democrata Muriel E. Bowser, alertou que os custos da celebração do 4 de julho de US$ 1,7 milhão, somados às despesas da polícia com os protestos do fim de semana, faliu o fundo especial da prefeitura.”
+FESTA nacional do 4 de julho faliu fundos de Washington, diz prefeita. O Estado de São Paulo, 10 jul. 2019. Disponível em:
+&lt;https://internacional.estadao.com.br/noticias/geral,festa-nacional-do-4-de-julho-faliu-fundos-de-washington-dizprefeito,70002917005&gt;. Acesso em: 19 fev. 2020.
+O 4 de julho é a data que marca a publicação da Declaração de Independência dos Estados Unidos. Sobre esse evento histórico e suas repercussões atuais é possível afirmar que</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>as festas atuais celebram a vitória dos colonos nas lutas contra a escravidão.</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>as comemorações visam relembrar o evento histórico fundador dos Estados Unidos enquanto uma nação soberana.</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>os gastos com a festa, na atualidade, demonstram a tentativa de esconder a derrota das Treze Colônias frente aos ingleses.</t>
+        </is>
+      </c>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>a celebração do 4 de julho expressa o projeto político de manutenção da Inglaterra como metrópole dos Estados Unidos.</t>
+        </is>
+      </c>
+      <c r="F731" t="inlineStr">
+        <is>
+          <t>as homenagens à Declaração da Independência dos Estados Unidos rememoram a derrota das Treze Colônias contra os países europeus colonizadores, como Inglaterra, Espanha e França.</t>
+        </is>
+      </c>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H731" t="inlineStr">
+        <is>
+          <t>A Declaração da Independência dos Estados Unidos afirma a vitória do país frente ao seu então colonizador, a Inglaterra, tornando-se o primeiro país da América a sair vitorioso em uma luta pela independência.</t>
+        </is>
+      </c>
+      <c r="I731" t="inlineStr">
+        <is>
+          <t>PH05</t>
+        </is>
+      </c>
+      <c r="J731" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K731" t="inlineStr"/>
+      <c r="L731" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>O horizonte me pede pra ir tão longe
+Será que eu vou?
+Ninguém tentou
+Se as ondas se abrirem pra mim de verdade
+Com o vento eu vou
+Se eu for não sei ao certo quão longe eu vou
+[...]
+Disponível em: https://www.letras.mus.br/disney/moana-saber-quem-sou/. Acesso em 28 de out. de 2024.
+Quanto à transitividade do verbo em destaque, é correto afirmar que é</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>intransitivo, pois não exige complemento.</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>transitivo direto, pois exige um objeto direto.</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>transitivo indireto, pois exige um objeto indireto.</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>de ligação, pois conecta o sujeito a um predicativo.</t>
+        </is>
+      </c>
+      <c r="F732" t="inlineStr">
+        <is>
+          <t>é bitransitivo, pois exige dois complementos: um direto e um indireto.</t>
+        </is>
+      </c>
+      <c r="G732" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H732" t="inlineStr">
+        <is>
+          <t>O verbo "ir" em "Será que eu vou?" é intransitivo, pois não exige complemento. Desse modo, "eu vou" possui sentido completo, expressando uma ação completa.</t>
+        </is>
+      </c>
+      <c r="I732" t="inlineStr">
+        <is>
+          <t>PH05</t>
+        </is>
+      </c>
+      <c r="J732" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K732" t="inlineStr"/>
+      <c r="L732" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>Esta cidade, na verdade
+Faz a gente se acomodar
+Eu sei muito bem pra onde estou indo
+E sinto que qualquer dia vou chegar
+Estou quase lá
+Quase lá
+Dizem por aí que sou doida
+Mas deixa pra lá
+Lutas e problemas
+Tive já
+Mas agora não vou desistir
+Porque eu estou quase lá
+[...]
+Disponível em: https://www.letras.mus.br/disney/1603277/. Acesso em 28 de out. de 2024
+O verbo em destaque é classificado como</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>intransitivo.</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>bitransitivo.</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>transitivo direto.</t>
+        </is>
+      </c>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>verbo de ligação.</t>
+        </is>
+      </c>
+      <c r="F733" t="inlineStr">
+        <is>
+          <t>transitivo indireto.</t>
+        </is>
+      </c>
+      <c r="G733" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H733" t="inlineStr">
+        <is>
+          <t>O verbo "estar" é um verbo de ligação. Esses verbos não expressam uma ação propriamente dita, mas sim um estado, condição ou característica do sujeito, conectando-o a um predicativo. No trecho da música, "Eu sei muito bem pra onde estou indo" e "porque eu estou quase lá", o verbo "estar" não indica uma ação realizada pelo sujeito, mas sim um estado ou condição em que ele se encontra. Assim, "estou" serve para ligar o sujeito "eu" ao estado de "indo" e "quase lá", funcionando como um verbo de ligação. Na canção, há também o uso do verbo estar como auxiliar, acompanhando o verbo ir (estou indo) para indicar uma ação que ocorrerá próximo do momento da enunciação. Contudo, neste caso, o verbo estar não desempenha função de verbo de ligação, pois não caracteriza o sujeito.</t>
+        </is>
+      </c>
+      <c r="I733" t="inlineStr">
+        <is>
+          <t>PH05</t>
+        </is>
+      </c>
+      <c r="J733" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K733" t="inlineStr"/>
+      <c r="L733" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>O que é o amor para você? Nessa crônica para crianças, vamos acompanhar a história do Amor, um coelho muito sapeca que, ao mesmo tempo, pode ser uma metáfora para próprio o sentimento. Quando pequenas, talvez as crianças não acessem todas as camadas de leitura da obra, mas isso faz que, com cada releitura, a cada nova fase da vida, o livro vá ganhando mais e mais significados para quem o lê. Então, não deixe de experimentar essa obra sensível sobre o amor.
+Disponível em: https://quindim.com.br/blog/cronicas-infantis/ Acesso em 28 de out. de 2024
+O verbo da frase em destaque é classificado como transitivo direto, pois exige</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>um objeto direto e um complemento circunstancial.</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>um objeto direto e um predicativo do objeto.</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>um sujeito e um predicativo do sujeito.</t>
+        </is>
+      </c>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>apenas um objeto direto.</t>
+        </is>
+      </c>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>dois objetos diretos.</t>
+        </is>
+      </c>
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H734" t="inlineStr">
+        <is>
+          <t>No trecho em destaque, o verbo "acompanhar" é transitivo direto, pois é acompanhado de um objeto direto ("a história") e um adjunto adnominal ("do Amor"), que especifica de quem é a história.</t>
+        </is>
+      </c>
+      <c r="I734" t="inlineStr">
+        <is>
+          <t>PH05</t>
+        </is>
+      </c>
+      <c r="J734" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K734" t="inlineStr"/>
+      <c r="L734" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>O meu avô
+Se você ainda não conhece Catarina Sobral, então corra já para ler algum livro dela! A autora, que encanta os pequenos com suas histórias e cores vibrantes da ilustração, faz aqui uma crônica sobre dois homens com vidas totalmente diferentes.
+Um curte tranquilamente a vida de avô e vive aproveitando cada momento. Já o outro está sempre atrasado, correndo para algum lugar, viajando e se estressando com mais trabalho. Mas será que essa vida moderna repleta de pressa e afazeres é realmente a melhor rotina? Descubra lendo com os pequenos essa obra encantadora.
+Disponível em: https://quindim.com.br/blog/cronicas-infantis/ Acesso em 28 de out. de 2024.
+Qual verbo do texto conecta o sujeito da oração ao predicativo?</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>Faz.</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>Está.</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>Corra.</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>Encanta.</t>
+        </is>
+      </c>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>Aproveitando.</t>
+        </is>
+      </c>
+      <c r="G735" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H735" t="inlineStr">
+        <is>
+          <t>O verbo "está" é um verbo de ligação, que conecta o sujeito ao predicativo do sujeito. No trecho "o outro está sempre atrasado", "está" conecta o sujeito "o outro" ao predicativo "sempre atrasado". Portanto, esta alternativa está correta.</t>
+        </is>
+      </c>
+      <c r="I735" t="inlineStr">
+        <is>
+          <t>PH05</t>
+        </is>
+      </c>
+      <c r="J735" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K735" t="inlineStr"/>
+      <c r="L735" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>Qual dos verbos da manchete é intransitivo?</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>Estar.</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>Deter.</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>Chegar.</t>
+        </is>
+      </c>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>Dominar.</t>
+        </is>
+      </c>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>Conseguir.</t>
+        </is>
+      </c>
+      <c r="G736" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H736" t="inlineStr">
+        <is>
+          <t>"Chegar" é um verbo intransitivo. Ele não necessita de um complemento para ter sentido completo, como em "eu cheguei". Embora possa ser seguido por um complemento circunstancial, como "chegar ao trabalho", ele ainda é considerado intransitivo porque o complemento não é necessário para o verbo ter sentido completo.</t>
+        </is>
+      </c>
+      <c r="I736" t="inlineStr">
+        <is>
+          <t>PH05</t>
+        </is>
+      </c>
+      <c r="J736" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K736" t="inlineStr">
+        <is>
+          <t>8a_ph05_por_05.jpg</t>
+        </is>
+      </c>
+      <c r="L736" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>Leia o trecho do livro Em casa, de Bill Bryson, para responder à questão.
+      Quase nada, no século XVII, escapava à astúcia dos que adulteravam alimentos. O açúcar e outros ingredientes caros muitas vezes eram aumentados com gesso, areia e poeira. A manteiga tinha o volume aumentado com sebo e banha. Quem tomasse chá, segundo autoridades da época, poderia ingerir, sem querer, uma série de coisas, desde serragem até esterco de carneiro pulverizado. [...]
+  (Em casa, 2011. Adaptado.)
+Em “Quase nada, no século XVII, escapava à astúcia dos que adulteravam alimentos”, o termo sublinhado é um verbo</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>transitivo direto.</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>intransitivo.</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>de ligação.</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>transitivo indireto.</t>
+        </is>
+      </c>
+      <c r="F737" t="inlineStr">
+        <is>
+          <t>transitivo direto e indireto.</t>
+        </is>
+      </c>
+      <c r="G737" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H737" t="inlineStr">
+        <is>
+          <t>Na frase, o verbo "escapar" exige um complemento que vem precedido por uma preposição, no caso, "à". Isso caracteriza o verbo como transitivo indireto, uma vez que a ação de "escapar" não se completa por si só e precisa de um complemento que indique de quem ou do que se está escapando. Assim, "à astúcia dos que adulteravam alimentos" é o complemento necessário para que a ação do verbo "escapar" faça sentido, confirmando que ele é um verbo transitivo indireto.</t>
+        </is>
+      </c>
+      <c r="I737" t="inlineStr">
+        <is>
+          <t>PH05</t>
+        </is>
+      </c>
+      <c r="J737" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K737" t="inlineStr"/>
+      <c r="L737" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>Apenas a artilharia, na extrema retaguarda, seguia vagarosa e unida, solene quase, na marcha habitual de uma revista, em que parava de quando em quando para varrer a disparos as macegas traiçoeiras; e prosseguindo depois, lentamente, rodando, inabordável, terrível...[...]
+Um a um tombavam os soldados da guarnição estoica. 
+Feridos ou espantados os muares da tração empacavam; torciam de rumo; impossibilitavam a marcha. [...]
+(Os sertões, 2016.)
+Em “Um a um tombavam os soldados da guarnição estoica.”, o termo destacado é um</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>verbo transitivo direto e indireto.</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>verbo intransitivo.</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>verbo transitivo indireto.</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>verbo de ligação.</t>
+        </is>
+      </c>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>verbo transitivo direto.</t>
+        </is>
+      </c>
+      <c r="G738" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H738" t="inlineStr">
+        <is>
+          <t>A intransitividade do verbo “tombar” pode ser conferida quando colocada na sua ordem direta: “Os soldados da guarnição estoica tombavam um a um”. Os verbos intransitivos costumam estar acompanhados de termos de valor adverbial – nesse caso, a expressão “um a um” desempenha esta função, mostrando a maneira como tombavam.</t>
+        </is>
+      </c>
+      <c r="I738" t="inlineStr">
+        <is>
+          <t>PH05</t>
+        </is>
+      </c>
+      <c r="J738" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K738" t="inlineStr"/>
+      <c r="L738" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>O verbo estar pode ser interpretado como sendo verbo de ligação, se indica apenas um estado, ou como verbo intransitivo, se representa a estada em determinado local. Considerando isso, assinale a opção em que o verbo estar seja verbo de ligação na primeira sentença e verbo intransitivo na segunda.</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>Astrogildo estava em casa. Ele estava cansado.</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>Astrogildo estava cansado. Por isso ele estava em casa.</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>Adalgiza está cansada. Ela está doente.</t>
+        </is>
+      </c>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>Publílio está em casa. Ele está em Maceió.</t>
+        </is>
+      </c>
+      <c r="F739" t="inlineStr">
+        <is>
+          <t>Epafrodito está no sítio do tio. Ele está em Rio Largo.</t>
+        </is>
+      </c>
+      <c r="G739" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H739" t="inlineStr">
+        <is>
+          <t>Na oração “Astrogildo estava cansado”, o verbo “estar” liga o estado de “cansado” ao Astrogildo, sendo assim um verbo de ligação. Na oração “Por isso ele estava em casa”, o verbo “estar” indica a estada de Astrogildo em um local, “casa”, sendo assim um verbo intransitivo.</t>
+        </is>
+      </c>
+      <c r="I739" t="inlineStr">
+        <is>
+          <t>PH05</t>
+        </is>
+      </c>
+      <c r="J739" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K739" t="inlineStr"/>
+      <c r="L739" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>“Ele entregou o bilhetinho a Alberto, que se voltou com frieza à mulher [...]”.
+GOETHE, Johann W. Os Sofrimentos do Jovem Weather. Porto Alegre: L&amp;PM, 2001.
+O predicado verbal “entregar”, no enunciado, constitui</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>verbo de ligação.</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>verbo bitransitivo.</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>verbo intransitivo.</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>verbo transitivo direto.</t>
+        </is>
+      </c>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>verbo transitivo indireto.</t>
+        </is>
+      </c>
+      <c r="G740" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H740" t="inlineStr">
+        <is>
+          <t>O predicado verbal “entregar” é classificado como verbo bitransitivo, por tomar um complemento direto (“o bilhetinho”) e um indireto (“a Alberto”).</t>
+        </is>
+      </c>
+      <c r="I740" t="inlineStr">
+        <is>
+          <t>PH05</t>
+        </is>
+      </c>
+      <c r="J740" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K740" t="inlineStr"/>
+      <c r="L740" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>“Trata-se aqui”, objetei eu, “de uma sensação desagradável, da qual cada um de nós gostaria de se ver livre”
+GOETHE, Johann W. Os Sofrimentos do Jovem Weather. Porto Alegre: L&amp;PM, 2001. p. 28
+“E disse aos pequenos que deveriam obedecer à mana Sofia como se fosse ela mesma [...]”.
+GOETHE, Johann W. Os Sofrimentos do Jovem Weather. Porto Alegre: L&amp;PM, 2001.
+“Conversei com Carlota sobre a inacreditável cegueira da alma humana [...]”.
+GOETHE, Johann W. Os Sofrimentos do Jovem Weather. Porto Alegre: L&amp;PM, 2001.
+Observe o complemento dos verbos em destaque nas frases e assinale a alternativa correta.</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>Os verbos em destaque são classificados como intransitivos, por possuírem sentido completo.</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>Os verbos em destaque são classificados como de ligação, por possuírem complementos preposicionados.</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>Os verbos em destaque são classificados como transitivos diretos, por possuírem complementos preposicionados.</t>
+        </is>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>Os verbos em destaque são classificados como transitivos indiretos, por possuírem complementos sem preposição.</t>
+        </is>
+      </c>
+      <c r="F741" t="inlineStr">
+        <is>
+          <t>Os verbos em destaque são classificados como transitivos indiretos, por possuírem complementos preposicionados.</t>
+        </is>
+      </c>
+      <c r="G741" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H741" t="inlineStr">
+        <is>
+          <t>Os verbos em destaque possuem como complemento sintagmas introduzidos por preposição (gostar de, obedecer a, conversar com), sendo, portanto, classificados como verbos transitivos indiretos.</t>
+        </is>
+      </c>
+      <c r="I741" t="inlineStr">
+        <is>
+          <t>PH05</t>
+        </is>
+      </c>
+      <c r="J741" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K741" t="inlineStr"/>
+      <c r="L741" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>Em uma fazenda, o agricultor está planejando a colheita de duas plantações diferentes. Ele anotou a quantidade de sacas de milho e soja colhidas em cada mês. As quantidades de sacas colhidas de milho e soja nos três primeiros meses do ano são representadas pelos polinômios  e  respectivamente. Para facilitar a análise, ele deseja simplificar a expressão que representa a soma das colheitas de milho e soja nesses meses.
+Qual é o polinômio que representa a soma das colheitas de milho e soja nos três primeiros meses do ano?</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>[img:8a_ph05_mat_01_a.png]</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>[img:8a_ph05_mat_01_b.png]</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>[img:8a_ph05_mat_01_c.png]</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>[img:8a_ph05_mat_01_d.png]</t>
+        </is>
+      </c>
+      <c r="F742" t="inlineStr">
+        <is>
+          <t>[img:8a_ph05_mat_01_e.png]</t>
+        </is>
+      </c>
+      <c r="G742" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H742" t="inlineStr">
+        <is>
+          <t>Para encontrar a soma dos polinômios P(x) e Q(x), somamos os termos semelhantes:</t>
+        </is>
+      </c>
+      <c r="I742" t="inlineStr">
+        <is>
+          <t>PH05</t>
+        </is>
+      </c>
+      <c r="J742" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K742" t="inlineStr">
+        <is>
+          <t>8a_ph05_mat_01.png</t>
+        </is>
+      </c>
+      <c r="L742" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>Uma fábrica de embalagens está produzindo caixas com uma estrutura de volume variável. O volume de uma caixa em função do comprimento, largura e altura é dado por  metros cúbicos. Durante um ajuste na linha de produção, a fábrica adiciona mais  metros cúbicos ao volume de cada caixa.
+Qual é o novo volume total de cada caixa?</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>[img:8a_ph05_mat_02_a.png]</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>[img:8a_ph05_mat_02_b.png]</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>[img:8a_ph05_mat_02_c.png]</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>[img:8a_ph05_mat_02_d.png]</t>
+        </is>
+      </c>
+      <c r="F743" t="inlineStr">
+        <is>
+          <t>[img:8a_ph05_mat_02_e.png]</t>
+        </is>
+      </c>
+      <c r="G743" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H743" t="inlineStr">
+        <is>
+          <t>Para determinar o novo volume, somamos os dois polinômios:</t>
+        </is>
+      </c>
+      <c r="I743" t="inlineStr">
+        <is>
+          <t>PH05</t>
+        </is>
+      </c>
+      <c r="J743" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K743" t="inlineStr">
+        <is>
+          <t>8a_ph05_mat_02.png</t>
+        </is>
+      </c>
+      <c r="L743" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>Em uma construção, um engenheiro precisa calcular o volume de concreto necessário para preencher uma laje de tem forma de um paralelepípedo. O volume é dado por V = x³ + 2x² - 5x + 6 metros cúbicos. Durante a execução da obra, foi necessário remover parte do concreto, e o volume removido foi de x² - 3x + 4 metros cúbicos.
+Qual é o volume final de concreto restante na laje após a remoção?</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>[img:8a_ph05_mat_03_a.png]</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>[img:8a_ph05_mat_03_b.png]</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>[img:8a_ph05_mat_03_c.png]</t>
+        </is>
+      </c>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>[img:8a_ph05_mat_03_d.png]</t>
+        </is>
+      </c>
+      <c r="F744" t="inlineStr">
+        <is>
+          <t>[img:8a_ph05_mat_03_e.png]</t>
+        </is>
+      </c>
+      <c r="G744" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H744" t="inlineStr">
+        <is>
+          <t>Para determinar o volume final, subtraímos o volume removido do volume inicial:</t>
+        </is>
+      </c>
+      <c r="I744" t="inlineStr">
+        <is>
+          <t>PH05</t>
+        </is>
+      </c>
+      <c r="J744" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K744" t="inlineStr"/>
+      <c r="L744" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>Um arquiteto está projetando a área de um jardim retangular cujas dimensões são dadas por 2x + 3 metros de largura e x + 5 metros de comprimento. Ele deseja calcular a área total do jardim.
+Qual é a expressão que representa a área do jardim?</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>[img:8a_ph05_mat_04_a.png]</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>[img:8a_ph05_mat_04_b.png]</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>[img:8a_ph05_mat_04_c.png]</t>
+        </is>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>[img:8a_ph05_mat_04_d.png]</t>
+        </is>
+      </c>
+      <c r="F745" t="inlineStr">
+        <is>
+          <t>[img:8a_ph05_mat_04_e.png]</t>
+        </is>
+      </c>
+      <c r="G745" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H745" t="inlineStr">
+        <is>
+          <t>Sabemos que a área de um retângulo é obtida pela multiplicação de sua largura pelo comprimento, assim, a área é dada por: 
+(2x + 3)(x + 5) = 2x(x+5) + 3(x+5) = 2x² + 10x + 3x + 15 = 2x² + 13x + 15</t>
+        </is>
+      </c>
+      <c r="I745" t="inlineStr">
+        <is>
+          <t>PH05</t>
+        </is>
+      </c>
+      <c r="J745" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K745" t="inlineStr"/>
+      <c r="L745" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>Uma empresa de jardinagem está planejando distribuir fertilizante em um grande jardim. A quantidade total de fertilizante disponível é dada pelo polinômio
+em que 
+ representa o número de lotes iguais que compõem cada setor do jardim.
+Cada setor do jardim é formado por 2x lotes iguais, e a empresa deseja dividir a quantidade total de fertilizante igualmente entre os lotes de um setor.
+Qual é o polinômio que representa a quantidade de fertilizante que cada lote receberá?</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>[img:8a_ph05_mat_05_a.png]</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>[img:8a_ph05_mat_05_b.png]</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>[img:8a_ph05_mat_05_c.png]</t>
+        </is>
+      </c>
+      <c r="E746" t="inlineStr">
+        <is>
+          <t>[img:8a_ph05_mat_05_d.png]</t>
+        </is>
+      </c>
+      <c r="F746" t="inlineStr">
+        <is>
+          <t>[img:8a_ph05_mat_05_e.png]</t>
+        </is>
+      </c>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H746" t="inlineStr">
+        <is>
+          <t>Para encontrar a quantidade de fertilizante que cada área do jardim receberá, dividimos o polinômio F(x) por 2x:
+Dividindo cada termo do polinômio por 2x:</t>
+        </is>
+      </c>
+      <c r="I746" t="inlineStr">
+        <is>
+          <t>PH05</t>
+        </is>
+      </c>
+      <c r="J746" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K746" t="inlineStr">
+        <is>
+          <t>8a_ph05_mat_05.png</t>
+        </is>
+      </c>
+      <c r="L746" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>Um triângulo retângulo possui lados com medidas: ,  e , ou seja, cateto, cateto e hipotenusa, respectivamente. Se a área desse tipo de triângulo pode ser obtida pela metade do produto dos catetos, qual polinômio representa a área desse triângulo?</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>[img:8a_ph05_mat_06_a.png]</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>[img:8a_ph05_mat_06_b.png]</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>[img:8a_ph05_mat_06_c.png]</t>
+        </is>
+      </c>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>[img:8a_ph05_mat_06_d.png]</t>
+        </is>
+      </c>
+      <c r="F747" t="inlineStr">
+        <is>
+          <t>[img:8a_ph05_mat_06_e.png]</t>
+        </is>
+      </c>
+      <c r="G747" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H747" t="inlineStr">
+        <is>
+          <t>A área desse triângulo é:</t>
+        </is>
+      </c>
+      <c r="I747" t="inlineStr">
+        <is>
+          <t>PH05</t>
+        </is>
+      </c>
+      <c r="J747" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K747" t="inlineStr">
+        <is>
+          <t>8a_ph05_mat_06.png</t>
+        </is>
+      </c>
+      <c r="L747" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>A área de um retângulo foi calculada, obtendo-se o seguinte polinômio: . Além disso, sabe-se que o comprimento é de . Qual polinômio representa o perímetro desse retângulo?</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>[img:8a_ph05_mat_07_a.png]</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>[img:8a_ph05_mat_07_b.png]</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>[img:8a_ph05_mat_07_c.png]</t>
+        </is>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>[img:8a_ph05_mat_07_d.png]</t>
+        </is>
+      </c>
+      <c r="F748" t="inlineStr">
+        <is>
+          <t>[img:8a_ph05_mat_07_e.png]</t>
+        </is>
+      </c>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H748" t="inlineStr">
+        <is>
+          <t>Para poder calcular o perímetro será necessário calcular a altura antes, dividindo a área pelo comprimento:
+Portanto, o perímetro será:</t>
+        </is>
+      </c>
+      <c r="I748" t="inlineStr">
+        <is>
+          <t>PH05</t>
+        </is>
+      </c>
+      <c r="J748" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K748" t="inlineStr">
+        <is>
+          <t>8a_ph05_mat_07.png</t>
+        </is>
+      </c>
+      <c r="L748" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>Uma parede retangular tem área de  e altura . Qual a medida de seu comprimento?</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>[img:8a_ph05_mat_08_a.png]</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>[img:8a_ph05_mat_08_b.png]</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>[img:8a_ph05_mat_08_c.png]</t>
+        </is>
+      </c>
+      <c r="E749" t="inlineStr">
+        <is>
+          <t>[img:8a_ph05_mat_08_d.png]</t>
+        </is>
+      </c>
+      <c r="F749" t="inlineStr">
+        <is>
+          <t>[img:8a_ph05_mat_08_e.png]</t>
+        </is>
+      </c>
+      <c r="G749" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H749" t="inlineStr">
+        <is>
+          <t>O comprimento da parede é: .</t>
+        </is>
+      </c>
+      <c r="I749" t="inlineStr">
+        <is>
+          <t>PH05</t>
+        </is>
+      </c>
+      <c r="J749" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K749" t="inlineStr">
+        <is>
+          <t>8a_ph05_mat_08.png</t>
+        </is>
+      </c>
+      <c r="L749" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>No projeto de uma casa, dois quartos, um quadrado e outro retangular, tiveram as suas medidas definidas da seguinte forma: o quadrado terá lado  e o retangular terá lados medindo  e .
+Qual a diferença entre as medidas dos perímetros dos quartos?</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F750" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G750" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H750" t="inlineStr">
+        <is>
+          <t>Vamos calcular o perímetro dos quartos:
+Quadrado: ;
+Retangular: .
+Ambos possuem o mesmo perímetro. Logo, a diferença entre os perímetros é zero.</t>
+        </is>
+      </c>
+      <c r="I750" t="inlineStr">
+        <is>
+          <t>PH05</t>
+        </is>
+      </c>
+      <c r="J750" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K750" t="inlineStr">
+        <is>
+          <t>8a_ph05_mat_09.png</t>
+        </is>
+      </c>
+      <c r="L750" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>Na figura 1, um quadrado de lado b foi retirado de um quadrado de lado a. Já a figura 2 é um retângulo com as dimensões indicadas.
+Qual a diferença de área das duas figuras?</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>[img:8a_ph05_mat_10_a.png]</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>[img:8a_ph05_mat_10_b.png]</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>[img:8a_ph05_mat_10_c.png]</t>
+        </is>
+      </c>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F751" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G751" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H751" t="inlineStr">
+        <is>
+          <t>A área da figura 1 é igual a área do quadrado de lado  subtraída da área do quadrado de lado : 
+Já a área da figura 2 é: .
+Como as duas áreas são iguais, a diferença é zero.</t>
+        </is>
+      </c>
+      <c r="I751" t="inlineStr">
+        <is>
+          <t>PH05</t>
+        </is>
+      </c>
+      <c r="J751" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K751" t="inlineStr">
+        <is>
+          <t>8a_ph05_mat_10.png</t>
+        </is>
+      </c>
+      <c r="L751" t="inlineStr">
         <is>
           <t>8ano</t>
         </is>

--- a/questoes.xlsx
+++ b/questoes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L751"/>
+  <dimension ref="A1:L801"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39038,7 +39038,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K702" t="inlineStr"/>
       <c r="L702" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -39098,7 +39097,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K703" t="inlineStr"/>
       <c r="L703" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -39158,7 +39156,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K704" t="inlineStr"/>
       <c r="L704" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -39218,7 +39215,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K705" t="inlineStr"/>
       <c r="L705" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -39277,7 +39273,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K706" t="inlineStr"/>
       <c r="L706" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -39337,7 +39332,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K707" t="inlineStr"/>
       <c r="L707" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -39396,7 +39390,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K708" t="inlineStr"/>
       <c r="L708" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -39455,7 +39448,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K709" t="inlineStr"/>
       <c r="L709" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -39514,7 +39506,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K710" t="inlineStr"/>
       <c r="L710" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -39573,7 +39564,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K711" t="inlineStr"/>
       <c r="L711" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -39633,7 +39623,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K712" t="inlineStr"/>
       <c r="L712" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -39693,7 +39682,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K713" t="inlineStr"/>
       <c r="L713" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -39753,7 +39741,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K714" t="inlineStr"/>
       <c r="L714" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -39813,7 +39800,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K715" t="inlineStr"/>
       <c r="L715" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -39874,7 +39860,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K716" t="inlineStr"/>
       <c r="L716" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -39934,7 +39919,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K717" t="inlineStr"/>
       <c r="L717" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -39996,7 +39980,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K718" t="inlineStr"/>
       <c r="L718" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -40054,7 +40037,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K719" t="inlineStr"/>
       <c r="L719" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -40112,7 +40094,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K720" t="inlineStr"/>
       <c r="L720" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -40237,7 +40218,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K722" t="inlineStr"/>
       <c r="L722" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -40299,7 +40279,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K723" t="inlineStr"/>
       <c r="L723" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -40361,7 +40340,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K724" t="inlineStr"/>
       <c r="L724" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -40424,7 +40402,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K725" t="inlineStr"/>
       <c r="L725" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -40484,7 +40461,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K726" t="inlineStr"/>
       <c r="L726" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -40608,7 +40584,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K728" t="inlineStr"/>
       <c r="L728" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -40735,7 +40710,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K730" t="inlineStr"/>
       <c r="L730" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -40796,7 +40770,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K731" t="inlineStr"/>
       <c r="L731" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -40862,7 +40835,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K732" t="inlineStr"/>
       <c r="L732" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -40934,7 +40906,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K733" t="inlineStr"/>
       <c r="L733" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -40994,7 +40965,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K734" t="inlineStr"/>
       <c r="L734" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -41056,7 +41026,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K735" t="inlineStr"/>
       <c r="L735" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -41179,7 +41148,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K737" t="inlineStr"/>
       <c r="L737" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -41241,7 +41209,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K738" t="inlineStr"/>
       <c r="L738" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -41299,7 +41266,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K739" t="inlineStr"/>
       <c r="L739" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -41359,7 +41325,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K740" t="inlineStr"/>
       <c r="L740" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -41423,7 +41388,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K741" t="inlineStr"/>
       <c r="L741" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -41608,7 +41572,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K744" t="inlineStr"/>
       <c r="L744" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -41668,7 +41631,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K745" t="inlineStr"/>
       <c r="L745" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -42060,6 +42022,3089 @@
         </is>
       </c>
     </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>O postulado de Lavoisier, que afirma que "Na natureza nada se cria, nada se perde, tudo se transforma", é um princípio fundamental da conservação de energia em um sistema.
+Qual das seguintes afirmações é um exemplo do postulado de Lavoisier aplicado à transformação de energia?</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>Uma lâmpada elétrica transforma energia térmica em energia luminosa.</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>A energia elétrica em uma bateria se cria e desaparece conforme o uso.</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>Um gerador eólico cria energia eólica e a converte em energia elétrica.</t>
+        </is>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>Uma usina hidrelétrica destrói energia potencial da água ao gerar eletricidade.</t>
+        </is>
+      </c>
+      <c r="F752" t="inlineStr">
+        <is>
+          <t>A energia química nos alimentos é transformada em energia cinética pelo corpo humano.</t>
+        </is>
+      </c>
+      <c r="G752" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H752" t="inlineStr">
+        <is>
+          <t>A energia química nos alimentos é transformada em energia cinética pelo corpo humano, exemplificando a transformação de energia conforme o postulado de Lavoisier.</t>
+        </is>
+      </c>
+      <c r="I752" t="inlineStr">
+        <is>
+          <t>PH06</t>
+        </is>
+      </c>
+      <c r="J752" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K752" t="inlineStr"/>
+      <c r="L752" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>A energia solar é captada por meio de painéis fotovoltaicos que convertem a luz do sol em eletricidade. Essa tecnologia tem se popularizado em residências devido à sua capacidade de reduzir a dependência de fontes não renováveis.
+Qual é a principal vantagem da energia solar em comparação com fontes não renováveis?</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>Maior eficiência na geração de energia.</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>Menor custo inicial de instalação.</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>Impacto ambiental reduzido.</t>
+        </is>
+      </c>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>Maior disponibilidade de matéria-prima.</t>
+        </is>
+      </c>
+      <c r="F753" t="inlineStr">
+        <is>
+          <t>Menor necessidade de manutenção.</t>
+        </is>
+      </c>
+      <c r="G753" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H753" t="inlineStr">
+        <is>
+          <t>A principal vantagem da energia solar é o impacto ambiental reduzido, pois não emite gases poluentes durante a geração de eletricidade.</t>
+        </is>
+      </c>
+      <c r="I753" t="inlineStr">
+        <is>
+          <t>PH06</t>
+        </is>
+      </c>
+      <c r="J753" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K753" t="inlineStr"/>
+      <c r="L753" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>A energia eólica é gerada a partir do movimento do ar, utilizando turbinas eólicas para converter a energia cinética do vento em energia elétrica. Este tipo de energia é considerado uma fonte renovável.
+Qual das seguintes características é uma desvantagem da energia eólica?</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>Emissão de gases poluentes.</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>Dependência de condições climáticas.</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>Alto custo de operação.</t>
+        </is>
+      </c>
+      <c r="E754" t="inlineStr">
+        <is>
+          <t>Escassez de matéria-prima.</t>
+        </is>
+      </c>
+      <c r="F754" t="inlineStr">
+        <is>
+          <t>Geração de resíduos tóxicos.</t>
+        </is>
+      </c>
+      <c r="G754" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H754" t="inlineStr">
+        <is>
+          <t>A dependência de condições climáticas é uma desvantagem, pois a geração de energia eólica depende da velocidade e constância do vento.</t>
+        </is>
+      </c>
+      <c r="I754" t="inlineStr">
+        <is>
+          <t>PH06</t>
+        </is>
+      </c>
+      <c r="J754" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K754" t="inlineStr"/>
+      <c r="L754" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>A energia hidrelétrica é gerada a partir do movimento da água em rios e reservatórios. Ela é uma das principais fontes de energia renovável utilizadas no mundo, especialmente em países com grande disponibilidade de recursos hídricos.
+Qual é uma das principais desvantagens da construção de usinas hidrelétricas?</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>Baixa eficiência energética.</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>Emissão de gases poluentes.</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>Impacto ambiental significativo.</t>
+        </is>
+      </c>
+      <c r="E755" t="inlineStr">
+        <is>
+          <t>Dependência de importações.</t>
+        </is>
+      </c>
+      <c r="F755" t="inlineStr">
+        <is>
+          <t>Alto custo de operação.</t>
+        </is>
+      </c>
+      <c r="G755" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H755" t="inlineStr">
+        <is>
+          <t>A construção de usinas hidrelétricas pode causar impacto ambiental significativo, como alagamento de áreas e alteração de ecossistemas.</t>
+        </is>
+      </c>
+      <c r="I755" t="inlineStr">
+        <is>
+          <t>PH06</t>
+        </is>
+      </c>
+      <c r="J755" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K755" t="inlineStr"/>
+      <c r="L755" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>A matriz energética mundial é composta por diversas fontes de energia, incluindo tanto fontes renováveis quanto não renováveis.
+Disponível em: https://www.epe.gov.br/pt/abcdenergia/matriz-energetica-e-eletrica.
+Considerando o gráfico apresentado, qual a classificação predominante na matriz energética mundial?</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>Majoritariamente renovável, com mais de 50% das fontes sendo renováveis.</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>Majoritariamente não renovável, com mais de 50% das fontes sendo não renováveis.</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>Equilibrada entre fontes renováveis e não renováveis, cada uma com cerca de 50%.</t>
+        </is>
+      </c>
+      <c r="E756" t="inlineStr">
+        <is>
+          <t>Predominantemente nuclear, com a maior contribuição de energia proveniente de fonte nuclear.</t>
+        </is>
+      </c>
+      <c r="F756" t="inlineStr">
+        <is>
+          <t>Predominantemente solar, com a maior contribuição de energia proveniente de energia solar fotovoltaica.</t>
+        </is>
+      </c>
+      <c r="G756" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H756" t="inlineStr">
+        <is>
+          <t>A matriz energética mundial é majoritariamente não renovável, com mais de 50% das fontes sendo não renováveis.</t>
+        </is>
+      </c>
+      <c r="I756" t="inlineStr">
+        <is>
+          <t>PH06</t>
+        </is>
+      </c>
+      <c r="J756" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K756" t="inlineStr">
+        <is>
+          <t>8a_ph06_cie_05.png</t>
+        </is>
+      </c>
+      <c r="L756" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>É comum usar a palavra energia no dia a dia em diversos contextos. Uma delas é quando falamos da conta de energia de uma casa.
+O termo correto para essa energia é:</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>energia mecânica.</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>máquina mecânica.</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>máquina elétrica.</t>
+        </is>
+      </c>
+      <c r="E757" t="inlineStr">
+        <is>
+          <t>energia elétrica.</t>
+        </is>
+      </c>
+      <c r="F757" t="inlineStr">
+        <is>
+          <t>trabalho elétrico.</t>
+        </is>
+      </c>
+      <c r="G757" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H757" t="inlineStr">
+        <is>
+          <t>A energia que consumimos com aparelhos eletrônicos é a energia elétrica.</t>
+        </is>
+      </c>
+      <c r="I757" t="inlineStr">
+        <is>
+          <t>PH06</t>
+        </is>
+      </c>
+      <c r="J757" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K757" t="inlineStr"/>
+      <c r="L757" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>Plantações de cana-de-açúcar, de soja e de milho podem ser usadas para diversas finalidades como alimentação, pecuária e também como biocombustível. 
+Qual alternativa é um exemplo de biocombustível?</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>Gasolina.</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>Gás natural.</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>Etanol.</t>
+        </is>
+      </c>
+      <c r="E758" t="inlineStr">
+        <is>
+          <t>Querosene.</t>
+        </is>
+      </c>
+      <c r="F758" t="inlineStr">
+        <is>
+          <t>Carvão.</t>
+        </is>
+      </c>
+      <c r="G758" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H758" t="inlineStr">
+        <is>
+          <t>Etanol é um exemplo de biocombustível, produzido a partir da cana-de-açúcar.</t>
+        </is>
+      </c>
+      <c r="I758" t="inlineStr">
+        <is>
+          <t>PH06</t>
+        </is>
+      </c>
+      <c r="J758" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K758" t="inlineStr"/>
+      <c r="L758" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>A energia eólica usa o vento como fonte para gerar energia elétrica. O local ideal para uma instalação de um parque eólico é:</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>onde bate muito Sol.</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>onde venta muito.</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>perto das casas na cidade.</t>
+        </is>
+      </c>
+      <c r="E759" t="inlineStr">
+        <is>
+          <t>perto de grandes rios e lagos.</t>
+        </is>
+      </c>
+      <c r="F759" t="inlineStr">
+        <is>
+          <t>no telhado de cada casa.</t>
+        </is>
+      </c>
+      <c r="G759" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H759" t="inlineStr">
+        <is>
+          <t>Como a energia eólica é gerado por ventos, o lugar ideal para uma instalação de parque eólico é onde venta muito. Geralmente afastado de casas pois as instalações são grandes e barulhentos.</t>
+        </is>
+      </c>
+      <c r="I759" t="inlineStr">
+        <is>
+          <t>PH06</t>
+        </is>
+      </c>
+      <c r="J759" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K759" t="inlineStr"/>
+      <c r="L759" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>A usina de Itaipu é a usina hidrelétrica que mais gera energia no mundo.
+Qual a fonte dessa usina?</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>Força dos ventos.</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>Queima de combustível.</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>Raios solares.</t>
+        </is>
+      </c>
+      <c r="E760" t="inlineStr">
+        <is>
+          <t>Aquecimento da água.</t>
+        </is>
+      </c>
+      <c r="F760" t="inlineStr">
+        <is>
+          <t>Queda da água.</t>
+        </is>
+      </c>
+      <c r="G760" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H760" t="inlineStr">
+        <is>
+          <t>A usina hidrelétrica tem como fonte a energia potencial da queda da água, que se transforma em energia cinética e por fim em energia elétrica.</t>
+        </is>
+      </c>
+      <c r="I760" t="inlineStr">
+        <is>
+          <t>PH06</t>
+        </is>
+      </c>
+      <c r="J760" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K760" t="inlineStr"/>
+      <c r="L760" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>Uma das fontes de energia não renovável é o petróleo, que ainda é bastante usado como combustível para carros, por exemplo.
+Como é formado o petróleo?</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>Pela decomposição de rochas.</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>Pela decomposição da matéria orgânica.</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>Pela queima de matéria orgânica.</t>
+        </is>
+      </c>
+      <c r="E761" t="inlineStr">
+        <is>
+          <t>Pela fermentação de cana-de-açúcar.</t>
+        </is>
+      </c>
+      <c r="F761" t="inlineStr">
+        <is>
+          <t>Pela reação nuclear do Sol.</t>
+        </is>
+      </c>
+      <c r="G761" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H761" t="inlineStr">
+        <is>
+          <t>O petróleo é formado pela decomposição de matéria orgânica durante milhões de anos, geralmente no fundo do oceano.</t>
+        </is>
+      </c>
+      <c r="I761" t="inlineStr">
+        <is>
+          <t>PH06</t>
+        </is>
+      </c>
+      <c r="J761" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K761" t="inlineStr"/>
+      <c r="L761" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>Imagem do tráfego aéreo mundial criada com observações do satélite PROBA-V, da Agência Espacial Europeia.ESA/DLR/SES
+A partir da análise da imagem, pode-se entender que a principal característica da distribuição das rotas aéreas mundiais</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>se concentram principalmente na África.</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>estão distribuídas uniformemente em todo o mundo.</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>se concentram apenas nas regiões polares.</t>
+        </is>
+      </c>
+      <c r="E762" t="inlineStr">
+        <is>
+          <t>se concentram na América do Norte e Europa.</t>
+        </is>
+      </c>
+      <c r="F762" t="inlineStr">
+        <is>
+          <t>são mais densas no Oceano Atlântico Sul.</t>
+        </is>
+      </c>
+      <c r="G762" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H762" t="inlineStr">
+        <is>
+          <t>A análise da imagem mostra que as rotas aéreas mundiais são mais densas nas regiões da América do Norte e Europa. Essas áreas têm uma alta concentração de voos devido à grande quantidade de aeroportos internacionais, alta demanda por viagens aéreas e intensa atividade econômica. As rotas são menos densas em regiões como a África, América do Sul e áreas polares.</t>
+        </is>
+      </c>
+      <c r="I762" t="inlineStr">
+        <is>
+          <t>PH06</t>
+        </is>
+      </c>
+      <c r="J762" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K762" t="inlineStr">
+        <is>
+          <t>8a_ph06_geo_01.png</t>
+        </is>
+      </c>
+      <c r="L762" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>Em Portugal, a terciarização (...) é um fenômeno analisado do ponto de vista econômico e sociológico, e tem sido investigado sob dois aspectos: a). como a expansão do setor terciário, ou seja, do setor de serviços (produtor de bens imateriais e intangíveis) e do comércio; ou b). como um movimento de reestruturação dos sistemas produtivos mediante a transformação interssetorial decorrente da crescente integração das atividades secundárias e terciárias. 
+ALVES, Tales Picchi; ARMOND, Geraldo Henrique de Souza; NASCIMENTO, Cristina Reginato Hoffmann. O processo de terciarização da economia e seu impacto sobre o direito do trabalho: a experiência de Portugal. Revista da Faculdade de Direito da Universidade de São Paulo, v. 104, p. 641-661, jan./dez. 2009.
+Qual é a principal característica da terciarização?</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>Expansão dos serviços e atividades comerciais.</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>Predominância da industrialização sobre os serviços.</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>Exclusiva expansão das atividades agrícolas e pecuárias.</t>
+        </is>
+      </c>
+      <c r="E763" t="inlineStr">
+        <is>
+          <t>Desvalorização do comércio e aumento das exportações.</t>
+        </is>
+      </c>
+      <c r="F763" t="inlineStr">
+        <is>
+          <t>Redução do setor de serviços e aumento do setor primário.</t>
+        </is>
+      </c>
+      <c r="G763" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H763" t="inlineStr">
+        <is>
+          <t>A principal característica da terciarização é a expansão do setor de serviços, que inclui comércio e atividades produtoras de bens imateriais e intangíveis. Esse fenômeno reflete a transformação e modernização dos sistemas produtivos, integrando atividades secundárias e terciárias.</t>
+        </is>
+      </c>
+      <c r="I763" t="inlineStr">
+        <is>
+          <t>PH06</t>
+        </is>
+      </c>
+      <c r="J763" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K763" t="inlineStr"/>
+      <c r="L763" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>Espera-se que a indústria de parques temáticos e de diversões dos EUA registre uma taxa de crescimento de mais de 3,5% durante o período de previsão 2020-2025, como resultado da crescente adoção dos avanços tecnológicos na forma de realidade aumentada e virtual. Espera-se que a inculcação de simuladores de movimento avançados, hidráulicos e pneumáticos, juntamente com o foco na experiência dos clientes, aumente a demanda do mercado nos próximos anos.
+O mercado está relativamente fragmentado, com cerca de 20% das ações detidas pelas cinco principais empresas que incluem Disney Parks and Resorts, Six Flags, Universal Parks and Resorts, Cedar Fair e SeaWorld.
+Disponível em: https://www.mordorintelligence.com/pt/industry-reports/united-states-amusement-and-theme-park-industry. 5 de nov de 2024.
+Considerando a tecnologia e as informações sobre o setor terciário nos Estados Unidos, qual é uma das principais características da indústria de parques temáticos e de diversões?</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>Exclusiva concentração em atividades agrícolas e pecuárias</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>Adoção de tecnologias avançadas para melhorar a experiência dos clientes</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>Predominância da industrialização sobre os serviços nos parques temáticos</t>
+        </is>
+      </c>
+      <c r="E764" t="inlineStr">
+        <is>
+          <t>Redução do setor de serviços e aumento do setor primário nos parques temáticos</t>
+        </is>
+      </c>
+      <c r="F764" t="inlineStr">
+        <is>
+          <t>Desvalorização do comércio e aumento das exportações dos parques temáticos</t>
+        </is>
+      </c>
+      <c r="G764" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H764" t="inlineStr">
+        <is>
+          <t>De acordo com o texto, a indústria de parques temáticos nos EUA está focada no uso de avanços tecnológicos para melhorar a experiência dos clientes, incluindo realidade aumentada e virtual, além de simuladores de movimento avançados. Isso coincide com a informação da imagem, que destaca a importância do setor terciário e a utilização de tecnologias como parte da estratégia para atrair visitantes e impulsionar a economia.</t>
+        </is>
+      </c>
+      <c r="I764" t="inlineStr">
+        <is>
+          <t>PH06</t>
+        </is>
+      </c>
+      <c r="J764" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K764" t="inlineStr"/>
+      <c r="L764" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>O setor terciário, ou setor de serviços, é uma parte fundamental da economia e se distingue dos setores primário e secundário. Em vez de produzir bens físicos, o setor terciário oferece serviços às pessoas e empresas. Isso inclui uma ampla variedade de atividades.
+Disponível em:https://investidorsardinha.r7.com/aprender/setor-terciario/. Acesso em: 5 nov 2024.
+Qual das alternativas abaixo descreve uma característica do setor terciário da economia?</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>Envolve o cultivo de plantas e a criação de animais</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>Refere-se à extração de minerais e outros recursos naturais</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>Concentra-se na transformação de matérias-primas em produtos</t>
+        </is>
+      </c>
+      <c r="E765" t="inlineStr">
+        <is>
+          <t>Oferece serviços como educação, saúde e transporte</t>
+        </is>
+      </c>
+      <c r="F765" t="inlineStr">
+        <is>
+          <t>Inclui a construção de edifícios e infraestrutura.</t>
+        </is>
+      </c>
+      <c r="G765" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H765" t="inlineStr">
+        <is>
+          <t>O setor terciário é responsável pela prestação de serviços, que podem incluir educação, saúde, transporte, turismo, comércio, entre outros. Esses serviços são essenciais para o funcionamento da sociedade e da economia, pois atendem às necessidades das pessoas e das empresas, diferenciando-se dos setores primário e secundário, que lidam com a produção de bens físicos.</t>
+        </is>
+      </c>
+      <c r="I765" t="inlineStr">
+        <is>
+          <t>PH06</t>
+        </is>
+      </c>
+      <c r="J765" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K765" t="inlineStr"/>
+      <c r="L765" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>Disponível em: https://upload.wikimedia.org/wikipedia/commons/8/8b/Class1rr.png. Acesso em 05 de nov de 2024.
+As ferrovias desempenham um papel crucial na infraestrutura de transporte da América Anglo-Saxônica. Elas foram fundamentais para o desenvolvimento econômico e territorial, facilitando o movimento de pessoas e mercadorias. Qual das alternativas abaixo descreve uma característica das ferrovias na América Anglo-Saxônica?</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>Conectam principalmente áreas urbanas dentro dos estados</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>São usadas principalmente para o transporte de minério de ferro</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>Facilitam o transporte de produtos agrícolas entre o norte e o sul</t>
+        </is>
+      </c>
+      <c r="E766" t="inlineStr">
+        <is>
+          <t>Conectam o leste e o oeste, facilitando o comércio</t>
+        </is>
+      </c>
+      <c r="F766" t="inlineStr">
+        <is>
+          <t>São utilizadas exclusivamente para o transporte de passageiros.</t>
+        </is>
+      </c>
+      <c r="G766" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H766" t="inlineStr">
+        <is>
+          <t>A construção de ferrovias transcontinentais foi essencial para conectar as costas leste e oeste, promovendo o desenvolvimento econômico, facilitando o comércio e permitindo a expansão territorial. Essa conexão foi crucial para o crescimento das economias dos Estados Unidos e do Canadá.</t>
+        </is>
+      </c>
+      <c r="I766" t="inlineStr">
+        <is>
+          <t>PH06</t>
+        </is>
+      </c>
+      <c r="J766" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K766" t="inlineStr">
+        <is>
+          <t>8a_ph06_geo_05.png</t>
+        </is>
+      </c>
+      <c r="L766" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>Considerando as afirmações a seguir, assinale a alternativa correta sobre as atividades econômicas do setor terciário nos Estados Unidos.
+I.   O setor terciário é o que mais cresce nos Estados Unidos.
+II.  O setor de serviços ocupa 70% da economia dos Estados Unidos.
+III. O setor terciário é o que mais gera emprego no Estados Unidos.</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>Apenas I e II estão corretas.</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>Apenas I e III estão corretas.</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>Apenas II e III estão corretas.</t>
+        </is>
+      </c>
+      <c r="E767" t="inlineStr">
+        <is>
+          <t>Todas as afirmações estão corretas.</t>
+        </is>
+      </c>
+      <c r="F767" t="inlineStr">
+        <is>
+          <t>Nenhuma das afirmações está correta.</t>
+        </is>
+      </c>
+      <c r="G767" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H767" t="inlineStr">
+        <is>
+          <t>I. Está correta porque o setor terciário é o que mais cresce nos Estados Unidos e no mundo, o seu crescimento desse setor está diretamente ligado à evolução urbana.
+II. Está correta porque o setor de serviços ocupa 70% da economia dos Estados Unidos, seguido das indústrias que ocupam 25% e a agropecuária que ocupa 5%.
+III. Está correta porque o setor terciário é o que mais gera emprego no Estados Unidos, pois os outros setores são muito mecanizados.</t>
+        </is>
+      </c>
+      <c r="I767" t="inlineStr">
+        <is>
+          <t>PH06</t>
+        </is>
+      </c>
+      <c r="J767" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K767" t="inlineStr"/>
+      <c r="L767" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>Logística não é só transporte, é também armazenamento, redes de comunicação, cidades, mercados. Esse conjunto gera verdadeiros territórios corporatizados.
+Disponível em: http://revistapesquisa.fapesp.br/wp-content/uploads/2004/08/012-017-entrevista.pdf. Acesso em: 09 maio 2018.
+A partir da leitura do trecho acima e dos conhecimentos adquiridos, escolha a alternativa que indique corretamente as característica da rede de logística nos Estados Unidos.</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>A rede de logística dos Estados Unidos é muito eficiente devido a forte integração dos transportes, das redes de comunicação, das cidades e dos mercados.</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>A rede de logística dos Estados Unidos apresenta fragilidade devido a baixa interligação das redes de comunicação, mesmo apresentando transportes eficientes.</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>A rede de logística dos Estados Unidos é marcada pela baixa integração dos transportes, o que faz com que ela apresente baixa eficiência.</t>
+        </is>
+      </c>
+      <c r="E768" t="inlineStr">
+        <is>
+          <t>A rede logística dos Estados Unidos é muito complexa e completa devido a sua grande integração, apesar disso, ela apresenta baixa eficiência.</t>
+        </is>
+      </c>
+      <c r="F768" t="inlineStr">
+        <is>
+          <t>A rede logística dos Estados Unidos apresenta grande eficiência e baixa complexidade que é resultado de uma baixa integração.</t>
+        </is>
+      </c>
+      <c r="G768" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H768" t="inlineStr">
+        <is>
+          <t>A rede logística dos Estados Unidos é muito integrada e complexa, ela possui uma grande interligação entre transporte, cidades, redes de comunicação. e mercados interiores e exteriores.</t>
+        </is>
+      </c>
+      <c r="I768" t="inlineStr">
+        <is>
+          <t>PH06</t>
+        </is>
+      </c>
+      <c r="J768" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K768" t="inlineStr"/>
+      <c r="L768" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>As ferrovias são frequentemente indicadas como a melhor opção para o escoamento de cargas e, até mesmo, de pessoas em todo mundo.
+A respeito das ferrovias presentes nos Estados Unidos, marque a alternativa que esteja correta.</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>As ferrovias nos Estados Unidos foram desenvolvidas fortemente desde o período colonial.</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>Os trens são muito relevantes para o transporte de cargas nos Estado Unidos.</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>O uso de ferrovias para o transporte de carga não interfere na quantidade de veículos nas rodovias.</t>
+        </is>
+      </c>
+      <c r="E769" t="inlineStr">
+        <is>
+          <t>O uso de ferrovias é o pior meio de escoar a produção e menos utilizado nos Estados Unidos.</t>
+        </is>
+      </c>
+      <c r="F769" t="inlineStr">
+        <is>
+          <t>O uso de ferrovias nos Estado Unidos é predominante para o transporte de passageiros.</t>
+        </is>
+      </c>
+      <c r="G769" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H769" t="inlineStr">
+        <is>
+          <t>Os trens são muito relevantes para o transporte de carga nos Estados Unidos, trata-se de um tipo de transporte com um custo relativamente menor do que os outros.</t>
+        </is>
+      </c>
+      <c r="I769" t="inlineStr">
+        <is>
+          <t>PH06</t>
+        </is>
+      </c>
+      <c r="J769" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K769" t="inlineStr"/>
+      <c r="L769" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>Um dos fatores que contribuem para o crescimento do setor terciário estadunidense é</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>o desenvolvimento da sociedade de consumo e as mudanças na estrutura demográfica.</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>a queda no avanço dos setores administrativos e econômicos.</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>o investimento estatal na agricultura e incentivos à exportação desses produtos.</t>
+        </is>
+      </c>
+      <c r="E770" t="inlineStr">
+        <is>
+          <t>a criação de leis de proteção ambiental na produção de matérias primas.</t>
+        </is>
+      </c>
+      <c r="F770" t="inlineStr">
+        <is>
+          <t>a baixa concentração demográfica nos grandes centros urbanos.</t>
+        </is>
+      </c>
+      <c r="G770" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H770" t="inlineStr">
+        <is>
+          <t>O crescimento do setor terciário está diretamente relacionado com o desenvolvimento da sociedade e as mudanças na estrutura demográfica, uma vez que o consumo exija uma enorme rede de serviços e a estrutura demográfica mais envelhecida necessite de cuidados extras,  não podendo ser empregada na indústria.</t>
+        </is>
+      </c>
+      <c r="I770" t="inlineStr">
+        <is>
+          <t>PH06</t>
+        </is>
+      </c>
+      <c r="J770" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K770" t="inlineStr"/>
+      <c r="L770" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>Durante o governo de Juscelino Kubitschek, no Brasil, houve em seu programa de governo dois pontos principais: o incentivo à indústria automobilística e ao transporte rodoviário. Entretanto, apesar do sucesso na implementação dessas metas no país, cabe ressaltar que esses feitos trouxeram malefícios no que tange as condições de deslocamento da população.
+CARVALHO, Milena.Governo JK: Política Rodoviarista. Disponível em:&lt;https://medium.com/@milenacarvalho_67013/governo-jkpol%C3%ADtica-rodoviarista-f57f880b3b68&gt;. Acesso em: 24 abr.2020.
+O contexto vivenciado no Brasil de JK possui semelhanças com o final do século XIX nos EUA, essas semelhanças correspondem:</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>Ao incentivo do transporte coletivo.</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>A expansão das rodovias.</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>A colonização do litoral.</t>
+        </is>
+      </c>
+      <c r="E771" t="inlineStr">
+        <is>
+          <t>Ao início da industrialização.</t>
+        </is>
+      </c>
+      <c r="F771" t="inlineStr">
+        <is>
+          <t>Ao pico do êxodo rural.</t>
+        </is>
+      </c>
+      <c r="G771" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H771" t="inlineStr">
+        <is>
+          <t>No Brasil, tal como nos EUA, a implantação da indústria automobilística veio acompanhada da política rodoviarista, que consiste em priorizar o transporte de cargas e pessoas através de rodovias.</t>
+        </is>
+      </c>
+      <c r="I771" t="inlineStr">
+        <is>
+          <t>PH06</t>
+        </is>
+      </c>
+      <c r="J771" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K771" t="inlineStr"/>
+      <c r="L771" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>O palácio foi palco de casamentos estratégicos e visitas de Estado. Mas a propriedade foi construída, na verdade, por outro motivo: diversão. Com seu parque arrebatador e os jardins ornamentados menores, o local era voltado para o prazer — e a luxúria. [...]
+O isolamento da monarquia em Versalhes desempenhou um papel na Revolução Francesa. [...]
+"Versalhes ajudou a fazer com que [Luís 16 e Maria Antonieta] se desconectassem da realidade", afirma Vergé-Franceschi.
+Disponível em: https://www.bbc.com/portuguese/vert-tra-64393620. Acesso em: 05 nov. 2024.
+Disponível em: https://commons.wikimedia.org/wiki/File:Vue_a%C3%A9rienne_du_domaine_de_Versailles_par_ToucanWings_-_Creative_Commons_By_Sa_3.0_-_073.jpg. Acesso em: 05 nov. 2024.
+O Palácio de Versalhes desempenhou um papel na Revolução Francesa na medida em que</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>serviu de abrigo para os membros da Igreja que fugiam dos protestantes.</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>foi construído pelos revolucionários para ser um espaço de discussão democrática.</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>era palco de reuniões dos sans-culottes para festas e para denúncias ao absolutismo.</t>
+        </is>
+      </c>
+      <c r="E772" t="inlineStr">
+        <is>
+          <t>representava as riquezas e privilégios da nobreza em comparação com a miséria do povo.</t>
+        </is>
+      </c>
+      <c r="F772" t="inlineStr">
+        <is>
+          <t>permitiu a reorganização da aristocracia e do clero para acabar com a revolta da burguesia.</t>
+        </is>
+      </c>
+      <c r="G772" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H772" t="inlineStr">
+        <is>
+          <t>O Palácio de Versalhes desempenhou um papel na Revolução Francesa ao simbolizar as riquezas e os privilégios da nobreza em contraste com a miséria do povo. O isolamento da monarquia em Versalhes contribuiu para a desconexão de Luís XVI e Maria Antonieta da realidade das condições de vida do povo francês, exacerbando o descontentamento popular e alimentando o fervor revolucionário.</t>
+        </is>
+      </c>
+      <c r="I772" t="inlineStr">
+        <is>
+          <t>PH06</t>
+        </is>
+      </c>
+      <c r="J772" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K772" t="inlineStr"/>
+      <c r="L772" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>Os Estados Gerais eram uma espécie de conselho consultivo do rei formado pela nobreza, clero e pelo terceiro estado. Este grupo, por sua vez, era composto pelos camponeses (pequenos proprietários, arrendatários, assalariados rurais), a burguesia (banqueiros, comerciantes, profissionais liberais e proprietários) e trabalhadores urbanos (pequenos lojistas, artesãos e assalariados em gerais) conhecidos como sans-cullotes.
+Nessa perspectiva, os Estados Gerais foram convocados para uma assembleia, cuja atribuição era realizar uma reforma nas leis francesas. O problema é que o sistema de votação adotado era a contagem por estado no lugar do número de membros. Assim, o clero e a nobreza formaram uma aliança, impedindo que as reivindicações do terceiro estado fossem atendidas.
+BUENO, I.; PALAR, J.; SILVA, M. O primado da Constituição como fator de desenvolvimento das relações de produção capitalistas. Disponível em: https://www.scielo.br/j/rdp/a/NrfjxP5hX4zczBbt4CfJfBd/. Acesso em: 05 nov. 2024.
+A dinâmica dos Estados Gerais na França do final do século XVIII levou a um(a)</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>reforço dos poderes do rei combinado com medidas de inspiração iluminista típicas do despotismo esclarecido.</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>reforma política que consolidou a monarquia constitucional e a divisão dos poderes entre os três estados.</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>revolução promovida pelo terceiro estado que buscou acabar com os privilégios dos demais estados.</t>
+        </is>
+      </c>
+      <c r="E773" t="inlineStr">
+        <is>
+          <t>legitimação dos poderes dos senhores feudais do segundo estado sobre seus territórios e servos.</t>
+        </is>
+      </c>
+      <c r="F773" t="inlineStr">
+        <is>
+          <t>destituição dos membros do primeiro estado por se recusarem a aceitar a reforma religiosa.</t>
+        </is>
+      </c>
+      <c r="G773" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H773" t="inlineStr">
+        <is>
+          <t>A dinâmica dos Estados Gerais na França do final do século XVIII levou a uma revolução promovida pelo terceiro estado. Frustrados com a falta de representatividade e os privilégios do clero e da nobreza, os membros do terceiro estado se proclamaram Assembleia Nacional e iniciaram um movimento revolucionário que buscou acabar com os privilégios dos demais estados e estabelecer uma nova ordem política e social.</t>
+        </is>
+      </c>
+      <c r="I773" t="inlineStr">
+        <is>
+          <t>PH06</t>
+        </is>
+      </c>
+      <c r="J773" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K773" t="inlineStr"/>
+      <c r="L773" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>Pois embora a extravagância de Versailles tenha sido constantemente culpada pela crise, os gastos da corte só significavam 6% dos gastos totais em 1788. A guerra, a marinha e a diplomacia constituíam um quarto, e metade era consumida pelo serviço da dívida existente. A guerra e a divida — a guerra americana e sua divida — partiram a espinha da monarquia.
+Assim, a Revolução começou como uma tentativa aristocrática de recapturar o Estado. Esta tentativa foi mal calculada por duas razões: ela subestimou as intenções independentes do “Terceiro Estado” — a entidade fictícia destinada a representar todos os que não eram nobres nem membros do clero, mas de fato dominada pela classe média — e desprezou a profunda crise sócio-econômicas no meio da qual lançava suas exigências políticas.
+HOBSBAWM, E. A Era das Revoluções. São Paulo, Paz e Terrra, 2012, 5ª ed.
+Uma das razões que desencadearam a Revolução Francesa foi a(o)</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>disputa entre a aristocracia pela exploração dos territórios coloniais como meio de pagar as dívidas de guerra.</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>crise econômica devido a guerras e a tentativa da aristocracia de fazer com que o terceiro estado a pagasse.</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>cobrança por parte da Igreja de dízimo sobre o Estado francês e seu respectivo endividamento.</t>
+        </is>
+      </c>
+      <c r="E774" t="inlineStr">
+        <is>
+          <t>desequilíbrio total das finanças francesas devido ao custeio da vida luxuosa da aristocracia.</t>
+        </is>
+      </c>
+      <c r="F774" t="inlineStr">
+        <is>
+          <t>falta de recursos para a guerra devido aos gastos excessivos com auxílios sociais.</t>
+        </is>
+      </c>
+      <c r="G774" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H774" t="inlineStr">
+        <is>
+          <t>A crise econômica devido às guerras e a tentativa da aristocracia de fazer com que o terceiro estado pagasse as dívidas foram fatores cruciais para o desencadeamento da Revolução Francesa. O texto menciona que a guerra e a dívida, especialmente a guerra americana, foram responsáveis por quebrar a espinha da monarquia. Além disso, a tentativa aristocrática de recapturar o Estado subestimou as intenções do terceiro estado e desprezou a crise socioeconômica.</t>
+        </is>
+      </c>
+      <c r="I774" t="inlineStr">
+        <is>
+          <t>PH06</t>
+        </is>
+      </c>
+      <c r="J774" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K774" t="inlineStr"/>
+      <c r="L774" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>Em 14 de julho de 1789, sete pessoas estavam presas na Bastilha, incluindo quatro falsificadores, um irlandês “lunático”, um jovem aristocrata degenerado, preso a pedido de sua família, e um homem que havia conspirado para assassinar Luís XV da França mais de 30 anos atrás.
+Ainda assim, a ideia da Bastilha era mais importante que a realidade. As pessoas ainda estavam sendo arbitrariamente presas e levadas para prisões, uma prática simbolizada pela Bastilha.
+[...] O prêmio que a multidão buscava estava lá dentro: 250 barris de pólvora.
+Disponível em: https://www.worldhistory.org/trans/pt/1-20766/a-tomada-da-bastilha/. Acesso em: 05 nov. 2024.
+O texto evidencia que, na Revolução Francesa, a Tomada da Bastilha</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>marcou o envolvimento das massas na revolução e um momento de avanço contra os poderes estabelecidos.</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>buscou se opor à formação da Assembleia Nacional em favor do foco na destruição do patrimônio do rei.</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>efetivou a aliança entre o terceiro estado e os demais estados contra da dinastia de Luís XVI.</t>
+        </is>
+      </c>
+      <c r="E775" t="inlineStr">
+        <is>
+          <t>resultou em um desgaste das forças revolucionárias francesas, levando ao fim da revolução.</t>
+        </is>
+      </c>
+      <c r="F775" t="inlineStr">
+        <is>
+          <t>não teve impacto na revolução por ter libertado poucas pessoas e chamado pouca atenção.</t>
+        </is>
+      </c>
+      <c r="G775" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H775" t="inlineStr">
+        <is>
+          <t>A Tomada da Bastilha marcou o envolvimento das massas na Revolução e um momento de avanço contra os poderes estabelecidos. O texto destaca que a queda da Bastilha simbolizou a vitória do povo sobre a opressão e a arbitrariedade do poder monárquico, desencadeando uma onda de ação revolucionária em toda a França.</t>
+        </is>
+      </c>
+      <c r="I775" t="inlineStr">
+        <is>
+          <t>PH06</t>
+        </is>
+      </c>
+      <c r="J775" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K775" t="inlineStr"/>
+      <c r="L775" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>A classe média e a aristocracia imediatamente aceitaram o inevitável: todos os privilégios feudais foram oficialmente abolidos embora, quando a situação política se acalmou, fosse fixado um preço rígido para sua remissão. O feudalismo só foi finalmente abolido em 1793. No final de agosto, a revolução tinha também adquirido seu manifesto formal, a Declaração dos Direitos do Homem e do Cidadão.
+HOBSBAWM, E. A Era das Revoluções. São Paulo, Paz e Terra, 2021, 5ª ed.
+O texto associa a Declaração dos Direitos do Homem e do Cidadão, aprovada na Revolução Francesa, à(ao)</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>abolição dos privilégios da aristocracia e do clero.</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>fortalecimento da intervenção do Estado na economia.</t>
+        </is>
+      </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>livre interpretação da Bíblia e à redução do poder da Igreja.</t>
+        </is>
+      </c>
+      <c r="E776" t="inlineStr">
+        <is>
+          <t>formação das monarquias nacionais com poderes centralizados.</t>
+        </is>
+      </c>
+      <c r="F776" t="inlineStr">
+        <is>
+          <t>divisão de terras entre a aristocracia e ao trabalho servil camponês.</t>
+        </is>
+      </c>
+      <c r="G776" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H776" t="inlineStr">
+        <is>
+          <t>A Declaração dos Direitos do Homem e do Cidadão, aprovada durante a Revolução Francesa, está diretamente associada à abolição dos privilégios da aristocracia e do clero, promovendo os princípios de igualdade e justiça social.</t>
+        </is>
+      </c>
+      <c r="I776" t="inlineStr">
+        <is>
+          <t>PH06</t>
+        </is>
+      </c>
+      <c r="J776" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K776" t="inlineStr"/>
+      <c r="L776" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>“diante de uma revolução como a que se produziu na França, que altera a ordem político-social, ‘insulta publicamente as ideias religiosas e viola tudo o que é sagrado para os homens’, não é mais possível, e nem mesmo permitido, que os outros Estados permaneçam apartados.”
+LOSURDO, Domenico. A revolução, a nação e paz. Estudos Avulsos, São Paulo, v. 22, n. 62, p. 12. Disponível em: &lt;http://www.scielo.br/scielo.php?script=sci_arttext&amp;pid=S0103-40142008000100003&amp;lang=pt&gt;. Acesso em: 19 mar. 2020
+O trecho acima expressa a opinião de Edmund Burke, político inglês, sobre os rumos da internacionalização da Revolução Francesa.
+Assinale a alternativa que contenha informações corretas sobre o que significou uma “revolução” para o contexto.</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>O conceito se define pela radicalidade de seus meios e de seus resultados.</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>A noção revolucionária se limita a ações de cunho nacional, como foi a Revolução Francesa.</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>A palavra tem como significado a manutenção de valores herdados em gerações anteriores.</t>
+        </is>
+      </c>
+      <c r="E777" t="inlineStr">
+        <is>
+          <t>O termo expressa mudanças nas instituições políticas e sociais, mas não na mentalidade popular.</t>
+        </is>
+      </c>
+      <c r="F777" t="inlineStr">
+        <is>
+          <t>A expressão denota uma melhoria do funcionamento das instituições, por isso foi defendida por Burke.​</t>
+        </is>
+      </c>
+      <c r="G777" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H777" t="inlineStr">
+        <is>
+          <t>O termo “revolução” é definido, em primeiro lugar, pelos seus modos extremos de execução, conforme se vê pela declaração de Burke, aterrorizado com as ações revolucionárias. Em segundo lugar, a revolução resulta em mudanças profundas no objeto mobilizado, atingindo o maior número de esferas possíveis e não conhecendo fronteiras nacionais.</t>
+        </is>
+      </c>
+      <c r="I777" t="inlineStr">
+        <is>
+          <t>PH06</t>
+        </is>
+      </c>
+      <c r="J777" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K777" t="inlineStr"/>
+      <c r="L777" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>“As mães, as filhas, as irmãs, representantes da nação, reivindicam constituírem-se em Assembleia Nacional. Considerando que a ignorância, o esquecimento ou o menosprezo dos direitos da mulher são as únicas causas das desgraças públicas e da corrupção do governo, resolveram expor, em uma declaração solene, os direitos naturais inalienáveis e sagrados da mulher.”
+GOUGES, Olympe de. Declaração dos Direitos da Mulher e da Cidadã. (1791). Em: INTERthesis – Revista Internacional Interdisciplinar, v. 4, n. 1, Florianópolis, jan./jun. 2007.
+Sobre a Declaração dos Direitos do Homem e do Cidadão e suas contradições, assinale a alternativa correta.</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>O registro demonstra preocupação quanto à escravidão que ocorria na zona rural francesa.</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>As propostas revolucionárias eram contrárias à ideia de que pessoas não nobres deveriam ter direitos básicos.</t>
+        </is>
+      </c>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>O documento considera que todas as pessoas, independente de classe ou gênero, possuem direitos naturais adquiridos no nascimento.</t>
+        </is>
+      </c>
+      <c r="E778" t="inlineStr">
+        <is>
+          <t>O escrito foi produzido pelo alto clero que desejava incluir os padres de pequenas províncias em um sistema de privilégios eclesiásticos.</t>
+        </is>
+      </c>
+      <c r="F778" t="inlineStr">
+        <is>
+          <t>A Declaração estipulava que a propriedade era um bem natural, o que expressa um interesse da burguesia, e não da maioria da população.</t>
+        </is>
+      </c>
+      <c r="G778" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H778" t="inlineStr">
+        <is>
+          <t>A Declaração dos Direitos do Homem e do Cidadão foi um documento escrito pelos revolucionários franceses e tinha como objetivo combater os privilégios do Primeiro e do Segundo Estado, garantindo igualdade entre todos os cidadãos. No entanto, não incluía as mulheres em sua redação, conforme demonstrado pelo texto-base, e o reconhecimento da propriedade privada como um direito natural não ia de encontro com o interesse da maioria da população, os trabalhadores, enquanto favorecia os grandes burgueses.</t>
+        </is>
+      </c>
+      <c r="I778" t="inlineStr">
+        <is>
+          <t>PH06</t>
+        </is>
+      </c>
+      <c r="J778" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K778" t="inlineStr"/>
+      <c r="L778" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>“Uma parceria entre especialistas em história, computação e ciências cognitivas está ajudando a mostrar como as ideias surgiram e vicejaram logo após a Revolução Francesa. Os pesquisadores analisaram transcrições de 40 mil discursos da Assembleia Nacional Constituinte. Enquanto os representantes à esquerda no espectro político utilizavam uma retórica inovadora para apresentar suas ideias, os mais conservadores adotavam um discurso com combinações de palavras familiares para se opor a mudanças.”
+CIÊNCIA de dados reconstrói a retórica da Revolução Francesa. Revista Fapesp, ed. 267, mai. 2018. Adaptado. Disponível em:
+&lt;https://revistapesquisa.fapesp.br/2018/05/23/ciencia-de-dados-reconstroi-a-retorica-da-revolucao-francesa/&gt;. Acesso em: 19 mar.2020. 
+Vicejar: brilhar, ostentar.
+A Assembleia Nacional Constituinte foi formada por grupos diversos porque</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>foi organizada pelo clero, pela nobreza e pelo Terceiro Estado, na busca de conciliar todos os interesses.</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>houve um decreto real para que todos estamentos fossem igualmente contemplados pela nova Constituição.</t>
+        </is>
+      </c>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>acolheu todos os membros do Terceiro Estado, o que resultou em consenso durante a escrita da Constituição.</t>
+        </is>
+      </c>
+      <c r="E779" t="inlineStr">
+        <is>
+          <t>almejava limitar a participação popular, garantindo que apenas o Primeiro e o Segundo Estado participassem do evento.</t>
+        </is>
+      </c>
+      <c r="F779" t="inlineStr">
+        <is>
+          <t>foi composta pelos membros do Terceiro Estado, que compreendia os mais diversos grupos, como trabalhadores rurais e urbanos, burgueses, entre outros.</t>
+        </is>
+      </c>
+      <c r="G779" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H779" t="inlineStr">
+        <is>
+          <t>A Assembleia Nacional Constituinte foi uma reação do Terceiro Estado à Convocação dos Estados Gerais, na qual o estamento não teve seus interesses contemplados. O Terceiro Estado era composto por toda a população que não pertencia ao alto clero e nem à nobreza, ou seja, compreendia uma população heterogênea. Por isso, na Assembleia Nacional Constituinte, houve posicionamentos distintos, conforme foi expresso pelo excerto.</t>
+        </is>
+      </c>
+      <c r="I779" t="inlineStr">
+        <is>
+          <t>PH06</t>
+        </is>
+      </c>
+      <c r="J779" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K779" t="inlineStr"/>
+      <c r="L779" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>“As revoluções camponesas são movimentos vastos, disformes, anônimos, mas irresistíveis. O que transformou uma epidemia de inquietação camponesa em uma convulsão irreversível foi a combinação dos levantes das cidades provincianas com uma onda de pânico de massa, que se espalhou de forma obscura mas rapidamente por grandes regiões do país: o chamado Grande Medo.”
+HOBSBAWN, Eric. A era das Revoluções. Rio de Janeiro: Paz e Terra, 1977, p. 80.
+Acerca da participação dos trabalhadores rurais do processo da Revolução Francesa, escolha a alternativa correta.</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>O Grande Medo foi organizado por artesãos provincianos que se revoltavam contra a Igreja Católica.</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>Os camponeses tiveram pouca expressão durante a Revolução Francesa pois o país era industrializado.</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>A produção agrícola francesa decaiu ao longo do século XVIII porque os camponeses organizavam motins constantemente.</t>
+        </is>
+      </c>
+      <c r="E780" t="inlineStr">
+        <is>
+          <t>A crise alimentícia pela qual a França passava estimulou a revolta dos camponeses, pois eles lidavam com a fome e com a crise econômica.</t>
+        </is>
+      </c>
+      <c r="F780" t="inlineStr">
+        <is>
+          <t>Os trabalhadores rurais eram a favor dos impostos feudais, ao contrário dos trabalhadores urbanos e, por isso, não houve conciliação entre esses grupos.</t>
+        </is>
+      </c>
+      <c r="G780" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H780" t="inlineStr">
+        <is>
+          <t>Uma das causas de insatisfação dos franceses durante o século XVIII foi a crise de subsistência, resultado de más colheitas. Os trabalhadores rurais, além de terem que lidar com a fome, tinham seu principal meio de vida, a venda de produtos agrícolas, prejudicado. Por isso, os camponeses se mostraram insatisfeitos e reagiram com saques e linchamentos a nobres, atos que configuraram o Grande Medo.</t>
+        </is>
+      </c>
+      <c r="I780" t="inlineStr">
+        <is>
+          <t>PH06</t>
+        </is>
+      </c>
+      <c r="J780" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K780" t="inlineStr"/>
+      <c r="L780" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>HELMAN, Isidore-Stanislaus; MONET, Charles. A abertura dos Estados Gerais, em Versalhes, em 5 de maio de 1789.
+Disponível em: &lt;https://pt.wikipedia.org/wiki/Ficheiro:Estatesgeneral.jpg&gt;. Acesso em: 19 mar. 2020. 
+A Convocação dos Estados Gerais de 1789, retratada na pintura, foi um(a)</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>organização rural para combater os impostos feudais.</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>festa organizada pelos reis franceses para celebrar a vitória na guerra contra a Inglaterra.</t>
+        </is>
+      </c>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>manifestação dos burgueses pelo fim da isenção tributária aos membros do Terceiro Estado.</t>
+        </is>
+      </c>
+      <c r="E781" t="inlineStr">
+        <is>
+          <t>conselho consultivo convocado pelo rei para discutir formas de superar a crise econômica.</t>
+        </is>
+      </c>
+      <c r="F781" t="inlineStr">
+        <is>
+          <t>reunião entre o Primeiro e o Segundo Estado para interromper os movimentos revolucionários iniciados no campo.</t>
+        </is>
+      </c>
+      <c r="G781" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H781" t="inlineStr">
+        <is>
+          <t>A Convocação dos Estados Gerais era um dispositivo que o rei poderia acionar e que deveria conter representantes dos três Estados, além de possuir caráter consultivo, e não deliberativo. Luís XVI, então rei da França, organizou a reunião para lidar com a crise econômica pela qual o país passava.</t>
+        </is>
+      </c>
+      <c r="I781" t="inlineStr">
+        <is>
+          <t>PH06</t>
+        </is>
+      </c>
+      <c r="J781" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K781" t="inlineStr">
+        <is>
+          <t>8a_ph06_his_10.png</t>
+        </is>
+      </c>
+      <c r="L781" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>Piotr foi em direção à saída. Ivan Ilitch estava com medo de ficar sozinho. “O que poderia detê-lo? Sim, o remédio.”
+- Piotr, dê-me o remédio.
+“Porque, talvez, o remédio ainda ajude.”
+Ele pegou a colher e tomou.
+“Não, não ajuda. Isso tudo é um absurdo, um engano”, decidiu ele, assim que sentiu aquele gosto enjoativo, familiar, irremediável. “Não, não posso acreditar. Mas a dor, a dor, se ao menos ela sossegasse por um minuto.”
+TOLSTÓI, Liev. A Morte de Ivan Ilitch. Principis. p. 70.
+O trecho acima corresponde a uma passagem do diálogo entre Ivan Ilich e seu criado Piotr, extraído da novela russa A morte de Ivan Ilitch. Na primeira fala de Ivan, há um verbo</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>bitransitivo e dois objetos diretos.</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>transitivo direto e um objeto direto.</t>
+        </is>
+      </c>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>transitivo direto e um objeto indireto.</t>
+        </is>
+      </c>
+      <c r="E782" t="inlineStr">
+        <is>
+          <t>bitransitivo e um objeto direito e um indireto.</t>
+        </is>
+      </c>
+      <c r="F782" t="inlineStr">
+        <is>
+          <t>transitivo indireto e um objeto direto e indireto.</t>
+        </is>
+      </c>
+      <c r="G782" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H782" t="inlineStr">
+        <is>
+          <t>Um verbo bitransitivo exige dois complementos: um objeto direto e um objeto indireto. A fala possui um verbo bitransitivo (dar) , um objeto indireto (a mim) e um objeto direto (o remédio).</t>
+        </is>
+      </c>
+      <c r="I782" t="inlineStr">
+        <is>
+          <t>PH06</t>
+        </is>
+      </c>
+      <c r="J782" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K782" t="inlineStr"/>
+      <c r="L782" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>Garcia, em pé, mirava e estalava as unhas; Fortunato, na cadeira de balanço, olhava para o teto;
+ASSIS, Machado de. A causa secreta. Obra Completa. Rio de Janeiro : Nova Aguilar 1994. v. II. p.18. Disponível em: http://www.dominiopublico.gov.br/download/texto/bv000256.pdf. Acesso em: 1 nov. 2024
+Qual o complemento verbal de olhar no texto?</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>O objeto direto "o teto".</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>O objeto direto "na cadeira".</t>
+        </is>
+      </c>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>O objeto indireto "para o teto".</t>
+        </is>
+      </c>
+      <c r="E783" t="inlineStr">
+        <is>
+          <t>A oração "mirava e estalava as unhas em pé".</t>
+        </is>
+      </c>
+      <c r="F783" t="inlineStr">
+        <is>
+          <t>A oração "olhava para o teto na cadeira de balanço."</t>
+        </is>
+      </c>
+      <c r="G783" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H783" t="inlineStr">
+        <is>
+          <t>O verbo "olhar" é transitivo indireto no trecho, exigindo um complemento introduzido pela preposição "para". Portanto, "para o teto" é o objeto indireto do verbo "olhar".</t>
+        </is>
+      </c>
+      <c r="I783" t="inlineStr">
+        <is>
+          <t>PH06</t>
+        </is>
+      </c>
+      <c r="J783" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K783" t="inlineStr"/>
+      <c r="L783" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>Maria Luísa ficou desconsolada com a zombaria do marido; mas o médico restituiu-lhe a satisfação anterior, voltando a referir a dedicação deste e as suas raras qualidades de enfermeiro; tão bom enfermeiro, concluiu ele, que, se algum dia fundar uma casa de saúde, irei convidá-lo.
+ASSIS, Machado de. A causa secreta. Obra Completa. Rio de Janeiro : Nova Aguilar 1994. v. II. p.18. Disponível em: http://www.dominiopublico.gov.br/download/texto/bv000256.pdf. Acesso em: 1 nov. 2024
+No trecho do conto de Machado de Assis, o verbo restituir é sinônimo de "devolver". Analisando sintaticamente esse verbo, conclui-se que ele é</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>verbo intransitivo, pois não complementado por nenhum objeto.</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>verbo transitivo direto, pois é complementado pelo objeto direto "a satisfação".</t>
+        </is>
+      </c>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>verbo transitivo indireto, pois é complementado pelo objeto indireto "com a zombaria".</t>
+        </is>
+      </c>
+      <c r="E784" t="inlineStr">
+        <is>
+          <t>verbo bitransitivo, pois é complementado pelos objetos: "a satisfação anterior" e "a ela".</t>
+        </is>
+      </c>
+      <c r="F784" t="inlineStr">
+        <is>
+          <t>verbo bitransitivo, pois é complementado pelos objetos: "a satisfação anterior" e "ao marido".</t>
+        </is>
+      </c>
+      <c r="G784" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H784" t="inlineStr">
+        <is>
+          <t>Um verbo bitransitivo exige dois complementos: um objeto direto e um objeto indireto. No trecho, "restituiu-lhe a satisfação anterior" tem "a satisfação anterior" como objeto direto e "lhe" (a ela) como objeto indireto.</t>
+        </is>
+      </c>
+      <c r="I784" t="inlineStr">
+        <is>
+          <t>PH06</t>
+        </is>
+      </c>
+      <c r="J784" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K784" t="inlineStr"/>
+      <c r="L784" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>Estou atrás
+do despojamento mais inteiro
+da simplicidade mais erma
+da palavra mais recém-nascida
+do inteiro mais despojado
+do ermo mais simples
+do nascimento a mais da palavra.
+CESAR, Ana Cristina. “Inéditos e dispersos”. [organização Armando Freitas Filho]. São Paulo: Editora Ática/IMS, 1999. Disponível em: https://www.revistaprosaversoearte.com/ana-cristina-cesar-poemas/#goog_rewarded. Acesso em 01 de nov 2024.
+Os versos do poema</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>não são objetos, pois não complementam nenhum verbo.</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>são objetos diretos do verbo bitransitivo "estar atrás".</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>não são objetos, mas complementam o título.</t>
+        </is>
+      </c>
+      <c r="E785" t="inlineStr">
+        <is>
+          <t>são objetos indiretos que completam o título.</t>
+        </is>
+      </c>
+      <c r="F785" t="inlineStr">
+        <is>
+          <t>são objetos diretos o verbo "estar".</t>
+        </is>
+      </c>
+      <c r="G785" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H785" t="inlineStr">
+        <is>
+          <t>O verbo "estar atrás" é transitivo indireto, exigindo um complemento introduzido por preposição ("de"). Portanto, os versos "do despojamento mais inteiro", "da simplicidade mais erma" etc. são objetos indiretos que completam o verbo "estar atrás".</t>
+        </is>
+      </c>
+      <c r="I785" t="inlineStr">
+        <is>
+          <t>PH06</t>
+        </is>
+      </c>
+      <c r="J785" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K785" t="inlineStr"/>
+      <c r="L785" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>[...]
+Eu não sabia
+que virar pelo avesso
+era uma experiência mortal.
+Ana Cristina Cesar, em “A teus pés”. São Paulo: Brasiliense, 1982.
+No trecho do poema de Ana Cristina Cesar, o verbo saber é complementado</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>pela oração subordinada "que virar pelo avesso era uma experiência mortal".</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>pela oração, mas não possui nenhum objeto.</t>
+        </is>
+      </c>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>pelo objeto direto "uma experiência mortal".</t>
+        </is>
+      </c>
+      <c r="E786" t="inlineStr">
+        <is>
+          <t>por dois objetos diretos "virar" e "era".</t>
+        </is>
+      </c>
+      <c r="F786" t="inlineStr">
+        <is>
+          <t>pelo objeto indireto "pelo avesso".</t>
+        </is>
+      </c>
+      <c r="G786" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H786" t="inlineStr">
+        <is>
+          <t>A oração subordinada "que virar pelo avesso era uma experiência mortal" complementa o verbo transitivo saber, indicando o objeto direto da ação expressa pelo verbo.</t>
+        </is>
+      </c>
+      <c r="I786" t="inlineStr">
+        <is>
+          <t>PH06</t>
+        </is>
+      </c>
+      <c r="J786" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K786" t="inlineStr"/>
+      <c r="L786" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>Leia o texto abaixo para responder à questão.
+Nise da Silveira
+Nise da Silveira foi uma médica psiquiatra que revolucionou o tratamento para pessoas com transtornos mentais.
+Nascida em Maceió, em 15 de fevereiro de 1905, era a estudiosa filha de uma pianista e de um professor de matemática.
+Formou-se na Faculdade de Medicina da Bahia em 1926 – a única mulher numa turma de 157 alunos.
+Quando começou a trabalhar num hospital psiquiátrico, Nise foi contra as formas agressivas de tratamento, como o isolamento e o eletrochoque. Muitas vezes, os doentes mentais sofriam maus-tratos e rejeição, e não eram vistos como seres humanos. Nise passou a cuidar deles, descobrindo diversas maneiras de dar-lhes voz e dignidade.
+Uma das descobertas de Nise foi o uso da arte como forma de expressão dos pacientes, que nem sempre conseguiam se comunicar por meio de palavras. Ela observou que muitos deles desenhavam mandalas (formas circulares), e resolveu escrever para Carl Jung, respeitado psicólogo suíço. Jung sugeriu que ela fizesse uma mostra das obras dos pacientes, exibida também na Suíça. Hoje, o prédio do instituto que leva o nome de Nise, no Rio de Janeiro, abriga mais de 350 mil obras (“imagens do inconsciente”) de artistas com problemas mentais.
+Nise também foi pioneira na pesquisa sobre o auxílio que os animais podem oferecer aos pacientes, por meio de vínculos emocionais.
+Nise foi uma mulher bem à frente de seu tempo, reconhecida internacionalmente por sua postura humanista e pela inestimável contribuição para a psiquiatria, com livros e artigos científicos.
+Esta é uma de suas recomendações: “Todo mundo tem um pouco de loucura. Vou lhes fazer um pedido: vivam a imaginação, pois ela é a nossa realidade mais profunda”.
+Ela morreu no Rio de Janeiro, em 1999.
+Disponível em: &lt;https://plenarinho.leg.br/index.php/2017/02/nise-da-silveira/&gt;. Acesso em: 26 mar. 2020. (Adaptado)
+Qual dos verbos retirados do texto é intransitivo?</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>“podem”.</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>“morreu”.</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>“foi”.</t>
+        </is>
+      </c>
+      <c r="E787" t="inlineStr">
+        <is>
+          <t>“é”.</t>
+        </is>
+      </c>
+      <c r="F787" t="inlineStr">
+        <is>
+          <t>"fizesse".</t>
+        </is>
+      </c>
+      <c r="G787" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H787" t="inlineStr">
+        <is>
+          <t>"Morrer" é um verbo intransitivo, ou seja, ele não necessita de um complemento para ter seu sentido completo. No contexto do texto, "morreu" é utilizado para indicar o falecimento de Nise da Silveira, e essa informação é suficiente por si só para transmitir a mensagem. Diferentemente dos verbos transitivos, que precisam de um objeto direto ou indireto para completar seu sentido, o verbo "morrer" já possui um significado completo sem a necessidade de um complemento. Por isso, "morreu" é classificado como um verbo intransitivo.</t>
+        </is>
+      </c>
+      <c r="I787" t="inlineStr">
+        <is>
+          <t>PH06</t>
+        </is>
+      </c>
+      <c r="J787" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K787" t="inlineStr"/>
+      <c r="L787" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>Leia abaixo um trecho do poema “José”, de Carlos Drummond de Andrade, para responder a questão.
+E agora, José?
+A festa acabou,
+a luz apagou,
+o povo sumiu,
+a noite esfriou,
+e agora, José?
+e agora, você?
+você que é sem nome,
+que zomba dos outros,
+você que faz versos,
+que ama, protesta?
+e agora, José?
+Disponível em: https://wp.ufpel.edu.br/aulusmm/2016/09/08/jose-carlos-drummond-de-andrade/. Acesso em: 25 mar. 2020. (Fragmento)
+Os verbos “acabou” e “apagou” são exemplos de</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>verbos intransitivos.</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>verbos transitivos.</t>
+        </is>
+      </c>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>objetos indiretos.</t>
+        </is>
+      </c>
+      <c r="E788" t="inlineStr">
+        <is>
+          <t>objetos diretos.</t>
+        </is>
+      </c>
+      <c r="F788" t="inlineStr">
+        <is>
+          <t>sujeitos.</t>
+        </is>
+      </c>
+      <c r="G788" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H788" t="inlineStr">
+        <is>
+          <t>Os verbos "acabou" e "apagou" são utilizados de maneira que não exigem complementos para que o sentido da frase seja completo. Verbos intransitivos são aqueles que possuem sentido completo por si só, sem a necessidade de um objeto direto ou indireto. No trecho do poema "José", de Carlos Drummond de Andrade, as ações de "acabar" e "apagar" são apresentadas de forma autossuficiente, ou seja, a festa simplesmente "acabou" e a luz simplesmente "apagou", sem que seja necessário especificar um complemento para essas ações.</t>
+        </is>
+      </c>
+      <c r="I788" t="inlineStr">
+        <is>
+          <t>PH06</t>
+        </is>
+      </c>
+      <c r="J788" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K788" t="inlineStr"/>
+      <c r="L788" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>Leia abaixo um trecho do poema “José”, de Carlos Drummond de Andrade, para responder a questão.
+E agora, José?
+A festa acabou,
+a luz apagou,
+o povo sumiu,
+a noite esfriou,
+e agora, José?
+e agora, você?
+você que é sem nome,
+que zomba dos outros,
+você que faz versos,
+que ama, protesta?
+e agora, José?
+Disponível em: https://wp.ufpel.edu.br/aulusmm/2016/09/08/jose-carlos-drummond-de-andrade/. Acesso em: 25 mar. 2020. (Fragmento)
+No poema, os termos em destaque são, respectivamente, classificados como</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>verbo transitivo e objeto direto.</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>verbo transitivo e objeto indireto.</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>verbo intransitivo e objeto direto.</t>
+        </is>
+      </c>
+      <c r="E789" t="inlineStr">
+        <is>
+          <t>verbo intransitivo e objeto indireto.</t>
+        </is>
+      </c>
+      <c r="F789" t="inlineStr">
+        <is>
+          <t>objeto direto e objeto indireto.</t>
+        </is>
+      </c>
+      <c r="G789" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H789" t="inlineStr">
+        <is>
+          <t>No trecho do poema "José", de Carlos Drummond de Andrade, o termo "zomba" é um verbo transitivo indireto. Isso significa que ele necessita de um complemento para completar seu sentido, e esse complemento é introduzido por uma preposição. No caso, o complemento é "dos outros", que é um objeto indireto, pois liga o verbo "zomba" através do uso da preposição "de".</t>
+        </is>
+      </c>
+      <c r="I789" t="inlineStr">
+        <is>
+          <t>PH06</t>
+        </is>
+      </c>
+      <c r="J789" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K789" t="inlineStr"/>
+      <c r="L789" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>Disponível em: &lt;http://www.adorocinema.com/filmes/filme-4834/fotos/detalhe/?cmediafile=20344781&gt;. Acesso em: 26 mar. 2020.
+Atua como complemento verbal:</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>“a coisa”.</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>“de Spike Lee”.</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>“uma viagem”.</t>
+        </is>
+      </c>
+      <c r="E790" t="inlineStr">
+        <is>
+          <t>“a coisa certa”.</t>
+        </is>
+      </c>
+      <c r="F790" t="inlineStr">
+        <is>
+          <t>"uma viagem de Spike Lee".</t>
+        </is>
+      </c>
+      <c r="G790" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H790" t="inlineStr">
+        <is>
+          <t>Entre as frases do pôster, "Faça a coisa certa" é a única que tem um verbo, "fazer". Por isso, a expressão "a coisa certa" atua como complemento verbal do verbo "faça". O verbo "faça" é um verbo transitivo direto, ou seja, ele necessita de um complemento para que seu sentido seja completo.</t>
+        </is>
+      </c>
+      <c r="I790" t="inlineStr">
+        <is>
+          <t>PH06</t>
+        </is>
+      </c>
+      <c r="J790" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K790" t="inlineStr">
+        <is>
+          <t>8a_ph06_por_09.png</t>
+        </is>
+      </c>
+      <c r="L790" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>Em qual das sentenças abaixo há presença de objeto direto e indireto?</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>Samira comunicou o conteúdo aos alunos.</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>Rafael irá à academia pela manhã.</t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>Bruno conversou comigo ontem.</t>
+        </is>
+      </c>
+      <c r="E791" t="inlineStr">
+        <is>
+          <t>Thiago estuda espanhol.</t>
+        </is>
+      </c>
+      <c r="F791" t="inlineStr">
+        <is>
+          <t>Caio jogou videogame hoje.</t>
+        </is>
+      </c>
+      <c r="G791" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H791" t="inlineStr">
+        <is>
+          <t>Em “Samira comunicou o conteúdo aos alunos”, o verbo “comunicar” necessita de complemento, uma vez que é transitivo. A oração conta com dois complementos: “o conteúdo” (objeto direto) e “aos alunos” (objetivo indireto).</t>
+        </is>
+      </c>
+      <c r="I791" t="inlineStr">
+        <is>
+          <t>PH06</t>
+        </is>
+      </c>
+      <c r="J791" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K791" t="inlineStr"/>
+      <c r="L791" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>Um menino que adora brincar de construir figuras geométricas com palitos de picolé, um dia, ele decide criar um quadrado com lado igual a a + b utilizando os palitos.  
+Fonte: Freepik. Disponível em: https://www.freepik.com/free-vector/realistic-set-bitten-chocolate-covered-ice-cream-with-nuts-wooden-sticks-isolated-vector-illustration_39221498.htm#fromView=search&amp;page=1&amp;position=12&amp;uuid=aecd7a31-f12d-4cb5-b7e6-1bf060f06635. Acesso em: 30 out. 2024
+Qual é a expressão algébrica que representa a área do quadrado construído pelo menino?</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>[img:8a_ph06_mat_01_a.png]</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>[img:8a_ph06_mat_01_b.png]</t>
+        </is>
+      </c>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>[img:8a_ph06_mat_01_c.png]</t>
+        </is>
+      </c>
+      <c r="E792" t="inlineStr">
+        <is>
+          <t>[img:8a_ph06_mat_01_d.png]</t>
+        </is>
+      </c>
+      <c r="F792" t="inlineStr">
+        <is>
+          <t>[img:8a_ph06_mat_01_e.png]</t>
+        </is>
+      </c>
+      <c r="G792" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H792" t="inlineStr">
+        <is>
+          <t>A área do quadrado construído pelo menino, com lado a + b, é dada por:
+Portanto, a expressão correta que representa a área do quadrado construído pelo menino é</t>
+        </is>
+      </c>
+      <c r="I792" t="inlineStr">
+        <is>
+          <t>PH06</t>
+        </is>
+      </c>
+      <c r="J792" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K792" t="inlineStr">
+        <is>
+          <t>8a_ph06_mat_01.png</t>
+        </is>
+      </c>
+      <c r="L792" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>Durante uma aula de matemática, a professora propôs um desafio aos alunos: calcular a diferença entre os quadrados de dois números inteiros consecutivos. Ela explicou que essa diferença poderia ser representada de forma algébrica e pediu que os alunos encontrassem a expressão correta.
+Qual é a expressão algébrica que representa a diferença entre os quadrados de dois números inteiros consecutivos a e b?</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>[img:8a_ph06_mat_02_a.png]</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>[img:8a_ph06_mat_02_b.png]</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>[img:8a_ph06_mat_02_c.png]</t>
+        </is>
+      </c>
+      <c r="E793" t="inlineStr">
+        <is>
+          <t>[img:8a_ph06_mat_02_d.png]</t>
+        </is>
+      </c>
+      <c r="F793" t="inlineStr">
+        <is>
+          <t>[img:8a_ph06_mat_02_e.png]</t>
+        </is>
+      </c>
+      <c r="G793" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H793" t="inlineStr">
+        <is>
+          <t>A diferença entre os quadrados de dois números inteiros consecutivos a e b é dada por:</t>
+        </is>
+      </c>
+      <c r="I793" t="inlineStr">
+        <is>
+          <t>PH06</t>
+        </is>
+      </c>
+      <c r="J793" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K793" t="inlineStr"/>
+      <c r="L793" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>Um carpinteiro está construindo uma caixa cúbica para armazenar seus os brinquedos de seu filho. Ele quer que a caixa tenha um lado de comprimento a + b. Para esta construção, ele precisa encontrar o volume dessa caixa.
+Qual é a expressão correta para o volume da caixa?</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>[img:8a_ph06_mat_03_a.png]</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>[img:8a_ph06_mat_03_b.png]</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>[img:8a_ph06_mat_03_c.png]</t>
+        </is>
+      </c>
+      <c r="E794" t="inlineStr">
+        <is>
+          <t>[img:8a_ph06_mat_03_d.png]</t>
+        </is>
+      </c>
+      <c r="F794" t="inlineStr">
+        <is>
+          <t>[img:8a_ph06_mat_03_e.png]</t>
+        </is>
+      </c>
+      <c r="G794" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H794" t="inlineStr">
+        <is>
+          <t>A expressão correta é  . Para encontrar o volume da caixa, utilizamos a fórmula do cubo da soma de dois termos:</t>
+        </is>
+      </c>
+      <c r="I794" t="inlineStr">
+        <is>
+          <t>PH06</t>
+        </is>
+      </c>
+      <c r="J794" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K794" t="inlineStr"/>
+      <c r="L794" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>Um matemático está construindo um modelo para representar a soma de dois volumes cúbicos. Ele tem dois cubos, um com aresta a e outro com aresta b. Agora, ele precisa encontrar a expressão correta para calcular a soma dos volumes dos dois cubos.
+Qual é a expressão correta para a soma dos volumes dos dois cubos?</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>[img:8a_ph06_mat_04_a.png]</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>[img:8a_ph06_mat_04_b.png]</t>
+        </is>
+      </c>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>[img:8a_ph06_mat_04_c.png]</t>
+        </is>
+      </c>
+      <c r="E795" t="inlineStr">
+        <is>
+          <t>[img:8a_ph06_mat_04_d.png]</t>
+        </is>
+      </c>
+      <c r="F795" t="inlineStr">
+        <is>
+          <t>[img:8a_ph06_mat_04_e.png]</t>
+        </is>
+      </c>
+      <c r="G795" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H795" t="inlineStr">
+        <is>
+          <t>O volume do primeiro cubo é a³ e o volume do segundo cubo é b³. Para encontrar a soma dos volumes dos dois cubos, utilizamos a fórmula da soma de dois cubos: 
+Portanto, a expressão correta é</t>
+        </is>
+      </c>
+      <c r="I795" t="inlineStr">
+        <is>
+          <t>PH06</t>
+        </is>
+      </c>
+      <c r="J795" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K795" t="inlineStr"/>
+      <c r="L795" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>Um jovem está construindo um modelo matemático para representar a soma de três termos a, b e c.
+Qual é a expressão correta para o quadrado da soma dos três termos a, b e c?</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>[img:8a_ph06_mat_05_a.png]</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>[img:8a_ph06_mat_05_b.png]</t>
+        </is>
+      </c>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>[img:8a_ph06_mat_05_c.png]</t>
+        </is>
+      </c>
+      <c r="E796" t="inlineStr">
+        <is>
+          <t>[img:8a_ph06_mat_05_d.png]</t>
+        </is>
+      </c>
+      <c r="F796" t="inlineStr">
+        <is>
+          <t>[img:8a_ph06_mat_05_e.png]</t>
+        </is>
+      </c>
+      <c r="G796" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H796" t="inlineStr">
+        <is>
+          <t>A expressão correta é  
+Para encontrar o quadrado da soma dos três termos, utilizamos a fórmula do quadrado da soma de três termos:</t>
+        </is>
+      </c>
+      <c r="I796" t="inlineStr">
+        <is>
+          <t>PH06</t>
+        </is>
+      </c>
+      <c r="J796" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K796" t="inlineStr"/>
+      <c r="L796" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>Uma piscina foi projetada de forma que sua superfície seja um quadrado, assim como sua borda. Observe a imagem a seguir.
+Qual a área da piscina?</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>[img:8a_ph06_mat_06_a.png]</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>[img:8a_ph06_mat_06_b.png]</t>
+        </is>
+      </c>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>[img:8a_ph06_mat_06_c.png]</t>
+        </is>
+      </c>
+      <c r="E797" t="inlineStr">
+        <is>
+          <t>[img:8a_ph06_mat_06_d.png]</t>
+        </is>
+      </c>
+      <c r="F797" t="inlineStr">
+        <is>
+          <t>[img:8a_ph06_mat_06_e.png]</t>
+        </is>
+      </c>
+      <c r="G797" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H797" t="inlineStr">
+        <is>
+          <t>A piscina será um quadrado de lado .
+Logo, sua área será: .</t>
+        </is>
+      </c>
+      <c r="I797" t="inlineStr">
+        <is>
+          <t>PH06</t>
+        </is>
+      </c>
+      <c r="J797" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K797" t="inlineStr">
+        <is>
+          <t>8a_ph06_mat_06.png</t>
+        </is>
+      </c>
+      <c r="L797" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>Se ab = 1 e (a + b)² = 12, então a² + b² vale</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>9.</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>10.</t>
+        </is>
+      </c>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>11.</t>
+        </is>
+      </c>
+      <c r="E798" t="inlineStr">
+        <is>
+          <t>12.</t>
+        </is>
+      </c>
+      <c r="F798" t="inlineStr">
+        <is>
+          <t>13.</t>
+        </is>
+      </c>
+      <c r="G798" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H798" t="inlineStr">
+        <is>
+          <t>Utilizando produtos notáveis para expandir a expressão, tem-se:</t>
+        </is>
+      </c>
+      <c r="I798" t="inlineStr">
+        <is>
+          <t>PH06</t>
+        </is>
+      </c>
+      <c r="J798" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K798" t="inlineStr"/>
+      <c r="L798" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>Cada aresta de um cubo foi dividida em duas partes diferentes.
+Se a área total do cubo é , qual será seu volume ao reduzir as arestas em ?</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>[img:8a_ph06_mat_08_a.png]</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>[img:8a_ph06_mat_08_b.png]</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>[img:8a_ph06_mat_08_c.png]</t>
+        </is>
+      </c>
+      <c r="E799" t="inlineStr">
+        <is>
+          <t>[img:8a_ph06_mat_08_d.png]</t>
+        </is>
+      </c>
+      <c r="F799" t="inlineStr">
+        <is>
+          <t>[img:8a_ph06_mat_08_e.png]</t>
+        </is>
+      </c>
+      <c r="G799" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H799" t="inlineStr">
+        <is>
+          <t>A área total de um cubo é igual a seis vezes o valor da área de uma face.
+Logo, a área de uma face é  e a medida da aresta é .
+Reduzindo todas as arestas em , as arestas resultantes terão tamanho .
+Portanto, o volume do cubo resultante será .</t>
+        </is>
+      </c>
+      <c r="I799" t="inlineStr">
+        <is>
+          <t>PH06</t>
+        </is>
+      </c>
+      <c r="J799" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K799" t="inlineStr">
+        <is>
+          <t>8a_ph06_mat_08.png</t>
+        </is>
+      </c>
+      <c r="L799" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>A partir de um grande quadrado, foram retirados outros 3 menores, de forma que suas diagonais juntas formem a diagonal do grande quadrado.
+Se os quadrados menores possuem lados medindo a, b e c, qual a área restante?</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>[img:8a_ph06_mat_09_a.png]</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>[img:8a_ph06_mat_09_b.png]</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>[img:8a_ph06_mat_09_c.png]</t>
+        </is>
+      </c>
+      <c r="E800" t="inlineStr">
+        <is>
+          <t>[img:8a_ph06_mat_09_d.png]</t>
+        </is>
+      </c>
+      <c r="F800" t="inlineStr">
+        <is>
+          <t>[img:8a_ph06_mat_09_e.png]</t>
+        </is>
+      </c>
+      <c r="G800" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H800" t="inlineStr">
+        <is>
+          <t>Os três lados dos quadrados menores juntos formam o lado do quadrado maior. Assim, o lado do grande quadrado mede .
+A área do grande quadrado será .
+Ao retirar as áreas dos quadrados menores do quadrado maior, obtêm-se: .</t>
+        </is>
+      </c>
+      <c r="I800" t="inlineStr">
+        <is>
+          <t>PH06</t>
+        </is>
+      </c>
+      <c r="J800" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K800" t="inlineStr">
+        <is>
+          <t>8a_ph06_mat_09.png</t>
+        </is>
+      </c>
+      <c r="L800" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>Quatro quadrados, de lado x cada um, estão encaixados em um de seus vértices. Se cada um desses quadrados teve seus lados aumentados em 4 unidades, qual é o aumento de área ocorrido?</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>[img:8a_ph06_mat_10_a.png]</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>[img:8a_ph06_mat_10_b.png]</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>[img:8a_ph06_mat_10_c.png]</t>
+        </is>
+      </c>
+      <c r="E801" t="inlineStr">
+        <is>
+          <t>[img:8a_ph06_mat_10_d.png]</t>
+        </is>
+      </c>
+      <c r="F801" t="inlineStr">
+        <is>
+          <t>[img:8a_ph06_mat_10_e.png]</t>
+        </is>
+      </c>
+      <c r="G801" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H801" t="inlineStr">
+        <is>
+          <t>A área de cada quadrado original é . O quadrado aumentado terá área de .
+A diferença de áreas é: .
+Logo, o aumento de área foi de .</t>
+        </is>
+      </c>
+      <c r="I801" t="inlineStr">
+        <is>
+          <t>PH06</t>
+        </is>
+      </c>
+      <c r="J801" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K801" t="inlineStr">
+        <is>
+          <t>8a_ph06_mat_10.png</t>
+        </is>
+      </c>
+      <c r="L801" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/questoes.xlsx
+++ b/questoes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L801"/>
+  <dimension ref="A1:L851"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42074,7 +42074,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K752" t="inlineStr"/>
       <c r="L752" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -42133,7 +42132,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K753" t="inlineStr"/>
       <c r="L753" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -42192,7 +42190,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K754" t="inlineStr"/>
       <c r="L754" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -42251,7 +42248,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K755" t="inlineStr"/>
       <c r="L755" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -42374,7 +42370,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K757" t="inlineStr"/>
       <c r="L757" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -42433,7 +42428,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K758" t="inlineStr"/>
       <c r="L758" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -42491,7 +42485,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K759" t="inlineStr"/>
       <c r="L759" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -42550,7 +42543,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K760" t="inlineStr"/>
       <c r="L760" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -42609,7 +42601,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K761" t="inlineStr"/>
       <c r="L761" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -42732,7 +42723,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K763" t="inlineStr"/>
       <c r="L763" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -42793,7 +42783,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K764" t="inlineStr"/>
       <c r="L764" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -42853,7 +42842,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K765" t="inlineStr"/>
       <c r="L765" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -42979,7 +42967,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K767" t="inlineStr"/>
       <c r="L767" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -43039,7 +43026,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K768" t="inlineStr"/>
       <c r="L768" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -43098,7 +43084,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K769" t="inlineStr"/>
       <c r="L769" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -43156,7 +43141,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K770" t="inlineStr"/>
       <c r="L770" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -43216,7 +43200,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K771" t="inlineStr"/>
       <c r="L771" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -43279,7 +43262,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K772" t="inlineStr"/>
       <c r="L772" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -43340,7 +43322,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K773" t="inlineStr"/>
       <c r="L773" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -43401,7 +43382,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K774" t="inlineStr"/>
       <c r="L774" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -43463,7 +43443,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K775" t="inlineStr"/>
       <c r="L775" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -43523,7 +43502,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K776" t="inlineStr"/>
       <c r="L776" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -43584,7 +43562,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K777" t="inlineStr"/>
       <c r="L777" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -43644,7 +43621,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K778" t="inlineStr"/>
       <c r="L778" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -43706,7 +43682,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K779" t="inlineStr"/>
       <c r="L779" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -43766,7 +43741,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K780" t="inlineStr"/>
       <c r="L780" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -43894,7 +43868,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K782" t="inlineStr"/>
       <c r="L782" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -43954,7 +43927,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K783" t="inlineStr"/>
       <c r="L783" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -44014,7 +43986,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K784" t="inlineStr"/>
       <c r="L784" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -44080,7 +44051,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K785" t="inlineStr"/>
       <c r="L785" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -44143,7 +44113,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K786" t="inlineStr"/>
       <c r="L786" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -44213,7 +44182,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K787" t="inlineStr"/>
       <c r="L787" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -44285,7 +44253,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K788" t="inlineStr"/>
       <c r="L788" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -44357,7 +44324,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K789" t="inlineStr"/>
       <c r="L789" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -44478,7 +44444,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K791" t="inlineStr"/>
       <c r="L791" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -44602,7 +44567,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K793" t="inlineStr"/>
       <c r="L793" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -44661,7 +44625,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K794" t="inlineStr"/>
       <c r="L794" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -44721,7 +44684,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K795" t="inlineStr"/>
       <c r="L795" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -44781,7 +44743,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K796" t="inlineStr"/>
       <c r="L796" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -44903,7 +44864,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K798" t="inlineStr"/>
       <c r="L798" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -45105,6 +45065,3044 @@
         </is>
       </c>
     </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>Roberto está montando um circuito elétrico com uma pilha, fios, uma lâmpada e um resistor. Ele quer garantir que a lâmpada funcione corretamente sem queimar.
+Qual é a função do resistor na lâmpada?</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>Limitar a corrente elétrica.</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>Aumentar a tensão elétrica.</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>Reduzir a resistência elétrica.</t>
+        </is>
+      </c>
+      <c r="E802" t="inlineStr">
+        <is>
+          <t>Aumentar a capacitância elétrica.</t>
+        </is>
+      </c>
+      <c r="F802" t="inlineStr">
+        <is>
+          <t>Diminuir a indutância elétrica.</t>
+        </is>
+      </c>
+      <c r="G802" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H802" t="inlineStr">
+        <is>
+          <t>O resistor é utilizado para limitar a corrente elétrica no circuito, protegendo a lâmpada de uma corrente excessiva que poderia queimá-la.</t>
+        </is>
+      </c>
+      <c r="I802" t="inlineStr">
+        <is>
+          <t>PH07</t>
+        </is>
+      </c>
+      <c r="J802" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K802" t="inlineStr"/>
+      <c r="L802" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>Pedro toca uma esfera metálica carregada com um bastão de vidro carregado e observa que a esfera metálica também fica carregada.
+Qual é o tipo de eletrização que ocorreu nesse experimento?</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>Eletrização por atrito.</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>Eletrização por contato.</t>
+        </is>
+      </c>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>Eletrização por indução.</t>
+        </is>
+      </c>
+      <c r="E803" t="inlineStr">
+        <is>
+          <t>Eletrização por fusão.</t>
+        </is>
+      </c>
+      <c r="F803" t="inlineStr">
+        <is>
+          <t>Eletrização por difusão.</t>
+        </is>
+      </c>
+      <c r="G803" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H803" t="inlineStr">
+        <is>
+          <t>Quando um corpo carregado toca outro corpo, ocorre transferência de cargas, caracterizando a eletrização por contato.</t>
+        </is>
+      </c>
+      <c r="I803" t="inlineStr">
+        <is>
+          <t>PH07</t>
+        </is>
+      </c>
+      <c r="J803" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K803" t="inlineStr"/>
+      <c r="L803" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>Lucas está comparando a eficiência de diferentes materiais condutores em um circuito elétrico. Ele observa que alguns materiais conduzem melhor a eletricidade do que outros.
+Qual é a melhor opção de material para atuar como condutor elétrico?</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>Vidro.</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>Cobre.</t>
+        </is>
+      </c>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>Plástico.</t>
+        </is>
+      </c>
+      <c r="E804" t="inlineStr">
+        <is>
+          <t>Madeira.</t>
+        </is>
+      </c>
+      <c r="F804" t="inlineStr">
+        <is>
+          <t>Borracha.</t>
+        </is>
+      </c>
+      <c r="G804" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H804" t="inlineStr">
+        <is>
+          <t>O cobre é um excelente condutor elétrico, amplamente utilizado em circuitos elétricos.</t>
+        </is>
+      </c>
+      <c r="I804" t="inlineStr">
+        <is>
+          <t>PH07</t>
+        </is>
+      </c>
+      <c r="J804" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K804" t="inlineStr"/>
+      <c r="L804" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>Marcos está verificando o sistema de aterramento de um edifício e observa que ele está conectado a uma haste metálica cravada no solo.
+Qual é a função dessa haste metálica no sistema de aterramento?</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>Dispersar a corrente elétrica no solo.</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>Aumentar a tensão elétrica no circuito.</t>
+        </is>
+      </c>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>Reduzir a resistência elétrica do circuito.</t>
+        </is>
+      </c>
+      <c r="E805" t="inlineStr">
+        <is>
+          <t>Aumentar a corrente elétrica no circuito.</t>
+        </is>
+      </c>
+      <c r="F805" t="inlineStr">
+        <is>
+          <t>Diminuir a capacitância elétrica do circuito.</t>
+        </is>
+      </c>
+      <c r="G805" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H805" t="inlineStr">
+        <is>
+          <t>A haste metálica no sistema de aterramento dispersa a corrente elétrica no solo, protegendo contra choques elétricos e surtos de tensão.</t>
+        </is>
+      </c>
+      <c r="I805" t="inlineStr">
+        <is>
+          <t>PH07</t>
+        </is>
+      </c>
+      <c r="J805" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K805" t="inlineStr"/>
+      <c r="L805" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>Julia está montando um circuito elétrico e quer calcular a resistência necessária para que a corrente elétrica seja de 2 A, sabendo que a tensão fornecida pela fonte é de 12 V.
+Qual deve ser o valor da resistência no circuito?</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>6Ω</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>8Ω</t>
+        </is>
+      </c>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>10Ω</t>
+        </is>
+      </c>
+      <c r="E806" t="inlineStr">
+        <is>
+          <t>12Ω</t>
+        </is>
+      </c>
+      <c r="F806" t="inlineStr">
+        <is>
+          <t>14Ω</t>
+        </is>
+      </c>
+      <c r="G806" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H806" t="inlineStr">
+        <is>
+          <t>Usando a Lei de Ohm, temos:</t>
+        </is>
+      </c>
+      <c r="I806" t="inlineStr">
+        <is>
+          <t>PH07</t>
+        </is>
+      </c>
+      <c r="J806" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K806" t="inlineStr"/>
+      <c r="L806" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>Ao assistir um filme de super herói, o aluno Miguel se surpreende no momento que o personagem principal do filme, Super Hokke, utiliza seus poderes elétricos para atrair objetos metálicos ao seu redor e usá-los como equipamento para salvar o dia. Questionando se poderia reproduzir essa cena em seu laboratório, Miguel separa três esferas metálicas X, Y, e Z eletricamente carregadas e percebe que ocorre uma atração entre X e Y e uma repulsão entre X e Z. Deste modo, é correto afirmar que é uma possibilidade que</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>A esfera X tem carga positiva e a esfera Y carga positiva.</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>A esfera X tem carga negativa e a esfera Y carga negativa.</t>
+        </is>
+      </c>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>A esfera Z possui carga positiva e a esfera X carga negativa.</t>
+        </is>
+      </c>
+      <c r="E807" t="inlineStr">
+        <is>
+          <t>A esfera X tem carga positiva e a esfera Y carga negativa.</t>
+        </is>
+      </c>
+      <c r="F807" t="inlineStr">
+        <is>
+          <t>A esfera X possui carga positiva e a esfera Z carga negativa.</t>
+        </is>
+      </c>
+      <c r="G807" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H807" t="inlineStr">
+        <is>
+          <t>Se ocorre uma atração entre as esferas X e Y, elas precisam possui cargas de sinais contrários.</t>
+        </is>
+      </c>
+      <c r="I807" t="inlineStr">
+        <is>
+          <t>PH07</t>
+        </is>
+      </c>
+      <c r="J807" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K807" t="inlineStr"/>
+      <c r="L807" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>É possível classificar os materiais conforme sua condutividade. Duas categorias importantes no estudo da eletricidade são: material condutor e material isolante.
+A diferença entre os dois é que</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>o isolante tem as cargas positivas livres com facilidade de se movimentar, enquanto o condutor não possui cargas neutras, não deixando a eletricidade passar.</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>o isolante tem as cargas negativas livres com facilidade de se movimentar, enquanto o condutor não possui cargas negativas livres, não deixando a eletricidade passar.</t>
+        </is>
+      </c>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>o condutor tem as cargas neutras livres com facilidade de se movimentar, enquanto o isolante não possui cargas neutras livres, não deixando a eletricidade passar.</t>
+        </is>
+      </c>
+      <c r="E808" t="inlineStr">
+        <is>
+          <t>o condutor tem as cargas positivas livres com facilidade de se movimentar, enquanto o isolante não possui cargas positivas livres, não deixando a eletricidade passar.</t>
+        </is>
+      </c>
+      <c r="F808" t="inlineStr">
+        <is>
+          <t>o condutor tem as cargas negativas livres com facilidade de se movimentar, enquanto o isolante não possui cargas negativas livres, não deixando a eletricidade passar.</t>
+        </is>
+      </c>
+      <c r="G808" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H808" t="inlineStr">
+        <is>
+          <t>O material condutor tem cargas negativas livres com facilidade de se movimentar ao longo do material, sendo bons condutores de eletricidade.
+Enquanto o material isolante não possui cargas negativas com essa facilidade, não deixando a eletricidade passar.</t>
+        </is>
+      </c>
+      <c r="I808" t="inlineStr">
+        <is>
+          <t>PH07</t>
+        </is>
+      </c>
+      <c r="J808" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K808" t="inlineStr"/>
+      <c r="L808" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>Os sinais das cargas determinam as interações que podem ocorrer entre duas ou  mais cargas.
+Analise as seguintes situações:
+A: uma carga positiva com outra carga positiva
+B: uma carga negativa com outra carga negativa
+C: uma carga negativa com uma carga positiva
+É possível afirmar que ocorrerá, respectivamente:</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>repulsão, repulsão e atração.</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>repulsão, atração e atração.</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>atração, atração e atração.</t>
+        </is>
+      </c>
+      <c r="E809" t="inlineStr">
+        <is>
+          <t>repulsão, repulsão e repulsão.</t>
+        </is>
+      </c>
+      <c r="F809" t="inlineStr">
+        <is>
+          <t>atração, atração e repulsão.</t>
+        </is>
+      </c>
+      <c r="G809" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H809" t="inlineStr">
+        <is>
+          <t>As cargas de mesmos sinais se repelem e as de sinais opostos se atraem, por tanto:
+A: repulsão
+B: repulsão
+C: atração</t>
+        </is>
+      </c>
+      <c r="I809" t="inlineStr">
+        <is>
+          <t>PH07</t>
+        </is>
+      </c>
+      <c r="J809" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K809" t="inlineStr"/>
+      <c r="L809" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>Uma criança brincando em um escorregador, toca em uma outra pessoa e sente um pequeno choque.
+A explicação, segundo os tipos de eletrizações, pode ser, respectivamente</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>eletrização por atrito seguida de eletrização por indução.</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>eletrização por atrito seguida de eletrização por contato.</t>
+        </is>
+      </c>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>eletrização por contato seguida de eletrização por contato.</t>
+        </is>
+      </c>
+      <c r="E810" t="inlineStr">
+        <is>
+          <t>eletrização por indução seguida de eletrização por atrito.</t>
+        </is>
+      </c>
+      <c r="F810" t="inlineStr">
+        <is>
+          <t>eletrização por contato seguida de eletrização por indução.</t>
+        </is>
+      </c>
+      <c r="G810" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H810" t="inlineStr">
+        <is>
+          <t>Ao escorregar, a criança sofre eletrização por atrito, entre a roupa e a superfície de contato do escorregador. Em seguida, ao entrar em contato, ocorre uma descarga elétrica, caracterizado pela eletrização de contato.</t>
+        </is>
+      </c>
+      <c r="I810" t="inlineStr">
+        <is>
+          <t>PH07</t>
+        </is>
+      </c>
+      <c r="J810" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K810" t="inlineStr"/>
+      <c r="L810" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>A partir de 2011, o padrão das tomadas brasileiras mudou. Agora ela tem dois ou três pinos redondos. O terceiro pino representa o aterramento, obrigatório em eletrodoméstico como geladeiras e micro-ondas, que apresentam perigo de choques elétricos.
+O aterramento evita o choque, pois</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>fica em contato com o eletrodoméstico.</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>fica em contato com a pessoa.</t>
+        </is>
+      </c>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>transforma o corpo positivo em um corpo neutro.</t>
+        </is>
+      </c>
+      <c r="E811" t="inlineStr">
+        <is>
+          <t>transforma o corpo eletrizado em um corpo neutro.</t>
+        </is>
+      </c>
+      <c r="F811" t="inlineStr">
+        <is>
+          <t>transforma o corpo neutro em um corpo eletrizado.</t>
+        </is>
+      </c>
+      <c r="G811" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H811" t="inlineStr">
+        <is>
+          <t>O aterramento é o processo de neutralizar um corpo eletrizado. Assim, ao tocar em um corpo aterrado, não sofrerá choque elétrico, que é a passagem de eletricidade pela diferença de carga.</t>
+        </is>
+      </c>
+      <c r="I811" t="inlineStr">
+        <is>
+          <t>PH07</t>
+        </is>
+      </c>
+      <c r="J811" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K811" t="inlineStr"/>
+      <c r="L811" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>“O poder é entendido, classicamente, pelo poder militar, então é o hard power, o poder de você obrigar os outros a fazer o que você quer. O soft power, por sua vez, vai se afirmar em oposição a esse conceito de hard power e vai tentar abarcar outros recursos para convencer sem a necessidade de recorrer à violência.”
+Disponível em: https://jornal.usp.br/radio-usp/soft-power-e-estrategia-para-paises-conquistarem-poder-e-prestigio-sem-o-uso-da-forca/. Acesso em: 6 nov 2024.
+Qual das opções a seguir é um exemplo de soft power?</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>imposição de sanções econômicas a um país para forçá-lo a mudar suas políticas internas.</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>utilização de campanhas de marketing cultural para promover a imagem de um país no exterior.</t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>realização de exercícios militares conjuntos para demonstrar força e dissuadir possíveis adversários.</t>
+        </is>
+      </c>
+      <c r="E812" t="inlineStr">
+        <is>
+          <t>construção de bases militares em territórios estrangeiros para garantir a segurança nacional.</t>
+        </is>
+      </c>
+      <c r="F812" t="inlineStr">
+        <is>
+          <t>implementação de bloqueios navais para impedir a entrada de mercadorias em um país adversário.</t>
+        </is>
+      </c>
+      <c r="G812" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H812" t="inlineStr">
+        <is>
+          <t>O soft power, envolve o uso de recursos culturais e de imagem para influenciar outros países sem recorrer à força ou coerção.</t>
+        </is>
+      </c>
+      <c r="I812" t="inlineStr">
+        <is>
+          <t>PH07</t>
+        </is>
+      </c>
+      <c r="J812" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K812" t="inlineStr"/>
+      <c r="L812" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>O “mundo multipolar”. Nascida no começo da década de 90 dos escombros do velho mundo, foi defendida principalmente pelo ex-secretário de Estado norte-americano, Henry Kissinger, como alternativa ao sistema bipolar, caído em desuso. No entanto, os Estados Unidos logo se deram conta de que essa teoria representava uma faca de dois gumes. Por isso, prontamente a abandonaram, tanto na prática como na teoria, preferindo ações enérgicas que visavam consolidar o mundo unipolar [...]. 
+Disponível em: https://diplomatique.org.br/a-teoria-do-mundo-multipolar/. Acesso em 6 de nov de 2024 (Adaptada.)
+No contexto das relações internacionais, como se diferenciam ações unilaterais de multilaterais?</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>Ações multilaterais envolvem vários países, enquanto ações unilaterais são conduzidas por um país.</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>Ações multilaterais são sempre mais eficazes do que ações unilaterais em qualquer contexto.</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>Ações unilaterais envolvem várias organizações internacionais em suas decisões.</t>
+        </is>
+      </c>
+      <c r="E813" t="inlineStr">
+        <is>
+          <t>Ações multilaterais ocorrem dentro das fronteiras de um único país sempre.</t>
+        </is>
+      </c>
+      <c r="F813" t="inlineStr">
+        <is>
+          <t>Ações unilaterais são realizadas em conjunto com aliados estratégicos.</t>
+        </is>
+      </c>
+      <c r="G813" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H813" t="inlineStr">
+        <is>
+          <t>Ações multilaterais envolvem a cooperação e o consenso de vários países, enquanto ações unilaterais são tomadas por um único país sem a necessidade de consultar ou obter o apoio de outros.</t>
+        </is>
+      </c>
+      <c r="I813" t="inlineStr">
+        <is>
+          <t>PH07</t>
+        </is>
+      </c>
+      <c r="J813" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K813" t="inlineStr"/>
+      <c r="L813" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>A influência não se restringia apenas ao hábito de fumar. Mas vinham dos idolatrados atores e atrizes as modas do vestir masculino e feminino, os cortes de cabelo, a maneira de aparar o bigode [...] Deixamos para trás o modelo europeu, predominantemente francês, para seguir os hábitos americanos. Tornamo-nos, em poucos anos, bebedores de Coca-Cola, comedores de sanduíche “macdonald”, adeptos do slack e da bermuda, até os dias presentes, quando, em ruidoso processo de globalização, somos praticamente uma caricatura do “grande irmão” do norte.
+DO “AMERICAN WAY OF LIFE” A INTERAÇÃO DE UM CONVÍVIO: BOA VIZINHANÇA, USO, SOLDADOS, NOVOS COSTUMES E OS CIDADÃOS FORTALEZENSES. REVERSON NASCIMENTO PAULA.
+Como o texto descreve a influência do American Way of Life na cultura de outros países?</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>adoção de hábitos alimentares e estilos americano.</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>rejeição completa do modelo europeu de vida.</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>valorização exclusiva dos produtos culturais franceses.</t>
+        </is>
+      </c>
+      <c r="E814" t="inlineStr">
+        <is>
+          <t>resistência ao consumo de produtos americanos.</t>
+        </is>
+      </c>
+      <c r="F814" t="inlineStr">
+        <is>
+          <t>preservação das tradições culturais locais.</t>
+        </is>
+      </c>
+      <c r="G814" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H814" t="inlineStr">
+        <is>
+          <t>O American Way of Life, conforme mencionado no texto, destaca a adoção de hábitos alimentares e vestimentas americanas, como beber Coca-Cola e usar bermudas.</t>
+        </is>
+      </c>
+      <c r="I814" t="inlineStr">
+        <is>
+          <t>PH07</t>
+        </is>
+      </c>
+      <c r="J814" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K814" t="inlineStr"/>
+      <c r="L814" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>Não durou muito sua suposta hegemonia. O grupo de Bin Laden se infiltrou no país e causou o maior ataque terrorista na história dos Estados Unidos. Em 1993, a Al-Qaeda  já havia atacado as Torres Gêmeas ao explodir um caminhão bomba no subsolo da torre norte. Em 2001 eles conseguiram um sucesso que nenhum grupo terrorista imaginaria.
+[...] O então presidente dos Estados Unidos, George W. Bush, membro do Partido Republicano e que governou entre 2001 e 2009, declarou em janeiro de 2002 que os Estados Unidos estavam a enfrentar um Eixo do Mal formado por Irã, Iraque e Coréia do Norte. Mais tarde, em maio de 2002, John Bolton, ex-secretário de Bush, afirmou que o Eixo do Mal deveria ser expandido e incluir Cuba, Síria e Líbia, por também considerá-los estados que financiavam o terrorismo. O terrorismo, depois da queda do comunismo, tornou-se o grande inimigo.
+Disponível em: https://diplomatique.org.br/vinte-anos-da-guerra/. Acesso em: 06 nov 2024.
+Qual foi a principal consequência do ataque terrorista de 2001 para a política externa dos Estados Unidos?</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>inicio da Guerra ao Terror e expansão do poder bélico americano.</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>retirada das tropas americanas do Oriente Médio.</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>diminuição do financiamento militar.</t>
+        </is>
+      </c>
+      <c r="E815" t="inlineStr">
+        <is>
+          <t>aliança com o Irã e a Coréia do Norte.</t>
+        </is>
+      </c>
+      <c r="F815" t="inlineStr"/>
+      <c r="G815" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H815" t="inlineStr">
+        <is>
+          <t>Após o ataque as Torres Gêmeas em 2001, o antigo presidente dos Estados Unidos, George W. Bush inicia um ataque a diversos países como o Irã, Iraque e Coréia do Norte, e mais tarde expandido para incluir Cuba, Síria e Líbia, expando sua influência mílitar.</t>
+        </is>
+      </c>
+      <c r="I815" t="inlineStr">
+        <is>
+          <t>PH07</t>
+        </is>
+      </c>
+      <c r="J815" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K815" t="inlineStr"/>
+      <c r="L815" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>Criada em 1949, conta com a participação de 28 países membros. Tem como objetivo principal a manutenção da segurança militar na Europa.
+Disponível em: https://www.suapesquisa.com/geografia/organizacoes_internacionais.html Acesso em: 6 nov 2024.
+A organização destacada é a:</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>ONU (Organização das Nações Unidas).</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>OTAN (Organização do Tratado do Atlântico Norte).</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>OMC (Organização Mundial do Comércio).</t>
+        </is>
+      </c>
+      <c r="E816" t="inlineStr">
+        <is>
+          <t>FMI (Fundo Monetário Internacional).</t>
+        </is>
+      </c>
+      <c r="F816" t="inlineStr">
+        <is>
+          <t>OEA (Organização dos Estados Americanos).</t>
+        </is>
+      </c>
+      <c r="G816" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H816" t="inlineStr">
+        <is>
+          <t>A OTAN foi criada em 1949 e tem como objetivo principal a manutenção da segurança militar na Europa. As demais alternativas referem-se a outras organizações internacionais com diferentes objetivos e datas de criação</t>
+        </is>
+      </c>
+      <c r="I816" t="inlineStr">
+        <is>
+          <t>PH07</t>
+        </is>
+      </c>
+      <c r="J816" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K816" t="inlineStr"/>
+      <c r="L816" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>A indústria cultural norte-americana teve enorme influência na vida social e cultural do Brasil e de toda a América Latina. Uma das mais importantes dessas influências esteve representada pela coluna de heróis e super-heróis, tais como: Flash Gordon, Jim das Selvas, Mandrake, Zorro, Fantasma, Tarzan, Super Homem, Capitão América, Batman, Homem de Borracha, Capitão Marvel e muitos outros. Juntamente com os personagens de Walt Disney, que chegam ao Brasil na década de 40, a “invasão” desses personagens assinala o novo contexto socioeconômico, político e cultural da nação brasileira.
+Dentre as opções abaixo aquela que indica corretamente como ficou conhecido o processo de difusão cultural dos EUA para mundo é:</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>Big Stick.</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>New Deal.</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>Globalização.</t>
+        </is>
+      </c>
+      <c r="E817" t="inlineStr">
+        <is>
+          <t>American Way of Life.</t>
+        </is>
+      </c>
+      <c r="F817" t="inlineStr">
+        <is>
+          <t>Estado de Bem estar social.</t>
+        </is>
+      </c>
+      <c r="G817" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H817" t="inlineStr">
+        <is>
+          <t>O American way of life foi o termo usado para difundir uma cultura fundamentada no consumismo. A desejada qualidade de vida estaria atrelada à capacidade de consumo de cada indivíduo, isto é, quanto maior o poder de consumo, maior seria a satisfação e a felicidade das pessoas.Esse processo foi fundamental para o crescimento econômico do país, pois favoreceu a divulgação da cultura estadunidense no espaço global. Desse modo, as grandes empresas multinacionais puderam se expandir, vendendo seus produtos mesmo em locais de difícil acesso na maior parte dos países.</t>
+        </is>
+      </c>
+      <c r="I817" t="inlineStr">
+        <is>
+          <t>PH07</t>
+        </is>
+      </c>
+      <c r="J817" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K817" t="inlineStr"/>
+      <c r="L817" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>O modelo econômico vigente nos Estados Unidos é o neoliberalismo.
+As principais características desse modelo econômico são:</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>intervenção do Estado na economia e socialização dos meios de produção.</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>muita intervenção do Estado na economia e privatização dos meios de produção.</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>pouca intervenção do Estado na economia e empresas com muita liberdade de atuação.</t>
+        </is>
+      </c>
+      <c r="E818" t="inlineStr">
+        <is>
+          <t>isenção de impostos e alto controle estatal.</t>
+        </is>
+      </c>
+      <c r="F818" t="inlineStr">
+        <is>
+          <t>maior presença de empresas estatais e investimentos públicos.</t>
+        </is>
+      </c>
+      <c r="G818" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H818" t="inlineStr">
+        <is>
+          <t>O modelo econômico neoliberal é caracterizado por haver uma baixa intervenção do Estado na economia para que as empresas tenham mais liberdade de atuação.</t>
+        </is>
+      </c>
+      <c r="I818" t="inlineStr">
+        <is>
+          <t>PH07</t>
+        </is>
+      </c>
+      <c r="J818" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K818" t="inlineStr"/>
+      <c r="L818" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>O Fundo Monetário Internacional (FMI) é uma agência especializada das Nações Unidas que foi concebida na conferência de Bretton Woods, New Hampshire, Estados Unidos, em julho de 1944.
+Disponível em:https://nacoesunidas.org/agencia/fmi/ Acesso em: 13 maio 2018.
+Para que um país possa pegar dinheiro do FMI é necessário que ele siga algumas regras neoliberais. Marque a alternativa que dê um exemplo dessas regras.</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>Aumento de controle estatal da economia.</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>Implementação da privatização de empresas públicas.</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>Fechamento ao capital externo.</t>
+        </is>
+      </c>
+      <c r="E819" t="inlineStr">
+        <is>
+          <t>Estatização de empresas privadas.</t>
+        </is>
+      </c>
+      <c r="F819" t="inlineStr">
+        <is>
+          <t>Incentivo aos gastos públicos desnecessários.</t>
+        </is>
+      </c>
+      <c r="G819" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H819" t="inlineStr">
+        <is>
+          <t>O modelo econômico neoliberal defende uma miníma intervenção estatal por parte do estado na economia, dessa forma, a privatização de empresas públicas é uma maneira de haver menor intervenção estatal na economia.</t>
+        </is>
+      </c>
+      <c r="I819" t="inlineStr">
+        <is>
+          <t>PH07</t>
+        </is>
+      </c>
+      <c r="J819" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K819" t="inlineStr"/>
+      <c r="L819" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>Observe a imagem a seguir:
+A imagem é uma fotografia de um ponto movimentado da cidade de Nova York. A partir da observação dela e dos conhecimentos adquiridos em sala de aula pode-se dizer corretamente que, de modo geral,</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>a população estadunidense tem um modo de vida muito consumista.</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>a população estadunidense possui um modo de vida saudável.</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>a população estadunidense possui um modo de vida baseado no baixo consumo.</t>
+        </is>
+      </c>
+      <c r="E820" t="inlineStr">
+        <is>
+          <t>a população estadunidense não está muito inserida no terceiro setor da economia.</t>
+        </is>
+      </c>
+      <c r="F820" t="inlineStr">
+        <is>
+          <t>a população estadunidense não está acostumada um grande número de propaganda publicitárias.</t>
+        </is>
+      </c>
+      <c r="G820" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H820" t="inlineStr">
+        <is>
+          <t>A população estadunidense está inserida em um modo de vida que possui altos índices de consumo.</t>
+        </is>
+      </c>
+      <c r="I820" t="inlineStr">
+        <is>
+          <t>PH07</t>
+        </is>
+      </c>
+      <c r="J820" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K820" t="inlineStr">
+        <is>
+          <t>8a_ph07_geo_09.jpg</t>
+        </is>
+      </c>
+      <c r="L820" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>Observe o gráfico a seguir:
+Com base no gráfico, os Estados Unidos possuem uma supremacia bélica porque</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>eles têm a maior população do mundo.</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>eles têm baixo desenvolvimento tecnológico.</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>é o país que mais investe nesse setor.</t>
+        </is>
+      </c>
+      <c r="E821" t="inlineStr">
+        <is>
+          <t>esse país foi uma colônia de povoamento, não de exploração.</t>
+        </is>
+      </c>
+      <c r="F821" t="inlineStr">
+        <is>
+          <t>eles têm como foco ajudar todos os países do mundo.</t>
+        </is>
+      </c>
+      <c r="G821" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H821" t="inlineStr">
+        <is>
+          <t>Os Estados Unidos é o país que mais investe dinheiro no setor militar e é o país que ocupa a maior parte do seu PIB para esses fins. Os gastos militares dos Estados Unidos são cerca de 5 vezes maiores do que os gastos da China, que é o segundo país que mais tem gastos militares.</t>
+        </is>
+      </c>
+      <c r="I821" t="inlineStr">
+        <is>
+          <t>PH07</t>
+        </is>
+      </c>
+      <c r="J821" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K821" t="inlineStr">
+        <is>
+          <t>8a_ph07_geo_10.jpg</t>
+        </is>
+      </c>
+      <c r="L821" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>A Lei sobre a Constituição Civil do Clero de 1790 visava reorganizar em profundidade a Igreja da França, transformando os párocos em "funcionários públicos eclesiásticos". Ela foi a base para a integração da Igreja Católica no novo sistema político introduzido pela Revolução de 1789.
+Segundo o historiador norte-americano Timothy Tackett, a lei introduziu uma fratura profunda e duradoura na França, ao aprofundar o efeito da Lei sobre a Abolição das Ordens Monásticas, de 13 de fevereiro do mesmo ano. Esta suprimira 100 mil membros do clero não ligados a uma paróquia, ou seja, os quase três quintos da classe considerados, na época, "não úteis". Os critérios de utilidade eram os sacramentos e o zelo das almas, assim como serviços à educação e às obras de caridade.
+Disponível em: https://www.dw.com/pt-br/1790-lu%C3%ADs-16-assina-constitui%C3%A7%C3%A3o-civil-do-clero/a-3768010. Acesso em: 07 nov. 2024.
+Na Revolução Francesa, o Código Civil do Clero representou o(a)</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>preservação dos privilégios do clero.</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>recuo do impulso revolucionário.</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>submissão da Igreja ao Estado.</t>
+        </is>
+      </c>
+      <c r="E822" t="inlineStr">
+        <is>
+          <t>adesão da Igreja à Revolução.</t>
+        </is>
+      </c>
+      <c r="F822" t="inlineStr">
+        <is>
+          <t>proibição do culto a religiões.</t>
+        </is>
+      </c>
+      <c r="G822" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H822" t="inlineStr">
+        <is>
+          <t>O Código Civil do Clero representou a submissão da Igreja ao Estado, nacionalizando seus bens e exigindo um juramento de lealdade à nova ordem constitucional.</t>
+        </is>
+      </c>
+      <c r="I822" t="inlineStr">
+        <is>
+          <t>PH07</t>
+        </is>
+      </c>
+      <c r="J822" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K822" t="inlineStr"/>
+      <c r="L822" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>A Fuga para Varennes foi um momento crucial da Revolução Francesa (1789-1799), na qual o rei Luís XVI da França (r. 1774-1792), sua esposa, a rainha Maria Antonieta (1755-1793), e seus filhos tentaram escapar de Paris na noite de 20-21 de junho de 1791. [...] a fuga mostrou que Luís XVI não era confiável e aumentou drasticamente o ódio e desconfiança pública em relação à monarquia. [...]
+Enraivecida, Maria Antonieta protestou contra a insolência da Assembleia em [exigir o retorno da família real a Paris], enquanto Luís lamentava sua perda de poder, gritando: “Não há mais um rei na França!”
+Disponível em: https://www.worldhistory.org/trans/pt/1-20975/a-fuga-para-varennes/. Acesso em: 07 nov. 2024. Adaptado.
+O texto indica que a Fuga para Varennes foi um evento que levou a Revolução Francesa a uma fase de</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>radicalização, estabelecendo as bases para a proclamação da república.</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>encerramento, restaurando o poder absolutista pelo fracasso dos jacobinos.</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>expansão, incentivando o exército francês a levar a revolução a outros países.</t>
+        </is>
+      </c>
+      <c r="E823" t="inlineStr">
+        <is>
+          <t>inicialização, promovendo a revolta do terceiro estado contra os demais estados.</t>
+        </is>
+      </c>
+      <c r="F823" t="inlineStr">
+        <is>
+          <t>conservadorismo, levando ao reconhecimento dos poderes constitucionais do rei.</t>
+        </is>
+      </c>
+      <c r="G823" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H823" t="inlineStr">
+        <is>
+          <t>O texto indica que a Fuga para Varennes foi um evento que levou a Revolução Francesa a uma fase de radicalização, estabelecendo as bases para a proclamação da república, ao revelar a fragilidade do compromisso do rei com a nova ordem constitucional e fortalecer as vozes mais radicais dentro do movimento revolucionário.</t>
+        </is>
+      </c>
+      <c r="I823" t="inlineStr">
+        <is>
+          <t>PH07</t>
+        </is>
+      </c>
+      <c r="J823" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K823" t="inlineStr"/>
+      <c r="L823" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>O rei, a nobreza francesa e a crescente emigração aristocrática e eclesiástica, acampados em várias cidades da Alemanha Ocidental, achavam que só a intervenção estrangeira poderia restaurar o velho regime. Esta intervenção não foi muito facilmente organizada, dadas as complexidades da situação internacional e a relativa tranquilidade política de outros países. Entretanto, era cada vez mais evidente para os nobres e os governantes por direito divino de outros países que a restauração do poder de Luís XVI não era meramente um ato de solidariedade de classe, mas uma proteção importante contra a difusão de ideias perturbadoras vindas da França. Consequentemente, as forças para reconquista da França concentraram-se no exterior.
+HOBSBAWM, E. A Era das Revoluções. São Paulo, Paz e Terra, 2007.
+O texto indica que as forças do Antigo Regime derrubadas pela Revolução Francesa</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>buscaram organizar regimes absolutistas nas colônias.</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>foram obrigados a trabalhar e se tornar parte do povo comum.</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>aceitaram a derrota política e fugiram para países absolutistas.</t>
+        </is>
+      </c>
+      <c r="E824" t="inlineStr">
+        <is>
+          <t>prepararam com aliados externos uma invasão de contrarrevolução.</t>
+        </is>
+      </c>
+      <c r="F824" t="inlineStr">
+        <is>
+          <t>resolveram se limitar à administração pública da República francesa.</t>
+        </is>
+      </c>
+      <c r="G824" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H824" t="inlineStr">
+        <is>
+          <t>O texto indica que as forças do Antigo Regime derrubadas pela Revolução Francesa prepararam com aliados externos uma invasão de contrarrevolução, concentrando-se no exterior para restaurar o poder de Luís XVI e combater a difusão de ideias revolucionárias.</t>
+        </is>
+      </c>
+      <c r="I824" t="inlineStr">
+        <is>
+          <t>PH07</t>
+        </is>
+      </c>
+      <c r="J824" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K824" t="inlineStr"/>
+      <c r="L824" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>A Montanha gastou o verão de 1793 perseguindo sua agenda de esquerda: eles aboliram a escravidão colonial e redigiram um projeto de nova constituição que prometia ser mais democrática do que qualquer outro governo, oferecendo sufrágio universal masculino.
+No entanto, enquanto A Montanha celebrava suas vitórias, a República Francesa estava em perigo. A queda dos girondinos resultou na erupção de revoltas federalistas nas principais cidades francesas, enquanto nas fronteiras, uma coalizão de exércitos estrangeiros forçava a França a ficar na defensiva. [...]
+Em 17 de setembro, a infame Lei dos Suspeitos foi aprovada, permitindo prisões de qualquer pessoa que, “por sua conduta, seus contatos, suas palavras ou seus escritos se mostrassem como apoiadores da tirania, do federalismo ou como inimigos da liberdade”.
+Glossário:
+Montanha: ala radical dos jacobinos.
+Disponível em: https://www.worldhistory.org/trans/pt/1-21142/reino-do-terror/. Acesso em: 07 nov. 2024.
+O texto sugere que a busca por defender as conquistas da revolução e o território francês contra inimigos externos levaram os jacobinos a</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>conciliar com os girondinos.</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>perseguir seus opositores.</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>acabar com a revolução.</t>
+        </is>
+      </c>
+      <c r="E825" t="inlineStr">
+        <is>
+          <t>restaurar a monarquia.</t>
+        </is>
+      </c>
+      <c r="F825" t="inlineStr">
+        <is>
+          <t>invadir outros países.</t>
+        </is>
+      </c>
+      <c r="G825" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H825" t="inlineStr">
+        <is>
+          <t>O texto sugere que, para defender as conquistas da revolução e o território francês contra inimigos externos, os jacobinos perseguiram seus opositores, como evidenciado pela aprovação da Lei dos Suspeitos, que permitia a prisão de qualquer pessoa considerada inimiga da liberdade.</t>
+        </is>
+      </c>
+      <c r="I825" t="inlineStr">
+        <is>
+          <t>PH07</t>
+        </is>
+      </c>
+      <c r="J825" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K825" t="inlineStr"/>
+      <c r="L825" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>Nessa altura os êxitos militares do exército da revolução diminuíram a tensão interna e a população passou a desejar o afrouxamento da repressão. Os girondinos, que tinham se isolado durante o Terror para salvar suas cabeças, voltaram à carga. Robespierre não tinha mais a massa de Paris para apoiá-lo, pois liquidara seus líderes. Em julho de 1794 (9 Termidor pelo novo calendário), Robespierre foi aprisionado juntamente com Saint-Just e, em seguida, foram guilhotinados. A alta burguesia estava voltando ao poder através dos girondinos.
+ARRUDA, J. História Moderna e Contemporânea. São Paulo, Ática, 1979, 10ª ed.
+A Reação Termidoriana descrita no texto deu início a uma fase da Revolução Francesa de</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>liderança dos sans-culottes.</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>restauração do absolutismo.</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>moderação e grande instabilidade.</t>
+        </is>
+      </c>
+      <c r="E826" t="inlineStr">
+        <is>
+          <t>vitória completa da contrarrevolução.</t>
+        </is>
+      </c>
+      <c r="F826" t="inlineStr">
+        <is>
+          <t>radicalização e repressão aos opositores.</t>
+        </is>
+      </c>
+      <c r="G826" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H826" t="inlineStr">
+        <is>
+          <t>A Reação Termidoriana descrita no texto deu início a uma fase da Revolução Francesa de moderação e grande instabilidade. O fim do Terror e a tentativa de estabilizar o governo após a queda de Robespierre levaram a uma sequência de golpes no que ficou conhecido como Diretório.</t>
+        </is>
+      </c>
+      <c r="I826" t="inlineStr">
+        <is>
+          <t>PH07</t>
+        </is>
+      </c>
+      <c r="J826" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K826" t="inlineStr"/>
+      <c r="L826" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>As mulheres, mesmo entre a maioria dos pensadores Iluministas que fizeram do século XVIII o “Século das Luzes”, defendendo as liberdades individuais, os direitos dos cidadãos contra o autoritarismo e o uso da razão, foram consideradas seres inferiores e fadadas aos desígnios da vida da casa
+SCHMIDT, Joessane de Freitas. As mulheres na Revolução Francesa. Revista Thema n. 09, vol. 02, 2012. p. 10.
+De acordo com o texto, como as mulheres eram vistas pelos pensadores do Iluminismo?</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>Como responsável pelo “Século das Luzes”.</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>De forma igualitária em relação aos homens.</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>Como pessoas restritas ao ambiente doméstico.</t>
+        </is>
+      </c>
+      <c r="E827" t="inlineStr">
+        <is>
+          <t>Como alguém que poderia transitar entre o ambiente político e o doméstico.</t>
+        </is>
+      </c>
+      <c r="F827" t="inlineStr">
+        <is>
+          <t>Como a portadora do sentimento revolucionário necessário para o enfrentamento do Antigo Regime.</t>
+        </is>
+      </c>
+      <c r="G827" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H827" t="inlineStr">
+        <is>
+          <t>O trecho “fadadas aos desígnios da vida da casa” demonstra que os pensadores iluministas consideravam a mulher como parte do ambiente doméstico e não como participante da esfera política. Isso foi determinante para a exclusão do voto feminino no contexto de promulgação do voto universal.</t>
+        </is>
+      </c>
+      <c r="I827" t="inlineStr">
+        <is>
+          <t>PH07</t>
+        </is>
+      </c>
+      <c r="J827" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K827" t="inlineStr"/>
+      <c r="L827" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>A ambição do projeto francês fica patente no título ‘Declaração dos Direitos do Homem e do Cidadão’: não apenas as garantias individuais, mas as garantias do cidadão, o agente da vida política.
+VOVELLE, Michel. A Revolução Francesa explicada à minha neta. Tradução de Fernando Santos. São Paulo: Editora UNESP, 2007. p. 43. Adaptado.
+Qual dos seguintes princípios estava presente na Declaração dos Direitos do Homem e do Cidadão?</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>A reforma agrária.</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>A proclamação da república.</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>A distinção entre classes sociais.</t>
+        </is>
+      </c>
+      <c r="E828" t="inlineStr">
+        <is>
+          <t>A defesa da propriedade privada.</t>
+        </is>
+      </c>
+      <c r="F828" t="inlineStr">
+        <is>
+          <t>A regulamentação do voto feminino.</t>
+        </is>
+      </c>
+      <c r="G828" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H828" t="inlineStr">
+        <is>
+          <t>Dentre os princípios constituintes da Declaração dos Direitos do Homem e do Cidadão estavam a igualdade jurídica e a defesa da propriedade privada.</t>
+        </is>
+      </c>
+      <c r="I828" t="inlineStr">
+        <is>
+          <t>PH07</t>
+        </is>
+      </c>
+      <c r="J828" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K828" t="inlineStr"/>
+      <c r="L828" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>[...] além do fato de terem reagido às circunstâncias, eles têm um grande ideal: fundar a República regenerando seus cidadãos. Eles tentam implantar uma pedagogia republicana por meio de textos e do discurso. Não perdem de vista a construção do ideal democrático: e é durante esse período que a Convenção decreta o fim da escravidão nas colônias francesas, dando continuidade à mensagem de emancipação da Declaração dos Direitos do Homem.
+VOVELLE, Michel. A Revolução Francesa explicada à minha neta. Tradução de Fernando Santos. Editora UNESP, 2007. p. 76 
+O excerto está se referindo aos</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>jacobinos.</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>girondinos.</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>sans-culottes.</t>
+        </is>
+      </c>
+      <c r="E829" t="inlineStr">
+        <is>
+          <t>reis franceses.</t>
+        </is>
+      </c>
+      <c r="F829" t="inlineStr">
+        <is>
+          <t>revolucionários que invadiram a Bastilha.</t>
+        </is>
+      </c>
+      <c r="G829" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H829" t="inlineStr">
+        <is>
+          <t>A descrição do excerto destaca a preocupação dos envolvidos em regenerar os cidadãos e fundar a República, ideais associados aos jacobinos durante a Revolução Francesa. Além disso, a menção à Convenção decretando o fim da escravidão nas colônias francesas está alinhada com a postura progressista dos jacobinos em relação aos direitos humanos e à igualdade.</t>
+        </is>
+      </c>
+      <c r="I829" t="inlineStr">
+        <is>
+          <t>PH07</t>
+        </is>
+      </c>
+      <c r="J829" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K829" t="inlineStr"/>
+      <c r="L829" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>Foi durante essa Revolução que foi aprovada a Lei dos Suspeitos, em virtude da qual foram condenados à guilhotina milhares de pessoas, pelo simples fato de terem sido foram consideradas suspeitas de serem contrários à Revolução, a qual entretanto se ufanava de defender a liberdade. O que fez Madame Roland (ela mesma uma revolucionária, mas de marcha lenta) exclamar antes de ser executada: “Liberdade, liberdade, quantos crimes se cometem em teu nome”.
+Disponível em: &lt;https://www.diariodasleis.com.br/bdi/18275-lei-dos-suspeitos-e-da-delauuo.html&gt;. Acesso em: 19 jan. 2024.
+A Lei dos Suspeitos,</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>instaurava a reforma agrária e educacional.</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>permitiu a chegada de Robespierre ao poder.</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>extinguiu os girondinos enquanto grupo político.</t>
+        </is>
+      </c>
+      <c r="E830" t="inlineStr">
+        <is>
+          <t>permitia a acusação de contrarrevolucionário mesmo sem provas.</t>
+        </is>
+      </c>
+      <c r="F830" t="inlineStr">
+        <is>
+          <t>proibiu a prisão de revolucionários sem julgamento observado pelo Estado.</t>
+        </is>
+      </c>
+      <c r="G830" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H830" t="inlineStr">
+        <is>
+          <t>Além da criação de um tribunal revolucionário, a promulgação da Lei dos Suspeitos permitia a acusação de contrarrevolucionário a qualquer um mesmo sem a sustentação através de provas.</t>
+        </is>
+      </c>
+      <c r="I830" t="inlineStr">
+        <is>
+          <t>PH07</t>
+        </is>
+      </c>
+      <c r="J830" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K830" t="inlineStr"/>
+      <c r="L830" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>O rei que protagonizou a fuga, Luís XVI, vivia confinado em uma “estranha realeza imaginada pela Revolução” de 1789. Ele detinha o comando do exército, a nomeação de ministros, a administração da justiça e das relações internacionais. Não mais detinha a antiga prerrogativa real de postos para atribuir e recompensas para distribuir, como comutar penas. Sem legislar, o rei dispunha ainda do veto suspensivo. Parecia-lhe pouco, diante das muitas “usurpações” que esvaziaram a majestade régia tão prezada na imaginação popular. Naquela sociedade de ordens – Clero, Nobreza, Terceiro Estado – a desigualdade social era um princípio da monarquia, nela a realeza estava aliada ao usufruto de privilégios. Esse rei cedeu diante das ameaças dos motins revolucionários, mas procurou fazer suas deliberações parecerem concessões, querendo tornar-se “um rei da igualdade”.
+MARTINEZ, Pablo Henrique. Varennes: A morte da realeza, 21 de junho de 1791. Perseu: História, Memória e Política, n. 06, 2011.
+A monarquia constitucional pressupunha a ação do rei em conjunto com</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>a Convenção.</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>os sans-culottes.</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>a Igreja Católica.</t>
+        </is>
+      </c>
+      <c r="E831" t="inlineStr">
+        <is>
+          <t>os filósofos iluministas.</t>
+        </is>
+      </c>
+      <c r="F831" t="inlineStr">
+        <is>
+          <t>uma Assembleia formada por homens eleitos.</t>
+        </is>
+      </c>
+      <c r="G831" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H831" t="inlineStr">
+        <is>
+          <t>A monarquia constitucional pressupunha o exercício do poder monárquico baseado na Constituição e na divisão do poder com uma Assembleia.</t>
+        </is>
+      </c>
+      <c r="I831" t="inlineStr">
+        <is>
+          <t>PH07</t>
+        </is>
+      </c>
+      <c r="J831" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K831" t="inlineStr"/>
+      <c r="L831" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>Disponível em: https://br.pinterest.com/pin/120612096256724568/. Acesso em 01 de nov 2024.
+O humor da tirinha se dá, pois</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>Rex obedece ao comando de sua dona.</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>Rex entende que “saia” é um objeto direto.</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>a dona não formula corretamente sua fala.</t>
+        </is>
+      </c>
+      <c r="E832" t="inlineStr">
+        <is>
+          <t>Rex entende que “pra fora” é um objeto pleonástico.</t>
+        </is>
+      </c>
+      <c r="F832" t="inlineStr">
+        <is>
+          <t>o cachorro azul entende que a fala era um pleonasmo, mas Rex não.</t>
+        </is>
+      </c>
+      <c r="G832" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H832" t="inlineStr">
+        <is>
+          <t>O humor da tirinha se dá pois o cachorro entende que "saia" é objeto direto do verbo "levar". No entanto, a fala "saia pra fora" é um pleonasmo vicioso, em que o termo "saia" não corresponde à peça de roupa, mas a forma imperativo do verbo "sair".</t>
+        </is>
+      </c>
+      <c r="I832" t="inlineStr">
+        <is>
+          <t>PH07</t>
+        </is>
+      </c>
+      <c r="J832" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K832" t="inlineStr">
+        <is>
+          <t>8a_ph07_por_01.jpg</t>
+        </is>
+      </c>
+      <c r="L832" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>Contudo contudo
+Caí pela escada abaixo subitamente,
+E até o som de cair era a gargalhada da queda.
+Cada degrau era a testemunha importuna e dura
+Do ridículo que fiz de mim.
+[...]
+Vi sempre o mundo independentemente de mim.
+Por trás disso estavam as minhas sensações vivíssimas,
+Mas isso era outro mundo.
+Contudo a minha mágoa nunca me fez ver negro o que era cor de laranja.
+Acima de tudo o mundo externo!
+Eu que me aguente comigo e com os comigos de mim.
+Poesias de Álvaro de Campos. Fernando Pessoa. Lisboa: Ática, 1944. Disponível em: http://www.dominiopublico.gov.br/download/texto/jp000011.pdf. Acesso em: 04 nov 2024.
+Os objetos pleonásticos utilizados no último verso do poema são</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>um pleonasmo vicioso, visto que tornam o poema mais subjetivo.</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>um pleonasmo vicioso, já que repetem desnecessariamente a figura do “eu”.</t>
+        </is>
+      </c>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>um pleonasmo literário, pois reforçam o sentimento de resignação do eu-lírico em ser que é.</t>
+        </is>
+      </c>
+      <c r="E833" t="inlineStr">
+        <is>
+          <t>um pleonasmo literário, já que dão ênfase para o sentimento de satisfação que o eu-lírico sente em ser ele mesmo.</t>
+        </is>
+      </c>
+      <c r="F833" t="inlineStr">
+        <is>
+          <t>um pleonasmo literário, visto que deixam o verso mais lírico e bonito esteticamente, mas são desnecessários do ponto de vista semântico.</t>
+        </is>
+      </c>
+      <c r="G833" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H833" t="inlineStr">
+        <is>
+          <t>O pleonasmo literário utilizado no último verso do poema é intencional e serve para enfatizar a resignação do eu-lírico em aceitar sua própria condição e complexidade. A repetição dos termos "comigo" e "com os comigos de mim" reforça essa aceitação e resignação, tornando o pleonasmo uma figura de linguagem significativa e não redundante.</t>
+        </is>
+      </c>
+      <c r="I833" t="inlineStr">
+        <is>
+          <t>PH07</t>
+        </is>
+      </c>
+      <c r="J833" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K833" t="inlineStr"/>
+      <c r="L833" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>Disponível em: https://questoes.grancursosonline.com.br/questoes-de-concursos/lingua-portuguesa-403587/2349694. Acesso em: 04 nov 2024.
+Se a frase do primeiro quadrinho estivesse com o objeto direto preposicionado, tal inversão de elementos sintáticos contribuiria para</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>criar um duplo-sentido na frase reelaborada.</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>evitar a ambiguidade presente na frase original.</t>
+        </is>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>dar ênfase ao objeto direto e tornar a frase mais elegante.</t>
+        </is>
+      </c>
+      <c r="E834" t="inlineStr">
+        <is>
+          <t>alterar a classe gramatical do objeto direto para objeto indireto.</t>
+        </is>
+      </c>
+      <c r="F834" t="inlineStr">
+        <is>
+          <t>indicar que se fala apenas do homem superior e não do homem comum.</t>
+        </is>
+      </c>
+      <c r="G834" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H834" t="inlineStr">
+        <is>
+          <t>Ao preposicionar o objeto direto na frase "O Homem superior atribui a culpa a si próprio", a frase ficaria "A culpa, o homem superior atribui a si próprio", o que contribui para dar ênfase ao objeto direto "a culpa" e pode tornar a frase mais elegante estilisticamente. Essa inversão é uma técnica comum em literatura e retórica para destacar certos elementos da frase.</t>
+        </is>
+      </c>
+      <c r="I834" t="inlineStr">
+        <is>
+          <t>PH07</t>
+        </is>
+      </c>
+      <c r="J834" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K834" t="inlineStr">
+        <is>
+          <t>8a_ph07_por_03.jpg</t>
+        </is>
+      </c>
+      <c r="L834" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>“Desaprender o que aprendeu você deve”.
+“Saber a diferença entre um professor e um aprendiz você quer?"
+"Distinguir o certo do errado você vai quando estiver calmo, em paz. Passivo. Um Jedi usa a Força para conhecimento e defesa, nunca para o ataque”.
+Disponível em: https://amenteemaravilhosa.com.br/as-20-melhores-frases-de-yoda-star-wars/. Acesso em: 04 nov 2024.
+As frases do mestre Yoda, personagem da saga Star Wars, são muito conhecidas pela inversão de elementos sintáticos. Analisando as frases, observa-se que essas trocas contribuem para</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>demonstrar a superioridade intelectual do personagem.</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>tornar a fala do personagem mais incompreensível.</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>tornar a fala do personagem mais divertida.</t>
+        </is>
+      </c>
+      <c r="E835" t="inlineStr">
+        <is>
+          <t>dar ênfase para o complemento do verbo.</t>
+        </is>
+      </c>
+      <c r="F835" t="inlineStr">
+        <is>
+          <t>introduzir ambiguidade propositalmente.</t>
+        </is>
+      </c>
+      <c r="G835" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H835" t="inlineStr">
+        <is>
+          <t>A inversão sintática nas frases de Yoda contribui para dar ênfase ao complemento do verbo. Essa construção estilística destaca a mensagem e reforça o tom de sabedoria e reflexão do personagem.</t>
+        </is>
+      </c>
+      <c r="I835" t="inlineStr">
+        <is>
+          <t>PH07</t>
+        </is>
+      </c>
+      <c r="J835" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K835" t="inlineStr"/>
+      <c r="L835" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>Em anexo, envio os recibos de compra. 
+Disponível em: https://guiadoestudante.abril.com.br/coluna/duvidas-portugues/8220-anexo-8221-ou-8220-em-anexo-8221.Acesso em: 04 nov 2024
+As preposições são essenciais para manter a coesão nos textos. Na frase acima, a preposição que acompanha o adjunto adverbial "em anexo" indica</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>finalidade.</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>posse.</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>modo.</t>
+        </is>
+      </c>
+      <c r="E836" t="inlineStr">
+        <is>
+          <t>lugar.</t>
+        </is>
+      </c>
+      <c r="F836" t="inlineStr">
+        <is>
+          <t>meio.</t>
+        </is>
+      </c>
+      <c r="G836" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H836" t="inlineStr">
+        <is>
+          <t>A preposição "em" na expressão "em anexo" indica a maneira como os recibos de compra estão sendo enviados, ou seja, anexados ao documento principal. Isso se refere ao modo como a ação de enviar está sendo realizada.</t>
+        </is>
+      </c>
+      <c r="I836" t="inlineStr">
+        <is>
+          <t>PH07</t>
+        </is>
+      </c>
+      <c r="J836" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K836" t="inlineStr"/>
+      <c r="L836" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>A flexibilidade sintática – ou seja, a flexibilidade que os elementos têm em se posicionar nas frases – varia muito de língua para língua, de acordo com características tais como conjugação verbal e presença ou ausência de declinações. No português, por exemplo, nós tendemos ao pleonasmo como forma de enfatizar aquilo que dizemos, facilitando a compreensão do interlocutor. Na frase “A minha amiga, ela me quer bem”, o pleonasmo cumpre a função de</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>enfatizar a quem a amiga quer bem.</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>enfatizar quem quer bem à amiga.</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>enfatizar quem quer bem ao locutor.</t>
+        </is>
+      </c>
+      <c r="E837" t="inlineStr">
+        <is>
+          <t>enfatizar qual o sentimento da amiga.</t>
+        </is>
+      </c>
+      <c r="F837" t="inlineStr">
+        <is>
+          <t>enfatizar quanto a amiga quer bem ao locutor.</t>
+        </is>
+      </c>
+      <c r="G837" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H837" t="inlineStr">
+        <is>
+          <t>Ao topicalizar o sujeito como se faz nessa oração, repetindo-o no pronome pessoal “ela”, é a ele que o locutor dá destaque. Ou seja, com isso o locutor explicita que é à sua amiga, e não a outra pessoa, que ele se refere.</t>
+        </is>
+      </c>
+      <c r="I837" t="inlineStr">
+        <is>
+          <t>PH07</t>
+        </is>
+      </c>
+      <c r="J837" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K837" t="inlineStr"/>
+      <c r="L837" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>Tal como o pleonasmo é a repetição de termos e ideias, o objeto pleonástico é a repetição de um objeto, direto ou indireto, numa mesma oração, em relação a um mesmo verbo. Também tal como o pleonasmo, ele pode ser resultado de vício de linguagem ou ser recurso estilístico. Identifique, nas frases abaixo, aquela em que há ocorrência de objeto pleonástico.</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>“Amo do nauta o doloroso grito / Em frágil prancha sobre mar de horrores” (Fagundes Varela).</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>“Casas entre bananeiras / mulheres entre laranjeiras / pomar amor cantar” (Carlos Drummond de Andrade).</t>
+        </is>
+      </c>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>“De tudo, ao meu amor serei atento” (Vinícius de Moraes).</t>
+        </is>
+      </c>
+      <c r="E838" t="inlineStr">
+        <is>
+          <t>“Na zona da mata o canavial novo / É um descanso verde que faz bem” (Mário de Andrade).</t>
+        </is>
+      </c>
+      <c r="F838" t="inlineStr">
+        <is>
+          <t>“Tuas palavras antigas / deixei-as todas, deixei-as” (Cecília Meireles).</t>
+        </is>
+      </c>
+      <c r="G838" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H838" t="inlineStr">
+        <is>
+          <t>O pleonasmo está na repetição do objeto “tuas palavras antigas”, presente no primeiro verso, enquanto pronome oblíquo no segundo verso (“deixei-as todas, deixei-as”), onde está o verbo.</t>
+        </is>
+      </c>
+      <c r="I838" t="inlineStr">
+        <is>
+          <t>PH07</t>
+        </is>
+      </c>
+      <c r="J838" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K838" t="inlineStr"/>
+      <c r="L838" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>Uma das funções do objeto direto preposicionado é a de representar uma parte do todo, a qual se chama partitivo. Por exemplo, a diferença entre as frases “eu comi essa macarronada” e “eu comi dessa macarronada” é que, na primeira, o sujeito não explicita se comeu ou não toda a macarronada, enquanto na segunda fica claro: ele comeu apenas uma parte dela. É para explicitar essa parte do todo que o verbo “comer”, que é transitivo direto, está seguido de preposição; “dessa macarronada” seria, portanto, o objeto direto preposicionado. Identifique, nas alternativas a seguir, frase em que ocorra objeto direto preposicionado por essa mesma razão.</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>É dessa tarefa que eu tenho cuidado.</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>É desse livro que eu não gosto.</t>
+        </is>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>Foi dessa ideia que eu desisti.</t>
+        </is>
+      </c>
+      <c r="E839" t="inlineStr">
+        <is>
+          <t>Foi desse projeto que eu participei.</t>
+        </is>
+      </c>
+      <c r="F839" t="inlineStr">
+        <is>
+          <t>Foi desse vinho que eu tomei.</t>
+        </is>
+      </c>
+      <c r="G839" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H839" t="inlineStr">
+        <is>
+          <t>O verbo “tomar” é transitivo direto – ou seja, não requer preposição –, e, aqui, seu objeto direto está acompanhado de preposição para representar uma parte do todo: o sujeito deixa claro que ele não tomou todo o vinho, mas parte dele.</t>
+        </is>
+      </c>
+      <c r="I839" t="inlineStr">
+        <is>
+          <t>PH07</t>
+        </is>
+      </c>
+      <c r="J839" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K839" t="inlineStr"/>
+      <c r="L839" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>O amor acaba
+O amor acaba. Numa esquina, por exemplo, num domingo de lua nova, depois de teatro e silêncio; acaba em cafés engordurados, diferentes dos parques de ouro onde começou a pulsar; de repente, ao meio do cigarro que ele atira de raiva contra um automóvel ou que ela esmaga no cinzeiro repleto, polvilhando de cinzas o escarlate das unhas; na acidez da aurora tropical, depois duma noite votada à alegria póstuma, que não veio; e acaba o amor no desenlace das mãos no cinema, como tentáculos saciados, e elas se movimentam no escuro como dois polvos de solidão; como se as mãos soubessem antes que o amor tinha acabado; na insônia dos braços luminosos do relógio; e acaba o amor nas sorveterias diante do colorido iceberg, entre frisos de alumínio e espelhos monótonos; e no olhar do cavaleiro errante que passou pela pensão; às vezes acaba o amor nos braços torturados de Jesus, filho crucificado de todas as mulheres; mecanicamente, no elevador, como se lhe faltasse energia; no andar diferente da irmã dentro de casa o amor pode acabar; na epifania da pretensão ridícula dos bigodes; nas ligas, nas cintas, nos brincos e nas silabadas femininas; quando a alma se habitua às províncias empoeiradas da Ásia, onde o amor pode ser outra coisa, o amor pode acabar; na compulsão da simplicidade simplesmente; no sábado, depois de três goles mornos de gim à beira da piscina; no filho tantas vezes semeado, às vezes vingado por alguns dias, mas que não floresceu, abrindo parágrafos de ódio inexplicável entre o pólen e o gineceu de duas flores; em apartamentos refrigerados, atapetados, aturdidos de delicadezas, onde há mais encanto que desejo; e o amor acaba na poeira que vertem os crepúsculos, caindo imperceptível no beijo de ir e vir; em salas esmaltadas com sangue, suor e desespero; nos roteiros do tédio para o tédio, na barca, no trem, no ônibus, ida e volta de nada para nada; em cavernas de sala e quarto conjugados o amor se eriça e acaba; no inferno o amor não começa; na usura o amor se dissolve; em Brasília o amor pode virar pó; no Rio, frivolidade; em Belo Horizonte, remorso; em São Paulo, dinheiro; uma carta que chegou depois, o amor acaba; uma carta que chegou antes, e o amor acaba; na descontrolada fantasia da libido; às vezes acaba na mesma música que começou, com o mesmo drinque, diante dos mesmos cisnes; e muitas vezes acaba em ouro e diamante, dispersado entre astros; e acaba nas encruzilhadas de Paris, Londres, Nova Iorque; no coração que se dilata e quebra, e o médico sentencia imprestável para o amor; e acaba no longo périplo, tocando em todos os portos, até se desfazer em mares gelados; e acaba depois que se viu a bruma que veste o mundo; na janela que se abre, na janela que se fecha; às vezes não acaba e é simplesmente esquecido como um espelho de bolsa, que continua reverberando sem razão até que alguém, humilde, o carregue consigo; às vezes o amor acaba como se fora melhor nunca ter existido; mas pode acabar com doçura e esperança; uma palavra, muda ou articulada, e acaba o amor; na verdade; o álcool; de manhã, de tarde, de noite; na floração excessiva da primavera; no abuso do verão; na dissonância do outono; no conforto do inverno; em todos os lugares o amor acaba; a qualquer hora o amor acaba; por qualquer motivo o amor acaba; para recomeçar em todos os lugares e a qualquer minuto o amor acaba.
+CAMPOS, Paulo Mendes. O amor acaba. In: UNESCO. O pequeno livro das grandes emoções. Brasília, DF: Unesco, 2009. p. 49-50.
+Por ter um fato do cotidiano como seu tema e não possuir personagens, o texto acima pode ser classificado como:</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>Poema</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>Conto</t>
+        </is>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>Crônica</t>
+        </is>
+      </c>
+      <c r="E840" t="inlineStr">
+        <is>
+          <t>Notícia</t>
+        </is>
+      </c>
+      <c r="F840" t="inlineStr">
+        <is>
+          <t>Artigo de Opinião</t>
+        </is>
+      </c>
+      <c r="G840" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H840" t="inlineStr">
+        <is>
+          <t>O texto acima é um exemplo de crônica em seu aspecto cotidiano, flertando com um tom poético ao valorizar a reflexão em detrimento do enredo.</t>
+        </is>
+      </c>
+      <c r="I840" t="inlineStr">
+        <is>
+          <t>PH07</t>
+        </is>
+      </c>
+      <c r="J840" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K840" t="inlineStr"/>
+      <c r="L840" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>O amor acaba
+O amor acaba. Numa esquina, por exemplo, num domingo de lua nova, depois de teatro e silêncio; acaba em cafés engordurados, diferentes dos parques de ouro onde começou a pulsar; de repente, ao meio do cigarro que ele atira de raiva contra um automóvel ou que ela esmaga no cinzeiro repleto, polvilhando de cinzas o escarlate das unhas; na acidez da aurora tropical, depois duma noite votada à alegria póstuma, que não veio; e acaba o amor no desenlace das mãos no cinema, como tentáculos saciados, e elas se movimentam no escuro como dois polvos de solidão; como se as mãos soubessem antes que o amor tinha acabado; na insônia dos braços luminosos do relógio; e acaba o amor nas sorveterias diante do colorido iceberg, entre frisos de alumínio e espelhos monótonos; e no olhar do cavaleiro errante que passou pela pensão; às vezes acaba o amor nos braços torturados de Jesus, filho crucificado de todas as mulheres; mecanicamente, no elevador, como se lhe faltasse energia; no andar diferente da irmã dentro de casa o amor pode acabar; na epifania da pretensão ridícula dos bigodes; nas ligas, nas cintas, nos brincos e nas silabadas femininas; quando a alma se habitua às províncias empoeiradas da Ásia, onde o amor pode ser outra coisa, o amor pode acabar; na compulsão da simplicidade simplesmente; no sábado, depois de três goles mornos de gim à beira da piscina; no filho tantas vezes semeado, às vezes vingado por alguns dias, mas que não floresceu, abrindo parágrafos de ódio inexplicável entre o pólen e o gineceu de duas flores; em apartamentos refrigerados, atapetados, aturdidos de delicadezas, onde há mais encanto que desejo; e o amor acaba na poeira que vertem os crepúsculos, caindo imperceptível no beijo de ir e vir; em salas esmaltadas com sangue, suor e desespero; nos roteiros do tédio para o tédio, na barca, no trem, no ônibus, ida e volta de nada para nada; em cavernas de sala e quarto conjugados o amor se eriça e acaba; no inferno o amor não começa; na usura o amor se dissolve; em Brasília o amor pode virar pó; no Rio, frivolidade; em Belo Horizonte, remorso; em São Paulo, dinheiro; uma carta que chegou depois, o amor acaba; uma carta que chegou antes, e o amor acaba; na descontrolada fantasia da libido; às vezes acaba na mesma música que começou, com o mesmo drinque, diante dos mesmos cisnes; e muitas vezes acaba em ouro e diamante, dispersado entre astros; e acaba nas encruzilhadas de Paris, Londres, Nova Iorque; no coração que se dilata e quebra, e o médico sentencia imprestável para o amor; e acaba no longo périplo, tocando em todos os portos, até se desfazer em mares gelados; e acaba depois que se viu a bruma que veste o mundo; na janela que se abre, na janela que se fecha; às vezes não acaba e é simplesmente esquecido como um espelho de bolsa, que continua reverberando sem razão até que alguém, humilde, o carregue consigo; às vezes o amor acaba como se fora melhor nunca ter existido; mas pode acabar com doçura e esperança; uma palavra, muda ou articulada, e acaba o amor; na verdade; o álcool; de manhã, de tarde, de noite; na floração excessiva da primavera; no abuso do verão; na dissonância do outono; no conforto do inverno; em todos os lugares o amor acaba; a qualquer hora o amor acaba; por qualquer motivo o amor acaba; para recomeçar em todos os lugares e a qualquer minuto o amor acaba.
+CAMPOS, Paulo Mendes. O amor acaba. In: UNESCO. O pequeno livro das grandes emoções. Brasília, DF: Unesco, 2009. p. 49-50.
+Segundo o texto, o fim do amor pode ser percebido</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>em grandes viagens românticas.</t>
+        </is>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>com o surgimento do ódio entre os amantes.</t>
+        </is>
+      </c>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>ao ouvir novamente a canção que marcara o primeiro encontro.</t>
+        </is>
+      </c>
+      <c r="E841" t="inlineStr">
+        <is>
+          <t>por meio de uma carta que é enviada ao destinatário antes da hora.</t>
+        </is>
+      </c>
+      <c r="F841" t="inlineStr">
+        <is>
+          <t>a qualquer momento, lugar ou pensamento cotidiano que se remeta ao amor.</t>
+        </is>
+      </c>
+      <c r="G841" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H841" t="inlineStr">
+        <is>
+          <t>A ideia central do texto, ao lançar mão de uma enumeração de situações, espaços e circunstâncias, é de que o amor, assim como desponta involuntariamente no decorrer da vida e da cotidianidade, nela encontra seu fim e pode ser assim percebido.</t>
+        </is>
+      </c>
+      <c r="I841" t="inlineStr">
+        <is>
+          <t>PH07</t>
+        </is>
+      </c>
+      <c r="J841" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K841" t="inlineStr"/>
+      <c r="L841" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>Dois amigos estão organizando uma feira para arrecadar fundos em sua escola. Eles estão comprando materiais para confeccionar sacolas e encontraram dois fornecedores. O primeiro fornecedor oferece 12 sacolas grandes e 18 sacolas pequenas por um valor X. O segundo fornecedor oferece 16 sacolas grandes e 24 sacolas pequenas pelo valor Y. Maria e Pedro desejam encontrar a melhor oferta, mas para isso precisam agrupar as sacolas em quantidades semelhantes.
+Qual é a forma fatorada da expressão que representa as quantidades de sacolas oferecidas pelo primeiro fornecedor?</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>12 g + 18 p = 5(2g + 3p)</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>12 g + 18 p = 6(2g + 3p)</t>
+        </is>
+      </c>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>12 g + 24 p = 12(1g + 2p)</t>
+        </is>
+      </c>
+      <c r="E842" t="inlineStr">
+        <is>
+          <t>16 g + 18 p = 2(8g + 9p)</t>
+        </is>
+      </c>
+      <c r="F842" t="inlineStr">
+        <is>
+          <t>16 g + 24 p = 8(2g + 3p)</t>
+        </is>
+      </c>
+      <c r="G842" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H842" t="inlineStr">
+        <is>
+          <t>O primeiro fornecedor oferece 12 sacolas grandes (g) e 18 sacolas pequenas (p), logo, tem-se que a forma fatorada da expressão que representa as quantidades de sacolas é: 12 g + 18 p = 6(2g + 3p).</t>
+        </is>
+      </c>
+      <c r="I842" t="inlineStr">
+        <is>
+          <t>PH07</t>
+        </is>
+      </c>
+      <c r="J842" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K842" t="inlineStr"/>
+      <c r="L842" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>Durante um projeto de jardinagem, uma equipe de alunos decide plantar flores em dois canteiros quadrados de tamanhos diferentes. O primeiro canteiro tem área de x² metros quadrados, enquanto o segundo tem área de y² metros quadrados. Eles desejam cercar ambos os canteiros, mas perceberam que podem economizar material cercando apenas a diferença entre as áreas dos dois canteiros.
+Qual é a forma fatorada que representa a diferença entre as áreas dos dois canteiros?</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>(x² – y²)(x² + y²)</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>(x³ – y³)(x³ + y³)</t>
+        </is>
+      </c>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>(x – y)(x + y)</t>
+        </is>
+      </c>
+      <c r="E843" t="inlineStr">
+        <is>
+          <t>x² + y²</t>
+        </is>
+      </c>
+      <c r="F843" t="inlineStr">
+        <is>
+          <t>x² – y²</t>
+        </is>
+      </c>
+      <c r="G843" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H843" t="inlineStr">
+        <is>
+          <t>A fórmula da diferença de dois quadrados é: a² – b² = (a – b)(a + b). Como a = x e b = y, logo a forma fatorada que representa a diferença entre as áreas dos dois canteiros é: x² – y² = (x – y)(x + y)</t>
+        </is>
+      </c>
+      <c r="I843" t="inlineStr">
+        <is>
+          <t>PH07</t>
+        </is>
+      </c>
+      <c r="J843" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K843" t="inlineStr"/>
+      <c r="L843" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>Ana está montando uma tabela para calcular os lucros de sua empresa. Ela percebeu que, ao analisar o crescimento de vendas mensais, a equação que descreve o lucro L em função do mês m é dada por L(m) = m² + 6m + 9. Ana quer saber se essa fórmula pode ser simplificada para entender melhor o crescimento.
+Como Ana pode fatorar a equação que representa o lucro em cada mês?</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>L(m) = (m + 3)²</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>L(m) = (m – 3)²</t>
+        </is>
+      </c>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>L(m) = (m + 6)²</t>
+        </is>
+      </c>
+      <c r="E844" t="inlineStr">
+        <is>
+          <t>L(m) = (m + 9)²</t>
+        </is>
+      </c>
+      <c r="F844" t="inlineStr">
+        <is>
+          <t>L(m) = m(m + 3)</t>
+        </is>
+      </c>
+      <c r="G844" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H844" t="inlineStr">
+        <is>
+          <t>A expressão L(m) = m² + 6m + 9 é um trinômio quadrado perfeito, pois está na forma a² + 2ab + b², e portanto, pode ser escrito como (m + 3)². Logo, a equação fatorada que representa o lucro em cada mês é L(m) = m² + 6m + 9  = (m + 3)².</t>
+        </is>
+      </c>
+      <c r="I844" t="inlineStr">
+        <is>
+          <t>PH07</t>
+        </is>
+      </c>
+      <c r="J844" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K844" t="inlineStr"/>
+      <c r="L844" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>Uma indústria química está misturando dois compostos em grandes tanques. A quantidade de cada composto em função do tempo é descrita por Q(t) = t(t + 1)(t – 1), onde t representa o tempo em horas. A equipe precisa calcular a produção total após um período de 10 horas. Antes, eles desejam fatorar a expressão para facilitar os cálculos.
+Qual é a forma fatorada mais simples da expressão que representa a quantidade de composto após t horas?</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>Q(t) = t(t + 1)(t – 1)</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>Q(t) = t²(t – 1)</t>
+        </is>
+      </c>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>Q(t) = t(t² + 1)</t>
+        </is>
+      </c>
+      <c r="E845" t="inlineStr">
+        <is>
+          <t>Q(t) = t(t² – 1)</t>
+        </is>
+      </c>
+      <c r="F845" t="inlineStr">
+        <is>
+          <t>Q(t) = t² – 1</t>
+        </is>
+      </c>
+      <c r="G845" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H845" t="inlineStr">
+        <is>
+          <t>Da expressão original: Q(t) = t(t + 1)(t – 1), tem-se que (t + 1)(t – 1) é um padrão conhecido como diferença de quadrados. A diferença de quadrados pode ser expressa como:
+(a + b)(a – b) = a² – b² .
+Nesse caso, a = t e b = 1: (t + 1)(t – 1) = t² – 1. Substituindo essa expressão de volta na equação original, encontra-se:
+Q(t) = t(t + 1)(t – 1) = t(t² – 1).</t>
+        </is>
+      </c>
+      <c r="I845" t="inlineStr">
+        <is>
+          <t>PH07</t>
+        </is>
+      </c>
+      <c r="J845" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K845" t="inlineStr"/>
+      <c r="L845" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>Uma fábrica de eletrônicos está projetando dois novos modelos de tablets, o Tablet A e o Tablet B, e precisa calcular a produção total para diferentes quantidades de peças fabricadas. A expressão polinomial que representa o número total de tablets produzidos por mês é:
+T(x) = x² + 12x + 35
+onde, x é o número de semanas do mês.
+O gerente da produção precisa dividir o total de tablets em dois grupos de semanas para uma melhor organização da linha de montagem.
+Como a expressão T(x) pode ser fatorada?</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>T(x) = (x + 6)(x + 6)</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>T(x) = (x - 7)(x + 5)</t>
+        </is>
+      </c>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>T(x) = (x + 7)(x + 5)</t>
+        </is>
+      </c>
+      <c r="E846" t="inlineStr">
+        <is>
+          <t>T(x) = (x + 8)(x + 4)</t>
+        </is>
+      </c>
+      <c r="F846" t="inlineStr">
+        <is>
+          <t>T(x) = (x + 12)(x + 35)</t>
+        </is>
+      </c>
+      <c r="G846" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H846" t="inlineStr">
+        <is>
+          <t>Pela fatoração do produto de Stevin, tem-se: x² + (a+b)x + ab = (x + a)(x + b). Então, para fatorar a expressão T(x) = x² + 12x + 35, procura-se dois números, a e b, de forma que a + b = 12 e ab = 35. Os números que satisfazem essa condição são 7 e 5, pois 7 + 5 = 12 e 7  5 = 35.
+Assim, a fatoração de T(x) é: T(x) = x² + 12x + 35 = (x + 7)(x + 5).</t>
+        </is>
+      </c>
+      <c r="I846" t="inlineStr">
+        <is>
+          <t>PH07</t>
+        </is>
+      </c>
+      <c r="J846" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K846" t="inlineStr"/>
+      <c r="L846" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>A expressão a3 + b3 pode ser fatorada como</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>(a + b)(a2 − ab + b2)</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>(a − b)(a2 + ab − b2)</t>
+        </is>
+      </c>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>(a + b)(a2 + ab + b2)</t>
+        </is>
+      </c>
+      <c r="E847" t="inlineStr">
+        <is>
+          <t>(a − b)(a2 + ab + b2)</t>
+        </is>
+      </c>
+      <c r="F847" t="inlineStr">
+        <is>
+          <t>(a + b)(a2 − ab − b2)</t>
+        </is>
+      </c>
+      <c r="G847" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H847" t="inlineStr">
+        <is>
+          <t>Tem-se que:
+a3 + b3 = a3 − a2b + ab2 + a2b − ab2 + b3 = (a + b)(a2 − ab + b2)</t>
+        </is>
+      </c>
+      <c r="I847" t="inlineStr">
+        <is>
+          <t>PH07</t>
+        </is>
+      </c>
+      <c r="J847" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K847" t="inlineStr"/>
+      <c r="L847" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>Um pátio de um prédio foi projetado de forma que ele fosse quadrado. Por uma questão estrutural, foi necessário colocar uma coluna, com base quadrada, no meio do pátio. Sabe-se que o lado da base da coluna mede  e o lado do pátio mede . Por causa disso, pensou-se em mudar o projeto do pátio para um retangular, com a mesma área que o original do projeto.
+Dentre os itens abaixo, qual representa as dimensões de um retângulo satisfazendo essa condição?</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="D848" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="E848" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="F848" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="G848" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H848" t="inlineStr">
+        <is>
+          <t>Façamos a diferença das duas áreas primeiro: .
+Essa conta é uma diferença de dois quadrados e, portanto, pode ser reescrita como: .
+Logo, o retângulo teria dimensões  e .</t>
+        </is>
+      </c>
+      <c r="I848" t="inlineStr">
+        <is>
+          <t>PH07</t>
+        </is>
+      </c>
+      <c r="J848" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K848" t="inlineStr">
+        <is>
+          <t>8a_ph07_mat_07.png</t>
+        </is>
+      </c>
+      <c r="L848" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>Um apartamento tem formato retangular, dividido em 4 cômodos retangulares, como mostra a planta.
+Considerando a área de cada cômodo que está indicada na figura, quais são as dimensões do apartamento?</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="E849" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="F849" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="G849" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H849" t="inlineStr">
+        <is>
+          <t>Ao somar todas as áreas, será obtida a área total do apartamento: .
+Fatorando por agrupamento, obtemos: .
+Portanto, as dimensões serão  e .</t>
+        </is>
+      </c>
+      <c r="I849" t="inlineStr">
+        <is>
+          <t>PH07</t>
+        </is>
+      </c>
+      <c r="J849" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K849" t="inlineStr">
+        <is>
+          <t>8a_ph07_mat_08.png</t>
+        </is>
+      </c>
+      <c r="L849" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>Um clube está projetando uma nova piscina para seus usuários no formato cúbico. Para fazer uma adaptação para que as crianças também possam utilizar essa piscina, será retirada uma parte da piscina, também cúbica, deixando a área acima mais rasa. Observe o projeto.
+Se a aresta do cubo maior mede 2x metros e a do cubo menor tem a metade dessa medida, qual o volume da piscina após a retirada para adaptação?</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>x3</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>7x2</t>
+        </is>
+      </c>
+      <c r="D850" t="inlineStr">
+        <is>
+          <t>8x2</t>
+        </is>
+      </c>
+      <c r="E850" t="inlineStr">
+        <is>
+          <t>4x3</t>
+        </is>
+      </c>
+      <c r="F850" t="inlineStr">
+        <is>
+          <t>7x3</t>
+        </is>
+      </c>
+      <c r="G850" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H850" t="inlineStr">
+        <is>
+          <t>O volume do cubo maior é (2x)3 e o do menor x3. Como o volume da piscina, após a adaptação para crianças é a diferença entre os volumes, tem-se:
+(2x)3 − x3 = 8x3 − x3 = 7x3</t>
+        </is>
+      </c>
+      <c r="I850" t="inlineStr">
+        <is>
+          <t>PH07</t>
+        </is>
+      </c>
+      <c r="J850" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K850" t="inlineStr">
+        <is>
+          <t>8a_ph07_mat_09.png</t>
+        </is>
+      </c>
+      <c r="L850" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>Uma sala quadrada possui lado medindo x metros. Aumentando seus lados numa mesma quantidade, a área passou a ser  metros quadrados. Qual o aumento, em metros, no perímetro?</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D851" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E851" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F851" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G851" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H851" t="inlineStr">
+        <is>
+          <t>Para determinar o novo lado, devemos fatorar o trinômio quadrado perfeito: .
+Portanto, o novo perímetro será: .
+Como o perímetro antigo era , a diferença será de  metros.</t>
+        </is>
+      </c>
+      <c r="I851" t="inlineStr">
+        <is>
+          <t>PH07</t>
+        </is>
+      </c>
+      <c r="J851" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K851" t="inlineStr">
+        <is>
+          <t>8a_ph07_mat_10.png</t>
+        </is>
+      </c>
+      <c r="L851" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/questoes.xlsx
+++ b/questoes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L851"/>
+  <dimension ref="A1:L901"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45117,7 +45117,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K802" t="inlineStr"/>
       <c r="L802" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -45176,7 +45175,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K803" t="inlineStr"/>
       <c r="L803" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -45235,7 +45233,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K804" t="inlineStr"/>
       <c r="L804" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -45294,7 +45291,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K805" t="inlineStr"/>
       <c r="L805" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -45353,7 +45349,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K806" t="inlineStr"/>
       <c r="L806" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -45411,7 +45406,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K807" t="inlineStr"/>
       <c r="L807" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -45471,7 +45465,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K808" t="inlineStr"/>
       <c r="L808" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -45537,7 +45530,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K809" t="inlineStr"/>
       <c r="L809" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -45596,7 +45588,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K810" t="inlineStr"/>
       <c r="L810" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -45655,7 +45646,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K811" t="inlineStr"/>
       <c r="L811" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -45715,7 +45705,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K812" t="inlineStr"/>
       <c r="L812" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -45775,7 +45764,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K813" t="inlineStr"/>
       <c r="L813" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -45835,7 +45823,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K814" t="inlineStr"/>
       <c r="L814" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -45871,7 +45858,6 @@
           <t>aliança com o Irã e a Coréia do Norte.</t>
         </is>
       </c>
-      <c r="F815" t="inlineStr"/>
       <c r="G815" t="inlineStr">
         <is>
           <t>A</t>
@@ -45892,7 +45878,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K815" t="inlineStr"/>
       <c r="L815" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -45952,7 +45937,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K816" t="inlineStr"/>
       <c r="L816" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -46011,7 +45995,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K817" t="inlineStr"/>
       <c r="L817" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -46070,7 +46053,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K818" t="inlineStr"/>
       <c r="L818" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -46130,7 +46112,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K819" t="inlineStr"/>
       <c r="L819" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -46317,7 +46298,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K822" t="inlineStr"/>
       <c r="L822" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -46378,7 +46358,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K823" t="inlineStr"/>
       <c r="L823" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -46438,7 +46417,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K824" t="inlineStr"/>
       <c r="L824" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -46502,7 +46480,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K825" t="inlineStr"/>
       <c r="L825" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -46562,7 +46539,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K826" t="inlineStr"/>
       <c r="L826" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -46622,7 +46598,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K827" t="inlineStr"/>
       <c r="L827" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -46682,7 +46657,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K828" t="inlineStr"/>
       <c r="L828" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -46742,7 +46716,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K829" t="inlineStr"/>
       <c r="L829" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -46802,7 +46775,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K830" t="inlineStr"/>
       <c r="L830" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -46862,7 +46834,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K831" t="inlineStr"/>
       <c r="L831" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -46996,7 +46967,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K833" t="inlineStr"/>
       <c r="L833" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -47121,7 +47091,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K835" t="inlineStr"/>
       <c r="L835" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -47181,7 +47150,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K836" t="inlineStr"/>
       <c r="L836" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -47239,7 +47207,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K837" t="inlineStr"/>
       <c r="L837" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -47297,7 +47264,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K838" t="inlineStr"/>
       <c r="L838" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -47355,7 +47321,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K839" t="inlineStr"/>
       <c r="L839" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -47416,7 +47381,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K840" t="inlineStr"/>
       <c r="L840" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -47477,7 +47441,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K841" t="inlineStr"/>
       <c r="L841" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -47536,7 +47499,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K842" t="inlineStr"/>
       <c r="L842" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -47595,7 +47557,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K843" t="inlineStr"/>
       <c r="L843" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -47654,7 +47615,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K844" t="inlineStr"/>
       <c r="L844" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -47716,7 +47676,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K845" t="inlineStr"/>
       <c r="L845" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -47779,7 +47738,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K846" t="inlineStr"/>
       <c r="L846" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -47838,7 +47796,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K847" t="inlineStr"/>
       <c r="L847" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -48098,6 +48055,3120 @@
         </is>
       </c>
       <c r="L851" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>Em circuitos elétricos residenciais, os dispositivos são frequentemente conectados em paralelo para garantir que cada dispositivo receba a mesma tensão da fonte de alimentação.
+Qual das seguintes afirmações é verdadeira sobre a intensidade da corrente e a tensão em associações em série e em paralelo?</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>Em série, a corrente é a mesma em todos os componentes, e a tensão é a soma das tensões em cada componente.</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>Em série, a tensão é a mesma em todos os componentes, e a corrente é a soma das correntes em cada componente.</t>
+        </is>
+      </c>
+      <c r="D852" t="inlineStr">
+        <is>
+          <t>Em paralelo, a corrente é a mesma em todos os componentes, e a tensão é a soma das tensões em cada componente.</t>
+        </is>
+      </c>
+      <c r="E852" t="inlineStr">
+        <is>
+          <t>Em paralelo, a corrente é a soma das correntes em cada componente, e a tensão é a soma das tensões em cada componente.</t>
+        </is>
+      </c>
+      <c r="F852" t="inlineStr">
+        <is>
+          <t>Em paralelo, a corrente e a tensão é a mesma em todos os componentes.</t>
+        </is>
+      </c>
+      <c r="G852" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H852" t="inlineStr">
+        <is>
+          <t>Quando os componentes de um circuito elétrico são conectados em série, a corrente que passa por cada componente é a mesma, pois há apenas um caminho para a corrente fluir. Além disso, a tensão total fornecida pela fonte é a soma das tensões em cada componente.</t>
+        </is>
+      </c>
+      <c r="I852" t="inlineStr">
+        <is>
+          <t>PH08</t>
+        </is>
+      </c>
+      <c r="J852" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K852" t="inlineStr"/>
+      <c r="L852" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>A Lei de Ohm estabelece que a tensão (U) em um resistor é igual ao produto da resistência (R) e sua corrente (I) que passa por ele, ou seja, U = R x I. Em uma associação em série, a corrente que passa por cada resistor é a mesma, e a tensão total é a soma das tensões em cada resistor.
+Considere um circuito em série com três resistores de resistências R1 ​= 2 Ω, R2 ​= 3 Ω e R3 ​= 5 Ω, e uma fonte de tensão de 20 V. Qual é a corrente que passa pelo circuito?</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>1 A</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>2 A</t>
+        </is>
+      </c>
+      <c r="D853" t="inlineStr">
+        <is>
+          <t>3 A</t>
+        </is>
+      </c>
+      <c r="E853" t="inlineStr">
+        <is>
+          <t>4 A</t>
+        </is>
+      </c>
+      <c r="F853" t="inlineStr">
+        <is>
+          <t>5 A</t>
+        </is>
+      </c>
+      <c r="G853" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H853" t="inlineStr">
+        <is>
+          <t>Ao calcular a corrente usando a Lei de Ohm, encontramos que a corrente é de 2 A.
+Req = 2 Ω + 3 Ω + 5 Ω = 10 Ω
+U = R x I
+I =  =</t>
+        </is>
+      </c>
+      <c r="I853" t="inlineStr">
+        <is>
+          <t>PH08</t>
+        </is>
+      </c>
+      <c r="J853" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K853" t="inlineStr"/>
+      <c r="L853" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>Em uma associação em paralelo, a tensão em cada resistor é a mesma, e a corrente total é a soma das correntes em cada resistor. A Lei de Ohm ainda se aplica a cada resistor individualmente.
+Considere um circuito em paralelo com dois resistores de resistências R1 = 4 Ω e R2 ​= 6 Ω, e uma fonte de tensão de 12 V. Qual é a corrente total fornecida pela fonte?</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>1 A</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>2 A</t>
+        </is>
+      </c>
+      <c r="D854" t="inlineStr">
+        <is>
+          <t>3 A</t>
+        </is>
+      </c>
+      <c r="E854" t="inlineStr">
+        <is>
+          <t>4 A</t>
+        </is>
+      </c>
+      <c r="F854" t="inlineStr">
+        <is>
+          <t>5 A</t>
+        </is>
+      </c>
+      <c r="G854" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H854" t="inlineStr">
+        <is>
+          <t>De acordo com os cálculos, a corrente total fornecida pela fonte é de 5 A.</t>
+        </is>
+      </c>
+      <c r="I854" t="inlineStr">
+        <is>
+          <t>PH08</t>
+        </is>
+      </c>
+      <c r="J854" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K854" t="inlineStr"/>
+      <c r="L854" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>A resistência equivalente de um circuito é a resistência total que um único resistor teria para produzir o mesmo efeito que todos os resistores combinados. Em uma associação em série, a resistência equivalente é a soma das resistências individuais. 
+Qual é a resistência equivalente de um circuito com três resistores em paralelo, com resistência</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>0,5 Ω</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>1 Ω</t>
+        </is>
+      </c>
+      <c r="D855" t="inlineStr">
+        <is>
+          <t>1,5 Ω</t>
+        </is>
+      </c>
+      <c r="E855" t="inlineStr">
+        <is>
+          <t>2 Ω</t>
+        </is>
+      </c>
+      <c r="F855" t="inlineStr">
+        <is>
+          <t>3 Ω</t>
+        </is>
+      </c>
+      <c r="G855" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H855" t="inlineStr">
+        <is>
+          <t>A resistência equivalente do circuito com três resistores em paralelo, com resistência é igual a 1 Ω.</t>
+        </is>
+      </c>
+      <c r="I855" t="inlineStr">
+        <is>
+          <t>PH08</t>
+        </is>
+      </c>
+      <c r="J855" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K855" t="inlineStr">
+        <is>
+          <t>8a_ph08_cie_04.png</t>
+        </is>
+      </c>
+      <c r="L855" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>Em circuitos elétricos residenciais, os dispositivos são frequentemente conectados em paralelo para garantir que cada dispositivo receba a mesma tensão da fonte de alimentação.
+No tipo de circuito citado, a corrente total é</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>igual à corrente que passa pelo dispositivo de maior resistência.</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>a soma das correntes que passam por cada dispositivo.</t>
+        </is>
+      </c>
+      <c r="D856" t="inlineStr">
+        <is>
+          <t>a média das correntes que passam por cada dispositivo.</t>
+        </is>
+      </c>
+      <c r="E856" t="inlineStr">
+        <is>
+          <t>à corrente que passa pelo dispositivo de menor resistência.</t>
+        </is>
+      </c>
+      <c r="F856" t="inlineStr">
+        <is>
+          <t>a diferença entre a corrente que passa pelos dispositivos de menor e maior resistência.</t>
+        </is>
+      </c>
+      <c r="G856" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H856" t="inlineStr">
+        <is>
+          <t>Em um circuito paralelo, a corrente total é a soma das correntes que passam por cada dispositivo. Isso ocorre porque a tensão é a mesma em todos os dispositivos, mas a corrente pode variar dependendo da resistência de cada dispositivo.</t>
+        </is>
+      </c>
+      <c r="I856" t="inlineStr">
+        <is>
+          <t>PH08</t>
+        </is>
+      </c>
+      <c r="J856" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K856" t="inlineStr"/>
+      <c r="L856" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>Quando uma lâmpada queima e para de funcionar, não há consequências para as outras lâmpadas e nem interfere nos aparelhos eletrônicos da casa.
+O tipo de ligação utilizada nas instalações nas residências, que apresenta característica acima é a ligação</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>simples.</t>
+        </is>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>em paralelo.</t>
+        </is>
+      </c>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>complexa.</t>
+        </is>
+      </c>
+      <c r="E857" t="inlineStr">
+        <is>
+          <t>em série.</t>
+        </is>
+      </c>
+      <c r="F857" t="inlineStr">
+        <is>
+          <t>em dupla.</t>
+        </is>
+      </c>
+      <c r="G857" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H857" t="inlineStr">
+        <is>
+          <t>A conexão das instalações elétricas residencial é feita em paralelo, assim, o funcionamento de um dispositivo é independente de outras.</t>
+        </is>
+      </c>
+      <c r="I857" t="inlineStr">
+        <is>
+          <t>PH08</t>
+        </is>
+      </c>
+      <c r="J857" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K857" t="inlineStr"/>
+      <c r="L857" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>A imagem a seguir alerta para um perigo ao empinar a pipa próximo às linhas de transmissão de energia elétrica.
+O que pode acontecer com esta situação se for ignorada a alerta?</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>Um choque de alta tensão.</t>
+        </is>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>Um choque de baixa tensão.</t>
+        </is>
+      </c>
+      <c r="D858" t="inlineStr">
+        <is>
+          <t>Uma cobrança indevida na conta de luz.</t>
+        </is>
+      </c>
+      <c r="E858" t="inlineStr">
+        <is>
+          <t>Um corte de fornecimento de energia elétrica.</t>
+        </is>
+      </c>
+      <c r="F858" t="inlineStr">
+        <is>
+          <t>Um disjuntor desarmado nas residências vizinhas.</t>
+        </is>
+      </c>
+      <c r="G858" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H858" t="inlineStr">
+        <is>
+          <t>A linha de transmissão é percorrida por uma alta tensão, portanto, ao brincar de pipa perto das linhas, o perigo é de um choque muito grande.</t>
+        </is>
+      </c>
+      <c r="I858" t="inlineStr">
+        <is>
+          <t>PH08</t>
+        </is>
+      </c>
+      <c r="J858" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K858" t="inlineStr">
+        <is>
+          <t>8a_ph08_cie_07.jpg</t>
+        </is>
+      </c>
+      <c r="L858" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>O aterramento realizado na rede elétrica da residência é obrigatório.
+Este procedimento é realizado com o objetivo de</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>proporcionar segurança para os moradores, para não tomarem choque.</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>proporcionar segurança para os animais, que podem chegar perto do fio.</t>
+        </is>
+      </c>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>causar descargas elétricas, evitando os choques nos moradores.</t>
+        </is>
+      </c>
+      <c r="E859" t="inlineStr">
+        <is>
+          <t>causar descargas elétricas, carregando os aparelhos elétricos.</t>
+        </is>
+      </c>
+      <c r="F859" t="inlineStr">
+        <is>
+          <t>economizar a energia elétrica, utilizando a energia da terra.</t>
+        </is>
+      </c>
+      <c r="G859" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H859" t="inlineStr">
+        <is>
+          <t>O aterramento possui como objetivo principal, a segurança, protegendo os moradores de possíveis choques elétricos.</t>
+        </is>
+      </c>
+      <c r="I859" t="inlineStr">
+        <is>
+          <t>PH08</t>
+        </is>
+      </c>
+      <c r="J859" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K859" t="inlineStr"/>
+      <c r="L859" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>O fornecimento de energia elétrica nas residências não é totalmente estável, podendo passar por algumas oscilações em eventos pontuais. Para que não danifique os aparelhos eletrônicos, alguns vem com um dispositivo que ao ser percorrido com uma corrente alta, protege o aparelho.
+Qual o nome deste dispositivo?</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>Disjuntor</t>
+        </is>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="D860" t="inlineStr">
+        <is>
+          <t>Interruptor</t>
+        </is>
+      </c>
+      <c r="E860" t="inlineStr">
+        <is>
+          <t>Fusível</t>
+        </is>
+      </c>
+      <c r="F860" t="inlineStr">
+        <is>
+          <t>Fio de cobre</t>
+        </is>
+      </c>
+      <c r="G860" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H860" t="inlineStr">
+        <is>
+          <t>O fusível tem a função de impedir que um aparelho eletrônico queime. Quando percorrido por uma corrente muito alta, haverá uma fusão do filamento e abrirá o circuito.</t>
+        </is>
+      </c>
+      <c r="I860" t="inlineStr">
+        <is>
+          <t>PH08</t>
+        </is>
+      </c>
+      <c r="J860" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K860" t="inlineStr"/>
+      <c r="L860" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>Ao realizar uma compra de produtos elétricos, é comum o vendedor questionar qual a voltagem que desejamos.
+É importante que compre um produto com as especificações certas para a sua casa, pois</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>todos os aparelhos eletrônicos funcionam em 110 V no Brasil.</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>todos os aparelhos eletrônicos funcionam em 220 V no Brasil.</t>
+        </is>
+      </c>
+      <c r="D861" t="inlineStr">
+        <is>
+          <t>todos os aparelhos eletrônicos funcionam em qualquer lugar do mundo.</t>
+        </is>
+      </c>
+      <c r="E861" t="inlineStr">
+        <is>
+          <t>alguns aparelhos eletrônicos funcionam somente na cozinha.</t>
+        </is>
+      </c>
+      <c r="F861" t="inlineStr">
+        <is>
+          <t>alguns aparelhos eletrônicos funcionam com uma tensão específica.</t>
+        </is>
+      </c>
+      <c r="G861" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H861" t="inlineStr">
+        <is>
+          <t>É importante atentar-se a informação das especificações dos aparelhos eletrônicos, para garantir o bom funcionamento na residência, com a tensão que cada lugar recebe de fornecimento.</t>
+        </is>
+      </c>
+      <c r="I861" t="inlineStr">
+        <is>
+          <t>PH08</t>
+        </is>
+      </c>
+      <c r="J861" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K861" t="inlineStr"/>
+      <c r="L861" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>O deserto do Atacama é um deserto costeiro localizado no norte do Chile. No entanto, também percorre outros países como Bolívia e Peru. Assim, ele forma uma faixa contínua de quase 1.000 km para leste, desde o Oceano Pacífico até a Cordilheira dos Andes. Considerado o deserto mais seco do mundo, o Atacama recebe, em média, menos de 5 mm de precipitação por ano e é caracterizado por condições climáticas extremas. Por isso, a região fornece à ciência diversas oportunidades de pesquisa.
+Disponível em: https://www.ecycle.com.br/deserto-do-atacama/. Acesso em 9 de dez de 2024.
+A aridez extrema do deserto do Atacama é resultado direto da:</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>Reclusão geográfica proporcionada pela Cordilheira dos Andes que impede a entrada de umidade do Oceano Atlântico.</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>Influência da corrente de Humboldt que traz ar quente e seco da Antártida, exacerbando a evaporação na região costeira.</t>
+        </is>
+      </c>
+      <c r="D862" t="inlineStr">
+        <is>
+          <t>Altitude da Cordilheira dos Andes e a corrente de Humboldt que bloqueiam a umidade vinda do mar e resfriam o ar, reduzindo a precipitação</t>
+        </is>
+      </c>
+      <c r="E862" t="inlineStr">
+        <is>
+          <t>Proximidade com a linha do Equador e a corrente de Humboldt que, devido à elevada insolação, evapora rapidamente qualquer precipitação</t>
+        </is>
+      </c>
+      <c r="F862" t="inlineStr">
+        <is>
+          <t>Presença da Cordilheira dos Andes que facilita a entrada de massas de ar frias e secas do interior do continente, aumentando a evaporatividade.</t>
+        </is>
+      </c>
+      <c r="G862" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H862" t="inlineStr">
+        <is>
+          <t>A elevação da Cordilheira dos Andes age como uma barreira que bloqueia a umidade vinda do Oceano Atlântico. A corrente de Humboldt, por sua vez, resfria o ar que chega do Oceano Pacífico, criando condições atmosféricas que reduzem ainda mais a possibilidade de precipitação, contribuindo para a extrema aridez do deserto.</t>
+        </is>
+      </c>
+      <c r="I862" t="inlineStr">
+        <is>
+          <t>PH08</t>
+        </is>
+      </c>
+      <c r="J862" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K862" t="inlineStr"/>
+      <c r="L862" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>A agricultura era o grande pilar da economia Inca, além de ser a fonte de toda a alimentação desse povo, fortemente baseada no milho e na batata. Portanto, era tratada com a importância devida e isso se reflete na engenhosidade das técnicas de terraceamento aplicadas pelos Incas.
+É uma técnica especialmente usada em regiões íngremes e bastante trabalhosa, exigindo bastante trabalho humano, sem muito espaço para o uso de maquinários. Ela é tão eficiente que, mesmo nos dias de hoje, com todo o avanço tecnológico, continua sendo relevante para diversas culturas agrícolas.
+Disponível em: https://machupicchubrasil.com.br/blog/terracos-incas-entenda-a-engenhosidade-dos-incas-na-agricultura/. Acesso em 9 de dez de 2024.
+A eficiência da técnica de terraceamento inca, conhecida como "andenes", era fundamental para a agricultura no Império Inca porque:</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>Permitia a plantação em vastas áreas planas, disponíveis na região dos Andes.</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>Evitava a erosão do solo e melhorava o controle da irrigação nas áreas montanhosas.</t>
+        </is>
+      </c>
+      <c r="D863" t="inlineStr">
+        <is>
+          <t>Facilitava a utilização de maquinários pesados na agricultura em áreas de difícil acesso</t>
+        </is>
+      </c>
+      <c r="E863" t="inlineStr">
+        <is>
+          <t>Aumentava a produção de milho e batata devido ao uso de fertilizantes químicos modernos</t>
+        </is>
+      </c>
+      <c r="F863" t="inlineStr">
+        <is>
+          <t>Garantia o isolamento das plantações de pragas e doenças devido à altitude elevada das terras cultivadas.</t>
+        </is>
+      </c>
+      <c r="G863" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H863" t="inlineStr">
+        <is>
+          <t>A técnica de "andenes" permitia o cultivo em terrenos íngremes ao criar terraços que evitavam a erosão do solo e facilitavam o controle da irrigação, sendo essencial para a agricultura nas áreas montanhosas dos Andes.</t>
+        </is>
+      </c>
+      <c r="I863" t="inlineStr">
+        <is>
+          <t>PH08</t>
+        </is>
+      </c>
+      <c r="J863" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K863" t="inlineStr"/>
+      <c r="L863" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>As placas tectônicas que formam o manto terrestre flutuam continuamente sobre camadas de rochas parcialmente sólidas e parcialmente derretidas. Nos lugares onde as placas colidem ou se despedaçam, a terra se mexe literalmente.
+Alguns vulcões podem se formar onde o manto é dilacerado – por exemplo, no Havaí, no meio da Placa do Pacífico. A maioria dos vulcões se localiza na região de encontro das placas tectônicas. Montanhas, como os Andes na América do Sul ou as Montanhas Rochosas na América do Norte, foram criadas dessa forma.
+Disponível em: https://www.dw.com/pt-br/seis-fatos-sobre-o-c%C3%ADrculo-de-fogo-do-pac%C3%ADfico/a-52005240. Acesso em 9 de dez de 2024.
+Sobre o Círculo de Fogo do Pacífico, é correto afirmar que:</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>No Círculo de Fogo do Pacífico, a atividade sísmica é baixa devido ao afastamento das placas tectônicas.</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>As montanhas formadas no Círculo de Fogo do Pacífico são resultado do afastamento das placas tectônicas.</t>
+        </is>
+      </c>
+      <c r="D864" t="inlineStr">
+        <is>
+          <t>As placas tectônicas no Círculo de Fogo do Pacífico colidem, resultando na intensa atividade sísmica e formação de vulcões.</t>
+        </is>
+      </c>
+      <c r="E864" t="inlineStr">
+        <is>
+          <t>O Círculo de Fogo do Pacífico abrange principalmente áreas de estabilidade geológica, com pouca atividade vulcânica e sísmica.</t>
+        </is>
+      </c>
+      <c r="F864" t="inlineStr">
+        <is>
+          <t>A atividade vulcânica no Círculo de Fogo do Pacífico é causada pela presença de uma única placa tectônica que cobre toda a região.</t>
+        </is>
+      </c>
+      <c r="G864" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H864" t="inlineStr">
+        <is>
+          <t>As colissões das placas tectônicas no Círculo de Fogo do Pacífico geram intensa atividade sísmica e vulcânica. A região é rica em vulcões ativos e terremotos frequentes devido à convergência e subducção das placas.</t>
+        </is>
+      </c>
+      <c r="I864" t="inlineStr">
+        <is>
+          <t>PH08</t>
+        </is>
+      </c>
+      <c r="J864" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K864" t="inlineStr"/>
+      <c r="L864" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>Libertadores está em sua terceira rodada da fase de grupos e Flamengo e Palmeiras jogam fora de casa (...). Os dois brasileiros terão que enfrentar as altitudes da Bolívia e do Equador, respectivamente.
+Os países localizados mais próximos da Cordillheira dos Andes possuem uma elevada altitude em relação ao nivel do mar. Para se ter uma ideia, o Rio de Janeiro, cidade litorânea, tem a altitude próxima a zero. Já São Paulo fica a 760 metros do nível do mar. 
+Disponível em: https://www.acidadeon.com/tudoep/tudo-esporte/libertadores-qual-a-dificuldade-de-jogar-na-altitude/. Acesso em 9 de dez de 2024.
+Sobre o desempenho dos times brasileiros na Libertadores, é correto afirmar que a altitude elevada encontrada em algumas cidades dos países andinos é considerada um fator de dificuldade porque:</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>A densidade do ar em altitudes elevadas é maior, o que faz com que a bola de futebol se mova mais lentamente no campo.</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>A menor densidade do ar em altitudes elevadas reduz a quantidade de oxigênio, o que pode causar cansaço nos jogadores.</t>
+        </is>
+      </c>
+      <c r="D865" t="inlineStr">
+        <is>
+          <t>A pressão atmosférica mais alta em altitudes elevadas aumenta a força da gravidade, dificultando a movimentação dos jogadores.</t>
+        </is>
+      </c>
+      <c r="E865" t="inlineStr">
+        <is>
+          <t>A umidade relativa do ar é mais baixa em altitudes altas, o que aumenta a desidratação dos jogadores e causa cansaço extremo.</t>
+        </is>
+      </c>
+      <c r="F865" t="inlineStr">
+        <is>
+          <t>A temperatura mais alta em altitudes mais elevadas faz com que os jogadores sintam mais calor e se desidratem mais rapidamente.</t>
+        </is>
+      </c>
+      <c r="G865" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H865" t="inlineStr">
+        <is>
+          <t>Nas altitudes elevadas, como as encontradas nos países andinos, há uma menor quantidade de oxigênio disponível devido à menor densidade do ar. Isso pode causar um cansaço mais rápido nos jogadores, que não estão acostumados a essas condições, afetando seu desempenho físico durante as partidas.</t>
+        </is>
+      </c>
+      <c r="I865" t="inlineStr">
+        <is>
+          <t>PH08</t>
+        </is>
+      </c>
+      <c r="J865" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K865" t="inlineStr"/>
+      <c r="L865" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>Os elementos climáticos são compreendidos pelas variáveis meteorológicas que influenciam as condições do clima em uma determinada região. Esses elementos incluem a temperatura do ar, umidade do ar, pressão atmosférica, entre outros. Nas regiões mais próximas à Linha do Equador são áreas mais quentes e conforme vamos nos distanciando do Equador a tendência é que essas regiões sejam mais frias. Outro elemento que se torna comum é quando se encontra os cumes das montanhas, regiões congeladas sendo importante levar um casaco caso deseje subir.
+Disponível em: https://sme.goiania.go.gov.br/conexaoescola/ensino_fundamental/geografia-mentos-cma/. Acesso em: 9 dez. 2024.
+Por que é importante considerar a altitude e a latitude ao analisar o clima de uma região?</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>Na Linha do Equador e em altas altitudes, encontramos as regiões mais frias devido à menor quantidade de insolação.</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>A altitude influencia diretamente a temperatura, sendo mais quente nos cumes das montanhas devido à maior proximidade com o Sol.</t>
+        </is>
+      </c>
+      <c r="D866" t="inlineStr">
+        <is>
+          <t>A latitude e altitude determinam a quantidade de radiação solar recebida, afetando a temperatura e condições climáticas locais.</t>
+        </is>
+      </c>
+      <c r="E866" t="inlineStr">
+        <is>
+          <t>Próximas ao Equador, as regiões tendem a ser mais frias devido à alta umidade do ar e menor pressão atmosférica.</t>
+        </is>
+      </c>
+      <c r="F866" t="inlineStr">
+        <is>
+          <t>Nas regiões polares e em baixas altitudes, encontramos as áreas mais quentes devido à menor densidade do ar.</t>
+        </is>
+      </c>
+      <c r="G866" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H866" t="inlineStr">
+        <is>
+          <t>A latitude influencia a quantidade de radiação solar que uma região recebe – mais intensa no Equador e menos nos polos. A altitude influencia a temperatura, com regiões mais altas sendo mais frias devido à menor densidade do ar e menor pressão atmosférica.</t>
+        </is>
+      </c>
+      <c r="I866" t="inlineStr">
+        <is>
+          <t>PH08</t>
+        </is>
+      </c>
+      <c r="J866" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K866" t="inlineStr"/>
+      <c r="L866" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>A grande extensão no sentido norte-sul, as diferentes latitudes e a variação climática conferem à América Latina uma enorme diversidade de formações vegetais. Sobre as características das formações vegetais, é correto afirmar que</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>a Caatinga, os Estepes e a Floresta Tropical estão associados à baixa umidade.</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>as Florestas Temperadas estão localizadas nas regiões próximas à linha do Equador.</t>
+        </is>
+      </c>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>a vegetação de deserto ocupa grande parte da América Latina.</t>
+        </is>
+      </c>
+      <c r="E867" t="inlineStr">
+        <is>
+          <t>a Floresta Equatorial se desenvolve em áreas úmidas e quentes.</t>
+        </is>
+      </c>
+      <c r="F867" t="inlineStr">
+        <is>
+          <t>a vegetação de Pampas apresenta árvores de porte alto.</t>
+        </is>
+      </c>
+      <c r="G867" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H867" t="inlineStr">
+        <is>
+          <t>A formação vegetal Floresta Equatorial está localizada próximo à linha do Equador, que é uma região de muita umidade, apresentando chuvas durante o ano todo, e altas temperaturas, pela intensa e vertical incidência solar.</t>
+        </is>
+      </c>
+      <c r="I867" t="inlineStr">
+        <is>
+          <t>PH08</t>
+        </is>
+      </c>
+      <c r="J867" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K867" t="inlineStr"/>
+      <c r="L867" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>Na bacia hidrográfica acima, localiza-se um enorme aquífero; um grande reservatório de águas subterrâneas localizado a centenas de metros de profundidade. Com cerca de 1,2 milhão de quilômetros quadrados, esse aquífero está presente em quatro países sul-americanos: Argentina, Brasil, Paraguai e Uruguai, sendo que aproximadamente 70% desse reservatório de água está localizado no Brasil, espalhado pelo subsolo de Mato Grosso, Mato Grosso do Sul, Goiás, Minas Gerais, São Paulo, Paraná, Rio Grande do Sul e Santa Catarina. Esse aquífero é denominado:</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>Sistema Aquífero Itapecuru.</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>Sistema Aquífero Guarani.</t>
+        </is>
+      </c>
+      <c r="D868" t="inlineStr">
+        <is>
+          <t>Sistema Aquífero Alter do Chão.</t>
+        </is>
+      </c>
+      <c r="E868" t="inlineStr">
+        <is>
+          <t>Sistema Aquífero Urucuia-Areado.</t>
+        </is>
+      </c>
+      <c r="F868" t="inlineStr">
+        <is>
+          <t>Sistema Aquífero Platino.</t>
+        </is>
+      </c>
+      <c r="G868" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H868" t="inlineStr">
+        <is>
+          <t>A área representada pelo mapa acima define a faixa de atuação do chamado Aquífero Guarani, que se expande pela Argentina, Paraguai, Uruguai, além da maior parte no Brasil (onde localiza-se 70% da área do reservatório), atingindo estados das regiões Centro-Oeste, Sudeste e Sul do país.</t>
+        </is>
+      </c>
+      <c r="I868" t="inlineStr">
+        <is>
+          <t>PH08</t>
+        </is>
+      </c>
+      <c r="J868" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K868" t="inlineStr">
+        <is>
+          <t>8a_ph08_geo_07.png</t>
+        </is>
+      </c>
+      <c r="L868" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>O continente americano, em toda a sua extensão, apresenta diversas formações de relevo. Analise as afirmativas a seguir sobre o relevo do continente americano:
+I. A costa oeste da América do Sul é marcada por altas montanhas, devido ao movimento convergente de placas tectônicas.
+II. A porção leste da América do Sul é constituída por planaltos de formação geológica muito antiga.
+III. As ilhas da América Central podem ser vulcões emersos, que se formaram pelo contato entre placas tectônicas.
+Estão corretas as afirmativas</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>I e II, apenas.</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>I e III, apenas.</t>
+        </is>
+      </c>
+      <c r="D869" t="inlineStr">
+        <is>
+          <t>I, II e III.</t>
+        </is>
+      </c>
+      <c r="E869" t="inlineStr">
+        <is>
+          <t>II e III.</t>
+        </is>
+      </c>
+      <c r="F869" t="inlineStr">
+        <is>
+          <t>III, apenas.</t>
+        </is>
+      </c>
+      <c r="G869" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H869" t="inlineStr">
+        <is>
+          <t>O litoral oeste do continente sul americano é marcado pela Cordilheira dos Andes, que é resultado do encontro entre as placas Americana e de Nazca. Já a porção leste do continente sul americano está no interior de uma placa tectônica e, por isso, possui formas de relevo muito antigas. As ilhas da América Central são vulcões resultado das atividades tectônicas da placa do Caribe.</t>
+        </is>
+      </c>
+      <c r="I869" t="inlineStr">
+        <is>
+          <t>PH08</t>
+        </is>
+      </c>
+      <c r="J869" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K869" t="inlineStr"/>
+      <c r="L869" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>O mapa abaixo mostra as principais áreas desérticas do mundo.
+Os desertos podem ser formados de diversas maneiras, como pouca precipitação, barreiras naturais ao ar úmido ou reversão sazonal de correntes de ar. Na América do Sul acontecem em decorrência da atuação da seguinte corrente marítima:</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>Corrente do Golfo do México.</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>Corrente do Pacífico Norte.</t>
+        </is>
+      </c>
+      <c r="D870" t="inlineStr">
+        <is>
+          <t>Corrente de Humboldt.</t>
+        </is>
+      </c>
+      <c r="E870" t="inlineStr">
+        <is>
+          <t>Corrente de Falklands.</t>
+        </is>
+      </c>
+      <c r="F870" t="inlineStr">
+        <is>
+          <t>Corrente do Pacífico Sul.</t>
+        </is>
+      </c>
+      <c r="G870" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H870" t="inlineStr">
+        <is>
+          <t>Na costa do Chile e do Peru passa a corrente de Humboldt, responsável pela baixa temperatura da água, e, em parte, pela redução da temperatura do ar. Como o ar e o mar trocam calor constantemente, a água mais fria dificulta a evaporação e propicia a condensação do vapor de água que se encontra no ar. Assim, a precipitação ocorre ainda no mar e as massas de ar chegam secas ao continente, condicionando a formação de desertos.</t>
+        </is>
+      </c>
+      <c r="I870" t="inlineStr">
+        <is>
+          <t>PH08</t>
+        </is>
+      </c>
+      <c r="J870" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K870" t="inlineStr">
+        <is>
+          <t>8a_ph08_geo_09.png</t>
+        </is>
+      </c>
+      <c r="L870" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>Considerada a rede hidrográfica mais extensa do mundo, [...] ocupa uma área total de 7.008.370 km2. Esta área vai desde as nascentes, nos Andes Peruanos, até sua foz (local onde o rio deságua) no Oceano Atlântico - 64,88% (ou 3.843.402 km2) desse total ficam em território brasileiro e o restante está dividido entre a Colômbia (16,14%), Bolívia (15,61%), Equador (2,31%), Guiana (1,35%), Peru (0,60%) e Venezuela (0,11%).
+Disponível em: http://www.brasil.gov.br/noticias/meio-ambiente/2009/10/rios-e-bacias-do-brasil-formam-uma-das-maiores-redes-fluviais-do-mundo. Acesso em: 1 abr. 2019.
+O texto faz referência à bacia hidrográfica sul americana chamada</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>Platina.</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>São Francisco.</t>
+        </is>
+      </c>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>Amazônica.</t>
+        </is>
+      </c>
+      <c r="E871" t="inlineStr">
+        <is>
+          <t>Paraná.</t>
+        </is>
+      </c>
+      <c r="F871" t="inlineStr">
+        <is>
+          <t>Guarani.</t>
+        </is>
+      </c>
+      <c r="G871" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H871" t="inlineStr">
+        <is>
+          <t>O texto se refere à bacia Amazônica, porque expõe que ela é a mais extensa do mundo, que recebe recarga nos Andes e deságua no Atlântico, indicando que está inserida em diversos países da América do Sul.</t>
+        </is>
+      </c>
+      <c r="I871" t="inlineStr">
+        <is>
+          <t>PH08</t>
+        </is>
+      </c>
+      <c r="J871" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K871" t="inlineStr"/>
+      <c r="L871" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>Por razões semelhantes, a empresa do continente europeu dependia muito mais do que a britânica de um aparato financeiro e de uma moderna legislação bancária, comercial e de negócios. De fato, a Revolução Francesa forneceu os dois: os códigos legais de Napoleão, com sua ênfase na liberdade contratual garantida legalmente, seu reconhecimento das letras de câmbio e outros papéis comerciais, e suas disposições em prol das empresas de capital social tornaram-se por esta razão os modelos gerais para o mundo.
+HOBSBAWM, E. A Era das Revoluções: 1789 - 1848. São Paulo, Paz e Terra. 4ª ed.
+Qual foi uma das principais contribuições do Código Civil Napoleônico para a sociedade francesa?</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>Promoveu a educação religiosa obrigatória.</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>Proibiu qualquer tipo de comércio internacional.</t>
+        </is>
+      </c>
+      <c r="D872" t="inlineStr">
+        <is>
+          <t>Aboliu completamente os direitos dos trabalhadores.</t>
+        </is>
+      </c>
+      <c r="E872" t="inlineStr">
+        <is>
+          <t>Estabeleceu a igualdade jurídica entre homens e mulheres.</t>
+        </is>
+      </c>
+      <c r="F872" t="inlineStr">
+        <is>
+          <t>Definiu regras para uma sociedade com mais liberdade individual.</t>
+        </is>
+      </c>
+      <c r="G872" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H872" t="inlineStr">
+        <is>
+          <t>O Código Civil Napoleônico foi responsável por estabelecer normas que diminuíam a intervenção estatal nas relações entre os cidadãos, promovendo a afirmação do individualismo e dos objetivos burgueses, alinhados aos princípios revolucionários iluministas. Este código teve um impacto significativo na sociedade francesa e em muitos códigos civis do mundo ocidental.</t>
+        </is>
+      </c>
+      <c r="I872" t="inlineStr">
+        <is>
+          <t>PH08</t>
+        </is>
+      </c>
+      <c r="J872" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K872" t="inlineStr"/>
+      <c r="L872" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>O brilhante sucesso da Campanha de Napoleão na Itália ganhou-lhe o amor de suas tropas, que se referiam carinhosamente a ele como “o Pequeno Cabo”. A Campanha na Itália também lançou Napoleão ao estrelato político na França; histórias como seus heroicos ataques pela ponte de Arcole tornaram-se famosas e formaram a base da lenda napoleônica. [....]
+Em outubro de 1799, Napoleão chegou na França e foi abordado por várias autoridades franceses descontentes, tais como Emmanuel-Joseph Sieyès, que queria utilizá-lo como a “espada” para um golpe de estado.
+Napoleão Bonaparte. Disponível em: https://www.worldhistory.org/trans/pt/1-21844/napoleao-bonaparte/. Acesso em: 05 dez. 2024.
+Os girondinos apoiaram Napoleão Bonaparte porque ele</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>era um jacobino convicto e influente.</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>reunia lealdade do exército e legitimidade.</t>
+        </is>
+      </c>
+      <c r="D873" t="inlineStr">
+        <is>
+          <t>se opôs a qualquer tipo de expansão territorial.</t>
+        </is>
+      </c>
+      <c r="E873" t="inlineStr">
+        <is>
+          <t>pretendia abolir os impostos sobre a burguesia.</t>
+        </is>
+      </c>
+      <c r="F873" t="inlineStr">
+        <is>
+          <t>prometeu restaurar a monarquia e os privilégios.</t>
+        </is>
+      </c>
+      <c r="G873" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H873" t="inlineStr">
+        <is>
+          <t>Napoleão foi apoiado pelos girondinos porque ele representava uma liderança militar e política convincente. Em um momento de desordem e insatisfação, Napoleão emergiu como uma figura capaz de trazer estabilidade e liderança, tanto na esfera militar quanto na política, o que era crucial para a França naquele período.</t>
+        </is>
+      </c>
+      <c r="I873" t="inlineStr">
+        <is>
+          <t>PH08</t>
+        </is>
+      </c>
+      <c r="J873" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K873" t="inlineStr"/>
+      <c r="L873" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>Nos primeiros anos do século XIX, grande parte da Europa estava sob o domínio de Napoleão Bonaparte, que se tornara imperador francês em 1804. O único obstáculo à consolidação de seu império na Europa era a Inglaterra, que, favorecida por sua posição insular, por seu poderio econômico e por sua supremacia naval, não conseguiria conquistar. Para tentar dominá-la, Napoleão usou a estratégia do Bloqueio Continental, ou seja, decretou o fechamento dos portos de todos os países europeus ao comércio inglês. Pretendia, dessa forma, enfraquecer a economia inglesa, que monopolizava o mercado consumidor europeu com seus produtos manufaturados. Com essa medida, Napoleão buscava garantir mercados consumidores para as manufaturas francesas.
+A vinda da família real para o Brasil: o Bloqueio Continental. Disponível em: https://multirio.rio.rj.gov.br/index.php/historia-do-brasil/brasil-monarquico/88
+47-a-vinda-da-fam%C3%ADlia-real-para-o-brasil-o-bloqueio-continental. Acesso em: 5 dez. 2024.
+Uma das principais causas para o fracasso do Bloqueio Continental foi a</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>incapacidade de Portugal barrar os negócios entre Inglaterra e Espanha.</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>insatisfação da Igreja, que orientou os reinos a furarem o bloqueio.</t>
+        </is>
+      </c>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>falta de cavalos para transportar as mercadorias pelo continente.</t>
+        </is>
+      </c>
+      <c r="E874" t="inlineStr">
+        <is>
+          <t>dificuldade em substituir os produtos industrializados ingleses.</t>
+        </is>
+      </c>
+      <c r="F874" t="inlineStr">
+        <is>
+          <t>crise econômica por falta de matéria-prima na Inglaterra.</t>
+        </is>
+      </c>
+      <c r="G874" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H874" t="inlineStr">
+        <is>
+          <t>A dificuldade em substituir os produtos industrializados ingleses foi uma das principais causas para o fracasso do Bloqueio Continental. A incapacidade da França em fornecer produtos equivalentes aos mercados europeus gerou insatisfação e desobediência às determinações de Napoleão, minando a eficácia do bloqueio.</t>
+        </is>
+      </c>
+      <c r="I874" t="inlineStr">
+        <is>
+          <t>PH08</t>
+        </is>
+      </c>
+      <c r="J874" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K874" t="inlineStr"/>
+      <c r="L874" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>Em 9 de novembro de 1799, no que ficou conhecido como Golpe do 18 Brumário, Napoleão ascendeu ao poder como cônsul. “As vitórias no campo militar e econômico – e o consequente apoio dos grupos mais abastados – deram a ele a legitimidade para alcançar a condição de imperador”, segundo Carvalho. Uma mudança na Constituição foi aprovada em 1804 e garantia que o governo da República seria confiado a um imperador, que assumiria o título de Imperador dos Franceses. 
+[...] “Muitos republicanos ficaram furiosos com um comandante militar que estava se fazendo ungir com algum suposto direito divino; muitos católicos ficaram chocados com o que entendiam ser a manipulação da fé e a humilhação do papa” [...].
+Napoleão Bonaparte é coroado Imperador. Disponível em: https://www.fflch.usp.br/41855. Acesso em: 5 dez. 2024.
+Qual contradição fundamental surgiu entre os princípios republicanos da Revolução Francesa e a consolidação de Napoleão Bonaparte como imperador da França em 1804?</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>A centralização do poder em uma figura autoritária.</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>A implementação de reformas econômicas liberais.</t>
+        </is>
+      </c>
+      <c r="D875" t="inlineStr">
+        <is>
+          <t>A criação de um sistema educacional laico e universal.</t>
+        </is>
+      </c>
+      <c r="E875" t="inlineStr">
+        <is>
+          <t>A promoção de igualdade jurídica entre todos os cidadãos.</t>
+        </is>
+      </c>
+      <c r="F875" t="inlineStr">
+        <is>
+          <t>A manutenção da eleição direta para os cargos de governo.</t>
+        </is>
+      </c>
+      <c r="G875" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H875" t="inlineStr">
+        <is>
+          <t>A contradição fundamental que surgiu entre os princípios republicanos da Revolução Francesa e a consolidação de Napoleão Bonaparte como imperador foi a centralização do poder em uma figura autoritária. Os princípios republicanos promoviam a soberania popular e a distribuição democrática do poder, enquanto Napoleão consolidou um regime autocrático, centralizando o poder em si mesmo e tornando-se imperador.</t>
+        </is>
+      </c>
+      <c r="I875" t="inlineStr">
+        <is>
+          <t>PH08</t>
+        </is>
+      </c>
+      <c r="J875" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K875" t="inlineStr"/>
+      <c r="L875" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>Napoleão se retirando da Rússia, 1850.
+Disponível em: https://commons.wikimedia.org/wiki/File:Napoleons_retreat_from_moscow.jpg. Acesso em: 5 dez. 2024.
+A imagem apresenta a retirada de Napoleão e de suas tropas da Rússia em 1812, após uma derrota esmagadora que teve como consequência a(o)</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>desmoralização das forças monarquistas e aristocráticas europeias.</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>aumento do apoio popular e dos políticos a Napoleão na França.</t>
+        </is>
+      </c>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>expansão do território do Império Francês para o Leste Europeu.</t>
+        </is>
+      </c>
+      <c r="E876" t="inlineStr">
+        <is>
+          <t>formação de uma nova aliança militar entre Rússia e França.</t>
+        </is>
+      </c>
+      <c r="F876" t="inlineStr">
+        <is>
+          <t>enfraquecimento do exército francês e do apoio a Napoleão.</t>
+        </is>
+      </c>
+      <c r="G876" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H876" t="inlineStr">
+        <is>
+          <t>A derrota de Napoleão Bonaparte na invasão da Rússia em 1812 resultou no enfraquecimento significativo do exército francês e na perda de apoio a Napoleão. A tática das terras arrasadas e o rigoroso inverno russo levaram à morte de mais de meio milhão de soldados, devastando tanto a moral das tropas quanto a posição política de Napoleão.</t>
+        </is>
+      </c>
+      <c r="I876" t="inlineStr">
+        <is>
+          <t>PH08</t>
+        </is>
+      </c>
+      <c r="J876" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K876" t="inlineStr">
+        <is>
+          <t>8a_ph08_his_05.png</t>
+        </is>
+      </c>
+      <c r="L876" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>Napoleão viu as negociações não como uma alternativa à luta, mas como o ditado de termos para derrotar os oponentes. Ao invadir a Rússia à frente do maior e melhor exército da Europa, com grande confiança nele e em si mesmo, Napoleão cometeu um erro irrecuperável de julgamento que levaria à destruição desse exército, à destruição de suas conquistas, ao fim de seu reinado e exílio. A Rússia não apresentou ameaça para a França ou seus domínios. Em vez disso, foi um obstáculo no caminho histórico de Napoleão - seu destino - e também um trampolim para a derrota da arqui-inimiga Inglaterra. Embora o desafio da Rússia não tivesse importância existencial para ele, Napoleão fez uma aposta existencial invadindo a Rússia e perdeu.
+BINNENDIJK, H.; GOMPERT, D. C.; LIN, B. Napoleon’s Invasion of Russia, 1812. 2014, p. 42. Tradução livre. Disponível em:
+&lt;https://www.jstor.org&gt;. Acesso em: 31 mar. 2020
+O conflito com a Rússia marca o início da decadência da Era Napoleônica. Apesar da superioridade militar francesa demonstrada pelo texto, os russos foram capazes de impedir a conquista francesa</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>apoiando-se no auxílio britânico, que garantiu a superioridade bélica das tropas russas no conflito.</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>adotando uma tática da “terra arrasada”, recuando para o interior do território e destruindo suprimentos durante o rigoroso inverno russo.</t>
+        </is>
+      </c>
+      <c r="D877" t="inlineStr">
+        <is>
+          <t>estabelecendo uma guerra de trincheiras na fronteira com a Polônia, impedindo o avanço francês pelo território até a chegada de tropas aliadas.</t>
+        </is>
+      </c>
+      <c r="E877" t="inlineStr">
+        <is>
+          <t>rendendo-se às tropas napoleônicas, sob a condição de que pudessem manter as relações comerciais com a Inglaterra, o que frustrou o Bloqueio Continental.</t>
+        </is>
+      </c>
+      <c r="F877" t="inlineStr">
+        <is>
+          <t>revertendo o avanço das tropas francesas no território russo e levando o combate para os territórios conquistados, reestabelecendo monarquias e destituindo governos aliados de Napoleão.</t>
+        </is>
+      </c>
+      <c r="G877" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H877" t="inlineStr">
+        <is>
+          <t>A estratégia adotada pelos russos que permitiu a vitória foi a tática da "terra arrasada". Ao recuar, os russos evitaram um confronto direto e prolongaram as linhas de suprimento do exército francês. Além disso, eles destruíram plantações, cidades e recursos vitais ao longo do caminho, deixando para trás uma paisagem desolada. Isso dificultou a sobrevivência do exército invasor, contribuindo para sua derrota devido à falta de suprimentos, fome e condições climáticas adversas durante o inverno russo.</t>
+        </is>
+      </c>
+      <c r="I877" t="inlineStr">
+        <is>
+          <t>PH08</t>
+        </is>
+      </c>
+      <c r="J877" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K877" t="inlineStr"/>
+      <c r="L877" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>Em junho de 1812, o Grande Exército do imperador Napoleão Bonaparte cruzou o Rio Niêmen, na fronteira da Polônia com a Rússia, rumo à capital Moscou. A idEia era atacar seu antigo aliado, o Czar Alexandre I [...]. Ao invés de planejar um contra-ataque bélico em igual proporção, os russos optaram pela estratégia de recuar e destruir os campos por onde o exército napoleônico passaria, impossibilitando seus atos de pilhagem, de alimentação e locomoção.[...] Dos 422 mil soldados que cruzaram o Rio Niêmen no início da campanha, apenas 10 mil o atravessaram com vida no retorno.
+BOVO, E. Grande história universal – Época napoleônica. Barcelona: Folio, 2007
+A campanha militar de Napolão contra a Rússia foi desastrosa e resultou em uma grande perda humana. O principal motivo da invasão da Rússia por Napoleão foi a(o)</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>eclosão da revolução russa liderada por Lenin.</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>quebra do Bloqueio Continental por parte dos russos.</t>
+        </is>
+      </c>
+      <c r="D878" t="inlineStr">
+        <is>
+          <t>investida russa em territórios controlados por Napoleão.</t>
+        </is>
+      </c>
+      <c r="E878" t="inlineStr">
+        <is>
+          <t>emergência do Império Russo como potência militar europeia.</t>
+        </is>
+      </c>
+      <c r="F878" t="inlineStr">
+        <is>
+          <t>necessidade de eliminar os grupos mais radicais da esquerda europeia.</t>
+        </is>
+      </c>
+      <c r="G878" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H878" t="inlineStr">
+        <is>
+          <t>A imposição do Bloqueio Continental foi penosa para diversos países, especialmente para a Rússia, que exportava produtos para a Inglaterra em larga escala. Abalada economicamente, a Rússia decidiu desobedecer Napoleão e restabelecer o comércio com a Inglaterra. Napoleão, então, tentou invadir a Rússia, que mesmo inferior militarmente, derrotou os franceses utilizando a estratégia da "terra arrasada".</t>
+        </is>
+      </c>
+      <c r="I878" t="inlineStr">
+        <is>
+          <t>PH08</t>
+        </is>
+      </c>
+      <c r="J878" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K878" t="inlineStr"/>
+      <c r="L878" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>Napoleão estava se preparando para uma invasão do Haiti. Um tratado preliminar foi assinado com a Inglaterra em 1º de outubro de 1801. Esse tratado tornou possível a intervenção de Napoleão no Haiti. Um general, com instruções secretas e 10.000 veteranos franceses, navegou de Brest ao Haiti para recuperar a ilha.
+WOODWARD, I. A. Toussaint Louverture and the struggle of his people against revolutionary France and Napoleon. Negro History
+Bulletin, vol. 23, n. 3, p. 55. Tradução livre. Adaptado. Disponível em: &lt;https://www.jstor.org/stable/&gt;. Acesso em: 31 mar. 2020.
+Em 1801, as tropas napoleônicas se dirigiram ao recém-independente Haiti com o objetivo de retomar o território para o império francês. A tentativa de recolonização do Haiti</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>foi apoiada pelos ingleses como uma condição para o fim do Bloqueio Continental imposto por Napoleão.</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>era uma forma de expandir o domínio francês para as Américas e combater os Estados Unidos recém-independentes.</t>
+        </is>
+      </c>
+      <c r="D879" t="inlineStr">
+        <is>
+          <t>buscava manter nas colônias francesas o trabalho assalariado e a igualdade jurídica e política frente aos franceses.</t>
+        </is>
+      </c>
+      <c r="E879" t="inlineStr">
+        <is>
+          <t>originava-se da preocupação francesa em expandir as políticas do Código Napoleônico e a Declaração dos Direitos do Homem e do Cidadão por toda a extensão terrestre.</t>
+        </is>
+      </c>
+      <c r="F879" t="inlineStr">
+        <is>
+          <t>exprimia a contradição entre a máxima “Liberdade, Igualdade e Fraternidade”, lema da Revolução Francesa, e as políticas adotadas por Napoleão sob esses ideais.</t>
+        </is>
+      </c>
+      <c r="G879" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H879" t="inlineStr">
+        <is>
+          <t>A tentativa de recolonização demonstra a divergência entre as propostas políticas de Revolução Francesa e sua herança com a prática política de Napoleão. Ao tentar recolonizar e restabelecer a escravidão nas colônias francesas, os ideais de Igualdade e Liberdade foram deixados de lado.</t>
+        </is>
+      </c>
+      <c r="I879" t="inlineStr">
+        <is>
+          <t>PH08</t>
+        </is>
+      </c>
+      <c r="J879" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K879" t="inlineStr"/>
+      <c r="L879" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>Império da França
+Disponível em: &lt; https://pt.wikipedia.org/wiki/Ficheiro:First_French_Empire_1812.svg&gt;. Acesso em: 13 abr. 2020
+ Entre as consequências da expansão das fronteiras e da influência francesa durante o Império Napoleônico, podemos citar a</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>propagação da fé católica.</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>expansão dos ideais monárquicos.</t>
+        </is>
+      </c>
+      <c r="D880" t="inlineStr">
+        <is>
+          <t>difusão dos ideais da Revolução Francesa.</t>
+        </is>
+      </c>
+      <c r="E880" t="inlineStr">
+        <is>
+          <t>demonstração da superioridade bélica inglesa.</t>
+        </is>
+      </c>
+      <c r="F880" t="inlineStr">
+        <is>
+          <t>testagem de práticas militares antes da invasão da Rússia.</t>
+        </is>
+      </c>
+      <c r="G880" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H880" t="inlineStr">
+        <is>
+          <t>O processo de expansão napoleônico teve como uma de suas principais consequências a difusão dos ideais revolucionários, contribuindo assim para a queda dos governos absolutistas ao longo do território europeu.</t>
+        </is>
+      </c>
+      <c r="I880" t="inlineStr">
+        <is>
+          <t>PH08</t>
+        </is>
+      </c>
+      <c r="J880" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K880" t="inlineStr">
+        <is>
+          <t>8a_ph08_his_09.png</t>
+        </is>
+      </c>
+      <c r="L880" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>O regime napoleônico representou uma síntese engenhosa de elementos antigos e novos, que enfrentaram com sucesso muitos dos problemas levantados pela década revolucionária anterior.
+CROOK, M. Polychronicon: Revolutionary emperor? Reinterpreting Napoleon. Teaching History, n. 158, p. 38. Tradução livre.
+Disponível em: &lt;https://www.jstor.org/&gt;. Acesso em: 31 mar. 2020. 
+O início da Era Napoleônica (1799-1815) foi marcado por uma série de mudanças estruturais na organização da sociedade francesa. Assinale a alternativa que apresenta mudanças empregadas durante o regime.</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>Criação do Código Civil e de uma moeda comum na Europa.</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>Reforço da centralização política e criação do Banco da França.</t>
+        </is>
+      </c>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>Submissão à Igreja Católica e assinatura de Tratados de Paz com países inimigos.</t>
+        </is>
+      </c>
+      <c r="E881" t="inlineStr">
+        <is>
+          <t>Alteração da moeda e responsabilização das indústrias pela formação educacional.</t>
+        </is>
+      </c>
+      <c r="F881" t="inlineStr">
+        <is>
+          <t>Restauração do Governo Jacobino durante a etapa imperial e alteração dos Códigos Jurídicos.</t>
+        </is>
+      </c>
+      <c r="G881" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H881" t="inlineStr">
+        <is>
+          <t>Com a chegada de Napoleão ao poder, suas medidas tinham por objetivo a reestruturação da França interna e externamente. Para isso, foi realizada a centralização do poder na figura de um líder maior e a reorganização econômica a partir da criação do Banco da França, de forma a solucionar a crise financeira pós-Revolução.</t>
+        </is>
+      </c>
+      <c r="I881" t="inlineStr">
+        <is>
+          <t>PH08</t>
+        </is>
+      </c>
+      <c r="J881" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K881" t="inlineStr"/>
+      <c r="L881" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>TODOS – Viva Miguel Federóvitch! Viva Miguel Federóvitch!
+MIGUEL – Senhor, não sei como agradecer a Vossa Majestade...
+PAI UBU – Ora, meu amigo, não tem de que. Leva tua caixa de ouro pra casa, Miguel. E vocês, dividam esta outra, cada um tira uma moeda de cada vez, até acabar.
+TODOS - Viva Miguel Federóvitch! Viva Pai Ubu!
+Disponível em: https://resistir.info/livros/ubu_rei.pdf. Acesso em 04 de dez. 2024.
+As reticências no trecho da peça foram utilizadas para</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>criar suspense.</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>sugerir continuidade.</t>
+        </is>
+      </c>
+      <c r="D882" t="inlineStr">
+        <is>
+          <t>omitir partes do texto.</t>
+        </is>
+      </c>
+      <c r="E882" t="inlineStr">
+        <is>
+          <t>expressar emoções não verbalizadas.</t>
+        </is>
+      </c>
+      <c r="F882" t="inlineStr">
+        <is>
+          <t>indicar interrupção da fala por outra personagem.</t>
+        </is>
+      </c>
+      <c r="G882" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H882" t="inlineStr">
+        <is>
+          <t>As reticências foram utilizadas para expressar pensamentos demasiado complexos que são difíceis de articular em palavras, indicando a dificuldade de Miguel em encontrar palavras para agradecer.</t>
+        </is>
+      </c>
+      <c r="I882" t="inlineStr">
+        <is>
+          <t>PH08</t>
+        </is>
+      </c>
+      <c r="J882" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K882" t="inlineStr"/>
+      <c r="L882" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>REI – Que loucura! O senhor Ubu é um fidalgo muito digno que obedece cegamente às minhas ordens
+Disponível em: https://resistir.info/livros/ubu_rei.pdf. Acesso em 4 de dez. 2024.
+Na fala do Rei, o verbo "obedecer" é</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>intransitivo ou transitivo direto.</t>
+        </is>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>transitivo direito que exige um objeto direto.</t>
+        </is>
+      </c>
+      <c r="D883" t="inlineStr">
+        <is>
+          <t>transitivo indireto que exige a preposição "a".</t>
+        </is>
+      </c>
+      <c r="E883" t="inlineStr">
+        <is>
+          <t>bitransitivo que exige complemento direto e indireto.</t>
+        </is>
+      </c>
+      <c r="F883" t="inlineStr">
+        <is>
+          <t>transitivo indireto que exige preposição e pronome relativo.</t>
+        </is>
+      </c>
+      <c r="G883" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H883" t="inlineStr">
+        <is>
+          <t>O verbo "obedece" é transitivo indireto e exige a preposição "a" para introduzir o complemento "às minhas ordens".</t>
+        </is>
+      </c>
+      <c r="I883" t="inlineStr">
+        <is>
+          <t>PH08</t>
+        </is>
+      </c>
+      <c r="J883" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K883" t="inlineStr"/>
+      <c r="L883" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>RAINHA – Oh, Bugrelau! Quando me lembro o quanto éramos felizes antes da chegada de Pai Ubu! Mas agora, ai de mim, tudo mudou!
+Disponível em: https://resistir.info/livros/ubu_rei.pdf Acesso em 04 de dez. 2024.
+A frase possui um erro de regência verbal, pois o verbo "lembrar" deveria ser seguido por um(a)</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>preposição ("de"), por causa do pronome "me".</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>objeto indireto, sem o pronome "me".</t>
+        </is>
+      </c>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>objeto direto, sem preposição.</t>
+        </is>
+      </c>
+      <c r="E884" t="inlineStr">
+        <is>
+          <t>objeto direto e indireto.</t>
+        </is>
+      </c>
+      <c r="F884" t="inlineStr">
+        <is>
+          <t>pronome relativo.</t>
+        </is>
+      </c>
+      <c r="G884" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H884" t="inlineStr">
+        <is>
+          <t>O verbo "lembrar", quando pronominal (lembrar-se), exige a preposição "de". Portanto, a frase correta seria "Quando me lembro do quanto éramos felizes".</t>
+        </is>
+      </c>
+      <c r="I884" t="inlineStr">
+        <is>
+          <t>PH08</t>
+        </is>
+      </c>
+      <c r="J884" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K884" t="inlineStr"/>
+      <c r="L884" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>MÃE UBU (sozinha) - Agora que esse bonecão de engonço foi embora, tratemos de nossos interesses: matar Bugrelau e nos apossar do tesouro.
+Disponível em: https://resistir.info/livros/ubu_rei.pdf. Acesso em 04 de dez. 2024.
+Os dois-pontos na fala da Mãe Ubu</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>explica a causa do personagem mencionado ir embora.</t>
+        </is>
+      </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>introduz uma pausa para criar suspense na fala.</t>
+        </is>
+      </c>
+      <c r="D885" t="inlineStr">
+        <is>
+          <t>esclarece uma ideia apresentada na frase.</t>
+        </is>
+      </c>
+      <c r="E885" t="inlineStr">
+        <is>
+          <t>conecta a frase principal à subordinada.</t>
+        </is>
+      </c>
+      <c r="F885" t="inlineStr">
+        <is>
+          <t>reproduz a fala de outra personagem.</t>
+        </is>
+      </c>
+      <c r="G885" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H885" t="inlineStr">
+        <is>
+          <t>Os dois-pontos são usados para esclarecer a ideia apresentada na frase, detalhando quais são os interesses da Mãe Ubu.</t>
+        </is>
+      </c>
+      <c r="I885" t="inlineStr">
+        <is>
+          <t>PH08</t>
+        </is>
+      </c>
+      <c r="J885" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K885" t="inlineStr"/>
+      <c r="L885" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>Peça triste e que mostra uma Medéia cheia de rancor e mágoa, capaz de fazer as maiores atrocidades para se vingar da traição de seu marido, Jasão. Este que se casou com a filha de Creonte, rei de Corinto, (provavelmente o mesmo Creonte irmão de Jocasta, pois após a morte do rei de Corinto, um arauto vai a Tebas e avisa Édipo de que agora é rei de Corinto e Tebas, com Édipo exilado e com Creonte no trono real de Tebas, o único que possui o direito sobre o reinado de Corinto é também ele).
+Disponível em: https://www.mitografias.com.br/2017/03/medeia-de-euripedes/. Acesso em 4 de dez. 2024.
+Sobre a regência verbal no trecho acima, é correto afirmar que o verbo</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>"casar" é transitivo direto e exige objeto direto.</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>"mostrar" exige complemento com preposição.</t>
+        </is>
+      </c>
+      <c r="D886" t="inlineStr">
+        <is>
+          <t>"vingar" é transitivo direto e exige objeto direto.</t>
+        </is>
+      </c>
+      <c r="E886" t="inlineStr">
+        <is>
+          <t>"possuir" é transitivo indireto e exige preposição.</t>
+        </is>
+      </c>
+      <c r="F886" t="inlineStr">
+        <is>
+          <t>"avisar" é transitivo direto e não exige preposição.</t>
+        </is>
+      </c>
+      <c r="G886" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H886" t="inlineStr">
+        <is>
+          <t>Embora o verbo "avisar" seja bitransitivo, na frase "um arauto vai a Tebas e avisa Édipo de que agora é rei de Corinto e Tebas" o verbo "avisar" é seguido diretamente pelo objeto direto "Édipo", o que demonstra que, no contexto fornecido, "avisar" está sendo utilizado como um verbo transitivo direto, sendo ligado diretamente ao seu complemento sem a intermediação de uma preposição.</t>
+        </is>
+      </c>
+      <c r="I886" t="inlineStr">
+        <is>
+          <t>PH08</t>
+        </is>
+      </c>
+      <c r="J886" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K886" t="inlineStr"/>
+      <c r="L886" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>O dramaturgo paraibano radicado em Pernambuco Ariano Suassuna é um dos maiores expoentes do teatro cômico brasileiro. Suas peças foram traduzidas a várias línguas e sua obra mais conhecida, Auto da Compadecida, já ganhou três adaptações ao cinema e uma à TV. A seguir, você lerá um trecho da comédia O santo e a porca.
+O pano abre na casa de EURICO ARÁBE, mais conhecido como EURICÃO ENGOLE-COBRA.
+CAROBA — E foi então que o patrão dele disse: “Pinhão, você sele o cavalo e vá na minha frente procurar Euricão...”
+EURICÃO — Euricão, não. Meu nome é Eurico.
+CAROBA — Sim, é isso mesmo. Seu Eudoro Vicente disse: “Pinhão, você sele o cavalo e vá na minha frente procurar Euriques...”
+EURICÃO — Eurico!
+CAROBA — “Vá procurar Euríquio...”
+EURICÃO — Chame Euricão mesmo.
+CAROBA — “Vá procurar Euricão Engole-Cobra...”
+EURICÃO — Engole-Cobra é a mãe! Não lhe dei licença de me chamar de Engole-Cobra, não! Só de Euricão!
+CAROBA — “Vá na minha frente procurar Euricão para entregar essa carta a ele.”
+EURICÃO — Onde está a carta? Dê cá! Que quererá Eudoro Vicente comigo?
+PINHÃO — Eu acho que é dinheiro emprestado.
+EURICÃO — (Devolvendo a carta.) Hein?
+PINHÃO — Toda vez que ele me manda assim na frente, a cavalo, é para isso.
+EURICÃO — E que ideia foi essa de que eu tenho dinheiro? Você andou espalhando isso! Foi você, Caroba miserável, você que não tem compaixão de um pobre como eu! Foi você, só pode ter sido você!
+CAROBA — Eu? Eu não!
+EURICÃO — Ai, meu Deus, com essa carestia! Ai a crise, ai a carestia! Tudo que se compra é pela hora da morte!
+CAROBA — E o que é que o senhor compra? Me diga mesmo, pelo amor de Deus! Só falta matar a gente de fome!
+SUASSUNA, Ariano. O santo e a porca. 26ª ed. Rio de Janeiro: José Olympio, 2012.
+A partir do trecho lido, é possível afirmar que uma das principais características da personagem Euricão é a</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>avareza.</t>
+        </is>
+      </c>
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>soberba.</t>
+        </is>
+      </c>
+      <c r="D887" t="inlineStr">
+        <is>
+          <t>preguiça.</t>
+        </is>
+      </c>
+      <c r="E887" t="inlineStr">
+        <is>
+          <t>esperteza.</t>
+        </is>
+      </c>
+      <c r="F887" t="inlineStr">
+        <is>
+          <t>honestidade.</t>
+        </is>
+      </c>
+      <c r="G887" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H887" t="inlineStr">
+        <is>
+          <t>A partir do trecho, é possível entrever que a avareza é uma das principais características da personagem Euricão, uma vez que ele se desespera com a simples possibilidade de que lhe peçam dinheiro emprestado.</t>
+        </is>
+      </c>
+      <c r="I887" t="inlineStr">
+        <is>
+          <t>PH08</t>
+        </is>
+      </c>
+      <c r="J887" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K887" t="inlineStr"/>
+      <c r="L887" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>O dramaturgo paraibano radicado em Pernambuco Ariano Suassuna é um dos maiores expoentes do teatro cômico brasileiro. Suas peças foram traduzidas a várias línguas e sua obra mais conhecida, Auto da Compadecida, já ganhou três adaptações ao cinema e uma à TV. A seguir, você lerá um trecho da comédia O santo e a porca.
+O pano abre na casa de EURICO ARÁBE, mais conhecido como EURICÃO ENGOLE-COBRA.
+CAROBA — E foi então que o patrão dele disse: “Pinhão, você sele o cavalo e vá na minha frente procurar Euricão...”
+EURICÃO — Euricão, não. Meu nome é Eurico.
+CAROBA — Sim, é isso mesmo. Seu Eudoro Vicente disse: “Pinhão, você sele o cavalo e vá na minha frente procurar Euriques...”
+EURICÃO — Eurico!
+CAROBA — “Vá procurar Euríquio...”
+EURICÃO — Chame Euricão mesmo.
+CAROBA — “Vá procurar Euricão Engole-Cobra...”
+EURICÃO — Engole-Cobra é a mãe! Não lhe dei licença de me chamar de Engole-Cobra, não! Só de Euricão!
+CAROBA — “Vá na minha frente procurar Euricão para entregar essa carta a ele.”
+EURICÃO — Onde está a carta? Dê cá! Que quererá Eudoro Vicente comigo?
+PINHÃO — Eu acho que é dinheiro emprestado.
+EURICÃO — (Devolvendo a carta.) Hein?
+PINHÃO — Toda vez que ele me manda assim na frente, a cavalo, é para isso.
+EURICÃO — E que ideia foi essa de que eu tenho dinheiro? Você andou espalhando isso! Foi você, Caroba miserável, você que não tem compaixão de um pobre como eu! Foi você, só pode ter sido você!
+CAROBA — Eu? Eu não!
+EURICÃO — Ai, meu Deus, com essa carestia! Ai a crise, ai a carestia! Tudo que se compra é pela hora da morte!
+CAROBA — E o que é que o senhor compra? Me diga mesmo, pelo amor de Deus! Só falta matar a gente de fome!
+SUASSUNA, Ariano. O santo e a porca. 26ª ed. Rio de Janeiro: José Olympio, 2012.
+No trecho, as aspas são usadas para</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>indicar ironia.</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>destacar expressões coloquiais.</t>
+        </is>
+      </c>
+      <c r="D888" t="inlineStr">
+        <is>
+          <t>assinalar títulos de obras literárias.</t>
+        </is>
+      </c>
+      <c r="E888" t="inlineStr">
+        <is>
+          <t>reproduzir falas de personagens ausentes da cena.</t>
+        </is>
+      </c>
+      <c r="F888" t="inlineStr">
+        <is>
+          <t>introduzir falas das personagens presentes na cena.</t>
+        </is>
+      </c>
+      <c r="G888" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H888" t="inlineStr">
+        <is>
+          <t>No trecho, as aspas são empregadas para reproduzir falas de uma personagem ausente da cena, Eudoro Vicente. No fragmento em questão, Caroba narra a Euricão o que supostamente Eudoro disse a Pinhão.</t>
+        </is>
+      </c>
+      <c r="I888" t="inlineStr">
+        <is>
+          <t>PH08</t>
+        </is>
+      </c>
+      <c r="J888" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K888" t="inlineStr"/>
+      <c r="L888" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>Uma vez, um amigo me mandou um recorte de jornal com o resultado de uma estatística dessas que certas organizações costumam fazer com inquéritos, junto ao público, na saída dos espetáculos. O resultado foi, para mim, algo surpreendente e terrificante. Eu nunca vira nenhuma delas; aceitaria de bom grado que as opiniões fossem unânimes, contra ou a favor. Mas nada disso acontecia. A peça considerada melhor pela estatística apresentava o seguinte resultado: 58 pessoas tinham dito que ela era ótima, 34 que era boa, três que era simplesmente regular e cinco que era decididamente ruim. Da peça considerada estatisticamente pior, o resultado era o seguinte: 18 pessoas tinham-na considerado má, 31 regular, 33 boa e 18 ótima.
+Meu Deus, que misterioso critério de julgamento levou aquelas cinco pessoas a considerarem mau um espetáculo que outras 58 diziam ser ótimo e outras 34 diziam ser bom? E que outra imprevisível escala de apreciação levou, no segundo caso, aquelas 18 pessoas a acharem ótima uma peça que outras 18 achavam decididamente má?
+É para nos desanimar, é mesmo para tirar conclusões pouco democráticas, no domínio da arte. Mas assim vai o mundo, e, ao que parece, pior do que o escuro em que nos debatemos é a mania de ser dono da luz. Assim, confessando que talvez esteja ainda mais no escuro do que os outros sobre o que faço, tento aqui a ordenação — ou uma das ordenações possíveis — para o mundo tumultuoso que inventei, não sei bem por que nem para quê.
+SUASSUNA, Ariano. O santo e a porca. 26ª ed. Rio de Janeiro: José Olympio, 2012.
+Releia o trecho:
+Assim, confessando que talvez esteja ainda mais no escuro do que os outros sobre o que faço, tento aqui a ordenação — ou uma das ordenações possíveis — para o mundo tumultuoso que inventei, não sei bem por que nem para quê.
+No fragmento acima, os travessões foram usados para</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>destacar termos regionais.</t>
+        </is>
+      </c>
+      <c r="C889" t="inlineStr">
+        <is>
+          <t>explicar termos anteriores a eles.</t>
+        </is>
+      </c>
+      <c r="D889" t="inlineStr">
+        <is>
+          <t>destacar uma expressão coloquial.</t>
+        </is>
+      </c>
+      <c r="E889" t="inlineStr">
+        <is>
+          <t>introduzir fala de um personagem.</t>
+        </is>
+      </c>
+      <c r="F889" t="inlineStr">
+        <is>
+          <t>introduzir informações complementares.</t>
+        </is>
+      </c>
+      <c r="G889" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H889" t="inlineStr">
+        <is>
+          <t>No trecho em questão, os travessões são utilizados para introduzir uma informação complementar. O autor, após dizer que tentará explicar, em seu prefácio, o universo em que se passa O santo e a porca, afirma que é possível que sua explicação seja apenas uma das possíveis, complementando o que acabara de dizer.</t>
+        </is>
+      </c>
+      <c r="I889" t="inlineStr">
+        <is>
+          <t>PH08</t>
+        </is>
+      </c>
+      <c r="J889" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K889" t="inlineStr"/>
+      <c r="L889" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>Uma vez, um amigo me mandou um recorte de jornal com o resultado de uma estatística dessas que certas organizações costumam fazer com inquéritos, junto ao público, na saída dos espetáculos. O resultado foi, para mim, algo surpreendente e terrificante. Eu nunca vira nenhuma delas; aceitaria de bom grado que as opiniões fossem unânimes, contra ou a favor. Mas nada disso acontecia. A peça considerada melhor pela estatística apresentava o seguinte resultado: 58 pessoas tinham dito que ela era ótima, 34 que era boa, três que era simplesmente regular e cinco que era decididamente ruim. Da peça considerada estatisticamente pior, o resultado era o seguinte: 18 pessoas tinham-na considerado má, 31 regular, 33 boa e 18 ótima.
+Meu Deus, que misterioso critério de julgamento levou aquelas cinco pessoas a considerarem mau um espetáculo que outras 58 diziam ser ótimo e outras 34 diziam ser bom? E que outra imprevisível escala de apreciação levou, no segundo caso, aquelas 18 pessoas a acharem ótima uma peça que outras 18 achavam decididamente má?
+É para nos desanimar, é mesmo para tirar conclusões pouco democráticas, no domínio da arte. Mas assim vai o mundo, e, ao que parece, pior do que o escuro em que nos debatemos é a mania de ser dono da luz. Assim, confessando que talvez esteja ainda mais no escuro do que os outros sobre o que faço, tento aqui a ordenação — ou uma das ordenações possíveis — para o mundo tumultuoso que inventei, não sei bem por que nem para quê.
+SUASSUNA, Ariano. O santo e a porca. 26ª ed. Rio de Janeiro: José Olympio, 2012.
+Sobe a oração “um amigo me mandou um recorte de jornal”, pode-se afirmar que</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>“mandar” atua como verbo intransitivo.</t>
+        </is>
+      </c>
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>“mandar” atua como verbo transitivo direto.</t>
+        </is>
+      </c>
+      <c r="D890" t="inlineStr">
+        <is>
+          <t>“mandar” atua como verbo transitivo indireto.</t>
+        </is>
+      </c>
+      <c r="E890" t="inlineStr">
+        <is>
+          <t>“mandar” atua como verbo transitivo direto e indireto.</t>
+        </is>
+      </c>
+      <c r="F890" t="inlineStr">
+        <is>
+          <t>“um recorte de jornal” atua como adjunto adverbial de modo.</t>
+        </is>
+      </c>
+      <c r="G890" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H890" t="inlineStr">
+        <is>
+          <t>No trecho em questão, o verbo “mandar” atua como transitivo direto e indireto, sendo “um recorte de jornal” o objeto direto da oração e o autor, a quem se refere o pronome oblíquo “me”, objeto indireto.</t>
+        </is>
+      </c>
+      <c r="I890" t="inlineStr">
+        <is>
+          <t>PH08</t>
+        </is>
+      </c>
+      <c r="J890" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K890" t="inlineStr"/>
+      <c r="L890" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>Leia, a seguir, um trecho da introdução escrita por Ariano Suassuna para a peça O santo e a porca.
+Uma vez, um amigo me mandou um recorte de jornal com o resultado de uma estatística dessas que certas organizações costumam fazer com inquéritos, junto ao público, na saída dos espetáculos. O resultado foi, para mim, algo surpreendente e terrificante. Eu nunca vira nenhuma delas; aceitaria de bom grado que as opiniões fossem unânimes, contra ou a favor. Mas nada disso acontecia. A peça considerada melhor pela estatística apresentava o seguinte resultado: 58 pessoas tinham dito que ela era ótima, 34 que era boa, três que era simplesmente regular e cinco que era decididamente ruim. Da peça considerada estatisticamente pior, o resultado era o seguinte: 18 pessoas tinham-na considerado má, 31 regular, 33 boa e 18 ótima.
+Meu Deus, que misterioso critério de julgamento levou aquelas cinco pessoas a considerarem mau um espetáculo que outras 58 diziam ser ótimo e outras 34 diziam ser bom? E que outra imprevisível escala de apreciação levou, no segundo caso, aquelas 18 pessoas a acharem ótima uma peça que outras 18 achavam decididamente má?
+É para nos desanimar, é mesmo para tirar conclusões pouco democráticas, no domínio da arte. Mas assim vai o mundo, e, ao que parece, pior do que o escuro em que nos debatemos é a mania de ser dono da luz. Assim, confessando que talvez esteja ainda mais no escuro do que os outros sobre o que faço, tento aqui a ordenação — ou uma das ordenações possíveis — para o mundo tumultuoso que inventei, não sei bem por que nem para quê.
+SUASSUNA, Ariano. O santo e a porca. 26ª ed. Rio de Janeiro: José Olympio, 2012.
+Para o escritor, a percepção que tem o público de um espetáculo é sempre</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>objetiva, de modo que são claras as razões pelas quais uma peça obtém ou não êxito.</t>
+        </is>
+      </c>
+      <c r="C891" t="inlineStr">
+        <is>
+          <t>uniforme, pois todos espectadores costumam apresentar uma opinião parecida sobre a peça.</t>
+        </is>
+      </c>
+      <c r="D891" t="inlineStr">
+        <is>
+          <t>rasa, uma vez que a maior partes dos espectadores não tem capacidade de julgar uma peça.</t>
+        </is>
+      </c>
+      <c r="E891" t="inlineStr">
+        <is>
+          <t>inapreensível, já que não há como mensurar o impacto que uma peça exerce sobre determinados espectadores.</t>
+        </is>
+      </c>
+      <c r="F891" t="inlineStr">
+        <is>
+          <t>subjetiva, sendo impossível compreender os motivos que levam os espectadores a apreciá-lo ou não.</t>
+        </is>
+      </c>
+      <c r="G891" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H891" t="inlineStr">
+        <is>
+          <t>De acordo com Ariano Sussuna, a percepção que um público tem sobre uma peça é subjetiva, podendo variar enormemente de acordo com o perfil dos espectadores.</t>
+        </is>
+      </c>
+      <c r="I891" t="inlineStr">
+        <is>
+          <t>PH08</t>
+        </is>
+      </c>
+      <c r="J891" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K891" t="inlineStr"/>
+      <c r="L891" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>Em uma fazenda, o agricultor precisa dividir uma área de plantio em partes iguais para diferentes tipos de culturas. Ele possui uma área total representada pela fração algébrica:
+Para facilitar o planejamento, ele precisa simplificar essa fração.
+Qual é a forma simplificada da fração algébrica?</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>[img:8a_ph08_mat_01_a.png]</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>[img:8a_ph08_mat_01_b.png]</t>
+        </is>
+      </c>
+      <c r="D892" t="inlineStr">
+        <is>
+          <t>[img:8a_ph08_mat_01_c.png]</t>
+        </is>
+      </c>
+      <c r="E892" t="inlineStr">
+        <is>
+          <t>[img:8a_ph08_mat_01_d.png]</t>
+        </is>
+      </c>
+      <c r="F892" t="inlineStr">
+        <is>
+          <t>[img:8a_ph08_mat_01_e.png]</t>
+        </is>
+      </c>
+      <c r="G892" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H892" t="inlineStr">
+        <is>
+          <t>Para simplificar a fração algébrica, deve-se dividir o numerador e o denominador pelo maior fator comum.
+Numerador: 
+Denominador:  
+Dividindo ambos pelo fator comum 3x, tem-se que:</t>
+        </is>
+      </c>
+      <c r="I892" t="inlineStr">
+        <is>
+          <t>PH08</t>
+        </is>
+      </c>
+      <c r="J892" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K892" t="inlineStr">
+        <is>
+          <t>8a_ph08_mat_01.png</t>
+        </is>
+      </c>
+      <c r="L892" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>Um engenheiro está projetando um sistema de irrigação que precisa funcionar em ciclos regulares. Ele tem dois polinômios que representam os tempos de funcionamento de duas bombas de água:
+Para sincronizar as bombas, ele precisa encontrar uma expressão que represente o menor ciclo comum de funcionamento das duas bombas.
+Qual expressão a seguir representa corretamente esse ciclo?</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>[img:8a_ph08_mat_02_a.png]</t>
+        </is>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>[img:8a_ph08_mat_02_b.png]</t>
+        </is>
+      </c>
+      <c r="D893" t="inlineStr">
+        <is>
+          <t>[img:8a_ph08_mat_02_c.png]</t>
+        </is>
+      </c>
+      <c r="E893" t="inlineStr">
+        <is>
+          <t>[img:8a_ph08_mat_02_d.png]</t>
+        </is>
+      </c>
+      <c r="F893" t="inlineStr">
+        <is>
+          <t>[img:8a_ph08_mat_02_e.png]</t>
+        </is>
+      </c>
+      <c r="G893" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H893" t="inlineStr">
+        <is>
+          <t>Para encontrar a expressão que representa o menor ciclo comum, primeiro fatora-se os polinômios:
+P(x) = x² - 4 = (x - 2)(x + 2)
+Q(x) = x² - 1 = (x - 1)(x + 1)
+O menor ciclo comum é o produto dos fatores distintos:
+MMC = (x - 2)(x + 2)(x - 1)(x + 1) =</t>
+        </is>
+      </c>
+      <c r="I893" t="inlineStr">
+        <is>
+          <t>PH08</t>
+        </is>
+      </c>
+      <c r="J893" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K893" t="inlineStr">
+        <is>
+          <t>8a_ph08_mat_02.png</t>
+        </is>
+      </c>
+      <c r="L893" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>Um químico está preparando uma solução e precisa misturar dois componentes em proporções representadas por frações algébricas. Ele tem a seguinte fração:
+Ele precisa encontrar uma fração equivalente simplificada para facilitar os cálculos.
+Qual é a fração equivalente simplificada?</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>[img:8a_ph08_mat_03_a.png]</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>[img:8a_ph08_mat_03_b.png]</t>
+        </is>
+      </c>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>[img:8a_ph08_mat_03_c.png]</t>
+        </is>
+      </c>
+      <c r="E894" t="inlineStr">
+        <is>
+          <t>[img:8a_ph08_mat_03_d.png]</t>
+        </is>
+      </c>
+      <c r="F894" t="inlineStr">
+        <is>
+          <t>[img:8a_ph08_mat_03_e.png]</t>
+        </is>
+      </c>
+      <c r="G894" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H894" t="inlineStr">
+        <is>
+          <t>Para simplificar a fração algébrica, basta fatorar o numerador e o denominador:
+Numerador: x² - 1 = (x - 1)(x + 1)
+Denominador: x² + 2x + 1 = (x + 1)²
+Simplificando, tem-se:</t>
+        </is>
+      </c>
+      <c r="I894" t="inlineStr">
+        <is>
+          <t>PH08</t>
+        </is>
+      </c>
+      <c r="J894" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K894" t="inlineStr">
+        <is>
+          <t>8a_ph08_mat_03.png</t>
+        </is>
+      </c>
+      <c r="L894" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>Um economista está analisando duas funções de custo representadas por frações algébricas. Ele precisa somar as funções para obter o custo total. As funções são:
+Qual é o custo total?</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>[img:8a_ph08_mat_04_a.png]</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>[img:8a_ph08_mat_04_b.png]</t>
+        </is>
+      </c>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>[img:8a_ph08_mat_04_c.png]</t>
+        </is>
+      </c>
+      <c r="E895" t="inlineStr">
+        <is>
+          <t>[img:8a_ph08_mat_04_d.png]</t>
+        </is>
+      </c>
+      <c r="F895" t="inlineStr">
+        <is>
+          <t>[img:8a_ph08_mat_04_e.png]</t>
+        </is>
+      </c>
+      <c r="G895" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H895" t="inlineStr">
+        <is>
+          <t>Para somar as frações algébricas, deve-se encontrar o denominador comum:
+Denominador comum: x² - 1 = (x - 1)(x + 1)
+Reescrevendo as frações com o denominador comum:
+Somando os numeradores:</t>
+        </is>
+      </c>
+      <c r="I895" t="inlineStr">
+        <is>
+          <t>PH08</t>
+        </is>
+      </c>
+      <c r="J895" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K895" t="inlineStr">
+        <is>
+          <t>8a_ph08_mat_04.png</t>
+        </is>
+      </c>
+      <c r="L895" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>Um biólogo está estudando a taxa de crescimento de uma população de bactérias, que pode ser representada por frações algébricas. Ele precisa calcular a multiplicação e a divisão das seguintes frações para determinar a taxa de crescimento:
+Qual é o resultado dessa multiplicação?</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>[img:8a_ph08_mat_05_a.png]</t>
+        </is>
+      </c>
+      <c r="C896" t="inlineStr">
+        <is>
+          <t>[img:8a_ph08_mat_05_b.png]</t>
+        </is>
+      </c>
+      <c r="D896" t="inlineStr">
+        <is>
+          <t>[img:8a_ph08_mat_05_c.png]</t>
+        </is>
+      </c>
+      <c r="E896" t="inlineStr">
+        <is>
+          <t>[img:8a_ph08_mat_05_d.png]</t>
+        </is>
+      </c>
+      <c r="F896" t="inlineStr">
+        <is>
+          <t>[img:8a_ph08_mat_05_e.png]</t>
+        </is>
+      </c>
+      <c r="G896" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H896" t="inlineStr">
+        <is>
+          <t>Para multiplicar as frações algébricas, devemos multiplicar os numeradores e os denominadores:
+Numerador: x² - 4 = (x - 2)(x + 2)
+Denominador: x + 2
+Multiplicando as frações:</t>
+        </is>
+      </c>
+      <c r="I896" t="inlineStr">
+        <is>
+          <t>PH08</t>
+        </is>
+      </c>
+      <c r="J896" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K896" t="inlineStr">
+        <is>
+          <t>8a_ph08_mat_05.png</t>
+        </is>
+      </c>
+      <c r="L896" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>Um motorista faz o trajeto de sua casa até seu trabalho com seu carro. Esse trajeto tem 50 quilômetros e teve uma certa velocidade média.
+Certo dia, por haver um engarrafamento, ele fez o mesmo percurso, gastando 1 hora a mais e reduzindo sua velocidade média em 15 km/h.
+Se para calcular a velocidade média do percurso divide-se o tamanho do percurso pelo tempo gasto, qual a expressão que representa a situação descrita considerando que o tempo gasto sem engarrafamento foi t?</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>[img:8a_ph08_mat_06_a.png]</t>
+        </is>
+      </c>
+      <c r="C897" t="inlineStr">
+        <is>
+          <t>[img:8a_ph08_mat_06_b.png]</t>
+        </is>
+      </c>
+      <c r="D897" t="inlineStr">
+        <is>
+          <t>[img:8a_ph08_mat_06_c.png]</t>
+        </is>
+      </c>
+      <c r="E897" t="inlineStr">
+        <is>
+          <t>[img:8a_ph08_mat_06_d.png]</t>
+        </is>
+      </c>
+      <c r="F897" t="inlineStr">
+        <is>
+          <t>[img:8a_ph08_mat_06_e.png]</t>
+        </is>
+      </c>
+      <c r="G897" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H897" t="inlineStr">
+        <is>
+          <t>Velocidade média sem engarrafamento: ;
+Velocidade média com engarrafamento: ;
+Comparando as duas velocidades: .</t>
+        </is>
+      </c>
+      <c r="I897" t="inlineStr">
+        <is>
+          <t>PH08</t>
+        </is>
+      </c>
+      <c r="J897" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K897" t="inlineStr"/>
+      <c r="L897" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>A figura abaixo representa um cubo de aresta α.
+A expressão que representa a soma de todas as arestas desse cubo, com  é:</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>[img:8a_ph08_mat_07_a.png]</t>
+        </is>
+      </c>
+      <c r="C898" t="inlineStr">
+        <is>
+          <t>[img:8a_ph08_mat_07_b.png]</t>
+        </is>
+      </c>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>[img:8a_ph08_mat_07_c.png]</t>
+        </is>
+      </c>
+      <c r="E898" t="inlineStr">
+        <is>
+          <t>[img:8a_ph08_mat_07_d.png]</t>
+        </is>
+      </c>
+      <c r="F898" t="inlineStr">
+        <is>
+          <t>[img:8a_ph08_mat_07_e.png]</t>
+        </is>
+      </c>
+      <c r="G898" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H898" t="inlineStr">
+        <is>
+          <t>Como o cubo tem 12 arestas, então temos:</t>
+        </is>
+      </c>
+      <c r="I898" t="inlineStr">
+        <is>
+          <t>PH08</t>
+        </is>
+      </c>
+      <c r="J898" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K898" t="inlineStr">
+        <is>
+          <t>8a_ph08_mat_07.png</t>
+        </is>
+      </c>
+      <c r="L898" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>A conta de um restaurante no valor de R$ 200,00 seria dividida por x pessoas. Três pessoas saíram sem pagar e a conta teve que ser redividida igualmente entre os restantes. Se cada um dos restantes pagou R$ 10,00 a mais do que pagaria inicialmente, qual expressão representa a situação descrita?</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>[img:8a_ph08_mat_08_a.png]</t>
+        </is>
+      </c>
+      <c r="C899" t="inlineStr">
+        <is>
+          <t>[img:8a_ph08_mat_08_b.png]</t>
+        </is>
+      </c>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>[img:8a_ph08_mat_08_c.png]</t>
+        </is>
+      </c>
+      <c r="E899" t="inlineStr">
+        <is>
+          <t>[img:8a_ph08_mat_08_d.png]</t>
+        </is>
+      </c>
+      <c r="F899" t="inlineStr">
+        <is>
+          <t>[img:8a_ph08_mat_08_e.png]</t>
+        </is>
+      </c>
+      <c r="G899" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H899" t="inlineStr">
+        <is>
+          <t>Inicialmente, cada um pagaria  reais.
+Após a saída de 3 pessoas, o novo valor a ser pago será de .
+Como foi dito que o novo valor é 10 reais a mais que o anterior, então temos: .</t>
+        </is>
+      </c>
+      <c r="I899" t="inlineStr">
+        <is>
+          <t>PH08</t>
+        </is>
+      </c>
+      <c r="J899" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K899" t="inlineStr"/>
+      <c r="L899" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>A figura abaixo representa um aquário cujas dimensões estão representadas algebricamente.
+Considere .
+Qual expressão algébrica representa o volume de água contida nesse aquário?</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>[img:8a_ph08_mat_09_a.png]</t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>[img:8a_ph08_mat_09_b.png]</t>
+        </is>
+      </c>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>[img:8a_ph08_mat_09_c.png]</t>
+        </is>
+      </c>
+      <c r="E900" t="inlineStr">
+        <is>
+          <t>[img:8a_ph08_mat_09_d.png]</t>
+        </is>
+      </c>
+      <c r="F900" t="inlineStr">
+        <is>
+          <t>[img:8a_ph08_mat_09_e.png]</t>
+        </is>
+      </c>
+      <c r="G900" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H900" t="inlineStr">
+        <is>
+          <t>Primeiro devemos descontar a parte acima do nível da água:
+Assim, temos que o volume de água contida é:</t>
+        </is>
+      </c>
+      <c r="I900" t="inlineStr">
+        <is>
+          <t>PH08</t>
+        </is>
+      </c>
+      <c r="J900" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K900" t="inlineStr">
+        <is>
+          <t>8a_ph08_mat_09.png</t>
+        </is>
+      </c>
+      <c r="L900" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>As figuras abaixo representam um retângulo e um quadrado com suas respectivas dimensões.
+Considere . Sendo R o perímetro do retângulo e Q o perímetro do quadrado, qual relação está correta?</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>[img:8a_ph08_mat_10_a.png]</t>
+        </is>
+      </c>
+      <c r="C901" t="inlineStr">
+        <is>
+          <t>[img:8a_ph08_mat_10_b.png]</t>
+        </is>
+      </c>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>[img:8a_ph08_mat_10_c.png]</t>
+        </is>
+      </c>
+      <c r="E901" t="inlineStr">
+        <is>
+          <t>[img:8a_ph08_mat_10_d.png]</t>
+        </is>
+      </c>
+      <c r="F901" t="inlineStr">
+        <is>
+          <t>[img:8a_ph08_mat_10_e.png]</t>
+        </is>
+      </c>
+      <c r="G901" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H901" t="inlineStr"/>
+      <c r="I901" t="inlineStr">
+        <is>
+          <t>PH08</t>
+        </is>
+      </c>
+      <c r="J901" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K901" t="inlineStr">
+        <is>
+          <t>8a_ph08_mat_10.png</t>
+        </is>
+      </c>
+      <c r="L901" t="inlineStr">
         <is>
           <t>8ano</t>
         </is>

--- a/questoes.xlsx
+++ b/questoes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L901"/>
+  <dimension ref="A1:L951"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48112,7 +48112,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K852" t="inlineStr"/>
       <c r="L852" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -48174,7 +48173,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K853" t="inlineStr"/>
       <c r="L853" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -48233,7 +48231,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K854" t="inlineStr"/>
       <c r="L854" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -48355,7 +48352,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K856" t="inlineStr"/>
       <c r="L856" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -48414,7 +48410,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K857" t="inlineStr"/>
       <c r="L857" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -48536,7 +48531,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K859" t="inlineStr"/>
       <c r="L859" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -48595,7 +48589,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K860" t="inlineStr"/>
       <c r="L860" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -48654,7 +48647,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K861" t="inlineStr"/>
       <c r="L861" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -48714,7 +48706,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K862" t="inlineStr"/>
       <c r="L862" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -48775,7 +48766,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K863" t="inlineStr"/>
       <c r="L863" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -48836,7 +48826,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K864" t="inlineStr"/>
       <c r="L864" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -48897,7 +48886,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K865" t="inlineStr"/>
       <c r="L865" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -48957,7 +48945,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K866" t="inlineStr"/>
       <c r="L866" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -49015,7 +49002,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K867" t="inlineStr"/>
       <c r="L867" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -49139,7 +49125,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K869" t="inlineStr"/>
       <c r="L869" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -49262,7 +49247,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K871" t="inlineStr"/>
       <c r="L871" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -49322,7 +49306,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K872" t="inlineStr"/>
       <c r="L872" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -49383,7 +49366,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K873" t="inlineStr"/>
       <c r="L873" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -49444,7 +49426,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K874" t="inlineStr"/>
       <c r="L874" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -49505,7 +49486,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K875" t="inlineStr"/>
       <c r="L875" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -49630,7 +49610,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K877" t="inlineStr"/>
       <c r="L877" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -49690,7 +49669,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K878" t="inlineStr"/>
       <c r="L878" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -49751,7 +49729,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K879" t="inlineStr"/>
       <c r="L879" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -49876,7 +49853,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K881" t="inlineStr"/>
       <c r="L881" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -49939,7 +49915,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K882" t="inlineStr"/>
       <c r="L882" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -49999,7 +49974,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K883" t="inlineStr"/>
       <c r="L883" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -50059,7 +50033,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K884" t="inlineStr"/>
       <c r="L884" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -50119,7 +50092,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K885" t="inlineStr"/>
       <c r="L885" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -50179,7 +50151,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K886" t="inlineStr"/>
       <c r="L886" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -50257,7 +50228,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K887" t="inlineStr"/>
       <c r="L887" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -50335,7 +50305,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K888" t="inlineStr"/>
       <c r="L888" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -50399,7 +50368,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K889" t="inlineStr"/>
       <c r="L889" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -50461,7 +50429,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K890" t="inlineStr"/>
       <c r="L890" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -50524,7 +50491,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K891" t="inlineStr"/>
       <c r="L891" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -50920,7 +50886,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K897" t="inlineStr"/>
       <c r="L897" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -51043,7 +51008,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K899" t="inlineStr"/>
       <c r="L899" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -51152,7 +51116,6 @@
           <t>C</t>
         </is>
       </c>
-      <c r="H901" t="inlineStr"/>
       <c r="I901" t="inlineStr">
         <is>
           <t>PH08</t>
@@ -51169,6 +51132,3061 @@
         </is>
       </c>
       <c r="L901" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>No filme brasileiro "Conversa com um Liquidificador", a trama gira em torno de um liquidificador que ganha vida e começa a conversar com sua dona. A voz do liquidificador é interpretada pelo ator Selton Mello, trazendo um toque especial e humorístico à história. Embora a história seja fictícia, um liquidificador comum é um aparelho que utiliza um motor elétrico para girar lâminas afiadas, triturando e misturando alimentos.
+Além da transformação de energia elétrica em energia cinética de um liquidificador comum, no filme também há a transformação em</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>energia térmica.</t>
+        </is>
+      </c>
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>energia gravitacional.</t>
+        </is>
+      </c>
+      <c r="D902" t="inlineStr">
+        <is>
+          <t>energia sonora.</t>
+        </is>
+      </c>
+      <c r="E902" t="inlineStr">
+        <is>
+          <t>energia luminosa.</t>
+        </is>
+      </c>
+      <c r="F902" t="inlineStr">
+        <is>
+          <t>energia magnética.</t>
+        </is>
+      </c>
+      <c r="G902" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H902" t="inlineStr">
+        <is>
+          <t>Quando o liquidificador está em funcionamento, ele emite som devido ao movimento das lâminas e ao motor. Portanto, há uma transformação de energia elétrica em energia sonora. No contexto do filme, essa transformação é ainda mais destacada, pois o liquidificador ganha a capacidade de falar, com a voz interpretada por Selton Mello. Isso enfatiza a presença de energia sonora de uma maneira fictícia e humorística.</t>
+        </is>
+      </c>
+      <c r="I902" t="inlineStr">
+        <is>
+          <t>PH09</t>
+        </is>
+      </c>
+      <c r="J902" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K902" t="inlineStr"/>
+      <c r="L902" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>Uma geladeira é um eletrodoméstico essencial em muitas residências. Ela utiliza um compressor que transforma a energia elétrica em trabalho mecânico, o que permite a circulação do fluido refrigerante e a manutenção da temperatura interna baixa.
+Qual tipo de transformação de energia ocorre no compressor de uma geladeira?</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>Energia elétrica em energia térmica.</t>
+        </is>
+      </c>
+      <c r="C903" t="inlineStr">
+        <is>
+          <t>Energia elétrica em energia cinética.</t>
+        </is>
+      </c>
+      <c r="D903" t="inlineStr">
+        <is>
+          <t>Energia elétrica em energia sonora.</t>
+        </is>
+      </c>
+      <c r="E903" t="inlineStr">
+        <is>
+          <t>Energia elétrica em energia luminosa.</t>
+        </is>
+      </c>
+      <c r="F903" t="inlineStr">
+        <is>
+          <t>Energia elétrica em energia magnética.</t>
+        </is>
+      </c>
+      <c r="G903" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H903" t="inlineStr">
+        <is>
+          <t>A energia cinética está associada ao movimento de um corpo  ao realizar trabalho o compressor transforma a energia elétrica em trabalho mecânico (energia cinética), que é utilizado para comprimir o fluido refrigerante.</t>
+        </is>
+      </c>
+      <c r="I903" t="inlineStr">
+        <is>
+          <t>PH09</t>
+        </is>
+      </c>
+      <c r="J903" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K903" t="inlineStr"/>
+      <c r="L903" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>Uma lâmpada incandescente é um dispositivo que, ao ser conectado à rede elétrica, emite luz. Esse fenômeno ocorre devido ao aquecimento de um filamento de tungstênio que, ao atingir altas temperaturas, começa a brilhar.
+No dispositivo citado, ocorre a transformação de energia elétrica em</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>Energia térmica e energia cinética.</t>
+        </is>
+      </c>
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>Energia térmica e energia sonora.</t>
+        </is>
+      </c>
+      <c r="D904" t="inlineStr">
+        <is>
+          <t>Energia térmica e energia luminosa.</t>
+        </is>
+      </c>
+      <c r="E904" t="inlineStr">
+        <is>
+          <t>Energia térmica e energia magnética.</t>
+        </is>
+      </c>
+      <c r="F904" t="inlineStr">
+        <is>
+          <t>Energia cinética e energia luminosa.</t>
+        </is>
+      </c>
+      <c r="G904" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H904" t="inlineStr">
+        <is>
+          <t>A principal transformação de energia em uma lâmpada incandescente é de energia elétrica em energia térmica e energia luminosa. O filamento de tungstênio aquece e, ao atingir altas temperaturas, emite luz visível.</t>
+        </is>
+      </c>
+      <c r="I904" t="inlineStr">
+        <is>
+          <t>PH09</t>
+        </is>
+      </c>
+      <c r="J904" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K904" t="inlineStr"/>
+      <c r="L904" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>Um ventilador é um aparelho muito utilizado em residências, especialmente em dias quentes. Ele possui um motor elétrico que, ao ser ligado, começa a girar suas hélices, proporcionando uma sensação de frescor ao ambiente. Esse processo envolve a transformação de energia elétrica em outro tipo de energia.
+Qual tipo de transformação de energia ocorre no aparelho citado?</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>Energia elétrica em energia térmica.</t>
+        </is>
+      </c>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>Energia elétrica em energia luminosa.</t>
+        </is>
+      </c>
+      <c r="D905" t="inlineStr">
+        <is>
+          <t>Energia elétrica em energia gravitacional.</t>
+        </is>
+      </c>
+      <c r="E905" t="inlineStr">
+        <is>
+          <t>Energia elétrica em energia cinética.</t>
+        </is>
+      </c>
+      <c r="F905" t="inlineStr">
+        <is>
+          <t>Energia elétrica em energia magnética.</t>
+        </is>
+      </c>
+      <c r="G905" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H905" t="inlineStr">
+        <is>
+          <t>O ventilador converte energia elétrica em energia cinética, que é o movimento das hélices. Esse movimento é o que permite a circulação do ar no ambiente.</t>
+        </is>
+      </c>
+      <c r="I905" t="inlineStr">
+        <is>
+          <t>PH09</t>
+        </is>
+      </c>
+      <c r="J905" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K905" t="inlineStr"/>
+      <c r="L905" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>O efeito Joule é o fenômeno pelo qual a passagem de uma corrente elétrica através de um condutor gera calor. Esse efeito é utilizado em diversos aparelhos elétricos, como aquecedores e ferros de passar roupas.
+Qual tipo de transformação de energia ocorre no efeito citado?</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>Energia elétrica em energia térmica.</t>
+        </is>
+      </c>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>Energia elétrica em energia cinética.</t>
+        </is>
+      </c>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>Energia elétrica em energia sonora.</t>
+        </is>
+      </c>
+      <c r="E906" t="inlineStr">
+        <is>
+          <t>Energia elétrica em energia luminosa.</t>
+        </is>
+      </c>
+      <c r="F906" t="inlineStr">
+        <is>
+          <t>Energia elétrica em energia magnética.</t>
+        </is>
+      </c>
+      <c r="G906" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H906" t="inlineStr">
+        <is>
+          <t>O efeito Joule transforma a energia elétrica em energia térmica, gerando calor quando a corrente elétrica passa através de um condutor.</t>
+        </is>
+      </c>
+      <c r="I906" t="inlineStr">
+        <is>
+          <t>PH09</t>
+        </is>
+      </c>
+      <c r="J906" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K906" t="inlineStr"/>
+      <c r="L906" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>Somos cercados de diversos tipos de energias: energia térmica, energia sonora, energia luminosa, energia química e energia elétrica, entre outras.
+Uma definição que todos os tipos de energia tem em comum é o fato de que</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>não se pode destruir, apenas criar ou transformar de um tipo de energia para outro.</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>se pode destruir, quando transformada em calor e dissipado para o ar.</t>
+        </is>
+      </c>
+      <c r="D907" t="inlineStr">
+        <is>
+          <t>não se pode criar, pois a energia só diminui com o tempo.</t>
+        </is>
+      </c>
+      <c r="E907" t="inlineStr">
+        <is>
+          <t>se pode criar, porém apenas utilizando energia mecânica.</t>
+        </is>
+      </c>
+      <c r="F907" t="inlineStr">
+        <is>
+          <t>não se pode criar, apenas transformar de um tipo de energia para o outro.</t>
+        </is>
+      </c>
+      <c r="G907" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H907" t="inlineStr">
+        <is>
+          <t>Existe uma conservação de energia, onde a energia não é criada nem destruída, apenas transformada de um tipo para o outro.</t>
+        </is>
+      </c>
+      <c r="I907" t="inlineStr">
+        <is>
+          <t>PH09</t>
+        </is>
+      </c>
+      <c r="J907" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K907" t="inlineStr"/>
+      <c r="L907" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>A televisão é um aparelho relativamente recente, que completará 100 anos de sua invenção em 2025. Cada dia ela avança mais e incorpora novas tecnologias.
+Sua função principal é transmitir imagens e sons e para isso ela precisa estar conectada em uma tomada para transformar</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>energia elétrica para energia sonora e luminosa.</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>energia elétrica em energia térmica e sonora.</t>
+        </is>
+      </c>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>energia elétrica em energia sonora e química.</t>
+        </is>
+      </c>
+      <c r="E908" t="inlineStr">
+        <is>
+          <t>energia química em energia luminosa e sonora.</t>
+        </is>
+      </c>
+      <c r="F908" t="inlineStr">
+        <is>
+          <t>energia química em energia luminosa e térmica.</t>
+        </is>
+      </c>
+      <c r="G908" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H908" t="inlineStr">
+        <is>
+          <t>A tomada fornece energia elétrica, que a televisão transformará em energia luminosa (imagem) e energia sonora (som).</t>
+        </is>
+      </c>
+      <c r="I908" t="inlineStr">
+        <is>
+          <t>PH09</t>
+        </is>
+      </c>
+      <c r="J908" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K908" t="inlineStr"/>
+      <c r="L908" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>Os motores elétricos estão presentes em aparelhos que produzem algum tipo de movimento, como por exemplo, ventilador ou máquina de lavar roupa.
+Nesses aparelhos, a energia elétrica é transformada em energia</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>potencial.</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>física.</t>
+        </is>
+      </c>
+      <c r="D909" t="inlineStr">
+        <is>
+          <t>química.</t>
+        </is>
+      </c>
+      <c r="E909" t="inlineStr">
+        <is>
+          <t>eletrônica.</t>
+        </is>
+      </c>
+      <c r="F909" t="inlineStr">
+        <is>
+          <t>mecânica.</t>
+        </is>
+      </c>
+      <c r="G909" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H909" t="inlineStr">
+        <is>
+          <t>A energia mecânica é aquela que gera movimento, logo em aparelhos com motores elétricos a energia elétrica é transformada em energia mecânica.</t>
+        </is>
+      </c>
+      <c r="I909" t="inlineStr">
+        <is>
+          <t>PH09</t>
+        </is>
+      </c>
+      <c r="J909" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K909" t="inlineStr"/>
+      <c r="L909" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>Chuveiros, torradeiras e fusíveis são exemplos de equipamentos resistivos.
+Sua principal característica é transformar energia</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>química em energia térmica.</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>térmica em energia mecânica.</t>
+        </is>
+      </c>
+      <c r="D910" t="inlineStr">
+        <is>
+          <t>térmica em energia elétrica.</t>
+        </is>
+      </c>
+      <c r="E910" t="inlineStr">
+        <is>
+          <t>elétrica em energia térmica.</t>
+        </is>
+      </c>
+      <c r="F910" t="inlineStr">
+        <is>
+          <t>elétrica em energia mecânica.</t>
+        </is>
+      </c>
+      <c r="G910" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H910" t="inlineStr">
+        <is>
+          <t>Equipamentos resistivos transformam energia elétrica em energia térmica.</t>
+        </is>
+      </c>
+      <c r="I910" t="inlineStr">
+        <is>
+          <t>PH09</t>
+        </is>
+      </c>
+      <c r="J910" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K910" t="inlineStr"/>
+      <c r="L910" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>Chuveiro elétrico é um tipo de equipamento resistivo, onde há transformação de energia.
+O fluxo que a água precisa percorrer para sair aquecida é:</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>entrar em contato com a tomada que fornece energia elétrica.</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>encher completamente o interior do chuveiro.</t>
+        </is>
+      </c>
+      <c r="D911" t="inlineStr">
+        <is>
+          <t>entrar em contato com a resistência que está aquecida.</t>
+        </is>
+      </c>
+      <c r="E911" t="inlineStr">
+        <is>
+          <t>passar pelo gerador que está com corrente.</t>
+        </is>
+      </c>
+      <c r="F911" t="inlineStr">
+        <is>
+          <t>entrar em contato com o motor elétrico que está movimentando.</t>
+        </is>
+      </c>
+      <c r="G911" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H911" t="inlineStr">
+        <is>
+          <t>A resistência é propositalmente acondicionada à estrutura do chuveiro, de modo a proporcionar o contato com a água – inicialmente em baixa temperatura –, definindo assim o sentido da troca de energia (calor) e deixando a água aquecida escoar do equipamento.</t>
+        </is>
+      </c>
+      <c r="I911" t="inlineStr">
+        <is>
+          <t>PH09</t>
+        </is>
+      </c>
+      <c r="J911" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K911" t="inlineStr"/>
+      <c r="L911" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>A expressão Consenso de Washington surgiu da denominação dada por John Williamson, economista e pesquisador do Institute of International Economics, sediado em Washington, para a convergência de pensamento sobre as políticas públicas dos anos 1980, a partir dos governos de Ronald Reagan e George Bush. Referia-se às ideias das principais autoridades da economia mundial: a alta burocracia das agências econômicas do governo dos Estados Unidos, o Federal Reserve Board, as agências financeiras internacionais, membros do Congresso norte-americano e consultores econômicos de maior poder simbólico internacional.
+Disponível em: https://sites.usp.br/portalatinoamericano/espanol-consenso-de-washington. Acesso em: 9 dez. 2024.
+O Consenso de Washington consistiu em um conjunto de diretrizes econômicas que incluía:</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>abertura financeira, eliminação de subsídios, controle da inflação e privatização das estatais.</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>aumento da intervenção governamental na economia, subsídios agrícolas e barreiras protecionistas.</t>
+        </is>
+      </c>
+      <c r="D912" t="inlineStr">
+        <is>
+          <t>nacionalização de setores estratégicos, controle rígido de preços e estímulo ao comércio interno.</t>
+        </is>
+      </c>
+      <c r="E912" t="inlineStr">
+        <is>
+          <t>controle da economia pelo Estado com bariamento protecionista e manutenção de subsídios para a produção local.</t>
+        </is>
+      </c>
+      <c r="F912" t="inlineStr">
+        <is>
+          <t>isolamento econômico, políticas de autossuficiência e restrição à entrada de capitais internacionais.</t>
+        </is>
+      </c>
+      <c r="G912" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H912" t="inlineStr">
+        <is>
+          <t>O Consenso de Washington envolvia diretrizes como abertura financeira, eliminação de subsídios, controle da inflação e privatização das empresas estatais, objetivando a liberalização econômica e redução do papel do Estado na economia.</t>
+        </is>
+      </c>
+      <c r="I912" t="inlineStr">
+        <is>
+          <t>PH09</t>
+        </is>
+      </c>
+      <c r="J912" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K912" t="inlineStr"/>
+      <c r="L912" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>O perigo de uma guerra atômica entre as maiores potências da época parece iminente e chegou a hora de falar abertamente ao mundo. "Qualquer míssil lançado de Cuba contra qualquer nação do Hemisfério Ocidental será considerado um ataque da União Soviética contra os Estados Unidos, exigindo uma resposta retaliatória total contra a União Soviética", advertiu Kennedy. Americanos, cubanos e soviéticos se prepararam para um confronto que por vários dias se acreditou inevitável. O terror tomou conta dos cidadãos. Os supermercados estavam lotados e as prateleiras, esvaziadas pela compra às pressas, tomada pelo pânico. Aqueles que podiam pagar construíram abrigos e os estocaram com os suprimentos que acreditavam serem necessários para sobreviver a um impacto atômico.
+Disponível em: https://www.bbc.com/portuguese/internacional-63309793. Acesso em: 9 dez. 2024.
+O evento descrito no texto é conhecido como:</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>A crise que colocou o mundo à beira de um conflito nuclear entre EUA e URSS.</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>A tentativa de invasão militar apoiada pelos EUA em um país do Caribe.</t>
+        </is>
+      </c>
+      <c r="D913" t="inlineStr">
+        <is>
+          <t>O conflito bélico prolongado entre EUA e forças vietcongues.</t>
+        </is>
+      </c>
+      <c r="E913" t="inlineStr">
+        <is>
+          <t>A guerra que ocorreu na península asiática entre o norte e o sul apoiados por potências rivais.</t>
+        </is>
+      </c>
+      <c r="F913" t="inlineStr">
+        <is>
+          <t>A disputa geopolítica envolvendo um importante canal de navegação no Oriente Médio.</t>
+        </is>
+      </c>
+      <c r="G913" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H913" t="inlineStr">
+        <is>
+          <t>A crise que colocou o mundo à beira de um conflito nuclear entre EUA e URSS é a Crise dos Mísseis, um momento tenso da Guerra Fria devido à instalação de mísseis soviéticos em Cuba.</t>
+        </is>
+      </c>
+      <c r="I913" t="inlineStr">
+        <is>
+          <t>PH09</t>
+        </is>
+      </c>
+      <c r="J913" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K913" t="inlineStr"/>
+      <c r="L913" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>Era novembro de 1978, quando o casal uruguaio de ativistas Lilián Celiberti e Universindo Rodríguez Díaz e seus dois filhos, Camilo, 8 anos, e Francesca, 3 anos, foram sequestrados em Porto Alegre. A família fora raptada em uma operação conjunta entre militares brasileiros e uruguaios que perseguiam os opositores das ditaduras para torturá-los e matá-los. Mas acabou fracassada após ser descoberta por dois jornalistas. O sequestro dos uruguaios, como o caso ficou conhecido, tornou-se, anos mais tarde, o exemplo mais emblemático de como ocorreu, na prática, a Operação Condor.
+Disponível em: https://brasil.elpais.com/brasil/2019/03/29/politica/1553895462_193096.html. Acesso em: 11 dez. 2024.
+O "sequestro dos uruguaios" ocorrido em Porto Alegre em novembro de 1978 tornou-se um exemplo emblemático da "Operação Condor". Esta operação foi caracterizada por uma coordenação entre os regimes ditatoriais da América do Sul com o objetivo de:</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>Promover reformas agrárias e redistribuir terras para a população camponesa.</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>Estabelecer acordos comerciais bilaterais entre os países do continente.</t>
+        </is>
+      </c>
+      <c r="D914" t="inlineStr">
+        <is>
+          <t>Coordenar atividades culturais e educacionais através dos ministérios de cultura.</t>
+        </is>
+      </c>
+      <c r="E914" t="inlineStr">
+        <is>
+          <t>Perseguir, torturar e eliminar opositores políticos dos regimes ditatoriais.</t>
+        </is>
+      </c>
+      <c r="F914" t="inlineStr">
+        <is>
+          <t>Fomentar a industrialização e desenvolvimento econômico conjunto dos países membros.</t>
+        </is>
+      </c>
+      <c r="G914" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H914" t="inlineStr">
+        <is>
+          <t>A Operação Condor foi uma operação de coordenação entre as ditaduras da América do Sul com o objetivo explícito de perseguir, torturar e eliminar opositores políticos. Este é o objetivo principal da operação e a razão pela qual ela ficou conhecida como um símbolo da repressão militar na região.</t>
+        </is>
+      </c>
+      <c r="I914" t="inlineStr">
+        <is>
+          <t>PH09</t>
+        </is>
+      </c>
+      <c r="J914" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K914" t="inlineStr"/>
+      <c r="L914" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>Observe a imagem. 
+Disponível em: https://blogger.googleusercontent.com/img/b/R29vZ2xl/AVvXsEhdG212cJtNYuyHJ4tlS3Nu6muv6ZA_IG6-GHA4XrCCiSluCS-jwkrZh8KE4a7fsmYMpVAjqvk70Pdu-D8BBV34W5JHQM8KLUDGIBn2aGI_Z29ZBJoRNDdmTLUX11hLRZs7tuljSXH7kvAf/s1600/Politica+boa+vizinhan%C3%A7a.jpg. Acesso em: 11 dez. 2024.
+A imagem apresentada é de um pôster do filme "Saludos Amigos" de Walt Disney, produzido em 1942. Este filme é um exemplo da política estadunidense da época, uma estratégia de política externa dos Estados Unidos durante a presidência de Franklin D. Roosevelt.
+Qual foi o principal objetivo dessa estratégia?</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>Promover a industrialização dos países da América Latina através de investimentos estrangeiros.</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>Estabelecer bases militares americanas em toda a América Latina para reforçar a segurança interna.</t>
+        </is>
+      </c>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>Fortalecer as relações culturais e econômicas entre os Estados Unidos e os países da América Latina.</t>
+        </is>
+      </c>
+      <c r="E915" t="inlineStr">
+        <is>
+          <t>Controlar politicamente e economicamente os governos da América Latina através de intervenções diretas e armadas.</t>
+        </is>
+      </c>
+      <c r="F915" t="inlineStr">
+        <is>
+          <t>Explorar os recursos naturais dos países da América Latina para abastecer o mercado americano sem se preocupar com os recursos internos.</t>
+        </is>
+      </c>
+      <c r="G915" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H915" t="inlineStr">
+        <is>
+          <t>A Política da Boa Vizinhança visava melhorar as relações através de intercâmbios culturais e econômicos, como forma de garantir o apoio dos países latino-americanos durante a Segunda Guerra Mundial. O filme "Saludos Amigos" é um exemplo desse esforço cultural de aproximação.</t>
+        </is>
+      </c>
+      <c r="I915" t="inlineStr">
+        <is>
+          <t>PH09</t>
+        </is>
+      </c>
+      <c r="J915" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K915" t="inlineStr">
+        <is>
+          <t>8a_ph09_geo_04.png</t>
+        </is>
+      </c>
+      <c r="L915" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>A noção de “República de Banana” está ligada ao neocolonialismo, uma forma de dominação que, ao invés de se basear no controle territorial direto, utiliza influências econômicas, políticas e culturais para manter a dependência.
+Disponível em: https://relacoesexteriores.com.br/glossario/republica-de-bananas/. Acesso em: 11 dez. 2024.
+Qual das alternativas a seguir melhor descreve em que consiste o termo "República das Bananas"?</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>Uma nação cujo principal produto de exportação é a banana, sendo economicamente estável e politicamente independente.</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>Um país onde o governo mantém controle total sobre todas as empresas estrangeiras operando no território nacional.</t>
+        </is>
+      </c>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>Uma nação instável, dependente de empresas estrangeiras e voltada para a exportação agrícola.</t>
+        </is>
+      </c>
+      <c r="E916" t="inlineStr">
+        <is>
+          <t>Um país desenvolvido com infraestrutura avançada e altos índices de desenvolvimento humano.</t>
+        </is>
+      </c>
+      <c r="F916" t="inlineStr">
+        <is>
+          <t>Uma nação sem nenhum envolvimento comercial internacional, com uma economia autossuficiente.</t>
+        </is>
+      </c>
+      <c r="G916" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H916" t="inlineStr">
+        <is>
+          <t>Esta descrição captura com precisão o conceito de "República das Bananas", destacando a instabilidade política e a dependência econômica de empresas estrangeiras, especialmente na exportação de produtos agrícolas.</t>
+        </is>
+      </c>
+      <c r="I916" t="inlineStr">
+        <is>
+          <t>PH09</t>
+        </is>
+      </c>
+      <c r="J916" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K916" t="inlineStr"/>
+      <c r="L916" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>Em decorrência da crise de 1929 e da 2.ª Guerra Mundial, o Brasil e a América Latina (AL) aproveitaram a circunstância de isolamento internacional gerada pelos distúrbios nos países ricos para se desenvolver. De algum modo vivemos hoje o inverso daquele período, reconhecido por nossa forte industrialização, apoiada na política de substituição de importações. Nos anos dourados, a independência nacional estava associada ao crescimento da indústria. A especialização na exportação de commodities, como o café, era vista como um dos principais elementos do subdesenvolvimento e da dependência externa. Até hoje há pouquíssimos exemplos de países primário-exportadores plenamente desenvolvidos, como a Austrália.
+Disponível em: https://economia.estadao.com.br/noticias/geral,substituicao-de-exportacoes-imp-,627720. Acesso em 16 abr. 2019.
+A política retratada no trecho se destacou no</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>Peru, Equador e Suriname.</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>Brasil, Argentina e México.</t>
+        </is>
+      </c>
+      <c r="D917" t="inlineStr">
+        <is>
+          <t>Chile, Venezuela e Bolívia.</t>
+        </is>
+      </c>
+      <c r="E917" t="inlineStr">
+        <is>
+          <t>Uruguai, Paraguai e Colômbia.</t>
+        </is>
+      </c>
+      <c r="F917" t="inlineStr">
+        <is>
+          <t>Nicarágua, Canadá e Cuba.</t>
+        </is>
+      </c>
+      <c r="G917" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H917" t="inlineStr">
+        <is>
+          <t>O processo de substituição das importações foi um elemento comum entre alguns países da América Latina (Brasil, México, Argentina, Chile, etc). Essas nações visavam diminuir a dependência do mercado externo, principalmente quanto a dependência de manufaturas.</t>
+        </is>
+      </c>
+      <c r="I917" t="inlineStr">
+        <is>
+          <t>PH09</t>
+        </is>
+      </c>
+      <c r="J917" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K917" t="inlineStr"/>
+      <c r="L917" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>A crise de 1929 e o envolvimento dos países industrializados nas guerras mundiais, contribuíram para aprofundar a industrialização de alguns países latino-americanos, esse processo pode ser resumido em:</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>O país deixa de comprar produtos estrangeiros e investe esse capital nas forças armadas.</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>Trata-se da produção interna de bens que antes eram importados de países industrializados e desenvolvidos.</t>
+        </is>
+      </c>
+      <c r="D918" t="inlineStr">
+        <is>
+          <t>A nação passa a produzir dentro de seus domínios os produtos que antes eram exportados.</t>
+        </is>
+      </c>
+      <c r="E918" t="inlineStr">
+        <is>
+          <t>O país começa a importar produtos que antes exportava para as potências ricas.</t>
+        </is>
+      </c>
+      <c r="F918" t="inlineStr">
+        <is>
+          <t>O país deixa de investir em setores sociais, e passa a investir no desenvolvimento industrial.</t>
+        </is>
+      </c>
+      <c r="G918" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H918" t="inlineStr">
+        <is>
+          <t>O modelo industrial adotado pelos países latinos ficou conhecido como substituição de importações, esse modelo consistia em produzir internamente o que antes era exportado. Esse modelo foi a alternativa encontrada para solucionar o “vácuo de produtos industriais”. A crise de 1929 e o envolvimento dos países industrializados nas guerras mundiais, contribuíram para aprofundar a industrialização de alguns países latino-americanos, com a redução da oferta de produtos industrializados no mercado mundial, a queda dos preços agrícolas e o caráter nacional-desenvolvimentista de alguns governos, o aprofundamento da industrialização surgiu como vetor de crescimento econômico.</t>
+        </is>
+      </c>
+      <c r="I918" t="inlineStr">
+        <is>
+          <t>PH09</t>
+        </is>
+      </c>
+      <c r="J918" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K918" t="inlineStr"/>
+      <c r="L918" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>Trata-se de uma industrialização que, como o nome sugere, foi historicamente atrasada em relação à original e ocorreu em muitos países subdesenvolvidos [...]. Foi mais comum no século XX, embora, em alguns casos, tenha se iniciado de forma tímida no fim do século XIX.
+Vesentini, José William. Geografia: o mundo em transição. São Paulo: Editora Ática, 2012. p.67.
+A forma de industrialização que  foi comum no Brasil e seu aspecto no pós guerra pode ser descrita como</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>do tipo clássica, caracterizada pelo predomínio das chamadas “indústrias de chaminés”, hoje obsoletas.</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>do tipo planificada, vista como a única forma de os países periféricos conseguirem se industrializar, sobre a forte proteção do Estado.</t>
+        </is>
+      </c>
+      <c r="D919" t="inlineStr">
+        <is>
+          <t>do tipo tardia, realizada, em geral, com a presença de capital estatal e privado.</t>
+        </is>
+      </c>
+      <c r="E919" t="inlineStr">
+        <is>
+          <t>do tipo planificada, realizada em países socialistas e keynesianistas, procurando articular o setor de bens de consumo.</t>
+        </is>
+      </c>
+      <c r="F919" t="inlineStr">
+        <is>
+          <t>do tipo tardia, realizada graças à emancipação econômica apenas recentemente conquistada pelos países subdesenvolvidos.</t>
+        </is>
+      </c>
+      <c r="G919" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H919" t="inlineStr">
+        <is>
+          <t>Em geral, a industrialização desses países marcou-se pela presença de empresas nacionais e privadas. A industrialização tardia tem dois momentos importantes: a substituição de importações, que alavancou as indústrias nacionais e a expansão de grupos estrangeiros no pós-guerra.</t>
+        </is>
+      </c>
+      <c r="I919" t="inlineStr">
+        <is>
+          <t>PH09</t>
+        </is>
+      </c>
+      <c r="J919" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K919" t="inlineStr"/>
+      <c r="L919" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>Filme relembra que há 17 anos (Abril dos anos 2000) a Bolívia viveu a Guerra da Água, uma consequência direta da privatização da água, inclusive a privatização da água de chuva. Essa foi uma exigência do FMI, Banco Mundial, para negociar a dívida externa da Bolívia. Infelizmente esta é uma estratégia que se intensifica e está hoje na ordem do dia de muitos governos, sob a "justificativa" das dívidas financeiras. E não se discute se estas dívidas são ou não legítimas.
+Disponível em:https://www.fenae.org.br/portal/fama-2018/noticias/ha-17-anos-bolivia-viveu-a-guerra-da-agua-consequencia-direta-da-privatizacao-desse-bem.htm. Acesso em: 16 abr. 2019.
+Considerando o desenvolvimento da conjuntura política latino-americana nas últimas décadas, a Guerra da Água pode ser entendida como</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>um movimento de contestação a políticas socialistas implantadas por Evo Morales.</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>exigência da troca das empresas concessionárias do abastecimento.</t>
+        </is>
+      </c>
+      <c r="D920" t="inlineStr">
+        <is>
+          <t>mobilização que exigia a adoção do keynesianismo como política econômica.</t>
+        </is>
+      </c>
+      <c r="E920" t="inlineStr">
+        <is>
+          <t>contestação ao modelo neoliberal estabelecido pelo Consenso de Washington.</t>
+        </is>
+      </c>
+      <c r="F920" t="inlineStr">
+        <is>
+          <t>mobilização executada pela classe média descontente com a ausência de políticas liberalizantes.</t>
+        </is>
+      </c>
+      <c r="G920" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H920" t="inlineStr">
+        <is>
+          <t>O Consenso de Washington defende o protagonismo do mercado frente a quase totalidade da sociedade, incluindo-se ai os serviços públicos essenciais. As políticas indicadas pelo FMI geraram revolta da população boliviana ao cobrar pelo acesso a água, tal revolta também pode ser entendida em razão da maior parte da população boliviana (60%) ser constituída por indígenas, que possuem relações mais diretas com os recursos naturais, sendo a lógica ultraliberal estranha para um povo com raízes indígenas.</t>
+        </is>
+      </c>
+      <c r="I920" t="inlineStr">
+        <is>
+          <t>PH09</t>
+        </is>
+      </c>
+      <c r="J920" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K920" t="inlineStr"/>
+      <c r="L920" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>A alternativa que indica os principais fatores externos que promoveram o desenvolvimento da indústria na América Latina é:</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>Crise do açúcar e a 1ª Guerra Mundial.</t>
+        </is>
+      </c>
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>1ª Guerra Mundial e a Crise de 1929.</t>
+        </is>
+      </c>
+      <c r="D921" t="inlineStr">
+        <is>
+          <t>Crise de 1929 e a Crise imobiliária.</t>
+        </is>
+      </c>
+      <c r="E921" t="inlineStr">
+        <is>
+          <t>2 ª Guerra Mundial e o Consenso de Washington.</t>
+        </is>
+      </c>
+      <c r="F921" t="inlineStr">
+        <is>
+          <t>Consenso de Washington e a Rodada de Doha.</t>
+        </is>
+      </c>
+      <c r="G921" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H921" t="inlineStr">
+        <is>
+          <t>Os países latino-americanos tinham dificuldade de competir com as indústrias europeia e estadunidense e importavam produtos industrializados de países hegemônicos, o que tornava a América Latina mais dependente economicamente. Somente a partir da década de 1930 a indústria passou a ser uma realidade mais evidente na América Latina. O contexto mundial marcado pela Primeira Guerra Mundial (1914-1918) e pela Crise de 1929 incentivou a industrialização latino-americana, que se desenvolveu com base na política de substituição de importações.</t>
+        </is>
+      </c>
+      <c r="I921" t="inlineStr">
+        <is>
+          <t>PH09</t>
+        </is>
+      </c>
+      <c r="J921" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K921" t="inlineStr"/>
+      <c r="L921" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>Considero o estado atual da América semelhante ao desmembrado império romano, em que cada parte formou um sistema político de acordo com seus interesses e situação ou seguindo a ambição particular de alguns chefes, famílias ou corporações;[...]
+[...] seremos capazes de manter em seu verdadeiro equilíbrio a difícil carga de uma república? Pode-se conceber que um povo recentemente liberto lance-se à esfera da liberdade sem que, como Ícaro, se lhe desfaçam as asas e caia no abismo? Tal prodígio é inconcebível, nunca visto. 
+BOLÍVAR, S. Política. Org: Manuel Belloto; Ana María Martínez. São Paulo, Editora Ática. 1983.
+Na Carta da Jamaica, Simón Bolívar destaca que, após a independência da América Espanhola, a maior dificuldade seria</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>construir uma América unificada e republicana.</t>
+        </is>
+      </c>
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>desenvolver a economia e acabar com a pobreza.</t>
+        </is>
+      </c>
+      <c r="D922" t="inlineStr">
+        <is>
+          <t>conquistar a autonomia de cada país recém-fundado.</t>
+        </is>
+      </c>
+      <c r="E922" t="inlineStr">
+        <is>
+          <t>expulsar as influências religiosas sobre os americanos.</t>
+        </is>
+      </c>
+      <c r="F922" t="inlineStr">
+        <is>
+          <t>formar elites intelectuais capazes de governar cada país.</t>
+        </is>
+      </c>
+      <c r="G922" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H922" t="inlineStr">
+        <is>
+          <t>Bolívar, na Carta da Jamaica, destaca a dificuldade de unir politicamente os países recém-independentes da América Espanhola em uma grande nação republicana. Ele compara a situação à fragmentação do Império Romano, indicando que cada região formaria sistemas políticos próprios, dificultando a unidade e a estabilidade republicana.</t>
+        </is>
+      </c>
+      <c r="I922" t="inlineStr">
+        <is>
+          <t>PH09</t>
+        </is>
+      </c>
+      <c r="J922" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K922" t="inlineStr"/>
+      <c r="L922" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>Os ideais da Revolução Francesa e da Revolução Americana do final do século 18 poderiam ter sido os precursores do sentimento de independência latino-americano, mas sem o vácuo de poder que ocorreu em Espanha com a invasão francesa, os acontecimentos poderiam ter sido muito diferentes. 
+Disponível em: https://www.bbc.com/portuguese/articles/c0vywp38j39o. Acesso em: 03 dez. 2024.
+Ao mencionar o vácuo de poder que impulsionou as independências da América Espanhola, o texto se refere a qual processo histórico?</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>A Revolução Russa.</t>
+        </is>
+      </c>
+      <c r="C923" t="inlineStr">
+        <is>
+          <t>A Revolução Industrial.</t>
+        </is>
+      </c>
+      <c r="D923" t="inlineStr">
+        <is>
+          <t>A Revolução Francesa.</t>
+        </is>
+      </c>
+      <c r="E923" t="inlineStr">
+        <is>
+          <t>A Primeira Guerra Mundial.</t>
+        </is>
+      </c>
+      <c r="F923" t="inlineStr">
+        <is>
+          <t>A expansão do Império Napoleônico.</t>
+        </is>
+      </c>
+      <c r="G923" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H923" t="inlineStr">
+        <is>
+          <t>A expansão do Império Napoleônico, especialmente a ocupação da Espanha, teve um impacto direto nas colônias, criando um vácuo de poder que facilitou movimentos de independência.</t>
+        </is>
+      </c>
+      <c r="I923" t="inlineStr">
+        <is>
+          <t>PH09</t>
+        </is>
+      </c>
+      <c r="J923" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K923" t="inlineStr"/>
+      <c r="L923" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>Em 1810, 18 milhões de habitantes viviam nas Américas sob o governo  da Espanha. [...] a minoria de quatro milhões era de brancos, tanto espanhóis peninsulares, os chamados chapetones, como crioulos, isto é, brancos nascidos nas Américas. Estes últimos viviam uma contraditória situação: estavam no topo da sociedade colonial, mas, no entanto, desempenhavam um papel secundário ante os espanhóis peninsulares em termos de privilégios, acesso à riqueza, aos monopólios, à administração e às decisões políticas.
+MADER, M. Revoluções de Independência na América Espanhola: uma reflexão historiográfica. Revista de História 159, PUC-RJ. 2º sem, 2008.
+Uma das principais razões para a elite criolla liderar os movimentos de independência na América Espanhola foi a(o)</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>exclusão dos criollos dos altos cargos administrativos.</t>
+        </is>
+      </c>
+      <c r="C924" t="inlineStr">
+        <is>
+          <t>influência direta das ideias comunistas europeias.</t>
+        </is>
+      </c>
+      <c r="D924" t="inlineStr">
+        <is>
+          <t>imposição de tributos excessivos pela metrópole.</t>
+        </is>
+      </c>
+      <c r="E924" t="inlineStr">
+        <is>
+          <t>proibição de comércio com outras nações.</t>
+        </is>
+      </c>
+      <c r="F924" t="inlineStr">
+        <is>
+          <t>apoio militar dos Estados Unidos.</t>
+        </is>
+      </c>
+      <c r="G924" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H924" t="inlineStr">
+        <is>
+          <t>A elite criolla, embora economicamente poderosa, era excluída dos altos cargos administrativos pela metrópole espanhola, o que gerava insatisfação e motivava a busca por independência.</t>
+        </is>
+      </c>
+      <c r="I924" t="inlineStr">
+        <is>
+          <t>PH09</t>
+        </is>
+      </c>
+      <c r="J924" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K924" t="inlineStr"/>
+      <c r="L924" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>Em primeiro lugar, é preciso afirmar que o Congresso e a própria formulação do projeto integrador não foram utopias ou “sonhos” de um líder visionário, mas iniciativas justificadas pelas potencialidades que emergiam da Revolução e cuidadosamente debatidas e preparadas durante anos pelos encarregados da diplomacia na América independente. Havia uma história comum justificando o projeto, bem como um grande objetivo – vencer a guerra e se defender de novas ameaças – além de objetivos menores, igualmente comuns.
+FIGUEIREDO, A; BRAGA, M. Simón Bolívar e o Congresso do Panamá: O primeiro integracionismo latino-americano. Disponível em:  https://www.historia.uff.br/revistapassagens/artigos_ing/v9n2a82017_ing.pdf. Acesso em: 3 dez. 2024.
+O trecho apresenta as justificativas para a realização do Congresso do Panamá no contexto das lutas de independência da América espanhola. O principal objetivo do Congresso do Panamá está ligado ao fato de que essas independências se deram pela</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>oferta de liberdade por parte da Coroa.</t>
+        </is>
+      </c>
+      <c r="C925" t="inlineStr">
+        <is>
+          <t>guerra com as forças espanholas.</t>
+        </is>
+      </c>
+      <c r="D925" t="inlineStr">
+        <is>
+          <t>negociação com as elites europeias.</t>
+        </is>
+      </c>
+      <c r="E925" t="inlineStr">
+        <is>
+          <t>revolta de escravizados negros e indígenas.</t>
+        </is>
+      </c>
+      <c r="F925" t="inlineStr">
+        <is>
+          <t>compra das terras americanas pelos criollos.</t>
+        </is>
+      </c>
+      <c r="G925" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H925" t="inlineStr">
+        <is>
+          <t>O principal objetivo do Congresso do Panamá estava ligado ao fato de que as independências das colônias espanholas na América foram conquistadas através de guerras contra as forças espanholas. Assim, esse Congresso tinha como uma de suas principais metas a defesa dessas novas nações contra possíveis ameaças e a consolidação de suas independências, que foram obtidas por meio de batalhas e conflitos armados.</t>
+        </is>
+      </c>
+      <c r="I925" t="inlineStr">
+        <is>
+          <t>PH09</t>
+        </is>
+      </c>
+      <c r="J925" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K925" t="inlineStr"/>
+      <c r="L925" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>Os escravizados desta parte da colônia  deram início ao processo revolucionário, desafiando não unicamente o colonialismo,  mas, a hierarquia racial sobre qual estava fundado todo o sistema escravista. [...] Como salienta Trouillot (2015), a revolução de 1791 ultrapassou os limites colocados pelo sistema escravista e derrubava os princípios fundamentais que formataram aquela sociedade.
+LOGIS, B. A Revolução Haitiana (1791-1804) como momento privilegiado na construção de  uma identidade “negra”. Disponível em: https://www.snh2019.anpuh.org/resources/anais/8/1565315599_ARQUIVO_TextoBernoAnpuh2019.pdf. Acesso em: 03 dez. 2024.
+A diferença da Revolução Haitiana para as demais revoluções de independência na América Espanhola, destacada no trecho acima, é a(o)</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>apoio militar e financeiro dos Estados Unidos aos revoltosos.</t>
+        </is>
+      </c>
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>formação de uma monarquia constitucional pelos escravistas.</t>
+        </is>
+      </c>
+      <c r="D926" t="inlineStr">
+        <is>
+          <t>protagonismo de africanos escravizados e seus descendentes.</t>
+        </is>
+      </c>
+      <c r="E926" t="inlineStr">
+        <is>
+          <t>liderança de uma elite criolla influenciada pela Revolução Francesa.</t>
+        </is>
+      </c>
+      <c r="F926" t="inlineStr">
+        <is>
+          <t>criação de uma confederação de Estados com outras colônias francesas.</t>
+        </is>
+      </c>
+      <c r="G926" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H926" t="inlineStr">
+        <is>
+          <t>A independência do Haiti foi única na América Latina porque foi realizada principalmente por africanos escravizados e seus descendentes, diferentemente das outras independências, que foram lideradas por elites criollas.</t>
+        </is>
+      </c>
+      <c r="I926" t="inlineStr">
+        <is>
+          <t>PH09</t>
+        </is>
+      </c>
+      <c r="J926" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K926" t="inlineStr"/>
+      <c r="L926" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>Se a América Espanhola não podia ter na Espanha um abastecedor industrial e socioeconômico, existia outra alternativa. Durante o século XVIII, a economia britânica estava efetuando uma mudança revolucionária, e de 1700 a 1800, quando a Revolução Industrial se torna realmente efetiva, experimentou um crescimento comercial sem precedentes.
+BETHELL, Leslie. História da América Latina. 5. La Independencia. Barcelona: Editorial Crítica, 1991, p. 3. Adaptado. Tradução livre.
+A relação entre a Revolução Industrial e as independências da América Latina se baseia no(a)</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>investimento inglês em indústrias coloniais espanholas para desenvolvê-las economicamente.</t>
+        </is>
+      </c>
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>recusa latino-americana em negociar com os ingleses, devido ao seu apego à metrópole espanhola.</t>
+        </is>
+      </c>
+      <c r="D927" t="inlineStr">
+        <is>
+          <t>despreparo espanhol para colonizar a América, resultando na transferência da responsabilidade para os ingleses.</t>
+        </is>
+      </c>
+      <c r="E927" t="inlineStr">
+        <is>
+          <t>apoio inglês aos espanhóis durante as guerras de independência, uma vez que os dois países europeus eram aliados.</t>
+        </is>
+      </c>
+      <c r="F927" t="inlineStr">
+        <is>
+          <t>interesse inglês em expandir seus produtos para o mercado consumidor de regiões até então colonizadas, como a América.</t>
+        </is>
+      </c>
+      <c r="G927" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H927" t="inlineStr">
+        <is>
+          <t>A Revolução Industrial na Inglaterra havia possibilitado que este país produzisse uma quantidade até então nunca vista de mercadorias. Na busca de mercados consumidores para esses produtos, a Inglaterra viu na América um caminho possível. Por isso, apoiou os países latino-americanos em suas guerras de independência contra a Espanha, já que se a independência fosse efetivada, o Exclusivo Comercial Metropolitano, que impedia que as colônias comercializassem com a Inglaterra – pois exigia que cada colônia comercializasse apenas com sua metrópole – seria revogado.</t>
+        </is>
+      </c>
+      <c r="I927" t="inlineStr">
+        <is>
+          <t>PH09</t>
+        </is>
+      </c>
+      <c r="J927" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K927" t="inlineStr"/>
+      <c r="L927" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>A administração ostentava o poder político, mas seu poder militar era escasso e assentava sua autoridade na soberania da coroa. [...] O maior poder econômico estava nas mãos das elites, proprietários rurais e urbanos, que englobavam [...] uma maioria de criollos. No século XVIII, as oligarquias locais, baseadas em importantes interesses territoriais, mineiros e mercantis, [...] com um forte sentido de identidade regional, estavam bem estabelecidas ao largo de toda a América.”
+BETHELL, Leslie. História da América Latina. 5. La Independencia. Barcelona: Editorial Crítica, 1991, p. 5. Tradução livre. (Adaptado).
+Assinale a alternativa que apresente, respectivamente, o grupo que dominava a administração política e o grupo que detinha o poder econômico na América Espanhola.</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>chapetones, espanhóis com privilégios concedidos pelo rei; criollos, nascidos e enriquecidos na colônia.</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>criollos, nascidos na colônia e contra a independência; chapetones, enriquecidos pela mineração e sem poder político.</t>
+        </is>
+      </c>
+      <c r="D928" t="inlineStr">
+        <is>
+          <t>chapetones, nascidos na colônia e explorados pela mineração; criollos, nascidos na Espanha e enriquecidos na colônia.</t>
+        </is>
+      </c>
+      <c r="E928" t="inlineStr">
+        <is>
+          <t>chapetones, espanhóis enriquecidos pela mineração; criollos, espanhóis enriquecidos por privilégios concedidos pelo rei.</t>
+        </is>
+      </c>
+      <c r="F928" t="inlineStr">
+        <is>
+          <t>criollos, nascidos na Espanha e empobrecidos durante a independência; chapetones, nascidos na Espanha e defensores da independência.</t>
+        </is>
+      </c>
+      <c r="G928" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H928" t="inlineStr">
+        <is>
+          <t>Os chapetones eram espanhóis nascidos na metrópole que tinham privilégios garantidos pelo rei nas colônias, como assumir cargos administrativos. Já os criollos eram espanhóis nascidos nas colônias que não recebiam nenhuma benesse da Coroa Espanhola, mas que detinham poder econômico e constituíam as elites locais.</t>
+        </is>
+      </c>
+      <c r="I928" t="inlineStr">
+        <is>
+          <t>PH09</t>
+        </is>
+      </c>
+      <c r="J928" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K928" t="inlineStr"/>
+      <c r="L928" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>O haitianismo animou negros e mulatos nos quatro cantos do continente americano, inclusive no Brasil. [...] Várias revoltas escravas e conspirações de negros livres aqui se inspiraram no que ocorrera no Haiti.
+REIS, João José. Quilombos e revoltas escravas no Brasil. Revista USP (28), 1996 p. 27. Disponível em:
+&lt;https://www.revistas.usp.br/revusp/article/view/28362&gt;. Acesso em: 11 maio 2020.
+Os movimentos de independência do Haiti tiveram influência sobre os escravizados do Brasil porque</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>culminaram no fim da escravidão em toda a América, incluindo o Brasil.</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>foram incentivados pelos criollos, classe que apoiava o fim da escravidão no Brasil e no Haiti.</t>
+        </is>
+      </c>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>resultaram da ação de escravizados que se encontravam em situação similar aos escravizados do Brasil.</t>
+        </is>
+      </c>
+      <c r="E929" t="inlineStr">
+        <is>
+          <t>incentivaram que os escravizados do Brasil se organizassem para apoiar os criollos na luta contra os espanhóis.</t>
+        </is>
+      </c>
+      <c r="F929" t="inlineStr">
+        <is>
+          <t>apoiaram os espanhóis contra o criollos, do mesmo modo que os escravizados do Brasil apoiaram os portugueses.</t>
+        </is>
+      </c>
+      <c r="G929" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H929" t="inlineStr">
+        <is>
+          <t>O movimento de independência do Haiti foi organizado por escravizados da então colônia, que objetivavam, também, a abolição da escravatura. Por ter sido um movimento de grandes proporções no mundo colonial, assustou as classes dirigentes que baseavam sua sociedade e economia na mão de obra escrava, como o Brasil, temendo que um movimento como este se alastrasse pela América.</t>
+        </is>
+      </c>
+      <c r="I929" t="inlineStr">
+        <is>
+          <t>PH09</t>
+        </is>
+      </c>
+      <c r="J929" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K929" t="inlineStr"/>
+      <c r="L929" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>Perto de uma baía no leste de Cuba, os Estados Unidos mantêm o último reduto das prisões secretas que criou em todo o mundo em sua ‘guerra ao terror’: o centro de detenção em Guantánamo. [...] A partir de janeiro de 2002, os primeiros prisioneiros começaram a chegar a Guantánamo e pouco a pouco a prisão improvisada em uma base militar no leste de Cuba estava cheia de alguns dos homens mais procurados do mundo.
+LIMA, Lioman. O que faz da prisão mantida pelos EUA em Guantánamo a mais cara do mundo. BBC News, 29 set. 2019. Disponível em:
+&lt;https://www.bbc.com/portuguese/internacional-49804838&gt;. Acesso em: 11 maio 2020.
+A existência de uma prisão estadunidense em território cubano, até os dias de hoje, é consequência do/a:</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>conflito comercial entre os dois países, que foi resolvido com o intercâmbio de seus territórios.</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>ajuda oferecida por Cuba depois da crise pela qual os Estados Unidos passaram por conta de sua independência.</t>
+        </is>
+      </c>
+      <c r="D930" t="inlineStr">
+        <is>
+          <t>ajuda estadunidense à independência cubana, que resultou na cessão de parte do território da ilha aos estadunidenses.</t>
+        </is>
+      </c>
+      <c r="E930" t="inlineStr">
+        <is>
+          <t>aliança que os dois países realizaram durante a guerra de independência dos Estados Unidos, em que Cuba forneceu crédito.</t>
+        </is>
+      </c>
+      <c r="F930" t="inlineStr">
+        <is>
+          <t>guerra entre Estados Unidos e Cuba, tendo como vitoriosos os primeiros e a continuidade da colonização do último.</t>
+        </is>
+      </c>
+      <c r="G930" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H930" t="inlineStr">
+        <is>
+          <t>Durante a guerra de independência de Cuba, os Estados Unidos ofereceram ajuda à ilha contra a Espanha. Quando Cuba formulou sua própria constituição, já independente, os Estados Unidos exigiram a inserção da Emenda Platt, que garantia aos estadunidenses o direito de intervir em Cuba e o acesso a parte de seu território. Esta última cláusula foi utilizada para a construção da prisão de Guantánamo, respondendo aos conflitos contemporâneos dos Estados Unidos.</t>
+        </is>
+      </c>
+      <c r="I930" t="inlineStr">
+        <is>
+          <t>PH09</t>
+        </is>
+      </c>
+      <c r="J930" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K930" t="inlineStr"/>
+      <c r="L930" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>Consagrado pela historiografia oficial como o maior herói militar nacional, e invocado até hoje com expressões como ‘Libertador da América’, ‘Pai da Pátria’. [...] A necessidade do Estado argentino de construir essa figura histórica emblemática foi articulada principalmente a partir de dois ângulos: foi decisiva para alcançar a independência política da Argentina, do Chile e do Peru; em segundo lugar, tornando a pessoa [...] um exemplo ético, que preferiu se retirar da cena política em pleno apogeu por não querer derramar ‘sangue argentino’ em guerras civis.”
+ROCA, Andrea. A vida social de um emblema nacional [...]. Mana, Rio de Janeiro, v. 18, n. 1, p. 121
+Escolha a alternativa que apresente corretamente quem é a “figura histórica emblemática” do texto acima e qual era sua proposta para a América Espanhola.</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>Simon Bolívar, que propunha a unificação em uma só república.</t>
+        </is>
+      </c>
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>José San Martín, que propunha a unificação em uma só república.</t>
+        </is>
+      </c>
+      <c r="D931" t="inlineStr">
+        <is>
+          <t>José San Martín, que propunha a organização em monarquias locais e constitucionais.</t>
+        </is>
+      </c>
+      <c r="E931" t="inlineStr">
+        <is>
+          <t>Simon Bolívar, que propunha a permanência dos vice-reinos sob a autoridade da Coroa Espanhola.</t>
+        </is>
+      </c>
+      <c r="F931" t="inlineStr">
+        <is>
+          <t>José San Martín, que propunha a permanência dos vice-reinos sob a autoridade da Coroa Espanhola.</t>
+        </is>
+      </c>
+      <c r="G931" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H931" t="inlineStr">
+        <is>
+          <t>Uma vez que o texto cita o responsável pela independência da Argentina, do Chile e do Peru, bem como menciona a paralisação repentina de suas atividades, é possível concluir que o texto se refere a José San Martín. Esse general propunha que, com a independência, a América Espanhola se organizasse em monarquias locais e constitucionais.</t>
+        </is>
+      </c>
+      <c r="I931" t="inlineStr">
+        <is>
+          <t>PH09</t>
+        </is>
+      </c>
+      <c r="J931" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K931" t="inlineStr"/>
+      <c r="L931" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>Federer homenageia Rafael Nadal em carta emocionante: “Sempre torcendo por você”
+Lendas do tênis se tornaram amigos após duelos históricos nas quadras
+Disponível em: https://www.cnnbrasil.com.br/esportes/tenis/federer-homenageia-rafael-nadal-em-carta-emocionante-sempre-torcendo-por-voce/. Acesso em 03 de dez. 2024.
+A partir da manchete acima, identifique a alternativa que apresenta corretamente a relação entre o predicativo do sujeito e o verbo de ligação.</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>O verbo "duelos" liga o sujeito "amigos" ao predicativo "lendas do tênis".</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>O predicativo do sujeito "se tornaram" é "amigos", ligado pelo verbo "históricos".</t>
+        </is>
+      </c>
+      <c r="D932" t="inlineStr">
+        <is>
+          <t>O verbo de ligação "se tornaram" indica transformação, e o predicativo do sujeito é "amigos".</t>
+        </is>
+      </c>
+      <c r="E932" t="inlineStr">
+        <is>
+          <t>O predicativo do sujeito "lendas do tênis" é "duelos históricos", ligado pelo verbo "se tornaram".</t>
+        </is>
+      </c>
+      <c r="F932" t="inlineStr">
+        <is>
+          <t>O sujeito "duelos históricos" está relacionado ao verbo de ligação "amigos", indicando uma qualidade.</t>
+        </is>
+      </c>
+      <c r="G932" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H932" t="inlineStr">
+        <is>
+          <t>Na frase "Lendas do tênis se tornaram amigos após duelos históricos nas quadras", o verbo "se tornaram" atua como um verbo de ligação, indicando uma transformação ou mudança de estado. Nesse contexto, o sujeito da frase é "Lendas do tênis", e o predicativo do sujeito, que descreve o novo estado ou condição do sujeito após a transformação, é "amigos". Portanto, o verbo de ligação "se tornaram" conecta o sujeito "Lendas do tênis" ao predicativo "amigos", indicando que as lendas do tênis passaram a ser amigos após os duelos históricos.</t>
+        </is>
+      </c>
+      <c r="I932" t="inlineStr">
+        <is>
+          <t>PH09</t>
+        </is>
+      </c>
+      <c r="J932" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K932" t="inlineStr"/>
+      <c r="L932" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>Federer relembra choro em carta emocionante a Nadal antes de possível adeus: 'Um dos momentos mais especiais'
+A iminência da aposentadoria de Rafael Nadal levou Roger Federer a prestar uma homenagem a seu principal adversário no tênis com uma carta pública, devolvendo o gesto do espanhol em setembro de 2022, quando o suíço estava prestes a deixar as quadras.
+Disponível em: https://www.espn.com.br/tenis/artigo/_/id/14461988/federer-relembra-choro-em-carta-emocionante-a-nadal-antes-de-possivel-adeus. Acesso em 03 de dez. 2024.
+O último verbo conjugado do texto é acompanhado por</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>um objeto direto.</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>um objeto indireto.</t>
+        </is>
+      </c>
+      <c r="D933" t="inlineStr">
+        <is>
+          <t>um predicativo do objeto.</t>
+        </is>
+      </c>
+      <c r="E933" t="inlineStr">
+        <is>
+          <t>um predicativo do sujeito.</t>
+        </is>
+      </c>
+      <c r="F933" t="inlineStr">
+        <is>
+          <t>um predicado verbo-nominal.</t>
+        </is>
+      </c>
+      <c r="G933" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H933" t="inlineStr">
+        <is>
+          <t>O último verbo conjugado do texto é "estava", na frase "quando o suíço estava prestes a deixar as quadras". Nesse contexto, "estava" é um verbo de ligação que conecta o sujeito "o suíço" ao seu predicativo "prestes a deixar as quadras". O predicativo do sujeito é a expressão que atribui uma característica ou estado ao sujeito, completando o sentido do verbo de ligação. Portanto, "prestes a deixar as quadras" funciona como predicativo do sujeito "o suíço".</t>
+        </is>
+      </c>
+      <c r="I933" t="inlineStr">
+        <is>
+          <t>PH09</t>
+        </is>
+      </c>
+      <c r="J933" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K933" t="inlineStr"/>
+      <c r="L933" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>Fábio Carille fica entusiasmado por causa de meio-campista do Santos.
+Meio-campista retorna ao Peixe após defender a Seleção Venezuelana, contra a Argentina.
+Disponível em: https://br.bolavip.com/santos/fabio-carille-fica-entusiasmado-por-causa-de-meio-campista-do-santos#:~:text=Carille%20est%C3%A1%20animado%20com%20retorno%20de%20meio%2Dcampista%20no%20Santos&amp;text=%C3%89%20bem%20verdade%20que%20em,isso%20vem%20intensificando%20os%20treinamentos.. Acesso em 07 jan. 2025.
+Na manchete, o verbo "ficar" tem a função de um verbo de ligação. Qual é o efeito de sentido produzido pelo uso desse verbo na oração?</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>Permanência.</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>Transitoriedade.</t>
+        </is>
+      </c>
+      <c r="D934" t="inlineStr">
+        <is>
+          <t>Mudança de estado.</t>
+        </is>
+      </c>
+      <c r="E934" t="inlineStr">
+        <is>
+          <t>Interrupção de estado.</t>
+        </is>
+      </c>
+      <c r="F934" t="inlineStr">
+        <is>
+          <t>Continuidade de estado.</t>
+        </is>
+      </c>
+      <c r="G934" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H934" t="inlineStr">
+        <is>
+          <t>Na manchete, o verbo "ficar" atua como um verbo de ligação, conectando o sujeito "Fábio Carille" ao predicativo "entusiasmado". Esse verbo de ligação indica uma mudança de estado, ou seja, Fábio Carille não estava entusiasmado anteriormente, mas passou a estar devido ao retorno do meio-campista do Santos. O uso do verbo "ficar" sugere que houve uma transição no estado emocional de Carille, de um estado anterior para um novo estado de entusiasmo.</t>
+        </is>
+      </c>
+      <c r="I934" t="inlineStr">
+        <is>
+          <t>PH09</t>
+        </is>
+      </c>
+      <c r="J934" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K934" t="inlineStr"/>
+      <c r="L934" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>O apresentador Fausto Silva desafiou Xande a criar um samba de partido alto ao vivo no palco do programa, e o sambista improvisou os versos para o auditório da Band.
+Disponível em: https://www.band.uol.com.br/entretenimento/faustao-na-band/noticias/o-que-e-o-partido-alto-xande-de-pilares-explica-esse-estilo-de-samba-16476499. Acesso em 03 de dez. 2024. 
+A correta classificação do predicado retirado do texto e seu respectivo núcleo é</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>Predicado verbal; núcleo: "desafiou"</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>Predicado nominal; núcleo: "desafiou"</t>
+        </is>
+      </c>
+      <c r="D935" t="inlineStr">
+        <is>
+          <t>Predicado nominal; núcleo: "improvisou"</t>
+        </is>
+      </c>
+      <c r="E935" t="inlineStr">
+        <is>
+          <t>Predicado verbo-nominal; núcleo: "criar"</t>
+        </is>
+      </c>
+      <c r="F935" t="inlineStr">
+        <is>
+          <t>Predicado verbo-nominal; núcleo: "improvisou"</t>
+        </is>
+      </c>
+      <c r="G935" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H935" t="inlineStr">
+        <is>
+          <t>O predicado "desafiou Xande a criar um samba de partido alto ao vivo no palco do programa" é um predicado verbal. Isso ocorre porque o verbo "desafiou" é um verbo transitivo direto, ou seja, ele exige um complemento (objeto direto) para completar seu sentido. No caso, o complemento é "Xande a criar um samba de partido alto ao vivo no palco do programa". O núcleo do predicado é o verbo "desafiou", que é a palavra mais importante do predicado e indica a ação realizada pelo sujeito "O apresentador Fausto Silva".</t>
+        </is>
+      </c>
+      <c r="I935" t="inlineStr">
+        <is>
+          <t>PH09</t>
+        </is>
+      </c>
+      <c r="J935" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K935" t="inlineStr"/>
+      <c r="L935" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>Conhecida como “Quelé”, Clementina de Jesus da Silva se tornou um dos nomes da música popular brasileira que representa as heranças africanas e que revolucionou o samba. Nascida em 1901 em Valença, na região cafeeira do estado do Rio de Janeiro, sua história retrata a realidade de grande parcela da população brasileira. Tendo trabalhado grande parte da vida como empregada doméstica; ela, que foi neta de escravizados, construiu uma carreira na música quando já completava seus 63 anos. 
+Disponível em: https://expresso.estadao.com.br/naperifa/saiba-quem-foi-clementina-de-jesus-cantora-que-resgatou-as-origens-negras-do-samba/. Acesso em 04 de dez. 2024.
+Quanto a concordância nominal da frase em destaque, é correto afirmar que</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>"seus 63 anos" deveria ser "suas 63 anos".</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>"neta" deveria concordar com "escravizados".</t>
+        </is>
+      </c>
+      <c r="D936" t="inlineStr">
+        <is>
+          <t>"carreira" deveria ser "carreiras" para concordar com "ela".</t>
+        </is>
+      </c>
+      <c r="E936" t="inlineStr">
+        <is>
+          <t>"neta" concorda com "ela" e "seus 63 anos" concorda com "ela".</t>
+        </is>
+      </c>
+      <c r="F936" t="inlineStr">
+        <is>
+          <t>"completava" deveria ser "completavam" para concordar com "63 anos".</t>
+        </is>
+      </c>
+      <c r="G936" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H936" t="inlineStr">
+        <is>
+          <t>Na frase "ela, que foi neta de escravizados, construiu uma carreira na música quando já completava seus 63 anos", a palavra "neta" concorda com "ela", que é um pronome feminino. Isso significa que "neta" está corretamente no gênero feminino para se referir à mulher mencionada, Clementina de Jesus. Além disso, a expressão "seus 63 anos" também está correta, pois "seus" é um pronome possessivo que concorda com "ela" em gênero e número. "Seus" é utilizado para indicar que os 63 anos pertencem a ela, e "anos" é um substantivo masculino, o que justifica o uso de "seus" em vez de "suas".</t>
+        </is>
+      </c>
+      <c r="I936" t="inlineStr">
+        <is>
+          <t>PH09</t>
+        </is>
+      </c>
+      <c r="J936" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K936" t="inlineStr"/>
+      <c r="L936" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>Machado de Assis
+Escritor carioca. Um dos maiores escritores da literatura em língua portuguesa. Mulato de origem pobre, cursou somente a escola primária. Como autodidata, angariou extensa cultura literária. Aos 16 anos, foi tipógrafo-aprendiz da Imprensa Nacional. Publicou seus primeiros versos na revista A Marmota, aos 18 anos. De 1858 em diante, colaborou no Correio Mercantil, Diário do Rio de Janeiro, Semana Ilustrada. Estreou em livro com o volume de poemas Crisálidas (1864). Escreveu peças teatrais no gênero cômico,entre as quais: Quase Ministro (1864) e Os Deuses de Casaca (1866). Trabalhou no Diário Oficial (1867-1873) e na Secretaria da Agricultura Comércio e Obras Públicas. Na década de 1870, vieram a lume obras descontos e romances inspirados no Romantismo, como: Contos Fluminenses (1870), A Mão e a Luva (1874), Helena (1876) e Iaiá Garcia (1878). A partir do romance Memórias Póstumas de Brás Cubas (1881), amadureceu e consagrou em suas criações o realismo psicológico e a análise da realidade social: Quincas Borba (1892), Dom Casmurro (1900), Esaú e Jacó (1904), Relíquias da Casa Velha (1906). Em 1897, fundou com outros intelectuais a Academia Brasileira de Letras, da qual foi o primeiro presidente.
+Machado de Assis. Disponível em: &lt;http://funag.gov.br/loja/download/565-Biografias.pdf&gt;. Acesso em: 14 maio 2018. p. 47. Adaptado.
+O trecho que introduz um predicativo do sujeito “Machado de Assis”, por meio do uso do verbo de ligação implícito, é</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>“De 1858 em diante, colaborou no Correio Mercantil, Diário do Rio de Janeiro, Semana Ilustrada”.</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>“Estreou em livro com o volume de poemas Crisálidas (1864)”.</t>
+        </is>
+      </c>
+      <c r="D937" t="inlineStr">
+        <is>
+          <t>“Publicou seus primeiros versos na revista A Marmota, aos 18 anos”.</t>
+        </is>
+      </c>
+      <c r="E937" t="inlineStr">
+        <is>
+          <t>“Trabalhou no Diário Oficial (1867-1873) e na Secretaria da Agricultura Comércio e Obras Públicas".</t>
+        </is>
+      </c>
+      <c r="F937" t="inlineStr">
+        <is>
+          <t>“Um dos maiores escritores em língua portuguesa”.</t>
+        </is>
+      </c>
+      <c r="G937" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H937" t="inlineStr">
+        <is>
+          <t>Esse trecho oculta o verbo "ser", conjugado na terceira pessoa do singular do pretérito perfeito do indicativo ("foi"). Mesmo oculto o verbo, o trecho atribui uma característica a Machado de Assis, o que configura um predicativo do sujeito.</t>
+        </is>
+      </c>
+      <c r="I937" t="inlineStr">
+        <is>
+          <t>PH09</t>
+        </is>
+      </c>
+      <c r="J937" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K937" t="inlineStr"/>
+      <c r="L937" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>"Chegando a casa, já ali achou o Gustavo, um pouco preocupado e a própria D. Amélia o parecia também. Entrou rindo, e perguntou ao amigo se lhe faltava alguma cousa.
+— Nada.
+— Nada?
+— Por quê?
+— Mete a mão no bolso; não te falta nada?
+— Falta-me a carteira, disse o Gustavo sem meter a mão no bolso.
+— Sabes se alguém a achou?
+— Achei-a eu, disse Honório entregando-lha.
+Machado de Assis. A carteira. Disponível em:
+&lt;http://www.dominiopublico.gov.br/download/texto/ua000180.pdf&gt;. Acesso em: 20 maio 2019.
+No trecho 'Chegando a casa, já ali achou o Gustavo, um pouco preocupado e a própria D. Amélia o parecia também', só é predicativo do objeto a expressão</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>"também".</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr">
+        <is>
+          <t>"ali".</t>
+        </is>
+      </c>
+      <c r="D938" t="inlineStr">
+        <is>
+          <t>"um pouco preocupado".</t>
+        </is>
+      </c>
+      <c r="E938" t="inlineStr">
+        <is>
+          <t>"a própria".</t>
+        </is>
+      </c>
+      <c r="F938" t="inlineStr">
+        <is>
+          <t>"a casa".</t>
+        </is>
+      </c>
+      <c r="G938" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H938" t="inlineStr">
+        <is>
+          <t>No trecho, o predicativo do objeto é “um pouco preocupado”, que se refere a Gustavo. Podemos checar tentando fazer a substituição de Gustavo por um pronome oblíquo, "Chegando em casa já ali achou-o um pouco preocupado".</t>
+        </is>
+      </c>
+      <c r="I938" t="inlineStr">
+        <is>
+          <t>PH09</t>
+        </is>
+      </c>
+      <c r="J938" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K938" t="inlineStr"/>
+      <c r="L938" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>Assinale a alternativa cujo termo sublinhado constitua um predicativo do objeto.</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>“As almas são incomunicáveis” (M. Bandeira)</t>
+        </is>
+      </c>
+      <c r="C939" t="inlineStr">
+        <is>
+          <t>“Gerebita tornara-se enfadonho” (M. Lobato)</t>
+        </is>
+      </c>
+      <c r="D939" t="inlineStr">
+        <is>
+          <t>“A terra, porém, permanece elevada...” (E. da Cunha)</t>
+        </is>
+      </c>
+      <c r="E939" t="inlineStr">
+        <is>
+          <t>“Os dentes continuavam alvíssimos” (G. Amado)</t>
+        </is>
+      </c>
+      <c r="F939" t="inlineStr">
+        <is>
+          <t>“Chamava-lhe perversa”. (M. de Assis)</t>
+        </is>
+      </c>
+      <c r="G939" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H939" t="inlineStr">
+        <is>
+          <t>O adjetivo “perversa” está predicando o objeto (-lhe) do verbo chamar. As demais alternativas contém apenas predicativos do sujeito ligados por verbo não nocional.</t>
+        </is>
+      </c>
+      <c r="I939" t="inlineStr">
+        <is>
+          <t>PH09</t>
+        </is>
+      </c>
+      <c r="J939" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K939" t="inlineStr"/>
+      <c r="L939" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>A uberdade nativa do solo é o fator que o condiciona. Mal a uberdade se esvai, pela reiterada sucção de uma seiva não composta, como no velho mundo, pelo adubo, o desenvolvimento da zona esmorece, foge dela o capital – e com ele os homens fortes, aptos para o trabalho. E lentamente cai a tapera nas almas e nas coisas.
+Em São Paulo temos perfeito exemplo disso na depressão profunda que entorpece boa parte do chamado Norte.
+Ali tudo foi, nada é. Não se conjugam verbos no presente. Tudo é pretérito. Umas tantas cidades moribundas arrastam um viver decrépito, gasto em chorar na mesquinhez de hoje as saudosas grandezas de dantes.
+Pelas ruas ermas, onde o transeunte é raro, não matracoleja sequer uma carroça; de há muito, em matéria de rodas, se voltou aos rodízios desse rechinante símbolo do viver colonial – o carro de boi. Erguem-se por ali soberbos casarões apalaçados, de dois e três andares, sólidos como fortalezas, tudo pedra, cal e cabiúna; casarões que lembram ossaturas de megatérios donde as carnes, o sangue, a vida para sempre refugiram.
+LOBATO, Monteiro. Cidades mortas.
+No trecho “Umas tantas cidades moribundas arrastam um viver decrépito, gasto em chorar na mesquinhez de hoje as saudosas grandezas de dantes”, os adjetivos destacados são, respectivamente, predicativos dos objetos</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>“viver” e “dantes”.</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>“viver” e “grandezas”.</t>
+        </is>
+      </c>
+      <c r="D940" t="inlineStr">
+        <is>
+          <t>“gasto” e “grandezas”.</t>
+        </is>
+      </c>
+      <c r="E940" t="inlineStr">
+        <is>
+          <t>“chorar” e “cidades”.</t>
+        </is>
+      </c>
+      <c r="F940" t="inlineStr">
+        <is>
+          <t>“chorar” e “grandezas”.</t>
+        </is>
+      </c>
+      <c r="G940" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H940" t="inlineStr">
+        <is>
+          <t>O adjetivo “decrépito” é predicativo do objeto “viver”, ligado ao verbo “arrastar”; o adjetivo “saudosas” é predicativo do objeto “grandezas”, que está ligado ao verbo “chorar”.</t>
+        </is>
+      </c>
+      <c r="I940" t="inlineStr">
+        <is>
+          <t>PH09</t>
+        </is>
+      </c>
+      <c r="J940" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K940" t="inlineStr"/>
+      <c r="L940" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>Em 1960, da noite para o dia, Carolina Maria de Jesus passou, de total desconhecida, a escritora famosa. Jamais havia ocorrido no Brasil tamanho sucesso editorial. Seu livro Quarto de despejo foi editado oito vezes, em tiragens de 10 mil exemplares cada.
+No ano seguinte, ela já era carta fora do baralho, no país. Publicou Casa de alvenaria, pouco vendido. Mas, no exterior, iniciaram-se as traduções de Quarto de despejo. Curiosamente, as primeiras foram a dinamarquesa e a holandesa. Em meados da década de 1960, o livro já existia em 14 idiomas.
+Hoje, Carolina Maria de Jesus é bem conhecida no estrangeiro, especialmente nos Estados Unidos, onde sempre teve seus livros reeditados. No Brasil, poucos se lembram dela e quase ninguém sabe que ela escreveu muito mais que seu famoso diário de 1960.
+A história da sua vida permaneceu cercada de mistérios. Por que Carolina tinha uma necessidade tão premente de escrever? Por que, repentinamente, tornou-se sucesso tão grande em seu país e, com igual rapidez, foi tão rejeitada? Por que continuou praticamente esquecida por tanto tempo, em sua terra natal? Como explicar tamanha atração exercida por sua obra no estrangeiro? Por que foi mais bem aceita no exterior do que aqui? Que aconteceu com ela e seus filhos depois do sucesso memorável? E com os diversos cadernos manuscritos de contos, poesias, provérbios, pensamentos, peças de teatro e romances já existentes e anunciados na mídia quando o diário foi descoberto?
+Nesta biografia, tenta-se responder a essas perguntas. No fim, fica a certeza de que Carolina Maria de Jesus foi uma pessoa corajosa, independente e sobretudo fascinante.
+CASTRO, Eliana de Moura; MACHADO, Marília Novais de Mata. Muito bem, Carolina!:
+biografia de Carolina Maria de Jesus. Belo Horizonte: C/ Arte, 2007. p. 11. (Adaptado).
+No trecho “Em 1960, da noite para o dia, Carolina Maria de Jesus passou, de total desconhecida, a escritora famosa”, o verbo “passar” é de ligação porque indica</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>a atividade de caminhar pelas ruas.</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>a passagem vertiginosa do tempo.</t>
+        </is>
+      </c>
+      <c r="D941" t="inlineStr">
+        <is>
+          <t>a sequenciação dos turnos dos dias.</t>
+        </is>
+      </c>
+      <c r="E941" t="inlineStr">
+        <is>
+          <t>a transformação de estado do sujeito.</t>
+        </is>
+      </c>
+      <c r="F941" t="inlineStr">
+        <is>
+          <t>a ultrapassagem de outros escritores​.</t>
+        </is>
+      </c>
+      <c r="G941" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H941" t="inlineStr">
+        <is>
+          <t>No trecho, o verbo “passar” funciona como verbo de ligação porque indica transformação do estado de espírito do sujeito e relaciona-o diretamente ao predicativo “escritora famosa”.</t>
+        </is>
+      </c>
+      <c r="I941" t="inlineStr">
+        <is>
+          <t>PH09</t>
+        </is>
+      </c>
+      <c r="J941" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K941" t="inlineStr"/>
+      <c r="L941" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>Uma empresa de alimentos deseja distribuir pacotes de biscoitos em caixas que serão enviadas para diferentes lojas. Cada caixa deve conter o mesmo número de pacotes. Para garantir que a distribuição seja justa, o gerente precisa determinar quantos pacotes serão acomodados em cada caixa , com base no número total de pacotes disponíveis. Ele encontrou a seguinte equação:
+onde x representa a quantidade de pacotes por caixa.
+Qual é o conjunto solução (S) da equação, considerando U = {1, 2, 3, 4, 5}?</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>S = {1}</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>S = {2}</t>
+        </is>
+      </c>
+      <c r="D942" t="inlineStr">
+        <is>
+          <t>S = {3}</t>
+        </is>
+      </c>
+      <c r="E942" t="inlineStr">
+        <is>
+          <t>S = {4}</t>
+        </is>
+      </c>
+      <c r="F942" t="inlineStr">
+        <is>
+          <t>S = {5}</t>
+        </is>
+      </c>
+      <c r="G942" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H942" t="inlineStr">
+        <is>
+          <t>O conjunto universo é dado: U = {1, 2, 3, 4, 5}. Para encontrar o conjunto solução (S), basta resolver a equação:
+Logo, S = {4}.</t>
+        </is>
+      </c>
+      <c r="I942" t="inlineStr">
+        <is>
+          <t>PH09</t>
+        </is>
+      </c>
+      <c r="J942" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K942" t="inlineStr">
+        <is>
+          <t>8a_ph09_mat_01.png</t>
+        </is>
+      </c>
+      <c r="L942" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>Um mecânico está ajustando a pressão dos pneus de um veículo. Ele sabe que a pressão ideal é dada pela fórmula:
+onde P é a pressão em psi (libras por polegada quadrada) e F é a força aplicada em libras-força (lbf).
+Se a pressão ideal é de 5 psi, determine a força aplicada F necessária para alcançar essa pressão.</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>8 libras-força (lbf).</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr">
+        <is>
+          <t>8,5 libras-força (lbf).</t>
+        </is>
+      </c>
+      <c r="D943" t="inlineStr">
+        <is>
+          <t>9 libras-força (lbf).</t>
+        </is>
+      </c>
+      <c r="E943" t="inlineStr">
+        <is>
+          <t>9,5 libras-força (lbf).</t>
+        </is>
+      </c>
+      <c r="F943" t="inlineStr">
+        <is>
+          <t>17 libras-força (lbf).</t>
+        </is>
+      </c>
+      <c r="G943" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H943" t="inlineStr">
+        <is>
+          <t>Para resolver essa questão, basta isolar a variável F na equação dada.
+ Libras-força (lbf).</t>
+        </is>
+      </c>
+      <c r="I943" t="inlineStr">
+        <is>
+          <t>PH09</t>
+        </is>
+      </c>
+      <c r="J943" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K943" t="inlineStr">
+        <is>
+          <t>8a_ph09_mat_02.png</t>
+        </is>
+      </c>
+      <c r="L943" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>Um engenheiro está projetando uma ponte e precisa calcular a força necessária para suportar uma carga. A força F é dada pela equação:
+F = 3x + 2
+onde x é a carga em toneladas.
+Se a força necessária é de 14 toneladas, qual é a carga suportada pela ponte?</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>3 toneladas</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>4 toneladas</t>
+        </is>
+      </c>
+      <c r="D944" t="inlineStr">
+        <is>
+          <t>5 toneladas</t>
+        </is>
+      </c>
+      <c r="E944" t="inlineStr">
+        <is>
+          <t>6 toneladas</t>
+        </is>
+      </c>
+      <c r="F944" t="inlineStr">
+        <is>
+          <t>7 toneladas</t>
+        </is>
+      </c>
+      <c r="G944" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H944" t="inlineStr">
+        <is>
+          <t>Para resolver essa questão, basta isolar a variável x na equação dada. Sabe-se que F = 14, logo:
+ toneladas.</t>
+        </is>
+      </c>
+      <c r="I944" t="inlineStr">
+        <is>
+          <t>PH09</t>
+        </is>
+      </c>
+      <c r="J944" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K944" t="inlineStr"/>
+      <c r="L944" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>Um químico está preparando uma solução e precisa misturar dois líquidos, A e B.
+A quantidade de líquido A é representada por x e a quantidade de líquido B é representada por y. A relação entre as quantidades é dada pela equação:
+2x + 3y = 12.
+Dado que a quantidade de líquido B é 2 litros, determine a quantidade de líquido A necessária para satisfazer a equação.</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>1 litro</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>2 litros</t>
+        </is>
+      </c>
+      <c r="D945" t="inlineStr">
+        <is>
+          <t>3 litros</t>
+        </is>
+      </c>
+      <c r="E945" t="inlineStr">
+        <is>
+          <t>4 litros</t>
+        </is>
+      </c>
+      <c r="F945" t="inlineStr">
+        <is>
+          <t>6 litros</t>
+        </is>
+      </c>
+      <c r="G945" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H945" t="inlineStr">
+        <is>
+          <t>Para resolver essa questão, basta substituir y = 2 na equação dada e resolver para x:
+ Litros.</t>
+        </is>
+      </c>
+      <c r="I945" t="inlineStr">
+        <is>
+          <t>PH09</t>
+        </is>
+      </c>
+      <c r="J945" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K945" t="inlineStr"/>
+      <c r="L945" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>Uma empresa está analisando a eficiência de sua produção utilizando uma fórmula matemática que relaciona o número de máquinas em operação e o tempo de produção em horas. Para verificar um padrão, a seguinte equação fracionária foi utilizada:
+, onde x representa o número de máquinas necessárias para produzir uma certa quantidade de produtos.
+Determine o valor de x que satisfaz a equação.</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>6.</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>8.</t>
+        </is>
+      </c>
+      <c r="D946" t="inlineStr">
+        <is>
+          <t>12.</t>
+        </is>
+      </c>
+      <c r="E946" t="inlineStr">
+        <is>
+          <t>16.</t>
+        </is>
+      </c>
+      <c r="F946" t="inlineStr">
+        <is>
+          <t>24.</t>
+        </is>
+      </c>
+      <c r="G946" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H946" t="inlineStr">
+        <is>
+          <t>Resolvendo a equação fracionária:
+Logo, x é igual à 8.</t>
+        </is>
+      </c>
+      <c r="I946" t="inlineStr">
+        <is>
+          <t>PH09</t>
+        </is>
+      </c>
+      <c r="J946" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K946" t="inlineStr">
+        <is>
+          <t>8a_ph09_mat_05.png</t>
+        </is>
+      </c>
+      <c r="L946" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>Considere as equações abaixo.
+ e .
+Sabendo que essas equações são equivalentes, qual é o valor de m?</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>[img:8a_ph09_mat_06_a.png]</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>[img:8a_ph09_mat_06_b.png]</t>
+        </is>
+      </c>
+      <c r="D947" t="inlineStr">
+        <is>
+          <t>[img:8a_ph09_mat_06_c.png]</t>
+        </is>
+      </c>
+      <c r="E947" t="inlineStr">
+        <is>
+          <t>[img:8a_ph09_mat_06_d.png]</t>
+        </is>
+      </c>
+      <c r="F947" t="inlineStr">
+        <is>
+          <t>[img:8a_ph09_mat_06_e.png]</t>
+        </is>
+      </c>
+      <c r="G947" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H947" t="inlineStr">
+        <is>
+          <t>Substituindo o valor de x na outra equação, obtemos:</t>
+        </is>
+      </c>
+      <c r="I947" t="inlineStr">
+        <is>
+          <t>PH09</t>
+        </is>
+      </c>
+      <c r="J947" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K947" t="inlineStr">
+        <is>
+          <t>8a_ph09_mat_06.png</t>
+        </is>
+      </c>
+      <c r="L947" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>Alguns alunos de uma turma do 8° ano escreveram a condição para que a equação , na incógnita x, pudesse ser resolvida. Veja o que cada um concluiu.
+Alan: .
+Breno: .
+Cícero: .
+Dener: .
+Ênio: .
+Qual aluno respondeu corretamente?</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>Alan.</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>Breno.</t>
+        </is>
+      </c>
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>Cícero.</t>
+        </is>
+      </c>
+      <c r="E948" t="inlineStr">
+        <is>
+          <t>Dener.</t>
+        </is>
+      </c>
+      <c r="F948" t="inlineStr">
+        <is>
+          <t>Ênio.</t>
+        </is>
+      </c>
+      <c r="G948" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H948" t="inlineStr">
+        <is>
+          <t>Portanto, Cícero respondeu corretamente.</t>
+        </is>
+      </c>
+      <c r="I948" t="inlineStr">
+        <is>
+          <t>PH09</t>
+        </is>
+      </c>
+      <c r="J948" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K948" t="inlineStr">
+        <is>
+          <t>8a_ph09_mat_07.png</t>
+        </is>
+      </c>
+      <c r="L948" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>Considere as equações abaixo.
+Qual é a associação correta de cada equação da esquerda com a sua solução à direita?</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>IV – a / III – b / II – c / I – d</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>I – a / II – b / III – c / IV – d</t>
+        </is>
+      </c>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>II – a / IV – b / I – c / III – d</t>
+        </is>
+      </c>
+      <c r="E949" t="inlineStr">
+        <is>
+          <t>III – a / I – b / IV – c / II – d</t>
+        </is>
+      </c>
+      <c r="F949" t="inlineStr">
+        <is>
+          <t>I – a / III – b / IV – c / II – d</t>
+        </is>
+      </c>
+      <c r="G949" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H949" t="inlineStr">
+        <is>
+          <t>Logo, a associação é IV – a / III – b / II – c / I – d.</t>
+        </is>
+      </c>
+      <c r="I949" t="inlineStr">
+        <is>
+          <t>PH09</t>
+        </is>
+      </c>
+      <c r="J949" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K949" t="inlineStr">
+        <is>
+          <t>8a_ph09_mat_08.png</t>
+        </is>
+      </c>
+      <c r="L949" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>A professora de uma turma do 8° ano pediu aos seus alunos que determinassem a condição para que a equação abaixo, na incógnita x, pudesse ser resolvida.
+Qual é essa condição?</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>[img:8a_ph09_mat_09_b.png]</t>
+        </is>
+      </c>
+      <c r="D950" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="E950" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="F950" t="inlineStr">
+        <is>
+          <t>[img:8a_ph09_mat_09_e.png]</t>
+        </is>
+      </c>
+      <c r="G950" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H950" t="inlineStr">
+        <is>
+          <t>Devemos ter as seguintes condições:
+Portanto,  e .</t>
+        </is>
+      </c>
+      <c r="I950" t="inlineStr">
+        <is>
+          <t>PH09</t>
+        </is>
+      </c>
+      <c r="J950" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K950" t="inlineStr">
+        <is>
+          <t>8a_ph09_mat_09.png</t>
+        </is>
+      </c>
+      <c r="L950" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>Considere as equações abaixo e os números na tabela.
+I	R	A	G	S	O	L	U	T	M	C
+12	5	2	-1	-0,8	6	10	-3	4	-0,4	-11
+Associando as raízes dessas equações, na ordem em que aparecem, às letras apresentadas na tabela anterior, forma-se qual das palavras abaixo?</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>AMIGO.</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>GASTO.</t>
+        </is>
+      </c>
+      <c r="D951" t="inlineStr">
+        <is>
+          <t>MICOS.</t>
+        </is>
+      </c>
+      <c r="E951" t="inlineStr">
+        <is>
+          <t>RATOS.</t>
+        </is>
+      </c>
+      <c r="F951" t="inlineStr">
+        <is>
+          <t>LUTAR.</t>
+        </is>
+      </c>
+      <c r="G951" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H951" t="inlineStr">
+        <is>
+          <t>Portanto, forma-se a palavra AMIGO.</t>
+        </is>
+      </c>
+      <c r="I951" t="inlineStr">
+        <is>
+          <t>PH09</t>
+        </is>
+      </c>
+      <c r="J951" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K951" t="inlineStr">
+        <is>
+          <t>8a_ph09_mat_10.png</t>
+        </is>
+      </c>
+      <c r="L951" t="inlineStr">
         <is>
           <t>8ano</t>
         </is>

--- a/questoes.xlsx
+++ b/questoes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L951"/>
+  <dimension ref="A1:L1001"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51189,7 +51189,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K902" t="inlineStr"/>
       <c r="L902" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -51248,7 +51247,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K903" t="inlineStr"/>
       <c r="L903" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -51307,7 +51305,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K904" t="inlineStr"/>
       <c r="L904" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -51366,7 +51363,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K905" t="inlineStr"/>
       <c r="L905" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -51425,7 +51421,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K906" t="inlineStr"/>
       <c r="L906" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -51484,7 +51479,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K907" t="inlineStr"/>
       <c r="L907" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -51543,7 +51537,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K908" t="inlineStr"/>
       <c r="L908" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -51602,7 +51595,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K909" t="inlineStr"/>
       <c r="L909" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -51661,7 +51653,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K910" t="inlineStr"/>
       <c r="L910" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -51720,7 +51711,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K911" t="inlineStr"/>
       <c r="L911" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -51780,7 +51770,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K912" t="inlineStr"/>
       <c r="L912" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -51840,7 +51829,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K913" t="inlineStr"/>
       <c r="L913" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -51900,7 +51888,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K914" t="inlineStr"/>
       <c r="L914" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -52025,7 +52012,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K916" t="inlineStr"/>
       <c r="L916" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -52085,7 +52071,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K917" t="inlineStr"/>
       <c r="L917" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -52143,7 +52128,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K918" t="inlineStr"/>
       <c r="L918" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -52203,7 +52187,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K919" t="inlineStr"/>
       <c r="L919" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -52263,7 +52246,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K920" t="inlineStr"/>
       <c r="L920" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -52321,7 +52303,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K921" t="inlineStr"/>
       <c r="L921" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -52382,7 +52363,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K922" t="inlineStr"/>
       <c r="L922" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -52442,7 +52422,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K923" t="inlineStr"/>
       <c r="L923" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -52502,7 +52481,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K924" t="inlineStr"/>
       <c r="L924" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -52562,7 +52540,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K925" t="inlineStr"/>
       <c r="L925" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -52622,7 +52599,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K926" t="inlineStr"/>
       <c r="L926" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -52682,7 +52658,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K927" t="inlineStr"/>
       <c r="L927" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -52742,7 +52717,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K928" t="inlineStr"/>
       <c r="L928" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -52803,7 +52777,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K929" t="inlineStr"/>
       <c r="L929" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -52864,7 +52837,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K930" t="inlineStr"/>
       <c r="L930" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -52924,7 +52896,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K931" t="inlineStr"/>
       <c r="L931" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -52985,7 +52956,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K932" t="inlineStr"/>
       <c r="L932" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -53046,7 +53016,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K933" t="inlineStr"/>
       <c r="L933" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -53107,7 +53076,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K934" t="inlineStr"/>
       <c r="L934" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -53167,7 +53135,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K935" t="inlineStr"/>
       <c r="L935" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -53227,7 +53194,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K936" t="inlineStr"/>
       <c r="L936" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -53288,7 +53254,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K937" t="inlineStr"/>
       <c r="L937" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -53356,7 +53321,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K938" t="inlineStr"/>
       <c r="L938" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -53414,7 +53378,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K939" t="inlineStr"/>
       <c r="L939" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -53477,7 +53440,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K940" t="inlineStr"/>
       <c r="L940" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -53542,7 +53504,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K941" t="inlineStr"/>
       <c r="L941" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -53734,7 +53695,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K944" t="inlineStr"/>
       <c r="L944" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -53796,7 +53756,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K945" t="inlineStr"/>
       <c r="L945" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -54192,6 +54151,3101 @@
         </is>
       </c>
     </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>A etiqueta de eficiência energética do INMETRO classifica os eletrodomésticos em diferentes categorias de acordo com sua eficiência. Suponha que um refrigerador de classe A consuma 30% menos energia do que um de classe B.
+Se um refrigerador de classe B consome 500 kWh por ano, quanto consome um refrigerador de classe A?</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>350 kWh.</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>400 kWh.</t>
+        </is>
+      </c>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>450 kWh.</t>
+        </is>
+      </c>
+      <c r="E952" t="inlineStr">
+        <is>
+          <t>500 kWh.</t>
+        </is>
+      </c>
+      <c r="F952" t="inlineStr">
+        <is>
+          <t>550 kWh.</t>
+        </is>
+      </c>
+      <c r="G952" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H952" t="inlineStr">
+        <is>
+          <t>De acordo com o cálculo, o refrigerador de classe A consome 350 kWh.
+Cálculo de 30% do consumo do refrigerador de classe B:
+Subtrair esse valor do consumo do refrigerador de classe B para encontrar o consumo do refrigerador de classe A:</t>
+        </is>
+      </c>
+      <c r="I952" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J952" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K952" t="inlineStr"/>
+      <c r="L952" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>Um aparelho elétrico tem uma potência nominal de 1500 W e é utilizado por 2 horas.
+Qual é o consumo de energia elétrica desse aparelho?</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>1,5 kWh.</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>2 kWh.</t>
+        </is>
+      </c>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>2,5 kWh.</t>
+        </is>
+      </c>
+      <c r="E953" t="inlineStr">
+        <is>
+          <t>3 kWh.</t>
+        </is>
+      </c>
+      <c r="F953" t="inlineStr">
+        <is>
+          <t>3,5 kWh.</t>
+        </is>
+      </c>
+      <c r="G953" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H953" t="inlineStr">
+        <is>
+          <t>Para resolver o problema de consumo de energia elétrica, precisamos usar a fórmula:
+E é o consumo de energia em quilowatt-hora (kWh),
+P é a potência em quilowatts (kW),
+t é o tempo em horas (h).
+Converter a potência de Watts para Quilowatts:
+Calcular o consumo de energia:</t>
+        </is>
+      </c>
+      <c r="I953" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J953" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K953" t="inlineStr"/>
+      <c r="L953" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>Um eletrodoméstico está conectado a uma tomada cuja a tensão (U) é de 220V em um circuito que a corrente elétrica que flui por esse aparelho é de 5A.
+Qual é a potência (P) do circuito?</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>550 w.</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>1100 W.</t>
+        </is>
+      </c>
+      <c r="D954" t="inlineStr">
+        <is>
+          <t>1320 W.</t>
+        </is>
+      </c>
+      <c r="E954" t="inlineStr">
+        <is>
+          <t>1400 W.</t>
+        </is>
+      </c>
+      <c r="F954" t="inlineStr">
+        <is>
+          <t>2200 W.</t>
+        </is>
+      </c>
+      <c r="G954" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H954" t="inlineStr">
+        <is>
+          <t>Para resolver essa questão, vamos utilizar a fórmula da potência elétrica:
+Onde:
+P é a potência em watts (W)
+U é a tensão em volts (V) = 220 V
+i é a corrente em amperes (A) = 5 A</t>
+        </is>
+      </c>
+      <c r="I954" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J954" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K954" t="inlineStr"/>
+      <c r="L954" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>Uma residência possui os seguintes eletrodomésticos:
+1 geladeira que consome 30 kWh por mês
+1 máquina de lavar que consome 20 kWh por mês
+1 ar-condicionado que consome 50 kWh por mês
+5 lâmpadas que consomem 5 kWh cada por mês
+Se o valor do kWh é de R$ 0,60, qual será o valor total da conta de energia elétrica dessa residência no final do mês?</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>R$ 60,00.</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>R$ 75,00.</t>
+        </is>
+      </c>
+      <c r="D955" t="inlineStr">
+        <is>
+          <t>R$ 84,00.</t>
+        </is>
+      </c>
+      <c r="E955" t="inlineStr">
+        <is>
+          <t>R$ 96,00.</t>
+        </is>
+      </c>
+      <c r="F955" t="inlineStr">
+        <is>
+          <t>R$ 108,00.</t>
+        </is>
+      </c>
+      <c r="G955" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H955" t="inlineStr">
+        <is>
+          <t>O consumo total das lâmpadas é:
+Todos os consumos: 
+Cálculo do valor total da conta de energia elétrica
+Sabendo que o valor de kWh é de R$ 0,60. Então, o valor total da conta de energia elétrica será:</t>
+        </is>
+      </c>
+      <c r="I955" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J955" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K955" t="inlineStr"/>
+      <c r="L955" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>[...] Lâmpadas LED com eficiência 10 vezes maior que uma lâmpada convencional estão hoje na iluminação doméstica e comercial, em faróis de automóveis, luzes de jardim, lanternas de bolso, etc. A iluminação LED branco pode ser usada não só para diminuir o consumo de energia, mas também para poupar recursos energéticos. Por exemplo, só nos EUA, calcula-se que, até 2020, a iluminação à base de LED branco evitará a construção de 133 usinas. [...]
+Ciência Hoje. Disponível em: &lt; https: acervo="" ch="" ch_321.pdf="" cienciahoje.periodicos.capes.gov.br="" storage=""&gt; Acesso em: 15 jan. 2025.
+Qual é a principal razão para a adoção de lâmpadas LED, conforme discutido no texto?</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>Aumento do consumo de energia.</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>Redução do consumo de energia.</t>
+        </is>
+      </c>
+      <c r="D956" t="inlineStr">
+        <is>
+          <t>Aumento da produção de energia.</t>
+        </is>
+      </c>
+      <c r="E956" t="inlineStr">
+        <is>
+          <t>Redução dos custos de produção de energia.</t>
+        </is>
+      </c>
+      <c r="F956" t="inlineStr">
+        <is>
+          <t>Aumento da eficiência das usinas de energia.</t>
+        </is>
+      </c>
+      <c r="G956" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H956" t="inlineStr">
+        <is>
+          <t>O texto destaca que a iluminação LED branco pode ser usada para diminuir o consumo de energia. Além disso, menciona que a eficiência das lâmpadas LED é 10 vezes maior que a das lâmpadas convencionais, o que contribui para a redução do consumo energético.</t>
+        </is>
+      </c>
+      <c r="I956" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J956" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K956" t="inlineStr"/>
+      <c r="L956" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>Pensando em comprar um ferro elétrico, um advogado depara-se na loja com modelos das marcas A e B, cujos dados são:
+marca A: 220 V – 1 500 W
+marca B: 115 V – 1 300 W
+Se a tensão elétrica fornecida nas tomadas da sua residência é de 110 V, qual a melhor opção para este advogado?</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>O advogado deve escolher o ferro elétrico B, pois o valor da tensão do produto é compatível com a rede elétrica e ele apresentará uma potência menor do que a A, quando ligado ambos em 110V.</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>O advogado não deve comprar nenhum deles, uma vez que ambos queimarão ao serem ligados, pois os valores das tensões dadas pelos fabricantes são maiores que 110 V.</t>
+        </is>
+      </c>
+      <c r="D957" t="inlineStr">
+        <is>
+          <t>O advogado deve escolher o ferro elétrico A, pois o valor da tensão do produto é maior do que a do ferro B, causando maior aquecimento.</t>
+        </is>
+      </c>
+      <c r="E957" t="inlineStr">
+        <is>
+          <t>O advogado deve escolher o ferro elétrico B, pois o valor da tensão do produto é compatível com a rede elétrica da sua casa e ele apresentará uma potência maior do que a A, quando ligado ambos em 110V.</t>
+        </is>
+      </c>
+      <c r="F957" t="inlineStr">
+        <is>
+          <t>O advogado deve escolher o ferro elétrico A, pois o valor da tensão do produto é compatível com a rede elétrica e ele apresentará uma potência maior do que a B, quando ligado ambos em 110V.</t>
+        </is>
+      </c>
+      <c r="G957" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H957" t="inlineStr">
+        <is>
+          <t>O advogado deve escolher o ferro cujo valor da tensão do produto é compatível com a rede elétrica a que sua residência está ligada. Como essa tensão é de 110 V, ele deve escolher o ferro B, cuja tensão dada é de 115 V. Não faz sentido comprar um ferro construído para funcionar em 220 V e ligá-lo em 110 V. Ele não queima, mas certamente tem um funcionamento inadequado.</t>
+        </is>
+      </c>
+      <c r="I957" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J957" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K957" t="inlineStr"/>
+      <c r="L957" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>Duas geladeiras possuem a mesma potência, porém uma deve ser ligada no 110 V e outra em uma tomada de 220 V.
+Considerando que elas são mantidas ligadas o tempo todo, qual grandeza física elas terão de diferente, além da tensão?</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>Corrente</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>Energia</t>
+        </is>
+      </c>
+      <c r="D958" t="inlineStr">
+        <is>
+          <t>Tempo</t>
+        </is>
+      </c>
+      <c r="E958" t="inlineStr">
+        <is>
+          <t>Força</t>
+        </is>
+      </c>
+      <c r="F958" t="inlineStr">
+        <is>
+          <t>Potência</t>
+        </is>
+      </c>
+      <c r="G958" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H958" t="inlineStr">
+        <is>
+          <t>Temos que a geladeira ligada na tensão 110 V tem potência:
+Para a geladeira ligada na tensão 220 V:
+Logo temos que a corrente da geladeira ligada na tensão 110 V é o dobro da geladeira ligada na tensão de 220 V, e portanto as correntes serão diferentes.</t>
+        </is>
+      </c>
+      <c r="I958" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J958" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K958" t="inlineStr"/>
+      <c r="L958" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>A geração de energia elétrica causa diversos impactos ao meio ambiente, dependendo daforma com que ela é gerada. Assim, reduzir o consumo de energia elétrica é uma forma de reduzir os danos causados à natureza.
+Como a energia elétrica consumida depende da potência dos aparelhos e de seu tempo de uso, marque a alternativa que representa o maior gasto energético:</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>Secador de cabelos – 1500 W, ligado durante 30 minutos.</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>Três lâmpadas incandescentes – 60 W cada, ligadas durante 1 h.</t>
+        </is>
+      </c>
+      <c r="D959" t="inlineStr">
+        <is>
+          <t>Ar-condicionado – 1 kW, ligado durante 3 h.</t>
+        </is>
+      </c>
+      <c r="E959" t="inlineStr">
+        <is>
+          <t>Chuveiro – 5000 W, ligado durante 1.800 segundos.</t>
+        </is>
+      </c>
+      <c r="F959" t="inlineStr">
+        <is>
+          <t>Ferro de passar – 1,3 kW, ligado durante 20 minutos.</t>
+        </is>
+      </c>
+      <c r="G959" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H959" t="inlineStr">
+        <is>
+          <t>Calculando a energia de cada aparelho:
+Secador de cabelos: E = P.t = 1500 W . 1/2 h = 750 Wh
+Três lâmpadas incandescentes: E = P.t = 3.60 W . 1 h = 180 Wh
+Ar-condicionado: E = P.t = 1000 W . 3 h = 3.000 Wh
+Chuveiro: E = P.t = 5000 W . 1/2 h = 2.500 Wh
+Ferro de passar: E = P.t = 1300 W . 1/3 h = 433,33 Wh
+Logo o ar-condicionado é o aparelho que mais consome energia.</t>
+        </is>
+      </c>
+      <c r="I959" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J959" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K959" t="inlineStr"/>
+      <c r="L959" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>Uma casa tem um consumo de energia elétrica de 152 000 Wh e o custo de cada kWh da empresa que fornece energia elétrica para esta casa é de R$ 0,80.
+Qual será a conta de luz desta família?</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>R$ 60,80</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>R$ 121,60</t>
+        </is>
+      </c>
+      <c r="D960" t="inlineStr">
+        <is>
+          <t>R$ 182,40</t>
+        </is>
+      </c>
+      <c r="E960" t="inlineStr">
+        <is>
+          <t>R$ 608,00</t>
+        </is>
+      </c>
+      <c r="F960" t="inlineStr">
+        <is>
+          <t>R$ 1216,00</t>
+        </is>
+      </c>
+      <c r="G960" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H960" t="inlineStr">
+        <is>
+          <t>O consumo de energia nesta residência foi de 152 000 Wh, que é o mesmo que 152 kWh. Se cada 1 kWh o custo é de R$ 0,80, para encontrar o valor cobrado no final do mês para esta família, calcula-se da seguinte forma:
+Por tanto, o valor cobrado será de R$ 121,60.</t>
+        </is>
+      </c>
+      <c r="I960" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J960" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K960" t="inlineStr"/>
+      <c r="L960" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>Com a intenção de diminuir a conta de luz, Marina deu algumas sugestões aos seus pais.
+Qual a sugestão que ajudaria a diminuir o consumo de energia elétrica?</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>Trocar o ventilador por ar condicionado.</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>Trocar o fogão a gás por um fogão elétrico.</t>
+        </is>
+      </c>
+      <c r="D961" t="inlineStr">
+        <is>
+          <t>Trocar as lâmpadas fluorescente para lâmpadas LED.</t>
+        </is>
+      </c>
+      <c r="E961" t="inlineStr">
+        <is>
+          <t>Usar o chuveiro com mais frequência no dia.</t>
+        </is>
+      </c>
+      <c r="F961" t="inlineStr">
+        <is>
+          <t>Usar secador de cabelo para secar as roupas molhadas.</t>
+        </is>
+      </c>
+      <c r="G961" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H961" t="inlineStr">
+        <is>
+          <t>Ao trocar as lâmpadas fluorescentes para lâmpadas LED, o consumo de energia será reduzido, pois a potência das lâmpadas LED são menores.</t>
+        </is>
+      </c>
+      <c r="I961" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J961" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K961" t="inlineStr"/>
+      <c r="L961" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>Leia o texto a seguir. 
+No México, as indústrias maquiladoras, instaladas na fronteira norte na década de 1990 exemplificam algumas das dinâmicas amplamente favorecidas pelo neoliberalismo. Impulsionadas pelos baixos salários no país, elas se concentram nas etapas mais intensivas em trabalho, na montagem – etapa de menor valor agregado – empregando uma maioria de mulheres, não raro migrantes que ficaram no país. Tudo isso em contraposição às atividades da cadeia desenvolvidas nos países mais ricos, de desenvolvimento intelectual do produto e fabricação de componentes mais avançados
+Disponível em: https://diplomatique.org.br/resistencias-mexicanas-entre-massacres-travessias-e-lutas/. Acesso em 17 de dez de 2024.
+Por que as indústrias maquiladoras se instalaram na fronteira norte do México na década de 1990?</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>Devido aos altos salários oferecidos no México.</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>Para se beneficiar dos baixos salários no país</t>
+        </is>
+      </c>
+      <c r="D962" t="inlineStr">
+        <is>
+          <t>Para desenvolver produtos intelectualmente avançados</t>
+        </is>
+      </c>
+      <c r="E962" t="inlineStr">
+        <is>
+          <t>Devido à alta qualificação da mão de obra local</t>
+        </is>
+      </c>
+      <c r="F962" t="inlineStr">
+        <is>
+          <t>Para promover igualdade salarial entre trabalhadores.</t>
+        </is>
+      </c>
+      <c r="G962" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H962" t="inlineStr">
+        <is>
+          <t>As indústrias maquiladoras se instalaram na fronteira norte do México para aproveitar os baixos salários oferecidos no país. Essa estratégia permitiu que as empresas reduzissem seus custos de produção, concentrando-se em etapas de trabalho intensivo, como a montagem, que requerem menos qualificação e oferecem menor valor agregado.</t>
+        </is>
+      </c>
+      <c r="I962" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J962" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K962" t="inlineStr"/>
+      <c r="L962" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>O império asteca floresceu entre c. 1345 e 1521 e dominou a antiga Mesoamérica. Esta nação jovem e belicosa foi muito bem-sucedida em expandir suas fronteiras e conquistar riquezas fabulosas, mas, então, chegaram estranhos visitantes de outro mundo. Liderados por Hernán Cortés, as armas formidáveis dos espanhóis e sua sede por tesouros iriam trazer uma destruição devastadora, além de doenças. Os Conquistadores imediatamente encontraram aliados locais, ansiosos para ajudar a derrubar o brutal regime dos astecas e libertar-se do fardo dos tributos e da necessidade de alimentar o insaciável apetite dos seus senhores por vítimas sacrificiais. Com isso, bastaram três anos para que caísse o maior império que já existira até então nas Américas do Norte e Central.
+Disponível em: https://www.worldhistory.org/trans/pt/2-916/cortes-e-a-queda-do-imperio-asteca/. Acesso em 17 de dez de 2024.
+Qual foi um dos principais fatores que contribuíram para a queda do império asteca?</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>A falta de recursos naturais na região.</t>
+        </is>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>A resistência dos astecas contra os invasores.</t>
+        </is>
+      </c>
+      <c r="D963" t="inlineStr">
+        <is>
+          <t>A ausência de doenças trazidas pelos europeus.</t>
+        </is>
+      </c>
+      <c r="E963" t="inlineStr">
+        <is>
+          <t>A incapacidade dos espanhóis de encontrar aliados.</t>
+        </is>
+      </c>
+      <c r="F963" t="inlineStr">
+        <is>
+          <t>A superioridade dos armamentos e microrganismos.</t>
+        </is>
+      </c>
+      <c r="G963" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H963" t="inlineStr">
+        <is>
+          <t>O texto destaca que a superioridade dos armamentos espanhóis e a introdução de doenças (microrganismos) foram fatores cruciais que devastaram a população asteca e contribuíram significativamente para a queda do império.</t>
+        </is>
+      </c>
+      <c r="I963" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J963" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K963" t="inlineStr"/>
+      <c r="L963" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>Observe a imagem. 
+Disponível em: https://upload.wikimedia.org/wikipedia/commons/0/0b/Border_USA_Mexico.jpg. Acesso em 17 de dez de 2024. 
+O muro fronteiriço entre o México e os Estados Unidos é uma estrutura física destinada a controlar a imigração ilegal e o tráfico de mercadorias entre os dois países. Milhares de pessoas tentam cruzar essa fronteira em busca de melhores condições de vida nos Estados Unidos, fugindo da violência, pobreza e falta de oportunidades presentes em seus países de origem. Contudo, as autoridades americanas investem fortemente em medidas para impedir essas travessias. Observando a imagem,  qual dos fatores a seguir é um dos principais motivadores para a migração de pessoas do México para os Estados Unidos?</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>Busca por melhores condições de trabalho e de vida.</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>Interesse em conhecer as paisagens do país vizinho.</t>
+        </is>
+      </c>
+      <c r="D964" t="inlineStr">
+        <is>
+          <t>Tentativa de fugir de regiões rurais para áreas urbanas.</t>
+        </is>
+      </c>
+      <c r="E964" t="inlineStr">
+        <is>
+          <t>Desejo de participar de programas de intercâmbio cultural.</t>
+        </is>
+      </c>
+      <c r="F964" t="inlineStr">
+        <is>
+          <t>Busca por áreas com menor densidade populacional.</t>
+        </is>
+      </c>
+      <c r="G964" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H964" t="inlineStr">
+        <is>
+          <t>A principal motivação para a migração de muitos mexicanos e outros latino-americanos para os Estados Unidos é a busca por melhores condições econômicas, mais oportunidades de emprego e um padrão de vida superior comparado ao de seus países de origem.</t>
+        </is>
+      </c>
+      <c r="I964" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J964" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K964" t="inlineStr">
+        <is>
+          <t>8a_ph10_geo_03.png</t>
+        </is>
+      </c>
+      <c r="L964" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>Observe a tabela a seguir.
+Disponível em: https://www.populationpyramid.net/pt/m%C3%A9xico/2021/. Acesso em: 17 dez 2024.
+A pirâmide etária do México em 2021 revela uma população jovem com sinais de envelhecimento em curso. Esse fenômeno é típico de países em desenvolvimento, onde a taxa de natalidade diminui e a expectativa de vida aumenta devido ao acesso à informação, urbanização e serviços de saúde. Com base nestas informações, qual das seguintes afirmações melhor descreve a tendência demográfica do México?</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>População principalmente idosa, com altas taxas de natalidade.</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>Alta taxa de natalidade e baixa expectativa de vida.</t>
+        </is>
+      </c>
+      <c r="D965" t="inlineStr">
+        <is>
+          <t>Rápido crescimento populacional, pequena porção de idosos.</t>
+        </is>
+      </c>
+      <c r="E965" t="inlineStr">
+        <is>
+          <t>População jovem e sinais claros de envelhecimento.</t>
+        </is>
+      </c>
+      <c r="F965" t="inlineStr">
+        <is>
+          <t>Alta mortalidade infantil e baixa expectativa de vida.</t>
+        </is>
+      </c>
+      <c r="G965" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H965" t="inlineStr">
+        <is>
+          <t>A pirâmide etária mostra uma base alargada (população jovem) e sinais de envelhecimento (proporção crescente de faixas etárias mais altas), alinhando-se com a descrição do fenômeno de transição demográfica.</t>
+        </is>
+      </c>
+      <c r="I965" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J965" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K965" t="inlineStr">
+        <is>
+          <t>8a_ph10_geo_04.png</t>
+        </is>
+      </c>
+      <c r="L965" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>O inchaço urbano é o crescimento desordenado das cidades, que ocorre em pequenos centros de determinadas regiões urbanas. A falta de planejamento durante a expansão da cidade faz com que haja uma área que concentra as atividades e os serviços locais, atraindo uma quantidade de pessoas que muitas vezes excede a capacidade do espaço disponível.
+Disponível em: https://www.politize.com.br/inchaco-urbano/. Acesso em 17 de dez de 2024.
+Qual das seguintes consequências é mais provável no contexto das cidades mexicanas que experienciam inchaço urbano?</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>Melhor distribuição de serviços e infraestruturas.</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>Redução da poluição e qualidade do ar melhorada.</t>
+        </is>
+      </c>
+      <c r="D966" t="inlineStr">
+        <is>
+          <t>Aumento da pressão sobre serviços e infraestruturas.</t>
+        </is>
+      </c>
+      <c r="E966" t="inlineStr">
+        <is>
+          <t>Maior equilíbrio e melhor qualidade de vida.</t>
+        </is>
+      </c>
+      <c r="F966" t="inlineStr">
+        <is>
+          <t>Expansão harmoniosa e bem planejada.</t>
+        </is>
+      </c>
+      <c r="G966" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H966" t="inlineStr">
+        <is>
+          <t>O texto indica que o crescimento desordenado leva a uma concentração de atividades e serviços, aumentando a pressão sobre a infraestrutura disponível.</t>
+        </is>
+      </c>
+      <c r="I966" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J966" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K966" t="inlineStr"/>
+      <c r="L966" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>O conceito de aldeia global foi criado na década de 1960 pelo filósofo canadense Marshall Mcluhan, então professor da Escola de Comunicações da Universidade de Toronto.Segundo esse conceito, o avanço nas tecnologias de informação e comunicação encurta as distâncias no mundo e facilita trocas culturais entre os diferentes povos.O autor acreditava que, devido à diminuição das distâncias e barreiras geográficas, o planeta se reduziria a uma organização semelhante a aldeias, onde tudo e todos estariam interconectados.
+Disponível em:&lt;https://www.significados.com.br/aldeia-global/&gt;. Acesso em: 29 jun.2020.
+Na fronteira entre o México e os Estados Unidos ocorrem fatos que desmentem a ideia de aldeia global. Como por exemplo</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>a ausência de vias de circulação modernas entre os dois países.</t>
+        </is>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>a restrição da entrada de trabalhadores mexicanos nos Estados Unidos.</t>
+        </is>
+      </c>
+      <c r="D967" t="inlineStr">
+        <is>
+          <t>a dificuldade de acesso de norte-americanos ao México.</t>
+        </is>
+      </c>
+      <c r="E967" t="inlineStr">
+        <is>
+          <t>a redução das exportações do norte do México para os Estados Unidos.</t>
+        </is>
+      </c>
+      <c r="F967" t="inlineStr">
+        <is>
+          <t>o embargo econômico dos Estados Unidos à produção agrícola do México.</t>
+        </is>
+      </c>
+      <c r="G967" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H967" t="inlineStr">
+        <is>
+          <t>A fronteira entre México e Estados Unidos é uma das mais vigiadas do planeta. Um polêmico muro foi construído para tentar conter a chegada de imigrantes ilegais, vistos por muitos cidadãos estadunidenses como os culpados por diversos problemas que atingiram a economia norte-americana nos últimos anos, como a elevação do desemprego no país.</t>
+        </is>
+      </c>
+      <c r="I967" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J967" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K967" t="inlineStr"/>
+      <c r="L967" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>O muro que Trump já está construindo inevitavelmente terá que correr paralelo às margens do rio, impedindo a circulação de espécies entre os dois países e piorando a situação de plantas e animais típicos que já estão ameaçados de extinção.
+VAIANO, Bruno Disponível em &lt;https://super.abril.com.br/ciencia/muro-de-trump-pode-levar-animais-e-plantas-do-texas-a-extincao/&gt; Acesso em: 23 maio 2018.
+Com base no trecho acima, assinale a alternativa correta.</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>No mundo atual, as contradições da globalização não geram impactos na natureza.</t>
+        </is>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>Um dos motivos para construção do muro separando EUA e México é o controle da passagem de animais silvestres.</t>
+        </is>
+      </c>
+      <c r="D968" t="inlineStr">
+        <is>
+          <t>O combate acrítico à imigração de mexicanos prejudica a biodiversidade.</t>
+        </is>
+      </c>
+      <c r="E968" t="inlineStr">
+        <is>
+          <t>A construção do muro entre os EUA e o México não extrapola questões ideológicas.</t>
+        </is>
+      </c>
+      <c r="F968" t="inlineStr">
+        <is>
+          <t>A construção do muro entre os EUA e o México reflete a baixa capacidade dos humanos interagirem com o espaço.</t>
+        </is>
+      </c>
+      <c r="G968" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H968" t="inlineStr">
+        <is>
+          <t>A construção de um muro por parte dos EUA visando deter processos migratórios que partem do México, prejudica a circulação de animais silvestres.</t>
+        </is>
+      </c>
+      <c r="I968" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J968" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K968" t="inlineStr"/>
+      <c r="L968" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>Estes trabalhadores, com autorizações temporárias, ficaram conhecidos como "braceros" (numa referência em espanhol à força braçal necessária para trabalho pesado).
+Disponível em:&lt;https://www.bbc.com/portuguese/reporterbbc/story/2008/10/081017_mexicanossalario.shtml&gt;. Acesso em: 29 jun.2020.
+Os braceros podem ser definidos como:</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>Trabalhadores mexicanos que se mudaram para o complexo turístico na Flórida.</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>Trabalhadores rurais mexicanos que migram anualmente para trabalhar em colheitas.</t>
+        </is>
+      </c>
+      <c r="D969" t="inlineStr">
+        <is>
+          <t>Camponeses mexicanos que fixam-se de maneira definitiva para garantir a produção de subsistência.</t>
+        </is>
+      </c>
+      <c r="E969" t="inlineStr">
+        <is>
+          <t>Trabalhadores que implementam a modernização das "Haciendas" mexicanas.</t>
+        </is>
+      </c>
+      <c r="F969" t="inlineStr">
+        <is>
+          <t>Camponeses que trabalham como monocultura de exportação dos latifúndios mexicanos.​</t>
+        </is>
+      </c>
+      <c r="G969" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H969" t="inlineStr">
+        <is>
+          <t>Os braceros, como são conhecidos os trabalhadores temporários do campo, migram sazonalmente (transumância). Alguns desses trabalhadores rurais são donos de pequenas propriedades no México, no entanto não conseguem sustentar suas famílias somente com sua pequena roça. Em geral as condições de trabalho temporário em áreas rurais são precárias e a remuneração é baixa.</t>
+        </is>
+      </c>
+      <c r="I969" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J969" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K969" t="inlineStr"/>
+      <c r="L969" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>A industrialização mexicana teve, a partir dos anos 1960, incentivos governamentais para a entrada de capital estrangeiro. Há uma grande variedade de empresas transnacionais no México, que empregam milhares de pessoas e são responsáveis por uma parcela significativa da riqueza produzida no país.
+O nome do modelo industrial adotado pelo México ficou conhecido como:</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>Substituição de Importações.</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>Plataformas de Exportações.</t>
+        </is>
+      </c>
+      <c r="D970" t="inlineStr">
+        <is>
+          <t>Substituição de Exportações.</t>
+        </is>
+      </c>
+      <c r="E970" t="inlineStr">
+        <is>
+          <t>Plataformas de importações.</t>
+        </is>
+      </c>
+      <c r="F970" t="inlineStr">
+        <is>
+          <t>Industrialização agrária.</t>
+        </is>
+      </c>
+      <c r="G970" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H970" t="inlineStr">
+        <is>
+          <t>O México está entre os países mais industrializados da região e seguiu o mesmo modelo de substituição de importações dos vizinhos latino-americanos. Esse um processo que leva ao aumento da produção interna de um país e a diminuição das suas importações. Ao longo da história econômica mundial, os processos de substituição de importações foram desencadeados por fatores políticos ou econômicos, e foram resultado de ações planejadas ou imposição das circunstâncias.</t>
+        </is>
+      </c>
+      <c r="I970" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J970" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K970" t="inlineStr"/>
+      <c r="L970" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>TEXTO I
+A televisão brasileira mudou muito ao longo dos anos, com séries e produções novas ano após ano. Mas um seriado mexicano, de baixo orçamento e produzido nos anos 70 é presença obrigatória na programação até os dias de hoje: Chaves! [...]
+Disponível em:&lt; https://www.aficionados.com.br/tudo-sobre-chaves/&gt;. Acesso em:06 jul.2020.
+TEXTO II
+Frida Kahlo foi uma das mais importantes artistas da história do México, marcada pela tradição vanguardista do modernismo surrealista. Nascida em 1907, na Cidade do México, era filha de uma família alemã com indígenas catequizados [...]
+65 ANOS SEM FRIDA KAHLO: DOR E ORGULHO
+Neste dia, em 1954, morria aquela que revolucionou a história da arte do México.
+ANDRÉ NOGUEIRA PUBLICADO EM 13/07/2019, ÀS 00H00
+Disponível em:&lt; https://aventurasnahistoria.uol.com.br/noticias/reportagem/a-vida-e-a-morte-de-frida-kahlo.phtml&gt;. Acesso em: 06 jul.2020.
+As notícias retratam</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>a cultura mexicana restrita.</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>o elitismo das produções mexicanas.</t>
+        </is>
+      </c>
+      <c r="D971" t="inlineStr">
+        <is>
+          <t>a atual estagnação cultural mexicana.</t>
+        </is>
+      </c>
+      <c r="E971" t="inlineStr">
+        <is>
+          <t>a eliminação do componente cultural indígena.</t>
+        </is>
+      </c>
+      <c r="F971" t="inlineStr">
+        <is>
+          <t>a diversidade e impacto da produção cultural mexicana.</t>
+        </is>
+      </c>
+      <c r="G971" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H971" t="inlineStr">
+        <is>
+          <t>Chaves e Frida Kahlo são famosas representações artísticas do México, evidenciando a popularidade e impacto social da cultura mexicana no Brasil e no mundo.</t>
+        </is>
+      </c>
+      <c r="I971" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J971" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K971" t="inlineStr"/>
+      <c r="L971" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>[...] "Se você vai se tornar independente da Espanha, por que continuaria a se submeter aos mandos e desmandos de Buenos Aires, por exemplo? A divisão por vice-reinos era burocrática. E as fronteiras atuais dos países da América Latina demoraram para ser consolidadas. Não era possível prevê-las antes de 1810, pois resultaram de disputas internas após a independência", explica.
+Mas é importante lembrar que também houve na América Espanhola planos de unificação, que não avançaram.
+Por que o Brasil continuou um só enquanto a América espanhola se dividiu em vários países? BBC News Brasil. Disponível em: https://www.bbc.com/portuguese/articles/c3gjpmvkv5eo. Acesso em: 17 dez. 2024.
+Qual a causa da fragmentação política da América Latina pós-independência retratada no texto?</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>A ausência de recursos naturais.</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>A influência das potências asiáticas.</t>
+        </is>
+      </c>
+      <c r="D972" t="inlineStr">
+        <is>
+          <t>A falta de influência das elites locais.</t>
+        </is>
+      </c>
+      <c r="E972" t="inlineStr">
+        <is>
+          <t>A homogeneidade cultural e linguística.</t>
+        </is>
+      </c>
+      <c r="F972" t="inlineStr">
+        <is>
+          <t>As disputas internas entre as elites criollas.</t>
+        </is>
+      </c>
+      <c r="G972" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H972" t="inlineStr">
+        <is>
+          <t>A fragmentação política foi causada pelas disputas internas entre as elites criollas pelo poder, que resultaram em uma série de conflitos e divisões territoriais. As elites criollas locais queriam garantir seu domínio sem se submeter a um poder superior, o que levou à formação de múltiplos estados-nacionais.</t>
+        </is>
+      </c>
+      <c r="I972" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J972" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K972" t="inlineStr"/>
+      <c r="L972" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>Mesmo países que apresentavam taxas de crescimento econômico bastante elevadas, tais como os latino-americanos, cuja independência política tinha sido alcançada no princípio do século XIX, estavam limitados pela profundidade da sua dependência econômica e política da economia internacional. Seu crescimento econômico parecia destinado a acumular miséria, analfabetismo e uma distribuição de renda desastrosa.
+SANTOS, Theotônio dos. A TEORIA DA DEPENDÊNCIA:UM BALANÇO HISTÓRICO E TEÓRICO. Disponível em: https://edisciplinas.usp.br/pluginfile.php/283339/mod_resource/content/1/ateoriadadependencia.pdf. Acesso em: 17 dez. 2024.
+Qual foi a consequência das políticas agroexportadoras na América Latina no século XIX?</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>Redução da desigualdade social.</t>
+        </is>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>Fortalecimento das indústrias locais.</t>
+        </is>
+      </c>
+      <c r="D973" t="inlineStr">
+        <is>
+          <t>Independência econômica total das ex-colônias.</t>
+        </is>
+      </c>
+      <c r="E973" t="inlineStr">
+        <is>
+          <t>Dependência das potências capitalistas europeias.</t>
+        </is>
+      </c>
+      <c r="F973" t="inlineStr">
+        <is>
+          <t>Unidade política entre os países latino-americanos.</t>
+        </is>
+      </c>
+      <c r="G973" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H973" t="inlineStr">
+        <is>
+          <t>A política agroexportadora manteve a dependência das ex-colônias às potências capitalistas europeias, uma vez que as economias locais foram estruturadas para fornecer matérias-primas e produtos agrícolas para os mercados europeus. Isso impediu a diversificação econômica e a industrialização independente.</t>
+        </is>
+      </c>
+      <c r="I973" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J973" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K973" t="inlineStr"/>
+      <c r="L973" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>Tratado França-Haiti, 1825. Disponível em: https://commons.wikimedia.org/wiki/File:Trait%C3%A9_France_Ha%C3%AFti_1825.jpg. Acesso em: 17 dez. 2024.
+A imagem retrata um episódio desvantajoso para o Haiti no início do século XIX. Quais foram os principais desafios enfrentados pelo Haiti após sua independência?</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>Terras pouco produtivas e greves urbanas.</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>Desastres naturais e endividamento externo.</t>
+        </is>
+      </c>
+      <c r="D974" t="inlineStr">
+        <is>
+          <t>Isolamento diplomático e a indenização à França.</t>
+        </is>
+      </c>
+      <c r="E974" t="inlineStr">
+        <is>
+          <t>Ocupação militar pelos Estados Unidos e doenças.</t>
+        </is>
+      </c>
+      <c r="F974" t="inlineStr">
+        <is>
+          <t>Revoltas contra a escravidão e fragmentação política.</t>
+        </is>
+      </c>
+      <c r="G974" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H974" t="inlineStr">
+        <is>
+          <t>O Haiti enfrentou sérios problemas de isolamento diplomático, pois muitos países, especialmente as potências coloniais, estavam relutantes em reconhecer a independência de uma nação fundada por ex-escravos. Além disso, teve que pagar uma indenização massiva à França para ser reconhecido como uma nação independente, o que causou um endividamento significativo.</t>
+        </is>
+      </c>
+      <c r="I974" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J974" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K974" t="inlineStr">
+        <is>
+          <t>8a_ph10_his_03.jpg</t>
+        </is>
+      </c>
+      <c r="L974" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>Disponível em: https://commons.wikimedia.org/wiki/File:Batalla_de_Cerro_Gordo.jpg. Acesso em: 17 dez. 2024.
+Após a independência do México, o país teve que lidar com um conflito retratado na imagem acima, que teve como consequência a</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>perda de metade das terras do país para os Estados Unidos.</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>união política entre México e os estados do sul dos EUA.</t>
+        </is>
+      </c>
+      <c r="D975" t="inlineStr">
+        <is>
+          <t>formação de uma república autônoma no norte do país.</t>
+        </is>
+      </c>
+      <c r="E975" t="inlineStr">
+        <is>
+          <t>abolição da escravidão em todo o território mexicano.</t>
+        </is>
+      </c>
+      <c r="F975" t="inlineStr">
+        <is>
+          <t>expansão mexicana por toda a América do Norte.</t>
+        </is>
+      </c>
+      <c r="G975" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H975" t="inlineStr">
+        <is>
+          <t>Após a Guerra Mexicano-Americana, concluída em 1848 com o Tratado de Guadalupe Hidalgo, o México perdeu aproximadamente metade do seu território para os Estados Unidos, incluindo os atuais estados da Califórnia, Nevada, Utah, Arizona, Novo México, Texas, e partes do Colorado, Wyoming, Kansas e Oklahoma.</t>
+        </is>
+      </c>
+      <c r="I975" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J975" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K975" t="inlineStr">
+        <is>
+          <t>8a_ph10_his_04.jpg</t>
+        </is>
+      </c>
+      <c r="L975" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>O historiador Felipe Pigna concorda que os motivos que terminaram com os negros na Argentina devem ser procurados na utilização da população masculina como “bucha de canhão” nas guerras da Independência, as civis que vieram a seguir e, por último, a ofensiva contra o Paraguai (1865-1871), além das epidemias de cólera (1861) e de febre amarela (1871) que provocaram grande mortandade entre os mais pobres, entre eles os afro-argentinos. “Mas, além disso, a natalidade era muito baixa, inclusive em comparação com outras sociedades latino-americanas. Os amos evitavam a todo custo o casamento de um escravo, assim como a gravidez de uma escrava, com o argumento de que isso a impedia de prestar todos os serviços para os quais foi comprada, além do risco de morrer em um problema no parto”, afirma.
+Disponível em: https://brasil.elpais.com/brasil/2017/01/07/internacional/1483795840_886159.html. Acesso em: 17 dez. 2024.
+Quais foram as políticas adotadas pela elite argentina para reduzir a população negra no século XIX?</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>Expulsão do país como punição pelo apoio à Espanha.</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>Promoção da imigração europeia para trabalhar nas fábricas.</t>
+        </is>
+      </c>
+      <c r="D976" t="inlineStr">
+        <is>
+          <t>Manutenção de boas relações entre as raças visando a miscigenação.</t>
+        </is>
+      </c>
+      <c r="E976" t="inlineStr">
+        <is>
+          <t>Envolvimento dos afro-argentinos como linha de frente em guerras.</t>
+        </is>
+      </c>
+      <c r="F976" t="inlineStr">
+        <is>
+          <t>Concessão de território separado da Argentina exclusivo para negros.</t>
+        </is>
+      </c>
+      <c r="G976" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H976" t="inlineStr">
+        <is>
+          <t>O texto aponta para o uso da população afro-argentina como “bucha de canhão” nas guerras da Independência, nas guerras civis e na ofensiva contra o Paraguai, contribuindo significantemente para a redução da população negra na Argentina do século XIX.</t>
+        </is>
+      </c>
+      <c r="I976" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J976" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K976" t="inlineStr"/>
+      <c r="L976" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>As independências não foram revoluções sociais porque as facções mais fortes das burguesias nativas nunca pretenderam mudar as relações de produção existentes, ou estender os direitos democráticos aos oprimidos, e sim tirar o controle das instituições políticas e militares dos espanhóis.
+Disponível em: https://www.fflch.usp.br/73202. Acesso em: 16 jan. 2025.
+A partir do texto, é correto afirmar que as lutas das independências latino-americanos</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>provocaram a ruptura com a metrópole, mas mantiveram boa parte das estruturas sociais coloniais.</t>
+        </is>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>foram comandadas pelos setores populares, mas fracassaram após serem traídas pelas elites criollas.</t>
+        </is>
+      </c>
+      <c r="D977" t="inlineStr">
+        <is>
+          <t>causaram um fortalecimento da exploração colonial, mas possibilitaram a libertação dos escravizados.</t>
+        </is>
+      </c>
+      <c r="E977" t="inlineStr">
+        <is>
+          <t>foram realizadas por representantes das elites coloniais, mas proporcionaram a igualdade social para toda a população.</t>
+        </is>
+      </c>
+      <c r="F977" t="inlineStr">
+        <is>
+          <t>resultaram na proclamação de diferentes repúblicas, mas que se tornaram monarquias por influência do Império do Brasil.</t>
+        </is>
+      </c>
+      <c r="G977" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H977" t="inlineStr">
+        <is>
+          <t>O texto destaca que as independências na América Latina não foram consideradas revoluções sociais porque as facções mais fortes das burguesias nativas não tinham a intenção de mudar as relações de mudar as estruturas sociais, mas apenas tirar o controle das instituições políticas e militares dos espanhóis. Assim, essas lutas de independência conseguiram romper com a metrópole colonial, mas mantiveram muitas das estruturas sociais e econômicas coloniais inalteradas, perpetuando as desigualdades existentes.</t>
+        </is>
+      </c>
+      <c r="I977" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J977" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K977" t="inlineStr"/>
+      <c r="L977" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>Entre 1878 e 1879, o Exército argentino foi levado aos pampas para, nas palavras do ministro da guerra e futuro presidente, Julio Roca, “expulsar os índios do deserto que se trata de conquistar, para não deixar um só inimigo na retaguarda, submetendo-os pela perseguição ou pela força, sem nos apressar a extirpar o mal pela raiz e destruir esses ninhos de bandoleiros”.
+A chamada “Conquista do Deserto”, como dizem os argentinos brancos, foi essa sequência de operações militares em que os indígenas foram deliberadamente eliminados.
+Disponível em: https://diplomatique.org.br/elites-argentinas-e-os-indigenas/. Acesso em: 16 jan. 2025.
+O texto evidencia que a formação do Estado-nacional argentino, no século XIX, foi marcado pelo(a)</t>
+        </is>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>perseguição e massacre dos povos indígenas.</t>
+        </is>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>coexistência pacífica com as comunidades indígenas.</t>
+        </is>
+      </c>
+      <c r="D978" t="inlineStr">
+        <is>
+          <t>ascensão das lideranças indígenas ao governo do país.</t>
+        </is>
+      </c>
+      <c r="E978" t="inlineStr">
+        <is>
+          <t>aliança entre indígenas e espanhóis contra as elites coloniais.</t>
+        </is>
+      </c>
+      <c r="F978" t="inlineStr">
+        <is>
+          <t>criação de regiões administrativas autônomas para os indígenas.</t>
+        </is>
+      </c>
+      <c r="G978" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H978" t="inlineStr">
+        <is>
+          <t>O texto descreve como, entre 1878 e 1879, o Exército argentino realizou uma série de operações militares nas quais os indígenas foram deliberadamente eliminados através de perseguição ou força. Isso demonstra que a formação do Estado-nacional argentino no século XIX foi marcada pela perseguição e massacre dos povos indígenas.</t>
+        </is>
+      </c>
+      <c r="I978" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J978" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K978" t="inlineStr"/>
+      <c r="L978" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>A maior das repercussões da revolução haitiana ocorreu no continente americano, ao destacar para os milhões de escravizados nas colônias portuguesas, espanholas, francesas e inglesas, além dos EUA que mantinham a escravidão, que os negros eram capazes de lutar por sua liberdade e constituir o primeiro estado livre das Américas.
+Disponível em: https://www.fflch.usp.br/36495#:~:text=Em%2022%20de%20agosto%20de,independ%C3%AAncia%20do%20Haiti%20foi%20proclamada.. Acesso em: 16 jan. 2025.
+A repercussão da Revolução Haitiana, mencionada no excerto, provocou a(o)</t>
+        </is>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>inimizade dos escravizados da América por não se verem representados pelos haitianos.</t>
+        </is>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>paz entre as elites brancas e os negros escravizados nas demais colônias do continente.</t>
+        </is>
+      </c>
+      <c r="D979" t="inlineStr">
+        <is>
+          <t>união das potências coloniais contra os revolucionários e a derrota da Revolução.</t>
+        </is>
+      </c>
+      <c r="E979" t="inlineStr">
+        <is>
+          <t>constante ameaça de intervenção no país por parte das nações europeias.</t>
+        </is>
+      </c>
+      <c r="F979" t="inlineStr">
+        <is>
+          <t>apoio por parte dos europeus à causa abolicionista nas demais colônias.</t>
+        </is>
+      </c>
+      <c r="G979" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H979" t="inlineStr">
+        <is>
+          <t>A Revolução Haitiana, que resultou na independência do Haiti e na abolição da escravidão no país, teve um grande impacto no continente americano e no mundo. O movimento alarmou as potências coloniais europeias que ainda dependiam da escravidão em suas colônias. Como resultado, o Haiti enfrentou uma constante ameaça de intervenção e ataques por parte das nações europeias, que temiam que o exemplo haitiano pudesse inspirar revoltas similares em suas próprias colônias.</t>
+        </is>
+      </c>
+      <c r="I979" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J979" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K979" t="inlineStr"/>
+      <c r="L979" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>O fato é que a história do austríaco Maximiliano de Habsburgo e sua mulher Carlota, no chamado Segundo Império mexicano, foi um episódio trágico da história do México — e um dos mais curiosos da América Latina.
+Primo do imperador brasileiro Dom Pedro 2º, Maximiliano era admirador do Brasil e sonhou com uma aliança regional entre os dois países, o que nunca se materializou. Jovem liberal, sabia pouco da realidade política no país que aceitou governar.
+Disponível em: https://www.bbc.com/portuguese/internacional-59394423. Acesso em: 16 jan. 2025.
+A ascensão de Maximiliano de Habsburgo ao trono do México deve ser compreendido como um(a)</t>
+        </is>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>tentativa de interferência francesa na política mexicana.</t>
+        </is>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>expressão do descontentamento dos mexicanos com a República.</t>
+        </is>
+      </c>
+      <c r="D980" t="inlineStr">
+        <is>
+          <t>manifestação da frustração popular pela falta de representação política.</t>
+        </is>
+      </c>
+      <c r="E980" t="inlineStr">
+        <is>
+          <t>esforço das elites locais para restaurar os vínculos coloniais com a Espanha.</t>
+        </is>
+      </c>
+      <c r="F980" t="inlineStr">
+        <is>
+          <t>sintoma das disputas políticas e territoriais entre o México e os Estados Unidos.</t>
+        </is>
+      </c>
+      <c r="G980" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H980" t="inlineStr">
+        <is>
+          <t>A ascensão de Maximiliano de Habsburgo ao trono do México foi resultado de uma tentativa de interferência francesa na política mexicana. Napoleão III, então imperador da França, aproveitou a instabilidade política no México para expandir a influência francesa no continente americano. Maximiliano, que pouco conhecia a realidade política do México, foi escolhido como imperador do chamado Segundo Império Mexicano. Essa intervenção estrangeira foi amplamente impopular entre os mexicanos, o que resultou na deposição e na execução de Maximiliano e a proclamação de uma República.</t>
+        </is>
+      </c>
+      <c r="I980" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J980" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K980" t="inlineStr"/>
+      <c r="L980" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>Em geral, o que se pode perceber foi que muitos militares que lutaram nas guerras de independência assumiram a autoridade política das regiões libertadas. Aí está a influência direta das guerras de independência para o surgimento desses personagens: foram delas que heróis militares ganharam poder e reconhecimento por parte da população.
+Disponível em: https://abrir.me/qwLkq. Acesso em: 16 jan. 2025.
+O texto descreve o surgimento de uma categoria de indivíduos que se destacou no período pós-independências, conhecidos como</t>
+        </is>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>reis.</t>
+        </is>
+      </c>
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>caudilhos.</t>
+        </is>
+      </c>
+      <c r="D981" t="inlineStr">
+        <is>
+          <t>presidentes.</t>
+        </is>
+      </c>
+      <c r="E981" t="inlineStr">
+        <is>
+          <t>imperadores.</t>
+        </is>
+      </c>
+      <c r="F981" t="inlineStr">
+        <is>
+          <t>libertadores.</t>
+        </is>
+      </c>
+      <c r="G981" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H981" t="inlineStr">
+        <is>
+          <t>Esses indivíduos são conhecidos como caudilhos, líderes que surgiram nas regiões recém-independentes da América Latina e que obtiveram um poder político e militar significativos, muitas vezes governando com autoritarismo e baseando sua autoridade no apoio popular e no controle militar.</t>
+        </is>
+      </c>
+      <c r="I981" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J981" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K981" t="inlineStr"/>
+      <c r="L981" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>Impactos da pandemia na educação no Brasil
+"Foi difícil. Eu trabalho home office e conciliar aula online com o trabalho foi complicado porque não tive apoio do meu esposo, porque ele trabalhou direto na pandemia. Eu tive que adaptar, acordar mais cedo para depois fazer tudo que eu tinha que fazer para entregar no dia e ajudar ela. Agora ela está se desenvolvendo bem, só que não concordo com as aulas online, ao invés de ajudar só prejudicou. O esforço maior foi meu."  (Mulher, Grupo Misto 41 a 60 anos – SP)
+Disponível em: https://www12.senado.leg.br/institucional/datasenado/materias/pesquisas/impactos-da-pandemia-na-educacao-no-brasil. Acesso em 19 de dez. 2024.
+No trecho acima, a palavra "meu" exerce a função de</t>
+        </is>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>verbo.</t>
+        </is>
+      </c>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>sujeito.</t>
+        </is>
+      </c>
+      <c r="D982" t="inlineStr">
+        <is>
+          <t>predicado.</t>
+        </is>
+      </c>
+      <c r="E982" t="inlineStr">
+        <is>
+          <t>adjunto adnominal.</t>
+        </is>
+      </c>
+      <c r="F982" t="inlineStr">
+        <is>
+          <t>complemento nominal.</t>
+        </is>
+      </c>
+      <c r="G982" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H982" t="inlineStr">
+        <is>
+          <t>No trecho "O esforço maior foi meu", a palavra "meu" exerce a função de adjunto adnominal. Um adjunto adnominal é um termo acessório da oração que se junta a um substantivo para caracterizá-lo ou determiná-lo, indicando posse, qualidade, quantidade, entre outras características. No caso específico, "meu" é um pronome possessivo que está qualificando o substantivo "esforço", indicando a quem pertence o esforço. Assim, "meu" está fornecendo uma informação adicional sobre o substantivo "esforço", especificando que o esforço pertence à pessoa que está falando. Essa função de qualificação e determinação do substantivo é exatamente o que define um adjunto adnominal.</t>
+        </is>
+      </c>
+      <c r="I982" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J982" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K982" t="inlineStr"/>
+      <c r="L982" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>Senado proíbe celular em escolas do ensino infantil, fundamental e médio
+Disponível em: https://www12.senado.leg.br/radio/1/noticia/2024/12/18/senado-aprova-proibicao-do-uso-de-celular-e-tablets-por-alunos-do-ensino-infantil-fundamental-e-medio. Acesso em 19 de dez. 2024.
+No título da notícia, exerce a função de adjunto adnominal a palavra:</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>Em</t>
+        </is>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>Senado</t>
+        </is>
+      </c>
+      <c r="D983" t="inlineStr">
+        <is>
+          <t>Proíbe</t>
+        </is>
+      </c>
+      <c r="E983" t="inlineStr">
+        <is>
+          <t>Celular</t>
+        </is>
+      </c>
+      <c r="F983" t="inlineStr">
+        <is>
+          <t>Fundamental</t>
+        </is>
+      </c>
+      <c r="G983" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H983" t="inlineStr">
+        <is>
+          <t>No título "Senado proíbe celular em escolas do ensino infantil, fundamental e médio", a palavra "fundamental" exerce a função de adjunto adnominal porque está qualificando o substantivo "ensino". O adjunto adnominal é um termo acessório da oração que tem a função de caracterizar ou determinar um substantivo, concordando com ele em gênero e número. No caso específico, "fundamental" está especificando o tipo de ensino ao qual a proibição se aplica, assim como "infantil" e "médio". Portanto, "fundamental" está atuando como um adjetivo que complementa o substantivo "ensino", caracterizando-o e, por isso, é considerado um adjunto adnominal.</t>
+        </is>
+      </c>
+      <c r="I983" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J983" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K983" t="inlineStr"/>
+      <c r="L983" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>O dia de 28 de abril é o Dia da Educação. A data é um incentivo para que tenhamos consciência sobre a importância da educação – seja escolar, social ou familiar na vida dos indivíduos. Valores essenciais e convívio saudável se formam com uma boa educação.
+Disponível em: http://mdb-sc.org.br/artigo-de-opiniao-educacao-e-essencial/. Acesso em 19 de dez. 2024.
+No trecho acima, a expressão "da educação" em destaque</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>retoma o sujeito “dia”.</t>
+        </is>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>completa o sentido de um verbo.</t>
+        </is>
+      </c>
+      <c r="D984" t="inlineStr">
+        <is>
+          <t>especifica uma data comemorativa.</t>
+        </is>
+      </c>
+      <c r="E984" t="inlineStr">
+        <is>
+          <t>indica o estado a que se refere o substantivo “dia”.</t>
+        </is>
+      </c>
+      <c r="F984" t="inlineStr">
+        <is>
+          <t>qualifica o substantivo, indicando a qual "dia" se refere.</t>
+        </is>
+      </c>
+      <c r="G984" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H984" t="inlineStr">
+        <is>
+          <t>A expressão "da educação" está qualificando o substantivo "dia", especificando a qual "dia" se refere. No contexto do trecho, "dia" é um substantivo genérico que poderia se referir a qualquer dia do ano. No entanto, ao adicionar a expressão "da educação", o substantivo passa a ser qualificado, indicando que se trata de um dia específico dedicado à educação.</t>
+        </is>
+      </c>
+      <c r="I984" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J984" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K984" t="inlineStr"/>
+      <c r="L984" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>Diante disso, a falta da educação familiar reflete na aprendizagem escolar. É notável a criança que não teve a primeira educação, pois o comportamento na escolar torna-se reflexo dos atos tidos, vividos ou assistidos em casa. Consequentemente, na escola a criança terá dificuldades de convívio e aprendizagem, haja vista que a educação familiar deve ensinar a uma boa educação e a socialização da criança com as outras pessoas.
+Disponível em: https://www.unesc.net/portal/blog/ver/53/38073. Acesso em 19 de dez. 2024.
+No trecho acima, a expressão "da educação familiar"</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>qualifica o substantivo "falta", indicando a sua origem.</t>
+        </is>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>especifica o modo como a "falta" ocorre.</t>
+        </is>
+      </c>
+      <c r="D985" t="inlineStr">
+        <is>
+          <t>completa o sentido de um verbo.</t>
+        </is>
+      </c>
+      <c r="E985" t="inlineStr">
+        <is>
+          <t>indica o estado do sujeito "falta".</t>
+        </is>
+      </c>
+      <c r="F985" t="inlineStr">
+        <is>
+          <t>retoma o sujeito "educação".</t>
+        </is>
+      </c>
+      <c r="G985" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H985" t="inlineStr">
+        <is>
+          <t>A expressão "da educação familiar" funciona como um adjunto adnominal, qualificando e especificando a origem da "falta". No contexto do trecho, a "falta" mencionada refere-se à ausência ou deficiência de educação que deveria ser fornecida pela família, ou seja, proporcionada no ambiente familiar.</t>
+        </is>
+      </c>
+      <c r="I985" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J985" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K985" t="inlineStr"/>
+      <c r="L985" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>Um dos pontos fracos na educação da criança é a dificuldade que os pais encontram em dar limites aos seus filhos. Sem limites, o comportamento da criança muitas vezas deixa a desejar, podendo muitas vezes gritar com seus pais, chegando a agredi-los, quando contrariados ou quando não ganham o que querem. Ou mesmo, sendo mal-educados com os que convivem, ou pessoas mais velhas e nem tendo respeito e boas atitudes com as pessoas em geral.
+Disponível em: https://www.unesc.net/portal/blog/ver/53/38073. Acesso em 19 de dez. 2024.
+Na expressão em destaque, é possível substituir “da criança” sem prejuízo de sentido por</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>"infantil".</t>
+        </is>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>"criancice".</t>
+        </is>
+      </c>
+      <c r="D986" t="inlineStr">
+        <is>
+          <t>"de garotos".</t>
+        </is>
+      </c>
+      <c r="E986" t="inlineStr">
+        <is>
+          <t>"infantilizada".</t>
+        </is>
+      </c>
+      <c r="F986" t="inlineStr">
+        <is>
+          <t>"de pequenos".</t>
+        </is>
+      </c>
+      <c r="G986" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H986" t="inlineStr">
+        <is>
+          <t>A palavra "infantil" funciona como um adjetivo que qualifica algum substantivo relacionado a crianças. No contexto da frase original, "Um dos pontos fracos na educação da criança é a dificuldade que os pais encontram em dar limites aos seus filhos", a expressão "da criança" refere-se à educação que é específica para crianças. Substituir "da criança" por "infantil" mantém o sentido original da frase, pois "educação infantil" é uma expressão comum e amplamente compreendida que se refere ao processo educativo voltado para crianças. As demais alternativas, como "criancice", "de garotos", "infantilizada" e "de pequenos", não se encaixam adequadamente no contexto, pois alteram o sentido ou não são expressões comumente usadas para descrever o tipo de educação mencionado.</t>
+        </is>
+      </c>
+      <c r="I986" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J986" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K986" t="inlineStr"/>
+      <c r="L986" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>Aprenda a chamar a polícia
+Eu tenho o sono muito leve, e numa noite dessas notei que havia alguém andando sorrateiramente no quintal de casa. Levantei em silêncio e fiquei acompanhando os leves ruídos que vinham lá de fora, até ver uma silhueta passando pela janela do banheiro. Como minha casa era muito segura, com grades nas janelas e trancas internas nas portas, não fiquei muito preocupado, mas era claro que eu não ia deixar um ladrão ali, espiando tranquilamente.
+Liguei baixinho para a polícia, informei a situação e o meu endereço.
+Perguntaram-me se o ladrão estava armado ou se já estava no interior da casa. Esclareci que não e disseram-me que não havia nenhuma viatura por perto para ajudar, mas que iriam mandar alguém assim que fosse possível.
+Um minuto depois, liguei de novo e disse com a voz calma:
+— Oi, eu liguei há pouco porque tinha alguém no meu quintal. Não precisa mais ter pressa. Eu já matei o ladrão com um tiro da escopeta calibre 12, que tenho guardada em casa para estas situações. O tiro fez um estrago danado no cara!
+Passados menos de três minutos, estavam na minha rua cinco carros da polícia, um helicóptero, uma unidade do resgate, uma equipe de TV e a turma dos direitos humanos, que não perderiam isso por nada neste mundo.
+Eles prenderam o ladrão em flagrante, que ficava olhando tudo com cara de assombrado. Talvez ele estivesse pensando que aquela era a casa do Comandante da Polícia.
+[...]
+VERÍSSIMO, Luís Fernando. Aprenda a chamar a polícia. Disponível em: &lt;http://www.refletirpararefletir.com.br/4-cronicas-de-luis-fernando-verissimo&gt;.
+Acesso em: 1 jun. 2018.
+No trecho “e a turma dos direitos humanos, que não perderiam isso por nada neste mundo”, o adjunto adnominal destacado é da classe gramatical dos</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>adjetivos.</t>
+        </is>
+      </c>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>advérbios.</t>
+        </is>
+      </c>
+      <c r="D987" t="inlineStr">
+        <is>
+          <t>artigos.</t>
+        </is>
+      </c>
+      <c r="E987" t="inlineStr">
+        <is>
+          <t>numerais.</t>
+        </is>
+      </c>
+      <c r="F987" t="inlineStr">
+        <is>
+          <t>pronomes.</t>
+        </is>
+      </c>
+      <c r="G987" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H987" t="inlineStr">
+        <is>
+          <t>A palavra “neste” é um pronome demonstrativo que, no trecho apresentado, exerce a função de adjunto adnominal do substantivo “mundo”.</t>
+        </is>
+      </c>
+      <c r="I987" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J987" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K987" t="inlineStr"/>
+      <c r="L987" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>O nascimento da crônica
+Há um meio certo de começar a crônica por uma trivialidade. É dizer: Que calor! Que desenfreado calor! Diz-se isto, agitando as pontas do lenço, bufando como um touro, ou simplesmente sacudindo a sobrecasaca. Resvala-se do calor aos fenômenos atmosféricos, fazem-se algumas conjeturas acerca do sol e da lua, outras sobre a febre amarela, manda-se um suspiro a Petrópolis, e La glace est rompue; está começada a crônica.
+[...]
+Não posso dizer positivamente em que ano nasceu a crônica; mas há toda a probabilidade de crer que foi coetânea das primeiras duas vizinhas. Essas vizinhas, entre o jantar e a merenda, sentaram-se à porta, para debicar os sucessos do dia. Provavelmente começaram a lastimar-se do calor. Uma dizia que não pudera comer ao jantar, outra que tinha a camisa mais ensopando que as ervas que comera. Passar das ervas às plantações do morador fronteiro, e logo às tropelias amatórias do dito morador, e ao resto, era a coisa mais fácil, natural e possível do mundo. Eis a origem da crônica.
+Que eu, sabedor ou conjeturador de tão alta prosápia, queira repetir o meio de que lançaram mãos as duas avós do cronista, é realmente cometer uma trivialidade; e contudo, leitor, seria difícil falar desta quinzena sem dar à canícula o lugar de honra que lhe compete. Seria; mas eu dispensarei esse meio quase tão velho como o mundo, para somente dizer que a verdade mais incontestável que achei debaixo do sol é que ninguém se deve queixar, porque cada pessoa é sempre mais feliz do que outra.
+ASSIS, Machado de. O nascimento da crônica. Disponível em: &lt;https://reticenciajornalistica.wordpress.com/2011/11/28/o-nascimento-da-cronica/&gt;.
+Acesso em: 1 jun. 2018.
+O trecho que apresenta um adjetivo exercendo a função de adjunto adnominal é</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>“bufando como um touro”.</t>
+        </is>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>“entre o jantar e a merenda”.</t>
+        </is>
+      </c>
+      <c r="D988" t="inlineStr">
+        <is>
+          <t>“manda-se um suspiro a Petrópolis”.</t>
+        </is>
+      </c>
+      <c r="E988" t="inlineStr">
+        <is>
+          <t>“Eis a origem da crônica”.</t>
+        </is>
+      </c>
+      <c r="F988" t="inlineStr">
+        <is>
+          <t>“Que desenfreado calor!”​.</t>
+        </is>
+      </c>
+      <c r="G988" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H988" t="inlineStr">
+        <is>
+          <t>No trecho “Que desenfreado calor!”, o termo “desenfreado” é um adjetivo que exerce a função de adjunto adnominal do substantivo “calor”.</t>
+        </is>
+      </c>
+      <c r="I988" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J988" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K988" t="inlineStr"/>
+      <c r="L988" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>O nascimento da crônica
+Há um meio certo de começar a crônica por uma trivialidade. É dizer: Que calor! Que desenfreado calor! Diz-se isto, agitando as pontas do lenço, bufando como um touro, ou simplesmente sacudindo a sobrecasaca. Resvala-se do calor aos fenômenos atmosféricos, fazem-se algumas conjeturas acerca do sol e da lua, outras sobre a febre amarela, manda-se um suspiro a Petrópolis, e La glace est rompue; está começada a crônica.
+[...]
+Não posso dizer positivamente em que ano nasceu a crônica; mas há toda a probabilidade de crer que foi coetânea das primeiras duas vizinhas. Essas vizinhas, entre o jantar e a merenda, sentaram-se à porta, para debicar os sucessos do dia. Provavelmente começaram a lastimar-se do calor. Uma dizia que não pudera comer ao jantar, outra que tinha a camisa mais ensopando que as ervas que comera. Passar das ervas às plantações do morador fronteiro, e logo às tropelias amatórias do dito morador, e ao resto, era a coisa mais fácil, natural e possível do mundo. Eis a origem da crônica.
+Que eu, sabedor ou conjeturador de tão alta prosápia, queira repetir o meio de que lançaram mãos as duas avós do cronista, é realmente cometer uma trivialidade; e contudo, leitor, seria difícil falar desta quinzena sem dar à canícula o lugar de honra que lhe compete. Seria; mas eu dispensarei esse meio quase tão velho como o mundo, para somente dizer que a verdade mais incontestável que achei debaixo do sol é que ninguém se deve queixar, porque cada pessoa é sempre mais feliz do que outra.
+ASSIS, Machado de. O nascimento da crônica. Disponível em: &lt;https://reticenciajornalistica.wordpress.com/2011/11/28/o-nascimento-da-cronica/&gt;.
+Acesso em: 1 jun. 2018.
+No trecho “Há um meio certo de começar a crônica por uma trivialidade”, os adjuntos adnominais ligados ao substantivo “meio” são</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>“certo” e “começar”.</t>
+        </is>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>“começar” e “crônica”.</t>
+        </is>
+      </c>
+      <c r="D989" t="inlineStr">
+        <is>
+          <t>“começar” e “uma”.</t>
+        </is>
+      </c>
+      <c r="E989" t="inlineStr">
+        <is>
+          <t>“há” e “certo”.</t>
+        </is>
+      </c>
+      <c r="F989" t="inlineStr">
+        <is>
+          <t>“um” e “certo”.</t>
+        </is>
+      </c>
+      <c r="G989" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H989" t="inlineStr">
+        <is>
+          <t>“Um” e “certo” são adjuntos adnominais do substantivo “meio” e ligam-se a ele para caracterizá-lo.</t>
+        </is>
+      </c>
+      <c r="I989" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J989" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K989" t="inlineStr"/>
+      <c r="L989" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>O nascimento da crônica
+Há um meio certo de começar a crônica por uma trivialidade. É dizer: Que calor! Que desenfreado calor! Diz-se isto, agitando as pontas do lenço, bufando como um touro, ou simplesmente sacudindo a sobrecasaca. Resvala-se do calor aos fenômenos atmosféricos, fazem-se algumas conjeturas acerca do sol e da lua, outras sobre a febre amarela, manda-se um suspiro a Petrópolis, e La glace est rompue; está começada a crônica.
+[...]
+Não posso dizer positivamente em que ano nasceu a crônica; mas há toda a probabilidade de crer que foi coetânea das primeiras duas vizinhas. Essas vizinhas, entre o jantar e a merenda, sentaram-se à porta, para debicar os sucessos do dia. Provavelmente começaram a lastimar-se do calor. Uma dizia que não pudera comer ao jantar, outra que tinha a camisa mais ensopando que as ervas que comera. Passar das ervas às plantações do morador fronteiro, e logo às tropelias amatórias do dito morador, e ao resto, era a coisa mais fácil, natural e possível do mundo. Eis a origem da crônica.
+Que eu, sabedor ou conjeturador de tão alta prosápia, queira repetir o meio de que lançaram mãos as duas avós do cronista, é realmente cometer uma trivialidade; e contudo, leitor, seria difícil falar desta quinzena sem dar à canícula o lugar de honra que lhe compete. Seria; mas eu dispensarei esse meio quase tão velho como o mundo, para somente dizer que a verdade mais incontestável que achei debaixo do sol é que ninguém se deve queixar, porque cada pessoa é sempre mais feliz do que outra.
+ASSIS, Machado de. O nascimento da crônica. Disponível em: &lt;https://reticenciajornalistica.wordpress.com/2011/11/28/o-nascimento-da-cronica/&gt;.
+Acesso em: 1 jun. 2018.
+No trecho “há toda a probabilidade de crer que foi coetânea das primeiras duas vizinhas”, o adjunto adnominal destacado tem a função de</t>
+        </is>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>comprovar a origem da crônica.</t>
+        </is>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>indicar o momento do evento.</t>
+        </is>
+      </c>
+      <c r="D990" t="inlineStr">
+        <is>
+          <t>narrar a amizade das mulheres.</t>
+        </is>
+      </c>
+      <c r="E990" t="inlineStr">
+        <is>
+          <t>quantificar o nome “vizinhas”.</t>
+        </is>
+      </c>
+      <c r="F990" t="inlineStr">
+        <is>
+          <t>situar o substantivo no espaço​.</t>
+        </is>
+      </c>
+      <c r="G990" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H990" t="inlineStr">
+        <is>
+          <t>O adjunto adnominal “duas” pertence à classe dos numerais, sendo usado, aqui, para quantificar o substantivo “vizinhas”.</t>
+        </is>
+      </c>
+      <c r="I990" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J990" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K990" t="inlineStr"/>
+      <c r="L990" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>Os terroristas​
+Era um professor duro, exigente e implacável. As provas eram feitas sem aviso prévio. Todos os trabalhos valiam nota e eram corrigidos segundo os critérios mais rigorosos. Resultado: no fim do ano quase todos os alunos estavam à beira da reprovação. As notas que ele anotava cuidadosamente no livro de chamada eram as mais baixas possíveis. O que fazer?
+Reuniam-se todos os dias no bar em frente ao colégio, para discutir a situação, mas nada lhes ocorria. Até que um deles teve uma ideia brilhante. O livro de chamada. A solução estava ali: tinham de se apossar do livro de chamada e mudar as notas. Um 0 poderia se transformar em 8. Um 1 poderia virar 7 (ou 10, dependendo do grau de ambição).
+O problema era pegar o livro, que o professor não largava nunca, nem mesmo para ir ao banheiro. Aparentemente só uma catástrofe poderia superá-los. Recorreram, pois, à catástrofe. Um dos alunos telefonou do orelhão em frente ao colégio, avisando que havia um princípio de incêndio na casa do professor. Avisado, o pobre homem saiu correndo da sala de aula, deixando sobre a mesa o famigerado livro de presenças.
+Acreditareis se eu disser que ninguém tocou no livro? Ninguém tocou no livro. Os rapazes se olhavam, mas nenhum deles tomou a iniciativa de mudar as notas. Às vezes a consciência pesa mais que a ameaça da reprovação.
+SCLIAR, Moacyr. Os terroristas. Disponível em: &lt;http://jornadapadremarzano.blogspot.com.br/2017/08/os-terroristas-moacyr-scliar.html&gt;. Acesso em: 1 jun. 2018.
+No trecho “Todos os trabalhos valiam nota e eram corrigidos segundo os critérios mais rigorosos”, o termo “rigorosos” concorda em gênero e número com</t>
+        </is>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>"corrigidos".</t>
+        </is>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>"critérios".</t>
+        </is>
+      </c>
+      <c r="D991" t="inlineStr">
+        <is>
+          <t>"mais".</t>
+        </is>
+      </c>
+      <c r="E991" t="inlineStr">
+        <is>
+          <t>"todos".</t>
+        </is>
+      </c>
+      <c r="F991" t="inlineStr">
+        <is>
+          <t>"trabalhos".</t>
+        </is>
+      </c>
+      <c r="G991" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H991" t="inlineStr">
+        <is>
+          <t>No trecho, o termo “rigorosos” é adjunto adnominal de “critérios”, concordando com ele em gênero e número.</t>
+        </is>
+      </c>
+      <c r="I991" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J991" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K991" t="inlineStr"/>
+      <c r="L991" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>Uma pastelaria vende dois tipos de pastéis: pastéis simples e pastéis especiais. No final do dia, o caixa registrou um total de 120 pastéis vendidos, sendo que a quantidade de pastéis simples foi o dobro da quantidade de pastéis especiais.
+Quantos pastéis especiais foram vendidos ao longo do dia?</t>
+        </is>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D992" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E992" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="F992" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="G992" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H992" t="inlineStr">
+        <is>
+          <t>Seja x a quantidade de pastéis simples vendidos e y a quantidade de pastéis especiais vendidos. Do enunciado sabe-se que o total de pastéis vendidos foi 120: x + y = 120.
+A quantidade de pastéis simples é o dobro da quantidade de pastéis especiais: x = 2y. Logo,  Portanto, foram 40 pastéis especiais vendidos.</t>
+        </is>
+      </c>
+      <c r="I992" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J992" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K992" t="inlineStr"/>
+      <c r="L992" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>Um vendedor de frutas vende maçãs e laranjas. Ele vendeu 3 vezes mais maçãs do que laranjas.
+Se ele vendeu um total de 40 frutas, quantas laranjas ele vendeu?</t>
+        </is>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D993" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E993" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F993" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="G993" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H993" t="inlineStr">
+        <is>
+          <t>Vamos representar a quantidade de maçãs por x e a quantidade de laranjas por y. Temos o sistema de equações:
+Substituindo x na segunda equação, temos:
+Portanto, ele vendeu 10 laranjas.</t>
+        </is>
+      </c>
+      <c r="I993" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J993" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K993" t="inlineStr"/>
+      <c r="L993" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>Um restaurante vende dois tipos de pratos: prato A e prato B. O prato A custa R$ 15,00 e o prato B custa R$ 20,00. Em um dia, o restaurante vendeu um total de 50 pratos e arrecadou R$ 850,00.
+Quantos pratos do tipo A foram vendidos?</t>
+        </is>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D994" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E994" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F994" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G994" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H994" t="inlineStr">
+        <is>
+          <t>Vamos representar a quantidade de pratos A por x e a quantidade de pratos B por y. Temos o sistema de equações: 
+Multiplicando a primeira equação por 15.
+Subtraindo a primeira equação da segunda:
+Substituindo y na primeira equação:
+Portanto, foram vendidos 30 pratos do tipo A.</t>
+        </is>
+      </c>
+      <c r="I994" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J994" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K994" t="inlineStr"/>
+      <c r="L994" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>Em um mercadinho o preço de 2 pacotes de arroz e feijão. O preço de 2 pacotes de arroz e 3 pacotes de feijão é R$ 45,00. Já o preço de 4 pacotes de arroz e 2 pacotes de feijão é R$ 60,00
+Quanto custa um pacote de arroz?</t>
+        </is>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>R$ 5,00</t>
+        </is>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>R$ 7,50</t>
+        </is>
+      </c>
+      <c r="D995" t="inlineStr">
+        <is>
+          <t>R$ 10,00</t>
+        </is>
+      </c>
+      <c r="E995" t="inlineStr">
+        <is>
+          <t>R$ 11,25</t>
+        </is>
+      </c>
+      <c r="F995" t="inlineStr">
+        <is>
+          <t>R$ 15,00</t>
+        </is>
+      </c>
+      <c r="G995" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H995" t="inlineStr">
+        <is>
+          <t>Seja x o preço do pacote de arroz e y o preço do pacote de feijão. O problema pode ser modelado pelo seguinte sistema de equações:
+Simplificando e somando as equações, tem-se:
+Este é o preço de um pacote de feijão (R$ 7,50). Substituindo este valor em , obtém-se:
+Portanto, o preço de um pacote de arroz é R$ 11,25.</t>
+        </is>
+      </c>
+      <c r="I995" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J995" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K995" t="inlineStr"/>
+      <c r="L995" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>Um mecânico trabalha com dois tipos de serviços: troca de óleo e alinhamento. Ele realizou 5 trocas de óleo e 3 alinhamentos em um dia, e recebeu um total de R$ 200,00. No dia seguinte, ele realizou 2 trocas de óleo e 4 alinhamentos, recebendo um total de R$ 160,00.
+Quanto ele cobra por cada troca de óleo?</t>
+        </is>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>R$ 40,00</t>
+        </is>
+      </c>
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>R$ 28,57</t>
+        </is>
+      </c>
+      <c r="D996" t="inlineStr">
+        <is>
+          <t>R$ 24,00</t>
+        </is>
+      </c>
+      <c r="E996" t="inlineStr">
+        <is>
+          <t>R$ 22,86</t>
+        </is>
+      </c>
+      <c r="F996" t="inlineStr">
+        <is>
+          <t>R$ 13,34</t>
+        </is>
+      </c>
+      <c r="G996" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H996" t="inlineStr">
+        <is>
+          <t>Vamos representar o valor da troca de óleo por x e o valor do alinhamento por y. Temos o sistema de equações:
+Simplificando e isolando o x na segunda equação, temos:
+Substituindo x na primeira equação:
+5(80 – 2y) + 3y = 200
+400 – 10y + 3y = 200 
+400 – 7y = - 200 
+y = 28.57
+Agora, substituindo y na equação x = 80 – 2y:
+x = 80 – 2(28.57) = 80 – 57,14 = 22,86.
+Portanto, o mecânico cobra aproximadamente R$ 22,86 por troca de óleo.</t>
+        </is>
+      </c>
+      <c r="I996" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J996" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K996" t="inlineStr"/>
+      <c r="L996" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>Um clube promoveu uma festa para arrecadar fundos para uma instituição de caridade. As pessoas que eram sócias do clube pagaram R$ 20,00 de entrada e as pessoas que não eram sócias do clube pagaram R$ 35,00. Se o clube vendeu 310 ingressos e arrecadou R$ 8 450,00 com a venda dos ingressos, quantas pessoas não associadas ao clube participaram da festa?</t>
+        </is>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>150.</t>
+        </is>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>160.</t>
+        </is>
+      </c>
+      <c r="D997" t="inlineStr">
+        <is>
+          <t>170.</t>
+        </is>
+      </c>
+      <c r="E997" t="inlineStr">
+        <is>
+          <t>180.</t>
+        </is>
+      </c>
+      <c r="F997" t="inlineStr">
+        <is>
+          <t>190.</t>
+        </is>
+      </c>
+      <c r="G997" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H997" t="inlineStr">
+        <is>
+          <t>Considere x o total de pessoas associadas e y as pessoas que não são sócias do clube. Assim, temos:
+Portanto, 150 pessoas que não são sócias do clube participaram da festa.</t>
+        </is>
+      </c>
+      <c r="I997" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J997" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K997" t="inlineStr"/>
+      <c r="L997" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>Considere o sistema abaixo.
+Qual é o valor da expressão x + y?</t>
+        </is>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>[img:8a_ph10_mat_07_a.png]</t>
+        </is>
+      </c>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>[img:8a_ph10_mat_07_b.png]</t>
+        </is>
+      </c>
+      <c r="D998" t="inlineStr">
+        <is>
+          <t>[img:8a_ph10_mat_07_c.png]</t>
+        </is>
+      </c>
+      <c r="E998" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F998" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G998" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H998" t="inlineStr">
+        <is>
+          <t>Condição de existência:
+Resolvendo o sistema temos:
+Os valores encontrados para x e y são diferentes de 0, logo eles são válidos.</t>
+        </is>
+      </c>
+      <c r="I998" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J998" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K998" t="inlineStr">
+        <is>
+          <t>8a_ph10_mat_07.png</t>
+        </is>
+      </c>
+      <c r="L998" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>Considere o sistema abaixo, com a ≠ 0 e b ≠ 0.
+Sobre a solução desse sistema, é verdade que</t>
+        </is>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>a e b são números primos.</t>
+        </is>
+      </c>
+      <c r="C999" t="inlineStr">
+        <is>
+          <t>b &lt; a.</t>
+        </is>
+      </c>
+      <c r="D999" t="inlineStr">
+        <is>
+          <t>a e b são números pares.</t>
+        </is>
+      </c>
+      <c r="E999" t="inlineStr">
+        <is>
+          <t>a é um número par e b não é primo.</t>
+        </is>
+      </c>
+      <c r="F999" t="inlineStr">
+        <is>
+          <t>a é um número ímpar e b não é primo.</t>
+        </is>
+      </c>
+      <c r="G999" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H999" t="inlineStr">
+        <is>
+          <t>Subtraindo (I) de (II):
+Substituindo o valor de b em (II):
+Portanto, a e b são números primos.</t>
+        </is>
+      </c>
+      <c r="I999" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J999" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K999" t="inlineStr">
+        <is>
+          <t>8a_ph10_mat_08.png</t>
+        </is>
+      </c>
+      <c r="L999" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>Em um jogo de certo ou errado, para cada pergunta respondida corretamente o candidato ganhava 2 pontos e, caso ele errasse a resposta, perdia 3 pontos. Otávio participou desse jogo e marcou 12 pontos.
+Se foram feitas a ele 11 perguntas, qual dos sistemas abaixo calcularia o número de perguntas respondidas corretamente por Otávio?</t>
+        </is>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>[img:8a_ph10_mat_09_a.png]</t>
+        </is>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>[img:8a_ph10_mat_09_b.png]</t>
+        </is>
+      </c>
+      <c r="D1000" t="inlineStr">
+        <is>
+          <t>[img:8a_ph10_mat_09_c.png]</t>
+        </is>
+      </c>
+      <c r="E1000" t="inlineStr">
+        <is>
+          <t>[img:8a_ph10_mat_09_d.png]</t>
+        </is>
+      </c>
+      <c r="F1000" t="inlineStr">
+        <is>
+          <t>[img:8a_ph10_mat_09_e.png]</t>
+        </is>
+      </c>
+      <c r="G1000" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H1000" t="inlineStr">
+        <is>
+          <t>Seja x o total de perguntas respondidas corretamente e y o total de perguntas respondidas erradas. Do enunciado, temos:</t>
+        </is>
+      </c>
+      <c r="I1000" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J1000" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K1000" t="inlineStr"/>
+      <c r="L1000" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>Em um jogo de certo ou errado, para cada pergunta respondida corretamente o candidato ganhava 2 pontos e, caso ele errasse a resposta, perdia 3 pontos. Otávio participou desse jogo e marcou 12 pontos.
+Sabendo que Otávio respondeu 11 perguntas, quantas destas Otávio acertou?</t>
+        </is>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D1001" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E1001" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F1001" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G1001" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H1001" t="inlineStr">
+        <is>
+          <t>Sejam x e y as quantidades de respostas certas e erradas, respectivamente.
+Portanto, 9 perguntas foram respondidas corretamente.</t>
+        </is>
+      </c>
+      <c r="I1001" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J1001" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K1001" t="inlineStr"/>
+      <c r="L1001" t="inlineStr">
+        <is>
+          <t>8ano</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/questoes.xlsx
+++ b/questoes.xlsx
@@ -51355,40 +51355,45 @@
     <row r="902">
       <c r="A902" t="inlineStr">
         <is>
-          <t>Com a queda de temperatura, normalmente as pessoas tendem a ficar mais tempo em locais fechados, o que ajuda a proliferar doenças respiratórias, uma vez que o vírus influenza tem alta transmissibilidade por espirro e tosse, além do contato direto das mãos e objetos comuns como corrimões e maçanetas.
-Disponível em: http://saude.sp.gov.br/coordenadoria-de-controle-de-doencas/noticias/23032024-gripe-resfriado-pneumonia-covid-19-virose-saiba-identificar-as-doencas-no-outono. Acesso em: 16 jan. 2025.
-Uma forma de prevenir a doença causada por esse vírus é</t>
+          <t>A etiqueta de eficiência energética do INMETRO classifica os eletrodomésticos em diferentes categorias de acordo com sua eficiência. Suponha que um refrigerador de classe A consuma 30% menos energia do que um de classe B.
+Se um refrigerador de classe B consome 500 kWh por ano, quanto consome um refrigerador de classe A?</t>
         </is>
       </c>
       <c r="B902" t="inlineStr">
         <is>
-          <t>tomar regularmente antibióticos e antivirais.</t>
+          <t>350 kWh.</t>
         </is>
       </c>
       <c r="C902" t="inlineStr">
         <is>
-          <t>higienizar as mãos apenas com álcool em gel.</t>
+          <t>400 kWh.</t>
         </is>
       </c>
       <c r="D902" t="inlineStr">
         <is>
-          <t>praticar atividades físicas ao ar livre regularmente.</t>
+          <t>450 kWh.</t>
         </is>
       </c>
       <c r="E902" t="inlineStr">
         <is>
-          <t>evitar aglomerações e ambientes fechados em estações frias.</t>
-        </is>
-      </c>
-      <c r="F902" t="inlineStr"/>
+          <t>500 kWh.</t>
+        </is>
+      </c>
+      <c r="F902" t="inlineStr">
+        <is>
+          <t>550 kWh.</t>
+        </is>
+      </c>
       <c r="G902" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H902" t="inlineStr">
         <is>
-          <t>Evitar aglomerações e ambientes fechados é uma medida eficaz para reduzir a exposição ao vírus influenza, que se transmite facilmente em locais com grande concentração de pessoas e pouca ventilação.</t>
+          <t>De acordo com o cálculo, o refrigerador de classe A consome 350 kWh.
+Cálculo de 30% do consumo do refrigerador de classe B:
+Subtrair esse valor do consumo do refrigerador de classe B para encontrar o consumo do refrigerador de classe A:</t>
         </is>
       </c>
       <c r="I902" t="inlineStr">
@@ -51404,46 +51409,55 @@
       <c r="K902" t="inlineStr"/>
       <c r="L902" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="903">
       <c r="A903" t="inlineStr">
         <is>
-          <t>O tétano é uma doença causada pela bactéria Clostridium tetani, que pode entrar no corpo humano através de ferimentos contaminados. A doença causa contrações musculares dolorosas e pode ser fatal se não tratada.
-Qual das seguintes alternativas é uma medida eficaz para prevenir essa doença?</t>
+          <t>Um aparelho elétrico tem uma potência nominal de 1500 W e é utilizado por 2 horas.
+Qual é o consumo de energia elétrica desse aparelho?</t>
         </is>
       </c>
       <c r="B903" t="inlineStr">
         <is>
-          <t>Manter a vacinação em dia.</t>
+          <t>1,5 kWh.</t>
         </is>
       </c>
       <c r="C903" t="inlineStr">
         <is>
-          <t>Tomar analgésicos regularmente.</t>
+          <t>2 kWh.</t>
         </is>
       </c>
       <c r="D903" t="inlineStr">
         <is>
-          <t>Consumir alimentos ricos em cálcio.</t>
+          <t>2,5 kWh.</t>
         </is>
       </c>
       <c r="E903" t="inlineStr">
         <is>
-          <t>Evitar contato com pessoas infectadas.</t>
-        </is>
-      </c>
-      <c r="F903" t="inlineStr"/>
+          <t>3 kWh.</t>
+        </is>
+      </c>
+      <c r="F903" t="inlineStr">
+        <is>
+          <t>3,5 kWh.</t>
+        </is>
+      </c>
       <c r="G903" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="H903" t="inlineStr">
         <is>
-          <t>Manter a vacinação em dia é uma medida eficaz para prevenir o tétano, pois a vacina protege contra a toxina produzida pela bactéria Clostridium tetani.</t>
+          <t>Para resolver o problema de consumo de energia elétrica, precisamos usar a fórmula:
+E é o consumo de energia em quilowatt-hora (kWh),
+P é a potência em quilowatts (kW),
+t é o tempo em horas (h).
+Converter a potência de Watts para Quilowatts:
+Calcular o consumo de energia:</t>
         </is>
       </c>
       <c r="I903" t="inlineStr">
@@ -51459,48 +51473,54 @@
       <c r="K903" t="inlineStr"/>
       <c r="L903" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="904">
       <c r="A904" t="inlineStr">
         <is>
-          <t>“A Aids era uma doença variada, e uniformemente fatal”, definiu Drauzio Varella num episódio recente de seu (ótimo) podcast, o Outras Histórias. “À medida que a imunidade ia caindo”, ele segue, “repetiam-se as infecções oportunistas: pneumonias, meningites, lesões cerebrais por toxoplasmose… Você tratava uma infecção e vinha outra, depois outra. Uma hora o doente estava tão debilitado não sobrevivia”.
-Drauzio usa o tempo verbal no passado por um motivo óbvio: Aids sem tratamento é uma página virada no Brasil. Começou há 30 anos, em 1991. Foi quando teve início a compra e a distribuição gratuita de remédios contra o HIV pelo SUS.
-Disponível em: https://super.abril.com.br/coluna/alexandre-versignassi/ha-30-anos-o-brasil-comecava-sua-revolucao-contra-a-aids/. Acesso em: 15 jan. 2025.
-Sobre a prevenção e o tratamento da AIDS, pode-se afirmar corretamente que</t>
+          <t>Um eletrodoméstico está conectado a uma tomada cuja a tensão (U) é de 220V em um circuito que a corrente elétrica que flui por esse aparelho é de 5A.
+Qual é a potência (P) do circuito?</t>
         </is>
       </c>
       <c r="B904" t="inlineStr">
         <is>
-          <t>o uso consistente de preservativos é a única forma eficaz de prevenir a transmissão do HIV.</t>
+          <t>550 w.</t>
         </is>
       </c>
       <c r="C904" t="inlineStr">
         <is>
-          <t>a descoberta dos remédios contra o HIV tornou a AIDS uma doença completamente controlável.</t>
+          <t>1100 W.</t>
         </is>
       </c>
       <c r="D904" t="inlineStr">
         <is>
-          <t>pessoas infectadas pelo HIV não devem ter filhos, pois a doença é transmitida geneticamente para os descendentes.</t>
+          <t>1320 W.</t>
         </is>
       </c>
       <c r="E904" t="inlineStr">
         <is>
-          <t>o tratamento antirretroviral pode permitir que pessoas com HIV tenham vidas saudáveis, mas não elimina completamente o vírus do organismo.</t>
-        </is>
-      </c>
-      <c r="F904" t="inlineStr"/>
+          <t>1400 W.</t>
+        </is>
+      </c>
+      <c r="F904" t="inlineStr">
+        <is>
+          <t>2200 W.</t>
+        </is>
+      </c>
       <c r="G904" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H904" t="inlineStr">
         <is>
-          <t>O tratamento antirretroviral (TAR) permite que pessoas vivendo com HIV mantenham uma carga viral indetectável, o que melhora significativamente a qualidade de vida e a expectativa de vida. No entanto, o TAR não elimina completamente o vírus do organismo, exigindo tratamento contínuo.</t>
+          <t>Para resolver essa questão, vamos utilizar a fórmula da potência elétrica:
+Onde:
+P é a potência em watts (W)
+U é a tensão em volts (V) = 220 V
+i é a corrente em amperes (A) = 5 A</t>
         </is>
       </c>
       <c r="I904" t="inlineStr">
@@ -51516,47 +51536,57 @@
       <c r="K904" t="inlineStr"/>
       <c r="L904" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="905">
       <c r="A905" t="inlineStr">
         <is>
-          <t>A tuberculose é uma doença infecciosa e transmissível, causada pela bactéria Mycobacterium tuberculosis, também conhecida como bacilo de Koch. A doença afeta prioritariamente os pulmões (forma pulmonar), embora possa acometer outros órgãos e/ou sistemas. [...] O tratamento da tuberculose dura no mínimo seis meses, é gratuito e está disponível no Sistema Único de Saúde (SUS). A tuberculose tem cura quando o tratamento é feito de forma adequada, até o final.
-Disponível em: https://www.gov.br/saude/pt-br/assuntos/saude-de-a-a-z/t/tuberculose#:~:text=A%20tuberculose%20%C3%A9%20uma%20doen%C3%A7a,outros%20%C3%B3rg%C3%A3os%20e%2Fou%20sistemas. Acesso em: 14 jan. 2025.
-Qual das seguintes alternativas descreve a importância de seguir o tratamento completo dessa doença?</t>
+          <t>Uma residência possui os seguintes eletrodomésticos:
+1 geladeira que consome 30 kWh por mês
+1 máquina de lavar que consome 20 kWh por mês
+1 ar-condicionado que consome 50 kWh por mês
+5 lâmpadas que consomem 5 kWh cada por mês
+Se o valor do kWh é de R$ 0,60, qual será o valor total da conta de energia elétrica dessa residência no final do mês?</t>
         </is>
       </c>
       <c r="B905" t="inlineStr">
         <is>
-          <t>Minimizar os efeitos colaterais dos antibióticos usados no tratamento.</t>
+          <t>R$ 60,00.</t>
         </is>
       </c>
       <c r="C905" t="inlineStr">
         <is>
-          <t>Reduzir a necessidade de campanhas de vacinação futuras contra a tuberculose.</t>
+          <t>R$ 75,00.</t>
         </is>
       </c>
       <c r="D905" t="inlineStr">
         <is>
-          <t>Garantir que a bactéria seja completamente eliminada e prevenir a resistência bacteriana.</t>
+          <t>R$ 84,00.</t>
         </is>
       </c>
       <c r="E905" t="inlineStr">
         <is>
-          <t>Evitar que a pessoa fique doente novamente no futuro sendo não transmissível após o início do tratamento.</t>
-        </is>
-      </c>
-      <c r="F905" t="inlineStr"/>
+          <t>R$ 96,00.</t>
+        </is>
+      </c>
+      <c r="F905" t="inlineStr">
+        <is>
+          <t>R$ 108,00.</t>
+        </is>
+      </c>
       <c r="G905" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H905" t="inlineStr">
         <is>
-          <t>Seguir o tratamento completo da tuberculose é crucial para garantir que a bactéria Mycobacterium tuberculosis seja completamente eliminada do organismo e para prevenir o desenvolvimento de resistência bacteriana. A adesão ao tratamento ajuda a evitar recaídas e a propagação de cepas resistentes da bactéria.</t>
+          <t>O consumo total das lâmpadas é:
+Todos os consumos: 
+Cálculo do valor total da conta de energia elétrica
+Sabendo que o valor de kWh é de R$ 0,60. Então, o valor total da conta de energia elétrica será:</t>
         </is>
       </c>
       <c r="I905" t="inlineStr">
@@ -51572,46 +51602,51 @@
       <c r="K905" t="inlineStr"/>
       <c r="L905" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="906">
       <c r="A906" t="inlineStr">
         <is>
-          <t>As bactérias e os vírus são microrganismos que podem causar doenças nos seres humanos, as bacterioses e as viroses. Embora ambos sejam agentes infecciosos, apresentam características e mecanismos de ação distintos. As bactérias são organismos unicelulares procariontes, capazes de se reproduzir por conta própria. Já os vírus são partículas infecciosas menores e mais simples, constituídas por material genético envolto por uma cápsula proteica.
-Qual a diferença entre as doenças causadas por esses microrganismos?</t>
+          <t>[...] Lâmpadas LED com eficiência 10 vezes maior que uma lâmpada convencional estão hoje na iluminação doméstica e comercial, em faróis de automóveis, luzes de jardim, lanternas de bolso, etc. A iluminação LED branco pode ser usada não só para diminuir o consumo de energia, mas também para poupar recursos energéticos. Por exemplo, só nos EUA, calcula-se que, até 2020, a iluminação à base de LED branco evitará a construção de 133 usinas. [...]
+Ciência Hoje. Disponível em: &lt; https: acervo="" ch="" ch_321.pdf="" cienciahoje.periodicos.capes.gov.br="" storage=""&gt; Acesso em: 15 jan. 2025.
+Qual é a principal razão para a adoção de lâmpadas LED, conforme discutido no texto?</t>
         </is>
       </c>
       <c r="B906" t="inlineStr">
         <is>
-          <t>Ambas são causadas pelos mesmos agentes infecciosos e apresentam sintomas idênticos.</t>
+          <t>Aumento do consumo de energia.</t>
         </is>
       </c>
       <c r="C906" t="inlineStr">
         <is>
-          <t>Viroses podem ser tratadas com antibióticos, enquanto bacterioses requerem apenas repouso e hidratação.</t>
+          <t>Redução do consumo de energia.</t>
         </is>
       </c>
       <c r="D906" t="inlineStr">
         <is>
-          <t>As bacterioses podem ser tratadas com antibióticos, enquanto viroses não respondem a esse tipo de tratamento.</t>
+          <t>Aumento da produção de energia.</t>
         </is>
       </c>
       <c r="E906" t="inlineStr">
         <is>
-          <t>As bacterioses, são causadas por organismos maiores e mais complexos, tendo um período de incubação mais longo do que as viroses.</t>
-        </is>
-      </c>
-      <c r="F906" t="inlineStr"/>
+          <t>Redução dos custos de produção de energia.</t>
+        </is>
+      </c>
+      <c r="F906" t="inlineStr">
+        <is>
+          <t>Aumento da eficiência das usinas de energia.</t>
+        </is>
+      </c>
       <c r="G906" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H906" t="inlineStr">
         <is>
-          <t>As bacterioses são causadas por bactérias e podem ser tratadas com antibióticos, que são eficazes em eliminar ou inibir o crescimento das bactérias. Viroses, por outro lado, são causadas por vírus e não respondem aos antibióticos. O tratamento das viroses geralmente foca em aliviar os sintomas enquanto o sistema imunológico combate o vírus.</t>
+          <t>O texto destaca que a iluminação LED branco pode ser usada para diminuir o consumo de energia. Além disso, menciona que a eficiência das lâmpadas LED é 10 vezes maior que a das lâmpadas convencionais, o que contribui para a redução do consumo energético.</t>
         </is>
       </c>
       <c r="I906" t="inlineStr">
@@ -51627,45 +51662,52 @@
       <c r="K906" t="inlineStr"/>
       <c r="L906" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="907">
       <c r="A907" t="inlineStr">
         <is>
-          <t>De acordo com as características dos vírus que foram descobertas a partir da década de 30, podemos dizer que:</t>
+          <t>Pensando em comprar um ferro elétrico, um advogado depara-se na loja com modelos das marcas A e B, cujos dados são:
+marca A: 220 V – 1 500 W
+marca B: 115 V – 1 300 W
+Se a tensão elétrica fornecida nas tomadas da sua residência é de 110 V, qual a melhor opção para este advogado?</t>
         </is>
       </c>
       <c r="B907" t="inlineStr">
         <is>
-          <t>os vírus são seres acelulares e só conseguem se reproduzir no interior de uma célula viva.</t>
+          <t>O advogado deve escolher o ferro elétrico B, pois o valor da tensão do produto é compatível com a rede elétrica e ele apresentará uma potência menor do que a A, quando ligado ambos em 110V.</t>
         </is>
       </c>
       <c r="C907" t="inlineStr">
         <is>
-          <t>os vírus são seres que possuem apenas um formato determinado e, por isso, conseguem infectar qualquer ser vivo.</t>
+          <t>O advogado não deve comprar nenhum deles, uma vez que ambos queimarão ao serem ligados, pois os valores das tensões dadas pelos fabricantes são maiores que 110 V.</t>
         </is>
       </c>
       <c r="D907" t="inlineStr">
         <is>
-          <t>os vírus possuem metabolismo próprio, pois conseguem sobreviver em qualquer ambiente, mesmo sendo acelulares.</t>
+          <t>O advogado deve escolher o ferro elétrico A, pois o valor da tensão do produto é maior do que a do ferro B, causando maior aquecimento.</t>
         </is>
       </c>
       <c r="E907" t="inlineStr">
         <is>
-          <t>os vírus são seres microscópicos com apenas uma célula, porém, não possuem capacidade de se reproduzirem sozinhos.</t>
-        </is>
-      </c>
-      <c r="F907" t="inlineStr"/>
+          <t>O advogado deve escolher o ferro elétrico B, pois o valor da tensão do produto é compatível com a rede elétrica da sua casa e ele apresentará uma potência maior do que a A, quando ligado ambos em 110V.</t>
+        </is>
+      </c>
+      <c r="F907" t="inlineStr">
+        <is>
+          <t>O advogado deve escolher o ferro elétrico A, pois o valor da tensão do produto é compatível com a rede elétrica e ele apresentará uma potência maior do que a B, quando ligado ambos em 110V.</t>
+        </is>
+      </c>
       <c r="G907" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="H907" t="inlineStr">
         <is>
-          <t>Os vírus não são constituídos por células sendo, portanto, considerados acelulares. A reprodução deles é obrigatoriamente realizada dentro da célula de um outro ser vivo. Também não apresentam metabolismo próprio, precisando utilizar o metabolismo da célula hospedeira.</t>
+          <t>O advogado deve escolher o ferro cujo valor da tensão do produto é compatível com a rede elétrica a que sua residência está ligada. Como essa tensão é de 110 V, ele deve escolher o ferro B, cuja tensão dada é de 115 V. Não faz sentido comprar um ferro construído para funcionar em 220 V e ligá-lo em 110 V. Ele não queima, mas certamente tem um funcionamento inadequado.</t>
         </is>
       </c>
       <c r="I907" t="inlineStr">
@@ -51681,45 +51723,52 @@
       <c r="K907" t="inlineStr"/>
       <c r="L907" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="908">
       <c r="A908" t="inlineStr">
         <is>
-          <t>Entre as doenças virais, a dengue continua tendo grande número de casos no Brasil. Como forma de prevenção à doença, a população pode adotar medidas simples como: não deixar água parada e utilizar repelentes. Sobre a transmissão da dengue pode-se afirmar corretamente que:</t>
+          <t>Duas geladeiras possuem a mesma potência, porém uma deve ser ligada no 110 V e outra em uma tomada de 220 V.
+Considerando que elas são mantidas ligadas o tempo todo, qual grandeza física elas terão de diferente, além da tensão?</t>
         </is>
       </c>
       <c r="B908" t="inlineStr">
         <is>
-          <t>o vírus da dengue é transmitido pelo mosquito Anopheles.</t>
+          <t>Corrente</t>
         </is>
       </c>
       <c r="C908" t="inlineStr">
         <is>
-          <t>somente o macho do mosquito Aedes aegypti ​causa a dengue.</t>
+          <t>Energia</t>
         </is>
       </c>
       <c r="D908" t="inlineStr">
         <is>
-          <t>o vírus da dengue é transmitido por fêmeas do mosquito Aedes aegypti, portadoras do vírus.</t>
+          <t>Tempo</t>
         </is>
       </c>
       <c r="E908" t="inlineStr">
         <is>
-          <t>o vírus causador da dengue é transmitido pela picada de machos e fêmeas do mosquito Aedes aegypti.</t>
-        </is>
-      </c>
-      <c r="F908" t="inlineStr"/>
+          <t>Força</t>
+        </is>
+      </c>
+      <c r="F908" t="inlineStr">
+        <is>
+          <t>Potência</t>
+        </is>
+      </c>
       <c r="G908" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H908" t="inlineStr">
         <is>
-          <t>A transmissão da dengue ocorre apenas com a picada da fêmea do mosquito Aedes aegypti, portadora do vírus.</t>
+          <t>Temos que a geladeira ligada na tensão 110 V tem potência:
+Para a geladeira ligada na tensão 220 V:
+Logo temos que a corrente da geladeira ligada na tensão 110 V é o dobro da geladeira ligada na tensão de 220 V, e portanto as correntes serão diferentes.</t>
         </is>
       </c>
       <c r="I908" t="inlineStr">
@@ -51735,46 +51784,56 @@
       <c r="K908" t="inlineStr"/>
       <c r="L908" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="909">
       <c r="A909" t="inlineStr">
         <is>
-          <t>A leptospirose é uma doença infecciosa onde ocorre uma febre aguda, dor de cabeça e dores pelo corpo, sua penetração sucede através do contato com mucosas, pele com ou sem lesões, mas imersa por longos períodos em água contaminada.
-A leptospirose é uma doença que se alastra em situações de enchente porque, nesses casos, aumenta a:</t>
+          <t>A geração de energia elétrica causa diversos impactos ao meio ambiente, dependendo daforma com que ela é gerada. Assim, reduzir o consumo de energia elétrica é uma forma de reduzir os danos causados à natureza.
+Como a energia elétrica consumida depende da potência dos aparelhos e de seu tempo de uso, marque a alternativa que representa o maior gasto energético:</t>
         </is>
       </c>
       <c r="B909" t="inlineStr">
         <is>
-          <t>presença de caramujos que transmite a doença.</t>
+          <t>Secador de cabelos – 1500 W, ligado durante 30 minutos.</t>
         </is>
       </c>
       <c r="C909" t="inlineStr">
         <is>
-          <t>proliferação de insetos que transmite a doença.</t>
+          <t>Três lâmpadas incandescentes – 60 W cada, ligadas durante 1 h.</t>
         </is>
       </c>
       <c r="D909" t="inlineStr">
         <is>
-          <t>contaminação do ar pela bactéria que causa a doença.</t>
+          <t>Ar-condicionado – 1 kW, ligado durante 3 h.</t>
         </is>
       </c>
       <c r="E909" t="inlineStr">
         <is>
-          <t>contaminação da água pela urina de rato que transmite a doença.</t>
-        </is>
-      </c>
-      <c r="F909" t="inlineStr"/>
+          <t>Chuveiro – 5000 W, ligado durante 1.800 segundos.</t>
+        </is>
+      </c>
+      <c r="F909" t="inlineStr">
+        <is>
+          <t>Ferro de passar – 1,3 kW, ligado durante 20 minutos.</t>
+        </is>
+      </c>
       <c r="G909" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H909" t="inlineStr">
         <is>
-          <t>A leptospirose é uma doença de origem bacteriana a qual tem como principal meio de disseminação a urina de rato, potencializada quando acontecem enchentes, pois o animal costuma urinar em esgotos os quais acabam entrando em contato com as pessoas através das enchentes.</t>
+          <t>Calculando a energia de cada aparelho:
+Secador de cabelos: E = P.t = 1500 W . 1/2 h = 750 Wh
+Três lâmpadas incandescentes: E = P.t = 3.60 W . 1 h = 180 Wh
+Ar-condicionado: E = P.t = 1000 W . 3 h = 3.000 Wh
+Chuveiro: E = P.t = 5000 W . 1/2 h = 2.500 Wh
+Ferro de passar: E = P.t = 1300 W . 1/3 h = 433,33 Wh
+Logo o ar-condicionado é o aparelho que mais consome energia.</t>
         </is>
       </c>
       <c r="I909" t="inlineStr">
@@ -51790,40 +51849,42 @@
       <c r="K909" t="inlineStr"/>
       <c r="L909" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="910">
       <c r="A910" t="inlineStr">
         <is>
-          <t>A imagem abaixo apresenta medidas gerais de prevenção a gripe, doença causada pelo vírus influenza.  
-Disponível em: Influenza (gripe) - Secretaria de Saúde do Distrito Federal. Acesso em: 04 fev. 2025.
-A circulação de vírus respiratórios aumenta em determinadas épocas do ano, exigindo medidas preventivas para reduzir o risco de contaminação. Além dessas medidas, a vacinação é uma importante forma de proteção contra essas doenças.
-Com base nisso, assinale a alternativa que diferencia a vacinação das outras medidas preventivas:</t>
+          <t>Uma casa tem um consumo de energia elétrica de 152 000 Wh e o custo de cada kWh da empresa que fornece energia elétrica para esta casa é de R$ 0,80.
+Qual será a conta de luz desta família?</t>
         </is>
       </c>
       <c r="B910" t="inlineStr">
         <is>
-          <t>A vacinação evita completamente o contato com vírus e bactérias, tornando desnecessárias outras medidas de prevenção.</t>
+          <t>R$ 60,80</t>
         </is>
       </c>
       <c r="C910" t="inlineStr">
         <is>
-          <t>A vacinação estimula o sistema imunológico a reconhecer e combater o vírus, reduzindo o risco de formas graves da doença.</t>
+          <t>R$ 121,60</t>
         </is>
       </c>
       <c r="D910" t="inlineStr">
         <is>
-          <t>A vacinação age imediatamente após a aplicação, garantindo proteção total contra qualquer tipo de patógeno.</t>
+          <t>R$ 182,40</t>
         </is>
       </c>
       <c r="E910" t="inlineStr">
         <is>
-          <t>A vacinação elimina completamente o vírus do ambiente, impedindo que ele se espalhe entre as pessoas.</t>
-        </is>
-      </c>
-      <c r="F910" t="inlineStr"/>
+          <t>R$ 608,00</t>
+        </is>
+      </c>
+      <c r="F910" t="inlineStr">
+        <is>
+          <t>R$ 1216,00</t>
+        </is>
+      </c>
       <c r="G910" t="inlineStr">
         <is>
           <t>B</t>
@@ -51831,7 +51892,8 @@
       </c>
       <c r="H910" t="inlineStr">
         <is>
-          <t>A vacinação é um método de imunização ativa, que prepara o sistema imunológico para reconhecer e reagir contra vírus e bactérias específicos. Ao receber a vacina, o organismo produz anticorpos e memória imunológica, tornando-se mais eficiente no combate ao agente infeccioso, caso ocorra uma exposição futura. Diferentemente das medidas preventivas gerais, como evitar aglomerações e higienizar as mãos, que reduzem a chance de exposição ao vírus, a vacinação protege o corpo internamente, diminuindo os riscos de infecção severa, hospitalização e até morte.</t>
+          <t>O consumo de energia nesta residência foi de 152 000 Wh, que é o mesmo que 152 kWh. Se cada 1 kWh o custo é de R$ 0,80, para encontrar o valor cobrado no final do mês para esta família, calcula-se da seguinte forma:
+Por tanto, o valor cobrado será de R$ 121,60.</t>
         </is>
       </c>
       <c r="I910" t="inlineStr">
@@ -51844,54 +51906,53 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K910" t="inlineStr">
-        <is>
-          <t>ph10_cie_09.jpg</t>
-        </is>
-      </c>
+      <c r="K910" t="inlineStr"/>
       <c r="L910" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="911">
       <c r="A911" t="inlineStr">
         <is>
-          <t>Uma pesquisa feita pela Universidade Federal de Minas Gerais (UFMG) identificou riscos sociais de longo prazo nas campanhas de desinformação sobre vacinas geradas pela pandemia. O crescimento de movimentos e discursos contra a vacinação, iniciante no Brasil até o início da pandemia de COVID-19, pode ter consequências de longo prazo para campanhas futuras, de acordo com pesquisadores. 
-Disponível em: https://www.em.com.br/app/noticia/bem-viver/2022/03/02/interna_bem_viver,1349446/covid-19-desinformacao-sobre-vacinas-pode-ter-consequencias-de-longo-prazo.shtml.Acesso em  16 nov. de 2023.
-Qual a importância da vacinação?</t>
+          <t>Com a intenção de diminuir a conta de luz, Marina deu algumas sugestões aos seus pais.
+Qual a sugestão que ajudaria a diminuir o consumo de energia elétrica?</t>
         </is>
       </c>
       <c r="B911" t="inlineStr">
         <is>
-          <t>A vacinação é o modo mais eficiente para prevenção e erradicação de doenças.</t>
+          <t>Trocar o ventilador por ar condicionado.</t>
         </is>
       </c>
       <c r="C911" t="inlineStr">
         <is>
-          <t>A vacinação é o modo mais eficiente de se recuperar de uma doença.</t>
+          <t>Trocar o fogão a gás por um fogão elétrico.</t>
         </is>
       </c>
       <c r="D911" t="inlineStr">
         <is>
-          <t>A vacinação é o modo mais eficiente para o tratamento de doenças.</t>
+          <t>Trocar as lâmpadas fluorescente para lâmpadas LED.</t>
         </is>
       </c>
       <c r="E911" t="inlineStr">
         <is>
-          <t>A vacinação é o modo mais eficiente de se contrair uma doença.</t>
-        </is>
-      </c>
-      <c r="F911" t="inlineStr"/>
+          <t>Usar o chuveiro com mais frequência no dia.</t>
+        </is>
+      </c>
+      <c r="F911" t="inlineStr">
+        <is>
+          <t>Usar secador de cabelo para secar as roupas molhadas.</t>
+        </is>
+      </c>
       <c r="G911" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H911" t="inlineStr">
         <is>
-          <t>A vacinação é o modo mais eficiente para prevenção e erradicação de doenças. Através dela o sarampo que estava controlado na população, está voltando a ser disseminado, muito também pela diminuição da cobertura vacinal incentivada pelo movimento antivacina.</t>
+          <t>Ao trocar as lâmpadas fluorescentes para lâmpadas LED, o consumo de energia será reduzido, pois a potência das lâmpadas LED são menores.</t>
         </is>
       </c>
       <c r="I911" t="inlineStr">
@@ -51907,46 +51968,52 @@
       <c r="K911" t="inlineStr"/>
       <c r="L911" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="912">
       <c r="A912" t="inlineStr">
         <is>
-          <t>Os movimentos migratórios são fenômenos complexos que envolvem a movimentação de pessoas de um local para outro. Esses movimentos podem ser motivados por diversos fatores, como a busca por melhores condições de vida, oportunidades de emprego, ou até mesmo a fuga de conflitos e perseguições. No Brasil, a migração interna tem sido uma característica marcante, especialmente com o êxodo rural e a urbanização acelerada nas últimas décadas.
-Qual dos seguintes fatores é um exemplo de fator de repulsão populacional?</t>
+          <t>Leia o texto a seguir. 
+No México, as indústrias maquiladoras, instaladas na fronteira norte na década de 1990 exemplificam algumas das dinâmicas amplamente favorecidas pelo neoliberalismo. Impulsionadas pelos baixos salários no país, elas se concentram nas etapas mais intensivas em trabalho, na montagem – etapa de menor valor agregado – empregando uma maioria de mulheres, não raro migrantes que ficaram no país. Tudo isso em contraposição às atividades da cadeia desenvolvidas nos países mais ricos, de desenvolvimento intelectual do produto e fabricação de componentes mais avançados
+Disponível em: https://diplomatique.org.br/resistencias-mexicanas-entre-massacres-travessias-e-lutas/. Acesso em 17 de dez de 2024.
+Por que as indústrias maquiladoras se instalaram na fronteira norte do México na década de 1990?</t>
         </is>
       </c>
       <c r="B912" t="inlineStr">
         <is>
-          <t>Oportunidades de emprego.</t>
+          <t>Devido aos altos salários oferecidos no México.</t>
         </is>
       </c>
       <c r="C912" t="inlineStr">
         <is>
-          <t>Qualidade de vida.</t>
+          <t>Para se beneficiar dos baixos salários no país</t>
         </is>
       </c>
       <c r="D912" t="inlineStr">
         <is>
-          <t>Conflitos armados.</t>
+          <t>Para desenvolver produtos intelectualmente avançados</t>
         </is>
       </c>
       <c r="E912" t="inlineStr">
         <is>
-          <t>Infraestrutura desenvolvida.</t>
-        </is>
-      </c>
-      <c r="F912" t="inlineStr"/>
+          <t>Devido à alta qualificação da mão de obra local</t>
+        </is>
+      </c>
+      <c r="F912" t="inlineStr">
+        <is>
+          <t>Para promover igualdade salarial entre trabalhadores.</t>
+        </is>
+      </c>
       <c r="G912" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H912" t="inlineStr">
         <is>
-          <t>Conflitos armados são um exemplo clássico de fator de repulsão populacional, pois forçam as pessoas a deixarem suas casas em busca de segurança.</t>
+          <t>As indústrias maquiladoras se instalaram na fronteira norte do México para aproveitar os baixos salários oferecidos no país. Essa estratégia permitiu que as empresas reduzissem seus custos de produção, concentrando-se em etapas de trabalho intensivo, como a montagem, que requerem menos qualificação e oferecem menor valor agregado.</t>
         </is>
       </c>
       <c r="I912" t="inlineStr">
@@ -51962,46 +52029,51 @@
       <c r="K912" t="inlineStr"/>
       <c r="L912" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="913">
       <c r="A913" t="inlineStr">
         <is>
-          <t>A migração de retorno é um fenômeno em que indivíduos que anteriormente migraram para outras regiões ou países decidem voltar ao seu local de origem. Esse movimento pode ser motivado por diversos fatores, como a busca por reestabelecer laços familiares e culturais.
-Qual dos seguintes fatores pode ser considerado um motivo para a migração de retorno?</t>
+          <t>O império asteca floresceu entre c. 1345 e 1521 e dominou a antiga Mesoamérica. Esta nação jovem e belicosa foi muito bem-sucedida em expandir suas fronteiras e conquistar riquezas fabulosas, mas, então, chegaram estranhos visitantes de outro mundo. Liderados por Hernán Cortés, as armas formidáveis dos espanhóis e sua sede por tesouros iriam trazer uma destruição devastadora, além de doenças. Os Conquistadores imediatamente encontraram aliados locais, ansiosos para ajudar a derrubar o brutal regime dos astecas e libertar-se do fardo dos tributos e da necessidade de alimentar o insaciável apetite dos seus senhores por vítimas sacrificiais. Com isso, bastaram três anos para que caísse o maior império que já existira até então nas Américas do Norte e Central.
+Disponível em: https://www.worldhistory.org/trans/pt/2-916/cortes-e-a-queda-do-imperio-asteca/. Acesso em 17 de dez de 2024.
+Qual foi um dos principais fatores que contribuíram para a queda do império asteca?</t>
         </is>
       </c>
       <c r="B913" t="inlineStr">
         <is>
-          <t>Aumento da violência na região de origem.</t>
+          <t>A falta de recursos naturais na região.</t>
         </is>
       </c>
       <c r="C913" t="inlineStr">
         <is>
-          <t>Melhoria das condições econômicas na região de origem.</t>
+          <t>A resistência dos astecas contra os invasores.</t>
         </is>
       </c>
       <c r="D913" t="inlineStr">
         <is>
-          <t>Falta de oportunidades de emprego na região de origem.</t>
+          <t>A ausência de doenças trazidas pelos europeus.</t>
         </is>
       </c>
       <c r="E913" t="inlineStr">
         <is>
-          <t>Desastres naturais na região de origem.</t>
-        </is>
-      </c>
-      <c r="F913" t="inlineStr"/>
+          <t>A incapacidade dos espanhóis de encontrar aliados.</t>
+        </is>
+      </c>
+      <c r="F913" t="inlineStr">
+        <is>
+          <t>A superioridade dos armamentos e microrganismos.</t>
+        </is>
+      </c>
       <c r="G913" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="H913" t="inlineStr">
         <is>
-          <t>A melhoria das condições econômicas na região de origem é um fator que pode motivar a migração de retorno, pois oferece melhores oportunidades para os indivíduos que desejam voltar.</t>
+          <t>O texto destaca que a superioridade dos armamentos espanhóis e a introdução de doenças (microrganismos) foram fatores cruciais que devastaram a população asteca e contribuíram significativamente para a queda do império.</t>
         </is>
       </c>
       <c r="I913" t="inlineStr">
@@ -52017,49 +52089,51 @@
       <c r="K913" t="inlineStr"/>
       <c r="L913" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="914">
       <c r="A914" t="inlineStr">
         <is>
-          <t>Qual das seguintes manchetes exemplifica um caso de xenofobia?</t>
+          <t>Observe a imagem. 
+Disponível em: https://upload.wikimedia.org/wikipedia/commons/0/0b/Border_USA_Mexico.jpg. Acesso em 17 de dez de 2024. 
+O muro fronteiriço entre o México e os Estados Unidos é uma estrutura física destinada a controlar a imigração ilegal e o tráfico de mercadorias entre os dois países. Milhares de pessoas tentam cruzar essa fronteira em busca de melhores condições de vida nos Estados Unidos, fugindo da violência, pobreza e falta de oportunidades presentes em seus países de origem. Contudo, as autoridades americanas investem fortemente em medidas para impedir essas travessias. Observando a imagem,  qual dos fatores a seguir é um dos principais motivadores para a migração de pessoas do México para os Estados Unidos?</t>
         </is>
       </c>
       <c r="B914" t="inlineStr">
         <is>
-          <t>Formação de professores para o acolhimento de imigrantes e refugiados
-(Gov.Br)</t>
+          <t>Busca por melhores condições de trabalho e de vida.</t>
         </is>
       </c>
       <c r="C914" t="inlineStr">
         <is>
-          <t>Milhares de pessoas protestam em Portugal contra imigrantes no país
-(UOL)</t>
+          <t>Interesse em conhecer as paisagens do país vizinho.</t>
         </is>
       </c>
       <c r="D914" t="inlineStr">
         <is>
-          <t>Prefeitura oferece curso de Língua Portuguesa gratuito para imigrantes
-(Prefeitura de São Paulo)</t>
+          <t>Tentativa de fugir de regiões rurais para áreas urbanas.</t>
         </is>
       </c>
       <c r="E914" t="inlineStr">
         <is>
-          <t>Brasil acolhe mais de 125 mil migrantes e refugiados venezuelanos por meio da Operação Acolhida
-(Agência GOV)</t>
-        </is>
-      </c>
-      <c r="F914" t="inlineStr"/>
+          <t>Desejo de participar de programas de intercâmbio cultural.</t>
+        </is>
+      </c>
+      <c r="F914" t="inlineStr">
+        <is>
+          <t>Busca por áreas com menor densidade populacional.</t>
+        </is>
+      </c>
       <c r="G914" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H914" t="inlineStr">
         <is>
-          <t>No caso, o gabarito é enfático ao demonstrar insatisfação de um grupo social direcionada aos imigrantes. Enquanto todas as outras ações estão relacionadas à diferentes formas de acolhimento e integração de de imigrantes na sociedade.</t>
+          <t>A principal motivação para a migração de muitos mexicanos e outros latino-americanos para os Estados Unidos é a busca por melhores condições econômicas, mais oportunidades de emprego e um padrão de vida superior comparado ao de seus países de origem.</t>
         </is>
       </c>
       <c r="I914" t="inlineStr">
@@ -52072,49 +52146,58 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K914" t="inlineStr"/>
+      <c r="K914" t="inlineStr">
+        <is>
+          <t>8a_ph10_geo_03.png</t>
+        </is>
+      </c>
       <c r="L914" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="915">
       <c r="A915" t="inlineStr">
         <is>
-          <t>O êxodo rural é um fenômeno migratório caracterizado pela saída de pessoas do campo para as cidades. Esse movimento é geralmente motivado pela busca de melhores condições de vida, como acesso a emprego, educação e serviços de saúde.
-No Brasil, o êxodo rural foi intensificado a partir da década de 1960 devido à/ao</t>
+          <t>Observe a tabela a seguir.
+Disponível em: https://www.populationpyramid.net/pt/m%C3%A9xico/2021/. Acesso em: 17 dez 2024.
+A pirâmide etária do México em 2021 revela uma população jovem com sinais de envelhecimento em curso. Esse fenômeno é típico de países em desenvolvimento, onde a taxa de natalidade diminui e a expectativa de vida aumenta devido ao acesso à informação, urbanização e serviços de saúde. Com base nestas informações, qual das seguintes afirmações melhor descreve a tendência demográfica do México?</t>
         </is>
       </c>
       <c r="B915" t="inlineStr">
         <is>
-          <t>aumento da oferta de empregos no campo.</t>
+          <t>População principalmente idosa, com altas taxas de natalidade.</t>
         </is>
       </c>
       <c r="C915" t="inlineStr">
         <is>
-          <t>mecanização da agricultura.</t>
+          <t>Alta taxa de natalidade e baixa expectativa de vida.</t>
         </is>
       </c>
       <c r="D915" t="inlineStr">
         <is>
-          <t>melhoria das condições de vida no campo.</t>
+          <t>Rápido crescimento populacional, pequena porção de idosos.</t>
         </is>
       </c>
       <c r="E915" t="inlineStr">
         <is>
-          <t>redução da urbanização.</t>
-        </is>
-      </c>
-      <c r="F915" t="inlineStr"/>
+          <t>População jovem e sinais claros de envelhecimento.</t>
+        </is>
+      </c>
+      <c r="F915" t="inlineStr">
+        <is>
+          <t>Alta mortalidade infantil e baixa expectativa de vida.</t>
+        </is>
+      </c>
       <c r="G915" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="H915" t="inlineStr">
         <is>
-          <t>A mecanização da agricultura reduziu a necessidade de mão de obra no campo, levando muitas pessoas a migrarem para as cidades em busca de emprego.</t>
+          <t>A pirâmide etária mostra uma base alargada (população jovem) e sinais de envelhecimento (proporção crescente de faixas etárias mais altas), alinhando-se com a descrição do fenômeno de transição demográfica.</t>
         </is>
       </c>
       <c r="I915" t="inlineStr">
@@ -52127,41 +52210,50 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K915" t="inlineStr"/>
+      <c r="K915" t="inlineStr">
+        <is>
+          <t>8a_ph10_geo_04.png</t>
+        </is>
+      </c>
       <c r="L915" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="916">
       <c r="A916" t="inlineStr">
         <is>
-          <t>A migração internacional envolve a movimentação de pessoas entre diferentes países. Esse tipo de migração pode ser motivado por fatores econômicos, políticos, sociais ou ambientais.
-Qual dos seguintes fatores é um exemplo de fator de atração para migrantes internacionais no Brasil?</t>
+          <t>O inchaço urbano é o crescimento desordenado das cidades, que ocorre em pequenos centros de determinadas regiões urbanas. A falta de planejamento durante a expansão da cidade faz com que haja uma área que concentra as atividades e os serviços locais, atraindo uma quantidade de pessoas que muitas vezes excede a capacidade do espaço disponível.
+Disponível em: https://www.politize.com.br/inchaco-urbano/. Acesso em 17 de dez de 2024.
+Qual das seguintes consequências é mais provável no contexto das cidades mexicanas que experienciam inchaço urbano?</t>
         </is>
       </c>
       <c r="B916" t="inlineStr">
         <is>
-          <t>Conflitos armados.</t>
+          <t>Melhor distribuição de serviços e infraestruturas.</t>
         </is>
       </c>
       <c r="C916" t="inlineStr">
         <is>
-          <t>Desemprego.</t>
+          <t>Redução da poluição e qualidade do ar melhorada.</t>
         </is>
       </c>
       <c r="D916" t="inlineStr">
         <is>
-          <t>Oportunidades de emprego.</t>
+          <t>Aumento da pressão sobre serviços e infraestruturas.</t>
         </is>
       </c>
       <c r="E916" t="inlineStr">
         <is>
-          <t>Perseguições políticas.</t>
-        </is>
-      </c>
-      <c r="F916" t="inlineStr"/>
+          <t>Maior equilíbrio e melhor qualidade de vida.</t>
+        </is>
+      </c>
+      <c r="F916" t="inlineStr">
+        <is>
+          <t>Expansão harmoniosa e bem planejada.</t>
+        </is>
+      </c>
       <c r="G916" t="inlineStr">
         <is>
           <t>C</t>
@@ -52169,7 +52261,7 @@
       </c>
       <c r="H916" t="inlineStr">
         <is>
-          <t>Oportunidades de emprego são um fator de atração para migrantes internacionais, pois oferecem melhores condições de vida e estabilidade econômica.</t>
+          <t>O texto indica que o crescimento desordenado leva a uma concentração de atividades e serviços, aumentando a pressão sobre a infraestrutura disponível.</t>
         </is>
       </c>
       <c r="I916" t="inlineStr">
@@ -52185,46 +52277,51 @@
       <c r="K916" t="inlineStr"/>
       <c r="L916" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="917">
       <c r="A917" t="inlineStr">
         <is>
-          <t>A saída da população de um país denomina-se__________________, sendo que esta região pode ser um local de grande _______________________, já a entrada de indivíduos em um país denomina-se________________, e esta região receptora pode ser uma área de forte ____________________.
-Assinale a alternativa que completa corretamente o trecho acima:</t>
+          <t>O conceito de aldeia global foi criado na década de 1960 pelo filósofo canadense Marshall Mcluhan, então professor da Escola de Comunicações da Universidade de Toronto.Segundo esse conceito, o avanço nas tecnologias de informação e comunicação encurta as distâncias no mundo e facilita trocas culturais entre os diferentes povos.O autor acreditava que, devido à diminuição das distâncias e barreiras geográficas, o planeta se reduziria a uma organização semelhante a aldeias, onde tudo e todos estariam interconectados.
+Disponível em:&lt;https://www.significados.com.br/aldeia-global/&gt;. Acesso em: 29 jun.2020.
+Na fronteira entre o México e os Estados Unidos ocorrem fatos que desmentem a ideia de aldeia global. Como por exemplo</t>
         </is>
       </c>
       <c r="B917" t="inlineStr">
         <is>
-          <t>imigração, repulsão demográfica, migração, atração demográfica.</t>
+          <t>a ausência de vias de circulação modernas entre os dois países.</t>
         </is>
       </c>
       <c r="C917" t="inlineStr">
         <is>
-          <t>emigração, atração demográfica, imigração, repulsão demográfica.</t>
+          <t>a restrição da entrada de trabalhadores mexicanos nos Estados Unidos.</t>
         </is>
       </c>
       <c r="D917" t="inlineStr">
         <is>
-          <t>migração, repulsão demográfica, imigração, fluxos migratórios.</t>
+          <t>a dificuldade de acesso de norte-americanos ao México.</t>
         </is>
       </c>
       <c r="E917" t="inlineStr">
         <is>
-          <t>emigração, repulsão demográfica, imigração, atração demográfica.</t>
-        </is>
-      </c>
-      <c r="F917" t="inlineStr"/>
+          <t>a redução das exportações do norte do México para os Estados Unidos.</t>
+        </is>
+      </c>
+      <c r="F917" t="inlineStr">
+        <is>
+          <t>o embargo econômico dos Estados Unidos à produção agrícola do México.</t>
+        </is>
+      </c>
       <c r="G917" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H917" t="inlineStr">
         <is>
-          <t>A emigração representa a saída de indivíduos de seu país de origem, sendo que este pode ter características que o tornem uma área de repulsão demográfica, como altas taxas de desemprego ou catástrofes climáticas. A imigração é a entrada de indivíduos de outros países em um novo, sendo que este pode ter qualidades que o tornem um local de atração demográfica, como oportunidades de emprego.</t>
+          <t>A fronteira entre México e Estados Unidos é uma das mais vigiadas do planeta. Um polêmico muro foi construído para tentar conter a chegada de imigrantes ilegais, vistos por muitos cidadãos estadunidenses como os culpados por diversos problemas que atingiram a economia norte-americana nos últimos anos, como a elevação do desemprego no país.</t>
         </is>
       </c>
       <c r="I917" t="inlineStr">
@@ -52240,46 +52337,51 @@
       <c r="K917" t="inlineStr"/>
       <c r="L917" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="918">
       <c r="A918" t="inlineStr">
         <is>
-          <t>Disponível em: https://goo.gl/images/zk5vQV Acesso em: 30 de jul. 2018
-De acordo com o mapa, o maior número de refugiados no Brasil vem da Síria. Qual o principal motivo que levou esse povo a deixar seu país de origem?</t>
+          <t>O muro que Trump já está construindo inevitavelmente terá que correr paralelo às margens do rio, impedindo a circulação de espécies entre os dois países e piorando a situação de plantas e animais típicos que já estão ameaçados de extinção.
+VAIANO, Bruno Disponível em &lt;https://super.abril.com.br/ciencia/muro-de-trump-pode-levar-animais-e-plantas-do-texas-a-extincao/&gt; Acesso em: 23 maio 2018.
+Com base no trecho acima, assinale a alternativa correta.</t>
         </is>
       </c>
       <c r="B918" t="inlineStr">
         <is>
-          <t>Xenofobia.</t>
+          <t>No mundo atual, as contradições da globalização não geram impactos na natureza.</t>
         </is>
       </c>
       <c r="C918" t="inlineStr">
         <is>
-          <t>Conflitos militares.</t>
+          <t>Um dos motivos para construção do muro separando EUA e México é o controle da passagem de animais silvestres.</t>
         </is>
       </c>
       <c r="D918" t="inlineStr">
         <is>
-          <t>Desemprego.</t>
+          <t>O combate acrítico à imigração de mexicanos prejudica a biodiversidade.</t>
         </is>
       </c>
       <c r="E918" t="inlineStr">
         <is>
-          <t>Misoginia.</t>
-        </is>
-      </c>
-      <c r="F918" t="inlineStr"/>
+          <t>A construção do muro entre os EUA e o México não extrapola questões ideológicas.</t>
+        </is>
+      </c>
+      <c r="F918" t="inlineStr">
+        <is>
+          <t>A construção do muro entre os EUA e o México reflete a baixa capacidade dos humanos interagirem com o espaço.</t>
+        </is>
+      </c>
       <c r="G918" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H918" t="inlineStr">
         <is>
-          <t>A guerra civil atualmente em curso na Síria obrigou grande parte de sua população a buscar asilo em outros países, sendo o Brasil um dos destinos dos refugiados sírios..</t>
+          <t>A construção de um muro por parte dos EUA visando deter processos migratórios que partem do México, prejudica a circulação de animais silvestres.</t>
         </is>
       </c>
       <c r="I918" t="inlineStr">
@@ -52292,52 +52394,54 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K918" t="inlineStr">
-        <is>
-          <t>ph10_geo_07.png</t>
-        </is>
-      </c>
+      <c r="K918" t="inlineStr"/>
       <c r="L918" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="919">
       <c r="A919" t="inlineStr">
         <is>
-          <t>Fome, epidemias, desemprego e guerras, são alguns exemplos de fatores que podem causar:</t>
+          <t>Estes trabalhadores, com autorizações temporárias, ficaram conhecidos como "braceros" (numa referência em espanhol à força braçal necessária para trabalho pesado).
+Disponível em:&lt;https://www.bbc.com/portuguese/reporterbbc/story/2008/10/081017_mexicanossalario.shtml&gt;. Acesso em: 29 jun.2020.
+Os braceros podem ser definidos como:</t>
         </is>
       </c>
       <c r="B919" t="inlineStr">
         <is>
-          <t>imigrações.</t>
+          <t>Trabalhadores mexicanos que se mudaram para o complexo turístico na Flórida.</t>
         </is>
       </c>
       <c r="C919" t="inlineStr">
         <is>
-          <t>atração populacional.</t>
+          <t>Trabalhadores rurais mexicanos que migram anualmente para trabalhar em colheitas.</t>
         </is>
       </c>
       <c r="D919" t="inlineStr">
         <is>
-          <t>repulsão populacional.</t>
+          <t>Camponeses mexicanos que fixam-se de maneira definitiva para garantir a produção de subsistência.</t>
         </is>
       </c>
       <c r="E919" t="inlineStr">
         <is>
-          <t>êxodo rural.</t>
-        </is>
-      </c>
-      <c r="F919" t="inlineStr"/>
+          <t>Trabalhadores que implementam a modernização das "Haciendas" mexicanas.</t>
+        </is>
+      </c>
+      <c r="F919" t="inlineStr">
+        <is>
+          <t>Camponeses que trabalham como monocultura de exportação dos latifúndios mexicanos.​</t>
+        </is>
+      </c>
       <c r="G919" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H919" t="inlineStr">
         <is>
-          <t>A repulsão populacional é causada por fatores que põe em risco a qualidade de vida da população.</t>
+          <t>Os braceros, como são conhecidos os trabalhadores temporários do campo, migram sazonalmente (transumância). Alguns desses trabalhadores rurais são donos de pequenas propriedades no México, no entanto não conseguem sustentar suas famílias somente com sua pequena roça. Em geral as condições de trabalho temporário em áreas rurais são precárias e a remuneração é baixa.</t>
         </is>
       </c>
       <c r="I919" t="inlineStr">
@@ -52353,46 +52457,50 @@
       <c r="K919" t="inlineStr"/>
       <c r="L919" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="920">
       <c r="A920" t="inlineStr">
         <is>
-          <t>Disponível em: https://goo.gl/images/uRx9Ng Acesso em: 30 de jul. 2018
-De acordo com os dados acima, os movimentos migratórios mais intensos aconteciam da região nordeste para a região sudeste do país, principalmente para o estado de São Paulo. Com o passar das décadas esse fluxo foi diminuindo e até mesmo invertido. Como é denominada a volta do migrante a sua terra de origem?</t>
+          <t>A industrialização mexicana teve, a partir dos anos 1960, incentivos governamentais para a entrada de capital estrangeiro. Há uma grande variedade de empresas transnacionais no México, que empregam milhares de pessoas e são responsáveis por uma parcela significativa da riqueza produzida no país.
+O nome do modelo industrial adotado pelo México ficou conhecido como:</t>
         </is>
       </c>
       <c r="B920" t="inlineStr">
         <is>
-          <t>Êxodo rural.</t>
+          <t>Substituição de Importações.</t>
         </is>
       </c>
       <c r="C920" t="inlineStr">
         <is>
-          <t>Migração de retorno.</t>
+          <t>Plataformas de Exportações.</t>
         </is>
       </c>
       <c r="D920" t="inlineStr">
         <is>
-          <t>Repulsão demográfica.</t>
+          <t>Substituição de Exportações.</t>
         </is>
       </c>
       <c r="E920" t="inlineStr">
         <is>
-          <t>Emigração.</t>
-        </is>
-      </c>
-      <c r="F920" t="inlineStr"/>
+          <t>Plataformas de importações.</t>
+        </is>
+      </c>
+      <c r="F920" t="inlineStr">
+        <is>
+          <t>Industrialização agrária.</t>
+        </is>
+      </c>
       <c r="G920" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H920" t="inlineStr">
         <is>
-          <t>A migração de retorno acontece quando os migrantes regressam a sua terra de origem após ter passado um período em outro lugar.</t>
+          <t>O México está entre os países mais industrializados da região e seguiu o mesmo modelo de substituição de importações dos vizinhos latino-americanos. Esse um processo que leva ao aumento da produção interna de um país e a diminuição das suas importações. Ao longo da história econômica mundial, os processos de substituição de importações foram desencadeados por fatores políticos ou econômicos, e foram resultado de ações planejadas ou imposição das circunstâncias.</t>
         </is>
       </c>
       <c r="I920" t="inlineStr">
@@ -52405,52 +52513,61 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K920" t="inlineStr">
-        <is>
-          <t>ph10_geo_09.jpg</t>
-        </is>
-      </c>
+      <c r="K920" t="inlineStr"/>
       <c r="L920" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="921">
       <c r="A921" t="inlineStr">
         <is>
-          <t>Na segunda metade do século XX, o Brasil passou por um intenso deslocamento populacional das zonas agrárias para áreas urbanizadas. Esse processo recebe o nome de Êxodo rural. Que fatores contribuíram para esse movimento migratório?</t>
+          <t>TEXTO I
+A televisão brasileira mudou muito ao longo dos anos, com séries e produções novas ano após ano. Mas um seriado mexicano, de baixo orçamento e produzido nos anos 70 é presença obrigatória na programação até os dias de hoje: Chaves! [...]
+Disponível em:&lt; https://www.aficionados.com.br/tudo-sobre-chaves/&gt;. Acesso em:06 jul.2020.
+TEXTO II
+Frida Kahlo foi uma das mais importantes artistas da história do México, marcada pela tradição vanguardista do modernismo surrealista. Nascida em 1907, na Cidade do México, era filha de uma família alemã com indígenas catequizados [...]
+65 ANOS SEM FRIDA KAHLO: DOR E ORGULHO
+Neste dia, em 1954, morria aquela que revolucionou a história da arte do México.
+ANDRÉ NOGUEIRA PUBLICADO EM 13/07/2019, ÀS 00H00
+Disponível em:&lt; https://aventurasnahistoria.uol.com.br/noticias/reportagem/a-vida-e-a-morte-de-frida-kahlo.phtml&gt;. Acesso em: 06 jul.2020.
+As notícias retratam</t>
         </is>
       </c>
       <c r="B921" t="inlineStr">
         <is>
-          <t>Mecanização agrícola, industrialização, estrutura fundiária concentradora.</t>
+          <t>a cultura mexicana restrita.</t>
         </is>
       </c>
       <c r="C921" t="inlineStr">
         <is>
-          <t>Urbanização, reforma agrária, marginalização do campo.</t>
+          <t>o elitismo das produções mexicanas.</t>
         </is>
       </c>
       <c r="D921" t="inlineStr">
         <is>
-          <t>Êxodo urbano, baixa produtividade, revolução industrial brasileira.</t>
+          <t>a atual estagnação cultural mexicana.</t>
         </is>
       </c>
       <c r="E921" t="inlineStr">
         <is>
-          <t>Mecanização da cidade, favelização do campo, reformas trabalhistas.</t>
-        </is>
-      </c>
-      <c r="F921" t="inlineStr"/>
+          <t>a eliminação do componente cultural indígena.</t>
+        </is>
+      </c>
+      <c r="F921" t="inlineStr">
+        <is>
+          <t>a diversidade e impacto da produção cultural mexicana.</t>
+        </is>
+      </c>
       <c r="G921" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="H921" t="inlineStr">
         <is>
-          <t>A mecanização agrícola no campo criou um forte processo de desemprego, já a industrialização nas áreas urbanas gerou empregos e melhores salários. A estrutura fundiária brasileira é extremamente concentradora pois a maior parte das terras pertencem a um grupo seleto da população. Esses fatores tornaram o campo pouco atrativo, causando a repulsa demográfica e por consequência o êxodo rural.</t>
+          <t>Chaves e Frida Kahlo são famosas representações artísticas do México, evidenciando a popularidade e impacto social da cultura mexicana no Brasil e no mundo.</t>
         </is>
       </c>
       <c r="I921" t="inlineStr">
@@ -52466,50 +52583,52 @@
       <c r="K921" t="inlineStr"/>
       <c r="L921" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="922">
       <c r="A922" t="inlineStr">
         <is>
-          <t>Em pleno centro da Espanha, em meio às terras frias e áridas castelhanas, ergue-se uma pequena cidade de 141 quilômetros quadrados.
-Atualmente ela é habitada por cerca de 9 mil pessoas e ostenta o título de "vila muito ilustre, antiga, coroada, leal e muito nobre".
-Ali ocorreu há 525 anos um fato histórico que determinou a configuração política e territorial da América, dividiu o mundo em dois hemisférios e definiu a língua e a cultura de milhões de pessoas.
-Essa cidade, chamada Tordesilhas, está localizada ao norte de Madri.
-Disponível em: https://www.bbc.com/portuguese/internacional-48554080. Acesso em: 13 dez. 2024.
-O Tratado de Tordesilhas foi responsável por</t>
+          <t>[...] "Se você vai se tornar independente da Espanha, por que continuaria a se submeter aos mandos e desmandos de Buenos Aires, por exemplo? A divisão por vice-reinos era burocrática. E as fronteiras atuais dos países da América Latina demoraram para ser consolidadas. Não era possível prevê-las antes de 1810, pois resultaram de disputas internas após a independência", explica.
+Mas é importante lembrar que também houve na América Espanhola planos de unificação, que não avançaram.
+Por que o Brasil continuou um só enquanto a América espanhola se dividiu em vários países? BBC News Brasil. Disponível em: https://www.bbc.com/portuguese/articles/c3gjpmvkv5eo. Acesso em: 17 dez. 2024.
+Qual a causa da fragmentação política da América Latina pós-independência retratada no texto?</t>
         </is>
       </c>
       <c r="B922" t="inlineStr">
         <is>
-          <t>firmar acordos de comércio entre a Espanha e as Índias.</t>
+          <t>A ausência de recursos naturais.</t>
         </is>
       </c>
       <c r="C922" t="inlineStr">
         <is>
-          <t>separar em definitivo as Igrejas Protestantes e a Igreja Católica.</t>
+          <t>A influência das potências asiáticas.</t>
         </is>
       </c>
       <c r="D922" t="inlineStr">
         <is>
-          <t>dividir as terras e os oceanos além da Europa entre Portugal e Espanha.</t>
+          <t>A falta de influência das elites locais.</t>
         </is>
       </c>
       <c r="E922" t="inlineStr">
         <is>
-          <t>consolidar a independência do Império do Brasil dos domínios portugueses.</t>
-        </is>
-      </c>
-      <c r="F922" t="inlineStr"/>
+          <t>A homogeneidade cultural e linguística.</t>
+        </is>
+      </c>
+      <c r="F922" t="inlineStr">
+        <is>
+          <t>As disputas internas entre as elites criollas.</t>
+        </is>
+      </c>
       <c r="G922" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="H922" t="inlineStr">
         <is>
-          <t>O Tratado de Tordesilhas, assinado em 1494, foi responsável por dividir as terras e os oceanos além da Europa entre Portugal e Espanha. Um meridiano a 370 léguas a oeste de Cabo Verde delimitou as áreas de domínio colonial dos dois países, com Portugal ficando com as terras a leste e a Espanha com as terras a oeste.</t>
+          <t>A fragmentação política foi causada pelas disputas internas entre as elites criollas pelo poder, que resultaram em uma série de conflitos e divisões territoriais. As elites criollas locais queriam garantir seu domínio sem se submeter a um poder superior, o que levou à formação de múltiplos estados-nacionais.</t>
         </is>
       </c>
       <c r="I922" t="inlineStr">
@@ -52525,47 +52644,51 @@
       <c r="K922" t="inlineStr"/>
       <c r="L922" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="923">
       <c r="A923" t="inlineStr">
         <is>
-          <t>Sua primeira viagem à Índia foi iniciada em 1497 e, no ano seguinte, o navegante português cruzou o cabo da Boa Esperança e alcançou seu destino. Chegar às Índias era importante pois apenas lá os portugueses podiam conseguir especiarias como pimenta e noz-moscada, artigos que, na Europa, valiam tanto quanto prata e ouro. O caminho marítimo para o Oriente aberto por Vasco da Gama ajudaria Portugal a se tornar uma potência mundial.
-Disponível em: https://super.abril.com.br/mundo-estranho/o-que-foram-as-grandes-navegacoes. Acesso em: 13 dez. 2024.
-A viagem de Vasco da Gama foi importante pelo fato de que</t>
+          <t>Mesmo países que apresentavam taxas de crescimento econômico bastante elevadas, tais como os latino-americanos, cuja independência política tinha sido alcançada no princípio do século XIX, estavam limitados pela profundidade da sua dependência econômica e política da economia internacional. Seu crescimento econômico parecia destinado a acumular miséria, analfabetismo e uma distribuição de renda desastrosa.
+SANTOS, Theotônio dos. A TEORIA DA DEPENDÊNCIA:UM BALANÇO HISTÓRICO E TEÓRICO. Disponível em: https://edisciplinas.usp.br/pluginfile.php/283339/mod_resource/content/1/ateoriadadependencia.pdf. Acesso em: 17 dez. 2024.
+Qual foi a consequência das políticas agroexportadoras na América Latina no século XIX?</t>
         </is>
       </c>
       <c r="B923" t="inlineStr">
         <is>
-          <t>abriu uma nova rota de comércio para a Índia.</t>
+          <t>Redução da desigualdade social.</t>
         </is>
       </c>
       <c r="C923" t="inlineStr">
         <is>
-          <t>determinou a supremacia espanhola nos mares.</t>
+          <t>Fortalecimento das indústrias locais.</t>
         </is>
       </c>
       <c r="D923" t="inlineStr">
         <is>
-          <t>representou a chegada dos portugueses ao Novo Mundo.</t>
+          <t>Independência econômica total das ex-colônias.</t>
         </is>
       </c>
       <c r="E923" t="inlineStr">
         <is>
-          <t>tornou a colonização do continente americano desnecessária.</t>
-        </is>
-      </c>
-      <c r="F923" t="inlineStr"/>
+          <t>Dependência das potências capitalistas europeias.</t>
+        </is>
+      </c>
+      <c r="F923" t="inlineStr">
+        <is>
+          <t>Unidade política entre os países latino-americanos.</t>
+        </is>
+      </c>
       <c r="G923" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="H923" t="inlineStr">
         <is>
-          <t>A viagem de Vasco da Gama foi importante porque abriu uma nova rota marítima para a Índia, através do Cabo da Boa Esperança, permitindo que os portugueses estabelecessem um comércio direto de especiarias como pimenta e noz-moscada, que eram extremamente valiosas na Europa.</t>
+          <t>A política agroexportadora manteve a dependência das ex-colônias às potências capitalistas europeias, uma vez que as economias locais foram estruturadas para fornecer matérias-primas e produtos agrícolas para os mercados europeus. Isso impediu a diversificação econômica e a industrialização independente.</t>
         </is>
       </c>
       <c r="I923" t="inlineStr">
@@ -52581,47 +52704,50 @@
       <c r="K923" t="inlineStr"/>
       <c r="L923" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="924">
       <c r="A924" t="inlineStr">
         <is>
-          <t>Bartolomeu Dias liderou a primeira expedição a atravessar, em 1488, o cabo das Tormentas, mais tarde rebatizado de cabo da Boa Esperança (no extremo sul da África). O curioso é que Bartolomeu Dias não percebeu o feito, pois passou pelo cabo durante uma forte tempestade. Poderia ter chegado à Índia, mas um motim da tripulação o obrigou a retornar a Portugal.
-Disponível em: https://super.abril.com.br/mundo-estranho/o-que-foram-as-grandes-navegacoes. Acesso em: 13 dez. 2024. (Adaptado).
-A expedição de Bartolomeu Dias representou a(o)</t>
+          <t>Tratado França-Haiti, 1825. Disponível em: https://commons.wikimedia.org/wiki/File:Trait%C3%A9_France_Ha%C3%AFti_1825.jpg. Acesso em: 17 dez. 2024.
+A imagem retrata um episódio desvantajoso para o Haiti no início do século XIX. Quais foram os principais desafios enfrentados pelo Haiti após sua independência?</t>
         </is>
       </c>
       <c r="B924" t="inlineStr">
         <is>
-          <t>fracasso dos objetivos expansionistas de Portugal.</t>
+          <t>Terras pouco produtivas e greves urbanas.</t>
         </is>
       </c>
       <c r="C924" t="inlineStr">
         <is>
-          <t>abandono por parte de Portugal de tentar chegar à Índia.</t>
+          <t>Desastres naturais e endividamento externo.</t>
         </is>
       </c>
       <c r="D924" t="inlineStr">
         <is>
-          <t>união dos países europeus no projeto de expansão marítima.</t>
+          <t>Isolamento diplomático e a indenização à França.</t>
         </is>
       </c>
       <c r="E924" t="inlineStr">
         <is>
-          <t>confirmação da viabilidade de uma rota marítima para a Índia.</t>
-        </is>
-      </c>
-      <c r="F924" t="inlineStr"/>
+          <t>Ocupação militar pelos Estados Unidos e doenças.</t>
+        </is>
+      </c>
+      <c r="F924" t="inlineStr">
+        <is>
+          <t>Revoltas contra a escravidão e fragmentação política.</t>
+        </is>
+      </c>
       <c r="G924" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H924" t="inlineStr">
         <is>
-          <t>A expedição de Bartolomeu Dias, ao atravessar o Cabo da Boa Esperança, confirmou que era possível navegar ao redor do sul da África, abrindo a perspectiva de uma rota marítima para a Índia, ainda que Dias não tenha completado a viagem até lá.</t>
+          <t>O Haiti enfrentou sérios problemas de isolamento diplomático, pois muitos países, especialmente as potências coloniais, estavam relutantes em reconhecer a independência de uma nação fundada por ex-escravos. Além disso, teve que pagar uma indenização massiva à França para ser reconhecido como uma nação independente, o que causou um endividamento significativo.</t>
         </is>
       </c>
       <c r="I924" t="inlineStr">
@@ -52634,50 +52760,57 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K924" t="inlineStr"/>
+      <c r="K924" t="inlineStr">
+        <is>
+          <t>8a_ph10_his_03.jpg</t>
+        </is>
+      </c>
       <c r="L924" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="925">
       <c r="A925" t="inlineStr">
         <is>
-          <t>Foram os mouros que aperfeiçoaram o astrolábio, instrumento de origem grega que permite a orientação em alto-mar pela observação de estrelas. Sua ciência náutica teve grande influência sobre a Escola de Sagres, em Portugal, de onde saíram os oficiais e marinheiros das navegações da Era dos Descobrimentos
-Disponível em: https://super.abril.com.br/mundo-estranho/como-foi-a-ocupacao-moura-da-peninsula-iberica. Acesso em: 13 dez. 2024.
-O texto deixa evidente a(o)</t>
+          <t>Disponível em: https://commons.wikimedia.org/wiki/File:Batalla_de_Cerro_Gordo.jpg. Acesso em: 17 dez. 2024.
+Após a independência do México, o país teve que lidar com um conflito retratado na imagem acima, que teve como consequência a</t>
         </is>
       </c>
       <c r="B925" t="inlineStr">
         <is>
-          <t>atraso tecnológico português no contexto das Grandes Navegações.</t>
+          <t>perda de metade das terras do país para os Estados Unidos.</t>
         </is>
       </c>
       <c r="C925" t="inlineStr">
         <is>
-          <t>acaso por trás da chegada dos portugueses ao continente americano.</t>
+          <t>união política entre México e os estados do sul dos EUA.</t>
         </is>
       </c>
       <c r="D925" t="inlineStr">
         <is>
-          <t>influência dos avanços tecnológicos muçulmanos no pioneirismo português.</t>
+          <t>formação de uma república autônoma no norte do país.</t>
         </is>
       </c>
       <c r="E925" t="inlineStr">
         <is>
-          <t>parceria firmada entre a Espanha e Portugal para a realização das expedições.</t>
-        </is>
-      </c>
-      <c r="F925" t="inlineStr"/>
+          <t>abolição da escravidão em todo o território mexicano.</t>
+        </is>
+      </c>
+      <c r="F925" t="inlineStr">
+        <is>
+          <t>expansão mexicana por toda a América do Norte.</t>
+        </is>
+      </c>
       <c r="G925" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H925" t="inlineStr">
         <is>
-          <t>O texto menciona que os mouros aperfeiçoaram o astrolábio e que sua ciência náutica teve grande influência sobre a Escola de Sagres em Portugal. Essa influência tecnológica foi crucial para o sucesso dos portugueses nas navegações da Era dos Descobrimentos.</t>
+          <t>Após a Guerra Mexicano-Americana, concluída em 1848 com o Tratado de Guadalupe Hidalgo, o México perdeu aproximadamente metade do seu território para os Estados Unidos, incluindo os atuais estados da Califórnia, Nevada, Utah, Arizona, Novo México, Texas, e partes do Colorado, Wyoming, Kansas e Oklahoma.</t>
         </is>
       </c>
       <c r="I925" t="inlineStr">
@@ -52690,50 +52823,58 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K925" t="inlineStr"/>
+      <c r="K925" t="inlineStr">
+        <is>
+          <t>8a_ph10_his_04.jpg</t>
+        </is>
+      </c>
       <c r="L925" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="926">
       <c r="A926" t="inlineStr">
         <is>
-          <t>O navegador genovês Cristóvão Colombo (1451-1506) nasceu em uma família pobre e começou a navegar cedo. Comandou um navio pela primeira vez em 1473, aos 22 anos. Ao retornar de sua primeira viagem continental, em 1493, recebe o título de “Vice-Rei e governador das Terras Firmes e Ilhas Descobertas e por Descobrir”. Apesar disso, morreu pobre e esquecido. Seu diário só foi recuperado por Fernando, seu filho, após a sua morte.
-Disponível em: https://super.abril.com.br/ciencia/diarios-da-descoberta-da-america. Acesso em: 13 dez. 2024.
-A importância histórica de Cristóvão Colombo se encontra no fato de que ele</t>
+          <t>O historiador Felipe Pigna concorda que os motivos que terminaram com os negros na Argentina devem ser procurados na utilização da população masculina como “bucha de canhão” nas guerras da Independência, as civis que vieram a seguir e, por último, a ofensiva contra o Paraguai (1865-1871), além das epidemias de cólera (1861) e de febre amarela (1871) que provocaram grande mortandade entre os mais pobres, entre eles os afro-argentinos. “Mas, além disso, a natalidade era muito baixa, inclusive em comparação com outras sociedades latino-americanas. Os amos evitavam a todo custo o casamento de um escravo, assim como a gravidez de uma escrava, com o argumento de que isso a impedia de prestar todos os serviços para os quais foi comprada, além do risco de morrer em um problema no parto”, afirma.
+Disponível em: https://brasil.elpais.com/brasil/2017/01/07/internacional/1483795840_886159.html. Acesso em: 17 dez. 2024.
+Quais foram as políticas adotadas pela elite argentina para reduzir a população negra no século XIX?</t>
         </is>
       </c>
       <c r="B926" t="inlineStr">
         <is>
-          <t>comandou a primeira expedição europeia a chegar na América.</t>
+          <t>Expulsão do país como punição pelo apoio à Espanha.</t>
         </is>
       </c>
       <c r="C926" t="inlineStr">
         <is>
-          <t>foi o primeiro europeu a navegar a pelo Cabo da Boa Esperança.</t>
+          <t>Promoção da imigração europeia para trabalhar nas fábricas.</t>
         </is>
       </c>
       <c r="D926" t="inlineStr">
         <is>
-          <t>liderou os cristãos nas guerras de Reconquista contra os mouros.</t>
+          <t>Manutenção de boas relações entre as raças visando a miscigenação.</t>
         </is>
       </c>
       <c r="E926" t="inlineStr">
         <is>
-          <t>protagonizou o surgimento das igrejas protestantes no século XVI.</t>
-        </is>
-      </c>
-      <c r="F926" t="inlineStr"/>
+          <t>Envolvimento dos afro-argentinos como linha de frente em guerras.</t>
+        </is>
+      </c>
+      <c r="F926" t="inlineStr">
+        <is>
+          <t>Concessão de território separado da Argentina exclusivo para negros.</t>
+        </is>
+      </c>
       <c r="G926" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="H926" t="inlineStr">
         <is>
-          <t>Cristóvão Colombo é historicamente famoso por comandar a primeira expedição europeia reconhecida a chegar na América em 1492, financiada pelos reis católicos da Espanha. Sua viagem marcou o início do contato sustentado entre a Europa e as Américas.</t>
+          <t>O texto aponta para o uso da população afro-argentina como “bucha de canhão” nas guerras da Independência, nas guerras civis e na ofensiva contra o Paraguai, contribuindo significantemente para a redução da população negra na Argentina do século XIX.</t>
         </is>
       </c>
       <c r="I926" t="inlineStr">
@@ -52749,52 +52890,51 @@
       <c r="K926" t="inlineStr"/>
       <c r="L926" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="927">
       <c r="A927" t="inlineStr">
         <is>
-          <t>E assim, não tendo a quem vencer na terra, 
-Vai cometer as ondas do Oceano 
-Este é o primeiro Rei que se desterra 
-Da pátria, por fazer que o Africano 
-Conheça, pelas armas, quanto excede 
-A lei de Cristo à lei de Mafamede
-CAMÕES. Os Lusíadas, IV, 48.
-Luís de Camões foi um dos maiores nome da literatura renascentista portuguesa. A temática do soneto de Camões apresentada acima se relaciona, na história de Portugal, com a/as</t>
+          <t>As independências não foram revoluções sociais porque as facções mais fortes das burguesias nativas nunca pretenderam mudar as relações de produção existentes, ou estender os direitos democráticos aos oprimidos, e sim tirar o controle das instituições políticas e militares dos espanhóis.
+Disponível em: https://www.fflch.usp.br/73202. Acesso em: 16 jan. 2025.
+A partir do texto, é correto afirmar que as lutas das independências latino-americanos</t>
         </is>
       </c>
       <c r="B927" t="inlineStr">
         <is>
-          <t>conquista do continente africano através das Cruzadas.</t>
+          <t>provocaram a ruptura com a metrópole, mas mantiveram boa parte das estruturas sociais coloniais.</t>
         </is>
       </c>
       <c r="C927" t="inlineStr">
         <is>
-          <t>à conquista de Ceuta como um marco da supremacia de Portugal e abertura para a expansão marítima.</t>
+          <t>foram comandadas pelos setores populares, mas fracassaram após serem traídas pelas elites criollas.</t>
         </is>
       </c>
       <c r="D927" t="inlineStr">
         <is>
-          <t>guerras de Reconquista contra os mouros do Norte da África.</t>
+          <t>causaram um fortalecimento da exploração colonial, mas possibilitaram a libertação dos escravizados.</t>
         </is>
       </c>
       <c r="E927" t="inlineStr">
         <is>
-          <t>expansão pelo continente europeu para derrubar os monarcas rivais.</t>
-        </is>
-      </c>
-      <c r="F927" t="inlineStr"/>
+          <t>foram realizadas por representantes das elites coloniais, mas proporcionaram a igualdade social para toda a população.</t>
+        </is>
+      </c>
+      <c r="F927" t="inlineStr">
+        <is>
+          <t>resultaram na proclamação de diferentes repúblicas, mas que se tornaram monarquias por influência do Império do Brasil.</t>
+        </is>
+      </c>
       <c r="G927" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H927" t="inlineStr">
         <is>
-          <t>Camões foi um reconhecido escritor português que em diversos sonetos tratou temas relativos à realidade em que vivia. Um traço marcante de Portugal no século XV foi a expansão marítima, resultado, entre outros fatores, da centralização política na figura do rei.</t>
+          <t>O texto destaca que as independências na América Latina não foram consideradas revoluções sociais porque as facções mais fortes das burguesias nativas não tinham a intenção de mudar as relações de mudar as estruturas sociais, mas apenas tirar o controle das instituições políticas e militares dos espanhóis. Assim, essas lutas de independência conseguiram romper com a metrópole colonial, mas mantiveram muitas das estruturas sociais e econômicas coloniais inalteradas, perpetuando as desigualdades existentes.</t>
         </is>
       </c>
       <c r="I927" t="inlineStr">
@@ -52810,39 +52950,44 @@
       <c r="K927" t="inlineStr"/>
       <c r="L927" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="928">
       <c r="A928" t="inlineStr">
         <is>
-          <t>Observe o mapa a seguir:
-Instituto Geográfico Nacional, Google, Geo-Basis-DE (BKG), 2009. Disponível em: https://www.google.com.br/maps/. Acesso em: 08 maio 2020.
-O mapa acima nos permite entender um fator que explica o pioneirismo de Portugal nas Grandes Navegações, que foi o(a)</t>
+          <t>Entre 1878 e 1879, o Exército argentino foi levado aos pampas para, nas palavras do ministro da guerra e futuro presidente, Julio Roca, “expulsar os índios do deserto que se trata de conquistar, para não deixar um só inimigo na retaguarda, submetendo-os pela perseguição ou pela força, sem nos apressar a extirpar o mal pela raiz e destruir esses ninhos de bandoleiros”.
+A chamada “Conquista do Deserto”, como dizem os argentinos brancos, foi essa sequência de operações militares em que os indígenas foram deliberadamente eliminados.
+Disponível em: https://diplomatique.org.br/elites-argentinas-e-os-indigenas/. Acesso em: 16 jan. 2025.
+O texto evidencia que a formação do Estado-nacional argentino, no século XIX, foi marcado pelo(a)</t>
         </is>
       </c>
       <c r="B928" t="inlineStr">
         <is>
-          <t>fácil acesso ao Oceano Atlântico.</t>
+          <t>perseguição e massacre dos povos indígenas.</t>
         </is>
       </c>
       <c r="C928" t="inlineStr">
         <is>
-          <t>fortalecimento da nobreza feudal.</t>
+          <t>coexistência pacífica com as comunidades indígenas.</t>
         </is>
       </c>
       <c r="D928" t="inlineStr">
         <is>
-          <t>enfraquecimento da autoridade real.</t>
+          <t>ascensão das lideranças indígenas ao governo do país.</t>
         </is>
       </c>
       <c r="E928" t="inlineStr">
         <is>
-          <t>concorrência da monarquia espanhola.</t>
-        </is>
-      </c>
-      <c r="F928" t="inlineStr"/>
+          <t>aliança entre indígenas e espanhóis contra as elites coloniais.</t>
+        </is>
+      </c>
+      <c r="F928" t="inlineStr">
+        <is>
+          <t>criação de regiões administrativas autônomas para os indígenas.</t>
+        </is>
+      </c>
       <c r="G928" t="inlineStr">
         <is>
           <t>A</t>
@@ -52850,7 +52995,7 @@
       </c>
       <c r="H928" t="inlineStr">
         <is>
-          <t>A mapa apresenta como Portugal se encontrava com acesso direito ao Oceano Atlântico. Esse fator geográfico, somado com a experiência prévia que os portugueses tinham com as atividades marítimas, facilitaram o seu lançamento ultramarino.</t>
+          <t>O texto descreve como, entre 1878 e 1879, o Exército argentino realizou uma série de operações militares nas quais os indígenas foram deliberadamente eliminados através de perseguição ou força. Isso demonstra que a formação do Estado-nacional argentino no século XIX foi marcada pela perseguição e massacre dos povos indígenas.</t>
         </is>
       </c>
       <c r="I928" t="inlineStr">
@@ -52863,45 +53008,46 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K928" t="inlineStr">
-        <is>
-          <t>ph10_his_07.png</t>
-        </is>
-      </c>
+      <c r="K928" t="inlineStr"/>
       <c r="L928" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="929">
       <c r="A929" t="inlineStr">
         <is>
-          <t>A representação a seguir foi feita por um italiano ao imaginar os seres míticos que poderiam habitar as regiões do Novo Mundo.
-Sobre a relação entre as crenças em seres como os da imagem e a expansão marítima, é correto afirmar que os viajantes do século XV</t>
+          <t>A maior das repercussões da revolução haitiana ocorreu no continente americano, ao destacar para os milhões de escravizados nas colônias portuguesas, espanholas, francesas e inglesas, além dos EUA que mantinham a escravidão, que os negros eram capazes de lutar por sua liberdade e constituir o primeiro estado livre das Américas.
+Disponível em: https://www.fflch.usp.br/36495#:~:text=Em%2022%20de%20agosto%20de,independ%C3%AAncia%20do%20Haiti%20foi%20proclamada.. Acesso em: 16 jan. 2025.
+A repercussão da Revolução Haitiana, mencionada no excerto, provocou a(o)</t>
         </is>
       </c>
       <c r="B929" t="inlineStr">
         <is>
-          <t>exploraram os mares sem receio, pois não tinham a tradição de acreditar em seres míticos, como sereias.</t>
+          <t>inimizade dos escravizados da América por não se verem representados pelos haitianos.</t>
         </is>
       </c>
       <c r="C929" t="inlineStr">
         <is>
-          <t>interromperam suas rotas ao descobrirem espécies que confirmavam seus medos de animais fantásticos no mar.</t>
+          <t>paz entre as elites brancas e os negros escravizados nas demais colônias do continente.</t>
         </is>
       </c>
       <c r="D929" t="inlineStr">
         <is>
-          <t>acompanharam o teocentrismo que se fortalecia na Europa e se recusaram a viajar para regiões que tivessem sereias.</t>
+          <t>união das potências coloniais contra os revolucionários e a derrota da Revolução.</t>
         </is>
       </c>
       <c r="E929" t="inlineStr">
         <is>
-          <t>superaram receios sobre esses seres conforme inovações técnicas desvendavam mitos como monstros e precipícios no fim do oceano.</t>
-        </is>
-      </c>
-      <c r="F929" t="inlineStr"/>
+          <t>constante ameaça de intervenção no país por parte das nações europeias.</t>
+        </is>
+      </c>
+      <c r="F929" t="inlineStr">
+        <is>
+          <t>apoio por parte dos europeus à causa abolicionista nas demais colônias.</t>
+        </is>
+      </c>
       <c r="G929" t="inlineStr">
         <is>
           <t>D</t>
@@ -52909,7 +53055,7 @@
       </c>
       <c r="H929" t="inlineStr">
         <is>
-          <t>Mitos sobre perigos de se viajar pelo oceano, como seres fantásticos e precipícios ao fim do mar, eram crenças que amedrontavam a população europeia. No entanto, conforme a mentalidade do continente tornou-se mais racionalista e as inovações técnicas permitiram que as viagens se tornassem mais seguras, essas crenças se desmistificaram e a exploração dos oceanos se popularizou.</t>
+          <t>A Revolução Haitiana, que resultou na independência do Haiti e na abolição da escravidão no país, teve um grande impacto no continente americano e no mundo. O movimento alarmou as potências coloniais europeias que ainda dependiam da escravidão em suas colônias. Como resultado, o Haiti enfrentou uma constante ameaça de intervenção e ataques por parte das nações europeias, que temiam que o exemplo haitiano pudesse inspirar revoltas similares em suas próprias colônias.</t>
         </is>
       </c>
       <c r="I929" t="inlineStr">
@@ -52922,54 +53068,55 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K929" t="inlineStr">
-        <is>
-          <t>ph10_his_08.png</t>
-        </is>
-      </c>
+      <c r="K929" t="inlineStr"/>
       <c r="L929" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="930">
       <c r="A930" t="inlineStr">
         <is>
-          <t>As zonas costeiras eram abastecidas por peixe fresco, o que não sucedia nas zonas interiores – onde algum ainda chegava às escassas elites –, apesar de se recorrer ao peixe de água doce. Havia que o importar, como sucedia com a sardinha, abundante em toda a costa, mais acessível e transportada salgada, mas que não chegava para as necessidades da procura. Há que ver, também, que o bacalhau, uma vez curado adequadamente, teria uma maior capacidade de conservação. Outros pequenos peixes, [...] ou o polvo seco [...] não tiveram uma difusão comparável à escala do país. O bacalhau tornou-se uma mercadoria importante, muitos séculos antes de a ciência moderna o valorizar como alimento excecional devido à sua carne branca e firme, quase isenta de gordura, que quando seca é um concentrado de proteínas.
-SOBRAL, José Manuel; RODRIGUES, Patrícia. O fiel amigo: o bacalhau e a identidade portuguesa. Etnográfica, Lisboa, v. 17, n. 3, p. 621. Disponível em: http://www.scielo.mec.pt/scielo.php?script=sci_arttext&amp;pid=S0873-65612013000300010&amp;lang=pt. Acesso em: 08 maio 2020.
-A proximidade da culinária portuguesa com o consumo de peixes expõe um fator para o pioneirismo português no processo de expansão marítima, que foi/foram</t>
+          <t>O fato é que a história do austríaco Maximiliano de Habsburgo e sua mulher Carlota, no chamado Segundo Império mexicano, foi um episódio trágico da história do México — e um dos mais curiosos da América Latina.
+Primo do imperador brasileiro Dom Pedro 2º, Maximiliano era admirador do Brasil e sonhou com uma aliança regional entre os dois países, o que nunca se materializou. Jovem liberal, sabia pouco da realidade política no país que aceitou governar.
+Disponível em: https://www.bbc.com/portuguese/internacional-59394423. Acesso em: 16 jan. 2025.
+A ascensão de Maximiliano de Habsburgo ao trono do México deve ser compreendido como um(a)</t>
         </is>
       </c>
       <c r="B930" t="inlineStr">
         <is>
-          <t>o controle de todo o litoral europeu.</t>
+          <t>tentativa de interferência francesa na política mexicana.</t>
         </is>
       </c>
       <c r="C930" t="inlineStr">
         <is>
-          <t>as alianças feitas com os povos do Novo Mundo.</t>
+          <t>expressão do descontentamento dos mexicanos com a República.</t>
         </is>
       </c>
       <c r="D930" t="inlineStr">
         <is>
-          <t>a experiência com atividades marítimas, como a pesca.</t>
+          <t>manifestação da frustração popular pela falta de representação política.</t>
         </is>
       </c>
       <c r="E930" t="inlineStr">
         <is>
-          <t>o princípio mercantilista que via nos pescados a fonte de riquezas.</t>
-        </is>
-      </c>
-      <c r="F930" t="inlineStr"/>
+          <t>esforço das elites locais para restaurar os vínculos coloniais com a Espanha.</t>
+        </is>
+      </c>
+      <c r="F930" t="inlineStr">
+        <is>
+          <t>sintoma das disputas políticas e territoriais entre o México e os Estados Unidos.</t>
+        </is>
+      </c>
       <c r="G930" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H930" t="inlineStr">
         <is>
-          <t>A prática da pesca demonstra a experiência que os portugueses tinham com as atividades marítimas. Isso lhes deu vantagem para realizar as Grandes Navegações, uma vez que já sabiam como conseguir alimento em alto mar.</t>
+          <t>A ascensão de Maximiliano de Habsburgo ao trono do México foi resultado de uma tentativa de interferência francesa na política mexicana. Napoleão III, então imperador da França, aproveitou a instabilidade política no México para expandir a influência francesa no continente americano. Maximiliano, que pouco conhecia a realidade política do México, foi escolhido como imperador do chamado Segundo Império Mexicano. Essa intervenção estrangeira foi amplamente impopular entre os mexicanos, o que resultou na deposição e na execução de Maximiliano e a proclamação de uma República.</t>
         </is>
       </c>
       <c r="I930" t="inlineStr">
@@ -52985,40 +53132,43 @@
       <c r="K930" t="inlineStr"/>
       <c r="L930" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="931">
       <c r="A931" t="inlineStr">
         <is>
-          <t>Além da experiência [...] dos navegantes, foram as velas latinas idealizadas pelos sábios da Escola de Sagres que ajudaram os aventureiros a atravessar o mar [...]. Os astrônomos e matemáticos da Escola de Sagres desenvolveram tabelas com a declinação dos astros, bem como eficientes instrumentos de navegação, como o astrolábio e a balestilha, usados para medir a posição dos astros e determinar a posição da embarcação.
-FILGUEIRAS, O. Vigia de ventos e ondas. Revista Fapesp, ed. 62, mar. 2000. (Adaptado).
-Disponível em: https://revistapesquisa.fapesp.br/2001/03/01/vigia-de-ventos-e-ondas/​. Acesso em: 8 maio 2020.
-O texto trata da controversa Escola de Sagres que teria sido fundada por D. Henrique. De acordo com o texto e seus conhecimentos, a Escola de Sagres representou um/a</t>
+          <t>Em geral, o que se pode perceber foi que muitos militares que lutaram nas guerras de independência assumiram a autoridade política das regiões libertadas. Aí está a influência direta das guerras de independência para o surgimento desses personagens: foram delas que heróis militares ganharam poder e reconhecimento por parte da população.
+Disponível em: https://abrir.me/qwLkq. Acesso em: 16 jan. 2025.
+O texto descreve o surgimento de uma categoria de indivíduos que se destacou no período pós-independências, conhecidos como</t>
         </is>
       </c>
       <c r="B931" t="inlineStr">
         <is>
-          <t>grande mercado de pescados portugueses.</t>
+          <t>reis.</t>
         </is>
       </c>
       <c r="C931" t="inlineStr">
         <is>
-          <t>ponto de encontro de navegadores lusitanos.</t>
+          <t>caudilhos.</t>
         </is>
       </c>
       <c r="D931" t="inlineStr">
         <is>
-          <t>universidade onde o principal curso era a navegação.</t>
+          <t>presidentes.</t>
         </is>
       </c>
       <c r="E931" t="inlineStr">
         <is>
-          <t>movimento criado por jesuítas que combatiam a navegação.</t>
-        </is>
-      </c>
-      <c r="F931" t="inlineStr"/>
+          <t>imperadores.</t>
+        </is>
+      </c>
+      <c r="F931" t="inlineStr">
+        <is>
+          <t>libertadores.</t>
+        </is>
+      </c>
       <c r="G931" t="inlineStr">
         <is>
           <t>B</t>
@@ -53026,7 +53176,7 @@
       </c>
       <c r="H931" t="inlineStr">
         <is>
-          <t>Não existem evidências de que de fato tenha existido fisicamente uma Escola de Sagres para navegadores, porém é sabido que uma vila foi construída com o intuito de dar apoio aos navegadores portugueses e se constituiu como um local de troca de experiências e conhecimentos entre os frequentadores.</t>
+          <t>Esses indivíduos são conhecidos como caudilhos, líderes que surgiram nas regiões recém-independentes da América Latina e que obtiveram um poder político e militar significativos, muitas vezes governando com autoritarismo e baseando sua autoridade no apoio popular e no controle militar.</t>
         </is>
       </c>
       <c r="I931" t="inlineStr">
@@ -53042,48 +53192,52 @@
       <c r="K931" t="inlineStr"/>
       <c r="L931" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="932">
       <c r="A932" t="inlineStr">
         <is>
-          <t>Pesquisadores japoneses desenvolvem plástico que se desfaz no oceano
-Pesquisadores do Centro de Ciência de Materiais Emergentes (Cems, na sigla em inglês), do instituto japonês Riken, desenvolveram um novo plástico biodegradável, que, além de ser durável e reciclável, decompõe-se quando em contato com a água do mar.
-Disponível em: https://www.jornaljoca.com.br/pesquisadores-japoneses-desenvolvem-plastico-que-se-desfaz-no-oceano/. Acesso em 18 dez. 2024.
-O pronome relativo “que” possui algumas variações. Por qual forma desse pronome o termo em destaque pode ser substituído?</t>
+          <t>Impactos da pandemia na educação no Brasil
+"Foi difícil. Eu trabalho home office e conciliar aula online com o trabalho foi complicado porque não tive apoio do meu esposo, porque ele trabalhou direto na pandemia. Eu tive que adaptar, acordar mais cedo para depois fazer tudo que eu tinha que fazer para entregar no dia e ajudar ela. Agora ela está se desenvolvendo bem, só que não concordo com as aulas online, ao invés de ajudar só prejudicou. O esforço maior foi meu."  (Mulher, Grupo Misto 41 a 60 anos – SP)
+Disponível em: https://www12.senado.leg.br/institucional/datasenado/materias/pesquisas/impactos-da-pandemia-na-educacao-no-brasil. Acesso em 19 de dez. 2024.
+No trecho acima, a palavra "meu" exerce a função de</t>
         </is>
       </c>
       <c r="B932" t="inlineStr">
         <is>
-          <t>O qual.</t>
+          <t>verbo.</t>
         </is>
       </c>
       <c r="C932" t="inlineStr">
         <is>
-          <t>Em que.</t>
+          <t>sujeito.</t>
         </is>
       </c>
       <c r="D932" t="inlineStr">
         <is>
-          <t>No qual.</t>
+          <t>predicado.</t>
         </is>
       </c>
       <c r="E932" t="inlineStr">
         <is>
-          <t>Pelo qual.</t>
-        </is>
-      </c>
-      <c r="F932" t="inlineStr"/>
+          <t>adjunto adnominal.</t>
+        </is>
+      </c>
+      <c r="F932" t="inlineStr">
+        <is>
+          <t>complemento nominal.</t>
+        </is>
+      </c>
       <c r="G932" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="H932" t="inlineStr">
         <is>
-          <t>O pronome relativo "o qual" pode substituir "que" na frase sem alterar o sentido, pois ambos se referem ao "plástico biodegradável" mencionado anteriormente. Essa substituição mantém a clareza e coesão do texto, sendo uma variação adequada do pronome relativo "que".</t>
+          <t>No trecho "O esforço maior foi meu", a palavra "meu" exerce a função de adjunto adnominal. Um adjunto adnominal é um termo acessório da oração que se junta a um substantivo para caracterizá-lo ou determiná-lo, indicando posse, qualidade, quantidade, entre outras características. No caso específico, "meu" é um pronome possessivo que está qualificando o substantivo "esforço", indicando a quem pertence o esforço. Assim, "meu" está fornecendo uma informação adicional sobre o substantivo "esforço", especificando que o esforço pertence à pessoa que está falando. Essa função de qualificação e determinação do substantivo é exatamente o que define um adjunto adnominal.</t>
         </is>
       </c>
       <c r="I932" t="inlineStr">
@@ -53099,47 +53253,51 @@
       <c r="K932" t="inlineStr"/>
       <c r="L932" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="933">
       <c r="A933" t="inlineStr">
         <is>
-          <t>Ao fundo, por trás do balcão, estava sentada uma mulher, cujo rosto amarelo e bexiguento não se destacava logo, à primeira vista; mas logo que se destacava era um espetáculo curioso.
-ASSIS, Machado de. Obra Completa. Disponível em: https://www.dominiopublico.gov.br/download/texto/bv000003.pdf. Acesso em: 19 dez. 2024.
-No excerto acima, o pronome relativo "cujo" estabelece uma relação entre as palavras</t>
+          <t>Senado proíbe celular em escolas do ensino infantil, fundamental e médio
+Disponível em: https://www12.senado.leg.br/radio/1/noticia/2024/12/18/senado-aprova-proibicao-do-uso-de-celular-e-tablets-por-alunos-do-ensino-infantil-fundamental-e-medio. Acesso em 19 de dez. 2024.
+No título da notícia, exerce a função de adjunto adnominal a palavra:</t>
         </is>
       </c>
       <c r="B933" t="inlineStr">
         <is>
-          <t>"mulher” e “bexiguento”.</t>
+          <t>Em</t>
         </is>
       </c>
       <c r="C933" t="inlineStr">
         <is>
-          <t>“mulher” e “amarelo”.</t>
+          <t>Senado</t>
         </is>
       </c>
       <c r="D933" t="inlineStr">
         <is>
-          <t>“mulher” e “balcão”.</t>
+          <t>Proíbe</t>
         </is>
       </c>
       <c r="E933" t="inlineStr">
         <is>
-          <t>“mulher” e “rosto”.</t>
-        </is>
-      </c>
-      <c r="F933" t="inlineStr"/>
+          <t>Celular</t>
+        </is>
+      </c>
+      <c r="F933" t="inlineStr">
+        <is>
+          <t>Fundamental</t>
+        </is>
+      </c>
       <c r="G933" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="H933" t="inlineStr">
         <is>
-          <t>O pronome relativo "cujo" é utilizado para indicar uma relação de posse entre dois substantivos. No excerto, "cujo" estabelece essa relação entre "mulher" e "rosto", indicando que o rosto pertence à mulher. O uso de "cujo" é apropriado para mostrar que o rosto, descrito como "amarelo e bexiguento", é uma característica da mulher sentada por trás do balcão.</t>
+          <t>No título "Senado proíbe celular em escolas do ensino infantil, fundamental e médio", a palavra "fundamental" exerce a função de adjunto adnominal porque está qualificando o substantivo "ensino". O adjunto adnominal é um termo acessório da oração que tem a função de caracterizar ou determinar um substantivo, concordando com ele em gênero e número. No caso específico, "fundamental" está especificando o tipo de ensino ao qual a proibição se aplica, assim como "infantil" e "médio". Portanto, "fundamental" está atuando como um adjetivo que complementa o substantivo "ensino", caracterizando-o e, por isso, é considerado um adjunto adnominal.</t>
         </is>
       </c>
       <c r="I933" t="inlineStr">
@@ -53155,58 +53313,51 @@
       <c r="K933" t="inlineStr"/>
       <c r="L933" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="934">
       <c r="A934" t="inlineStr">
         <is>
-          <t>Canção do Exílio
-Minha terra tem palmeiras,
-Onde canta o Sabiá;
-As aves, que aqui gorjeiam,
-Não gorjeiam como lá.
-[…]
-Não permita Deus que eu morra,
-Sem que eu volte para lá;
-Sem que disfrute os primores
-Que não encontro por cá;
-Sem qu'inda aviste as palmeiras,
-Onde canta o Sabiá. 
-DIAS, Gonçalves. Primeiros cantos. Disponível em: http://www.horizonte.unam.mx/brasil/gdias.html.
-No excerto acima, o pronome relativo "onde" substitui qual termo?</t>
+          <t>O dia de 28 de abril é o Dia da Educação. A data é um incentivo para que tenhamos consciência sobre a importância da educação – seja escolar, social ou familiar na vida dos indivíduos. Valores essenciais e convívio saudável se formam com uma boa educação.
+Disponível em: http://mdb-sc.org.br/artigo-de-opiniao-educacao-e-essencial/. Acesso em 19 de dez. 2024.
+No trecho acima, a expressão "da educação" em destaque</t>
         </is>
       </c>
       <c r="B934" t="inlineStr">
         <is>
-          <t>Aves.</t>
+          <t>retoma o sujeito “dia”.</t>
         </is>
       </c>
       <c r="C934" t="inlineStr">
         <is>
-          <t>Terra.</t>
+          <t>completa o sentido de um verbo.</t>
         </is>
       </c>
       <c r="D934" t="inlineStr">
         <is>
-          <t>Sabiá.</t>
+          <t>especifica uma data comemorativa.</t>
         </is>
       </c>
       <c r="E934" t="inlineStr">
         <is>
-          <t>Palmeiras.</t>
-        </is>
-      </c>
-      <c r="F934" t="inlineStr"/>
+          <t>indica o estado a que se refere o substantivo “dia”.</t>
+        </is>
+      </c>
+      <c r="F934" t="inlineStr">
+        <is>
+          <t>qualifica o substantivo, indicando a qual "dia" se refere.</t>
+        </is>
+      </c>
       <c r="G934" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="H934" t="inlineStr">
         <is>
-          <t>O pronome “onde” indica o local em que o sabiá canta. Além disso, é preciso atentar-se à interpretação do poema e depreender que o sabiá está cantando especificamente na palmeira.</t>
+          <t>A expressão "da educação" está qualificando o substantivo "dia", especificando a qual "dia" se refere. No contexto do trecho, "dia" é um substantivo genérico que poderia se referir a qualquer dia do ano. No entanto, ao adicionar a expressão "da educação", o substantivo passa a ser qualificado, indicando que se trata de um dia específico dedicado à educação.</t>
         </is>
       </c>
       <c r="I934" t="inlineStr">
@@ -53222,50 +53373,51 @@
       <c r="K934" t="inlineStr"/>
       <c r="L934" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="935">
       <c r="A935" t="inlineStr">
         <is>
-          <t>Não havia remédio senão ir.
-— Diga-lhe que vou.
-— Aonde? perguntou D. Plácida.
-— Onde ela disse que me espera.
-ASSIS, Machado de. Obra Completa. Disponível em: https://www.dominiopublico.gov.br/download/texto/bv000003.pdf. Acesso em: 19 dez. 2024.
-No excerto acima são usados os pronomes relativos "aonde" e "onde", que muitas vezes causam confusão na língua falada. Qual é a explicação para o uso desses pronomes, de acordo com a norma culta?</t>
+          <t>Diante disso, a falta da educação familiar reflete na aprendizagem escolar. É notável a criança que não teve a primeira educação, pois o comportamento na escolar torna-se reflexo dos atos tidos, vividos ou assistidos em casa. Consequentemente, na escola a criança terá dificuldades de convívio e aprendizagem, haja vista que a educação familiar deve ensinar a uma boa educação e a socialização da criança com as outras pessoas.
+Disponível em: https://www.unesc.net/portal/blog/ver/53/38073. Acesso em 19 de dez. 2024.
+No trecho acima, a expressão "da educação familiar"</t>
         </is>
       </c>
       <c r="B935" t="inlineStr">
         <is>
-          <t>"Aonde" e "onde" são iguais, por isso aparecem no mesmo excerto.</t>
+          <t>qualifica o substantivo "falta", indicando a sua origem.</t>
         </is>
       </c>
       <c r="C935" t="inlineStr">
         <is>
-          <t>"Aonde" é uma palavra mais formal, enquanto "onde" é usada no dia a dia.</t>
+          <t>especifica o modo como a "falta" ocorre.</t>
         </is>
       </c>
       <c r="D935" t="inlineStr">
         <is>
-          <t>"Aonde" é usado para começar uma pergunta, enquanto "onde" é só para respostas.</t>
+          <t>completa o sentido de um verbo.</t>
         </is>
       </c>
       <c r="E935" t="inlineStr">
         <is>
-          <t>"Aonde" é usado para indicar movimento para algum lugar, o pronome "onde", por sua vez, é usado para mostrar que algo está em um lugar.</t>
-        </is>
-      </c>
-      <c r="F935" t="inlineStr"/>
+          <t>indica o estado do sujeito "falta".</t>
+        </is>
+      </c>
+      <c r="F935" t="inlineStr">
+        <is>
+          <t>retoma o sujeito "educação".</t>
+        </is>
+      </c>
       <c r="G935" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H935" t="inlineStr">
         <is>
-          <t>"Aonde" é usado para indicar movimento em direção a um lugar, já "onde" mostra permanência em um lugar.</t>
+          <t>A expressão "da educação familiar" funciona como um adjunto adnominal, qualificando e especificando a origem da "falta". No contexto do trecho, a "falta" mencionada refere-se à ausência ou deficiência de educação que deveria ser fornecida pela família, ou seja, proporcionada no ambiente familiar.</t>
         </is>
       </c>
       <c r="I935" t="inlineStr">
@@ -53281,53 +53433,51 @@
       <c r="K935" t="inlineStr"/>
       <c r="L935" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="936">
       <c r="A936" t="inlineStr">
         <is>
-          <t>COMO O REMÉDIO CHEGA AONDE DÓI?
-O nosso corpo é totalmente coberto por vasos sanguíneos. Da mesma forma que se espalham pela nossa pele (basta um pequeno corte para vermos o sangue e constatarmos que eles estão ali!), eles também estão nos nossos demais órgãos. Assim, quando tomamos um medicamento, ele vai para a corrente sanguínea e percorre os órgãos do nosso corpo, através dos vasos sanguíneos, em busca do endereço da dor, ou seja, do lugar da nossa queixa.
-A célula que tiver o receptor específico para o medicamento vai recebê-lo. É como se fosse uma chave, que só entra na fechadura certa para ela! Ao abrir essa porta, temos então o efeito desejado para aliviar a dor ou o mal-estar. Em resumo: todo medicamento carrega um endereço certo onde deve chegar!
-Disponível em: https://chc.org.br/artigo/mundo-de-curiosidades-361/. Acesso em 18 dez. 2024.
-Leia as frases a seguir e escolha a alternativa que preenche corretamente com "onde" ou "aonde":
-1. O nosso corpo é coberto por vasos sanguíneos, ________ o sangue circula.
-2. O remédio procura ________ ele deve agir, percorrendo a corrente sanguínea.
-3. Você sabe ________ o remédio encontra o receptor específico?
-4. Os medicamentos vão ________ está a célula da queixa.</t>
+          <t>Um dos pontos fracos na educação da criança é a dificuldade que os pais encontram em dar limites aos seus filhos. Sem limites, o comportamento da criança muitas vezas deixa a desejar, podendo muitas vezes gritar com seus pais, chegando a agredi-los, quando contrariados ou quando não ganham o que querem. Ou mesmo, sendo mal-educados com os que convivem, ou pessoas mais velhas e nem tendo respeito e boas atitudes com as pessoas em geral.
+Disponível em: https://www.unesc.net/portal/blog/ver/53/38073. Acesso em 19 de dez. 2024.
+Na expressão em destaque, é possível substituir “da criança” sem prejuízo de sentido por</t>
         </is>
       </c>
       <c r="B936" t="inlineStr">
         <is>
-          <t>onde, aonde, onde, onde.</t>
+          <t>"infantil".</t>
         </is>
       </c>
       <c r="C936" t="inlineStr">
         <is>
-          <t>onde, onde, onde, aonde.</t>
+          <t>"criancice".</t>
         </is>
       </c>
       <c r="D936" t="inlineStr">
         <is>
-          <t>aonde, onde, onde, onde.</t>
+          <t>"de garotos".</t>
         </is>
       </c>
       <c r="E936" t="inlineStr">
         <is>
-          <t>onde, aonde, aonde, onde.</t>
-        </is>
-      </c>
-      <c r="F936" t="inlineStr"/>
+          <t>"infantilizada".</t>
+        </is>
+      </c>
+      <c r="F936" t="inlineStr">
+        <is>
+          <t>"de pequenos".</t>
+        </is>
+      </c>
       <c r="G936" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H936" t="inlineStr">
         <is>
-          <t>Nas três primeiras frases, a regência dos verbos não exige o uso da preposição “a”, por isso o correto seria o uso de “onde”, indicando um local e não a direção de um movimento. Já na última frase, o verbo “ir” (“vão”) pede o uso dessa preposição e, portanto, o pronome relativo correto seria “aonde”.</t>
+          <t>A palavra "infantil" funciona como um adjetivo que qualifica algum substantivo relacionado a crianças. No contexto da frase original, "Um dos pontos fracos na educação da criança é a dificuldade que os pais encontram em dar limites aos seus filhos", a expressão "da criança" refere-se à educação que é específica para crianças. Substituir "da criança" por "infantil" mantém o sentido original da frase, pois "educação infantil" é uma expressão comum e amplamente compreendida que se refere ao processo educativo voltado para crianças. As demais alternativas, como "criancice", "de garotos", "infantilizada" e "de pequenos", não se encaixam adequadamente no contexto, pois alteram o sentido ou não são expressões comumente usadas para descrever o tipo de educação mencionado.</t>
         </is>
       </c>
       <c r="I936" t="inlineStr">
@@ -53343,49 +53493,60 @@
       <c r="K936" t="inlineStr"/>
       <c r="L936" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="937">
       <c r="A937" t="inlineStr">
         <is>
-          <t>Se temos de esperar,
-que seja para colher a semente boa
-que lançamos hoje no solo da vida.
-CORALINA, Cora.
-O termo “que”, presente no 3º verso, classifica-se como</t>
+          <t>Aprenda a chamar a polícia
+Eu tenho o sono muito leve, e numa noite dessas notei que havia alguém andando sorrateiramente no quintal de casa. Levantei em silêncio e fiquei acompanhando os leves ruídos que vinham lá de fora, até ver uma silhueta passando pela janela do banheiro. Como minha casa era muito segura, com grades nas janelas e trancas internas nas portas, não fiquei muito preocupado, mas era claro que eu não ia deixar um ladrão ali, espiando tranquilamente.
+Liguei baixinho para a polícia, informei a situação e o meu endereço.
+Perguntaram-me se o ladrão estava armado ou se já estava no interior da casa. Esclareci que não e disseram-me que não havia nenhuma viatura por perto para ajudar, mas que iriam mandar alguém assim que fosse possível.
+Um minuto depois, liguei de novo e disse com a voz calma:
+— Oi, eu liguei há pouco porque tinha alguém no meu quintal. Não precisa mais ter pressa. Eu já matei o ladrão com um tiro da escopeta calibre 12, que tenho guardada em casa para estas situações. O tiro fez um estrago danado no cara!
+Passados menos de três minutos, estavam na minha rua cinco carros da polícia, um helicóptero, uma unidade do resgate, uma equipe de TV e a turma dos direitos humanos, que não perderiam isso por nada neste mundo.
+Eles prenderam o ladrão em flagrante, que ficava olhando tudo com cara de assombrado. Talvez ele estivesse pensando que aquela era a casa do Comandante da Polícia.
+[...]
+VERÍSSIMO, Luís Fernando. Aprenda a chamar a polícia. Disponível em: &lt;http://www.refletirpararefletir.com.br/4-cronicas-de-luis-fernando-verissimo&gt;.
+Acesso em: 1 jun. 2018.
+No trecho “e a turma dos direitos humanos, que não perderiam isso por nada neste mundo”, o adjunto adnominal destacado é da classe gramatical dos</t>
         </is>
       </c>
       <c r="B937" t="inlineStr">
         <is>
-          <t>artigo definido, pois indetermina o substantivo.</t>
+          <t>adjetivos.</t>
         </is>
       </c>
       <c r="C937" t="inlineStr">
         <is>
-          <t>advérbio, pois atribui uma circunstância ao verbo.</t>
+          <t>advérbios.</t>
         </is>
       </c>
       <c r="D937" t="inlineStr">
         <is>
-          <t>pronome relativo, pois refere-se a um termo anterior.</t>
+          <t>artigos.</t>
         </is>
       </c>
       <c r="E937" t="inlineStr">
         <is>
-          <t>pronome pessoal, pois designa a pessoa do discurso.</t>
-        </is>
-      </c>
-      <c r="F937" t="inlineStr"/>
+          <t>numerais.</t>
+        </is>
+      </c>
+      <c r="F937" t="inlineStr">
+        <is>
+          <t>pronomes.</t>
+        </is>
+      </c>
       <c r="G937" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="H937" t="inlineStr">
         <is>
-          <t>O termo “que” está retomando a expressão “semente boa” do verso anterior. Assim, o verso “que lançamos hoje no solo da vida” poderia ser substituído por “Lançamos a semente boa hoje no solo da vida”.</t>
+          <t>A palavra “neste” é um pronome demonstrativo que, no trecho apresentado, exerce a função de adjunto adnominal do substantivo “mundo”.</t>
         </is>
       </c>
       <c r="I937" t="inlineStr">
@@ -53401,51 +53562,56 @@
       <c r="K937" t="inlineStr"/>
       <c r="L937" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="938">
       <c r="A938" t="inlineStr">
         <is>
-          <t>Redação em construção
-É sabido que o fato novo assusta os indivíduos, que preferem o mal velho, testado e vivido, à experiência nova, sempre ameaçadora. Se você disser ao cidadão desprevenido que o leite, por ser essencial, deve sair das mãos dos particulares para cooperativas ou entidades estatais, se você disser que os bancos, vivendo exclusivamente das poupanças populares, não têm nenhuma razão de estar em mãos privadas, o cidadão o olhará com olhos perplexos de quem vê alguém propondo algo muito perigoso. Mas, se, ao contrário, você advogar a tese de que a água deveria ser explorada por particulares, todos se voltarão contra você pois – com toda razão – jamais poderiam admitir essa hipótese, tão acostumados estão com essa que é uma das mais antigas realizações comunitárias do homem: a água é direito e serventia de todos. Por isso o cidadão deve ficar alerta, sobretudo para com os malucos, excepcionais e marginais, pois estes, quase sempre, são os que trazem as mais espantosas propostas de renovação contra tudo o que foi estabelecido.
-FERNANDES, Millôr. In: CARNEIRO, Agostinho Dias. Redação em construção. São Paulo: Moderna. p. 105.
-Glossário:
-Advogar: defender alguém ou alguma causa.
-“[...] trazem as mais espantosas propostas de renovação [...]”
-A língua oferece diferentes possibilidades de organização para se expressar um mesmo conteúdo. Assinale a alternativa que demonstre a reescrita do trecho acima, substituindo, sem mudança de sentido, o adjetivo “espantosas” pelo verbo “espantar” em uma oração que seja introduzida por pronome relativo.</t>
+          <t>O nascimento da crônica
+Há um meio certo de começar a crônica por uma trivialidade. É dizer: Que calor! Que desenfreado calor! Diz-se isto, agitando as pontas do lenço, bufando como um touro, ou simplesmente sacudindo a sobrecasaca. Resvala-se do calor aos fenômenos atmosféricos, fazem-se algumas conjeturas acerca do sol e da lua, outras sobre a febre amarela, manda-se um suspiro a Petrópolis, e La glace est rompue; está começada a crônica.
+[...]
+Não posso dizer positivamente em que ano nasceu a crônica; mas há toda a probabilidade de crer que foi coetânea das primeiras duas vizinhas. Essas vizinhas, entre o jantar e a merenda, sentaram-se à porta, para debicar os sucessos do dia. Provavelmente começaram a lastimar-se do calor. Uma dizia que não pudera comer ao jantar, outra que tinha a camisa mais ensopando que as ervas que comera. Passar das ervas às plantações do morador fronteiro, e logo às tropelias amatórias do dito morador, e ao resto, era a coisa mais fácil, natural e possível do mundo. Eis a origem da crônica.
+Que eu, sabedor ou conjeturador de tão alta prosápia, queira repetir o meio de que lançaram mãos as duas avós do cronista, é realmente cometer uma trivialidade; e contudo, leitor, seria difícil falar desta quinzena sem dar à canícula o lugar de honra que lhe compete. Seria; mas eu dispensarei esse meio quase tão velho como o mundo, para somente dizer que a verdade mais incontestável que achei debaixo do sol é que ninguém se deve queixar, porque cada pessoa é sempre mais feliz do que outra.
+ASSIS, Machado de. O nascimento da crônica. Disponível em: &lt;https://reticenciajornalistica.wordpress.com/2011/11/28/o-nascimento-da-cronica/&gt;.
+Acesso em: 1 jun. 2018.
+O trecho que apresenta um adjetivo exercendo a função de adjunto adnominal é</t>
         </is>
       </c>
       <c r="B938" t="inlineStr">
         <is>
-          <t>Trazem as propostas de renovação cujo mais espantam.</t>
+          <t>“bufando como um touro”.</t>
         </is>
       </c>
       <c r="C938" t="inlineStr">
         <is>
-          <t>Trazem as propostas de renovação onde mais espantam.</t>
+          <t>“entre o jantar e a merenda”.</t>
         </is>
       </c>
       <c r="D938" t="inlineStr">
         <is>
-          <t>Trazem as propostas de renovação aonde mais espantam.</t>
+          <t>“manda-se um suspiro a Petrópolis”.</t>
         </is>
       </c>
       <c r="E938" t="inlineStr">
         <is>
-          <t>Trazem as propostas de renovação que mais espantam.</t>
-        </is>
-      </c>
-      <c r="F938" t="inlineStr"/>
+          <t>“Eis a origem da crônica”.</t>
+        </is>
+      </c>
+      <c r="F938" t="inlineStr">
+        <is>
+          <t>“Que desenfreado calor!”​.</t>
+        </is>
+      </c>
       <c r="G938" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="H938" t="inlineStr">
         <is>
-          <t>O pronome relativo “que” seria adequado, sem prejuízo de sentido, para retomar o substantivo “propostas”.</t>
+          <t>No trecho “Que desenfreado calor!”, o termo “desenfreado” é um adjetivo que exerce a função de adjunto adnominal do substantivo “calor”.</t>
         </is>
       </c>
       <c r="I938" t="inlineStr">
@@ -53461,53 +53627,56 @@
       <c r="K938" t="inlineStr"/>
       <c r="L938" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="939">
       <c r="A939" t="inlineStr">
         <is>
-          <t>Leia o texto a seguir.
-Fake news ganha espaço no Facebook e jornalismo profissional perde
-Em janeiro, páginas de notícias falsas engajaram cinco vezes mais do que as de jornalismo
-Do último trimestre do ano passado até o momento, as páginas brasileiras de notícias falsas e sensacionalistas ganharam engajamento no Facebook, e o jornalismo profissional apresentou queda.
-É o que mostra análise feita pela Folha com base em 21 páginas que postam “fake news” e 51 de jornalismo profissional. A taxa média de interações no primeiro grupo aumentou 61,6% entre outubro do ano passado e janeiro deste ano. Já o segundo grupo viu queda de 17% no mesmo período.
-As interações dos usuários com as páginas, incluindo curtidas, reações, comentários e compartilhamentos, foram analisadas de outubro de 2017 até 3 de fevereiro.
-Fake news ganha espaço no Facebook e jornalismo profissional perde. Folha de S.Paulo. São Paulo, 8 fev. 2018. Disponível em:
-&lt;https://www1.folha.uol.com.br/poder/2018/02/fake- news-ganha-espaco-no-facebook-e-jornalismoprofissional-perde.shtml&gt;. Acesso em: 8 fev. 2018.
-No segundo parágrafo dessa notícia, o verbo “postar” encontra-se na terceira pessoa do plural porque faz referência</t>
+          <t>O nascimento da crônica
+Há um meio certo de começar a crônica por uma trivialidade. É dizer: Que calor! Que desenfreado calor! Diz-se isto, agitando as pontas do lenço, bufando como um touro, ou simplesmente sacudindo a sobrecasaca. Resvala-se do calor aos fenômenos atmosféricos, fazem-se algumas conjeturas acerca do sol e da lua, outras sobre a febre amarela, manda-se um suspiro a Petrópolis, e La glace est rompue; está começada a crônica.
+[...]
+Não posso dizer positivamente em que ano nasceu a crônica; mas há toda a probabilidade de crer que foi coetânea das primeiras duas vizinhas. Essas vizinhas, entre o jantar e a merenda, sentaram-se à porta, para debicar os sucessos do dia. Provavelmente começaram a lastimar-se do calor. Uma dizia que não pudera comer ao jantar, outra que tinha a camisa mais ensopando que as ervas que comera. Passar das ervas às plantações do morador fronteiro, e logo às tropelias amatórias do dito morador, e ao resto, era a coisa mais fácil, natural e possível do mundo. Eis a origem da crônica.
+Que eu, sabedor ou conjeturador de tão alta prosápia, queira repetir o meio de que lançaram mãos as duas avós do cronista, é realmente cometer uma trivialidade; e contudo, leitor, seria difícil falar desta quinzena sem dar à canícula o lugar de honra que lhe compete. Seria; mas eu dispensarei esse meio quase tão velho como o mundo, para somente dizer que a verdade mais incontestável que achei debaixo do sol é que ninguém se deve queixar, porque cada pessoa é sempre mais feliz do que outra.
+ASSIS, Machado de. O nascimento da crônica. Disponível em: &lt;https://reticenciajornalistica.wordpress.com/2011/11/28/o-nascimento-da-cronica/&gt;.
+Acesso em: 1 jun. 2018.
+No trecho “Há um meio certo de começar a crônica por uma trivialidade”, os adjuntos adnominais ligados ao substantivo “meio” são</t>
         </is>
       </c>
       <c r="B939" t="inlineStr">
         <is>
-          <t>ao pronome relativo “que”, que desempenha função de sujeito no período.</t>
+          <t>“certo” e “começar”.</t>
         </is>
       </c>
       <c r="C939" t="inlineStr">
         <is>
-          <t>ao substantivo próprio “Folha”, implicando desvio de concordância.</t>
+          <t>“começar” e “crônica”.</t>
         </is>
       </c>
       <c r="D939" t="inlineStr">
         <is>
-          <t>ao numeral “21”, núcleo do sujeito, com o qual o verbo “postar” concorda.</t>
+          <t>“começar” e “uma”.</t>
         </is>
       </c>
       <c r="E939" t="inlineStr">
         <is>
-          <t>ao sujeito composto, cujos núcleos são “fake news” e “jornalismo profissional”.</t>
-        </is>
-      </c>
-      <c r="F939" t="inlineStr"/>
+          <t>“há” e “certo”.</t>
+        </is>
+      </c>
+      <c r="F939" t="inlineStr">
+        <is>
+          <t>“um” e “certo”.</t>
+        </is>
+      </c>
       <c r="G939" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="H939" t="inlineStr">
         <is>
-          <t>O verbo “postar” encontra-se na terceira pessoa do plural porque a concordância verbal, quando o pronome relativo “que” desempenha função de sujeito no período, é feita com o termo a que ele se refere (seu antecedente), ou seja, nesse caso, “21 páginas”.</t>
+          <t>“Um” e “certo” são adjuntos adnominais do substantivo “meio” e ligam-se a ele para caracterizá-lo.</t>
         </is>
       </c>
       <c r="I939" t="inlineStr">
@@ -53523,47 +53692,56 @@
       <c r="K939" t="inlineStr"/>
       <c r="L939" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="940">
       <c r="A940" t="inlineStr">
         <is>
-          <t>Leia o texto a seguir.
-Disponível em: &lt;https://www.nsctotal.com.br/noticias/quem-impos-os-cortes-foi-a-realidade-nao-o-governo-afirma-secretario-joao-paulo-kleinubing&gt;. Acesso em: 18 ago. 2020.
-O verbo “impor” foi flexionado na terceira pessoa do singular porque</t>
+          <t>O nascimento da crônica
+Há um meio certo de começar a crônica por uma trivialidade. É dizer: Que calor! Que desenfreado calor! Diz-se isto, agitando as pontas do lenço, bufando como um touro, ou simplesmente sacudindo a sobrecasaca. Resvala-se do calor aos fenômenos atmosféricos, fazem-se algumas conjeturas acerca do sol e da lua, outras sobre a febre amarela, manda-se um suspiro a Petrópolis, e La glace est rompue; está começada a crônica.
+[...]
+Não posso dizer positivamente em que ano nasceu a crônica; mas há toda a probabilidade de crer que foi coetânea das primeiras duas vizinhas. Essas vizinhas, entre o jantar e a merenda, sentaram-se à porta, para debicar os sucessos do dia. Provavelmente começaram a lastimar-se do calor. Uma dizia que não pudera comer ao jantar, outra que tinha a camisa mais ensopando que as ervas que comera. Passar das ervas às plantações do morador fronteiro, e logo às tropelias amatórias do dito morador, e ao resto, era a coisa mais fácil, natural e possível do mundo. Eis a origem da crônica.
+Que eu, sabedor ou conjeturador de tão alta prosápia, queira repetir o meio de que lançaram mãos as duas avós do cronista, é realmente cometer uma trivialidade; e contudo, leitor, seria difícil falar desta quinzena sem dar à canícula o lugar de honra que lhe compete. Seria; mas eu dispensarei esse meio quase tão velho como o mundo, para somente dizer que a verdade mais incontestável que achei debaixo do sol é que ninguém se deve queixar, porque cada pessoa é sempre mais feliz do que outra.
+ASSIS, Machado de. O nascimento da crônica. Disponível em: &lt;https://reticenciajornalistica.wordpress.com/2011/11/28/o-nascimento-da-cronica/&gt;.
+Acesso em: 1 jun. 2018.
+No trecho “há toda a probabilidade de crer que foi coetânea das primeiras duas vizinhas”, o adjunto adnominal destacado tem a função de</t>
         </is>
       </c>
       <c r="B940" t="inlineStr">
         <is>
-          <t>não há um sujeito específico nesse período.</t>
+          <t>comprovar a origem da crônica.</t>
         </is>
       </c>
       <c r="C940" t="inlineStr">
         <is>
-          <t>concorda com o sujeito simples "João Paulo Kleinübing".</t>
+          <t>indicar o momento do evento.</t>
         </is>
       </c>
       <c r="D940" t="inlineStr">
         <is>
-          <t>concorda com o pronome relativo "quem", cuja referência é “realidade”.</t>
+          <t>narrar a amizade das mulheres.</t>
         </is>
       </c>
       <c r="E940" t="inlineStr">
         <is>
-          <t>concorda com "secretário", que exige o verbo na terceira pessoa do singular.</t>
-        </is>
-      </c>
-      <c r="F940" t="inlineStr"/>
+          <t>quantificar o nome “vizinhas”.</t>
+        </is>
+      </c>
+      <c r="F940" t="inlineStr">
+        <is>
+          <t>situar o substantivo no espaço​.</t>
+        </is>
+      </c>
       <c r="G940" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="H940" t="inlineStr">
         <is>
-          <t>A concordância com o pronome relativo “quem” pode ser feita com o seu referente ou o verbo pode ficar na terceira pessoa do singular. Neste caso, o verbo “impor” poderia ser flexionado somente na terceira pessoa do singular, respeitando ou o pronome relativo ou o referente, “realidade”, que está na terceira pessoa do singular.</t>
+          <t>O adjunto adnominal “duas” pertence à classe dos numerais, sendo usado, aqui, para quantificar o substantivo “vizinhas”.</t>
         </is>
       </c>
       <c r="I940" t="inlineStr">
@@ -53576,59 +53754,58 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K940" t="inlineStr">
-        <is>
-          <t>ph10_por_09.png</t>
-        </is>
-      </c>
+      <c r="K940" t="inlineStr"/>
       <c r="L940" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="941">
       <c r="A941" t="inlineStr">
         <is>
-          <t>Leia o trecho da música "Vilarejo" de Marisa Monte e responda à questão:
-Há um vilarejo ali
-Onde areja um vento bom
-Na varanda, quem descansa
-Vê o horizonte deitar no chão
-[...]
-Disponível em: https://www.vagalume.com.br/marisa-monte/vilarejo.html. Acesso em 14 jan. 2025.
-Sobre o uso do pronome relativo "onde" no trecho acima,</t>
+          <t>Os terroristas​
+Era um professor duro, exigente e implacável. As provas eram feitas sem aviso prévio. Todos os trabalhos valiam nota e eram corrigidos segundo os critérios mais rigorosos. Resultado: no fim do ano quase todos os alunos estavam à beira da reprovação. As notas que ele anotava cuidadosamente no livro de chamada eram as mais baixas possíveis. O que fazer?
+Reuniam-se todos os dias no bar em frente ao colégio, para discutir a situação, mas nada lhes ocorria. Até que um deles teve uma ideia brilhante. O livro de chamada. A solução estava ali: tinham de se apossar do livro de chamada e mudar as notas. Um 0 poderia se transformar em 8. Um 1 poderia virar 7 (ou 10, dependendo do grau de ambição).
+O problema era pegar o livro, que o professor não largava nunca, nem mesmo para ir ao banheiro. Aparentemente só uma catástrofe poderia superá-los. Recorreram, pois, à catástrofe. Um dos alunos telefonou do orelhão em frente ao colégio, avisando que havia um princípio de incêndio na casa do professor. Avisado, o pobre homem saiu correndo da sala de aula, deixando sobre a mesa o famigerado livro de presenças.
+Acreditareis se eu disser que ninguém tocou no livro? Ninguém tocou no livro. Os rapazes se olhavam, mas nenhum deles tomou a iniciativa de mudar as notas. Às vezes a consciência pesa mais que a ameaça da reprovação.
+SCLIAR, Moacyr. Os terroristas. Disponível em: &lt;http://jornadapadremarzano.blogspot.com.br/2017/08/os-terroristas-moacyr-scliar.html&gt;. Acesso em: 1 jun. 2018.
+No trecho “Todos os trabalhos valiam nota e eram corrigidos segundo os critérios mais rigorosos”, o termo “rigorosos” concorda em gênero e número com</t>
         </is>
       </c>
       <c r="B941" t="inlineStr">
         <is>
-          <t>menciona a palavra "vento" e indica o local onde o vento areja.</t>
+          <t>"corrigidos".</t>
         </is>
       </c>
       <c r="C941" t="inlineStr">
         <is>
-          <t>nomeia a palavra "varanda" e indica o local onde alguém descansa.</t>
+          <t>"critérios".</t>
         </is>
       </c>
       <c r="D941" t="inlineStr">
         <is>
-          <t>referencia a palavra "vilarejo" e indica o local onde areja um vento bom.</t>
+          <t>"mais".</t>
         </is>
       </c>
       <c r="E941" t="inlineStr">
         <is>
-          <t>alude à palavra "horizonte" e indica o local onde o horizonte deita no chão.</t>
-        </is>
-      </c>
-      <c r="F941" t="inlineStr"/>
+          <t>"todos".</t>
+        </is>
+      </c>
+      <c r="F941" t="inlineStr">
+        <is>
+          <t>"trabalhos".</t>
+        </is>
+      </c>
       <c r="G941" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H941" t="inlineStr">
         <is>
-          <t>O pronome relativo "onde" está sendo utilizado para substituir o substantivo "vilarejo" e é adequado para indicar um lugar. No trecho da música, "onde" está introduzindo uma oração relativa que fornece uma informação adicional sobre o vilarejo, especificando que é o local onde areja um vento bom.</t>
+          <t>No trecho, o termo “rigorosos” é adjunto adnominal de “critérios”, concordando com ele em gênero e número.</t>
         </is>
       </c>
       <c r="I941" t="inlineStr">
@@ -53644,52 +53821,51 @@
       <c r="K941" t="inlineStr"/>
       <c r="L941" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="942">
       <c r="A942" t="inlineStr">
         <is>
-          <t>Ana e Bruno estão construindo triângulos utilizando palitos de fósforo. Ana escolheu três palitos com medidas 4 cm, 5 cm e 9 cm, enquanto Bruno escolheu palitos com medidas 3 cm, 5 cm e 8 cm.
-Após a construção, qual dos dois amigos conseguiu formar um triângulo?</t>
+          <t>Uma pastelaria vende dois tipos de pastéis: pastéis simples e pastéis especiais. No final do dia, o caixa registrou um total de 120 pastéis vendidos, sendo que a quantidade de pastéis simples foi o dobro da quantidade de pastéis especiais.
+Quantos pastéis especiais foram vendidos ao longo do dia?</t>
         </is>
       </c>
       <c r="B942" t="inlineStr">
         <is>
-          <t>Apenas Ana.</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C942" t="inlineStr">
         <is>
-          <t>Apenas Bruno.</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D942" t="inlineStr">
         <is>
-          <t>Nenhum dos dois</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E942" t="inlineStr">
         <is>
-          <t>Ambos, Ana e Bruno.</t>
-        </is>
-      </c>
-      <c r="F942" t="inlineStr"/>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="F942" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
       <c r="G942" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H942" t="inlineStr">
         <is>
-          <t>Para que três segmentos de reta formem um triângulo, a medida de cada lado deve ser menor que a soma das medidas dos outros dois lados.
-Triângulo de Ana:
-4 cm + 5 cm = 9 cm
-9 cm é igual à soma dos outros dois lados. Portanto, Ana não consegue formar um triângulo.
-Triângulo de Bruno:
-3 cm + 5 cm = 8 cm
-8 cm é igual à soma dos outros dois lados. Portanto, Bruno não consegue formar um triângulo.</t>
+          <t>Seja x a quantidade de pastéis simples vendidos e y a quantidade de pastéis especiais vendidos. Do enunciado sabe-se que o total de pastéis vendidos foi 120: x + y = 120.
+A quantidade de pastéis simples é o dobro da quantidade de pastéis especiais: x = 2y. Logo,  Portanto, foram 40 pastéis especiais vendidos.</t>
         </is>
       </c>
       <c r="I942" t="inlineStr">
@@ -53705,46 +53881,52 @@
       <c r="K942" t="inlineStr"/>
       <c r="L942" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="943">
       <c r="A943" t="inlineStr">
         <is>
-          <t>Um engenheiro civil está projetando uma ponte que precisa ser extremamente estável e resistente a deformações. Ele está considerando diferentes formas geométricas para a estrutura da ponte e sabe que a rigidez é um fator crucial. Ele está avaliando o uso de triângulos na construção da estrutura da ponte.
-Por que o engenheiro deve preferir o uso de triângulos na construção da estrutura da ponte para garantir a rigidez e a estabilidade?</t>
+          <t>Um vendedor de frutas vende maçãs e laranjas. Ele vendeu 3 vezes mais maçãs do que laranjas.
+Se ele vendeu um total de 40 frutas, quantas laranjas ele vendeu?</t>
         </is>
       </c>
       <c r="B943" t="inlineStr">
         <is>
-          <t>Porque os triângulos têm lados iguais, o que garante a rigidez.</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C943" t="inlineStr">
         <is>
-          <t>Porque os triângulos têm ângulos iguais, o que garante a rigidez.</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D943" t="inlineStr">
         <is>
-          <t>Porque os triângulos têm todos os lados diferentes, o que garante a rigidez.</t>
+          <t>30</t>
         </is>
       </c>
       <c r="E943" t="inlineStr">
         <is>
-          <t>Porque os triângulos são figuras geométricas rígidas, o que garante a estabilidade.</t>
-        </is>
-      </c>
-      <c r="F943" t="inlineStr"/>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F943" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
       <c r="G943" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H943" t="inlineStr">
         <is>
-          <t>Os triângulos são figuras geométricas rígidas, o que significa que, uma vez construídos, eles não mudam de forma, mesmo quando submetidos a forças externas. Isso ocorre porque a soma dos ângulos internos de um triângulo é sempre 180°, e a relação entre os lados e os ângulos é fixa. Por isso, o engenheiro deve preferir o uso de triângulos na construção da estrutura da ponte para garantir a rigidez e a estabilidade.</t>
+          <t>Vamos representar a quantidade de maçãs por x e a quantidade de laranjas por y. Temos o sistema de equações:
+Substituindo x na segunda equação, temos:
+Portanto, ele vendeu 10 laranjas.</t>
         </is>
       </c>
       <c r="I943" t="inlineStr">
@@ -53760,51 +53942,54 @@
       <c r="K943" t="inlineStr"/>
       <c r="L943" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="944">
       <c r="A944" t="inlineStr">
         <is>
-          <t>Um professor de matemática pediu aos alunos que descrevessem um algoritmo para a construção de um triângulo qualquer, conhecidas as medidas dos três lados: 6 cm, 8 cm e 10 cm.
-Qual é a sequência correta de passos para construir um triângulo com lados de 6 cm, 8 cm e 10 cm?</t>
+          <t>Um restaurante vende dois tipos de pratos: prato A e prato B. O prato A custa R$ 15,00 e o prato B custa R$ 20,00. Em um dia, o restaurante vendeu um total de 50 pratos e arrecadou R$ 850,00.
+Quantos pratos do tipo A foram vendidos?</t>
         </is>
       </c>
       <c r="B944" t="inlineStr">
         <is>
-          <t>Desenhe um segmento de 6 cm, depois desenhe um segmento de 10 cm a partir de uma extremidade do primeiro segmento, e finalmente desenhe um segmento de 8 cm a partir da extremidade do segundo segmento.</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C944" t="inlineStr">
         <is>
-          <t>Desenhe um segmento de 6 cm, depois desenhe um segmento de 8 cm a partir de uma extremidade do primeiro segmento, e finalmente desenhe um segmento de 10 cm a partir da outra extremidade do primeiro segmento.</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D944" t="inlineStr">
         <is>
-          <t>Desenhe um segmento de 6 cm, depois desenhe um segmento de 8 cm a partir de uma extremidade do primeiro segmento, e finalmente desenhe um segmento de 10 cm a partir da extremidade do segundo segmento, encontrando a outra extremidade do primeiro segmento.</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E944" t="inlineStr">
         <is>
-          <t>Desenhe um segmento de 6 cm, depois, com um compasso, trace um arco de 8 cm a partir de uma extremidade do segmento de 6 cm, e um arco de 10 cm a partir da outra extremidade do segmento de 6 cm. O ponto de interseção dos arcos será o terceiro vértice do triângulo.</t>
-        </is>
-      </c>
-      <c r="F944" t="inlineStr"/>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F944" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="G944" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H944" t="inlineStr">
         <is>
-          <t>Para construir um triângulo com lados de 6 cm, 8 cm e 10 cm, o algoritmo correto é:
-Desenhe um segmento de 6 cm.
-Com um compasso, abra uma medida de 8 cm e trace um arco a partir de uma extremidade do segmento de 6 cm.
-Com o compasso, abra uma medida de 10 cm e trace um arco a partir da outra extremidade do segmento de 6 cm.
-O ponto de interseção dos dois arcos será o terceiro vértice do triângulo.
-Conecte esse ponto de interseção às extremidades do segmento de 6 cm para formar o triângulo.</t>
+          <t>Vamos representar a quantidade de pratos A por x e a quantidade de pratos B por y. Temos o sistema de equações: 
+Multiplicando a primeira equação por 15.
+Subtraindo a primeira equação da segunda:
+Substituindo y na primeira equação:
+Portanto, foram vendidos 30 pratos do tipo A.</t>
         </is>
       </c>
       <c r="I944" t="inlineStr">
@@ -53820,46 +54005,53 @@
       <c r="K944" t="inlineStr"/>
       <c r="L944" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="945">
       <c r="A945" t="inlineStr">
         <is>
-          <t>Em uma aula de geometria, o professor pediu aos alunos que calculassem a medida de um dos ângulos internos de um triângulo, sabendo que os outros dois ângulos medem 50° e 70°.
-Qual é a medida do terceiro ângulo interno desse triângulo?</t>
+          <t>Em um mercadinho o preço de 2 pacotes de arroz e feijão. O preço de 2 pacotes de arroz e 3 pacotes de feijão é R$ 45,00. Já o preço de 4 pacotes de arroz e 2 pacotes de feijão é R$ 60,00
+Quanto custa um pacote de arroz?</t>
         </is>
       </c>
       <c r="B945" t="inlineStr">
         <is>
-          <t>50º</t>
+          <t>R$ 5,00</t>
         </is>
       </c>
       <c r="C945" t="inlineStr">
         <is>
-          <t>60º</t>
+          <t>R$ 7,50</t>
         </is>
       </c>
       <c r="D945" t="inlineStr">
         <is>
-          <t>70º</t>
+          <t>R$ 10,00</t>
         </is>
       </c>
       <c r="E945" t="inlineStr">
         <is>
-          <t>80º</t>
-        </is>
-      </c>
-      <c r="F945" t="inlineStr"/>
+          <t>R$ 11,25</t>
+        </is>
+      </c>
+      <c r="F945" t="inlineStr">
+        <is>
+          <t>R$ 15,00</t>
+        </is>
+      </c>
       <c r="G945" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="H945" t="inlineStr">
         <is>
-          <t>A soma dos ângulos internos de um triângulo é sempre 180°. Sabendo que dois dos ângulos medem 50° e 70°, podemos encontrar a medida do terceiro ângulo subtraindo a soma dos dois ângulos conhecidos de 180°:</t>
+          <t>Seja x o preço do pacote de arroz e y o preço do pacote de feijão. O problema pode ser modelado pelo seguinte sistema de equações:
+Simplificando e somando as equações, tem-se:
+Este é o preço de um pacote de feijão (R$ 7,50). Substituindo este valor em , obtém-se:
+Portanto, o preço de um pacote de arroz é R$ 11,25.</t>
         </is>
       </c>
       <c r="I945" t="inlineStr">
@@ -53875,46 +54067,59 @@
       <c r="K945" t="inlineStr"/>
       <c r="L945" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="946">
       <c r="A946" t="inlineStr">
         <is>
-          <t>Em um triângulo , o ângulo externo  é formado pela extensão do lado AB. Sabe-se que os ângulos internos  medem 45° e 55°, respectivamente.
-Qual é a medida do ângulo externo ?</t>
+          <t>Um mecânico trabalha com dois tipos de serviços: troca de óleo e alinhamento. Ele realizou 5 trocas de óleo e 3 alinhamentos em um dia, e recebeu um total de R$ 200,00. No dia seguinte, ele realizou 2 trocas de óleo e 4 alinhamentos, recebendo um total de R$ 160,00.
+Quanto ele cobra por cada troca de óleo?</t>
         </is>
       </c>
       <c r="B946" t="inlineStr">
         <is>
-          <t>90º</t>
+          <t>R$ 40,00</t>
         </is>
       </c>
       <c r="C946" t="inlineStr">
         <is>
-          <t>100º</t>
+          <t>R$ 28,57</t>
         </is>
       </c>
       <c r="D946" t="inlineStr">
         <is>
-          <t>110º</t>
+          <t>R$ 24,00</t>
         </is>
       </c>
       <c r="E946" t="inlineStr">
         <is>
-          <t>120º</t>
-        </is>
-      </c>
-      <c r="F946" t="inlineStr"/>
+          <t>R$ 22,86</t>
+        </is>
+      </c>
+      <c r="F946" t="inlineStr">
+        <is>
+          <t>R$ 13,34</t>
+        </is>
+      </c>
       <c r="G946" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="H946" t="inlineStr">
         <is>
-          <t>A relação entre um ângulo externo e os dois ângulos internos não adjacentes de um triângulo é que o ângulo externo é igual à soma dos dois ângulos internos não adjacentes. Portanto, a medida do ângulo externo  é:</t>
+          <t>Vamos representar o valor da troca de óleo por x e o valor do alinhamento por y. Temos o sistema de equações:
+Simplificando e isolando o x na segunda equação, temos:
+Substituindo x na primeira equação:
+5(80 – 2y) + 3y = 200
+400 – 10y + 3y = 200 
+400 – 7y = - 200 
+y = 28.57
+Agora, substituindo y na equação x = 80 – 2y:
+x = 80 – 2(28.57) = 80 – 57,14 = 22,86.
+Portanto, o mecânico cobra aproximadamente R$ 22,86 por troca de óleo.</t>
         </is>
       </c>
       <c r="I946" t="inlineStr">
@@ -53927,54 +54132,53 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K946" t="inlineStr">
-        <is>
-          <t>ph10_mat_05.png</t>
-        </is>
-      </c>
+      <c r="K946" t="inlineStr"/>
       <c r="L946" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="947">
       <c r="A947" t="inlineStr">
         <is>
-          <t>Observe o triângulo abaixo:
-A relação que existe entre a medida dos lados deste triângulo é</t>
+          <t>Um clube promoveu uma festa para arrecadar fundos para uma instituição de caridade. As pessoas que eram sócias do clube pagaram R$ 20,00 de entrada e as pessoas que não eram sócias do clube pagaram R$ 35,00. Se o clube vendeu 310 ingressos e arrecadou R$ 8 450,00 com a venda dos ingressos, quantas pessoas não associadas ao clube participaram da festa?</t>
         </is>
       </c>
       <c r="B947" t="inlineStr">
         <is>
-          <t>[img:ph10_mat_06_a.png]</t>
+          <t>150.</t>
         </is>
       </c>
       <c r="C947" t="inlineStr">
         <is>
-          <t>[img:ph10_mat_06_b.png]</t>
+          <t>160.</t>
         </is>
       </c>
       <c r="D947" t="inlineStr">
         <is>
-          <t>[img:ph10_mat_06_c.png]</t>
+          <t>170.</t>
         </is>
       </c>
       <c r="E947" t="inlineStr">
         <is>
-          <t>[img:ph10_mat_06_d.png]</t>
-        </is>
-      </c>
-      <c r="F947" t="inlineStr"/>
+          <t>180.</t>
+        </is>
+      </c>
+      <c r="F947" t="inlineStr">
+        <is>
+          <t>190.</t>
+        </is>
+      </c>
       <c r="G947" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H947" t="inlineStr">
         <is>
-          <t>Em um triângulo, o maior dos lados é oposto ao maior dos ângulos, assim como o menor lado é oposto ao menor ângulo.
-Desta forma, como  então .</t>
+          <t>Considere x o total de pessoas associadas e y as pessoas que não são sócias do clube. Assim, temos:
+Portanto, 150 pessoas que não são sócias do clube participaram da festa.</t>
         </is>
       </c>
       <c r="I947" t="inlineStr">
@@ -53987,54 +54191,55 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K947" t="inlineStr">
-        <is>
-          <t>ph10_mat_06.png</t>
-        </is>
-      </c>
+      <c r="K947" t="inlineStr"/>
       <c r="L947" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="948">
       <c r="A948" t="inlineStr">
         <is>
-          <t>Na figura abaixo estão marcados 4 ângulos, de forma que a soma da medida do ângulo reto com a medida do ângulo  é 130°..
-Qual é a medida do ângulo ?</t>
+          <t>Considere o sistema abaixo.
+Qual é o valor da expressão x + y?</t>
         </is>
       </c>
       <c r="B948" t="inlineStr">
         <is>
-          <t>40°</t>
+          <t>[img:8a_ph10_mat_07_a.png]</t>
         </is>
       </c>
       <c r="C948" t="inlineStr">
         <is>
-          <t>45°</t>
+          <t>[img:8a_ph10_mat_07_b.png]</t>
         </is>
       </c>
       <c r="D948" t="inlineStr">
         <is>
-          <t>55°</t>
+          <t>[img:8a_ph10_mat_07_c.png]</t>
         </is>
       </c>
       <c r="E948" t="inlineStr">
         <is>
-          <t>65°</t>
-        </is>
-      </c>
-      <c r="F948" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F948" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="G948" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H948" t="inlineStr">
         <is>
-          <t>O ângulo  é externo ao triângulo que contém os ângulos  e 25°, logo ele é dado pela medida desses dois ângulos.
-Como a soma da medida do ângulo reto com a medida do ângulo  é 130° e de 90° para 130° faltam 40°, logo a medida de  = 40° e a medida de  = 40° + 25° ⟹  = 65°.</t>
+          <t>Condição de existência:
+Resolvendo o sistema temos:
+Os valores encontrados para x e y são diferentes de 0, logo eles são válidos.</t>
         </is>
       </c>
       <c r="I948" t="inlineStr">
@@ -54049,51 +54254,57 @@
       </c>
       <c r="K948" t="inlineStr">
         <is>
-          <t>ph10_mat_07.png</t>
+          <t>8a_ph10_mat_07.png</t>
         </is>
       </c>
       <c r="L948" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="949">
       <c r="A949" t="inlineStr">
         <is>
-          <t>Observe a figura abaixo:
-Qual é a medida de ?</t>
+          <t>Considere o sistema abaixo, com a ≠ 0 e b ≠ 0.
+Sobre a solução desse sistema, é verdade que</t>
         </is>
       </c>
       <c r="B949" t="inlineStr">
         <is>
-          <t>20°</t>
+          <t>a e b são números primos.</t>
         </is>
       </c>
       <c r="C949" t="inlineStr">
         <is>
-          <t>30°</t>
+          <t>b &lt; a.</t>
         </is>
       </c>
       <c r="D949" t="inlineStr">
         <is>
-          <t>40°</t>
+          <t>a e b são números pares.</t>
         </is>
       </c>
       <c r="E949" t="inlineStr">
         <is>
-          <t>50°</t>
-        </is>
-      </c>
-      <c r="F949" t="inlineStr"/>
+          <t>a é um número par e b não é primo.</t>
+        </is>
+      </c>
+      <c r="F949" t="inlineStr">
+        <is>
+          <t>a é um número ímpar e b não é primo.</t>
+        </is>
+      </c>
       <c r="G949" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H949" t="inlineStr">
         <is>
-          <t>Para descobrir o valor de , basta subtrair de 180° os ângulos internos que sabemos o valor: 180° - 115° - 25° = 40°.</t>
+          <t>Subtraindo (I) de (II):
+Substituindo o valor de b em (II):
+Portanto, a e b são números primos.</t>
         </is>
       </c>
       <c r="I949" t="inlineStr">
@@ -54108,52 +54319,55 @@
       </c>
       <c r="K949" t="inlineStr">
         <is>
-          <t>ph10_mat_08.png</t>
+          <t>8a_ph10_mat_08.png</t>
         </is>
       </c>
       <c r="L949" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="950">
       <c r="A950" t="inlineStr">
         <is>
-          <t>Observe a figura desenhada abaixo, formada por um quadrado e 4 triângulos equiláteros de lados com a mesma medida, além de dois segmentos: FC e FD.
-Qual a medida do ângulo ?</t>
+          <t>Em um jogo de certo ou errado, para cada pergunta respondida corretamente o candidato ganhava 2 pontos e, caso ele errasse a resposta, perdia 3 pontos. Otávio participou desse jogo e marcou 12 pontos.
+Se foram feitas a ele 11 perguntas, qual dos sistemas abaixo calcularia o número de perguntas respondidas corretamente por Otávio?</t>
         </is>
       </c>
       <c r="B950" t="inlineStr">
         <is>
-          <t>15°</t>
+          <t>[img:8a_ph10_mat_09_a.png]</t>
         </is>
       </c>
       <c r="C950" t="inlineStr">
         <is>
-          <t>30°</t>
+          <t>[img:8a_ph10_mat_09_b.png]</t>
         </is>
       </c>
       <c r="D950" t="inlineStr">
         <is>
-          <t>40°</t>
+          <t>[img:8a_ph10_mat_09_c.png]</t>
         </is>
       </c>
       <c r="E950" t="inlineStr">
         <is>
-          <t>45°</t>
-        </is>
-      </c>
-      <c r="F950" t="inlineStr"/>
+          <t>[img:8a_ph10_mat_09_d.png]</t>
+        </is>
+      </c>
+      <c r="F950" t="inlineStr">
+        <is>
+          <t>[img:8a_ph10_mat_09_e.png]</t>
+        </is>
+      </c>
       <c r="G950" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H950" t="inlineStr">
         <is>
-          <t>O triângulo ADF é isósceles, pois o lado do quadrado e o lado do triângulo equilátero têm a mesma medida.
-Logo, o ângulo A do triângulo ADF será de 60° + 90° = 150°. O que falta para chegar a 180° será dividido em dois ângulos congruentes:</t>
+          <t>Seja x o total de perguntas respondidas corretamente e y o total de perguntas respondidas erradas. Do enunciado, temos:</t>
         </is>
       </c>
       <c r="I950" t="inlineStr">
@@ -54166,56 +54380,54 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K950" t="inlineStr">
-        <is>
-          <t>ph10_mat_09.png</t>
-        </is>
-      </c>
+      <c r="K950" t="inlineStr"/>
       <c r="L950" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>
     <row r="951">
       <c r="A951" t="inlineStr">
         <is>
-          <t>Observe a figura desenhada abaixo, formada por um quadrado e 4 triângulos equiláteros de lados com a mesma medida, além de dois segmentos: FC e FD.
- ​
-Qual a medida do ângulo ?</t>
+          <t>Em um jogo de certo ou errado, para cada pergunta respondida corretamente o candidato ganhava 2 pontos e, caso ele errasse a resposta, perdia 3 pontos. Otávio participou desse jogo e marcou 12 pontos.
+Sabendo que Otávio respondeu 11 perguntas, quantas destas Otávio acertou?</t>
         </is>
       </c>
       <c r="B951" t="inlineStr">
         <is>
-          <t>45°</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C951" t="inlineStr">
         <is>
-          <t>60°</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D951" t="inlineStr">
         <is>
-          <t>75°</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E951" t="inlineStr">
         <is>
-          <t>80°</t>
-        </is>
-      </c>
-      <c r="F951" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F951" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="G951" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="H951" t="inlineStr">
         <is>
-          <t>Como o triângulo ADF é isósceles, e o ângulo DAF mede , então o ângulo D do triângulo ADF será de .
-É possível concluir que:
-A soma de (beta) com a medida do ângulo ADF é 90°, de 15° para 90° faltam 75°. Logo, β = 75°.</t>
+          <t>Sejam x e y as quantidades de respostas certas e erradas, respectivamente.
+Portanto, 9 perguntas foram respondidas corretamente.</t>
         </is>
       </c>
       <c r="I951" t="inlineStr">
@@ -54228,14 +54440,10 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K951" t="inlineStr">
-        <is>
-          <t>ph10_mat_10.png</t>
-        </is>
-      </c>
+      <c r="K951" t="inlineStr"/>
       <c r="L951" t="inlineStr">
         <is>
-          <t>7ano</t>
+          <t>8ano</t>
         </is>
       </c>
     </row>

--- a/questoes.xlsx
+++ b/questoes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L951"/>
+  <dimension ref="A1:L1001"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51406,7 +51406,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K902" t="inlineStr"/>
       <c r="L902" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -51470,7 +51469,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K903" t="inlineStr"/>
       <c r="L903" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -51533,7 +51531,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K904" t="inlineStr"/>
       <c r="L904" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -51599,7 +51596,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K905" t="inlineStr"/>
       <c r="L905" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -51659,7 +51655,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K906" t="inlineStr"/>
       <c r="L906" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -51720,7 +51715,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K907" t="inlineStr"/>
       <c r="L907" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -51781,7 +51775,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K908" t="inlineStr"/>
       <c r="L908" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -51846,7 +51839,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K909" t="inlineStr"/>
       <c r="L909" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -51906,7 +51898,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K910" t="inlineStr"/>
       <c r="L910" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -51965,7 +51956,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K911" t="inlineStr"/>
       <c r="L911" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -52026,7 +52016,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K912" t="inlineStr"/>
       <c r="L912" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -52086,7 +52075,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K913" t="inlineStr"/>
       <c r="L913" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -52274,7 +52262,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K916" t="inlineStr"/>
       <c r="L916" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -52334,7 +52321,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K917" t="inlineStr"/>
       <c r="L917" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -52394,7 +52380,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K918" t="inlineStr"/>
       <c r="L918" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -52454,7 +52439,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K919" t="inlineStr"/>
       <c r="L919" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -52513,7 +52497,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K920" t="inlineStr"/>
       <c r="L920" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -52580,7 +52563,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K921" t="inlineStr"/>
       <c r="L921" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -52641,7 +52623,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K922" t="inlineStr"/>
       <c r="L922" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -52701,7 +52682,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K923" t="inlineStr"/>
       <c r="L923" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -52887,7 +52867,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K926" t="inlineStr"/>
       <c r="L926" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -52947,7 +52926,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K927" t="inlineStr"/>
       <c r="L927" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -53008,7 +52986,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K928" t="inlineStr"/>
       <c r="L928" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -53068,7 +53045,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K929" t="inlineStr"/>
       <c r="L929" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -53129,7 +53105,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K930" t="inlineStr"/>
       <c r="L930" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -53189,7 +53164,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K931" t="inlineStr"/>
       <c r="L931" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -53250,7 +53224,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K932" t="inlineStr"/>
       <c r="L932" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -53310,7 +53283,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K933" t="inlineStr"/>
       <c r="L933" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -53370,7 +53342,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K934" t="inlineStr"/>
       <c r="L934" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -53430,7 +53401,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K935" t="inlineStr"/>
       <c r="L935" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -53490,7 +53460,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K936" t="inlineStr"/>
       <c r="L936" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -53559,7 +53528,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K937" t="inlineStr"/>
       <c r="L937" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -53624,7 +53592,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K938" t="inlineStr"/>
       <c r="L938" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -53689,7 +53656,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K939" t="inlineStr"/>
       <c r="L939" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -53754,7 +53720,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K940" t="inlineStr"/>
       <c r="L940" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -53818,7 +53783,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K941" t="inlineStr"/>
       <c r="L941" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -53878,7 +53842,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K942" t="inlineStr"/>
       <c r="L942" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -53939,7 +53902,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K943" t="inlineStr"/>
       <c r="L943" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -54002,7 +53964,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K944" t="inlineStr"/>
       <c r="L944" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -54064,7 +54025,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K945" t="inlineStr"/>
       <c r="L945" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -54132,7 +54092,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K946" t="inlineStr"/>
       <c r="L946" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -54191,7 +54150,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K947" t="inlineStr"/>
       <c r="L947" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -54380,7 +54338,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K950" t="inlineStr"/>
       <c r="L950" t="inlineStr">
         <is>
           <t>8ano</t>
@@ -54440,10 +54397,2896 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K951" t="inlineStr"/>
       <c r="L951" t="inlineStr">
         <is>
           <t>8ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>Com a queda de temperatura, normalmente as pessoas tendem a ficar mais tempo em locais fechados, o que ajuda a proliferar doenças respiratórias, uma vez que o vírus influenza tem alta transmissibilidade por espirro e tosse, além do contato direto das mãos e objetos comuns como corrimões e maçanetas.
+Disponível em: http://saude.sp.gov.br/coordenadoria-de-controle-de-doencas/noticias/23032024-gripe-resfriado-pneumonia-covid-19-virose-saiba-identificar-as-doencas-no-outono. Acesso em: 16 jan. 2025.
+Uma forma de prevenir a doença causada por esse vírus é</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>tomar regularmente antibióticos e antivirais.</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>higienizar as mãos apenas com álcool em gel.</t>
+        </is>
+      </c>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>praticar atividades físicas ao ar livre regularmente.</t>
+        </is>
+      </c>
+      <c r="E952" t="inlineStr">
+        <is>
+          <t>evitar aglomerações e ambientes fechados em estações frias.</t>
+        </is>
+      </c>
+      <c r="F952" t="inlineStr"/>
+      <c r="G952" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H952" t="inlineStr">
+        <is>
+          <t>Evitar aglomerações e ambientes fechados é uma medida eficaz para reduzir a exposição ao vírus influenza, que se transmite facilmente em locais com grande concentração de pessoas e pouca ventilação.</t>
+        </is>
+      </c>
+      <c r="I952" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J952" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K952" t="inlineStr"/>
+      <c r="L952" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>O tétano é uma doença causada pela bactéria Clostridium tetani, que pode entrar no corpo humano através de ferimentos contaminados. A doença causa contrações musculares dolorosas e pode ser fatal se não tratada.
+Qual das seguintes alternativas é uma medida eficaz para prevenir essa doença?</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>Manter a vacinação em dia.</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>Tomar analgésicos regularmente.</t>
+        </is>
+      </c>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>Consumir alimentos ricos em cálcio.</t>
+        </is>
+      </c>
+      <c r="E953" t="inlineStr">
+        <is>
+          <t>Evitar contato com pessoas infectadas.</t>
+        </is>
+      </c>
+      <c r="F953" t="inlineStr"/>
+      <c r="G953" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H953" t="inlineStr">
+        <is>
+          <t>Manter a vacinação em dia é uma medida eficaz para prevenir o tétano, pois a vacina protege contra a toxina produzida pela bactéria Clostridium tetani.</t>
+        </is>
+      </c>
+      <c r="I953" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J953" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K953" t="inlineStr"/>
+      <c r="L953" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>“A Aids era uma doença variada, e uniformemente fatal”, definiu Drauzio Varella num episódio recente de seu (ótimo) podcast, o Outras Histórias. “À medida que a imunidade ia caindo”, ele segue, “repetiam-se as infecções oportunistas: pneumonias, meningites, lesões cerebrais por toxoplasmose… Você tratava uma infecção e vinha outra, depois outra. Uma hora o doente estava tão debilitado não sobrevivia”.
+Drauzio usa o tempo verbal no passado por um motivo óbvio: Aids sem tratamento é uma página virada no Brasil. Começou há 30 anos, em 1991. Foi quando teve início a compra e a distribuição gratuita de remédios contra o HIV pelo SUS.
+Disponível em: https://super.abril.com.br/coluna/alexandre-versignassi/ha-30-anos-o-brasil-comecava-sua-revolucao-contra-a-aids/. Acesso em: 15 jan. 2025.
+Sobre a prevenção e o tratamento da AIDS, pode-se afirmar corretamente que</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>o uso consistente de preservativos é a única forma eficaz de prevenir a transmissão do HIV.</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>a descoberta dos remédios contra o HIV tornou a AIDS uma doença completamente controlável.</t>
+        </is>
+      </c>
+      <c r="D954" t="inlineStr">
+        <is>
+          <t>pessoas infectadas pelo HIV não devem ter filhos, pois a doença é transmitida geneticamente para os descendentes.</t>
+        </is>
+      </c>
+      <c r="E954" t="inlineStr">
+        <is>
+          <t>o tratamento antirretroviral pode permitir que pessoas com HIV tenham vidas saudáveis, mas não elimina completamente o vírus do organismo.</t>
+        </is>
+      </c>
+      <c r="F954" t="inlineStr"/>
+      <c r="G954" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H954" t="inlineStr">
+        <is>
+          <t>O tratamento antirretroviral (TAR) permite que pessoas vivendo com HIV mantenham uma carga viral indetectável, o que melhora significativamente a qualidade de vida e a expectativa de vida. No entanto, o TAR não elimina completamente o vírus do organismo, exigindo tratamento contínuo.</t>
+        </is>
+      </c>
+      <c r="I954" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J954" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K954" t="inlineStr"/>
+      <c r="L954" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>A tuberculose é uma doença infecciosa e transmissível, causada pela bactéria Mycobacterium tuberculosis, também conhecida como bacilo de Koch. A doença afeta prioritariamente os pulmões (forma pulmonar), embora possa acometer outros órgãos e/ou sistemas. [...] O tratamento da tuberculose dura no mínimo seis meses, é gratuito e está disponível no Sistema Único de Saúde (SUS). A tuberculose tem cura quando o tratamento é feito de forma adequada, até o final.
+Disponível em: https://www.gov.br/saude/pt-br/assuntos/saude-de-a-a-z/t/tuberculose#:~:text=A%20tuberculose%20%C3%A9%20uma%20doen%C3%A7a,outros%20%C3%B3rg%C3%A3os%20e%2Fou%20sistemas. Acesso em: 14 jan. 2025.
+Qual das seguintes alternativas descreve a importância de seguir o tratamento completo dessa doença?</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>Minimizar os efeitos colaterais dos antibióticos usados no tratamento.</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>Reduzir a necessidade de campanhas de vacinação futuras contra a tuberculose.</t>
+        </is>
+      </c>
+      <c r="D955" t="inlineStr">
+        <is>
+          <t>Garantir que a bactéria seja completamente eliminada e prevenir a resistência bacteriana.</t>
+        </is>
+      </c>
+      <c r="E955" t="inlineStr">
+        <is>
+          <t>Evitar que a pessoa fique doente novamente no futuro sendo não transmissível após o início do tratamento.</t>
+        </is>
+      </c>
+      <c r="F955" t="inlineStr"/>
+      <c r="G955" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H955" t="inlineStr">
+        <is>
+          <t>Seguir o tratamento completo da tuberculose é crucial para garantir que a bactéria Mycobacterium tuberculosis seja completamente eliminada do organismo e para prevenir o desenvolvimento de resistência bacteriana. A adesão ao tratamento ajuda a evitar recaídas e a propagação de cepas resistentes da bactéria.</t>
+        </is>
+      </c>
+      <c r="I955" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J955" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K955" t="inlineStr"/>
+      <c r="L955" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>As bactérias e os vírus são microrganismos que podem causar doenças nos seres humanos, as bacterioses e as viroses. Embora ambos sejam agentes infecciosos, apresentam características e mecanismos de ação distintos. As bactérias são organismos unicelulares procariontes, capazes de se reproduzir por conta própria. Já os vírus são partículas infecciosas menores e mais simples, constituídas por material genético envolto por uma cápsula proteica.
+Qual a diferença entre as doenças causadas por esses microrganismos?</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>Ambas são causadas pelos mesmos agentes infecciosos e apresentam sintomas idênticos.</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>Viroses podem ser tratadas com antibióticos, enquanto bacterioses requerem apenas repouso e hidratação.</t>
+        </is>
+      </c>
+      <c r="D956" t="inlineStr">
+        <is>
+          <t>As bacterioses podem ser tratadas com antibióticos, enquanto viroses não respondem a esse tipo de tratamento.</t>
+        </is>
+      </c>
+      <c r="E956" t="inlineStr">
+        <is>
+          <t>As bacterioses, são causadas por organismos maiores e mais complexos, tendo um período de incubação mais longo do que as viroses.</t>
+        </is>
+      </c>
+      <c r="F956" t="inlineStr"/>
+      <c r="G956" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H956" t="inlineStr">
+        <is>
+          <t>As bacterioses são causadas por bactérias e podem ser tratadas com antibióticos, que são eficazes em eliminar ou inibir o crescimento das bactérias. Viroses, por outro lado, são causadas por vírus e não respondem aos antibióticos. O tratamento das viroses geralmente foca em aliviar os sintomas enquanto o sistema imunológico combate o vírus.</t>
+        </is>
+      </c>
+      <c r="I956" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J956" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K956" t="inlineStr"/>
+      <c r="L956" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>De acordo com as características dos vírus que foram descobertas a partir da década de 30, podemos dizer que:</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>os vírus são seres acelulares e só conseguem se reproduzir no interior de uma célula viva.</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>os vírus são seres que possuem apenas um formato determinado e, por isso, conseguem infectar qualquer ser vivo.</t>
+        </is>
+      </c>
+      <c r="D957" t="inlineStr">
+        <is>
+          <t>os vírus possuem metabolismo próprio, pois conseguem sobreviver em qualquer ambiente, mesmo sendo acelulares.</t>
+        </is>
+      </c>
+      <c r="E957" t="inlineStr">
+        <is>
+          <t>os vírus são seres microscópicos com apenas uma célula, porém, não possuem capacidade de se reproduzirem sozinhos.</t>
+        </is>
+      </c>
+      <c r="F957" t="inlineStr"/>
+      <c r="G957" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H957" t="inlineStr">
+        <is>
+          <t>Os vírus não são constituídos por células sendo, portanto, considerados acelulares. A reprodução deles é obrigatoriamente realizada dentro da célula de um outro ser vivo. Também não apresentam metabolismo próprio, precisando utilizar o metabolismo da célula hospedeira.</t>
+        </is>
+      </c>
+      <c r="I957" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J957" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K957" t="inlineStr"/>
+      <c r="L957" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>Entre as doenças virais, a dengue continua tendo grande número de casos no Brasil. Como forma de prevenção à doença, a população pode adotar medidas simples como: não deixar água parada e utilizar repelentes. Sobre a transmissão da dengue pode-se afirmar corretamente que:</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>o vírus da dengue é transmitido pelo mosquito Anopheles.</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>somente o macho do mosquito Aedes aegypti ​causa a dengue.</t>
+        </is>
+      </c>
+      <c r="D958" t="inlineStr">
+        <is>
+          <t>o vírus da dengue é transmitido por fêmeas do mosquito Aedes aegypti, portadoras do vírus.</t>
+        </is>
+      </c>
+      <c r="E958" t="inlineStr">
+        <is>
+          <t>o vírus causador da dengue é transmitido pela picada de machos e fêmeas do mosquito Aedes aegypti.</t>
+        </is>
+      </c>
+      <c r="F958" t="inlineStr"/>
+      <c r="G958" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H958" t="inlineStr">
+        <is>
+          <t>A transmissão da dengue ocorre apenas com a picada da fêmea do mosquito Aedes aegypti, portadora do vírus.</t>
+        </is>
+      </c>
+      <c r="I958" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J958" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K958" t="inlineStr"/>
+      <c r="L958" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>A leptospirose é uma doença infecciosa onde ocorre uma febre aguda, dor de cabeça e dores pelo corpo, sua penetração sucede através do contato com mucosas, pele com ou sem lesões, mas imersa por longos períodos em água contaminada.
+A leptospirose é uma doença que se alastra em situações de enchente porque, nesses casos, aumenta a:</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>presença de caramujos que transmite a doença.</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>proliferação de insetos que transmite a doença.</t>
+        </is>
+      </c>
+      <c r="D959" t="inlineStr">
+        <is>
+          <t>contaminação do ar pela bactéria que causa a doença.</t>
+        </is>
+      </c>
+      <c r="E959" t="inlineStr">
+        <is>
+          <t>contaminação da água pela urina de rato que transmite a doença.</t>
+        </is>
+      </c>
+      <c r="F959" t="inlineStr"/>
+      <c r="G959" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H959" t="inlineStr">
+        <is>
+          <t>A leptospirose é uma doença de origem bacteriana a qual tem como principal meio de disseminação a urina de rato, potencializada quando acontecem enchentes, pois o animal costuma urinar em esgotos os quais acabam entrando em contato com as pessoas através das enchentes.</t>
+        </is>
+      </c>
+      <c r="I959" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J959" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K959" t="inlineStr"/>
+      <c r="L959" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>A imagem abaixo apresenta medidas gerais de prevenção a gripe, doença causada pelo vírus influenza.  
+Disponível em: Influenza (gripe) - Secretaria de Saúde do Distrito Federal. Acesso em: 04 fev. 2025.
+A circulação de vírus respiratórios aumenta em determinadas épocas do ano, exigindo medidas preventivas para reduzir o risco de contaminação. Além dessas medidas, a vacinação é uma importante forma de proteção contra essas doenças.
+Com base nisso, assinale a alternativa que diferencia a vacinação das outras medidas preventivas:</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>A vacinação evita completamente o contato com vírus e bactérias, tornando desnecessárias outras medidas de prevenção.</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>A vacinação estimula o sistema imunológico a reconhecer e combater o vírus, reduzindo o risco de formas graves da doença.</t>
+        </is>
+      </c>
+      <c r="D960" t="inlineStr">
+        <is>
+          <t>A vacinação age imediatamente após a aplicação, garantindo proteção total contra qualquer tipo de patógeno.</t>
+        </is>
+      </c>
+      <c r="E960" t="inlineStr">
+        <is>
+          <t>A vacinação elimina completamente o vírus do ambiente, impedindo que ele se espalhe entre as pessoas.</t>
+        </is>
+      </c>
+      <c r="F960" t="inlineStr"/>
+      <c r="G960" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H960" t="inlineStr">
+        <is>
+          <t>A vacinação é um método de imunização ativa, que prepara o sistema imunológico para reconhecer e reagir contra vírus e bactérias específicos. Ao receber a vacina, o organismo produz anticorpos e memória imunológica, tornando-se mais eficiente no combate ao agente infeccioso, caso ocorra uma exposição futura. Diferentemente das medidas preventivas gerais, como evitar aglomerações e higienizar as mãos, que reduzem a chance de exposição ao vírus, a vacinação protege o corpo internamente, diminuindo os riscos de infecção severa, hospitalização e até morte.</t>
+        </is>
+      </c>
+      <c r="I960" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J960" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K960" t="inlineStr">
+        <is>
+          <t>ph10_cie_09.jpg</t>
+        </is>
+      </c>
+      <c r="L960" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>Uma pesquisa feita pela Universidade Federal de Minas Gerais (UFMG) identificou riscos sociais de longo prazo nas campanhas de desinformação sobre vacinas geradas pela pandemia. O crescimento de movimentos e discursos contra a vacinação, iniciante no Brasil até o início da pandemia de COVID-19, pode ter consequências de longo prazo para campanhas futuras, de acordo com pesquisadores. 
+Disponível em: https://www.em.com.br/app/noticia/bem-viver/2022/03/02/interna_bem_viver,1349446/covid-19-desinformacao-sobre-vacinas-pode-ter-consequencias-de-longo-prazo.shtml.Acesso em  16 nov. de 2023.
+Qual a importância da vacinação?</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>A vacinação é o modo mais eficiente para prevenção e erradicação de doenças.</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>A vacinação é o modo mais eficiente de se recuperar de uma doença.</t>
+        </is>
+      </c>
+      <c r="D961" t="inlineStr">
+        <is>
+          <t>A vacinação é o modo mais eficiente para o tratamento de doenças.</t>
+        </is>
+      </c>
+      <c r="E961" t="inlineStr">
+        <is>
+          <t>A vacinação é o modo mais eficiente de se contrair uma doença.</t>
+        </is>
+      </c>
+      <c r="F961" t="inlineStr"/>
+      <c r="G961" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H961" t="inlineStr">
+        <is>
+          <t>A vacinação é o modo mais eficiente para prevenção e erradicação de doenças. Através dela o sarampo que estava controlado na população, está voltando a ser disseminado, muito também pela diminuição da cobertura vacinal incentivada pelo movimento antivacina.</t>
+        </is>
+      </c>
+      <c r="I961" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J961" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K961" t="inlineStr"/>
+      <c r="L961" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>Os movimentos migratórios são fenômenos complexos que envolvem a movimentação de pessoas de um local para outro. Esses movimentos podem ser motivados por diversos fatores, como a busca por melhores condições de vida, oportunidades de emprego, ou até mesmo a fuga de conflitos e perseguições. No Brasil, a migração interna tem sido uma característica marcante, especialmente com o êxodo rural e a urbanização acelerada nas últimas décadas.
+Qual dos seguintes fatores é um exemplo de fator de repulsão populacional?</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>Oportunidades de emprego.</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>Qualidade de vida.</t>
+        </is>
+      </c>
+      <c r="D962" t="inlineStr">
+        <is>
+          <t>Conflitos armados.</t>
+        </is>
+      </c>
+      <c r="E962" t="inlineStr">
+        <is>
+          <t>Infraestrutura desenvolvida.</t>
+        </is>
+      </c>
+      <c r="F962" t="inlineStr"/>
+      <c r="G962" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H962" t="inlineStr">
+        <is>
+          <t>Conflitos armados são um exemplo clássico de fator de repulsão populacional, pois forçam as pessoas a deixarem suas casas em busca de segurança.</t>
+        </is>
+      </c>
+      <c r="I962" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J962" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K962" t="inlineStr"/>
+      <c r="L962" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>A migração de retorno é um fenômeno em que indivíduos que anteriormente migraram para outras regiões ou países decidem voltar ao seu local de origem. Esse movimento pode ser motivado por diversos fatores, como a busca por reestabelecer laços familiares e culturais.
+Qual dos seguintes fatores pode ser considerado um motivo para a migração de retorno?</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>Aumento da violência na região de origem.</t>
+        </is>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>Melhoria das condições econômicas na região de origem.</t>
+        </is>
+      </c>
+      <c r="D963" t="inlineStr">
+        <is>
+          <t>Falta de oportunidades de emprego na região de origem.</t>
+        </is>
+      </c>
+      <c r="E963" t="inlineStr">
+        <is>
+          <t>Desastres naturais na região de origem.</t>
+        </is>
+      </c>
+      <c r="F963" t="inlineStr"/>
+      <c r="G963" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H963" t="inlineStr">
+        <is>
+          <t>A melhoria das condições econômicas na região de origem é um fator que pode motivar a migração de retorno, pois oferece melhores oportunidades para os indivíduos que desejam voltar.</t>
+        </is>
+      </c>
+      <c r="I963" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J963" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K963" t="inlineStr"/>
+      <c r="L963" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>Qual das seguintes manchetes exemplifica um caso de xenofobia?</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>Formação de professores para o acolhimento de imigrantes e refugiados
+(Gov.Br)</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>Milhares de pessoas protestam em Portugal contra imigrantes no país
+(UOL)</t>
+        </is>
+      </c>
+      <c r="D964" t="inlineStr">
+        <is>
+          <t>Prefeitura oferece curso de Língua Portuguesa gratuito para imigrantes
+(Prefeitura de São Paulo)</t>
+        </is>
+      </c>
+      <c r="E964" t="inlineStr">
+        <is>
+          <t>Brasil acolhe mais de 125 mil migrantes e refugiados venezuelanos por meio da Operação Acolhida
+(Agência GOV)</t>
+        </is>
+      </c>
+      <c r="F964" t="inlineStr"/>
+      <c r="G964" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H964" t="inlineStr">
+        <is>
+          <t>No caso, o gabarito é enfático ao demonstrar insatisfação de um grupo social direcionada aos imigrantes. Enquanto todas as outras ações estão relacionadas à diferentes formas de acolhimento e integração de de imigrantes na sociedade.</t>
+        </is>
+      </c>
+      <c r="I964" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J964" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K964" t="inlineStr"/>
+      <c r="L964" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>O êxodo rural é um fenômeno migratório caracterizado pela saída de pessoas do campo para as cidades. Esse movimento é geralmente motivado pela busca de melhores condições de vida, como acesso a emprego, educação e serviços de saúde.
+No Brasil, o êxodo rural foi intensificado a partir da década de 1960 devido à/ao</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>aumento da oferta de empregos no campo.</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>mecanização da agricultura.</t>
+        </is>
+      </c>
+      <c r="D965" t="inlineStr">
+        <is>
+          <t>melhoria das condições de vida no campo.</t>
+        </is>
+      </c>
+      <c r="E965" t="inlineStr">
+        <is>
+          <t>redução da urbanização.</t>
+        </is>
+      </c>
+      <c r="F965" t="inlineStr"/>
+      <c r="G965" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H965" t="inlineStr">
+        <is>
+          <t>A mecanização da agricultura reduziu a necessidade de mão de obra no campo, levando muitas pessoas a migrarem para as cidades em busca de emprego.</t>
+        </is>
+      </c>
+      <c r="I965" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J965" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K965" t="inlineStr"/>
+      <c r="L965" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>A migração internacional envolve a movimentação de pessoas entre diferentes países. Esse tipo de migração pode ser motivado por fatores econômicos, políticos, sociais ou ambientais.
+Qual dos seguintes fatores é um exemplo de fator de atração para migrantes internacionais no Brasil?</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>Conflitos armados.</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>Desemprego.</t>
+        </is>
+      </c>
+      <c r="D966" t="inlineStr">
+        <is>
+          <t>Oportunidades de emprego.</t>
+        </is>
+      </c>
+      <c r="E966" t="inlineStr">
+        <is>
+          <t>Perseguições políticas.</t>
+        </is>
+      </c>
+      <c r="F966" t="inlineStr"/>
+      <c r="G966" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H966" t="inlineStr">
+        <is>
+          <t>Oportunidades de emprego são um fator de atração para migrantes internacionais, pois oferecem melhores condições de vida e estabilidade econômica.</t>
+        </is>
+      </c>
+      <c r="I966" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J966" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K966" t="inlineStr"/>
+      <c r="L966" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>A saída da população de um país denomina-se__________________, sendo que esta região pode ser um local de grande _______________________, já a entrada de indivíduos em um país denomina-se________________, e esta região receptora pode ser uma área de forte ____________________.
+Assinale a alternativa que completa corretamente o trecho acima:</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>imigração, repulsão demográfica, migração, atração demográfica.</t>
+        </is>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>emigração, atração demográfica, imigração, repulsão demográfica.</t>
+        </is>
+      </c>
+      <c r="D967" t="inlineStr">
+        <is>
+          <t>migração, repulsão demográfica, imigração, fluxos migratórios.</t>
+        </is>
+      </c>
+      <c r="E967" t="inlineStr">
+        <is>
+          <t>emigração, repulsão demográfica, imigração, atração demográfica.</t>
+        </is>
+      </c>
+      <c r="F967" t="inlineStr"/>
+      <c r="G967" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H967" t="inlineStr">
+        <is>
+          <t>A emigração representa a saída de indivíduos de seu país de origem, sendo que este pode ter características que o tornem uma área de repulsão demográfica, como altas taxas de desemprego ou catástrofes climáticas. A imigração é a entrada de indivíduos de outros países em um novo, sendo que este pode ter qualidades que o tornem um local de atração demográfica, como oportunidades de emprego.</t>
+        </is>
+      </c>
+      <c r="I967" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J967" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K967" t="inlineStr"/>
+      <c r="L967" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>Disponível em: https://goo.gl/images/zk5vQV Acesso em: 30 de jul. 2018
+De acordo com o mapa, o maior número de refugiados no Brasil vem da Síria. Qual o principal motivo que levou esse povo a deixar seu país de origem?</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>Xenofobia.</t>
+        </is>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>Conflitos militares.</t>
+        </is>
+      </c>
+      <c r="D968" t="inlineStr">
+        <is>
+          <t>Desemprego.</t>
+        </is>
+      </c>
+      <c r="E968" t="inlineStr">
+        <is>
+          <t>Misoginia.</t>
+        </is>
+      </c>
+      <c r="F968" t="inlineStr"/>
+      <c r="G968" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H968" t="inlineStr">
+        <is>
+          <t>A guerra civil atualmente em curso na Síria obrigou grande parte de sua população a buscar asilo em outros países, sendo o Brasil um dos destinos dos refugiados sírios..</t>
+        </is>
+      </c>
+      <c r="I968" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J968" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K968" t="inlineStr">
+        <is>
+          <t>ph10_geo_07.png</t>
+        </is>
+      </c>
+      <c r="L968" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>Fome, epidemias, desemprego e guerras, são alguns exemplos de fatores que podem causar:</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>imigrações.</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>atração populacional.</t>
+        </is>
+      </c>
+      <c r="D969" t="inlineStr">
+        <is>
+          <t>repulsão populacional.</t>
+        </is>
+      </c>
+      <c r="E969" t="inlineStr">
+        <is>
+          <t>êxodo rural.</t>
+        </is>
+      </c>
+      <c r="F969" t="inlineStr"/>
+      <c r="G969" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H969" t="inlineStr">
+        <is>
+          <t>A repulsão populacional é causada por fatores que põe em risco a qualidade de vida da população.</t>
+        </is>
+      </c>
+      <c r="I969" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J969" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K969" t="inlineStr"/>
+      <c r="L969" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>Disponível em: https://goo.gl/images/uRx9Ng Acesso em: 30 de jul. 2018
+De acordo com os dados acima, os movimentos migratórios mais intensos aconteciam da região nordeste para a região sudeste do país, principalmente para o estado de São Paulo. Com o passar das décadas esse fluxo foi diminuindo e até mesmo invertido. Como é denominada a volta do migrante a sua terra de origem?</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>Êxodo rural.</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>Migração de retorno.</t>
+        </is>
+      </c>
+      <c r="D970" t="inlineStr">
+        <is>
+          <t>Repulsão demográfica.</t>
+        </is>
+      </c>
+      <c r="E970" t="inlineStr">
+        <is>
+          <t>Emigração.</t>
+        </is>
+      </c>
+      <c r="F970" t="inlineStr"/>
+      <c r="G970" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H970" t="inlineStr">
+        <is>
+          <t>A migração de retorno acontece quando os migrantes regressam a sua terra de origem após ter passado um período em outro lugar.</t>
+        </is>
+      </c>
+      <c r="I970" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J970" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K970" t="inlineStr">
+        <is>
+          <t>ph10_geo_09.jpg</t>
+        </is>
+      </c>
+      <c r="L970" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>Na segunda metade do século XX, o Brasil passou por um intenso deslocamento populacional das zonas agrárias para áreas urbanizadas. Esse processo recebe o nome de Êxodo rural. Que fatores contribuíram para esse movimento migratório?</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>Mecanização agrícola, industrialização, estrutura fundiária concentradora.</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>Urbanização, reforma agrária, marginalização do campo.</t>
+        </is>
+      </c>
+      <c r="D971" t="inlineStr">
+        <is>
+          <t>Êxodo urbano, baixa produtividade, revolução industrial brasileira.</t>
+        </is>
+      </c>
+      <c r="E971" t="inlineStr">
+        <is>
+          <t>Mecanização da cidade, favelização do campo, reformas trabalhistas.</t>
+        </is>
+      </c>
+      <c r="F971" t="inlineStr"/>
+      <c r="G971" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H971" t="inlineStr">
+        <is>
+          <t>A mecanização agrícola no campo criou um forte processo de desemprego, já a industrialização nas áreas urbanas gerou empregos e melhores salários. A estrutura fundiária brasileira é extremamente concentradora pois a maior parte das terras pertencem a um grupo seleto da população. Esses fatores tornaram o campo pouco atrativo, causando a repulsa demográfica e por consequência o êxodo rural.</t>
+        </is>
+      </c>
+      <c r="I971" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J971" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K971" t="inlineStr"/>
+      <c r="L971" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>Em pleno centro da Espanha, em meio às terras frias e áridas castelhanas, ergue-se uma pequena cidade de 141 quilômetros quadrados.
+Atualmente ela é habitada por cerca de 9 mil pessoas e ostenta o título de "vila muito ilustre, antiga, coroada, leal e muito nobre".
+Ali ocorreu há 525 anos um fato histórico que determinou a configuração política e territorial da América, dividiu o mundo em dois hemisférios e definiu a língua e a cultura de milhões de pessoas.
+Essa cidade, chamada Tordesilhas, está localizada ao norte de Madri.
+Disponível em: https://www.bbc.com/portuguese/internacional-48554080. Acesso em: 13 dez. 2024.
+O Tratado de Tordesilhas foi responsável por</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>firmar acordos de comércio entre a Espanha e as Índias.</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>separar em definitivo as Igrejas Protestantes e a Igreja Católica.</t>
+        </is>
+      </c>
+      <c r="D972" t="inlineStr">
+        <is>
+          <t>dividir as terras e os oceanos além da Europa entre Portugal e Espanha.</t>
+        </is>
+      </c>
+      <c r="E972" t="inlineStr">
+        <is>
+          <t>consolidar a independência do Império do Brasil dos domínios portugueses.</t>
+        </is>
+      </c>
+      <c r="F972" t="inlineStr"/>
+      <c r="G972" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H972" t="inlineStr">
+        <is>
+          <t>O Tratado de Tordesilhas, assinado em 1494, foi responsável por dividir as terras e os oceanos além da Europa entre Portugal e Espanha. Um meridiano a 370 léguas a oeste de Cabo Verde delimitou as áreas de domínio colonial dos dois países, com Portugal ficando com as terras a leste e a Espanha com as terras a oeste.</t>
+        </is>
+      </c>
+      <c r="I972" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J972" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K972" t="inlineStr"/>
+      <c r="L972" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>Sua primeira viagem à Índia foi iniciada em 1497 e, no ano seguinte, o navegante português cruzou o cabo da Boa Esperança e alcançou seu destino. Chegar às Índias era importante pois apenas lá os portugueses podiam conseguir especiarias como pimenta e noz-moscada, artigos que, na Europa, valiam tanto quanto prata e ouro. O caminho marítimo para o Oriente aberto por Vasco da Gama ajudaria Portugal a se tornar uma potência mundial.
+Disponível em: https://super.abril.com.br/mundo-estranho/o-que-foram-as-grandes-navegacoes. Acesso em: 13 dez. 2024.
+A viagem de Vasco da Gama foi importante pelo fato de que</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>abriu uma nova rota de comércio para a Índia.</t>
+        </is>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>determinou a supremacia espanhola nos mares.</t>
+        </is>
+      </c>
+      <c r="D973" t="inlineStr">
+        <is>
+          <t>representou a chegada dos portugueses ao Novo Mundo.</t>
+        </is>
+      </c>
+      <c r="E973" t="inlineStr">
+        <is>
+          <t>tornou a colonização do continente americano desnecessária.</t>
+        </is>
+      </c>
+      <c r="F973" t="inlineStr"/>
+      <c r="G973" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H973" t="inlineStr">
+        <is>
+          <t>A viagem de Vasco da Gama foi importante porque abriu uma nova rota marítima para a Índia, através do Cabo da Boa Esperança, permitindo que os portugueses estabelecessem um comércio direto de especiarias como pimenta e noz-moscada, que eram extremamente valiosas na Europa.</t>
+        </is>
+      </c>
+      <c r="I973" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J973" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K973" t="inlineStr"/>
+      <c r="L973" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>Bartolomeu Dias liderou a primeira expedição a atravessar, em 1488, o cabo das Tormentas, mais tarde rebatizado de cabo da Boa Esperança (no extremo sul da África). O curioso é que Bartolomeu Dias não percebeu o feito, pois passou pelo cabo durante uma forte tempestade. Poderia ter chegado à Índia, mas um motim da tripulação o obrigou a retornar a Portugal.
+Disponível em: https://super.abril.com.br/mundo-estranho/o-que-foram-as-grandes-navegacoes. Acesso em: 13 dez. 2024. (Adaptado).
+A expedição de Bartolomeu Dias representou a(o)</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>fracasso dos objetivos expansionistas de Portugal.</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>abandono por parte de Portugal de tentar chegar à Índia.</t>
+        </is>
+      </c>
+      <c r="D974" t="inlineStr">
+        <is>
+          <t>união dos países europeus no projeto de expansão marítima.</t>
+        </is>
+      </c>
+      <c r="E974" t="inlineStr">
+        <is>
+          <t>confirmação da viabilidade de uma rota marítima para a Índia.</t>
+        </is>
+      </c>
+      <c r="F974" t="inlineStr"/>
+      <c r="G974" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H974" t="inlineStr">
+        <is>
+          <t>A expedição de Bartolomeu Dias, ao atravessar o Cabo da Boa Esperança, confirmou que era possível navegar ao redor do sul da África, abrindo a perspectiva de uma rota marítima para a Índia, ainda que Dias não tenha completado a viagem até lá.</t>
+        </is>
+      </c>
+      <c r="I974" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J974" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K974" t="inlineStr"/>
+      <c r="L974" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>Foram os mouros que aperfeiçoaram o astrolábio, instrumento de origem grega que permite a orientação em alto-mar pela observação de estrelas. Sua ciência náutica teve grande influência sobre a Escola de Sagres, em Portugal, de onde saíram os oficiais e marinheiros das navegações da Era dos Descobrimentos
+Disponível em: https://super.abril.com.br/mundo-estranho/como-foi-a-ocupacao-moura-da-peninsula-iberica. Acesso em: 13 dez. 2024.
+O texto deixa evidente a(o)</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>atraso tecnológico português no contexto das Grandes Navegações.</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>acaso por trás da chegada dos portugueses ao continente americano.</t>
+        </is>
+      </c>
+      <c r="D975" t="inlineStr">
+        <is>
+          <t>influência dos avanços tecnológicos muçulmanos no pioneirismo português.</t>
+        </is>
+      </c>
+      <c r="E975" t="inlineStr">
+        <is>
+          <t>parceria firmada entre a Espanha e Portugal para a realização das expedições.</t>
+        </is>
+      </c>
+      <c r="F975" t="inlineStr"/>
+      <c r="G975" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H975" t="inlineStr">
+        <is>
+          <t>O texto menciona que os mouros aperfeiçoaram o astrolábio e que sua ciência náutica teve grande influência sobre a Escola de Sagres em Portugal. Essa influência tecnológica foi crucial para o sucesso dos portugueses nas navegações da Era dos Descobrimentos.</t>
+        </is>
+      </c>
+      <c r="I975" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J975" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K975" t="inlineStr"/>
+      <c r="L975" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>O navegador genovês Cristóvão Colombo (1451-1506) nasceu em uma família pobre e começou a navegar cedo. Comandou um navio pela primeira vez em 1473, aos 22 anos. Ao retornar de sua primeira viagem continental, em 1493, recebe o título de “Vice-Rei e governador das Terras Firmes e Ilhas Descobertas e por Descobrir”. Apesar disso, morreu pobre e esquecido. Seu diário só foi recuperado por Fernando, seu filho, após a sua morte.
+Disponível em: https://super.abril.com.br/ciencia/diarios-da-descoberta-da-america. Acesso em: 13 dez. 2024.
+A importância histórica de Cristóvão Colombo se encontra no fato de que ele</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>comandou a primeira expedição europeia a chegar na América.</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>foi o primeiro europeu a navegar a pelo Cabo da Boa Esperança.</t>
+        </is>
+      </c>
+      <c r="D976" t="inlineStr">
+        <is>
+          <t>liderou os cristãos nas guerras de Reconquista contra os mouros.</t>
+        </is>
+      </c>
+      <c r="E976" t="inlineStr">
+        <is>
+          <t>protagonizou o surgimento das igrejas protestantes no século XVI.</t>
+        </is>
+      </c>
+      <c r="F976" t="inlineStr"/>
+      <c r="G976" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H976" t="inlineStr">
+        <is>
+          <t>Cristóvão Colombo é historicamente famoso por comandar a primeira expedição europeia reconhecida a chegar na América em 1492, financiada pelos reis católicos da Espanha. Sua viagem marcou o início do contato sustentado entre a Europa e as Américas.</t>
+        </is>
+      </c>
+      <c r="I976" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J976" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K976" t="inlineStr"/>
+      <c r="L976" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>E assim, não tendo a quem vencer na terra, 
+Vai cometer as ondas do Oceano 
+Este é o primeiro Rei que se desterra 
+Da pátria, por fazer que o Africano 
+Conheça, pelas armas, quanto excede 
+A lei de Cristo à lei de Mafamede
+CAMÕES. Os Lusíadas, IV, 48.
+Luís de Camões foi um dos maiores nome da literatura renascentista portuguesa. A temática do soneto de Camões apresentada acima se relaciona, na história de Portugal, com a/as</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>conquista do continente africano através das Cruzadas.</t>
+        </is>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>à conquista de Ceuta como um marco da supremacia de Portugal e abertura para a expansão marítima.</t>
+        </is>
+      </c>
+      <c r="D977" t="inlineStr">
+        <is>
+          <t>guerras de Reconquista contra os mouros do Norte da África.</t>
+        </is>
+      </c>
+      <c r="E977" t="inlineStr">
+        <is>
+          <t>expansão pelo continente europeu para derrubar os monarcas rivais.</t>
+        </is>
+      </c>
+      <c r="F977" t="inlineStr"/>
+      <c r="G977" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H977" t="inlineStr">
+        <is>
+          <t>Camões foi um reconhecido escritor português que em diversos sonetos tratou temas relativos à realidade em que vivia. Um traço marcante de Portugal no século XV foi a expansão marítima, resultado, entre outros fatores, da centralização política na figura do rei.</t>
+        </is>
+      </c>
+      <c r="I977" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J977" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K977" t="inlineStr"/>
+      <c r="L977" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>Observe o mapa a seguir:
+Instituto Geográfico Nacional, Google, Geo-Basis-DE (BKG), 2009. Disponível em: https://www.google.com.br/maps/. Acesso em: 08 maio 2020.
+O mapa acima nos permite entender um fator que explica o pioneirismo de Portugal nas Grandes Navegações, que foi o(a)</t>
+        </is>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>fácil acesso ao Oceano Atlântico.</t>
+        </is>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>fortalecimento da nobreza feudal.</t>
+        </is>
+      </c>
+      <c r="D978" t="inlineStr">
+        <is>
+          <t>enfraquecimento da autoridade real.</t>
+        </is>
+      </c>
+      <c r="E978" t="inlineStr">
+        <is>
+          <t>concorrência da monarquia espanhola.</t>
+        </is>
+      </c>
+      <c r="F978" t="inlineStr"/>
+      <c r="G978" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H978" t="inlineStr">
+        <is>
+          <t>A mapa apresenta como Portugal se encontrava com acesso direito ao Oceano Atlântico. Esse fator geográfico, somado com a experiência prévia que os portugueses tinham com as atividades marítimas, facilitaram o seu lançamento ultramarino.</t>
+        </is>
+      </c>
+      <c r="I978" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J978" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K978" t="inlineStr">
+        <is>
+          <t>ph10_his_07.png</t>
+        </is>
+      </c>
+      <c r="L978" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>A representação a seguir foi feita por um italiano ao imaginar os seres míticos que poderiam habitar as regiões do Novo Mundo.
+Sobre a relação entre as crenças em seres como os da imagem e a expansão marítima, é correto afirmar que os viajantes do século XV</t>
+        </is>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>exploraram os mares sem receio, pois não tinham a tradição de acreditar em seres míticos, como sereias.</t>
+        </is>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>interromperam suas rotas ao descobrirem espécies que confirmavam seus medos de animais fantásticos no mar.</t>
+        </is>
+      </c>
+      <c r="D979" t="inlineStr">
+        <is>
+          <t>acompanharam o teocentrismo que se fortalecia na Europa e se recusaram a viajar para regiões que tivessem sereias.</t>
+        </is>
+      </c>
+      <c r="E979" t="inlineStr">
+        <is>
+          <t>superaram receios sobre esses seres conforme inovações técnicas desvendavam mitos como monstros e precipícios no fim do oceano.</t>
+        </is>
+      </c>
+      <c r="F979" t="inlineStr"/>
+      <c r="G979" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H979" t="inlineStr">
+        <is>
+          <t>Mitos sobre perigos de se viajar pelo oceano, como seres fantásticos e precipícios ao fim do mar, eram crenças que amedrontavam a população europeia. No entanto, conforme a mentalidade do continente tornou-se mais racionalista e as inovações técnicas permitiram que as viagens se tornassem mais seguras, essas crenças se desmistificaram e a exploração dos oceanos se popularizou.</t>
+        </is>
+      </c>
+      <c r="I979" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J979" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K979" t="inlineStr">
+        <is>
+          <t>ph10_his_08.png</t>
+        </is>
+      </c>
+      <c r="L979" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>As zonas costeiras eram abastecidas por peixe fresco, o que não sucedia nas zonas interiores – onde algum ainda chegava às escassas elites –, apesar de se recorrer ao peixe de água doce. Havia que o importar, como sucedia com a sardinha, abundante em toda a costa, mais acessível e transportada salgada, mas que não chegava para as necessidades da procura. Há que ver, também, que o bacalhau, uma vez curado adequadamente, teria uma maior capacidade de conservação. Outros pequenos peixes, [...] ou o polvo seco [...] não tiveram uma difusão comparável à escala do país. O bacalhau tornou-se uma mercadoria importante, muitos séculos antes de a ciência moderna o valorizar como alimento excecional devido à sua carne branca e firme, quase isenta de gordura, que quando seca é um concentrado de proteínas.
+SOBRAL, José Manuel; RODRIGUES, Patrícia. O fiel amigo: o bacalhau e a identidade portuguesa. Etnográfica, Lisboa, v. 17, n. 3, p. 621. Disponível em: http://www.scielo.mec.pt/scielo.php?script=sci_arttext&amp;pid=S0873-65612013000300010&amp;lang=pt. Acesso em: 08 maio 2020.
+A proximidade da culinária portuguesa com o consumo de peixes expõe um fator para o pioneirismo português no processo de expansão marítima, que foi/foram</t>
+        </is>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>o controle de todo o litoral europeu.</t>
+        </is>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>as alianças feitas com os povos do Novo Mundo.</t>
+        </is>
+      </c>
+      <c r="D980" t="inlineStr">
+        <is>
+          <t>a experiência com atividades marítimas, como a pesca.</t>
+        </is>
+      </c>
+      <c r="E980" t="inlineStr">
+        <is>
+          <t>o princípio mercantilista que via nos pescados a fonte de riquezas.</t>
+        </is>
+      </c>
+      <c r="F980" t="inlineStr"/>
+      <c r="G980" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H980" t="inlineStr">
+        <is>
+          <t>A prática da pesca demonstra a experiência que os portugueses tinham com as atividades marítimas. Isso lhes deu vantagem para realizar as Grandes Navegações, uma vez que já sabiam como conseguir alimento em alto mar.</t>
+        </is>
+      </c>
+      <c r="I980" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J980" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K980" t="inlineStr"/>
+      <c r="L980" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>Além da experiência [...] dos navegantes, foram as velas latinas idealizadas pelos sábios da Escola de Sagres que ajudaram os aventureiros a atravessar o mar [...]. Os astrônomos e matemáticos da Escola de Sagres desenvolveram tabelas com a declinação dos astros, bem como eficientes instrumentos de navegação, como o astrolábio e a balestilha, usados para medir a posição dos astros e determinar a posição da embarcação.
+FILGUEIRAS, O. Vigia de ventos e ondas. Revista Fapesp, ed. 62, mar. 2000. (Adaptado).
+Disponível em: https://revistapesquisa.fapesp.br/2001/03/01/vigia-de-ventos-e-ondas/​. Acesso em: 8 maio 2020.
+O texto trata da controversa Escola de Sagres que teria sido fundada por D. Henrique. De acordo com o texto e seus conhecimentos, a Escola de Sagres representou um/a</t>
+        </is>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>grande mercado de pescados portugueses.</t>
+        </is>
+      </c>
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>ponto de encontro de navegadores lusitanos.</t>
+        </is>
+      </c>
+      <c r="D981" t="inlineStr">
+        <is>
+          <t>universidade onde o principal curso era a navegação.</t>
+        </is>
+      </c>
+      <c r="E981" t="inlineStr">
+        <is>
+          <t>movimento criado por jesuítas que combatiam a navegação.</t>
+        </is>
+      </c>
+      <c r="F981" t="inlineStr"/>
+      <c r="G981" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H981" t="inlineStr">
+        <is>
+          <t>Não existem evidências de que de fato tenha existido fisicamente uma Escola de Sagres para navegadores, porém é sabido que uma vila foi construída com o intuito de dar apoio aos navegadores portugueses e se constituiu como um local de troca de experiências e conhecimentos entre os frequentadores.</t>
+        </is>
+      </c>
+      <c r="I981" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J981" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K981" t="inlineStr"/>
+      <c r="L981" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>Pesquisadores japoneses desenvolvem plástico que se desfaz no oceano
+Pesquisadores do Centro de Ciência de Materiais Emergentes (Cems, na sigla em inglês), do instituto japonês Riken, desenvolveram um novo plástico biodegradável, que, além de ser durável e reciclável, decompõe-se quando em contato com a água do mar.
+Disponível em: https://www.jornaljoca.com.br/pesquisadores-japoneses-desenvolvem-plastico-que-se-desfaz-no-oceano/. Acesso em 18 dez. 2024.
+O pronome relativo “que” possui algumas variações. Por qual forma desse pronome o termo em destaque pode ser substituído?</t>
+        </is>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>O qual.</t>
+        </is>
+      </c>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>Em que.</t>
+        </is>
+      </c>
+      <c r="D982" t="inlineStr">
+        <is>
+          <t>No qual.</t>
+        </is>
+      </c>
+      <c r="E982" t="inlineStr">
+        <is>
+          <t>Pelo qual.</t>
+        </is>
+      </c>
+      <c r="F982" t="inlineStr"/>
+      <c r="G982" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H982" t="inlineStr">
+        <is>
+          <t>O pronome relativo "o qual" pode substituir "que" na frase sem alterar o sentido, pois ambos se referem ao "plástico biodegradável" mencionado anteriormente. Essa substituição mantém a clareza e coesão do texto, sendo uma variação adequada do pronome relativo "que".</t>
+        </is>
+      </c>
+      <c r="I982" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J982" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K982" t="inlineStr"/>
+      <c r="L982" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>Ao fundo, por trás do balcão, estava sentada uma mulher, cujo rosto amarelo e bexiguento não se destacava logo, à primeira vista; mas logo que se destacava era um espetáculo curioso.
+ASSIS, Machado de. Obra Completa. Disponível em: https://www.dominiopublico.gov.br/download/texto/bv000003.pdf. Acesso em: 19 dez. 2024.
+No excerto acima, o pronome relativo "cujo" estabelece uma relação entre as palavras</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>"mulher” e “bexiguento”.</t>
+        </is>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>“mulher” e “amarelo”.</t>
+        </is>
+      </c>
+      <c r="D983" t="inlineStr">
+        <is>
+          <t>“mulher” e “balcão”.</t>
+        </is>
+      </c>
+      <c r="E983" t="inlineStr">
+        <is>
+          <t>“mulher” e “rosto”.</t>
+        </is>
+      </c>
+      <c r="F983" t="inlineStr"/>
+      <c r="G983" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H983" t="inlineStr">
+        <is>
+          <t>O pronome relativo "cujo" é utilizado para indicar uma relação de posse entre dois substantivos. No excerto, "cujo" estabelece essa relação entre "mulher" e "rosto", indicando que o rosto pertence à mulher. O uso de "cujo" é apropriado para mostrar que o rosto, descrito como "amarelo e bexiguento", é uma característica da mulher sentada por trás do balcão.</t>
+        </is>
+      </c>
+      <c r="I983" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J983" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K983" t="inlineStr"/>
+      <c r="L983" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>Canção do Exílio
+Minha terra tem palmeiras,
+Onde canta o Sabiá;
+As aves, que aqui gorjeiam,
+Não gorjeiam como lá.
+[…]
+Não permita Deus que eu morra,
+Sem que eu volte para lá;
+Sem que disfrute os primores
+Que não encontro por cá;
+Sem qu'inda aviste as palmeiras,
+Onde canta o Sabiá. 
+DIAS, Gonçalves. Primeiros cantos. Disponível em: http://www.horizonte.unam.mx/brasil/gdias.html.
+No excerto acima, o pronome relativo "onde" substitui qual termo?</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>Aves.</t>
+        </is>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>Terra.</t>
+        </is>
+      </c>
+      <c r="D984" t="inlineStr">
+        <is>
+          <t>Sabiá.</t>
+        </is>
+      </c>
+      <c r="E984" t="inlineStr">
+        <is>
+          <t>Palmeiras.</t>
+        </is>
+      </c>
+      <c r="F984" t="inlineStr"/>
+      <c r="G984" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H984" t="inlineStr">
+        <is>
+          <t>O pronome “onde” indica o local em que o sabiá canta. Além disso, é preciso atentar-se à interpretação do poema e depreender que o sabiá está cantando especificamente na palmeira.</t>
+        </is>
+      </c>
+      <c r="I984" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J984" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K984" t="inlineStr"/>
+      <c r="L984" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>Não havia remédio senão ir.
+— Diga-lhe que vou.
+— Aonde? perguntou D. Plácida.
+— Onde ela disse que me espera.
+ASSIS, Machado de. Obra Completa. Disponível em: https://www.dominiopublico.gov.br/download/texto/bv000003.pdf. Acesso em: 19 dez. 2024.
+No excerto acima são usados os pronomes relativos "aonde" e "onde", que muitas vezes causam confusão na língua falada. Qual é a explicação para o uso desses pronomes, de acordo com a norma culta?</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>"Aonde" e "onde" são iguais, por isso aparecem no mesmo excerto.</t>
+        </is>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>"Aonde" é uma palavra mais formal, enquanto "onde" é usada no dia a dia.</t>
+        </is>
+      </c>
+      <c r="D985" t="inlineStr">
+        <is>
+          <t>"Aonde" é usado para começar uma pergunta, enquanto "onde" é só para respostas.</t>
+        </is>
+      </c>
+      <c r="E985" t="inlineStr">
+        <is>
+          <t>"Aonde" é usado para indicar movimento para algum lugar, o pronome "onde", por sua vez, é usado para mostrar que algo está em um lugar.</t>
+        </is>
+      </c>
+      <c r="F985" t="inlineStr"/>
+      <c r="G985" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H985" t="inlineStr">
+        <is>
+          <t>"Aonde" é usado para indicar movimento em direção a um lugar, já "onde" mostra permanência em um lugar.</t>
+        </is>
+      </c>
+      <c r="I985" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J985" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K985" t="inlineStr"/>
+      <c r="L985" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>COMO O REMÉDIO CHEGA AONDE DÓI?
+O nosso corpo é totalmente coberto por vasos sanguíneos. Da mesma forma que se espalham pela nossa pele (basta um pequeno corte para vermos o sangue e constatarmos que eles estão ali!), eles também estão nos nossos demais órgãos. Assim, quando tomamos um medicamento, ele vai para a corrente sanguínea e percorre os órgãos do nosso corpo, através dos vasos sanguíneos, em busca do endereço da dor, ou seja, do lugar da nossa queixa.
+A célula que tiver o receptor específico para o medicamento vai recebê-lo. É como se fosse uma chave, que só entra na fechadura certa para ela! Ao abrir essa porta, temos então o efeito desejado para aliviar a dor ou o mal-estar. Em resumo: todo medicamento carrega um endereço certo onde deve chegar!
+Disponível em: https://chc.org.br/artigo/mundo-de-curiosidades-361/. Acesso em 18 dez. 2024.
+Leia as frases a seguir e escolha a alternativa que preenche corretamente com "onde" ou "aonde":
+1. O nosso corpo é coberto por vasos sanguíneos, ________ o sangue circula.
+2. O remédio procura ________ ele deve agir, percorrendo a corrente sanguínea.
+3. Você sabe ________ o remédio encontra o receptor específico?
+4. Os medicamentos vão ________ está a célula da queixa.</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>onde, aonde, onde, onde.</t>
+        </is>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>onde, onde, onde, aonde.</t>
+        </is>
+      </c>
+      <c r="D986" t="inlineStr">
+        <is>
+          <t>aonde, onde, onde, onde.</t>
+        </is>
+      </c>
+      <c r="E986" t="inlineStr">
+        <is>
+          <t>onde, aonde, aonde, onde.</t>
+        </is>
+      </c>
+      <c r="F986" t="inlineStr"/>
+      <c r="G986" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H986" t="inlineStr">
+        <is>
+          <t>Nas três primeiras frases, a regência dos verbos não exige o uso da preposição “a”, por isso o correto seria o uso de “onde”, indicando um local e não a direção de um movimento. Já na última frase, o verbo “ir” (“vão”) pede o uso dessa preposição e, portanto, o pronome relativo correto seria “aonde”.</t>
+        </is>
+      </c>
+      <c r="I986" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J986" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K986" t="inlineStr"/>
+      <c r="L986" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>Se temos de esperar,
+que seja para colher a semente boa
+que lançamos hoje no solo da vida.
+CORALINA, Cora.
+O termo “que”, presente no 3º verso, classifica-se como</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>artigo definido, pois indetermina o substantivo.</t>
+        </is>
+      </c>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>advérbio, pois atribui uma circunstância ao verbo.</t>
+        </is>
+      </c>
+      <c r="D987" t="inlineStr">
+        <is>
+          <t>pronome relativo, pois refere-se a um termo anterior.</t>
+        </is>
+      </c>
+      <c r="E987" t="inlineStr">
+        <is>
+          <t>pronome pessoal, pois designa a pessoa do discurso.</t>
+        </is>
+      </c>
+      <c r="F987" t="inlineStr"/>
+      <c r="G987" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H987" t="inlineStr">
+        <is>
+          <t>O termo “que” está retomando a expressão “semente boa” do verso anterior. Assim, o verso “que lançamos hoje no solo da vida” poderia ser substituído por “Lançamos a semente boa hoje no solo da vida”.</t>
+        </is>
+      </c>
+      <c r="I987" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J987" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K987" t="inlineStr"/>
+      <c r="L987" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>Redação em construção
+É sabido que o fato novo assusta os indivíduos, que preferem o mal velho, testado e vivido, à experiência nova, sempre ameaçadora. Se você disser ao cidadão desprevenido que o leite, por ser essencial, deve sair das mãos dos particulares para cooperativas ou entidades estatais, se você disser que os bancos, vivendo exclusivamente das poupanças populares, não têm nenhuma razão de estar em mãos privadas, o cidadão o olhará com olhos perplexos de quem vê alguém propondo algo muito perigoso. Mas, se, ao contrário, você advogar a tese de que a água deveria ser explorada por particulares, todos se voltarão contra você pois – com toda razão – jamais poderiam admitir essa hipótese, tão acostumados estão com essa que é uma das mais antigas realizações comunitárias do homem: a água é direito e serventia de todos. Por isso o cidadão deve ficar alerta, sobretudo para com os malucos, excepcionais e marginais, pois estes, quase sempre, são os que trazem as mais espantosas propostas de renovação contra tudo o que foi estabelecido.
+FERNANDES, Millôr. In: CARNEIRO, Agostinho Dias. Redação em construção. São Paulo: Moderna. p. 105.
+Glossário:
+Advogar: defender alguém ou alguma causa.
+“[...] trazem as mais espantosas propostas de renovação [...]”
+A língua oferece diferentes possibilidades de organização para se expressar um mesmo conteúdo. Assinale a alternativa que demonstre a reescrita do trecho acima, substituindo, sem mudança de sentido, o adjetivo “espantosas” pelo verbo “espantar” em uma oração que seja introduzida por pronome relativo.</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>Trazem as propostas de renovação cujo mais espantam.</t>
+        </is>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>Trazem as propostas de renovação onde mais espantam.</t>
+        </is>
+      </c>
+      <c r="D988" t="inlineStr">
+        <is>
+          <t>Trazem as propostas de renovação aonde mais espantam.</t>
+        </is>
+      </c>
+      <c r="E988" t="inlineStr">
+        <is>
+          <t>Trazem as propostas de renovação que mais espantam.</t>
+        </is>
+      </c>
+      <c r="F988" t="inlineStr"/>
+      <c r="G988" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H988" t="inlineStr">
+        <is>
+          <t>O pronome relativo “que” seria adequado, sem prejuízo de sentido, para retomar o substantivo “propostas”.</t>
+        </is>
+      </c>
+      <c r="I988" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J988" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K988" t="inlineStr"/>
+      <c r="L988" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>Leia o texto a seguir.
+Fake news ganha espaço no Facebook e jornalismo profissional perde
+Em janeiro, páginas de notícias falsas engajaram cinco vezes mais do que as de jornalismo
+Do último trimestre do ano passado até o momento, as páginas brasileiras de notícias falsas e sensacionalistas ganharam engajamento no Facebook, e o jornalismo profissional apresentou queda.
+É o que mostra análise feita pela Folha com base em 21 páginas que postam “fake news” e 51 de jornalismo profissional. A taxa média de interações no primeiro grupo aumentou 61,6% entre outubro do ano passado e janeiro deste ano. Já o segundo grupo viu queda de 17% no mesmo período.
+As interações dos usuários com as páginas, incluindo curtidas, reações, comentários e compartilhamentos, foram analisadas de outubro de 2017 até 3 de fevereiro.
+Fake news ganha espaço no Facebook e jornalismo profissional perde. Folha de S.Paulo. São Paulo, 8 fev. 2018. Disponível em:
+&lt;https://www1.folha.uol.com.br/poder/2018/02/fake- news-ganha-espaco-no-facebook-e-jornalismoprofissional-perde.shtml&gt;. Acesso em: 8 fev. 2018.
+No segundo parágrafo dessa notícia, o verbo “postar” encontra-se na terceira pessoa do plural porque faz referência</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>ao pronome relativo “que”, que desempenha função de sujeito no período.</t>
+        </is>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>ao substantivo próprio “Folha”, implicando desvio de concordância.</t>
+        </is>
+      </c>
+      <c r="D989" t="inlineStr">
+        <is>
+          <t>ao numeral “21”, núcleo do sujeito, com o qual o verbo “postar” concorda.</t>
+        </is>
+      </c>
+      <c r="E989" t="inlineStr">
+        <is>
+          <t>ao sujeito composto, cujos núcleos são “fake news” e “jornalismo profissional”.</t>
+        </is>
+      </c>
+      <c r="F989" t="inlineStr"/>
+      <c r="G989" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H989" t="inlineStr">
+        <is>
+          <t>O verbo “postar” encontra-se na terceira pessoa do plural porque a concordância verbal, quando o pronome relativo “que” desempenha função de sujeito no período, é feita com o termo a que ele se refere (seu antecedente), ou seja, nesse caso, “21 páginas”.</t>
+        </is>
+      </c>
+      <c r="I989" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J989" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K989" t="inlineStr"/>
+      <c r="L989" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>Leia o texto a seguir.
+Disponível em: &lt;https://www.nsctotal.com.br/noticias/quem-impos-os-cortes-foi-a-realidade-nao-o-governo-afirma-secretario-joao-paulo-kleinubing&gt;. Acesso em: 18 ago. 2020.
+O verbo “impor” foi flexionado na terceira pessoa do singular porque</t>
+        </is>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>não há um sujeito específico nesse período.</t>
+        </is>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>concorda com o sujeito simples "João Paulo Kleinübing".</t>
+        </is>
+      </c>
+      <c r="D990" t="inlineStr">
+        <is>
+          <t>concorda com o pronome relativo "quem", cuja referência é “realidade”.</t>
+        </is>
+      </c>
+      <c r="E990" t="inlineStr">
+        <is>
+          <t>concorda com "secretário", que exige o verbo na terceira pessoa do singular.</t>
+        </is>
+      </c>
+      <c r="F990" t="inlineStr"/>
+      <c r="G990" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H990" t="inlineStr">
+        <is>
+          <t>A concordância com o pronome relativo “quem” pode ser feita com o seu referente ou o verbo pode ficar na terceira pessoa do singular. Neste caso, o verbo “impor” poderia ser flexionado somente na terceira pessoa do singular, respeitando ou o pronome relativo ou o referente, “realidade”, que está na terceira pessoa do singular.</t>
+        </is>
+      </c>
+      <c r="I990" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J990" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K990" t="inlineStr">
+        <is>
+          <t>ph10_por_09.png</t>
+        </is>
+      </c>
+      <c r="L990" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>Leia o trecho da música "Vilarejo" de Marisa Monte e responda à questão:
+Há um vilarejo ali
+Onde areja um vento bom
+Na varanda, quem descansa
+Vê o horizonte deitar no chão
+[...]
+Disponível em: https://www.vagalume.com.br/marisa-monte/vilarejo.html. Acesso em 14 jan. 2025.
+Sobre o uso do pronome relativo "onde" no trecho acima,</t>
+        </is>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>menciona a palavra "vento" e indica o local onde o vento areja.</t>
+        </is>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>nomeia a palavra "varanda" e indica o local onde alguém descansa.</t>
+        </is>
+      </c>
+      <c r="D991" t="inlineStr">
+        <is>
+          <t>referencia a palavra "vilarejo" e indica o local onde areja um vento bom.</t>
+        </is>
+      </c>
+      <c r="E991" t="inlineStr">
+        <is>
+          <t>alude à palavra "horizonte" e indica o local onde o horizonte deita no chão.</t>
+        </is>
+      </c>
+      <c r="F991" t="inlineStr"/>
+      <c r="G991" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H991" t="inlineStr">
+        <is>
+          <t>O pronome relativo "onde" está sendo utilizado para substituir o substantivo "vilarejo" e é adequado para indicar um lugar. No trecho da música, "onde" está introduzindo uma oração relativa que fornece uma informação adicional sobre o vilarejo, especificando que é o local onde areja um vento bom.</t>
+        </is>
+      </c>
+      <c r="I991" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J991" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K991" t="inlineStr"/>
+      <c r="L991" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>Ana e Bruno estão construindo triângulos utilizando palitos de fósforo. Ana escolheu três palitos com medidas 4 cm, 5 cm e 9 cm, enquanto Bruno escolheu palitos com medidas 3 cm, 5 cm e 8 cm.
+Após a construção, qual dos dois amigos conseguiu formar um triângulo?</t>
+        </is>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>Apenas Ana.</t>
+        </is>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>Apenas Bruno.</t>
+        </is>
+      </c>
+      <c r="D992" t="inlineStr">
+        <is>
+          <t>Nenhum dos dois</t>
+        </is>
+      </c>
+      <c r="E992" t="inlineStr">
+        <is>
+          <t>Ambos, Ana e Bruno.</t>
+        </is>
+      </c>
+      <c r="F992" t="inlineStr"/>
+      <c r="G992" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H992" t="inlineStr">
+        <is>
+          <t>Para que três segmentos de reta formem um triângulo, a medida de cada lado deve ser menor que a soma das medidas dos outros dois lados.
+Triângulo de Ana:
+4 cm + 5 cm = 9 cm
+9 cm é igual à soma dos outros dois lados. Portanto, Ana não consegue formar um triângulo.
+Triângulo de Bruno:
+3 cm + 5 cm = 8 cm
+8 cm é igual à soma dos outros dois lados. Portanto, Bruno não consegue formar um triângulo.</t>
+        </is>
+      </c>
+      <c r="I992" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J992" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K992" t="inlineStr"/>
+      <c r="L992" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>Um engenheiro civil está projetando uma ponte que precisa ser extremamente estável e resistente a deformações. Ele está considerando diferentes formas geométricas para a estrutura da ponte e sabe que a rigidez é um fator crucial. Ele está avaliando o uso de triângulos na construção da estrutura da ponte.
+Por que o engenheiro deve preferir o uso de triângulos na construção da estrutura da ponte para garantir a rigidez e a estabilidade?</t>
+        </is>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>Porque os triângulos têm lados iguais, o que garante a rigidez.</t>
+        </is>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>Porque os triângulos têm ângulos iguais, o que garante a rigidez.</t>
+        </is>
+      </c>
+      <c r="D993" t="inlineStr">
+        <is>
+          <t>Porque os triângulos têm todos os lados diferentes, o que garante a rigidez.</t>
+        </is>
+      </c>
+      <c r="E993" t="inlineStr">
+        <is>
+          <t>Porque os triângulos são figuras geométricas rígidas, o que garante a estabilidade.</t>
+        </is>
+      </c>
+      <c r="F993" t="inlineStr"/>
+      <c r="G993" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H993" t="inlineStr">
+        <is>
+          <t>Os triângulos são figuras geométricas rígidas, o que significa que, uma vez construídos, eles não mudam de forma, mesmo quando submetidos a forças externas. Isso ocorre porque a soma dos ângulos internos de um triângulo é sempre 180°, e a relação entre os lados e os ângulos é fixa. Por isso, o engenheiro deve preferir o uso de triângulos na construção da estrutura da ponte para garantir a rigidez e a estabilidade.</t>
+        </is>
+      </c>
+      <c r="I993" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J993" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K993" t="inlineStr"/>
+      <c r="L993" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>Um professor de matemática pediu aos alunos que descrevessem um algoritmo para a construção de um triângulo qualquer, conhecidas as medidas dos três lados: 6 cm, 8 cm e 10 cm.
+Qual é a sequência correta de passos para construir um triângulo com lados de 6 cm, 8 cm e 10 cm?</t>
+        </is>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>Desenhe um segmento de 6 cm, depois desenhe um segmento de 10 cm a partir de uma extremidade do primeiro segmento, e finalmente desenhe um segmento de 8 cm a partir da extremidade do segundo segmento.</t>
+        </is>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>Desenhe um segmento de 6 cm, depois desenhe um segmento de 8 cm a partir de uma extremidade do primeiro segmento, e finalmente desenhe um segmento de 10 cm a partir da outra extremidade do primeiro segmento.</t>
+        </is>
+      </c>
+      <c r="D994" t="inlineStr">
+        <is>
+          <t>Desenhe um segmento de 6 cm, depois desenhe um segmento de 8 cm a partir de uma extremidade do primeiro segmento, e finalmente desenhe um segmento de 10 cm a partir da extremidade do segundo segmento, encontrando a outra extremidade do primeiro segmento.</t>
+        </is>
+      </c>
+      <c r="E994" t="inlineStr">
+        <is>
+          <t>Desenhe um segmento de 6 cm, depois, com um compasso, trace um arco de 8 cm a partir de uma extremidade do segmento de 6 cm, e um arco de 10 cm a partir da outra extremidade do segmento de 6 cm. O ponto de interseção dos arcos será o terceiro vértice do triângulo.</t>
+        </is>
+      </c>
+      <c r="F994" t="inlineStr"/>
+      <c r="G994" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H994" t="inlineStr">
+        <is>
+          <t>Para construir um triângulo com lados de 6 cm, 8 cm e 10 cm, o algoritmo correto é:
+Desenhe um segmento de 6 cm.
+Com um compasso, abra uma medida de 8 cm e trace um arco a partir de uma extremidade do segmento de 6 cm.
+Com o compasso, abra uma medida de 10 cm e trace um arco a partir da outra extremidade do segmento de 6 cm.
+O ponto de interseção dos dois arcos será o terceiro vértice do triângulo.
+Conecte esse ponto de interseção às extremidades do segmento de 6 cm para formar o triângulo.</t>
+        </is>
+      </c>
+      <c r="I994" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J994" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K994" t="inlineStr"/>
+      <c r="L994" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>Em uma aula de geometria, o professor pediu aos alunos que calculassem a medida de um dos ângulos internos de um triângulo, sabendo que os outros dois ângulos medem 50° e 70°.
+Qual é a medida do terceiro ângulo interno desse triângulo?</t>
+        </is>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>50º</t>
+        </is>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>60º</t>
+        </is>
+      </c>
+      <c r="D995" t="inlineStr">
+        <is>
+          <t>70º</t>
+        </is>
+      </c>
+      <c r="E995" t="inlineStr">
+        <is>
+          <t>80º</t>
+        </is>
+      </c>
+      <c r="F995" t="inlineStr"/>
+      <c r="G995" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H995" t="inlineStr">
+        <is>
+          <t>A soma dos ângulos internos de um triângulo é sempre 180°. Sabendo que dois dos ângulos medem 50° e 70°, podemos encontrar a medida do terceiro ângulo subtraindo a soma dos dois ângulos conhecidos de 180°:</t>
+        </is>
+      </c>
+      <c r="I995" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J995" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K995" t="inlineStr"/>
+      <c r="L995" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>Em um triângulo , o ângulo externo  é formado pela extensão do lado AB. Sabe-se que os ângulos internos  medem 45° e 55°, respectivamente.
+Qual é a medida do ângulo externo ?</t>
+        </is>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>90º</t>
+        </is>
+      </c>
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>100º</t>
+        </is>
+      </c>
+      <c r="D996" t="inlineStr">
+        <is>
+          <t>110º</t>
+        </is>
+      </c>
+      <c r="E996" t="inlineStr">
+        <is>
+          <t>120º</t>
+        </is>
+      </c>
+      <c r="F996" t="inlineStr"/>
+      <c r="G996" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H996" t="inlineStr">
+        <is>
+          <t>A relação entre um ângulo externo e os dois ângulos internos não adjacentes de um triângulo é que o ângulo externo é igual à soma dos dois ângulos internos não adjacentes. Portanto, a medida do ângulo externo  é:</t>
+        </is>
+      </c>
+      <c r="I996" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J996" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K996" t="inlineStr">
+        <is>
+          <t>ph10_mat_05.png</t>
+        </is>
+      </c>
+      <c r="L996" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>Observe o triângulo abaixo:
+A relação que existe entre a medida dos lados deste triângulo é</t>
+        </is>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>[img:ph10_mat_06_a.png]</t>
+        </is>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>[img:ph10_mat_06_b.png]</t>
+        </is>
+      </c>
+      <c r="D997" t="inlineStr">
+        <is>
+          <t>[img:ph10_mat_06_c.png]</t>
+        </is>
+      </c>
+      <c r="E997" t="inlineStr">
+        <is>
+          <t>[img:ph10_mat_06_d.png]</t>
+        </is>
+      </c>
+      <c r="F997" t="inlineStr"/>
+      <c r="G997" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H997" t="inlineStr">
+        <is>
+          <t>Em um triângulo, o maior dos lados é oposto ao maior dos ângulos, assim como o menor lado é oposto ao menor ângulo.
+Desta forma, como  então .</t>
+        </is>
+      </c>
+      <c r="I997" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J997" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K997" t="inlineStr">
+        <is>
+          <t>ph10_mat_06.png</t>
+        </is>
+      </c>
+      <c r="L997" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>Na figura abaixo estão marcados 4 ângulos, de forma que a soma da medida do ângulo reto com a medida do ângulo  é 130°..
+Qual é a medida do ângulo ?</t>
+        </is>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>40°</t>
+        </is>
+      </c>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>45°</t>
+        </is>
+      </c>
+      <c r="D998" t="inlineStr">
+        <is>
+          <t>55°</t>
+        </is>
+      </c>
+      <c r="E998" t="inlineStr">
+        <is>
+          <t>65°</t>
+        </is>
+      </c>
+      <c r="F998" t="inlineStr"/>
+      <c r="G998" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H998" t="inlineStr">
+        <is>
+          <t>O ângulo  é externo ao triângulo que contém os ângulos  e 25°, logo ele é dado pela medida desses dois ângulos.
+Como a soma da medida do ângulo reto com a medida do ângulo  é 130° e de 90° para 130° faltam 40°, logo a medida de  = 40° e a medida de  = 40° + 25° ⟹  = 65°.</t>
+        </is>
+      </c>
+      <c r="I998" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J998" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K998" t="inlineStr">
+        <is>
+          <t>ph10_mat_07.png</t>
+        </is>
+      </c>
+      <c r="L998" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>Observe a figura abaixo:
+Qual é a medida de ?</t>
+        </is>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>20°</t>
+        </is>
+      </c>
+      <c r="C999" t="inlineStr">
+        <is>
+          <t>30°</t>
+        </is>
+      </c>
+      <c r="D999" t="inlineStr">
+        <is>
+          <t>40°</t>
+        </is>
+      </c>
+      <c r="E999" t="inlineStr">
+        <is>
+          <t>50°</t>
+        </is>
+      </c>
+      <c r="F999" t="inlineStr"/>
+      <c r="G999" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H999" t="inlineStr">
+        <is>
+          <t>Para descobrir o valor de , basta subtrair de 180° os ângulos internos que sabemos o valor: 180° - 115° - 25° = 40°.</t>
+        </is>
+      </c>
+      <c r="I999" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J999" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K999" t="inlineStr">
+        <is>
+          <t>ph10_mat_08.png</t>
+        </is>
+      </c>
+      <c r="L999" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>Observe a figura desenhada abaixo, formada por um quadrado e 4 triângulos equiláteros de lados com a mesma medida, além de dois segmentos: FC e FD.
+Qual a medida do ângulo ?</t>
+        </is>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>15°</t>
+        </is>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>30°</t>
+        </is>
+      </c>
+      <c r="D1000" t="inlineStr">
+        <is>
+          <t>40°</t>
+        </is>
+      </c>
+      <c r="E1000" t="inlineStr">
+        <is>
+          <t>45°</t>
+        </is>
+      </c>
+      <c r="F1000" t="inlineStr"/>
+      <c r="G1000" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H1000" t="inlineStr">
+        <is>
+          <t>O triângulo ADF é isósceles, pois o lado do quadrado e o lado do triângulo equilátero têm a mesma medida.
+Logo, o ângulo A do triângulo ADF será de 60° + 90° = 150°. O que falta para chegar a 180° será dividido em dois ângulos congruentes:</t>
+        </is>
+      </c>
+      <c r="I1000" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J1000" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K1000" t="inlineStr">
+        <is>
+          <t>ph10_mat_09.png</t>
+        </is>
+      </c>
+      <c r="L1000" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>Observe a figura desenhada abaixo, formada por um quadrado e 4 triângulos equiláteros de lados com a mesma medida, além de dois segmentos: FC e FD.
+ ​
+Qual a medida do ângulo ?</t>
+        </is>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>45°</t>
+        </is>
+      </c>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>60°</t>
+        </is>
+      </c>
+      <c r="D1001" t="inlineStr">
+        <is>
+          <t>75°</t>
+        </is>
+      </c>
+      <c r="E1001" t="inlineStr">
+        <is>
+          <t>80°</t>
+        </is>
+      </c>
+      <c r="F1001" t="inlineStr"/>
+      <c r="G1001" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H1001" t="inlineStr">
+        <is>
+          <t>Como o triângulo ADF é isósceles, e o ângulo DAF mede , então o ângulo D do triângulo ADF será de .
+É possível concluir que:
+A soma de (beta) com a medida do ângulo ADF é 90°, de 15° para 90° faltam 75°. Logo, β = 75°.</t>
+        </is>
+      </c>
+      <c r="I1001" t="inlineStr">
+        <is>
+          <t>PH10</t>
+        </is>
+      </c>
+      <c r="J1001" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="K1001" t="inlineStr">
+        <is>
+          <t>ph10_mat_10.png</t>
+        </is>
+      </c>
+      <c r="L1001" t="inlineStr">
+        <is>
+          <t>7ano</t>
         </is>
       </c>
     </row>

--- a/questoes.xlsx
+++ b/questoes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1001"/>
+  <dimension ref="A1:L951"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51355,3167 +51355,116 @@
     <row r="902">
       <c r="A902" t="inlineStr">
         <is>
-          <t>A etiqueta de eficiência energética do INMETRO classifica os eletrodomésticos em diferentes categorias de acordo com sua eficiência. Suponha que um refrigerador de classe A consuma 30% menos energia do que um de classe B.
-Se um refrigerador de classe B consome 500 kWh por ano, quanto consome um refrigerador de classe A?</t>
-        </is>
-      </c>
-      <c r="B902" t="inlineStr">
-        <is>
-          <t>350 kWh.</t>
-        </is>
-      </c>
-      <c r="C902" t="inlineStr">
-        <is>
-          <t>400 kWh.</t>
-        </is>
-      </c>
-      <c r="D902" t="inlineStr">
-        <is>
-          <t>450 kWh.</t>
-        </is>
-      </c>
-      <c r="E902" t="inlineStr">
-        <is>
-          <t>500 kWh.</t>
-        </is>
-      </c>
-      <c r="F902" t="inlineStr">
-        <is>
-          <t>550 kWh.</t>
-        </is>
-      </c>
-      <c r="G902" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H902" t="inlineStr">
-        <is>
-          <t>De acordo com o cálculo, o refrigerador de classe A consome 350 kWh.
-Cálculo de 30% do consumo do refrigerador de classe B:
-Subtrair esse valor do consumo do refrigerador de classe B para encontrar o consumo do refrigerador de classe A:</t>
-        </is>
-      </c>
-      <c r="I902" t="inlineStr">
-        <is>
-          <t>PH10</t>
-        </is>
-      </c>
-      <c r="J902" t="inlineStr">
-        <is>
-          <t>Ciências</t>
-        </is>
-      </c>
-      <c r="L902" t="inlineStr">
-        <is>
-          <t>8ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="903">
-      <c r="A903" t="inlineStr">
-        <is>
-          <t>Um aparelho elétrico tem uma potência nominal de 1500 W e é utilizado por 2 horas.
-Qual é o consumo de energia elétrica desse aparelho?</t>
-        </is>
-      </c>
-      <c r="B903" t="inlineStr">
-        <is>
-          <t>1,5 kWh.</t>
-        </is>
-      </c>
-      <c r="C903" t="inlineStr">
-        <is>
-          <t>2 kWh.</t>
-        </is>
-      </c>
-      <c r="D903" t="inlineStr">
-        <is>
-          <t>2,5 kWh.</t>
-        </is>
-      </c>
-      <c r="E903" t="inlineStr">
-        <is>
-          <t>3 kWh.</t>
-        </is>
-      </c>
-      <c r="F903" t="inlineStr">
-        <is>
-          <t>3,5 kWh.</t>
-        </is>
-      </c>
-      <c r="G903" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="H903" t="inlineStr">
-        <is>
-          <t>Para resolver o problema de consumo de energia elétrica, precisamos usar a fórmula:
-E é o consumo de energia em quilowatt-hora (kWh),
-P é a potência em quilowatts (kW),
-t é o tempo em horas (h).
-Converter a potência de Watts para Quilowatts:
-Calcular o consumo de energia:</t>
-        </is>
-      </c>
-      <c r="I903" t="inlineStr">
-        <is>
-          <t>PH10</t>
-        </is>
-      </c>
-      <c r="J903" t="inlineStr">
-        <is>
-          <t>Ciências</t>
-        </is>
-      </c>
-      <c r="L903" t="inlineStr">
-        <is>
-          <t>8ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="904">
-      <c r="A904" t="inlineStr">
-        <is>
-          <t>Um eletrodoméstico está conectado a uma tomada cuja a tensão (U) é de 220V em um circuito que a corrente elétrica que flui por esse aparelho é de 5A.
-Qual é a potência (P) do circuito?</t>
-        </is>
-      </c>
-      <c r="B904" t="inlineStr">
-        <is>
-          <t>550 w.</t>
-        </is>
-      </c>
-      <c r="C904" t="inlineStr">
-        <is>
-          <t>1100 W.</t>
-        </is>
-      </c>
-      <c r="D904" t="inlineStr">
-        <is>
-          <t>1320 W.</t>
-        </is>
-      </c>
-      <c r="E904" t="inlineStr">
-        <is>
-          <t>1400 W.</t>
-        </is>
-      </c>
-      <c r="F904" t="inlineStr">
-        <is>
-          <t>2200 W.</t>
-        </is>
-      </c>
-      <c r="G904" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H904" t="inlineStr">
-        <is>
-          <t>Para resolver essa questão, vamos utilizar a fórmula da potência elétrica:
-Onde:
-P é a potência em watts (W)
-U é a tensão em volts (V) = 220 V
-i é a corrente em amperes (A) = 5 A</t>
-        </is>
-      </c>
-      <c r="I904" t="inlineStr">
-        <is>
-          <t>PH10</t>
-        </is>
-      </c>
-      <c r="J904" t="inlineStr">
-        <is>
-          <t>Ciências</t>
-        </is>
-      </c>
-      <c r="L904" t="inlineStr">
-        <is>
-          <t>8ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="905">
-      <c r="A905" t="inlineStr">
-        <is>
-          <t>Uma residência possui os seguintes eletrodomésticos:
-1 geladeira que consome 30 kWh por mês
-1 máquina de lavar que consome 20 kWh por mês
-1 ar-condicionado que consome 50 kWh por mês
-5 lâmpadas que consomem 5 kWh cada por mês
-Se o valor do kWh é de R$ 0,60, qual será o valor total da conta de energia elétrica dessa residência no final do mês?</t>
-        </is>
-      </c>
-      <c r="B905" t="inlineStr">
-        <is>
-          <t>R$ 60,00.</t>
-        </is>
-      </c>
-      <c r="C905" t="inlineStr">
-        <is>
-          <t>R$ 75,00.</t>
-        </is>
-      </c>
-      <c r="D905" t="inlineStr">
-        <is>
-          <t>R$ 84,00.</t>
-        </is>
-      </c>
-      <c r="E905" t="inlineStr">
-        <is>
-          <t>R$ 96,00.</t>
-        </is>
-      </c>
-      <c r="F905" t="inlineStr">
-        <is>
-          <t>R$ 108,00.</t>
-        </is>
-      </c>
-      <c r="G905" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H905" t="inlineStr">
-        <is>
-          <t>O consumo total das lâmpadas é:
-Todos os consumos: 
-Cálculo do valor total da conta de energia elétrica
-Sabendo que o valor de kWh é de R$ 0,60. Então, o valor total da conta de energia elétrica será:</t>
-        </is>
-      </c>
-      <c r="I905" t="inlineStr">
-        <is>
-          <t>PH10</t>
-        </is>
-      </c>
-      <c r="J905" t="inlineStr">
-        <is>
-          <t>Ciências</t>
-        </is>
-      </c>
-      <c r="L905" t="inlineStr">
-        <is>
-          <t>8ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="906">
-      <c r="A906" t="inlineStr">
-        <is>
-          <t>[...] Lâmpadas LED com eficiência 10 vezes maior que uma lâmpada convencional estão hoje na iluminação doméstica e comercial, em faróis de automóveis, luzes de jardim, lanternas de bolso, etc. A iluminação LED branco pode ser usada não só para diminuir o consumo de energia, mas também para poupar recursos energéticos. Por exemplo, só nos EUA, calcula-se que, até 2020, a iluminação à base de LED branco evitará a construção de 133 usinas. [...]
-Ciência Hoje. Disponível em: &lt; https: acervo="" ch="" ch_321.pdf="" cienciahoje.periodicos.capes.gov.br="" storage=""&gt; Acesso em: 15 jan. 2025.
-Qual é a principal razão para a adoção de lâmpadas LED, conforme discutido no texto?</t>
-        </is>
-      </c>
-      <c r="B906" t="inlineStr">
-        <is>
-          <t>Aumento do consumo de energia.</t>
-        </is>
-      </c>
-      <c r="C906" t="inlineStr">
-        <is>
-          <t>Redução do consumo de energia.</t>
-        </is>
-      </c>
-      <c r="D906" t="inlineStr">
-        <is>
-          <t>Aumento da produção de energia.</t>
-        </is>
-      </c>
-      <c r="E906" t="inlineStr">
-        <is>
-          <t>Redução dos custos de produção de energia.</t>
-        </is>
-      </c>
-      <c r="F906" t="inlineStr">
-        <is>
-          <t>Aumento da eficiência das usinas de energia.</t>
-        </is>
-      </c>
-      <c r="G906" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H906" t="inlineStr">
-        <is>
-          <t>O texto destaca que a iluminação LED branco pode ser usada para diminuir o consumo de energia. Além disso, menciona que a eficiência das lâmpadas LED é 10 vezes maior que a das lâmpadas convencionais, o que contribui para a redução do consumo energético.</t>
-        </is>
-      </c>
-      <c r="I906" t="inlineStr">
-        <is>
-          <t>PH10</t>
-        </is>
-      </c>
-      <c r="J906" t="inlineStr">
-        <is>
-          <t>Ciências</t>
-        </is>
-      </c>
-      <c r="L906" t="inlineStr">
-        <is>
-          <t>8ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="907">
-      <c r="A907" t="inlineStr">
-        <is>
-          <t>Pensando em comprar um ferro elétrico, um advogado depara-se na loja com modelos das marcas A e B, cujos dados são:
-marca A: 220 V – 1 500 W
-marca B: 115 V – 1 300 W
-Se a tensão elétrica fornecida nas tomadas da sua residência é de 110 V, qual a melhor opção para este advogado?</t>
-        </is>
-      </c>
-      <c r="B907" t="inlineStr">
-        <is>
-          <t>O advogado deve escolher o ferro elétrico B, pois o valor da tensão do produto é compatível com a rede elétrica e ele apresentará uma potência menor do que a A, quando ligado ambos em 110V.</t>
-        </is>
-      </c>
-      <c r="C907" t="inlineStr">
-        <is>
-          <t>O advogado não deve comprar nenhum deles, uma vez que ambos queimarão ao serem ligados, pois os valores das tensões dadas pelos fabricantes são maiores que 110 V.</t>
-        </is>
-      </c>
-      <c r="D907" t="inlineStr">
-        <is>
-          <t>O advogado deve escolher o ferro elétrico A, pois o valor da tensão do produto é maior do que a do ferro B, causando maior aquecimento.</t>
-        </is>
-      </c>
-      <c r="E907" t="inlineStr">
-        <is>
-          <t>O advogado deve escolher o ferro elétrico B, pois o valor da tensão do produto é compatível com a rede elétrica da sua casa e ele apresentará uma potência maior do que a A, quando ligado ambos em 110V.</t>
-        </is>
-      </c>
-      <c r="F907" t="inlineStr">
-        <is>
-          <t>O advogado deve escolher o ferro elétrico A, pois o valor da tensão do produto é compatível com a rede elétrica e ele apresentará uma potência maior do que a B, quando ligado ambos em 110V.</t>
-        </is>
-      </c>
-      <c r="G907" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="H907" t="inlineStr">
-        <is>
-          <t>O advogado deve escolher o ferro cujo valor da tensão do produto é compatível com a rede elétrica a que sua residência está ligada. Como essa tensão é de 110 V, ele deve escolher o ferro B, cuja tensão dada é de 115 V. Não faz sentido comprar um ferro construído para funcionar em 220 V e ligá-lo em 110 V. Ele não queima, mas certamente tem um funcionamento inadequado.</t>
-        </is>
-      </c>
-      <c r="I907" t="inlineStr">
-        <is>
-          <t>PH10</t>
-        </is>
-      </c>
-      <c r="J907" t="inlineStr">
-        <is>
-          <t>Ciências</t>
-        </is>
-      </c>
-      <c r="L907" t="inlineStr">
-        <is>
-          <t>8ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="908">
-      <c r="A908" t="inlineStr">
-        <is>
-          <t>Duas geladeiras possuem a mesma potência, porém uma deve ser ligada no 110 V e outra em uma tomada de 220 V.
-Considerando que elas são mantidas ligadas o tempo todo, qual grandeza física elas terão de diferente, além da tensão?</t>
-        </is>
-      </c>
-      <c r="B908" t="inlineStr">
-        <is>
-          <t>Corrente</t>
-        </is>
-      </c>
-      <c r="C908" t="inlineStr">
-        <is>
-          <t>Energia</t>
-        </is>
-      </c>
-      <c r="D908" t="inlineStr">
-        <is>
-          <t>Tempo</t>
-        </is>
-      </c>
-      <c r="E908" t="inlineStr">
-        <is>
-          <t>Força</t>
-        </is>
-      </c>
-      <c r="F908" t="inlineStr">
-        <is>
-          <t>Potência</t>
-        </is>
-      </c>
-      <c r="G908" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H908" t="inlineStr">
-        <is>
-          <t>Temos que a geladeira ligada na tensão 110 V tem potência:
-Para a geladeira ligada na tensão 220 V:
-Logo temos que a corrente da geladeira ligada na tensão 110 V é o dobro da geladeira ligada na tensão de 220 V, e portanto as correntes serão diferentes.</t>
-        </is>
-      </c>
-      <c r="I908" t="inlineStr">
-        <is>
-          <t>PH10</t>
-        </is>
-      </c>
-      <c r="J908" t="inlineStr">
-        <is>
-          <t>Ciências</t>
-        </is>
-      </c>
-      <c r="L908" t="inlineStr">
-        <is>
-          <t>8ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="909">
-      <c r="A909" t="inlineStr">
-        <is>
-          <t>A geração de energia elétrica causa diversos impactos ao meio ambiente, dependendo daforma com que ela é gerada. Assim, reduzir o consumo de energia elétrica é uma forma de reduzir os danos causados à natureza.
-Como a energia elétrica consumida depende da potência dos aparelhos e de seu tempo de uso, marque a alternativa que representa o maior gasto energético:</t>
-        </is>
-      </c>
-      <c r="B909" t="inlineStr">
-        <is>
-          <t>Secador de cabelos – 1500 W, ligado durante 30 minutos.</t>
-        </is>
-      </c>
-      <c r="C909" t="inlineStr">
-        <is>
-          <t>Três lâmpadas incandescentes – 60 W cada, ligadas durante 1 h.</t>
-        </is>
-      </c>
-      <c r="D909" t="inlineStr">
-        <is>
-          <t>Ar-condicionado – 1 kW, ligado durante 3 h.</t>
-        </is>
-      </c>
-      <c r="E909" t="inlineStr">
-        <is>
-          <t>Chuveiro – 5000 W, ligado durante 1.800 segundos.</t>
-        </is>
-      </c>
-      <c r="F909" t="inlineStr">
-        <is>
-          <t>Ferro de passar – 1,3 kW, ligado durante 20 minutos.</t>
-        </is>
-      </c>
-      <c r="G909" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H909" t="inlineStr">
-        <is>
-          <t>Calculando a energia de cada aparelho:
-Secador de cabelos: E = P.t = 1500 W . 1/2 h = 750 Wh
-Três lâmpadas incandescentes: E = P.t = 3.60 W . 1 h = 180 Wh
-Ar-condicionado: E = P.t = 1000 W . 3 h = 3.000 Wh
-Chuveiro: E = P.t = 5000 W . 1/2 h = 2.500 Wh
-Ferro de passar: E = P.t = 1300 W . 1/3 h = 433,33 Wh
-Logo o ar-condicionado é o aparelho que mais consome energia.</t>
-        </is>
-      </c>
-      <c r="I909" t="inlineStr">
-        <is>
-          <t>PH10</t>
-        </is>
-      </c>
-      <c r="J909" t="inlineStr">
-        <is>
-          <t>Ciências</t>
-        </is>
-      </c>
-      <c r="L909" t="inlineStr">
-        <is>
-          <t>8ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="910">
-      <c r="A910" t="inlineStr">
-        <is>
-          <t>Uma casa tem um consumo de energia elétrica de 152 000 Wh e o custo de cada kWh da empresa que fornece energia elétrica para esta casa é de R$ 0,80.
-Qual será a conta de luz desta família?</t>
-        </is>
-      </c>
-      <c r="B910" t="inlineStr">
-        <is>
-          <t>R$ 60,80</t>
-        </is>
-      </c>
-      <c r="C910" t="inlineStr">
-        <is>
-          <t>R$ 121,60</t>
-        </is>
-      </c>
-      <c r="D910" t="inlineStr">
-        <is>
-          <t>R$ 182,40</t>
-        </is>
-      </c>
-      <c r="E910" t="inlineStr">
-        <is>
-          <t>R$ 608,00</t>
-        </is>
-      </c>
-      <c r="F910" t="inlineStr">
-        <is>
-          <t>R$ 1216,00</t>
-        </is>
-      </c>
-      <c r="G910" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H910" t="inlineStr">
-        <is>
-          <t>O consumo de energia nesta residência foi de 152 000 Wh, que é o mesmo que 152 kWh. Se cada 1 kWh o custo é de R$ 0,80, para encontrar o valor cobrado no final do mês para esta família, calcula-se da seguinte forma:
-Por tanto, o valor cobrado será de R$ 121,60.</t>
-        </is>
-      </c>
-      <c r="I910" t="inlineStr">
-        <is>
-          <t>PH10</t>
-        </is>
-      </c>
-      <c r="J910" t="inlineStr">
-        <is>
-          <t>Ciências</t>
-        </is>
-      </c>
-      <c r="L910" t="inlineStr">
-        <is>
-          <t>8ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="911">
-      <c r="A911" t="inlineStr">
-        <is>
-          <t>Com a intenção de diminuir a conta de luz, Marina deu algumas sugestões aos seus pais.
-Qual a sugestão que ajudaria a diminuir o consumo de energia elétrica?</t>
-        </is>
-      </c>
-      <c r="B911" t="inlineStr">
-        <is>
-          <t>Trocar o ventilador por ar condicionado.</t>
-        </is>
-      </c>
-      <c r="C911" t="inlineStr">
-        <is>
-          <t>Trocar o fogão a gás por um fogão elétrico.</t>
-        </is>
-      </c>
-      <c r="D911" t="inlineStr">
-        <is>
-          <t>Trocar as lâmpadas fluorescente para lâmpadas LED.</t>
-        </is>
-      </c>
-      <c r="E911" t="inlineStr">
-        <is>
-          <t>Usar o chuveiro com mais frequência no dia.</t>
-        </is>
-      </c>
-      <c r="F911" t="inlineStr">
-        <is>
-          <t>Usar secador de cabelo para secar as roupas molhadas.</t>
-        </is>
-      </c>
-      <c r="G911" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H911" t="inlineStr">
-        <is>
-          <t>Ao trocar as lâmpadas fluorescentes para lâmpadas LED, o consumo de energia será reduzido, pois a potência das lâmpadas LED são menores.</t>
-        </is>
-      </c>
-      <c r="I911" t="inlineStr">
-        <is>
-          <t>PH10</t>
-        </is>
-      </c>
-      <c r="J911" t="inlineStr">
-        <is>
-          <t>Ciências</t>
-        </is>
-      </c>
-      <c r="L911" t="inlineStr">
-        <is>
-          <t>8ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="912">
-      <c r="A912" t="inlineStr">
-        <is>
-          <t>Leia o texto a seguir. 
-No México, as indústrias maquiladoras, instaladas na fronteira norte na década de 1990 exemplificam algumas das dinâmicas amplamente favorecidas pelo neoliberalismo. Impulsionadas pelos baixos salários no país, elas se concentram nas etapas mais intensivas em trabalho, na montagem – etapa de menor valor agregado – empregando uma maioria de mulheres, não raro migrantes que ficaram no país. Tudo isso em contraposição às atividades da cadeia desenvolvidas nos países mais ricos, de desenvolvimento intelectual do produto e fabricação de componentes mais avançados
-Disponível em: https://diplomatique.org.br/resistencias-mexicanas-entre-massacres-travessias-e-lutas/. Acesso em 17 de dez de 2024.
-Por que as indústrias maquiladoras se instalaram na fronteira norte do México na década de 1990?</t>
-        </is>
-      </c>
-      <c r="B912" t="inlineStr">
-        <is>
-          <t>Devido aos altos salários oferecidos no México.</t>
-        </is>
-      </c>
-      <c r="C912" t="inlineStr">
-        <is>
-          <t>Para se beneficiar dos baixos salários no país</t>
-        </is>
-      </c>
-      <c r="D912" t="inlineStr">
-        <is>
-          <t>Para desenvolver produtos intelectualmente avançados</t>
-        </is>
-      </c>
-      <c r="E912" t="inlineStr">
-        <is>
-          <t>Devido à alta qualificação da mão de obra local</t>
-        </is>
-      </c>
-      <c r="F912" t="inlineStr">
-        <is>
-          <t>Para promover igualdade salarial entre trabalhadores.</t>
-        </is>
-      </c>
-      <c r="G912" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H912" t="inlineStr">
-        <is>
-          <t>As indústrias maquiladoras se instalaram na fronteira norte do México para aproveitar os baixos salários oferecidos no país. Essa estratégia permitiu que as empresas reduzissem seus custos de produção, concentrando-se em etapas de trabalho intensivo, como a montagem, que requerem menos qualificação e oferecem menor valor agregado.</t>
-        </is>
-      </c>
-      <c r="I912" t="inlineStr">
-        <is>
-          <t>PH10</t>
-        </is>
-      </c>
-      <c r="J912" t="inlineStr">
-        <is>
-          <t>Geografia</t>
-        </is>
-      </c>
-      <c r="L912" t="inlineStr">
-        <is>
-          <t>8ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="913">
-      <c r="A913" t="inlineStr">
-        <is>
-          <t>O império asteca floresceu entre c. 1345 e 1521 e dominou a antiga Mesoamérica. Esta nação jovem e belicosa foi muito bem-sucedida em expandir suas fronteiras e conquistar riquezas fabulosas, mas, então, chegaram estranhos visitantes de outro mundo. Liderados por Hernán Cortés, as armas formidáveis dos espanhóis e sua sede por tesouros iriam trazer uma destruição devastadora, além de doenças. Os Conquistadores imediatamente encontraram aliados locais, ansiosos para ajudar a derrubar o brutal regime dos astecas e libertar-se do fardo dos tributos e da necessidade de alimentar o insaciável apetite dos seus senhores por vítimas sacrificiais. Com isso, bastaram três anos para que caísse o maior império que já existira até então nas Américas do Norte e Central.
-Disponível em: https://www.worldhistory.org/trans/pt/2-916/cortes-e-a-queda-do-imperio-asteca/. Acesso em 17 de dez de 2024.
-Qual foi um dos principais fatores que contribuíram para a queda do império asteca?</t>
-        </is>
-      </c>
-      <c r="B913" t="inlineStr">
-        <is>
-          <t>A falta de recursos naturais na região.</t>
-        </is>
-      </c>
-      <c r="C913" t="inlineStr">
-        <is>
-          <t>A resistência dos astecas contra os invasores.</t>
-        </is>
-      </c>
-      <c r="D913" t="inlineStr">
-        <is>
-          <t>A ausência de doenças trazidas pelos europeus.</t>
-        </is>
-      </c>
-      <c r="E913" t="inlineStr">
-        <is>
-          <t>A incapacidade dos espanhóis de encontrar aliados.</t>
-        </is>
-      </c>
-      <c r="F913" t="inlineStr">
-        <is>
-          <t>A superioridade dos armamentos e microrganismos.</t>
-        </is>
-      </c>
-      <c r="G913" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="H913" t="inlineStr">
-        <is>
-          <t>O texto destaca que a superioridade dos armamentos espanhóis e a introdução de doenças (microrganismos) foram fatores cruciais que devastaram a população asteca e contribuíram significativamente para a queda do império.</t>
-        </is>
-      </c>
-      <c r="I913" t="inlineStr">
-        <is>
-          <t>PH10</t>
-        </is>
-      </c>
-      <c r="J913" t="inlineStr">
-        <is>
-          <t>Geografia</t>
-        </is>
-      </c>
-      <c r="L913" t="inlineStr">
-        <is>
-          <t>8ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="914">
-      <c r="A914" t="inlineStr">
-        <is>
-          <t>Observe a imagem. 
-Disponível em: https://upload.wikimedia.org/wikipedia/commons/0/0b/Border_USA_Mexico.jpg. Acesso em 17 de dez de 2024. 
-O muro fronteiriço entre o México e os Estados Unidos é uma estrutura física destinada a controlar a imigração ilegal e o tráfico de mercadorias entre os dois países. Milhares de pessoas tentam cruzar essa fronteira em busca de melhores condições de vida nos Estados Unidos, fugindo da violência, pobreza e falta de oportunidades presentes em seus países de origem. Contudo, as autoridades americanas investem fortemente em medidas para impedir essas travessias. Observando a imagem,  qual dos fatores a seguir é um dos principais motivadores para a migração de pessoas do México para os Estados Unidos?</t>
-        </is>
-      </c>
-      <c r="B914" t="inlineStr">
-        <is>
-          <t>Busca por melhores condições de trabalho e de vida.</t>
-        </is>
-      </c>
-      <c r="C914" t="inlineStr">
-        <is>
-          <t>Interesse em conhecer as paisagens do país vizinho.</t>
-        </is>
-      </c>
-      <c r="D914" t="inlineStr">
-        <is>
-          <t>Tentativa de fugir de regiões rurais para áreas urbanas.</t>
-        </is>
-      </c>
-      <c r="E914" t="inlineStr">
-        <is>
-          <t>Desejo de participar de programas de intercâmbio cultural.</t>
-        </is>
-      </c>
-      <c r="F914" t="inlineStr">
-        <is>
-          <t>Busca por áreas com menor densidade populacional.</t>
-        </is>
-      </c>
-      <c r="G914" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H914" t="inlineStr">
-        <is>
-          <t>A principal motivação para a migração de muitos mexicanos e outros latino-americanos para os Estados Unidos é a busca por melhores condições econômicas, mais oportunidades de emprego e um padrão de vida superior comparado ao de seus países de origem.</t>
-        </is>
-      </c>
-      <c r="I914" t="inlineStr">
-        <is>
-          <t>PH10</t>
-        </is>
-      </c>
-      <c r="J914" t="inlineStr">
-        <is>
-          <t>Geografia</t>
-        </is>
-      </c>
-      <c r="K914" t="inlineStr">
-        <is>
-          <t>8a_ph10_geo_03.png</t>
-        </is>
-      </c>
-      <c r="L914" t="inlineStr">
-        <is>
-          <t>8ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="915">
-      <c r="A915" t="inlineStr">
-        <is>
-          <t>Observe a tabela a seguir.
-Disponível em: https://www.populationpyramid.net/pt/m%C3%A9xico/2021/. Acesso em: 17 dez 2024.
-A pirâmide etária do México em 2021 revela uma população jovem com sinais de envelhecimento em curso. Esse fenômeno é típico de países em desenvolvimento, onde a taxa de natalidade diminui e a expectativa de vida aumenta devido ao acesso à informação, urbanização e serviços de saúde. Com base nestas informações, qual das seguintes afirmações melhor descreve a tendência demográfica do México?</t>
-        </is>
-      </c>
-      <c r="B915" t="inlineStr">
-        <is>
-          <t>População principalmente idosa, com altas taxas de natalidade.</t>
-        </is>
-      </c>
-      <c r="C915" t="inlineStr">
-        <is>
-          <t>Alta taxa de natalidade e baixa expectativa de vida.</t>
-        </is>
-      </c>
-      <c r="D915" t="inlineStr">
-        <is>
-          <t>Rápido crescimento populacional, pequena porção de idosos.</t>
-        </is>
-      </c>
-      <c r="E915" t="inlineStr">
-        <is>
-          <t>População jovem e sinais claros de envelhecimento.</t>
-        </is>
-      </c>
-      <c r="F915" t="inlineStr">
-        <is>
-          <t>Alta mortalidade infantil e baixa expectativa de vida.</t>
-        </is>
-      </c>
-      <c r="G915" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="H915" t="inlineStr">
-        <is>
-          <t>A pirâmide etária mostra uma base alargada (população jovem) e sinais de envelhecimento (proporção crescente de faixas etárias mais altas), alinhando-se com a descrição do fenômeno de transição demográfica.</t>
-        </is>
-      </c>
-      <c r="I915" t="inlineStr">
-        <is>
-          <t>PH10</t>
-        </is>
-      </c>
-      <c r="J915" t="inlineStr">
-        <is>
-          <t>Geografia</t>
-        </is>
-      </c>
-      <c r="K915" t="inlineStr">
-        <is>
-          <t>8a_ph10_geo_04.png</t>
-        </is>
-      </c>
-      <c r="L915" t="inlineStr">
-        <is>
-          <t>8ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="916">
-      <c r="A916" t="inlineStr">
-        <is>
-          <t>O inchaço urbano é o crescimento desordenado das cidades, que ocorre em pequenos centros de determinadas regiões urbanas. A falta de planejamento durante a expansão da cidade faz com que haja uma área que concentra as atividades e os serviços locais, atraindo uma quantidade de pessoas que muitas vezes excede a capacidade do espaço disponível.
-Disponível em: https://www.politize.com.br/inchaco-urbano/. Acesso em 17 de dez de 2024.
-Qual das seguintes consequências é mais provável no contexto das cidades mexicanas que experienciam inchaço urbano?</t>
-        </is>
-      </c>
-      <c r="B916" t="inlineStr">
-        <is>
-          <t>Melhor distribuição de serviços e infraestruturas.</t>
-        </is>
-      </c>
-      <c r="C916" t="inlineStr">
-        <is>
-          <t>Redução da poluição e qualidade do ar melhorada.</t>
-        </is>
-      </c>
-      <c r="D916" t="inlineStr">
-        <is>
-          <t>Aumento da pressão sobre serviços e infraestruturas.</t>
-        </is>
-      </c>
-      <c r="E916" t="inlineStr">
-        <is>
-          <t>Maior equilíbrio e melhor qualidade de vida.</t>
-        </is>
-      </c>
-      <c r="F916" t="inlineStr">
-        <is>
-          <t>Expansão harmoniosa e bem planejada.</t>
-        </is>
-      </c>
-      <c r="G916" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H916" t="inlineStr">
-        <is>
-          <t>O texto indica que o crescimento desordenado leva a uma concentração de atividades e serviços, aumentando a pressão sobre a infraestrutura disponível.</t>
-        </is>
-      </c>
-      <c r="I916" t="inlineStr">
-        <is>
-          <t>PH10</t>
-        </is>
-      </c>
-      <c r="J916" t="inlineStr">
-        <is>
-          <t>Geografia</t>
-        </is>
-      </c>
-      <c r="L916" t="inlineStr">
-        <is>
-          <t>8ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="917">
-      <c r="A917" t="inlineStr">
-        <is>
-          <t>O conceito de aldeia global foi criado na década de 1960 pelo filósofo canadense Marshall Mcluhan, então professor da Escola de Comunicações da Universidade de Toronto.Segundo esse conceito, o avanço nas tecnologias de informação e comunicação encurta as distâncias no mundo e facilita trocas culturais entre os diferentes povos.O autor acreditava que, devido à diminuição das distâncias e barreiras geográficas, o planeta se reduziria a uma organização semelhante a aldeias, onde tudo e todos estariam interconectados.
-Disponível em:&lt;https://www.significados.com.br/aldeia-global/&gt;. Acesso em: 29 jun.2020.
-Na fronteira entre o México e os Estados Unidos ocorrem fatos que desmentem a ideia de aldeia global. Como por exemplo</t>
-        </is>
-      </c>
-      <c r="B917" t="inlineStr">
-        <is>
-          <t>a ausência de vias de circulação modernas entre os dois países.</t>
-        </is>
-      </c>
-      <c r="C917" t="inlineStr">
-        <is>
-          <t>a restrição da entrada de trabalhadores mexicanos nos Estados Unidos.</t>
-        </is>
-      </c>
-      <c r="D917" t="inlineStr">
-        <is>
-          <t>a dificuldade de acesso de norte-americanos ao México.</t>
-        </is>
-      </c>
-      <c r="E917" t="inlineStr">
-        <is>
-          <t>a redução das exportações do norte do México para os Estados Unidos.</t>
-        </is>
-      </c>
-      <c r="F917" t="inlineStr">
-        <is>
-          <t>o embargo econômico dos Estados Unidos à produção agrícola do México.</t>
-        </is>
-      </c>
-      <c r="G917" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H917" t="inlineStr">
-        <is>
-          <t>A fronteira entre México e Estados Unidos é uma das mais vigiadas do planeta. Um polêmico muro foi construído para tentar conter a chegada de imigrantes ilegais, vistos por muitos cidadãos estadunidenses como os culpados por diversos problemas que atingiram a economia norte-americana nos últimos anos, como a elevação do desemprego no país.</t>
-        </is>
-      </c>
-      <c r="I917" t="inlineStr">
-        <is>
-          <t>PH10</t>
-        </is>
-      </c>
-      <c r="J917" t="inlineStr">
-        <is>
-          <t>Geografia</t>
-        </is>
-      </c>
-      <c r="L917" t="inlineStr">
-        <is>
-          <t>8ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="918">
-      <c r="A918" t="inlineStr">
-        <is>
-          <t>O muro que Trump já está construindo inevitavelmente terá que correr paralelo às margens do rio, impedindo a circulação de espécies entre os dois países e piorando a situação de plantas e animais típicos que já estão ameaçados de extinção.
-VAIANO, Bruno Disponível em &lt;https://super.abril.com.br/ciencia/muro-de-trump-pode-levar-animais-e-plantas-do-texas-a-extincao/&gt; Acesso em: 23 maio 2018.
-Com base no trecho acima, assinale a alternativa correta.</t>
-        </is>
-      </c>
-      <c r="B918" t="inlineStr">
-        <is>
-          <t>No mundo atual, as contradições da globalização não geram impactos na natureza.</t>
-        </is>
-      </c>
-      <c r="C918" t="inlineStr">
-        <is>
-          <t>Um dos motivos para construção do muro separando EUA e México é o controle da passagem de animais silvestres.</t>
-        </is>
-      </c>
-      <c r="D918" t="inlineStr">
-        <is>
-          <t>O combate acrítico à imigração de mexicanos prejudica a biodiversidade.</t>
-        </is>
-      </c>
-      <c r="E918" t="inlineStr">
-        <is>
-          <t>A construção do muro entre os EUA e o México não extrapola questões ideológicas.</t>
-        </is>
-      </c>
-      <c r="F918" t="inlineStr">
-        <is>
-          <t>A construção do muro entre os EUA e o México reflete a baixa capacidade dos humanos interagirem com o espaço.</t>
-        </is>
-      </c>
-      <c r="G918" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H918" t="inlineStr">
-        <is>
-          <t>A construção de um muro por parte dos EUA visando deter processos migratórios que partem do México, prejudica a circulação de animais silvestres.</t>
-        </is>
-      </c>
-      <c r="I918" t="inlineStr">
-        <is>
-          <t>PH10</t>
-        </is>
-      </c>
-      <c r="J918" t="inlineStr">
-        <is>
-          <t>Geografia</t>
-        </is>
-      </c>
-      <c r="L918" t="inlineStr">
-        <is>
-          <t>8ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="919">
-      <c r="A919" t="inlineStr">
-        <is>
-          <t>Estes trabalhadores, com autorizações temporárias, ficaram conhecidos como "braceros" (numa referência em espanhol à força braçal necessária para trabalho pesado).
-Disponível em:&lt;https://www.bbc.com/portuguese/reporterbbc/story/2008/10/081017_mexicanossalario.shtml&gt;. Acesso em: 29 jun.2020.
-Os braceros podem ser definidos como:</t>
-        </is>
-      </c>
-      <c r="B919" t="inlineStr">
-        <is>
-          <t>Trabalhadores mexicanos que se mudaram para o complexo turístico na Flórida.</t>
-        </is>
-      </c>
-      <c r="C919" t="inlineStr">
-        <is>
-          <t>Trabalhadores rurais mexicanos que migram anualmente para trabalhar em colheitas.</t>
-        </is>
-      </c>
-      <c r="D919" t="inlineStr">
-        <is>
-          <t>Camponeses mexicanos que fixam-se de maneira definitiva para garantir a produção de subsistência.</t>
-        </is>
-      </c>
-      <c r="E919" t="inlineStr">
-        <is>
-          <t>Trabalhadores que implementam a modernização das "Haciendas" mexicanas.</t>
-        </is>
-      </c>
-      <c r="F919" t="inlineStr">
-        <is>
-          <t>Camponeses que trabalham como monocultura de exportação dos latifúndios mexicanos.​</t>
-        </is>
-      </c>
-      <c r="G919" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H919" t="inlineStr">
-        <is>
-          <t>Os braceros, como são conhecidos os trabalhadores temporários do campo, migram sazonalmente (transumância). Alguns desses trabalhadores rurais são donos de pequenas propriedades no México, no entanto não conseguem sustentar suas famílias somente com sua pequena roça. Em geral as condições de trabalho temporário em áreas rurais são precárias e a remuneração é baixa.</t>
-        </is>
-      </c>
-      <c r="I919" t="inlineStr">
-        <is>
-          <t>PH10</t>
-        </is>
-      </c>
-      <c r="J919" t="inlineStr">
-        <is>
-          <t>Geografia</t>
-        </is>
-      </c>
-      <c r="L919" t="inlineStr">
-        <is>
-          <t>8ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="920">
-      <c r="A920" t="inlineStr">
-        <is>
-          <t>A industrialização mexicana teve, a partir dos anos 1960, incentivos governamentais para a entrada de capital estrangeiro. Há uma grande variedade de empresas transnacionais no México, que empregam milhares de pessoas e são responsáveis por uma parcela significativa da riqueza produzida no país.
-O nome do modelo industrial adotado pelo México ficou conhecido como:</t>
-        </is>
-      </c>
-      <c r="B920" t="inlineStr">
-        <is>
-          <t>Substituição de Importações.</t>
-        </is>
-      </c>
-      <c r="C920" t="inlineStr">
-        <is>
-          <t>Plataformas de Exportações.</t>
-        </is>
-      </c>
-      <c r="D920" t="inlineStr">
-        <is>
-          <t>Substituição de Exportações.</t>
-        </is>
-      </c>
-      <c r="E920" t="inlineStr">
-        <is>
-          <t>Plataformas de importações.</t>
-        </is>
-      </c>
-      <c r="F920" t="inlineStr">
-        <is>
-          <t>Industrialização agrária.</t>
-        </is>
-      </c>
-      <c r="G920" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H920" t="inlineStr">
-        <is>
-          <t>O México está entre os países mais industrializados da região e seguiu o mesmo modelo de substituição de importações dos vizinhos latino-americanos. Esse um processo que leva ao aumento da produção interna de um país e a diminuição das suas importações. Ao longo da história econômica mundial, os processos de substituição de importações foram desencadeados por fatores políticos ou econômicos, e foram resultado de ações planejadas ou imposição das circunstâncias.</t>
-        </is>
-      </c>
-      <c r="I920" t="inlineStr">
-        <is>
-          <t>PH10</t>
-        </is>
-      </c>
-      <c r="J920" t="inlineStr">
-        <is>
-          <t>Geografia</t>
-        </is>
-      </c>
-      <c r="L920" t="inlineStr">
-        <is>
-          <t>8ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="921">
-      <c r="A921" t="inlineStr">
-        <is>
-          <t>TEXTO I
-A televisão brasileira mudou muito ao longo dos anos, com séries e produções novas ano após ano. Mas um seriado mexicano, de baixo orçamento e produzido nos anos 70 é presença obrigatória na programação até os dias de hoje: Chaves! [...]
-Disponível em:&lt; https://www.aficionados.com.br/tudo-sobre-chaves/&gt;. Acesso em:06 jul.2020.
-TEXTO II
-Frida Kahlo foi uma das mais importantes artistas da história do México, marcada pela tradição vanguardista do modernismo surrealista. Nascida em 1907, na Cidade do México, era filha de uma família alemã com indígenas catequizados [...]
-65 ANOS SEM FRIDA KAHLO: DOR E ORGULHO
-Neste dia, em 1954, morria aquela que revolucionou a história da arte do México.
-ANDRÉ NOGUEIRA PUBLICADO EM 13/07/2019, ÀS 00H00
-Disponível em:&lt; https://aventurasnahistoria.uol.com.br/noticias/reportagem/a-vida-e-a-morte-de-frida-kahlo.phtml&gt;. Acesso em: 06 jul.2020.
-As notícias retratam</t>
-        </is>
-      </c>
-      <c r="B921" t="inlineStr">
-        <is>
-          <t>a cultura mexicana restrita.</t>
-        </is>
-      </c>
-      <c r="C921" t="inlineStr">
-        <is>
-          <t>o elitismo das produções mexicanas.</t>
-        </is>
-      </c>
-      <c r="D921" t="inlineStr">
-        <is>
-          <t>a atual estagnação cultural mexicana.</t>
-        </is>
-      </c>
-      <c r="E921" t="inlineStr">
-        <is>
-          <t>a eliminação do componente cultural indígena.</t>
-        </is>
-      </c>
-      <c r="F921" t="inlineStr">
-        <is>
-          <t>a diversidade e impacto da produção cultural mexicana.</t>
-        </is>
-      </c>
-      <c r="G921" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="H921" t="inlineStr">
-        <is>
-          <t>Chaves e Frida Kahlo são famosas representações artísticas do México, evidenciando a popularidade e impacto social da cultura mexicana no Brasil e no mundo.</t>
-        </is>
-      </c>
-      <c r="I921" t="inlineStr">
-        <is>
-          <t>PH10</t>
-        </is>
-      </c>
-      <c r="J921" t="inlineStr">
-        <is>
-          <t>Geografia</t>
-        </is>
-      </c>
-      <c r="L921" t="inlineStr">
-        <is>
-          <t>8ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="922">
-      <c r="A922" t="inlineStr">
-        <is>
-          <t>[...] "Se você vai se tornar independente da Espanha, por que continuaria a se submeter aos mandos e desmandos de Buenos Aires, por exemplo? A divisão por vice-reinos era burocrática. E as fronteiras atuais dos países da América Latina demoraram para ser consolidadas. Não era possível prevê-las antes de 1810, pois resultaram de disputas internas após a independência", explica.
-Mas é importante lembrar que também houve na América Espanhola planos de unificação, que não avançaram.
-Por que o Brasil continuou um só enquanto a América espanhola se dividiu em vários países? BBC News Brasil. Disponível em: https://www.bbc.com/portuguese/articles/c3gjpmvkv5eo. Acesso em: 17 dez. 2024.
-Qual a causa da fragmentação política da América Latina pós-independência retratada no texto?</t>
-        </is>
-      </c>
-      <c r="B922" t="inlineStr">
-        <is>
-          <t>A ausência de recursos naturais.</t>
-        </is>
-      </c>
-      <c r="C922" t="inlineStr">
-        <is>
-          <t>A influência das potências asiáticas.</t>
-        </is>
-      </c>
-      <c r="D922" t="inlineStr">
-        <is>
-          <t>A falta de influência das elites locais.</t>
-        </is>
-      </c>
-      <c r="E922" t="inlineStr">
-        <is>
-          <t>A homogeneidade cultural e linguística.</t>
-        </is>
-      </c>
-      <c r="F922" t="inlineStr">
-        <is>
-          <t>As disputas internas entre as elites criollas.</t>
-        </is>
-      </c>
-      <c r="G922" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="H922" t="inlineStr">
-        <is>
-          <t>A fragmentação política foi causada pelas disputas internas entre as elites criollas pelo poder, que resultaram em uma série de conflitos e divisões territoriais. As elites criollas locais queriam garantir seu domínio sem se submeter a um poder superior, o que levou à formação de múltiplos estados-nacionais.</t>
-        </is>
-      </c>
-      <c r="I922" t="inlineStr">
-        <is>
-          <t>PH10</t>
-        </is>
-      </c>
-      <c r="J922" t="inlineStr">
-        <is>
-          <t>História</t>
-        </is>
-      </c>
-      <c r="L922" t="inlineStr">
-        <is>
-          <t>8ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="923">
-      <c r="A923" t="inlineStr">
-        <is>
-          <t>Mesmo países que apresentavam taxas de crescimento econômico bastante elevadas, tais como os latino-americanos, cuja independência política tinha sido alcançada no princípio do século XIX, estavam limitados pela profundidade da sua dependência econômica e política da economia internacional. Seu crescimento econômico parecia destinado a acumular miséria, analfabetismo e uma distribuição de renda desastrosa.
-SANTOS, Theotônio dos. A TEORIA DA DEPENDÊNCIA:UM BALANÇO HISTÓRICO E TEÓRICO. Disponível em: https://edisciplinas.usp.br/pluginfile.php/283339/mod_resource/content/1/ateoriadadependencia.pdf. Acesso em: 17 dez. 2024.
-Qual foi a consequência das políticas agroexportadoras na América Latina no século XIX?</t>
-        </is>
-      </c>
-      <c r="B923" t="inlineStr">
-        <is>
-          <t>Redução da desigualdade social.</t>
-        </is>
-      </c>
-      <c r="C923" t="inlineStr">
-        <is>
-          <t>Fortalecimento das indústrias locais.</t>
-        </is>
-      </c>
-      <c r="D923" t="inlineStr">
-        <is>
-          <t>Independência econômica total das ex-colônias.</t>
-        </is>
-      </c>
-      <c r="E923" t="inlineStr">
-        <is>
-          <t>Dependência das potências capitalistas europeias.</t>
-        </is>
-      </c>
-      <c r="F923" t="inlineStr">
-        <is>
-          <t>Unidade política entre os países latino-americanos.</t>
-        </is>
-      </c>
-      <c r="G923" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="H923" t="inlineStr">
-        <is>
-          <t>A política agroexportadora manteve a dependência das ex-colônias às potências capitalistas europeias, uma vez que as economias locais foram estruturadas para fornecer matérias-primas e produtos agrícolas para os mercados europeus. Isso impediu a diversificação econômica e a industrialização independente.</t>
-        </is>
-      </c>
-      <c r="I923" t="inlineStr">
-        <is>
-          <t>PH10</t>
-        </is>
-      </c>
-      <c r="J923" t="inlineStr">
-        <is>
-          <t>História</t>
-        </is>
-      </c>
-      <c r="L923" t="inlineStr">
-        <is>
-          <t>8ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="924">
-      <c r="A924" t="inlineStr">
-        <is>
-          <t>Tratado França-Haiti, 1825. Disponível em: https://commons.wikimedia.org/wiki/File:Trait%C3%A9_France_Ha%C3%AFti_1825.jpg. Acesso em: 17 dez. 2024.
-A imagem retrata um episódio desvantajoso para o Haiti no início do século XIX. Quais foram os principais desafios enfrentados pelo Haiti após sua independência?</t>
-        </is>
-      </c>
-      <c r="B924" t="inlineStr">
-        <is>
-          <t>Terras pouco produtivas e greves urbanas.</t>
-        </is>
-      </c>
-      <c r="C924" t="inlineStr">
-        <is>
-          <t>Desastres naturais e endividamento externo.</t>
-        </is>
-      </c>
-      <c r="D924" t="inlineStr">
-        <is>
-          <t>Isolamento diplomático e a indenização à França.</t>
-        </is>
-      </c>
-      <c r="E924" t="inlineStr">
-        <is>
-          <t>Ocupação militar pelos Estados Unidos e doenças.</t>
-        </is>
-      </c>
-      <c r="F924" t="inlineStr">
-        <is>
-          <t>Revoltas contra a escravidão e fragmentação política.</t>
-        </is>
-      </c>
-      <c r="G924" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H924" t="inlineStr">
-        <is>
-          <t>O Haiti enfrentou sérios problemas de isolamento diplomático, pois muitos países, especialmente as potências coloniais, estavam relutantes em reconhecer a independência de uma nação fundada por ex-escravos. Além disso, teve que pagar uma indenização massiva à França para ser reconhecido como uma nação independente, o que causou um endividamento significativo.</t>
-        </is>
-      </c>
-      <c r="I924" t="inlineStr">
-        <is>
-          <t>PH10</t>
-        </is>
-      </c>
-      <c r="J924" t="inlineStr">
-        <is>
-          <t>História</t>
-        </is>
-      </c>
-      <c r="K924" t="inlineStr">
-        <is>
-          <t>8a_ph10_his_03.jpg</t>
-        </is>
-      </c>
-      <c r="L924" t="inlineStr">
-        <is>
-          <t>8ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="925">
-      <c r="A925" t="inlineStr">
-        <is>
-          <t>Disponível em: https://commons.wikimedia.org/wiki/File:Batalla_de_Cerro_Gordo.jpg. Acesso em: 17 dez. 2024.
-Após a independência do México, o país teve que lidar com um conflito retratado na imagem acima, que teve como consequência a</t>
-        </is>
-      </c>
-      <c r="B925" t="inlineStr">
-        <is>
-          <t>perda de metade das terras do país para os Estados Unidos.</t>
-        </is>
-      </c>
-      <c r="C925" t="inlineStr">
-        <is>
-          <t>união política entre México e os estados do sul dos EUA.</t>
-        </is>
-      </c>
-      <c r="D925" t="inlineStr">
-        <is>
-          <t>formação de uma república autônoma no norte do país.</t>
-        </is>
-      </c>
-      <c r="E925" t="inlineStr">
-        <is>
-          <t>abolição da escravidão em todo o território mexicano.</t>
-        </is>
-      </c>
-      <c r="F925" t="inlineStr">
-        <is>
-          <t>expansão mexicana por toda a América do Norte.</t>
-        </is>
-      </c>
-      <c r="G925" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H925" t="inlineStr">
-        <is>
-          <t>Após a Guerra Mexicano-Americana, concluída em 1848 com o Tratado de Guadalupe Hidalgo, o México perdeu aproximadamente metade do seu território para os Estados Unidos, incluindo os atuais estados da Califórnia, Nevada, Utah, Arizona, Novo México, Texas, e partes do Colorado, Wyoming, Kansas e Oklahoma.</t>
-        </is>
-      </c>
-      <c r="I925" t="inlineStr">
-        <is>
-          <t>PH10</t>
-        </is>
-      </c>
-      <c r="J925" t="inlineStr">
-        <is>
-          <t>História</t>
-        </is>
-      </c>
-      <c r="K925" t="inlineStr">
-        <is>
-          <t>8a_ph10_his_04.jpg</t>
-        </is>
-      </c>
-      <c r="L925" t="inlineStr">
-        <is>
-          <t>8ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="926">
-      <c r="A926" t="inlineStr">
-        <is>
-          <t>O historiador Felipe Pigna concorda que os motivos que terminaram com os negros na Argentina devem ser procurados na utilização da população masculina como “bucha de canhão” nas guerras da Independência, as civis que vieram a seguir e, por último, a ofensiva contra o Paraguai (1865-1871), além das epidemias de cólera (1861) e de febre amarela (1871) que provocaram grande mortandade entre os mais pobres, entre eles os afro-argentinos. “Mas, além disso, a natalidade era muito baixa, inclusive em comparação com outras sociedades latino-americanas. Os amos evitavam a todo custo o casamento de um escravo, assim como a gravidez de uma escrava, com o argumento de que isso a impedia de prestar todos os serviços para os quais foi comprada, além do risco de morrer em um problema no parto”, afirma.
-Disponível em: https://brasil.elpais.com/brasil/2017/01/07/internacional/1483795840_886159.html. Acesso em: 17 dez. 2024.
-Quais foram as políticas adotadas pela elite argentina para reduzir a população negra no século XIX?</t>
-        </is>
-      </c>
-      <c r="B926" t="inlineStr">
-        <is>
-          <t>Expulsão do país como punição pelo apoio à Espanha.</t>
-        </is>
-      </c>
-      <c r="C926" t="inlineStr">
-        <is>
-          <t>Promoção da imigração europeia para trabalhar nas fábricas.</t>
-        </is>
-      </c>
-      <c r="D926" t="inlineStr">
-        <is>
-          <t>Manutenção de boas relações entre as raças visando a miscigenação.</t>
-        </is>
-      </c>
-      <c r="E926" t="inlineStr">
-        <is>
-          <t>Envolvimento dos afro-argentinos como linha de frente em guerras.</t>
-        </is>
-      </c>
-      <c r="F926" t="inlineStr">
-        <is>
-          <t>Concessão de território separado da Argentina exclusivo para negros.</t>
-        </is>
-      </c>
-      <c r="G926" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="H926" t="inlineStr">
-        <is>
-          <t>O texto aponta para o uso da população afro-argentina como “bucha de canhão” nas guerras da Independência, nas guerras civis e na ofensiva contra o Paraguai, contribuindo significantemente para a redução da população negra na Argentina do século XIX.</t>
-        </is>
-      </c>
-      <c r="I926" t="inlineStr">
-        <is>
-          <t>PH10</t>
-        </is>
-      </c>
-      <c r="J926" t="inlineStr">
-        <is>
-          <t>História</t>
-        </is>
-      </c>
-      <c r="L926" t="inlineStr">
-        <is>
-          <t>8ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="927">
-      <c r="A927" t="inlineStr">
-        <is>
-          <t>As independências não foram revoluções sociais porque as facções mais fortes das burguesias nativas nunca pretenderam mudar as relações de produção existentes, ou estender os direitos democráticos aos oprimidos, e sim tirar o controle das instituições políticas e militares dos espanhóis.
-Disponível em: https://www.fflch.usp.br/73202. Acesso em: 16 jan. 2025.
-A partir do texto, é correto afirmar que as lutas das independências latino-americanos</t>
-        </is>
-      </c>
-      <c r="B927" t="inlineStr">
-        <is>
-          <t>provocaram a ruptura com a metrópole, mas mantiveram boa parte das estruturas sociais coloniais.</t>
-        </is>
-      </c>
-      <c r="C927" t="inlineStr">
-        <is>
-          <t>foram comandadas pelos setores populares, mas fracassaram após serem traídas pelas elites criollas.</t>
-        </is>
-      </c>
-      <c r="D927" t="inlineStr">
-        <is>
-          <t>causaram um fortalecimento da exploração colonial, mas possibilitaram a libertação dos escravizados.</t>
-        </is>
-      </c>
-      <c r="E927" t="inlineStr">
-        <is>
-          <t>foram realizadas por representantes das elites coloniais, mas proporcionaram a igualdade social para toda a população.</t>
-        </is>
-      </c>
-      <c r="F927" t="inlineStr">
-        <is>
-          <t>resultaram na proclamação de diferentes repúblicas, mas que se tornaram monarquias por influência do Império do Brasil.</t>
-        </is>
-      </c>
-      <c r="G927" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H927" t="inlineStr">
-        <is>
-          <t>O texto destaca que as independências na América Latina não foram consideradas revoluções sociais porque as facções mais fortes das burguesias nativas não tinham a intenção de mudar as relações de mudar as estruturas sociais, mas apenas tirar o controle das instituições políticas e militares dos espanhóis. Assim, essas lutas de independência conseguiram romper com a metrópole colonial, mas mantiveram muitas das estruturas sociais e econômicas coloniais inalteradas, perpetuando as desigualdades existentes.</t>
-        </is>
-      </c>
-      <c r="I927" t="inlineStr">
-        <is>
-          <t>PH10</t>
-        </is>
-      </c>
-      <c r="J927" t="inlineStr">
-        <is>
-          <t>História</t>
-        </is>
-      </c>
-      <c r="L927" t="inlineStr">
-        <is>
-          <t>8ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="928">
-      <c r="A928" t="inlineStr">
-        <is>
-          <t>Entre 1878 e 1879, o Exército argentino foi levado aos pampas para, nas palavras do ministro da guerra e futuro presidente, Julio Roca, “expulsar os índios do deserto que se trata de conquistar, para não deixar um só inimigo na retaguarda, submetendo-os pela perseguição ou pela força, sem nos apressar a extirpar o mal pela raiz e destruir esses ninhos de bandoleiros”.
-A chamada “Conquista do Deserto”, como dizem os argentinos brancos, foi essa sequência de operações militares em que os indígenas foram deliberadamente eliminados.
-Disponível em: https://diplomatique.org.br/elites-argentinas-e-os-indigenas/. Acesso em: 16 jan. 2025.
-O texto evidencia que a formação do Estado-nacional argentino, no século XIX, foi marcado pelo(a)</t>
-        </is>
-      </c>
-      <c r="B928" t="inlineStr">
-        <is>
-          <t>perseguição e massacre dos povos indígenas.</t>
-        </is>
-      </c>
-      <c r="C928" t="inlineStr">
-        <is>
-          <t>coexistência pacífica com as comunidades indígenas.</t>
-        </is>
-      </c>
-      <c r="D928" t="inlineStr">
-        <is>
-          <t>ascensão das lideranças indígenas ao governo do país.</t>
-        </is>
-      </c>
-      <c r="E928" t="inlineStr">
-        <is>
-          <t>aliança entre indígenas e espanhóis contra as elites coloniais.</t>
-        </is>
-      </c>
-      <c r="F928" t="inlineStr">
-        <is>
-          <t>criação de regiões administrativas autônomas para os indígenas.</t>
-        </is>
-      </c>
-      <c r="G928" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H928" t="inlineStr">
-        <is>
-          <t>O texto descreve como, entre 1878 e 1879, o Exército argentino realizou uma série de operações militares nas quais os indígenas foram deliberadamente eliminados através de perseguição ou força. Isso demonstra que a formação do Estado-nacional argentino no século XIX foi marcada pela perseguição e massacre dos povos indígenas.</t>
-        </is>
-      </c>
-      <c r="I928" t="inlineStr">
-        <is>
-          <t>PH10</t>
-        </is>
-      </c>
-      <c r="J928" t="inlineStr">
-        <is>
-          <t>História</t>
-        </is>
-      </c>
-      <c r="L928" t="inlineStr">
-        <is>
-          <t>8ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="929">
-      <c r="A929" t="inlineStr">
-        <is>
-          <t>A maior das repercussões da revolução haitiana ocorreu no continente americano, ao destacar para os milhões de escravizados nas colônias portuguesas, espanholas, francesas e inglesas, além dos EUA que mantinham a escravidão, que os negros eram capazes de lutar por sua liberdade e constituir o primeiro estado livre das Américas.
-Disponível em: https://www.fflch.usp.br/36495#:~:text=Em%2022%20de%20agosto%20de,independ%C3%AAncia%20do%20Haiti%20foi%20proclamada.. Acesso em: 16 jan. 2025.
-A repercussão da Revolução Haitiana, mencionada no excerto, provocou a(o)</t>
-        </is>
-      </c>
-      <c r="B929" t="inlineStr">
-        <is>
-          <t>inimizade dos escravizados da América por não se verem representados pelos haitianos.</t>
-        </is>
-      </c>
-      <c r="C929" t="inlineStr">
-        <is>
-          <t>paz entre as elites brancas e os negros escravizados nas demais colônias do continente.</t>
-        </is>
-      </c>
-      <c r="D929" t="inlineStr">
-        <is>
-          <t>união das potências coloniais contra os revolucionários e a derrota da Revolução.</t>
-        </is>
-      </c>
-      <c r="E929" t="inlineStr">
-        <is>
-          <t>constante ameaça de intervenção no país por parte das nações europeias.</t>
-        </is>
-      </c>
-      <c r="F929" t="inlineStr">
-        <is>
-          <t>apoio por parte dos europeus à causa abolicionista nas demais colônias.</t>
-        </is>
-      </c>
-      <c r="G929" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="H929" t="inlineStr">
-        <is>
-          <t>A Revolução Haitiana, que resultou na independência do Haiti e na abolição da escravidão no país, teve um grande impacto no continente americano e no mundo. O movimento alarmou as potências coloniais europeias que ainda dependiam da escravidão em suas colônias. Como resultado, o Haiti enfrentou uma constante ameaça de intervenção e ataques por parte das nações europeias, que temiam que o exemplo haitiano pudesse inspirar revoltas similares em suas próprias colônias.</t>
-        </is>
-      </c>
-      <c r="I929" t="inlineStr">
-        <is>
-          <t>PH10</t>
-        </is>
-      </c>
-      <c r="J929" t="inlineStr">
-        <is>
-          <t>História</t>
-        </is>
-      </c>
-      <c r="L929" t="inlineStr">
-        <is>
-          <t>8ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="930">
-      <c r="A930" t="inlineStr">
-        <is>
-          <t>O fato é que a história do austríaco Maximiliano de Habsburgo e sua mulher Carlota, no chamado Segundo Império mexicano, foi um episódio trágico da história do México — e um dos mais curiosos da América Latina.
-Primo do imperador brasileiro Dom Pedro 2º, Maximiliano era admirador do Brasil e sonhou com uma aliança regional entre os dois países, o que nunca se materializou. Jovem liberal, sabia pouco da realidade política no país que aceitou governar.
-Disponível em: https://www.bbc.com/portuguese/internacional-59394423. Acesso em: 16 jan. 2025.
-A ascensão de Maximiliano de Habsburgo ao trono do México deve ser compreendido como um(a)</t>
-        </is>
-      </c>
-      <c r="B930" t="inlineStr">
-        <is>
-          <t>tentativa de interferência francesa na política mexicana.</t>
-        </is>
-      </c>
-      <c r="C930" t="inlineStr">
-        <is>
-          <t>expressão do descontentamento dos mexicanos com a República.</t>
-        </is>
-      </c>
-      <c r="D930" t="inlineStr">
-        <is>
-          <t>manifestação da frustração popular pela falta de representação política.</t>
-        </is>
-      </c>
-      <c r="E930" t="inlineStr">
-        <is>
-          <t>esforço das elites locais para restaurar os vínculos coloniais com a Espanha.</t>
-        </is>
-      </c>
-      <c r="F930" t="inlineStr">
-        <is>
-          <t>sintoma das disputas políticas e territoriais entre o México e os Estados Unidos.</t>
-        </is>
-      </c>
-      <c r="G930" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H930" t="inlineStr">
-        <is>
-          <t>A ascensão de Maximiliano de Habsburgo ao trono do México foi resultado de uma tentativa de interferência francesa na política mexicana. Napoleão III, então imperador da França, aproveitou a instabilidade política no México para expandir a influência francesa no continente americano. Maximiliano, que pouco conhecia a realidade política do México, foi escolhido como imperador do chamado Segundo Império Mexicano. Essa intervenção estrangeira foi amplamente impopular entre os mexicanos, o que resultou na deposição e na execução de Maximiliano e a proclamação de uma República.</t>
-        </is>
-      </c>
-      <c r="I930" t="inlineStr">
-        <is>
-          <t>PH10</t>
-        </is>
-      </c>
-      <c r="J930" t="inlineStr">
-        <is>
-          <t>História</t>
-        </is>
-      </c>
-      <c r="L930" t="inlineStr">
-        <is>
-          <t>8ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="931">
-      <c r="A931" t="inlineStr">
-        <is>
-          <t>Em geral, o que se pode perceber foi que muitos militares que lutaram nas guerras de independência assumiram a autoridade política das regiões libertadas. Aí está a influência direta das guerras de independência para o surgimento desses personagens: foram delas que heróis militares ganharam poder e reconhecimento por parte da população.
-Disponível em: https://abrir.me/qwLkq. Acesso em: 16 jan. 2025.
-O texto descreve o surgimento de uma categoria de indivíduos que se destacou no período pós-independências, conhecidos como</t>
-        </is>
-      </c>
-      <c r="B931" t="inlineStr">
-        <is>
-          <t>reis.</t>
-        </is>
-      </c>
-      <c r="C931" t="inlineStr">
-        <is>
-          <t>caudilhos.</t>
-        </is>
-      </c>
-      <c r="D931" t="inlineStr">
-        <is>
-          <t>presidentes.</t>
-        </is>
-      </c>
-      <c r="E931" t="inlineStr">
-        <is>
-          <t>imperadores.</t>
-        </is>
-      </c>
-      <c r="F931" t="inlineStr">
-        <is>
-          <t>libertadores.</t>
-        </is>
-      </c>
-      <c r="G931" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H931" t="inlineStr">
-        <is>
-          <t>Esses indivíduos são conhecidos como caudilhos, líderes que surgiram nas regiões recém-independentes da América Latina e que obtiveram um poder político e militar significativos, muitas vezes governando com autoritarismo e baseando sua autoridade no apoio popular e no controle militar.</t>
-        </is>
-      </c>
-      <c r="I931" t="inlineStr">
-        <is>
-          <t>PH10</t>
-        </is>
-      </c>
-      <c r="J931" t="inlineStr">
-        <is>
-          <t>História</t>
-        </is>
-      </c>
-      <c r="L931" t="inlineStr">
-        <is>
-          <t>8ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="932">
-      <c r="A932" t="inlineStr">
-        <is>
-          <t>Impactos da pandemia na educação no Brasil
-"Foi difícil. Eu trabalho home office e conciliar aula online com o trabalho foi complicado porque não tive apoio do meu esposo, porque ele trabalhou direto na pandemia. Eu tive que adaptar, acordar mais cedo para depois fazer tudo que eu tinha que fazer para entregar no dia e ajudar ela. Agora ela está se desenvolvendo bem, só que não concordo com as aulas online, ao invés de ajudar só prejudicou. O esforço maior foi meu."  (Mulher, Grupo Misto 41 a 60 anos – SP)
-Disponível em: https://www12.senado.leg.br/institucional/datasenado/materias/pesquisas/impactos-da-pandemia-na-educacao-no-brasil. Acesso em 19 de dez. 2024.
-No trecho acima, a palavra "meu" exerce a função de</t>
-        </is>
-      </c>
-      <c r="B932" t="inlineStr">
-        <is>
-          <t>verbo.</t>
-        </is>
-      </c>
-      <c r="C932" t="inlineStr">
-        <is>
-          <t>sujeito.</t>
-        </is>
-      </c>
-      <c r="D932" t="inlineStr">
-        <is>
-          <t>predicado.</t>
-        </is>
-      </c>
-      <c r="E932" t="inlineStr">
-        <is>
-          <t>adjunto adnominal.</t>
-        </is>
-      </c>
-      <c r="F932" t="inlineStr">
-        <is>
-          <t>complemento nominal.</t>
-        </is>
-      </c>
-      <c r="G932" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="H932" t="inlineStr">
-        <is>
-          <t>No trecho "O esforço maior foi meu", a palavra "meu" exerce a função de adjunto adnominal. Um adjunto adnominal é um termo acessório da oração que se junta a um substantivo para caracterizá-lo ou determiná-lo, indicando posse, qualidade, quantidade, entre outras características. No caso específico, "meu" é um pronome possessivo que está qualificando o substantivo "esforço", indicando a quem pertence o esforço. Assim, "meu" está fornecendo uma informação adicional sobre o substantivo "esforço", especificando que o esforço pertence à pessoa que está falando. Essa função de qualificação e determinação do substantivo é exatamente o que define um adjunto adnominal.</t>
-        </is>
-      </c>
-      <c r="I932" t="inlineStr">
-        <is>
-          <t>PH10</t>
-        </is>
-      </c>
-      <c r="J932" t="inlineStr">
-        <is>
-          <t>Português</t>
-        </is>
-      </c>
-      <c r="L932" t="inlineStr">
-        <is>
-          <t>8ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="933">
-      <c r="A933" t="inlineStr">
-        <is>
-          <t>Senado proíbe celular em escolas do ensino infantil, fundamental e médio
-Disponível em: https://www12.senado.leg.br/radio/1/noticia/2024/12/18/senado-aprova-proibicao-do-uso-de-celular-e-tablets-por-alunos-do-ensino-infantil-fundamental-e-medio. Acesso em 19 de dez. 2024.
-No título da notícia, exerce a função de adjunto adnominal a palavra:</t>
-        </is>
-      </c>
-      <c r="B933" t="inlineStr">
-        <is>
-          <t>Em</t>
-        </is>
-      </c>
-      <c r="C933" t="inlineStr">
-        <is>
-          <t>Senado</t>
-        </is>
-      </c>
-      <c r="D933" t="inlineStr">
-        <is>
-          <t>Proíbe</t>
-        </is>
-      </c>
-      <c r="E933" t="inlineStr">
-        <is>
-          <t>Celular</t>
-        </is>
-      </c>
-      <c r="F933" t="inlineStr">
-        <is>
-          <t>Fundamental</t>
-        </is>
-      </c>
-      <c r="G933" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="H933" t="inlineStr">
-        <is>
-          <t>No título "Senado proíbe celular em escolas do ensino infantil, fundamental e médio", a palavra "fundamental" exerce a função de adjunto adnominal porque está qualificando o substantivo "ensino". O adjunto adnominal é um termo acessório da oração que tem a função de caracterizar ou determinar um substantivo, concordando com ele em gênero e número. No caso específico, "fundamental" está especificando o tipo de ensino ao qual a proibição se aplica, assim como "infantil" e "médio". Portanto, "fundamental" está atuando como um adjetivo que complementa o substantivo "ensino", caracterizando-o e, por isso, é considerado um adjunto adnominal.</t>
-        </is>
-      </c>
-      <c r="I933" t="inlineStr">
-        <is>
-          <t>PH10</t>
-        </is>
-      </c>
-      <c r="J933" t="inlineStr">
-        <is>
-          <t>Português</t>
-        </is>
-      </c>
-      <c r="L933" t="inlineStr">
-        <is>
-          <t>8ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="934">
-      <c r="A934" t="inlineStr">
-        <is>
-          <t>O dia de 28 de abril é o Dia da Educação. A data é um incentivo para que tenhamos consciência sobre a importância da educação – seja escolar, social ou familiar na vida dos indivíduos. Valores essenciais e convívio saudável se formam com uma boa educação.
-Disponível em: http://mdb-sc.org.br/artigo-de-opiniao-educacao-e-essencial/. Acesso em 19 de dez. 2024.
-No trecho acima, a expressão "da educação" em destaque</t>
-        </is>
-      </c>
-      <c r="B934" t="inlineStr">
-        <is>
-          <t>retoma o sujeito “dia”.</t>
-        </is>
-      </c>
-      <c r="C934" t="inlineStr">
-        <is>
-          <t>completa o sentido de um verbo.</t>
-        </is>
-      </c>
-      <c r="D934" t="inlineStr">
-        <is>
-          <t>especifica uma data comemorativa.</t>
-        </is>
-      </c>
-      <c r="E934" t="inlineStr">
-        <is>
-          <t>indica o estado a que se refere o substantivo “dia”.</t>
-        </is>
-      </c>
-      <c r="F934" t="inlineStr">
-        <is>
-          <t>qualifica o substantivo, indicando a qual "dia" se refere.</t>
-        </is>
-      </c>
-      <c r="G934" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="H934" t="inlineStr">
-        <is>
-          <t>A expressão "da educação" está qualificando o substantivo "dia", especificando a qual "dia" se refere. No contexto do trecho, "dia" é um substantivo genérico que poderia se referir a qualquer dia do ano. No entanto, ao adicionar a expressão "da educação", o substantivo passa a ser qualificado, indicando que se trata de um dia específico dedicado à educação.</t>
-        </is>
-      </c>
-      <c r="I934" t="inlineStr">
-        <is>
-          <t>PH10</t>
-        </is>
-      </c>
-      <c r="J934" t="inlineStr">
-        <is>
-          <t>Português</t>
-        </is>
-      </c>
-      <c r="L934" t="inlineStr">
-        <is>
-          <t>8ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="935">
-      <c r="A935" t="inlineStr">
-        <is>
-          <t>Diante disso, a falta da educação familiar reflete na aprendizagem escolar. É notável a criança que não teve a primeira educação, pois o comportamento na escolar torna-se reflexo dos atos tidos, vividos ou assistidos em casa. Consequentemente, na escola a criança terá dificuldades de convívio e aprendizagem, haja vista que a educação familiar deve ensinar a uma boa educação e a socialização da criança com as outras pessoas.
-Disponível em: https://www.unesc.net/portal/blog/ver/53/38073. Acesso em 19 de dez. 2024.
-No trecho acima, a expressão "da educação familiar"</t>
-        </is>
-      </c>
-      <c r="B935" t="inlineStr">
-        <is>
-          <t>qualifica o substantivo "falta", indicando a sua origem.</t>
-        </is>
-      </c>
-      <c r="C935" t="inlineStr">
-        <is>
-          <t>especifica o modo como a "falta" ocorre.</t>
-        </is>
-      </c>
-      <c r="D935" t="inlineStr">
-        <is>
-          <t>completa o sentido de um verbo.</t>
-        </is>
-      </c>
-      <c r="E935" t="inlineStr">
-        <is>
-          <t>indica o estado do sujeito "falta".</t>
-        </is>
-      </c>
-      <c r="F935" t="inlineStr">
-        <is>
-          <t>retoma o sujeito "educação".</t>
-        </is>
-      </c>
-      <c r="G935" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H935" t="inlineStr">
-        <is>
-          <t>A expressão "da educação familiar" funciona como um adjunto adnominal, qualificando e especificando a origem da "falta". No contexto do trecho, a "falta" mencionada refere-se à ausência ou deficiência de educação que deveria ser fornecida pela família, ou seja, proporcionada no ambiente familiar.</t>
-        </is>
-      </c>
-      <c r="I935" t="inlineStr">
-        <is>
-          <t>PH10</t>
-        </is>
-      </c>
-      <c r="J935" t="inlineStr">
-        <is>
-          <t>Português</t>
-        </is>
-      </c>
-      <c r="L935" t="inlineStr">
-        <is>
-          <t>8ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="936">
-      <c r="A936" t="inlineStr">
-        <is>
-          <t>Um dos pontos fracos na educação da criança é a dificuldade que os pais encontram em dar limites aos seus filhos. Sem limites, o comportamento da criança muitas vezas deixa a desejar, podendo muitas vezes gritar com seus pais, chegando a agredi-los, quando contrariados ou quando não ganham o que querem. Ou mesmo, sendo mal-educados com os que convivem, ou pessoas mais velhas e nem tendo respeito e boas atitudes com as pessoas em geral.
-Disponível em: https://www.unesc.net/portal/blog/ver/53/38073. Acesso em 19 de dez. 2024.
-Na expressão em destaque, é possível substituir “da criança” sem prejuízo de sentido por</t>
-        </is>
-      </c>
-      <c r="B936" t="inlineStr">
-        <is>
-          <t>"infantil".</t>
-        </is>
-      </c>
-      <c r="C936" t="inlineStr">
-        <is>
-          <t>"criancice".</t>
-        </is>
-      </c>
-      <c r="D936" t="inlineStr">
-        <is>
-          <t>"de garotos".</t>
-        </is>
-      </c>
-      <c r="E936" t="inlineStr">
-        <is>
-          <t>"infantilizada".</t>
-        </is>
-      </c>
-      <c r="F936" t="inlineStr">
-        <is>
-          <t>"de pequenos".</t>
-        </is>
-      </c>
-      <c r="G936" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H936" t="inlineStr">
-        <is>
-          <t>A palavra "infantil" funciona como um adjetivo que qualifica algum substantivo relacionado a crianças. No contexto da frase original, "Um dos pontos fracos na educação da criança é a dificuldade que os pais encontram em dar limites aos seus filhos", a expressão "da criança" refere-se à educação que é específica para crianças. Substituir "da criança" por "infantil" mantém o sentido original da frase, pois "educação infantil" é uma expressão comum e amplamente compreendida que se refere ao processo educativo voltado para crianças. As demais alternativas, como "criancice", "de garotos", "infantilizada" e "de pequenos", não se encaixam adequadamente no contexto, pois alteram o sentido ou não são expressões comumente usadas para descrever o tipo de educação mencionado.</t>
-        </is>
-      </c>
-      <c r="I936" t="inlineStr">
-        <is>
-          <t>PH10</t>
-        </is>
-      </c>
-      <c r="J936" t="inlineStr">
-        <is>
-          <t>Português</t>
-        </is>
-      </c>
-      <c r="L936" t="inlineStr">
-        <is>
-          <t>8ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="937">
-      <c r="A937" t="inlineStr">
-        <is>
-          <t>Aprenda a chamar a polícia
-Eu tenho o sono muito leve, e numa noite dessas notei que havia alguém andando sorrateiramente no quintal de casa. Levantei em silêncio e fiquei acompanhando os leves ruídos que vinham lá de fora, até ver uma silhueta passando pela janela do banheiro. Como minha casa era muito segura, com grades nas janelas e trancas internas nas portas, não fiquei muito preocupado, mas era claro que eu não ia deixar um ladrão ali, espiando tranquilamente.
-Liguei baixinho para a polícia, informei a situação e o meu endereço.
-Perguntaram-me se o ladrão estava armado ou se já estava no interior da casa. Esclareci que não e disseram-me que não havia nenhuma viatura por perto para ajudar, mas que iriam mandar alguém assim que fosse possível.
-Um minuto depois, liguei de novo e disse com a voz calma:
-— Oi, eu liguei há pouco porque tinha alguém no meu quintal. Não precisa mais ter pressa. Eu já matei o ladrão com um tiro da escopeta calibre 12, que tenho guardada em casa para estas situações. O tiro fez um estrago danado no cara!
-Passados menos de três minutos, estavam na minha rua cinco carros da polícia, um helicóptero, uma unidade do resgate, uma equipe de TV e a turma dos direitos humanos, que não perderiam isso por nada neste mundo.
-Eles prenderam o ladrão em flagrante, que ficava olhando tudo com cara de assombrado. Talvez ele estivesse pensando que aquela era a casa do Comandante da Polícia.
-[...]
-VERÍSSIMO, Luís Fernando. Aprenda a chamar a polícia. Disponível em: &lt;http://www.refletirpararefletir.com.br/4-cronicas-de-luis-fernando-verissimo&gt;.
-Acesso em: 1 jun. 2018.
-No trecho “e a turma dos direitos humanos, que não perderiam isso por nada neste mundo”, o adjunto adnominal destacado é da classe gramatical dos</t>
-        </is>
-      </c>
-      <c r="B937" t="inlineStr">
-        <is>
-          <t>adjetivos.</t>
-        </is>
-      </c>
-      <c r="C937" t="inlineStr">
-        <is>
-          <t>advérbios.</t>
-        </is>
-      </c>
-      <c r="D937" t="inlineStr">
-        <is>
-          <t>artigos.</t>
-        </is>
-      </c>
-      <c r="E937" t="inlineStr">
-        <is>
-          <t>numerais.</t>
-        </is>
-      </c>
-      <c r="F937" t="inlineStr">
-        <is>
-          <t>pronomes.</t>
-        </is>
-      </c>
-      <c r="G937" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="H937" t="inlineStr">
-        <is>
-          <t>A palavra “neste” é um pronome demonstrativo que, no trecho apresentado, exerce a função de adjunto adnominal do substantivo “mundo”.</t>
-        </is>
-      </c>
-      <c r="I937" t="inlineStr">
-        <is>
-          <t>PH10</t>
-        </is>
-      </c>
-      <c r="J937" t="inlineStr">
-        <is>
-          <t>Português</t>
-        </is>
-      </c>
-      <c r="L937" t="inlineStr">
-        <is>
-          <t>8ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="938">
-      <c r="A938" t="inlineStr">
-        <is>
-          <t>O nascimento da crônica
-Há um meio certo de começar a crônica por uma trivialidade. É dizer: Que calor! Que desenfreado calor! Diz-se isto, agitando as pontas do lenço, bufando como um touro, ou simplesmente sacudindo a sobrecasaca. Resvala-se do calor aos fenômenos atmosféricos, fazem-se algumas conjeturas acerca do sol e da lua, outras sobre a febre amarela, manda-se um suspiro a Petrópolis, e La glace est rompue; está começada a crônica.
-[...]
-Não posso dizer positivamente em que ano nasceu a crônica; mas há toda a probabilidade de crer que foi coetânea das primeiras duas vizinhas. Essas vizinhas, entre o jantar e a merenda, sentaram-se à porta, para debicar os sucessos do dia. Provavelmente começaram a lastimar-se do calor. Uma dizia que não pudera comer ao jantar, outra que tinha a camisa mais ensopando que as ervas que comera. Passar das ervas às plantações do morador fronteiro, e logo às tropelias amatórias do dito morador, e ao resto, era a coisa mais fácil, natural e possível do mundo. Eis a origem da crônica.
-Que eu, sabedor ou conjeturador de tão alta prosápia, queira repetir o meio de que lançaram mãos as duas avós do cronista, é realmente cometer uma trivialidade; e contudo, leitor, seria difícil falar desta quinzena sem dar à canícula o lugar de honra que lhe compete. Seria; mas eu dispensarei esse meio quase tão velho como o mundo, para somente dizer que a verdade mais incontestável que achei debaixo do sol é que ninguém se deve queixar, porque cada pessoa é sempre mais feliz do que outra.
-ASSIS, Machado de. O nascimento da crônica. Disponível em: &lt;https://reticenciajornalistica.wordpress.com/2011/11/28/o-nascimento-da-cronica/&gt;.
-Acesso em: 1 jun. 2018.
-O trecho que apresenta um adjetivo exercendo a função de adjunto adnominal é</t>
-        </is>
-      </c>
-      <c r="B938" t="inlineStr">
-        <is>
-          <t>“bufando como um touro”.</t>
-        </is>
-      </c>
-      <c r="C938" t="inlineStr">
-        <is>
-          <t>“entre o jantar e a merenda”.</t>
-        </is>
-      </c>
-      <c r="D938" t="inlineStr">
-        <is>
-          <t>“manda-se um suspiro a Petrópolis”.</t>
-        </is>
-      </c>
-      <c r="E938" t="inlineStr">
-        <is>
-          <t>“Eis a origem da crônica”.</t>
-        </is>
-      </c>
-      <c r="F938" t="inlineStr">
-        <is>
-          <t>“Que desenfreado calor!”​.</t>
-        </is>
-      </c>
-      <c r="G938" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="H938" t="inlineStr">
-        <is>
-          <t>No trecho “Que desenfreado calor!”, o termo “desenfreado” é um adjetivo que exerce a função de adjunto adnominal do substantivo “calor”.</t>
-        </is>
-      </c>
-      <c r="I938" t="inlineStr">
-        <is>
-          <t>PH10</t>
-        </is>
-      </c>
-      <c r="J938" t="inlineStr">
-        <is>
-          <t>Português</t>
-        </is>
-      </c>
-      <c r="L938" t="inlineStr">
-        <is>
-          <t>8ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="939">
-      <c r="A939" t="inlineStr">
-        <is>
-          <t>O nascimento da crônica
-Há um meio certo de começar a crônica por uma trivialidade. É dizer: Que calor! Que desenfreado calor! Diz-se isto, agitando as pontas do lenço, bufando como um touro, ou simplesmente sacudindo a sobrecasaca. Resvala-se do calor aos fenômenos atmosféricos, fazem-se algumas conjeturas acerca do sol e da lua, outras sobre a febre amarela, manda-se um suspiro a Petrópolis, e La glace est rompue; está começada a crônica.
-[...]
-Não posso dizer positivamente em que ano nasceu a crônica; mas há toda a probabilidade de crer que foi coetânea das primeiras duas vizinhas. Essas vizinhas, entre o jantar e a merenda, sentaram-se à porta, para debicar os sucessos do dia. Provavelmente começaram a lastimar-se do calor. Uma dizia que não pudera comer ao jantar, outra que tinha a camisa mais ensopando que as ervas que comera. Passar das ervas às plantações do morador fronteiro, e logo às tropelias amatórias do dito morador, e ao resto, era a coisa mais fácil, natural e possível do mundo. Eis a origem da crônica.
-Que eu, sabedor ou conjeturador de tão alta prosápia, queira repetir o meio de que lançaram mãos as duas avós do cronista, é realmente cometer uma trivialidade; e contudo, leitor, seria difícil falar desta quinzena sem dar à canícula o lugar de honra que lhe compete. Seria; mas eu dispensarei esse meio quase tão velho como o mundo, para somente dizer que a verdade mais incontestável que achei debaixo do sol é que ninguém se deve queixar, porque cada pessoa é sempre mais feliz do que outra.
-ASSIS, Machado de. O nascimento da crônica. Disponível em: &lt;https://reticenciajornalistica.wordpress.com/2011/11/28/o-nascimento-da-cronica/&gt;.
-Acesso em: 1 jun. 2018.
-No trecho “Há um meio certo de começar a crônica por uma trivialidade”, os adjuntos adnominais ligados ao substantivo “meio” são</t>
-        </is>
-      </c>
-      <c r="B939" t="inlineStr">
-        <is>
-          <t>“certo” e “começar”.</t>
-        </is>
-      </c>
-      <c r="C939" t="inlineStr">
-        <is>
-          <t>“começar” e “crônica”.</t>
-        </is>
-      </c>
-      <c r="D939" t="inlineStr">
-        <is>
-          <t>“começar” e “uma”.</t>
-        </is>
-      </c>
-      <c r="E939" t="inlineStr">
-        <is>
-          <t>“há” e “certo”.</t>
-        </is>
-      </c>
-      <c r="F939" t="inlineStr">
-        <is>
-          <t>“um” e “certo”.</t>
-        </is>
-      </c>
-      <c r="G939" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="H939" t="inlineStr">
-        <is>
-          <t>“Um” e “certo” são adjuntos adnominais do substantivo “meio” e ligam-se a ele para caracterizá-lo.</t>
-        </is>
-      </c>
-      <c r="I939" t="inlineStr">
-        <is>
-          <t>PH10</t>
-        </is>
-      </c>
-      <c r="J939" t="inlineStr">
-        <is>
-          <t>Português</t>
-        </is>
-      </c>
-      <c r="L939" t="inlineStr">
-        <is>
-          <t>8ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="940">
-      <c r="A940" t="inlineStr">
-        <is>
-          <t>O nascimento da crônica
-Há um meio certo de começar a crônica por uma trivialidade. É dizer: Que calor! Que desenfreado calor! Diz-se isto, agitando as pontas do lenço, bufando como um touro, ou simplesmente sacudindo a sobrecasaca. Resvala-se do calor aos fenômenos atmosféricos, fazem-se algumas conjeturas acerca do sol e da lua, outras sobre a febre amarela, manda-se um suspiro a Petrópolis, e La glace est rompue; está começada a crônica.
-[...]
-Não posso dizer positivamente em que ano nasceu a crônica; mas há toda a probabilidade de crer que foi coetânea das primeiras duas vizinhas. Essas vizinhas, entre o jantar e a merenda, sentaram-se à porta, para debicar os sucessos do dia. Provavelmente começaram a lastimar-se do calor. Uma dizia que não pudera comer ao jantar, outra que tinha a camisa mais ensopando que as ervas que comera. Passar das ervas às plantações do morador fronteiro, e logo às tropelias amatórias do dito morador, e ao resto, era a coisa mais fácil, natural e possível do mundo. Eis a origem da crônica.
-Que eu, sabedor ou conjeturador de tão alta prosápia, queira repetir o meio de que lançaram mãos as duas avós do cronista, é realmente cometer uma trivialidade; e contudo, leitor, seria difícil falar desta quinzena sem dar à canícula o lugar de honra que lhe compete. Seria; mas eu dispensarei esse meio quase tão velho como o mundo, para somente dizer que a verdade mais incontestável que achei debaixo do sol é que ninguém se deve queixar, porque cada pessoa é sempre mais feliz do que outra.
-ASSIS, Machado de. O nascimento da crônica. Disponível em: &lt;https://reticenciajornalistica.wordpress.com/2011/11/28/o-nascimento-da-cronica/&gt;.
-Acesso em: 1 jun. 2018.
-No trecho “há toda a probabilidade de crer que foi coetânea das primeiras duas vizinhas”, o adjunto adnominal destacado tem a função de</t>
-        </is>
-      </c>
-      <c r="B940" t="inlineStr">
-        <is>
-          <t>comprovar a origem da crônica.</t>
-        </is>
-      </c>
-      <c r="C940" t="inlineStr">
-        <is>
-          <t>indicar o momento do evento.</t>
-        </is>
-      </c>
-      <c r="D940" t="inlineStr">
-        <is>
-          <t>narrar a amizade das mulheres.</t>
-        </is>
-      </c>
-      <c r="E940" t="inlineStr">
-        <is>
-          <t>quantificar o nome “vizinhas”.</t>
-        </is>
-      </c>
-      <c r="F940" t="inlineStr">
-        <is>
-          <t>situar o substantivo no espaço​.</t>
-        </is>
-      </c>
-      <c r="G940" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="H940" t="inlineStr">
-        <is>
-          <t>O adjunto adnominal “duas” pertence à classe dos numerais, sendo usado, aqui, para quantificar o substantivo “vizinhas”.</t>
-        </is>
-      </c>
-      <c r="I940" t="inlineStr">
-        <is>
-          <t>PH10</t>
-        </is>
-      </c>
-      <c r="J940" t="inlineStr">
-        <is>
-          <t>Português</t>
-        </is>
-      </c>
-      <c r="L940" t="inlineStr">
-        <is>
-          <t>8ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="941">
-      <c r="A941" t="inlineStr">
-        <is>
-          <t>Os terroristas​
-Era um professor duro, exigente e implacável. As provas eram feitas sem aviso prévio. Todos os trabalhos valiam nota e eram corrigidos segundo os critérios mais rigorosos. Resultado: no fim do ano quase todos os alunos estavam à beira da reprovação. As notas que ele anotava cuidadosamente no livro de chamada eram as mais baixas possíveis. O que fazer?
-Reuniam-se todos os dias no bar em frente ao colégio, para discutir a situação, mas nada lhes ocorria. Até que um deles teve uma ideia brilhante. O livro de chamada. A solução estava ali: tinham de se apossar do livro de chamada e mudar as notas. Um 0 poderia se transformar em 8. Um 1 poderia virar 7 (ou 10, dependendo do grau de ambição).
-O problema era pegar o livro, que o professor não largava nunca, nem mesmo para ir ao banheiro. Aparentemente só uma catástrofe poderia superá-los. Recorreram, pois, à catástrofe. Um dos alunos telefonou do orelhão em frente ao colégio, avisando que havia um princípio de incêndio na casa do professor. Avisado, o pobre homem saiu correndo da sala de aula, deixando sobre a mesa o famigerado livro de presenças.
-Acreditareis se eu disser que ninguém tocou no livro? Ninguém tocou no livro. Os rapazes se olhavam, mas nenhum deles tomou a iniciativa de mudar as notas. Às vezes a consciência pesa mais que a ameaça da reprovação.
-SCLIAR, Moacyr. Os terroristas. Disponível em: &lt;http://jornadapadremarzano.blogspot.com.br/2017/08/os-terroristas-moacyr-scliar.html&gt;. Acesso em: 1 jun. 2018.
-No trecho “Todos os trabalhos valiam nota e eram corrigidos segundo os critérios mais rigorosos”, o termo “rigorosos” concorda em gênero e número com</t>
-        </is>
-      </c>
-      <c r="B941" t="inlineStr">
-        <is>
-          <t>"corrigidos".</t>
-        </is>
-      </c>
-      <c r="C941" t="inlineStr">
-        <is>
-          <t>"critérios".</t>
-        </is>
-      </c>
-      <c r="D941" t="inlineStr">
-        <is>
-          <t>"mais".</t>
-        </is>
-      </c>
-      <c r="E941" t="inlineStr">
-        <is>
-          <t>"todos".</t>
-        </is>
-      </c>
-      <c r="F941" t="inlineStr">
-        <is>
-          <t>"trabalhos".</t>
-        </is>
-      </c>
-      <c r="G941" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H941" t="inlineStr">
-        <is>
-          <t>No trecho, o termo “rigorosos” é adjunto adnominal de “critérios”, concordando com ele em gênero e número.</t>
-        </is>
-      </c>
-      <c r="I941" t="inlineStr">
-        <is>
-          <t>PH10</t>
-        </is>
-      </c>
-      <c r="J941" t="inlineStr">
-        <is>
-          <t>Português</t>
-        </is>
-      </c>
-      <c r="L941" t="inlineStr">
-        <is>
-          <t>8ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="942">
-      <c r="A942" t="inlineStr">
-        <is>
-          <t>Uma pastelaria vende dois tipos de pastéis: pastéis simples e pastéis especiais. No final do dia, o caixa registrou um total de 120 pastéis vendidos, sendo que a quantidade de pastéis simples foi o dobro da quantidade de pastéis especiais.
-Quantos pastéis especiais foram vendidos ao longo do dia?</t>
-        </is>
-      </c>
-      <c r="B942" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="C942" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="D942" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="E942" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="F942" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="G942" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H942" t="inlineStr">
-        <is>
-          <t>Seja x a quantidade de pastéis simples vendidos e y a quantidade de pastéis especiais vendidos. Do enunciado sabe-se que o total de pastéis vendidos foi 120: x + y = 120.
-A quantidade de pastéis simples é o dobro da quantidade de pastéis especiais: x = 2y. Logo,  Portanto, foram 40 pastéis especiais vendidos.</t>
-        </is>
-      </c>
-      <c r="I942" t="inlineStr">
-        <is>
-          <t>PH10</t>
-        </is>
-      </c>
-      <c r="J942" t="inlineStr">
-        <is>
-          <t>Matemática</t>
-        </is>
-      </c>
-      <c r="L942" t="inlineStr">
-        <is>
-          <t>8ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="943">
-      <c r="A943" t="inlineStr">
-        <is>
-          <t>Um vendedor de frutas vende maçãs e laranjas. Ele vendeu 3 vezes mais maçãs do que laranjas.
-Se ele vendeu um total de 40 frutas, quantas laranjas ele vendeu?</t>
-        </is>
-      </c>
-      <c r="B943" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C943" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="D943" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="E943" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="F943" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="G943" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H943" t="inlineStr">
-        <is>
-          <t>Vamos representar a quantidade de maçãs por x e a quantidade de laranjas por y. Temos o sistema de equações:
-Substituindo x na segunda equação, temos:
-Portanto, ele vendeu 10 laranjas.</t>
-        </is>
-      </c>
-      <c r="I943" t="inlineStr">
-        <is>
-          <t>PH10</t>
-        </is>
-      </c>
-      <c r="J943" t="inlineStr">
-        <is>
-          <t>Matemática</t>
-        </is>
-      </c>
-      <c r="L943" t="inlineStr">
-        <is>
-          <t>8ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="944">
-      <c r="A944" t="inlineStr">
-        <is>
-          <t>Um restaurante vende dois tipos de pratos: prato A e prato B. O prato A custa R$ 15,00 e o prato B custa R$ 20,00. Em um dia, o restaurante vendeu um total de 50 pratos e arrecadou R$ 850,00.
-Quantos pratos do tipo A foram vendidos?</t>
-        </is>
-      </c>
-      <c r="B944" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="C944" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="D944" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E944" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="F944" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G944" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H944" t="inlineStr">
-        <is>
-          <t>Vamos representar a quantidade de pratos A por x e a quantidade de pratos B por y. Temos o sistema de equações: 
-Multiplicando a primeira equação por 15.
-Subtraindo a primeira equação da segunda:
-Substituindo y na primeira equação:
-Portanto, foram vendidos 30 pratos do tipo A.</t>
-        </is>
-      </c>
-      <c r="I944" t="inlineStr">
-        <is>
-          <t>PH10</t>
-        </is>
-      </c>
-      <c r="J944" t="inlineStr">
-        <is>
-          <t>Matemática</t>
-        </is>
-      </c>
-      <c r="L944" t="inlineStr">
-        <is>
-          <t>8ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="945">
-      <c r="A945" t="inlineStr">
-        <is>
-          <t>Em um mercadinho o preço de 2 pacotes de arroz e feijão. O preço de 2 pacotes de arroz e 3 pacotes de feijão é R$ 45,00. Já o preço de 4 pacotes de arroz e 2 pacotes de feijão é R$ 60,00
-Quanto custa um pacote de arroz?</t>
-        </is>
-      </c>
-      <c r="B945" t="inlineStr">
-        <is>
-          <t>R$ 5,00</t>
-        </is>
-      </c>
-      <c r="C945" t="inlineStr">
-        <is>
-          <t>R$ 7,50</t>
-        </is>
-      </c>
-      <c r="D945" t="inlineStr">
-        <is>
-          <t>R$ 10,00</t>
-        </is>
-      </c>
-      <c r="E945" t="inlineStr">
-        <is>
-          <t>R$ 11,25</t>
-        </is>
-      </c>
-      <c r="F945" t="inlineStr">
-        <is>
-          <t>R$ 15,00</t>
-        </is>
-      </c>
-      <c r="G945" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="H945" t="inlineStr">
-        <is>
-          <t>Seja x o preço do pacote de arroz e y o preço do pacote de feijão. O problema pode ser modelado pelo seguinte sistema de equações:
-Simplificando e somando as equações, tem-se:
-Este é o preço de um pacote de feijão (R$ 7,50). Substituindo este valor em , obtém-se:
-Portanto, o preço de um pacote de arroz é R$ 11,25.</t>
-        </is>
-      </c>
-      <c r="I945" t="inlineStr">
-        <is>
-          <t>PH10</t>
-        </is>
-      </c>
-      <c r="J945" t="inlineStr">
-        <is>
-          <t>Matemática</t>
-        </is>
-      </c>
-      <c r="L945" t="inlineStr">
-        <is>
-          <t>8ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="946">
-      <c r="A946" t="inlineStr">
-        <is>
-          <t>Um mecânico trabalha com dois tipos de serviços: troca de óleo e alinhamento. Ele realizou 5 trocas de óleo e 3 alinhamentos em um dia, e recebeu um total de R$ 200,00. No dia seguinte, ele realizou 2 trocas de óleo e 4 alinhamentos, recebendo um total de R$ 160,00.
-Quanto ele cobra por cada troca de óleo?</t>
-        </is>
-      </c>
-      <c r="B946" t="inlineStr">
-        <is>
-          <t>R$ 40,00</t>
-        </is>
-      </c>
-      <c r="C946" t="inlineStr">
-        <is>
-          <t>R$ 28,57</t>
-        </is>
-      </c>
-      <c r="D946" t="inlineStr">
-        <is>
-          <t>R$ 24,00</t>
-        </is>
-      </c>
-      <c r="E946" t="inlineStr">
-        <is>
-          <t>R$ 22,86</t>
-        </is>
-      </c>
-      <c r="F946" t="inlineStr">
-        <is>
-          <t>R$ 13,34</t>
-        </is>
-      </c>
-      <c r="G946" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="H946" t="inlineStr">
-        <is>
-          <t>Vamos representar o valor da troca de óleo por x e o valor do alinhamento por y. Temos o sistema de equações:
-Simplificando e isolando o x na segunda equação, temos:
-Substituindo x na primeira equação:
-5(80 – 2y) + 3y = 200
-400 – 10y + 3y = 200 
-400 – 7y = - 200 
-y = 28.57
-Agora, substituindo y na equação x = 80 – 2y:
-x = 80 – 2(28.57) = 80 – 57,14 = 22,86.
-Portanto, o mecânico cobra aproximadamente R$ 22,86 por troca de óleo.</t>
-        </is>
-      </c>
-      <c r="I946" t="inlineStr">
-        <is>
-          <t>PH10</t>
-        </is>
-      </c>
-      <c r="J946" t="inlineStr">
-        <is>
-          <t>Matemática</t>
-        </is>
-      </c>
-      <c r="L946" t="inlineStr">
-        <is>
-          <t>8ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="947">
-      <c r="A947" t="inlineStr">
-        <is>
-          <t>Um clube promoveu uma festa para arrecadar fundos para uma instituição de caridade. As pessoas que eram sócias do clube pagaram R$ 20,00 de entrada e as pessoas que não eram sócias do clube pagaram R$ 35,00. Se o clube vendeu 310 ingressos e arrecadou R$ 8 450,00 com a venda dos ingressos, quantas pessoas não associadas ao clube participaram da festa?</t>
-        </is>
-      </c>
-      <c r="B947" t="inlineStr">
-        <is>
-          <t>150.</t>
-        </is>
-      </c>
-      <c r="C947" t="inlineStr">
-        <is>
-          <t>160.</t>
-        </is>
-      </c>
-      <c r="D947" t="inlineStr">
-        <is>
-          <t>170.</t>
-        </is>
-      </c>
-      <c r="E947" t="inlineStr">
-        <is>
-          <t>180.</t>
-        </is>
-      </c>
-      <c r="F947" t="inlineStr">
-        <is>
-          <t>190.</t>
-        </is>
-      </c>
-      <c r="G947" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H947" t="inlineStr">
-        <is>
-          <t>Considere x o total de pessoas associadas e y as pessoas que não são sócias do clube. Assim, temos:
-Portanto, 150 pessoas que não são sócias do clube participaram da festa.</t>
-        </is>
-      </c>
-      <c r="I947" t="inlineStr">
-        <is>
-          <t>PH10</t>
-        </is>
-      </c>
-      <c r="J947" t="inlineStr">
-        <is>
-          <t>Matemática</t>
-        </is>
-      </c>
-      <c r="L947" t="inlineStr">
-        <is>
-          <t>8ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="948">
-      <c r="A948" t="inlineStr">
-        <is>
-          <t>Considere o sistema abaixo.
-Qual é o valor da expressão x + y?</t>
-        </is>
-      </c>
-      <c r="B948" t="inlineStr">
-        <is>
-          <t>[img:8a_ph10_mat_07_a.png]</t>
-        </is>
-      </c>
-      <c r="C948" t="inlineStr">
-        <is>
-          <t>[img:8a_ph10_mat_07_b.png]</t>
-        </is>
-      </c>
-      <c r="D948" t="inlineStr">
-        <is>
-          <t>[img:8a_ph10_mat_07_c.png]</t>
-        </is>
-      </c>
-      <c r="E948" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="F948" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="G948" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H948" t="inlineStr">
-        <is>
-          <t>Condição de existência:
-Resolvendo o sistema temos:
-Os valores encontrados para x e y são diferentes de 0, logo eles são válidos.</t>
-        </is>
-      </c>
-      <c r="I948" t="inlineStr">
-        <is>
-          <t>PH10</t>
-        </is>
-      </c>
-      <c r="J948" t="inlineStr">
-        <is>
-          <t>Matemática</t>
-        </is>
-      </c>
-      <c r="K948" t="inlineStr">
-        <is>
-          <t>8a_ph10_mat_07.png</t>
-        </is>
-      </c>
-      <c r="L948" t="inlineStr">
-        <is>
-          <t>8ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="949">
-      <c r="A949" t="inlineStr">
-        <is>
-          <t>Considere o sistema abaixo, com a ≠ 0 e b ≠ 0.
-Sobre a solução desse sistema, é verdade que</t>
-        </is>
-      </c>
-      <c r="B949" t="inlineStr">
-        <is>
-          <t>a e b são números primos.</t>
-        </is>
-      </c>
-      <c r="C949" t="inlineStr">
-        <is>
-          <t>b &lt; a.</t>
-        </is>
-      </c>
-      <c r="D949" t="inlineStr">
-        <is>
-          <t>a e b são números pares.</t>
-        </is>
-      </c>
-      <c r="E949" t="inlineStr">
-        <is>
-          <t>a é um número par e b não é primo.</t>
-        </is>
-      </c>
-      <c r="F949" t="inlineStr">
-        <is>
-          <t>a é um número ímpar e b não é primo.</t>
-        </is>
-      </c>
-      <c r="G949" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H949" t="inlineStr">
-        <is>
-          <t>Subtraindo (I) de (II):
-Substituindo o valor de b em (II):
-Portanto, a e b são números primos.</t>
-        </is>
-      </c>
-      <c r="I949" t="inlineStr">
-        <is>
-          <t>PH10</t>
-        </is>
-      </c>
-      <c r="J949" t="inlineStr">
-        <is>
-          <t>Matemática</t>
-        </is>
-      </c>
-      <c r="K949" t="inlineStr">
-        <is>
-          <t>8a_ph10_mat_08.png</t>
-        </is>
-      </c>
-      <c r="L949" t="inlineStr">
-        <is>
-          <t>8ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="950">
-      <c r="A950" t="inlineStr">
-        <is>
-          <t>Em um jogo de certo ou errado, para cada pergunta respondida corretamente o candidato ganhava 2 pontos e, caso ele errasse a resposta, perdia 3 pontos. Otávio participou desse jogo e marcou 12 pontos.
-Se foram feitas a ele 11 perguntas, qual dos sistemas abaixo calcularia o número de perguntas respondidas corretamente por Otávio?</t>
-        </is>
-      </c>
-      <c r="B950" t="inlineStr">
-        <is>
-          <t>[img:8a_ph10_mat_09_a.png]</t>
-        </is>
-      </c>
-      <c r="C950" t="inlineStr">
-        <is>
-          <t>[img:8a_ph10_mat_09_b.png]</t>
-        </is>
-      </c>
-      <c r="D950" t="inlineStr">
-        <is>
-          <t>[img:8a_ph10_mat_09_c.png]</t>
-        </is>
-      </c>
-      <c r="E950" t="inlineStr">
-        <is>
-          <t>[img:8a_ph10_mat_09_d.png]</t>
-        </is>
-      </c>
-      <c r="F950" t="inlineStr">
-        <is>
-          <t>[img:8a_ph10_mat_09_e.png]</t>
-        </is>
-      </c>
-      <c r="G950" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H950" t="inlineStr">
-        <is>
-          <t>Seja x o total de perguntas respondidas corretamente e y o total de perguntas respondidas erradas. Do enunciado, temos:</t>
-        </is>
-      </c>
-      <c r="I950" t="inlineStr">
-        <is>
-          <t>PH10</t>
-        </is>
-      </c>
-      <c r="J950" t="inlineStr">
-        <is>
-          <t>Matemática</t>
-        </is>
-      </c>
-      <c r="L950" t="inlineStr">
-        <is>
-          <t>8ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="951">
-      <c r="A951" t="inlineStr">
-        <is>
-          <t>Em um jogo de certo ou errado, para cada pergunta respondida corretamente o candidato ganhava 2 pontos e, caso ele errasse a resposta, perdia 3 pontos. Otávio participou desse jogo e marcou 12 pontos.
-Sabendo que Otávio respondeu 11 perguntas, quantas destas Otávio acertou?</t>
-        </is>
-      </c>
-      <c r="B951" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C951" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D951" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E951" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="F951" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="G951" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="H951" t="inlineStr">
-        <is>
-          <t>Sejam x e y as quantidades de respostas certas e erradas, respectivamente.
-Portanto, 9 perguntas foram respondidas corretamente.</t>
-        </is>
-      </c>
-      <c r="I951" t="inlineStr">
-        <is>
-          <t>PH10</t>
-        </is>
-      </c>
-      <c r="J951" t="inlineStr">
-        <is>
-          <t>Matemática</t>
-        </is>
-      </c>
-      <c r="L951" t="inlineStr">
-        <is>
-          <t>8ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="952">
-      <c r="A952" t="inlineStr">
-        <is>
           <t>Com a queda de temperatura, normalmente as pessoas tendem a ficar mais tempo em locais fechados, o que ajuda a proliferar doenças respiratórias, uma vez que o vírus influenza tem alta transmissibilidade por espirro e tosse, além do contato direto das mãos e objetos comuns como corrimões e maçanetas.
 Disponível em: http://saude.sp.gov.br/coordenadoria-de-controle-de-doencas/noticias/23032024-gripe-resfriado-pneumonia-covid-19-virose-saiba-identificar-as-doencas-no-outono. Acesso em: 16 jan. 2025.
 Uma forma de prevenir a doença causada por esse vírus é</t>
         </is>
       </c>
-      <c r="B952" t="inlineStr">
+      <c r="B902" t="inlineStr">
         <is>
           <t>tomar regularmente antibióticos e antivirais.</t>
         </is>
       </c>
-      <c r="C952" t="inlineStr">
+      <c r="C902" t="inlineStr">
         <is>
           <t>higienizar as mãos apenas com álcool em gel.</t>
         </is>
       </c>
-      <c r="D952" t="inlineStr">
+      <c r="D902" t="inlineStr">
         <is>
           <t>praticar atividades físicas ao ar livre regularmente.</t>
         </is>
       </c>
-      <c r="E952" t="inlineStr">
+      <c r="E902" t="inlineStr">
         <is>
           <t>evitar aglomerações e ambientes fechados em estações frias.</t>
         </is>
       </c>
-      <c r="F952" t="inlineStr"/>
-      <c r="G952" t="inlineStr">
+      <c r="F902" t="inlineStr"/>
+      <c r="G902" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H952" t="inlineStr">
+      <c r="H902" t="inlineStr">
         <is>
           <t>Evitar aglomerações e ambientes fechados é uma medida eficaz para reduzir a exposição ao vírus influenza, que se transmite facilmente em locais com grande concentração de pessoas e pouca ventilação.</t>
         </is>
       </c>
-      <c r="I952" t="inlineStr">
+      <c r="I902" t="inlineStr">
         <is>
           <t>PH10</t>
         </is>
       </c>
-      <c r="J952" t="inlineStr">
+      <c r="J902" t="inlineStr">
         <is>
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K952" t="inlineStr"/>
-      <c r="L952" t="inlineStr">
+      <c r="K902" t="inlineStr"/>
+      <c r="L902" t="inlineStr">
         <is>
           <t>7ano</t>
         </is>
       </c>
     </row>
-    <row r="953">
-      <c r="A953" t="inlineStr">
+    <row r="903">
+      <c r="A903" t="inlineStr">
         <is>
           <t>O tétano é uma doença causada pela bactéria Clostridium tetani, que pode entrar no corpo humano através de ferimentos contaminados. A doença causa contrações musculares dolorosas e pode ser fatal se não tratada.
 Qual das seguintes alternativas é uma medida eficaz para prevenir essa doença?</t>
         </is>
       </c>
-      <c r="B953" t="inlineStr">
+      <c r="B903" t="inlineStr">
         <is>
           <t>Manter a vacinação em dia.</t>
         </is>
       </c>
-      <c r="C953" t="inlineStr">
+      <c r="C903" t="inlineStr">
         <is>
           <t>Tomar analgésicos regularmente.</t>
         </is>
       </c>
-      <c r="D953" t="inlineStr">
+      <c r="D903" t="inlineStr">
         <is>
           <t>Consumir alimentos ricos em cálcio.</t>
         </is>
       </c>
-      <c r="E953" t="inlineStr">
+      <c r="E903" t="inlineStr">
         <is>
           <t>Evitar contato com pessoas infectadas.</t>
         </is>
       </c>
-      <c r="F953" t="inlineStr"/>
-      <c r="G953" t="inlineStr">
+      <c r="F903" t="inlineStr"/>
+      <c r="G903" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H953" t="inlineStr">
+      <c r="H903" t="inlineStr">
         <is>
           <t>Manter a vacinação em dia é uma medida eficaz para prevenir o tétano, pois a vacina protege contra a toxina produzida pela bactéria Clostridium tetani.</t>
         </is>
       </c>
-      <c r="I953" t="inlineStr">
+      <c r="I903" t="inlineStr">
         <is>
           <t>PH10</t>
         </is>
       </c>
-      <c r="J953" t="inlineStr">
+      <c r="J903" t="inlineStr">
         <is>
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K953" t="inlineStr"/>
-      <c r="L953" t="inlineStr">
+      <c r="K903" t="inlineStr"/>
+      <c r="L903" t="inlineStr">
         <is>
           <t>7ano</t>
         </is>
       </c>
     </row>
-    <row r="954">
-      <c r="A954" t="inlineStr">
+    <row r="904">
+      <c r="A904" t="inlineStr">
         <is>
           <t>“A Aids era uma doença variada, e uniformemente fatal”, definiu Drauzio Varella num episódio recente de seu (ótimo) podcast, o Outras Histórias. “À medida que a imunidade ia caindo”, ele segue, “repetiam-se as infecções oportunistas: pneumonias, meningites, lesões cerebrais por toxoplasmose… Você tratava uma infecção e vinha outra, depois outra. Uma hora o doente estava tão debilitado não sobrevivia”.
 Drauzio usa o tempo verbal no passado por um motivo óbvio: Aids sem tratamento é uma página virada no Brasil. Começou há 30 anos, em 1991. Foi quando teve início a compra e a distribuição gratuita de remédios contra o HIV pelo SUS.
@@ -54523,1006 +51472,997 @@
 Sobre a prevenção e o tratamento da AIDS, pode-se afirmar corretamente que</t>
         </is>
       </c>
-      <c r="B954" t="inlineStr">
+      <c r="B904" t="inlineStr">
         <is>
           <t>o uso consistente de preservativos é a única forma eficaz de prevenir a transmissão do HIV.</t>
         </is>
       </c>
-      <c r="C954" t="inlineStr">
+      <c r="C904" t="inlineStr">
         <is>
           <t>a descoberta dos remédios contra o HIV tornou a AIDS uma doença completamente controlável.</t>
         </is>
       </c>
-      <c r="D954" t="inlineStr">
+      <c r="D904" t="inlineStr">
         <is>
           <t>pessoas infectadas pelo HIV não devem ter filhos, pois a doença é transmitida geneticamente para os descendentes.</t>
         </is>
       </c>
-      <c r="E954" t="inlineStr">
+      <c r="E904" t="inlineStr">
         <is>
           <t>o tratamento antirretroviral pode permitir que pessoas com HIV tenham vidas saudáveis, mas não elimina completamente o vírus do organismo.</t>
         </is>
       </c>
-      <c r="F954" t="inlineStr"/>
-      <c r="G954" t="inlineStr">
+      <c r="F904" t="inlineStr"/>
+      <c r="G904" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H954" t="inlineStr">
+      <c r="H904" t="inlineStr">
         <is>
           <t>O tratamento antirretroviral (TAR) permite que pessoas vivendo com HIV mantenham uma carga viral indetectável, o que melhora significativamente a qualidade de vida e a expectativa de vida. No entanto, o TAR não elimina completamente o vírus do organismo, exigindo tratamento contínuo.</t>
         </is>
       </c>
-      <c r="I954" t="inlineStr">
+      <c r="I904" t="inlineStr">
         <is>
           <t>PH10</t>
         </is>
       </c>
-      <c r="J954" t="inlineStr">
+      <c r="J904" t="inlineStr">
         <is>
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K954" t="inlineStr"/>
-      <c r="L954" t="inlineStr">
+      <c r="K904" t="inlineStr"/>
+      <c r="L904" t="inlineStr">
         <is>
           <t>7ano</t>
         </is>
       </c>
     </row>
-    <row r="955">
-      <c r="A955" t="inlineStr">
+    <row r="905">
+      <c r="A905" t="inlineStr">
         <is>
           <t>A tuberculose é uma doença infecciosa e transmissível, causada pela bactéria Mycobacterium tuberculosis, também conhecida como bacilo de Koch. A doença afeta prioritariamente os pulmões (forma pulmonar), embora possa acometer outros órgãos e/ou sistemas. [...] O tratamento da tuberculose dura no mínimo seis meses, é gratuito e está disponível no Sistema Único de Saúde (SUS). A tuberculose tem cura quando o tratamento é feito de forma adequada, até o final.
 Disponível em: https://www.gov.br/saude/pt-br/assuntos/saude-de-a-a-z/t/tuberculose#:~:text=A%20tuberculose%20%C3%A9%20uma%20doen%C3%A7a,outros%20%C3%B3rg%C3%A3os%20e%2Fou%20sistemas. Acesso em: 14 jan. 2025.
 Qual das seguintes alternativas descreve a importância de seguir o tratamento completo dessa doença?</t>
         </is>
       </c>
-      <c r="B955" t="inlineStr">
+      <c r="B905" t="inlineStr">
         <is>
           <t>Minimizar os efeitos colaterais dos antibióticos usados no tratamento.</t>
         </is>
       </c>
-      <c r="C955" t="inlineStr">
+      <c r="C905" t="inlineStr">
         <is>
           <t>Reduzir a necessidade de campanhas de vacinação futuras contra a tuberculose.</t>
         </is>
       </c>
-      <c r="D955" t="inlineStr">
+      <c r="D905" t="inlineStr">
         <is>
           <t>Garantir que a bactéria seja completamente eliminada e prevenir a resistência bacteriana.</t>
         </is>
       </c>
-      <c r="E955" t="inlineStr">
+      <c r="E905" t="inlineStr">
         <is>
           <t>Evitar que a pessoa fique doente novamente no futuro sendo não transmissível após o início do tratamento.</t>
         </is>
       </c>
-      <c r="F955" t="inlineStr"/>
-      <c r="G955" t="inlineStr">
+      <c r="F905" t="inlineStr"/>
+      <c r="G905" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H955" t="inlineStr">
+      <c r="H905" t="inlineStr">
         <is>
           <t>Seguir o tratamento completo da tuberculose é crucial para garantir que a bactéria Mycobacterium tuberculosis seja completamente eliminada do organismo e para prevenir o desenvolvimento de resistência bacteriana. A adesão ao tratamento ajuda a evitar recaídas e a propagação de cepas resistentes da bactéria.</t>
         </is>
       </c>
-      <c r="I955" t="inlineStr">
+      <c r="I905" t="inlineStr">
         <is>
           <t>PH10</t>
         </is>
       </c>
-      <c r="J955" t="inlineStr">
+      <c r="J905" t="inlineStr">
         <is>
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K955" t="inlineStr"/>
-      <c r="L955" t="inlineStr">
+      <c r="K905" t="inlineStr"/>
+      <c r="L905" t="inlineStr">
         <is>
           <t>7ano</t>
         </is>
       </c>
     </row>
-    <row r="956">
-      <c r="A956" t="inlineStr">
+    <row r="906">
+      <c r="A906" t="inlineStr">
         <is>
           <t>As bactérias e os vírus são microrganismos que podem causar doenças nos seres humanos, as bacterioses e as viroses. Embora ambos sejam agentes infecciosos, apresentam características e mecanismos de ação distintos. As bactérias são organismos unicelulares procariontes, capazes de se reproduzir por conta própria. Já os vírus são partículas infecciosas menores e mais simples, constituídas por material genético envolto por uma cápsula proteica.
 Qual a diferença entre as doenças causadas por esses microrganismos?</t>
         </is>
       </c>
-      <c r="B956" t="inlineStr">
+      <c r="B906" t="inlineStr">
         <is>
           <t>Ambas são causadas pelos mesmos agentes infecciosos e apresentam sintomas idênticos.</t>
         </is>
       </c>
-      <c r="C956" t="inlineStr">
+      <c r="C906" t="inlineStr">
         <is>
           <t>Viroses podem ser tratadas com antibióticos, enquanto bacterioses requerem apenas repouso e hidratação.</t>
         </is>
       </c>
-      <c r="D956" t="inlineStr">
+      <c r="D906" t="inlineStr">
         <is>
           <t>As bacterioses podem ser tratadas com antibióticos, enquanto viroses não respondem a esse tipo de tratamento.</t>
         </is>
       </c>
-      <c r="E956" t="inlineStr">
+      <c r="E906" t="inlineStr">
         <is>
           <t>As bacterioses, são causadas por organismos maiores e mais complexos, tendo um período de incubação mais longo do que as viroses.</t>
         </is>
       </c>
-      <c r="F956" t="inlineStr"/>
-      <c r="G956" t="inlineStr">
+      <c r="F906" t="inlineStr"/>
+      <c r="G906" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H956" t="inlineStr">
+      <c r="H906" t="inlineStr">
         <is>
           <t>As bacterioses são causadas por bactérias e podem ser tratadas com antibióticos, que são eficazes em eliminar ou inibir o crescimento das bactérias. Viroses, por outro lado, são causadas por vírus e não respondem aos antibióticos. O tratamento das viroses geralmente foca em aliviar os sintomas enquanto o sistema imunológico combate o vírus.</t>
         </is>
       </c>
-      <c r="I956" t="inlineStr">
+      <c r="I906" t="inlineStr">
         <is>
           <t>PH10</t>
         </is>
       </c>
-      <c r="J956" t="inlineStr">
+      <c r="J906" t="inlineStr">
         <is>
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K956" t="inlineStr"/>
-      <c r="L956" t="inlineStr">
+      <c r="K906" t="inlineStr"/>
+      <c r="L906" t="inlineStr">
         <is>
           <t>7ano</t>
         </is>
       </c>
     </row>
-    <row r="957">
-      <c r="A957" t="inlineStr">
+    <row r="907">
+      <c r="A907" t="inlineStr">
         <is>
           <t>De acordo com as características dos vírus que foram descobertas a partir da década de 30, podemos dizer que:</t>
         </is>
       </c>
-      <c r="B957" t="inlineStr">
+      <c r="B907" t="inlineStr">
         <is>
           <t>os vírus são seres acelulares e só conseguem se reproduzir no interior de uma célula viva.</t>
         </is>
       </c>
-      <c r="C957" t="inlineStr">
+      <c r="C907" t="inlineStr">
         <is>
           <t>os vírus são seres que possuem apenas um formato determinado e, por isso, conseguem infectar qualquer ser vivo.</t>
         </is>
       </c>
-      <c r="D957" t="inlineStr">
+      <c r="D907" t="inlineStr">
         <is>
           <t>os vírus possuem metabolismo próprio, pois conseguem sobreviver em qualquer ambiente, mesmo sendo acelulares.</t>
         </is>
       </c>
-      <c r="E957" t="inlineStr">
+      <c r="E907" t="inlineStr">
         <is>
           <t>os vírus são seres microscópicos com apenas uma célula, porém, não possuem capacidade de se reproduzirem sozinhos.</t>
         </is>
       </c>
-      <c r="F957" t="inlineStr"/>
-      <c r="G957" t="inlineStr">
+      <c r="F907" t="inlineStr"/>
+      <c r="G907" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H957" t="inlineStr">
+      <c r="H907" t="inlineStr">
         <is>
           <t>Os vírus não são constituídos por células sendo, portanto, considerados acelulares. A reprodução deles é obrigatoriamente realizada dentro da célula de um outro ser vivo. Também não apresentam metabolismo próprio, precisando utilizar o metabolismo da célula hospedeira.</t>
         </is>
       </c>
-      <c r="I957" t="inlineStr">
+      <c r="I907" t="inlineStr">
         <is>
           <t>PH10</t>
         </is>
       </c>
-      <c r="J957" t="inlineStr">
+      <c r="J907" t="inlineStr">
         <is>
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K957" t="inlineStr"/>
-      <c r="L957" t="inlineStr">
+      <c r="K907" t="inlineStr"/>
+      <c r="L907" t="inlineStr">
         <is>
           <t>7ano</t>
         </is>
       </c>
     </row>
-    <row r="958">
-      <c r="A958" t="inlineStr">
+    <row r="908">
+      <c r="A908" t="inlineStr">
         <is>
           <t>Entre as doenças virais, a dengue continua tendo grande número de casos no Brasil. Como forma de prevenção à doença, a população pode adotar medidas simples como: não deixar água parada e utilizar repelentes. Sobre a transmissão da dengue pode-se afirmar corretamente que:</t>
         </is>
       </c>
-      <c r="B958" t="inlineStr">
+      <c r="B908" t="inlineStr">
         <is>
           <t>o vírus da dengue é transmitido pelo mosquito Anopheles.</t>
         </is>
       </c>
-      <c r="C958" t="inlineStr">
+      <c r="C908" t="inlineStr">
         <is>
           <t>somente o macho do mosquito Aedes aegypti ​causa a dengue.</t>
         </is>
       </c>
-      <c r="D958" t="inlineStr">
+      <c r="D908" t="inlineStr">
         <is>
           <t>o vírus da dengue é transmitido por fêmeas do mosquito Aedes aegypti, portadoras do vírus.</t>
         </is>
       </c>
-      <c r="E958" t="inlineStr">
+      <c r="E908" t="inlineStr">
         <is>
           <t>o vírus causador da dengue é transmitido pela picada de machos e fêmeas do mosquito Aedes aegypti.</t>
         </is>
       </c>
-      <c r="F958" t="inlineStr"/>
-      <c r="G958" t="inlineStr">
+      <c r="F908" t="inlineStr"/>
+      <c r="G908" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H958" t="inlineStr">
+      <c r="H908" t="inlineStr">
         <is>
           <t>A transmissão da dengue ocorre apenas com a picada da fêmea do mosquito Aedes aegypti, portadora do vírus.</t>
         </is>
       </c>
-      <c r="I958" t="inlineStr">
+      <c r="I908" t="inlineStr">
         <is>
           <t>PH10</t>
         </is>
       </c>
-      <c r="J958" t="inlineStr">
+      <c r="J908" t="inlineStr">
         <is>
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K958" t="inlineStr"/>
-      <c r="L958" t="inlineStr">
+      <c r="K908" t="inlineStr"/>
+      <c r="L908" t="inlineStr">
         <is>
           <t>7ano</t>
         </is>
       </c>
     </row>
-    <row r="959">
-      <c r="A959" t="inlineStr">
+    <row r="909">
+      <c r="A909" t="inlineStr">
         <is>
           <t>A leptospirose é uma doença infecciosa onde ocorre uma febre aguda, dor de cabeça e dores pelo corpo, sua penetração sucede através do contato com mucosas, pele com ou sem lesões, mas imersa por longos períodos em água contaminada.
-A leptospirose é uma doença que se alastra em situações de enchente porque, nesses casos, aumenta a:</t>
-        </is>
-      </c>
-      <c r="B959" t="inlineStr">
+ A leptospirose é uma doença que se alastra em situações de enchente porque, nesses casos, aumenta a:</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
         <is>
           <t>presença de caramujos que transmite a doença.</t>
         </is>
       </c>
-      <c r="C959" t="inlineStr">
+      <c r="C909" t="inlineStr">
         <is>
           <t>proliferação de insetos que transmite a doença.</t>
         </is>
       </c>
-      <c r="D959" t="inlineStr">
+      <c r="D909" t="inlineStr">
         <is>
           <t>contaminação do ar pela bactéria que causa a doença.</t>
         </is>
       </c>
-      <c r="E959" t="inlineStr">
+      <c r="E909" t="inlineStr">
         <is>
           <t>contaminação da água pela urina de rato que transmite a doença.</t>
         </is>
       </c>
-      <c r="F959" t="inlineStr"/>
-      <c r="G959" t="inlineStr">
+      <c r="F909" t="inlineStr"/>
+      <c r="G909" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H959" t="inlineStr">
+      <c r="H909" t="inlineStr">
         <is>
           <t>A leptospirose é uma doença de origem bacteriana a qual tem como principal meio de disseminação a urina de rato, potencializada quando acontecem enchentes, pois o animal costuma urinar em esgotos os quais acabam entrando em contato com as pessoas através das enchentes.</t>
         </is>
       </c>
-      <c r="I959" t="inlineStr">
+      <c r="I909" t="inlineStr">
         <is>
           <t>PH10</t>
         </is>
       </c>
-      <c r="J959" t="inlineStr">
+      <c r="J909" t="inlineStr">
         <is>
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K959" t="inlineStr"/>
-      <c r="L959" t="inlineStr">
+      <c r="K909" t="inlineStr"/>
+      <c r="L909" t="inlineStr">
         <is>
           <t>7ano</t>
         </is>
       </c>
     </row>
-    <row r="960">
-      <c r="A960" t="inlineStr">
+    <row r="910">
+      <c r="A910" t="inlineStr">
         <is>
           <t>A imagem abaixo apresenta medidas gerais de prevenção a gripe, doença causada pelo vírus influenza.  
+[img:ph10_cie_09.jpg]
 Disponível em: Influenza (gripe) - Secretaria de Saúde do Distrito Federal. Acesso em: 04 fev. 2025.
 A circulação de vírus respiratórios aumenta em determinadas épocas do ano, exigindo medidas preventivas para reduzir o risco de contaminação. Além dessas medidas, a vacinação é uma importante forma de proteção contra essas doenças.
-Com base nisso, assinale a alternativa que diferencia a vacinação das outras medidas preventivas:</t>
-        </is>
-      </c>
-      <c r="B960" t="inlineStr">
+ Com base nisso, assinale a alternativa que diferencia a vacinação das outras medidas preventivas:</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
         <is>
           <t>A vacinação evita completamente o contato com vírus e bactérias, tornando desnecessárias outras medidas de prevenção.</t>
         </is>
       </c>
-      <c r="C960" t="inlineStr">
+      <c r="C910" t="inlineStr">
         <is>
           <t>A vacinação estimula o sistema imunológico a reconhecer e combater o vírus, reduzindo o risco de formas graves da doença.</t>
         </is>
       </c>
-      <c r="D960" t="inlineStr">
+      <c r="D910" t="inlineStr">
         <is>
           <t>A vacinação age imediatamente após a aplicação, garantindo proteção total contra qualquer tipo de patógeno.</t>
         </is>
       </c>
-      <c r="E960" t="inlineStr">
+      <c r="E910" t="inlineStr">
         <is>
           <t>A vacinação elimina completamente o vírus do ambiente, impedindo que ele se espalhe entre as pessoas.</t>
         </is>
       </c>
-      <c r="F960" t="inlineStr"/>
-      <c r="G960" t="inlineStr">
+      <c r="F910" t="inlineStr"/>
+      <c r="G910" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H960" t="inlineStr">
+      <c r="H910" t="inlineStr">
         <is>
           <t>A vacinação é um método de imunização ativa, que prepara o sistema imunológico para reconhecer e reagir contra vírus e bactérias específicos. Ao receber a vacina, o organismo produz anticorpos e memória imunológica, tornando-se mais eficiente no combate ao agente infeccioso, caso ocorra uma exposição futura. Diferentemente das medidas preventivas gerais, como evitar aglomerações e higienizar as mãos, que reduzem a chance de exposição ao vírus, a vacinação protege o corpo internamente, diminuindo os riscos de infecção severa, hospitalização e até morte.</t>
         </is>
       </c>
-      <c r="I960" t="inlineStr">
+      <c r="I910" t="inlineStr">
         <is>
           <t>PH10</t>
         </is>
       </c>
-      <c r="J960" t="inlineStr">
+      <c r="J910" t="inlineStr">
         <is>
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K960" t="inlineStr">
-        <is>
-          <t>ph10_cie_09.jpg</t>
-        </is>
-      </c>
-      <c r="L960" t="inlineStr">
+      <c r="K910" t="inlineStr"/>
+      <c r="L910" t="inlineStr">
         <is>
           <t>7ano</t>
         </is>
       </c>
     </row>
-    <row r="961">
-      <c r="A961" t="inlineStr">
+    <row r="911">
+      <c r="A911" t="inlineStr">
         <is>
           <t>Uma pesquisa feita pela Universidade Federal de Minas Gerais (UFMG) identificou riscos sociais de longo prazo nas campanhas de desinformação sobre vacinas geradas pela pandemia. O crescimento de movimentos e discursos contra a vacinação, iniciante no Brasil até o início da pandemia de COVID-19, pode ter consequências de longo prazo para campanhas futuras, de acordo com pesquisadores. 
 Disponível em: https://www.em.com.br/app/noticia/bem-viver/2022/03/02/interna_bem_viver,1349446/covid-19-desinformacao-sobre-vacinas-pode-ter-consequencias-de-longo-prazo.shtml.Acesso em  16 nov. de 2023.
 Qual a importância da vacinação?</t>
         </is>
       </c>
-      <c r="B961" t="inlineStr">
+      <c r="B911" t="inlineStr">
         <is>
           <t>A vacinação é o modo mais eficiente para prevenção e erradicação de doenças.</t>
         </is>
       </c>
-      <c r="C961" t="inlineStr">
+      <c r="C911" t="inlineStr">
         <is>
           <t>A vacinação é o modo mais eficiente de se recuperar de uma doença.</t>
         </is>
       </c>
-      <c r="D961" t="inlineStr">
+      <c r="D911" t="inlineStr">
         <is>
           <t>A vacinação é o modo mais eficiente para o tratamento de doenças.</t>
         </is>
       </c>
-      <c r="E961" t="inlineStr">
+      <c r="E911" t="inlineStr">
         <is>
           <t>A vacinação é o modo mais eficiente de se contrair uma doença.</t>
         </is>
       </c>
-      <c r="F961" t="inlineStr"/>
-      <c r="G961" t="inlineStr">
+      <c r="F911" t="inlineStr"/>
+      <c r="G911" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H961" t="inlineStr">
+      <c r="H911" t="inlineStr">
         <is>
           <t>A vacinação é o modo mais eficiente para prevenção e erradicação de doenças. Através dela o sarampo que estava controlado na população, está voltando a ser disseminado, muito também pela diminuição da cobertura vacinal incentivada pelo movimento antivacina.</t>
         </is>
       </c>
-      <c r="I961" t="inlineStr">
+      <c r="I911" t="inlineStr">
         <is>
           <t>PH10</t>
         </is>
       </c>
-      <c r="J961" t="inlineStr">
+      <c r="J911" t="inlineStr">
         <is>
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K961" t="inlineStr"/>
-      <c r="L961" t="inlineStr">
+      <c r="K911" t="inlineStr"/>
+      <c r="L911" t="inlineStr">
         <is>
           <t>7ano</t>
         </is>
       </c>
     </row>
-    <row r="962">
-      <c r="A962" t="inlineStr">
+    <row r="912">
+      <c r="A912" t="inlineStr">
         <is>
           <t>Os movimentos migratórios são fenômenos complexos que envolvem a movimentação de pessoas de um local para outro. Esses movimentos podem ser motivados por diversos fatores, como a busca por melhores condições de vida, oportunidades de emprego, ou até mesmo a fuga de conflitos e perseguições. No Brasil, a migração interna tem sido uma característica marcante, especialmente com o êxodo rural e a urbanização acelerada nas últimas décadas.
 Qual dos seguintes fatores é um exemplo de fator de repulsão populacional?</t>
         </is>
       </c>
-      <c r="B962" t="inlineStr">
+      <c r="B912" t="inlineStr">
         <is>
           <t>Oportunidades de emprego.</t>
         </is>
       </c>
-      <c r="C962" t="inlineStr">
+      <c r="C912" t="inlineStr">
         <is>
           <t>Qualidade de vida.</t>
         </is>
       </c>
-      <c r="D962" t="inlineStr">
+      <c r="D912" t="inlineStr">
         <is>
           <t>Conflitos armados.</t>
         </is>
       </c>
-      <c r="E962" t="inlineStr">
+      <c r="E912" t="inlineStr">
         <is>
           <t>Infraestrutura desenvolvida.</t>
         </is>
       </c>
-      <c r="F962" t="inlineStr"/>
-      <c r="G962" t="inlineStr">
+      <c r="F912" t="inlineStr"/>
+      <c r="G912" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H962" t="inlineStr">
+      <c r="H912" t="inlineStr">
         <is>
           <t>Conflitos armados são um exemplo clássico de fator de repulsão populacional, pois forçam as pessoas a deixarem suas casas em busca de segurança.</t>
         </is>
       </c>
-      <c r="I962" t="inlineStr">
+      <c r="I912" t="inlineStr">
         <is>
           <t>PH10</t>
         </is>
       </c>
-      <c r="J962" t="inlineStr">
+      <c r="J912" t="inlineStr">
         <is>
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K962" t="inlineStr"/>
-      <c r="L962" t="inlineStr">
+      <c r="K912" t="inlineStr"/>
+      <c r="L912" t="inlineStr">
         <is>
           <t>7ano</t>
         </is>
       </c>
     </row>
-    <row r="963">
-      <c r="A963" t="inlineStr">
+    <row r="913">
+      <c r="A913" t="inlineStr">
         <is>
           <t>A migração de retorno é um fenômeno em que indivíduos que anteriormente migraram para outras regiões ou países decidem voltar ao seu local de origem. Esse movimento pode ser motivado por diversos fatores, como a busca por reestabelecer laços familiares e culturais.
 Qual dos seguintes fatores pode ser considerado um motivo para a migração de retorno?</t>
         </is>
       </c>
-      <c r="B963" t="inlineStr">
+      <c r="B913" t="inlineStr">
         <is>
           <t>Aumento da violência na região de origem.</t>
         </is>
       </c>
-      <c r="C963" t="inlineStr">
+      <c r="C913" t="inlineStr">
         <is>
           <t>Melhoria das condições econômicas na região de origem.</t>
         </is>
       </c>
-      <c r="D963" t="inlineStr">
+      <c r="D913" t="inlineStr">
         <is>
           <t>Falta de oportunidades de emprego na região de origem.</t>
         </is>
       </c>
-      <c r="E963" t="inlineStr">
+      <c r="E913" t="inlineStr">
         <is>
           <t>Desastres naturais na região de origem.</t>
         </is>
       </c>
-      <c r="F963" t="inlineStr"/>
-      <c r="G963" t="inlineStr">
+      <c r="F913" t="inlineStr"/>
+      <c r="G913" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H963" t="inlineStr">
+      <c r="H913" t="inlineStr">
         <is>
           <t>A melhoria das condições econômicas na região de origem é um fator que pode motivar a migração de retorno, pois oferece melhores oportunidades para os indivíduos que desejam voltar.</t>
         </is>
       </c>
-      <c r="I963" t="inlineStr">
+      <c r="I913" t="inlineStr">
         <is>
           <t>PH10</t>
         </is>
       </c>
-      <c r="J963" t="inlineStr">
+      <c r="J913" t="inlineStr">
         <is>
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K963" t="inlineStr"/>
-      <c r="L963" t="inlineStr">
+      <c r="K913" t="inlineStr"/>
+      <c r="L913" t="inlineStr">
         <is>
           <t>7ano</t>
         </is>
       </c>
     </row>
-    <row r="964">
-      <c r="A964" t="inlineStr">
+    <row r="914">
+      <c r="A914" t="inlineStr">
         <is>
           <t>Qual das seguintes manchetes exemplifica um caso de xenofobia?</t>
         </is>
       </c>
-      <c r="B964" t="inlineStr">
+      <c r="B914" t="inlineStr">
         <is>
           <t>Formação de professores para o acolhimento de imigrantes e refugiados
 (Gov.Br)</t>
         </is>
       </c>
-      <c r="C964" t="inlineStr">
+      <c r="C914" t="inlineStr">
         <is>
           <t>Milhares de pessoas protestam em Portugal contra imigrantes no país
 (UOL)</t>
         </is>
       </c>
-      <c r="D964" t="inlineStr">
+      <c r="D914" t="inlineStr">
         <is>
           <t>Prefeitura oferece curso de Língua Portuguesa gratuito para imigrantes
 (Prefeitura de São Paulo)</t>
         </is>
       </c>
-      <c r="E964" t="inlineStr">
+      <c r="E914" t="inlineStr">
         <is>
           <t>Brasil acolhe mais de 125 mil migrantes e refugiados venezuelanos por meio da Operação Acolhida
 (Agência GOV)</t>
         </is>
       </c>
-      <c r="F964" t="inlineStr"/>
-      <c r="G964" t="inlineStr">
+      <c r="F914" t="inlineStr"/>
+      <c r="G914" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H964" t="inlineStr">
+      <c r="H914" t="inlineStr">
         <is>
           <t>No caso, o gabarito é enfático ao demonstrar insatisfação de um grupo social direcionada aos imigrantes. Enquanto todas as outras ações estão relacionadas à diferentes formas de acolhimento e integração de de imigrantes na sociedade.</t>
         </is>
       </c>
-      <c r="I964" t="inlineStr">
+      <c r="I914" t="inlineStr">
         <is>
           <t>PH10</t>
         </is>
       </c>
-      <c r="J964" t="inlineStr">
+      <c r="J914" t="inlineStr">
         <is>
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K964" t="inlineStr"/>
-      <c r="L964" t="inlineStr">
+      <c r="K914" t="inlineStr"/>
+      <c r="L914" t="inlineStr">
         <is>
           <t>7ano</t>
         </is>
       </c>
     </row>
-    <row r="965">
-      <c r="A965" t="inlineStr">
+    <row r="915">
+      <c r="A915" t="inlineStr">
         <is>
           <t>O êxodo rural é um fenômeno migratório caracterizado pela saída de pessoas do campo para as cidades. Esse movimento é geralmente motivado pela busca de melhores condições de vida, como acesso a emprego, educação e serviços de saúde.
 No Brasil, o êxodo rural foi intensificado a partir da década de 1960 devido à/ao</t>
         </is>
       </c>
-      <c r="B965" t="inlineStr">
+      <c r="B915" t="inlineStr">
         <is>
           <t>aumento da oferta de empregos no campo.</t>
         </is>
       </c>
-      <c r="C965" t="inlineStr">
+      <c r="C915" t="inlineStr">
         <is>
           <t>mecanização da agricultura.</t>
         </is>
       </c>
-      <c r="D965" t="inlineStr">
+      <c r="D915" t="inlineStr">
         <is>
           <t>melhoria das condições de vida no campo.</t>
         </is>
       </c>
-      <c r="E965" t="inlineStr">
+      <c r="E915" t="inlineStr">
         <is>
           <t>redução da urbanização.</t>
         </is>
       </c>
-      <c r="F965" t="inlineStr"/>
-      <c r="G965" t="inlineStr">
+      <c r="F915" t="inlineStr"/>
+      <c r="G915" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H965" t="inlineStr">
+      <c r="H915" t="inlineStr">
         <is>
           <t>A mecanização da agricultura reduziu a necessidade de mão de obra no campo, levando muitas pessoas a migrarem para as cidades em busca de emprego.</t>
         </is>
       </c>
-      <c r="I965" t="inlineStr">
+      <c r="I915" t="inlineStr">
         <is>
           <t>PH10</t>
         </is>
       </c>
-      <c r="J965" t="inlineStr">
+      <c r="J915" t="inlineStr">
         <is>
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K965" t="inlineStr"/>
-      <c r="L965" t="inlineStr">
+      <c r="K915" t="inlineStr"/>
+      <c r="L915" t="inlineStr">
         <is>
           <t>7ano</t>
         </is>
       </c>
     </row>
-    <row r="966">
-      <c r="A966" t="inlineStr">
+    <row r="916">
+      <c r="A916" t="inlineStr">
         <is>
           <t>A migração internacional envolve a movimentação de pessoas entre diferentes países. Esse tipo de migração pode ser motivado por fatores econômicos, políticos, sociais ou ambientais.
 Qual dos seguintes fatores é um exemplo de fator de atração para migrantes internacionais no Brasil?</t>
         </is>
       </c>
-      <c r="B966" t="inlineStr">
+      <c r="B916" t="inlineStr">
         <is>
           <t>Conflitos armados.</t>
         </is>
       </c>
-      <c r="C966" t="inlineStr">
+      <c r="C916" t="inlineStr">
         <is>
           <t>Desemprego.</t>
         </is>
       </c>
-      <c r="D966" t="inlineStr">
+      <c r="D916" t="inlineStr">
         <is>
           <t>Oportunidades de emprego.</t>
         </is>
       </c>
-      <c r="E966" t="inlineStr">
+      <c r="E916" t="inlineStr">
         <is>
           <t>Perseguições políticas.</t>
         </is>
       </c>
-      <c r="F966" t="inlineStr"/>
-      <c r="G966" t="inlineStr">
+      <c r="F916" t="inlineStr"/>
+      <c r="G916" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H966" t="inlineStr">
+      <c r="H916" t="inlineStr">
         <is>
           <t>Oportunidades de emprego são um fator de atração para migrantes internacionais, pois oferecem melhores condições de vida e estabilidade econômica.</t>
         </is>
       </c>
-      <c r="I966" t="inlineStr">
+      <c r="I916" t="inlineStr">
         <is>
           <t>PH10</t>
         </is>
       </c>
-      <c r="J966" t="inlineStr">
+      <c r="J916" t="inlineStr">
         <is>
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K966" t="inlineStr"/>
-      <c r="L966" t="inlineStr">
+      <c r="K916" t="inlineStr"/>
+      <c r="L916" t="inlineStr">
         <is>
           <t>7ano</t>
         </is>
       </c>
     </row>
-    <row r="967">
-      <c r="A967" t="inlineStr">
+    <row r="917">
+      <c r="A917" t="inlineStr">
         <is>
           <t>A saída da população de um país denomina-se__________________, sendo que esta região pode ser um local de grande _______________________, já a entrada de indivíduos em um país denomina-se________________, e esta região receptora pode ser uma área de forte ____________________.
 Assinale a alternativa que completa corretamente o trecho acima:</t>
         </is>
       </c>
-      <c r="B967" t="inlineStr">
+      <c r="B917" t="inlineStr">
         <is>
           <t>imigração, repulsão demográfica, migração, atração demográfica.</t>
         </is>
       </c>
-      <c r="C967" t="inlineStr">
+      <c r="C917" t="inlineStr">
         <is>
           <t>emigração, atração demográfica, imigração, repulsão demográfica.</t>
         </is>
       </c>
-      <c r="D967" t="inlineStr">
+      <c r="D917" t="inlineStr">
         <is>
           <t>migração, repulsão demográfica, imigração, fluxos migratórios.</t>
         </is>
       </c>
-      <c r="E967" t="inlineStr">
+      <c r="E917" t="inlineStr">
         <is>
           <t>emigração, repulsão demográfica, imigração, atração demográfica.</t>
         </is>
       </c>
-      <c r="F967" t="inlineStr"/>
-      <c r="G967" t="inlineStr">
+      <c r="F917" t="inlineStr"/>
+      <c r="G917" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H967" t="inlineStr">
+      <c r="H917" t="inlineStr">
         <is>
           <t>A emigração representa a saída de indivíduos de seu país de origem, sendo que este pode ter características que o tornem uma área de repulsão demográfica, como altas taxas de desemprego ou catástrofes climáticas. A imigração é a entrada de indivíduos de outros países em um novo, sendo que este pode ter qualidades que o tornem um local de atração demográfica, como oportunidades de emprego.</t>
         </is>
       </c>
-      <c r="I967" t="inlineStr">
+      <c r="I917" t="inlineStr">
         <is>
           <t>PH10</t>
         </is>
       </c>
-      <c r="J967" t="inlineStr">
+      <c r="J917" t="inlineStr">
         <is>
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K967" t="inlineStr"/>
-      <c r="L967" t="inlineStr">
+      <c r="K917" t="inlineStr"/>
+      <c r="L917" t="inlineStr">
         <is>
           <t>7ano</t>
         </is>
       </c>
     </row>
-    <row r="968">
-      <c r="A968" t="inlineStr">
-        <is>
-          <t>Disponível em: https://goo.gl/images/zk5vQV Acesso em: 30 de jul. 2018
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>[img:ph10_geo_07.png]
+Disponível em: https://goo.gl/images/zk5vQV Acesso em: 30 de jul. 2018
 De acordo com o mapa, o maior número de refugiados no Brasil vem da Síria. Qual o principal motivo que levou esse povo a deixar seu país de origem?</t>
         </is>
       </c>
-      <c r="B968" t="inlineStr">
+      <c r="B918" t="inlineStr">
         <is>
           <t>Xenofobia.</t>
         </is>
       </c>
-      <c r="C968" t="inlineStr">
+      <c r="C918" t="inlineStr">
         <is>
           <t>Conflitos militares.</t>
         </is>
       </c>
-      <c r="D968" t="inlineStr">
+      <c r="D918" t="inlineStr">
         <is>
           <t>Desemprego.</t>
         </is>
       </c>
-      <c r="E968" t="inlineStr">
+      <c r="E918" t="inlineStr">
         <is>
           <t>Misoginia.</t>
         </is>
       </c>
-      <c r="F968" t="inlineStr"/>
-      <c r="G968" t="inlineStr">
+      <c r="F918" t="inlineStr"/>
+      <c r="G918" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H968" t="inlineStr">
+      <c r="H918" t="inlineStr">
         <is>
           <t>A guerra civil atualmente em curso na Síria obrigou grande parte de sua população a buscar asilo em outros países, sendo o Brasil um dos destinos dos refugiados sírios..</t>
         </is>
       </c>
-      <c r="I968" t="inlineStr">
+      <c r="I918" t="inlineStr">
         <is>
           <t>PH10</t>
         </is>
       </c>
-      <c r="J968" t="inlineStr">
+      <c r="J918" t="inlineStr">
         <is>
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K968" t="inlineStr">
-        <is>
-          <t>ph10_geo_07.png</t>
-        </is>
-      </c>
-      <c r="L968" t="inlineStr">
+      <c r="K918" t="inlineStr"/>
+      <c r="L918" t="inlineStr">
         <is>
           <t>7ano</t>
         </is>
       </c>
     </row>
-    <row r="969">
-      <c r="A969" t="inlineStr">
+    <row r="919">
+      <c r="A919" t="inlineStr">
         <is>
           <t>Fome, epidemias, desemprego e guerras, são alguns exemplos de fatores que podem causar:</t>
         </is>
       </c>
-      <c r="B969" t="inlineStr">
+      <c r="B919" t="inlineStr">
         <is>
           <t>imigrações.</t>
         </is>
       </c>
-      <c r="C969" t="inlineStr">
+      <c r="C919" t="inlineStr">
         <is>
           <t>atração populacional.</t>
         </is>
       </c>
-      <c r="D969" t="inlineStr">
+      <c r="D919" t="inlineStr">
         <is>
           <t>repulsão populacional.</t>
         </is>
       </c>
-      <c r="E969" t="inlineStr">
+      <c r="E919" t="inlineStr">
         <is>
           <t>êxodo rural.</t>
         </is>
       </c>
-      <c r="F969" t="inlineStr"/>
-      <c r="G969" t="inlineStr">
+      <c r="F919" t="inlineStr"/>
+      <c r="G919" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H969" t="inlineStr">
+      <c r="H919" t="inlineStr">
         <is>
           <t>A repulsão populacional é causada por fatores que põe em risco a qualidade de vida da população.</t>
         </is>
       </c>
-      <c r="I969" t="inlineStr">
+      <c r="I919" t="inlineStr">
         <is>
           <t>PH10</t>
         </is>
       </c>
-      <c r="J969" t="inlineStr">
+      <c r="J919" t="inlineStr">
         <is>
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K969" t="inlineStr"/>
-      <c r="L969" t="inlineStr">
+      <c r="K919" t="inlineStr"/>
+      <c r="L919" t="inlineStr">
         <is>
           <t>7ano</t>
         </is>
       </c>
     </row>
-    <row r="970">
-      <c r="A970" t="inlineStr">
-        <is>
-          <t>Disponível em: https://goo.gl/images/uRx9Ng Acesso em: 30 de jul. 2018
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>[img:ph10_geo_09.jpg]
+Disponível em: https://goo.gl/images/uRx9Ng Acesso em: 30 de jul. 2018
 De acordo com os dados acima, os movimentos migratórios mais intensos aconteciam da região nordeste para a região sudeste do país, principalmente para o estado de São Paulo. Com o passar das décadas esse fluxo foi diminuindo e até mesmo invertido. Como é denominada a volta do migrante a sua terra de origem?</t>
         </is>
       </c>
-      <c r="B970" t="inlineStr">
+      <c r="B920" t="inlineStr">
         <is>
           <t>Êxodo rural.</t>
         </is>
       </c>
-      <c r="C970" t="inlineStr">
+      <c r="C920" t="inlineStr">
         <is>
           <t>Migração de retorno.</t>
         </is>
       </c>
-      <c r="D970" t="inlineStr">
+      <c r="D920" t="inlineStr">
         <is>
           <t>Repulsão demográfica.</t>
         </is>
       </c>
-      <c r="E970" t="inlineStr">
+      <c r="E920" t="inlineStr">
         <is>
           <t>Emigração.</t>
         </is>
       </c>
-      <c r="F970" t="inlineStr"/>
-      <c r="G970" t="inlineStr">
+      <c r="F920" t="inlineStr"/>
+      <c r="G920" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H970" t="inlineStr">
+      <c r="H920" t="inlineStr">
         <is>
           <t>A migração de retorno acontece quando os migrantes regressam a sua terra de origem após ter passado um período em outro lugar.</t>
         </is>
       </c>
-      <c r="I970" t="inlineStr">
+      <c r="I920" t="inlineStr">
         <is>
           <t>PH10</t>
         </is>
       </c>
-      <c r="J970" t="inlineStr">
+      <c r="J920" t="inlineStr">
         <is>
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K970" t="inlineStr">
-        <is>
-          <t>ph10_geo_09.jpg</t>
-        </is>
-      </c>
-      <c r="L970" t="inlineStr">
+      <c r="K920" t="inlineStr"/>
+      <c r="L920" t="inlineStr">
         <is>
           <t>7ano</t>
         </is>
       </c>
     </row>
-    <row r="971">
-      <c r="A971" t="inlineStr">
+    <row r="921">
+      <c r="A921" t="inlineStr">
         <is>
           <t>Na segunda metade do século XX, o Brasil passou por um intenso deslocamento populacional das zonas agrárias para áreas urbanizadas. Esse processo recebe o nome de Êxodo rural. Que fatores contribuíram para esse movimento migratório?</t>
         </is>
       </c>
-      <c r="B971" t="inlineStr">
+      <c r="B921" t="inlineStr">
         <is>
           <t>Mecanização agrícola, industrialização, estrutura fundiária concentradora.</t>
         </is>
       </c>
-      <c r="C971" t="inlineStr">
+      <c r="C921" t="inlineStr">
         <is>
           <t>Urbanização, reforma agrária, marginalização do campo.</t>
         </is>
       </c>
-      <c r="D971" t="inlineStr">
+      <c r="D921" t="inlineStr">
         <is>
           <t>Êxodo urbano, baixa produtividade, revolução industrial brasileira.</t>
         </is>
       </c>
-      <c r="E971" t="inlineStr">
+      <c r="E921" t="inlineStr">
         <is>
           <t>Mecanização da cidade, favelização do campo, reformas trabalhistas.</t>
         </is>
       </c>
-      <c r="F971" t="inlineStr"/>
-      <c r="G971" t="inlineStr">
+      <c r="F921" t="inlineStr"/>
+      <c r="G921" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H971" t="inlineStr">
+      <c r="H921" t="inlineStr">
         <is>
           <t>A mecanização agrícola no campo criou um forte processo de desemprego, já a industrialização nas áreas urbanas gerou empregos e melhores salários. A estrutura fundiária brasileira é extremamente concentradora pois a maior parte das terras pertencem a um grupo seleto da população. Esses fatores tornaram o campo pouco atrativo, causando a repulsa demográfica e por consequência o êxodo rural.</t>
         </is>
       </c>
-      <c r="I971" t="inlineStr">
+      <c r="I921" t="inlineStr">
         <is>
           <t>PH10</t>
         </is>
       </c>
-      <c r="J971" t="inlineStr">
+      <c r="J921" t="inlineStr">
         <is>
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K971" t="inlineStr"/>
-      <c r="L971" t="inlineStr">
+      <c r="K921" t="inlineStr"/>
+      <c r="L921" t="inlineStr">
         <is>
           <t>7ano</t>
         </is>
       </c>
     </row>
-    <row r="972">
-      <c r="A972" t="inlineStr">
+    <row r="922">
+      <c r="A922" t="inlineStr">
         <is>
           <t>Em pleno centro da Espanha, em meio às terras frias e áridas castelhanas, ergue-se uma pequena cidade de 141 quilômetros quadrados.
 Atualmente ela é habitada por cerca de 9 mil pessoas e ostenta o título de "vila muito ilustre, antiga, coroada, leal e muito nobre".
@@ -55532,280 +52472,280 @@
 O Tratado de Tordesilhas foi responsável por</t>
         </is>
       </c>
-      <c r="B972" t="inlineStr">
+      <c r="B922" t="inlineStr">
         <is>
           <t>firmar acordos de comércio entre a Espanha e as Índias.</t>
         </is>
       </c>
-      <c r="C972" t="inlineStr">
+      <c r="C922" t="inlineStr">
         <is>
           <t>separar em definitivo as Igrejas Protestantes e a Igreja Católica.</t>
         </is>
       </c>
-      <c r="D972" t="inlineStr">
+      <c r="D922" t="inlineStr">
         <is>
           <t>dividir as terras e os oceanos além da Europa entre Portugal e Espanha.</t>
         </is>
       </c>
-      <c r="E972" t="inlineStr">
+      <c r="E922" t="inlineStr">
         <is>
           <t>consolidar a independência do Império do Brasil dos domínios portugueses.</t>
         </is>
       </c>
-      <c r="F972" t="inlineStr"/>
-      <c r="G972" t="inlineStr">
+      <c r="F922" t="inlineStr"/>
+      <c r="G922" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H972" t="inlineStr">
+      <c r="H922" t="inlineStr">
         <is>
           <t>O Tratado de Tordesilhas, assinado em 1494, foi responsável por dividir as terras e os oceanos além da Europa entre Portugal e Espanha. Um meridiano a 370 léguas a oeste de Cabo Verde delimitou as áreas de domínio colonial dos dois países, com Portugal ficando com as terras a leste e a Espanha com as terras a oeste.</t>
         </is>
       </c>
-      <c r="I972" t="inlineStr">
+      <c r="I922" t="inlineStr">
         <is>
           <t>PH10</t>
         </is>
       </c>
-      <c r="J972" t="inlineStr">
+      <c r="J922" t="inlineStr">
         <is>
           <t>História</t>
         </is>
       </c>
-      <c r="K972" t="inlineStr"/>
-      <c r="L972" t="inlineStr">
+      <c r="K922" t="inlineStr"/>
+      <c r="L922" t="inlineStr">
         <is>
           <t>7ano</t>
         </is>
       </c>
     </row>
-    <row r="973">
-      <c r="A973" t="inlineStr">
+    <row r="923">
+      <c r="A923" t="inlineStr">
         <is>
           <t>Sua primeira viagem à Índia foi iniciada em 1497 e, no ano seguinte, o navegante português cruzou o cabo da Boa Esperança e alcançou seu destino. Chegar às Índias era importante pois apenas lá os portugueses podiam conseguir especiarias como pimenta e noz-moscada, artigos que, na Europa, valiam tanto quanto prata e ouro. O caminho marítimo para o Oriente aberto por Vasco da Gama ajudaria Portugal a se tornar uma potência mundial.
 Disponível em: https://super.abril.com.br/mundo-estranho/o-que-foram-as-grandes-navegacoes. Acesso em: 13 dez. 2024.
 A viagem de Vasco da Gama foi importante pelo fato de que</t>
         </is>
       </c>
-      <c r="B973" t="inlineStr">
+      <c r="B923" t="inlineStr">
         <is>
           <t>abriu uma nova rota de comércio para a Índia.</t>
         </is>
       </c>
-      <c r="C973" t="inlineStr">
+      <c r="C923" t="inlineStr">
         <is>
           <t>determinou a supremacia espanhola nos mares.</t>
         </is>
       </c>
-      <c r="D973" t="inlineStr">
+      <c r="D923" t="inlineStr">
         <is>
           <t>representou a chegada dos portugueses ao Novo Mundo.</t>
         </is>
       </c>
-      <c r="E973" t="inlineStr">
+      <c r="E923" t="inlineStr">
         <is>
           <t>tornou a colonização do continente americano desnecessária.</t>
         </is>
       </c>
-      <c r="F973" t="inlineStr"/>
-      <c r="G973" t="inlineStr">
+      <c r="F923" t="inlineStr"/>
+      <c r="G923" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H973" t="inlineStr">
+      <c r="H923" t="inlineStr">
         <is>
           <t>A viagem de Vasco da Gama foi importante porque abriu uma nova rota marítima para a Índia, através do Cabo da Boa Esperança, permitindo que os portugueses estabelecessem um comércio direto de especiarias como pimenta e noz-moscada, que eram extremamente valiosas na Europa.</t>
         </is>
       </c>
-      <c r="I973" t="inlineStr">
+      <c r="I923" t="inlineStr">
         <is>
           <t>PH10</t>
         </is>
       </c>
-      <c r="J973" t="inlineStr">
+      <c r="J923" t="inlineStr">
         <is>
           <t>História</t>
         </is>
       </c>
-      <c r="K973" t="inlineStr"/>
-      <c r="L973" t="inlineStr">
+      <c r="K923" t="inlineStr"/>
+      <c r="L923" t="inlineStr">
         <is>
           <t>7ano</t>
         </is>
       </c>
     </row>
-    <row r="974">
-      <c r="A974" t="inlineStr">
+    <row r="924">
+      <c r="A924" t="inlineStr">
         <is>
           <t>Bartolomeu Dias liderou a primeira expedição a atravessar, em 1488, o cabo das Tormentas, mais tarde rebatizado de cabo da Boa Esperança (no extremo sul da África). O curioso é que Bartolomeu Dias não percebeu o feito, pois passou pelo cabo durante uma forte tempestade. Poderia ter chegado à Índia, mas um motim da tripulação o obrigou a retornar a Portugal.
 Disponível em: https://super.abril.com.br/mundo-estranho/o-que-foram-as-grandes-navegacoes. Acesso em: 13 dez. 2024. (Adaptado).
 A expedição de Bartolomeu Dias representou a(o)</t>
         </is>
       </c>
-      <c r="B974" t="inlineStr">
+      <c r="B924" t="inlineStr">
         <is>
           <t>fracasso dos objetivos expansionistas de Portugal.</t>
         </is>
       </c>
-      <c r="C974" t="inlineStr">
+      <c r="C924" t="inlineStr">
         <is>
           <t>abandono por parte de Portugal de tentar chegar à Índia.</t>
         </is>
       </c>
-      <c r="D974" t="inlineStr">
+      <c r="D924" t="inlineStr">
         <is>
           <t>união dos países europeus no projeto de expansão marítima.</t>
         </is>
       </c>
-      <c r="E974" t="inlineStr">
+      <c r="E924" t="inlineStr">
         <is>
           <t>confirmação da viabilidade de uma rota marítima para a Índia.</t>
         </is>
       </c>
-      <c r="F974" t="inlineStr"/>
-      <c r="G974" t="inlineStr">
+      <c r="F924" t="inlineStr"/>
+      <c r="G924" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H974" t="inlineStr">
+      <c r="H924" t="inlineStr">
         <is>
           <t>A expedição de Bartolomeu Dias, ao atravessar o Cabo da Boa Esperança, confirmou que era possível navegar ao redor do sul da África, abrindo a perspectiva de uma rota marítima para a Índia, ainda que Dias não tenha completado a viagem até lá.</t>
         </is>
       </c>
-      <c r="I974" t="inlineStr">
+      <c r="I924" t="inlineStr">
         <is>
           <t>PH10</t>
         </is>
       </c>
-      <c r="J974" t="inlineStr">
+      <c r="J924" t="inlineStr">
         <is>
           <t>História</t>
         </is>
       </c>
-      <c r="K974" t="inlineStr"/>
-      <c r="L974" t="inlineStr">
+      <c r="K924" t="inlineStr"/>
+      <c r="L924" t="inlineStr">
         <is>
           <t>7ano</t>
         </is>
       </c>
     </row>
-    <row r="975">
-      <c r="A975" t="inlineStr">
+    <row r="925">
+      <c r="A925" t="inlineStr">
         <is>
           <t>Foram os mouros que aperfeiçoaram o astrolábio, instrumento de origem grega que permite a orientação em alto-mar pela observação de estrelas. Sua ciência náutica teve grande influência sobre a Escola de Sagres, em Portugal, de onde saíram os oficiais e marinheiros das navegações da Era dos Descobrimentos
 Disponível em: https://super.abril.com.br/mundo-estranho/como-foi-a-ocupacao-moura-da-peninsula-iberica. Acesso em: 13 dez. 2024.
 O texto deixa evidente a(o)</t>
         </is>
       </c>
-      <c r="B975" t="inlineStr">
+      <c r="B925" t="inlineStr">
         <is>
           <t>atraso tecnológico português no contexto das Grandes Navegações.</t>
         </is>
       </c>
-      <c r="C975" t="inlineStr">
+      <c r="C925" t="inlineStr">
         <is>
           <t>acaso por trás da chegada dos portugueses ao continente americano.</t>
         </is>
       </c>
-      <c r="D975" t="inlineStr">
+      <c r="D925" t="inlineStr">
         <is>
           <t>influência dos avanços tecnológicos muçulmanos no pioneirismo português.</t>
         </is>
       </c>
-      <c r="E975" t="inlineStr">
+      <c r="E925" t="inlineStr">
         <is>
           <t>parceria firmada entre a Espanha e Portugal para a realização das expedições.</t>
         </is>
       </c>
-      <c r="F975" t="inlineStr"/>
-      <c r="G975" t="inlineStr">
+      <c r="F925" t="inlineStr"/>
+      <c r="G925" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H975" t="inlineStr">
+      <c r="H925" t="inlineStr">
         <is>
           <t>O texto menciona que os mouros aperfeiçoaram o astrolábio e que sua ciência náutica teve grande influência sobre a Escola de Sagres em Portugal. Essa influência tecnológica foi crucial para o sucesso dos portugueses nas navegações da Era dos Descobrimentos.</t>
         </is>
       </c>
-      <c r="I975" t="inlineStr">
+      <c r="I925" t="inlineStr">
         <is>
           <t>PH10</t>
         </is>
       </c>
-      <c r="J975" t="inlineStr">
+      <c r="J925" t="inlineStr">
         <is>
           <t>História</t>
         </is>
       </c>
-      <c r="K975" t="inlineStr"/>
-      <c r="L975" t="inlineStr">
+      <c r="K925" t="inlineStr"/>
+      <c r="L925" t="inlineStr">
         <is>
           <t>7ano</t>
         </is>
       </c>
     </row>
-    <row r="976">
-      <c r="A976" t="inlineStr">
+    <row r="926">
+      <c r="A926" t="inlineStr">
         <is>
           <t>O navegador genovês Cristóvão Colombo (1451-1506) nasceu em uma família pobre e começou a navegar cedo. Comandou um navio pela primeira vez em 1473, aos 22 anos. Ao retornar de sua primeira viagem continental, em 1493, recebe o título de “Vice-Rei e governador das Terras Firmes e Ilhas Descobertas e por Descobrir”. Apesar disso, morreu pobre e esquecido. Seu diário só foi recuperado por Fernando, seu filho, após a sua morte.
 Disponível em: https://super.abril.com.br/ciencia/diarios-da-descoberta-da-america. Acesso em: 13 dez. 2024.
 A importância histórica de Cristóvão Colombo se encontra no fato de que ele</t>
         </is>
       </c>
-      <c r="B976" t="inlineStr">
+      <c r="B926" t="inlineStr">
         <is>
           <t>comandou a primeira expedição europeia a chegar na América.</t>
         </is>
       </c>
-      <c r="C976" t="inlineStr">
+      <c r="C926" t="inlineStr">
         <is>
           <t>foi o primeiro europeu a navegar a pelo Cabo da Boa Esperança.</t>
         </is>
       </c>
-      <c r="D976" t="inlineStr">
+      <c r="D926" t="inlineStr">
         <is>
           <t>liderou os cristãos nas guerras de Reconquista contra os mouros.</t>
         </is>
       </c>
-      <c r="E976" t="inlineStr">
+      <c r="E926" t="inlineStr">
         <is>
           <t>protagonizou o surgimento das igrejas protestantes no século XVI.</t>
         </is>
       </c>
-      <c r="F976" t="inlineStr"/>
-      <c r="G976" t="inlineStr">
+      <c r="F926" t="inlineStr"/>
+      <c r="G926" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H976" t="inlineStr">
+      <c r="H926" t="inlineStr">
         <is>
           <t>Cristóvão Colombo é historicamente famoso por comandar a primeira expedição europeia reconhecida a chegar na América em 1492, financiada pelos reis católicos da Espanha. Sua viagem marcou o início do contato sustentado entre a Europa e as Américas.</t>
         </is>
       </c>
-      <c r="I976" t="inlineStr">
+      <c r="I926" t="inlineStr">
         <is>
           <t>PH10</t>
         </is>
       </c>
-      <c r="J976" t="inlineStr">
+      <c r="J926" t="inlineStr">
         <is>
           <t>História</t>
         </is>
       </c>
-      <c r="K976" t="inlineStr"/>
-      <c r="L976" t="inlineStr">
+      <c r="K926" t="inlineStr"/>
+      <c r="L926" t="inlineStr">
         <is>
           <t>7ano</t>
         </is>
       </c>
     </row>
-    <row r="977">
-      <c r="A977" t="inlineStr">
+    <row r="927">
+      <c r="A927" t="inlineStr">
         <is>
           <t>E assim, não tendo a quem vencer na terra, 
 Vai cometer as ondas do Oceano 
@@ -55817,231 +52757,225 @@
 Luís de Camões foi um dos maiores nome da literatura renascentista portuguesa. A temática do soneto de Camões apresentada acima se relaciona, na história de Portugal, com a/as</t>
         </is>
       </c>
-      <c r="B977" t="inlineStr">
+      <c r="B927" t="inlineStr">
         <is>
           <t>conquista do continente africano através das Cruzadas.</t>
         </is>
       </c>
-      <c r="C977" t="inlineStr">
+      <c r="C927" t="inlineStr">
         <is>
           <t>à conquista de Ceuta como um marco da supremacia de Portugal e abertura para a expansão marítima.</t>
         </is>
       </c>
-      <c r="D977" t="inlineStr">
+      <c r="D927" t="inlineStr">
         <is>
           <t>guerras de Reconquista contra os mouros do Norte da África.</t>
         </is>
       </c>
-      <c r="E977" t="inlineStr">
+      <c r="E927" t="inlineStr">
         <is>
           <t>expansão pelo continente europeu para derrubar os monarcas rivais.</t>
         </is>
       </c>
-      <c r="F977" t="inlineStr"/>
-      <c r="G977" t="inlineStr">
+      <c r="F927" t="inlineStr"/>
+      <c r="G927" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H977" t="inlineStr">
+      <c r="H927" t="inlineStr">
         <is>
           <t>Camões foi um reconhecido escritor português que em diversos sonetos tratou temas relativos à realidade em que vivia. Um traço marcante de Portugal no século XV foi a expansão marítima, resultado, entre outros fatores, da centralização política na figura do rei.</t>
         </is>
       </c>
-      <c r="I977" t="inlineStr">
+      <c r="I927" t="inlineStr">
         <is>
           <t>PH10</t>
         </is>
       </c>
-      <c r="J977" t="inlineStr">
+      <c r="J927" t="inlineStr">
         <is>
           <t>História</t>
         </is>
       </c>
-      <c r="K977" t="inlineStr"/>
-      <c r="L977" t="inlineStr">
+      <c r="K927" t="inlineStr"/>
+      <c r="L927" t="inlineStr">
         <is>
           <t>7ano</t>
         </is>
       </c>
     </row>
-    <row r="978">
-      <c r="A978" t="inlineStr">
+    <row r="928">
+      <c r="A928" t="inlineStr">
         <is>
           <t>Observe o mapa a seguir:
+[img:ph10_his_07.png]   
 Instituto Geográfico Nacional, Google, Geo-Basis-DE (BKG), 2009. Disponível em: https://www.google.com.br/maps/. Acesso em: 08 maio 2020.
 O mapa acima nos permite entender um fator que explica o pioneirismo de Portugal nas Grandes Navegações, que foi o(a)</t>
         </is>
       </c>
-      <c r="B978" t="inlineStr">
+      <c r="B928" t="inlineStr">
         <is>
           <t>fácil acesso ao Oceano Atlântico.</t>
         </is>
       </c>
-      <c r="C978" t="inlineStr">
+      <c r="C928" t="inlineStr">
         <is>
           <t>fortalecimento da nobreza feudal.</t>
         </is>
       </c>
-      <c r="D978" t="inlineStr">
+      <c r="D928" t="inlineStr">
         <is>
           <t>enfraquecimento da autoridade real.</t>
         </is>
       </c>
-      <c r="E978" t="inlineStr">
+      <c r="E928" t="inlineStr">
         <is>
           <t>concorrência da monarquia espanhola.</t>
         </is>
       </c>
-      <c r="F978" t="inlineStr"/>
-      <c r="G978" t="inlineStr">
+      <c r="F928" t="inlineStr"/>
+      <c r="G928" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H978" t="inlineStr">
+      <c r="H928" t="inlineStr">
         <is>
           <t>A mapa apresenta como Portugal se encontrava com acesso direito ao Oceano Atlântico. Esse fator geográfico, somado com a experiência prévia que os portugueses tinham com as atividades marítimas, facilitaram o seu lançamento ultramarino.</t>
         </is>
       </c>
-      <c r="I978" t="inlineStr">
+      <c r="I928" t="inlineStr">
         <is>
           <t>PH10</t>
         </is>
       </c>
-      <c r="J978" t="inlineStr">
+      <c r="J928" t="inlineStr">
         <is>
           <t>História</t>
         </is>
       </c>
-      <c r="K978" t="inlineStr">
-        <is>
-          <t>ph10_his_07.png</t>
-        </is>
-      </c>
-      <c r="L978" t="inlineStr">
+      <c r="K928" t="inlineStr"/>
+      <c r="L928" t="inlineStr">
         <is>
           <t>7ano</t>
         </is>
       </c>
     </row>
-    <row r="979">
-      <c r="A979" t="inlineStr">
+    <row r="929">
+      <c r="A929" t="inlineStr">
         <is>
           <t>A representação a seguir foi feita por um italiano ao imaginar os seres míticos que poderiam habitar as regiões do Novo Mundo.
+[img:ph10_his_08.png]
 Sobre a relação entre as crenças em seres como os da imagem e a expansão marítima, é correto afirmar que os viajantes do século XV</t>
         </is>
       </c>
-      <c r="B979" t="inlineStr">
+      <c r="B929" t="inlineStr">
         <is>
           <t>exploraram os mares sem receio, pois não tinham a tradição de acreditar em seres míticos, como sereias.</t>
         </is>
       </c>
-      <c r="C979" t="inlineStr">
+      <c r="C929" t="inlineStr">
         <is>
           <t>interromperam suas rotas ao descobrirem espécies que confirmavam seus medos de animais fantásticos no mar.</t>
         </is>
       </c>
-      <c r="D979" t="inlineStr">
+      <c r="D929" t="inlineStr">
         <is>
           <t>acompanharam o teocentrismo que se fortalecia na Europa e se recusaram a viajar para regiões que tivessem sereias.</t>
         </is>
       </c>
-      <c r="E979" t="inlineStr">
+      <c r="E929" t="inlineStr">
         <is>
           <t>superaram receios sobre esses seres conforme inovações técnicas desvendavam mitos como monstros e precipícios no fim do oceano.</t>
         </is>
       </c>
-      <c r="F979" t="inlineStr"/>
-      <c r="G979" t="inlineStr">
+      <c r="F929" t="inlineStr"/>
+      <c r="G929" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H979" t="inlineStr">
+      <c r="H929" t="inlineStr">
         <is>
           <t>Mitos sobre perigos de se viajar pelo oceano, como seres fantásticos e precipícios ao fim do mar, eram crenças que amedrontavam a população europeia. No entanto, conforme a mentalidade do continente tornou-se mais racionalista e as inovações técnicas permitiram que as viagens se tornassem mais seguras, essas crenças se desmistificaram e a exploração dos oceanos se popularizou.</t>
         </is>
       </c>
-      <c r="I979" t="inlineStr">
+      <c r="I929" t="inlineStr">
         <is>
           <t>PH10</t>
         </is>
       </c>
-      <c r="J979" t="inlineStr">
+      <c r="J929" t="inlineStr">
         <is>
           <t>História</t>
         </is>
       </c>
-      <c r="K979" t="inlineStr">
-        <is>
-          <t>ph10_his_08.png</t>
-        </is>
-      </c>
-      <c r="L979" t="inlineStr">
+      <c r="K929" t="inlineStr"/>
+      <c r="L929" t="inlineStr">
         <is>
           <t>7ano</t>
         </is>
       </c>
     </row>
-    <row r="980">
-      <c r="A980" t="inlineStr">
+    <row r="930">
+      <c r="A930" t="inlineStr">
         <is>
           <t>As zonas costeiras eram abastecidas por peixe fresco, o que não sucedia nas zonas interiores – onde algum ainda chegava às escassas elites –, apesar de se recorrer ao peixe de água doce. Havia que o importar, como sucedia com a sardinha, abundante em toda a costa, mais acessível e transportada salgada, mas que não chegava para as necessidades da procura. Há que ver, também, que o bacalhau, uma vez curado adequadamente, teria uma maior capacidade de conservação. Outros pequenos peixes, [...] ou o polvo seco [...] não tiveram uma difusão comparável à escala do país. O bacalhau tornou-se uma mercadoria importante, muitos séculos antes de a ciência moderna o valorizar como alimento excecional devido à sua carne branca e firme, quase isenta de gordura, que quando seca é um concentrado de proteínas.
 SOBRAL, José Manuel; RODRIGUES, Patrícia. O fiel amigo: o bacalhau e a identidade portuguesa. Etnográfica, Lisboa, v. 17, n. 3, p. 621. Disponível em: http://www.scielo.mec.pt/scielo.php?script=sci_arttext&amp;pid=S0873-65612013000300010&amp;lang=pt. Acesso em: 08 maio 2020.
 A proximidade da culinária portuguesa com o consumo de peixes expõe um fator para o pioneirismo português no processo de expansão marítima, que foi/foram</t>
         </is>
       </c>
-      <c r="B980" t="inlineStr">
+      <c r="B930" t="inlineStr">
         <is>
           <t>o controle de todo o litoral europeu.</t>
         </is>
       </c>
-      <c r="C980" t="inlineStr">
+      <c r="C930" t="inlineStr">
         <is>
           <t>as alianças feitas com os povos do Novo Mundo.</t>
         </is>
       </c>
-      <c r="D980" t="inlineStr">
+      <c r="D930" t="inlineStr">
         <is>
           <t>a experiência com atividades marítimas, como a pesca.</t>
         </is>
       </c>
-      <c r="E980" t="inlineStr">
+      <c r="E930" t="inlineStr">
         <is>
           <t>o princípio mercantilista que via nos pescados a fonte de riquezas.</t>
         </is>
       </c>
-      <c r="F980" t="inlineStr"/>
-      <c r="G980" t="inlineStr">
+      <c r="F930" t="inlineStr"/>
+      <c r="G930" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H980" t="inlineStr">
+      <c r="H930" t="inlineStr">
         <is>
           <t>A prática da pesca demonstra a experiência que os portugueses tinham com as atividades marítimas. Isso lhes deu vantagem para realizar as Grandes Navegações, uma vez que já sabiam como conseguir alimento em alto mar.</t>
         </is>
       </c>
-      <c r="I980" t="inlineStr">
+      <c r="I930" t="inlineStr">
         <is>
           <t>PH10</t>
         </is>
       </c>
-      <c r="J980" t="inlineStr">
+      <c r="J930" t="inlineStr">
         <is>
           <t>História</t>
         </is>
       </c>
-      <c r="K980" t="inlineStr"/>
-      <c r="L980" t="inlineStr">
+      <c r="K930" t="inlineStr"/>
+      <c r="L930" t="inlineStr">
         <is>
           <t>7ano</t>
         </is>
       </c>
     </row>
-    <row r="981">
-      <c r="A981" t="inlineStr">
+    <row r="931">
+      <c r="A931" t="inlineStr">
         <is>
           <t>Além da experiência [...] dos navegantes, foram as velas latinas idealizadas pelos sábios da Escola de Sagres que ajudaram os aventureiros a atravessar o mar [...]. Os astrônomos e matemáticos da Escola de Sagres desenvolveram tabelas com a declinação dos astros, bem como eficientes instrumentos de navegação, como o astrolábio e a balestilha, usados para medir a posição dos astros e determinar a posição da embarcação.
 FILGUEIRAS, O. Vigia de ventos e ondas. Revista Fapesp, ed. 62, mar. 2000. (Adaptado).
@@ -56049,56 +52983,56 @@
 O texto trata da controversa Escola de Sagres que teria sido fundada por D. Henrique. De acordo com o texto e seus conhecimentos, a Escola de Sagres representou um/a</t>
         </is>
       </c>
-      <c r="B981" t="inlineStr">
+      <c r="B931" t="inlineStr">
         <is>
           <t>grande mercado de pescados portugueses.</t>
         </is>
       </c>
-      <c r="C981" t="inlineStr">
+      <c r="C931" t="inlineStr">
         <is>
           <t>ponto de encontro de navegadores lusitanos.</t>
         </is>
       </c>
-      <c r="D981" t="inlineStr">
+      <c r="D931" t="inlineStr">
         <is>
           <t>universidade onde o principal curso era a navegação.</t>
         </is>
       </c>
-      <c r="E981" t="inlineStr">
+      <c r="E931" t="inlineStr">
         <is>
           <t>movimento criado por jesuítas que combatiam a navegação.</t>
         </is>
       </c>
-      <c r="F981" t="inlineStr"/>
-      <c r="G981" t="inlineStr">
+      <c r="F931" t="inlineStr"/>
+      <c r="G931" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H981" t="inlineStr">
+      <c r="H931" t="inlineStr">
         <is>
           <t>Não existem evidências de que de fato tenha existido fisicamente uma Escola de Sagres para navegadores, porém é sabido que uma vila foi construída com o intuito de dar apoio aos navegadores portugueses e se constituiu como um local de troca de experiências e conhecimentos entre os frequentadores.</t>
         </is>
       </c>
-      <c r="I981" t="inlineStr">
+      <c r="I931" t="inlineStr">
         <is>
           <t>PH10</t>
         </is>
       </c>
-      <c r="J981" t="inlineStr">
+      <c r="J931" t="inlineStr">
         <is>
           <t>História</t>
         </is>
       </c>
-      <c r="K981" t="inlineStr"/>
-      <c r="L981" t="inlineStr">
+      <c r="K931" t="inlineStr"/>
+      <c r="L931" t="inlineStr">
         <is>
           <t>7ano</t>
         </is>
       </c>
     </row>
-    <row r="982">
-      <c r="A982" t="inlineStr">
+    <row r="932">
+      <c r="A932" t="inlineStr">
         <is>
           <t>Pesquisadores japoneses desenvolvem plástico que se desfaz no oceano
 Pesquisadores do Centro de Ciência de Materiais Emergentes (Cems, na sigla em inglês), do instituto japonês Riken, desenvolveram um novo plástico biodegradável, que, além de ser durável e reciclável, decompõe-se quando em contato com a água do mar.
@@ -56106,112 +53040,112 @@
 O pronome relativo “que” possui algumas variações. Por qual forma desse pronome o termo em destaque pode ser substituído?</t>
         </is>
       </c>
-      <c r="B982" t="inlineStr">
+      <c r="B932" t="inlineStr">
         <is>
           <t>O qual.</t>
         </is>
       </c>
-      <c r="C982" t="inlineStr">
+      <c r="C932" t="inlineStr">
         <is>
           <t>Em que.</t>
         </is>
       </c>
-      <c r="D982" t="inlineStr">
+      <c r="D932" t="inlineStr">
         <is>
           <t>No qual.</t>
         </is>
       </c>
-      <c r="E982" t="inlineStr">
+      <c r="E932" t="inlineStr">
         <is>
           <t>Pelo qual.</t>
         </is>
       </c>
-      <c r="F982" t="inlineStr"/>
-      <c r="G982" t="inlineStr">
+      <c r="F932" t="inlineStr"/>
+      <c r="G932" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H982" t="inlineStr">
+      <c r="H932" t="inlineStr">
         <is>
           <t>O pronome relativo "o qual" pode substituir "que" na frase sem alterar o sentido, pois ambos se referem ao "plástico biodegradável" mencionado anteriormente. Essa substituição mantém a clareza e coesão do texto, sendo uma variação adequada do pronome relativo "que".</t>
         </is>
       </c>
-      <c r="I982" t="inlineStr">
+      <c r="I932" t="inlineStr">
         <is>
           <t>PH10</t>
         </is>
       </c>
-      <c r="J982" t="inlineStr">
+      <c r="J932" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="K982" t="inlineStr"/>
-      <c r="L982" t="inlineStr">
+      <c r="K932" t="inlineStr"/>
+      <c r="L932" t="inlineStr">
         <is>
           <t>7ano</t>
         </is>
       </c>
     </row>
-    <row r="983">
-      <c r="A983" t="inlineStr">
+    <row r="933">
+      <c r="A933" t="inlineStr">
         <is>
           <t>Ao fundo, por trás do balcão, estava sentada uma mulher, cujo rosto amarelo e bexiguento não se destacava logo, à primeira vista; mas logo que se destacava era um espetáculo curioso.
 ASSIS, Machado de. Obra Completa. Disponível em: https://www.dominiopublico.gov.br/download/texto/bv000003.pdf. Acesso em: 19 dez. 2024.
 No excerto acima, o pronome relativo "cujo" estabelece uma relação entre as palavras</t>
         </is>
       </c>
-      <c r="B983" t="inlineStr">
+      <c r="B933" t="inlineStr">
         <is>
           <t>"mulher” e “bexiguento”.</t>
         </is>
       </c>
-      <c r="C983" t="inlineStr">
+      <c r="C933" t="inlineStr">
         <is>
           <t>“mulher” e “amarelo”.</t>
         </is>
       </c>
-      <c r="D983" t="inlineStr">
+      <c r="D933" t="inlineStr">
         <is>
           <t>“mulher” e “balcão”.</t>
         </is>
       </c>
-      <c r="E983" t="inlineStr">
+      <c r="E933" t="inlineStr">
         <is>
           <t>“mulher” e “rosto”.</t>
         </is>
       </c>
-      <c r="F983" t="inlineStr"/>
-      <c r="G983" t="inlineStr">
+      <c r="F933" t="inlineStr"/>
+      <c r="G933" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H983" t="inlineStr">
+      <c r="H933" t="inlineStr">
         <is>
           <t>O pronome relativo "cujo" é utilizado para indicar uma relação de posse entre dois substantivos. No excerto, "cujo" estabelece essa relação entre "mulher" e "rosto", indicando que o rosto pertence à mulher. O uso de "cujo" é apropriado para mostrar que o rosto, descrito como "amarelo e bexiguento", é uma característica da mulher sentada por trás do balcão.</t>
         </is>
       </c>
-      <c r="I983" t="inlineStr">
+      <c r="I933" t="inlineStr">
         <is>
           <t>PH10</t>
         </is>
       </c>
-      <c r="J983" t="inlineStr">
+      <c r="J933" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="K983" t="inlineStr"/>
-      <c r="L983" t="inlineStr">
+      <c r="K933" t="inlineStr"/>
+      <c r="L933" t="inlineStr">
         <is>
           <t>7ano</t>
         </is>
       </c>
     </row>
-    <row r="984">
-      <c r="A984" t="inlineStr">
+    <row r="934">
+      <c r="A934" t="inlineStr">
         <is>
           <t>Canção do Exílio
 Minha terra tem palmeiras,
@@ -56229,56 +53163,56 @@
 No excerto acima, o pronome relativo "onde" substitui qual termo?</t>
         </is>
       </c>
-      <c r="B984" t="inlineStr">
+      <c r="B934" t="inlineStr">
         <is>
           <t>Aves.</t>
         </is>
       </c>
-      <c r="C984" t="inlineStr">
+      <c r="C934" t="inlineStr">
         <is>
           <t>Terra.</t>
         </is>
       </c>
-      <c r="D984" t="inlineStr">
+      <c r="D934" t="inlineStr">
         <is>
           <t>Sabiá.</t>
         </is>
       </c>
-      <c r="E984" t="inlineStr">
+      <c r="E934" t="inlineStr">
         <is>
           <t>Palmeiras.</t>
         </is>
       </c>
-      <c r="F984" t="inlineStr"/>
-      <c r="G984" t="inlineStr">
+      <c r="F934" t="inlineStr"/>
+      <c r="G934" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H984" t="inlineStr">
+      <c r="H934" t="inlineStr">
         <is>
           <t>O pronome “onde” indica o local em que o sabiá canta. Além disso, é preciso atentar-se à interpretação do poema e depreender que o sabiá está cantando especificamente na palmeira.</t>
         </is>
       </c>
-      <c r="I984" t="inlineStr">
+      <c r="I934" t="inlineStr">
         <is>
           <t>PH10</t>
         </is>
       </c>
-      <c r="J984" t="inlineStr">
+      <c r="J934" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="K984" t="inlineStr"/>
-      <c r="L984" t="inlineStr">
+      <c r="K934" t="inlineStr"/>
+      <c r="L934" t="inlineStr">
         <is>
           <t>7ano</t>
         </is>
       </c>
     </row>
-    <row r="985">
-      <c r="A985" t="inlineStr">
+    <row r="935">
+      <c r="A935" t="inlineStr">
         <is>
           <t>Não havia remédio senão ir.
 — Diga-lhe que vou.
@@ -56288,56 +53222,56 @@
 No excerto acima são usados os pronomes relativos "aonde" e "onde", que muitas vezes causam confusão na língua falada. Qual é a explicação para o uso desses pronomes, de acordo com a norma culta?</t>
         </is>
       </c>
-      <c r="B985" t="inlineStr">
+      <c r="B935" t="inlineStr">
         <is>
           <t>"Aonde" e "onde" são iguais, por isso aparecem no mesmo excerto.</t>
         </is>
       </c>
-      <c r="C985" t="inlineStr">
+      <c r="C935" t="inlineStr">
         <is>
           <t>"Aonde" é uma palavra mais formal, enquanto "onde" é usada no dia a dia.</t>
         </is>
       </c>
-      <c r="D985" t="inlineStr">
+      <c r="D935" t="inlineStr">
         <is>
           <t>"Aonde" é usado para começar uma pergunta, enquanto "onde" é só para respostas.</t>
         </is>
       </c>
-      <c r="E985" t="inlineStr">
+      <c r="E935" t="inlineStr">
         <is>
           <t>"Aonde" é usado para indicar movimento para algum lugar, o pronome "onde", por sua vez, é usado para mostrar que algo está em um lugar.</t>
         </is>
       </c>
-      <c r="F985" t="inlineStr"/>
-      <c r="G985" t="inlineStr">
+      <c r="F935" t="inlineStr"/>
+      <c r="G935" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H985" t="inlineStr">
+      <c r="H935" t="inlineStr">
         <is>
           <t>"Aonde" é usado para indicar movimento em direção a um lugar, já "onde" mostra permanência em um lugar.</t>
         </is>
       </c>
-      <c r="I985" t="inlineStr">
+      <c r="I935" t="inlineStr">
         <is>
           <t>PH10</t>
         </is>
       </c>
-      <c r="J985" t="inlineStr">
+      <c r="J935" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="K985" t="inlineStr"/>
-      <c r="L985" t="inlineStr">
+      <c r="K935" t="inlineStr"/>
+      <c r="L935" t="inlineStr">
         <is>
           <t>7ano</t>
         </is>
       </c>
     </row>
-    <row r="986">
-      <c r="A986" t="inlineStr">
+    <row r="936">
+      <c r="A936" t="inlineStr">
         <is>
           <t>COMO O REMÉDIO CHEGA AONDE DÓI?
 O nosso corpo é totalmente coberto por vasos sanguíneos. Da mesma forma que se espalham pela nossa pele (basta um pequeno corte para vermos o sangue e constatarmos que eles estão ali!), eles também estão nos nossos demais órgãos. Assim, quando tomamos um medicamento, ele vai para a corrente sanguínea e percorre os órgãos do nosso corpo, através dos vasos sanguíneos, em busca do endereço da dor, ou seja, do lugar da nossa queixa.
@@ -56350,56 +53284,56 @@
 4. Os medicamentos vão ________ está a célula da queixa.</t>
         </is>
       </c>
-      <c r="B986" t="inlineStr">
+      <c r="B936" t="inlineStr">
         <is>
           <t>onde, aonde, onde, onde.</t>
         </is>
       </c>
-      <c r="C986" t="inlineStr">
+      <c r="C936" t="inlineStr">
         <is>
           <t>onde, onde, onde, aonde.</t>
         </is>
       </c>
-      <c r="D986" t="inlineStr">
+      <c r="D936" t="inlineStr">
         <is>
           <t>aonde, onde, onde, onde.</t>
         </is>
       </c>
-      <c r="E986" t="inlineStr">
+      <c r="E936" t="inlineStr">
         <is>
           <t>onde, aonde, aonde, onde.</t>
         </is>
       </c>
-      <c r="F986" t="inlineStr"/>
-      <c r="G986" t="inlineStr">
+      <c r="F936" t="inlineStr"/>
+      <c r="G936" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H986" t="inlineStr">
+      <c r="H936" t="inlineStr">
         <is>
           <t>Nas três primeiras frases, a regência dos verbos não exige o uso da preposição “a”, por isso o correto seria o uso de “onde”, indicando um local e não a direção de um movimento. Já na última frase, o verbo “ir” (“vão”) pede o uso dessa preposição e, portanto, o pronome relativo correto seria “aonde”.</t>
         </is>
       </c>
-      <c r="I986" t="inlineStr">
+      <c r="I936" t="inlineStr">
         <is>
           <t>PH10</t>
         </is>
       </c>
-      <c r="J986" t="inlineStr">
+      <c r="J936" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="K986" t="inlineStr"/>
-      <c r="L986" t="inlineStr">
+      <c r="K936" t="inlineStr"/>
+      <c r="L936" t="inlineStr">
         <is>
           <t>7ano</t>
         </is>
       </c>
     </row>
-    <row r="987">
-      <c r="A987" t="inlineStr">
+    <row r="937">
+      <c r="A937" t="inlineStr">
         <is>
           <t>Se temos de esperar,
 que seja para colher a semente boa
@@ -56408,56 +53342,56 @@
 O termo “que”, presente no 3º verso, classifica-se como</t>
         </is>
       </c>
-      <c r="B987" t="inlineStr">
+      <c r="B937" t="inlineStr">
         <is>
           <t>artigo definido, pois indetermina o substantivo.</t>
         </is>
       </c>
-      <c r="C987" t="inlineStr">
+      <c r="C937" t="inlineStr">
         <is>
           <t>advérbio, pois atribui uma circunstância ao verbo.</t>
         </is>
       </c>
-      <c r="D987" t="inlineStr">
+      <c r="D937" t="inlineStr">
         <is>
           <t>pronome relativo, pois refere-se a um termo anterior.</t>
         </is>
       </c>
-      <c r="E987" t="inlineStr">
+      <c r="E937" t="inlineStr">
         <is>
           <t>pronome pessoal, pois designa a pessoa do discurso.</t>
         </is>
       </c>
-      <c r="F987" t="inlineStr"/>
-      <c r="G987" t="inlineStr">
+      <c r="F937" t="inlineStr"/>
+      <c r="G937" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H987" t="inlineStr">
+      <c r="H937" t="inlineStr">
         <is>
           <t>O termo “que” está retomando a expressão “semente boa” do verso anterior. Assim, o verso “que lançamos hoje no solo da vida” poderia ser substituído por “Lançamos a semente boa hoje no solo da vida”.</t>
         </is>
       </c>
-      <c r="I987" t="inlineStr">
+      <c r="I937" t="inlineStr">
         <is>
           <t>PH10</t>
         </is>
       </c>
-      <c r="J987" t="inlineStr">
+      <c r="J937" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="K987" t="inlineStr"/>
-      <c r="L987" t="inlineStr">
+      <c r="K937" t="inlineStr"/>
+      <c r="L937" t="inlineStr">
         <is>
           <t>7ano</t>
         </is>
       </c>
     </row>
-    <row r="988">
-      <c r="A988" t="inlineStr">
+    <row r="938">
+      <c r="A938" t="inlineStr">
         <is>
           <t>Redação em construção
 É sabido que o fato novo assusta os indivíduos, que preferem o mal velho, testado e vivido, à experiência nova, sempre ameaçadora. Se você disser ao cidadão desprevenido que o leite, por ser essencial, deve sair das mãos dos particulares para cooperativas ou entidades estatais, se você disser que os bancos, vivendo exclusivamente das poupanças populares, não têm nenhuma razão de estar em mãos privadas, o cidadão o olhará com olhos perplexos de quem vê alguém propondo algo muito perigoso. Mas, se, ao contrário, você advogar a tese de que a água deveria ser explorada por particulares, todos se voltarão contra você pois – com toda razão – jamais poderiam admitir essa hipótese, tão acostumados estão com essa que é uma das mais antigas realizações comunitárias do homem: a água é direito e serventia de todos. Por isso o cidadão deve ficar alerta, sobretudo para com os malucos, excepcionais e marginais, pois estes, quase sempre, são os que trazem as mais espantosas propostas de renovação contra tudo o que foi estabelecido.
@@ -56468,56 +53402,56 @@
 A língua oferece diferentes possibilidades de organização para se expressar um mesmo conteúdo. Assinale a alternativa que demonstre a reescrita do trecho acima, substituindo, sem mudança de sentido, o adjetivo “espantosas” pelo verbo “espantar” em uma oração que seja introduzida por pronome relativo.</t>
         </is>
       </c>
-      <c r="B988" t="inlineStr">
+      <c r="B938" t="inlineStr">
         <is>
           <t>Trazem as propostas de renovação cujo mais espantam.</t>
         </is>
       </c>
-      <c r="C988" t="inlineStr">
+      <c r="C938" t="inlineStr">
         <is>
           <t>Trazem as propostas de renovação onde mais espantam.</t>
         </is>
       </c>
-      <c r="D988" t="inlineStr">
+      <c r="D938" t="inlineStr">
         <is>
           <t>Trazem as propostas de renovação aonde mais espantam.</t>
         </is>
       </c>
-      <c r="E988" t="inlineStr">
+      <c r="E938" t="inlineStr">
         <is>
           <t>Trazem as propostas de renovação que mais espantam.</t>
         </is>
       </c>
-      <c r="F988" t="inlineStr"/>
-      <c r="G988" t="inlineStr">
+      <c r="F938" t="inlineStr"/>
+      <c r="G938" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H988" t="inlineStr">
+      <c r="H938" t="inlineStr">
         <is>
           <t>O pronome relativo “que” seria adequado, sem prejuízo de sentido, para retomar o substantivo “propostas”.</t>
         </is>
       </c>
-      <c r="I988" t="inlineStr">
+      <c r="I938" t="inlineStr">
         <is>
           <t>PH10</t>
         </is>
       </c>
-      <c r="J988" t="inlineStr">
+      <c r="J938" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="K988" t="inlineStr"/>
-      <c r="L988" t="inlineStr">
+      <c r="K938" t="inlineStr"/>
+      <c r="L938" t="inlineStr">
         <is>
           <t>7ano</t>
         </is>
       </c>
     </row>
-    <row r="989">
-      <c r="A989" t="inlineStr">
+    <row r="939">
+      <c r="A939" t="inlineStr">
         <is>
           <t>Leia o texto a seguir.
 Fake news ganha espaço no Facebook e jornalismo profissional perde
@@ -56530,116 +53464,113 @@
 No segundo parágrafo dessa notícia, o verbo “postar” encontra-se na terceira pessoa do plural porque faz referência</t>
         </is>
       </c>
-      <c r="B989" t="inlineStr">
+      <c r="B939" t="inlineStr">
         <is>
           <t>ao pronome relativo “que”, que desempenha função de sujeito no período.</t>
         </is>
       </c>
-      <c r="C989" t="inlineStr">
+      <c r="C939" t="inlineStr">
         <is>
           <t>ao substantivo próprio “Folha”, implicando desvio de concordância.</t>
         </is>
       </c>
-      <c r="D989" t="inlineStr">
+      <c r="D939" t="inlineStr">
         <is>
           <t>ao numeral “21”, núcleo do sujeito, com o qual o verbo “postar” concorda.</t>
         </is>
       </c>
-      <c r="E989" t="inlineStr">
+      <c r="E939" t="inlineStr">
         <is>
           <t>ao sujeito composto, cujos núcleos são “fake news” e “jornalismo profissional”.</t>
         </is>
       </c>
-      <c r="F989" t="inlineStr"/>
-      <c r="G989" t="inlineStr">
+      <c r="F939" t="inlineStr"/>
+      <c r="G939" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H989" t="inlineStr">
+      <c r="H939" t="inlineStr">
         <is>
           <t>O verbo “postar” encontra-se na terceira pessoa do plural porque a concordância verbal, quando o pronome relativo “que” desempenha função de sujeito no período, é feita com o termo a que ele se refere (seu antecedente), ou seja, nesse caso, “21 páginas”.</t>
         </is>
       </c>
-      <c r="I989" t="inlineStr">
+      <c r="I939" t="inlineStr">
         <is>
           <t>PH10</t>
         </is>
       </c>
-      <c r="J989" t="inlineStr">
+      <c r="J939" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="K989" t="inlineStr"/>
-      <c r="L989" t="inlineStr">
+      <c r="K939" t="inlineStr"/>
+      <c r="L939" t="inlineStr">
         <is>
           <t>7ano</t>
         </is>
       </c>
     </row>
-    <row r="990">
-      <c r="A990" t="inlineStr">
+    <row r="940">
+      <c r="A940" t="inlineStr">
         <is>
           <t>Leia o texto a seguir.
+[img:ph10_por_09.png]
 Disponível em: &lt;https://www.nsctotal.com.br/noticias/quem-impos-os-cortes-foi-a-realidade-nao-o-governo-afirma-secretario-joao-paulo-kleinubing&gt;. Acesso em: 18 ago. 2020.
-O verbo “impor” foi flexionado na terceira pessoa do singular porque</t>
-        </is>
-      </c>
-      <c r="B990" t="inlineStr">
+ O verbo “impor” foi flexionado na terceira pessoa do singular porque</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
         <is>
           <t>não há um sujeito específico nesse período.</t>
         </is>
       </c>
-      <c r="C990" t="inlineStr">
+      <c r="C940" t="inlineStr">
         <is>
           <t>concorda com o sujeito simples "João Paulo Kleinübing".</t>
         </is>
       </c>
-      <c r="D990" t="inlineStr">
+      <c r="D940" t="inlineStr">
         <is>
           <t>concorda com o pronome relativo "quem", cuja referência é “realidade”.</t>
         </is>
       </c>
-      <c r="E990" t="inlineStr">
+      <c r="E940" t="inlineStr">
         <is>
           <t>concorda com "secretário", que exige o verbo na terceira pessoa do singular.</t>
         </is>
       </c>
-      <c r="F990" t="inlineStr"/>
-      <c r="G990" t="inlineStr">
+      <c r="F940" t="inlineStr"/>
+      <c r="G940" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H990" t="inlineStr">
+      <c r="H940" t="inlineStr">
         <is>
           <t>A concordância com o pronome relativo “quem” pode ser feita com o seu referente ou o verbo pode ficar na terceira pessoa do singular. Neste caso, o verbo “impor” poderia ser flexionado somente na terceira pessoa do singular, respeitando ou o pronome relativo ou o referente, “realidade”, que está na terceira pessoa do singular.</t>
         </is>
       </c>
-      <c r="I990" t="inlineStr">
+      <c r="I940" t="inlineStr">
         <is>
           <t>PH10</t>
         </is>
       </c>
-      <c r="J990" t="inlineStr">
+      <c r="J940" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="K990" t="inlineStr">
-        <is>
-          <t>ph10_por_09.png</t>
-        </is>
-      </c>
-      <c r="L990" t="inlineStr">
+      <c r="K940" t="inlineStr"/>
+      <c r="L940" t="inlineStr">
         <is>
           <t>7ano</t>
         </is>
       </c>
     </row>
-    <row r="991">
-      <c r="A991" t="inlineStr">
+    <row r="941">
+      <c r="A941" t="inlineStr">
         <is>
           <t>Leia o trecho da música "Vilarejo" de Marisa Monte e responda à questão:
 Há um vilarejo ali
@@ -56651,88 +53582,88 @@
 Sobre o uso do pronome relativo "onde" no trecho acima,</t>
         </is>
       </c>
-      <c r="B991" t="inlineStr">
+      <c r="B941" t="inlineStr">
         <is>
           <t>menciona a palavra "vento" e indica o local onde o vento areja.</t>
         </is>
       </c>
-      <c r="C991" t="inlineStr">
+      <c r="C941" t="inlineStr">
         <is>
           <t>nomeia a palavra "varanda" e indica o local onde alguém descansa.</t>
         </is>
       </c>
-      <c r="D991" t="inlineStr">
+      <c r="D941" t="inlineStr">
         <is>
           <t>referencia a palavra "vilarejo" e indica o local onde areja um vento bom.</t>
         </is>
       </c>
-      <c r="E991" t="inlineStr">
+      <c r="E941" t="inlineStr">
         <is>
           <t>alude à palavra "horizonte" e indica o local onde o horizonte deita no chão.</t>
         </is>
       </c>
-      <c r="F991" t="inlineStr"/>
-      <c r="G991" t="inlineStr">
+      <c r="F941" t="inlineStr"/>
+      <c r="G941" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H991" t="inlineStr">
+      <c r="H941" t="inlineStr">
         <is>
           <t>O pronome relativo "onde" está sendo utilizado para substituir o substantivo "vilarejo" e é adequado para indicar um lugar. No trecho da música, "onde" está introduzindo uma oração relativa que fornece uma informação adicional sobre o vilarejo, especificando que é o local onde areja um vento bom.</t>
         </is>
       </c>
-      <c r="I991" t="inlineStr">
+      <c r="I941" t="inlineStr">
         <is>
           <t>PH10</t>
         </is>
       </c>
-      <c r="J991" t="inlineStr">
+      <c r="J941" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="K991" t="inlineStr"/>
-      <c r="L991" t="inlineStr">
+      <c r="K941" t="inlineStr"/>
+      <c r="L941" t="inlineStr">
         <is>
           <t>7ano</t>
         </is>
       </c>
     </row>
-    <row r="992">
-      <c r="A992" t="inlineStr">
+    <row r="942">
+      <c r="A942" t="inlineStr">
         <is>
           <t>Ana e Bruno estão construindo triângulos utilizando palitos de fósforo. Ana escolheu três palitos com medidas 4 cm, 5 cm e 9 cm, enquanto Bruno escolheu palitos com medidas 3 cm, 5 cm e 8 cm.
 Após a construção, qual dos dois amigos conseguiu formar um triângulo?</t>
         </is>
       </c>
-      <c r="B992" t="inlineStr">
+      <c r="B942" t="inlineStr">
         <is>
           <t>Apenas Ana.</t>
         </is>
       </c>
-      <c r="C992" t="inlineStr">
+      <c r="C942" t="inlineStr">
         <is>
           <t>Apenas Bruno.</t>
         </is>
       </c>
-      <c r="D992" t="inlineStr">
+      <c r="D942" t="inlineStr">
         <is>
           <t>Nenhum dos dois</t>
         </is>
       </c>
-      <c r="E992" t="inlineStr">
+      <c r="E942" t="inlineStr">
         <is>
           <t>Ambos, Ana e Bruno.</t>
         </is>
       </c>
-      <c r="F992" t="inlineStr"/>
-      <c r="G992" t="inlineStr">
+      <c r="F942" t="inlineStr"/>
+      <c r="G942" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H992" t="inlineStr">
+      <c r="H942" t="inlineStr">
         <is>
           <t>Para que três segmentos de reta formem um triângulo, a medida de cada lado deve ser menor que a soma das medidas dos outros dois lados.
 Triângulo de Ana:
@@ -56743,112 +53674,112 @@
 8 cm é igual à soma dos outros dois lados. Portanto, Bruno não consegue formar um triângulo.</t>
         </is>
       </c>
-      <c r="I992" t="inlineStr">
+      <c r="I942" t="inlineStr">
         <is>
           <t>PH10</t>
         </is>
       </c>
-      <c r="J992" t="inlineStr">
+      <c r="J942" t="inlineStr">
         <is>
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K992" t="inlineStr"/>
-      <c r="L992" t="inlineStr">
+      <c r="K942" t="inlineStr"/>
+      <c r="L942" t="inlineStr">
         <is>
           <t>7ano</t>
         </is>
       </c>
     </row>
-    <row r="993">
-      <c r="A993" t="inlineStr">
+    <row r="943">
+      <c r="A943" t="inlineStr">
         <is>
           <t>Um engenheiro civil está projetando uma ponte que precisa ser extremamente estável e resistente a deformações. Ele está considerando diferentes formas geométricas para a estrutura da ponte e sabe que a rigidez é um fator crucial. Ele está avaliando o uso de triângulos na construção da estrutura da ponte.
 Por que o engenheiro deve preferir o uso de triângulos na construção da estrutura da ponte para garantir a rigidez e a estabilidade?</t>
         </is>
       </c>
-      <c r="B993" t="inlineStr">
+      <c r="B943" t="inlineStr">
         <is>
           <t>Porque os triângulos têm lados iguais, o que garante a rigidez.</t>
         </is>
       </c>
-      <c r="C993" t="inlineStr">
+      <c r="C943" t="inlineStr">
         <is>
           <t>Porque os triângulos têm ângulos iguais, o que garante a rigidez.</t>
         </is>
       </c>
-      <c r="D993" t="inlineStr">
+      <c r="D943" t="inlineStr">
         <is>
           <t>Porque os triângulos têm todos os lados diferentes, o que garante a rigidez.</t>
         </is>
       </c>
-      <c r="E993" t="inlineStr">
+      <c r="E943" t="inlineStr">
         <is>
           <t>Porque os triângulos são figuras geométricas rígidas, o que garante a estabilidade.</t>
         </is>
       </c>
-      <c r="F993" t="inlineStr"/>
-      <c r="G993" t="inlineStr">
+      <c r="F943" t="inlineStr"/>
+      <c r="G943" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H993" t="inlineStr">
+      <c r="H943" t="inlineStr">
         <is>
           <t>Os triângulos são figuras geométricas rígidas, o que significa que, uma vez construídos, eles não mudam de forma, mesmo quando submetidos a forças externas. Isso ocorre porque a soma dos ângulos internos de um triângulo é sempre 180°, e a relação entre os lados e os ângulos é fixa. Por isso, o engenheiro deve preferir o uso de triângulos na construção da estrutura da ponte para garantir a rigidez e a estabilidade.</t>
         </is>
       </c>
-      <c r="I993" t="inlineStr">
+      <c r="I943" t="inlineStr">
         <is>
           <t>PH10</t>
         </is>
       </c>
-      <c r="J993" t="inlineStr">
+      <c r="J943" t="inlineStr">
         <is>
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K993" t="inlineStr"/>
-      <c r="L993" t="inlineStr">
+      <c r="K943" t="inlineStr"/>
+      <c r="L943" t="inlineStr">
         <is>
           <t>7ano</t>
         </is>
       </c>
     </row>
-    <row r="994">
-      <c r="A994" t="inlineStr">
+    <row r="944">
+      <c r="A944" t="inlineStr">
         <is>
           <t>Um professor de matemática pediu aos alunos que descrevessem um algoritmo para a construção de um triângulo qualquer, conhecidas as medidas dos três lados: 6 cm, 8 cm e 10 cm.
 Qual é a sequência correta de passos para construir um triângulo com lados de 6 cm, 8 cm e 10 cm?</t>
         </is>
       </c>
-      <c r="B994" t="inlineStr">
+      <c r="B944" t="inlineStr">
         <is>
           <t>Desenhe um segmento de 6 cm, depois desenhe um segmento de 10 cm a partir de uma extremidade do primeiro segmento, e finalmente desenhe um segmento de 8 cm a partir da extremidade do segundo segmento.</t>
         </is>
       </c>
-      <c r="C994" t="inlineStr">
+      <c r="C944" t="inlineStr">
         <is>
           <t>Desenhe um segmento de 6 cm, depois desenhe um segmento de 8 cm a partir de uma extremidade do primeiro segmento, e finalmente desenhe um segmento de 10 cm a partir da outra extremidade do primeiro segmento.</t>
         </is>
       </c>
-      <c r="D994" t="inlineStr">
+      <c r="D944" t="inlineStr">
         <is>
           <t>Desenhe um segmento de 6 cm, depois desenhe um segmento de 8 cm a partir de uma extremidade do primeiro segmento, e finalmente desenhe um segmento de 10 cm a partir da extremidade do segundo segmento, encontrando a outra extremidade do primeiro segmento.</t>
         </is>
       </c>
-      <c r="E994" t="inlineStr">
+      <c r="E944" t="inlineStr">
         <is>
           <t>Desenhe um segmento de 6 cm, depois, com um compasso, trace um arco de 8 cm a partir de uma extremidade do segmento de 6 cm, e um arco de 10 cm a partir da outra extremidade do segmento de 6 cm. O ponto de interseção dos arcos será o terceiro vértice do triângulo.</t>
         </is>
       </c>
-      <c r="F994" t="inlineStr"/>
-      <c r="G994" t="inlineStr">
+      <c r="F944" t="inlineStr"/>
+      <c r="G944" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H994" t="inlineStr">
+      <c r="H944" t="inlineStr">
         <is>
           <t>Para construir um triângulo com lados de 6 cm, 8 cm e 10 cm, o algoritmo correto é:
 Desenhe um segmento de 6 cm.
@@ -56858,433 +53789,413 @@
 Conecte esse ponto de interseção às extremidades do segmento de 6 cm para formar o triângulo.</t>
         </is>
       </c>
-      <c r="I994" t="inlineStr">
+      <c r="I944" t="inlineStr">
         <is>
           <t>PH10</t>
         </is>
       </c>
-      <c r="J994" t="inlineStr">
+      <c r="J944" t="inlineStr">
         <is>
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K994" t="inlineStr"/>
-      <c r="L994" t="inlineStr">
+      <c r="K944" t="inlineStr"/>
+      <c r="L944" t="inlineStr">
         <is>
           <t>7ano</t>
         </is>
       </c>
     </row>
-    <row r="995">
-      <c r="A995" t="inlineStr">
+    <row r="945">
+      <c r="A945" t="inlineStr">
         <is>
           <t>Em uma aula de geometria, o professor pediu aos alunos que calculassem a medida de um dos ângulos internos de um triângulo, sabendo que os outros dois ângulos medem 50° e 70°.
 Qual é a medida do terceiro ângulo interno desse triângulo?</t>
         </is>
       </c>
-      <c r="B995" t="inlineStr">
+      <c r="B945" t="inlineStr">
         <is>
           <t>50º</t>
         </is>
       </c>
-      <c r="C995" t="inlineStr">
+      <c r="C945" t="inlineStr">
         <is>
           <t>60º</t>
         </is>
       </c>
-      <c r="D995" t="inlineStr">
+      <c r="D945" t="inlineStr">
         <is>
           <t>70º</t>
         </is>
       </c>
-      <c r="E995" t="inlineStr">
+      <c r="E945" t="inlineStr">
         <is>
           <t>80º</t>
         </is>
       </c>
-      <c r="F995" t="inlineStr"/>
-      <c r="G995" t="inlineStr">
+      <c r="F945" t="inlineStr"/>
+      <c r="G945" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H995" t="inlineStr">
+      <c r="H945" t="inlineStr">
         <is>
           <t>A soma dos ângulos internos de um triângulo é sempre 180°. Sabendo que dois dos ângulos medem 50° e 70°, podemos encontrar a medida do terceiro ângulo subtraindo a soma dos dois ângulos conhecidos de 180°:</t>
         </is>
       </c>
-      <c r="I995" t="inlineStr">
+      <c r="I945" t="inlineStr">
         <is>
           <t>PH10</t>
         </is>
       </c>
-      <c r="J995" t="inlineStr">
+      <c r="J945" t="inlineStr">
         <is>
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K995" t="inlineStr"/>
-      <c r="L995" t="inlineStr">
+      <c r="K945" t="inlineStr"/>
+      <c r="L945" t="inlineStr">
         <is>
           <t>7ano</t>
         </is>
       </c>
     </row>
-    <row r="996">
-      <c r="A996" t="inlineStr">
-        <is>
-          <t>Em um triângulo , o ângulo externo  é formado pela extensão do lado AB. Sabe-se que os ângulos internos  medem 45° e 55°, respectivamente.
-Qual é a medida do ângulo externo ?</t>
-        </is>
-      </c>
-      <c r="B996" t="inlineStr">
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>Em um triângulo [img:ph10_mat_05.png], o ângulo externo [img:ph10_mat_05_t1.png] é formado pela extensão do lado AB. Sabe-se que os ângulos internos [img:ph10_mat_05_t2.png] medem 45° e 55°, respectivamente.
+Qual é a medida do ângulo externo [img:ph10_mat_05_t3.png]?</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
         <is>
           <t>90º</t>
         </is>
       </c>
-      <c r="C996" t="inlineStr">
+      <c r="C946" t="inlineStr">
         <is>
           <t>100º</t>
         </is>
       </c>
-      <c r="D996" t="inlineStr">
+      <c r="D946" t="inlineStr">
         <is>
           <t>110º</t>
         </is>
       </c>
-      <c r="E996" t="inlineStr">
+      <c r="E946" t="inlineStr">
         <is>
           <t>120º</t>
         </is>
       </c>
-      <c r="F996" t="inlineStr"/>
-      <c r="G996" t="inlineStr">
+      <c r="F946" t="inlineStr"/>
+      <c r="G946" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H996" t="inlineStr">
+      <c r="H946" t="inlineStr">
         <is>
           <t>A relação entre um ângulo externo e os dois ângulos internos não adjacentes de um triângulo é que o ângulo externo é igual à soma dos dois ângulos internos não adjacentes. Portanto, a medida do ângulo externo  é:</t>
         </is>
       </c>
-      <c r="I996" t="inlineStr">
+      <c r="I946" t="inlineStr">
         <is>
           <t>PH10</t>
         </is>
       </c>
-      <c r="J996" t="inlineStr">
+      <c r="J946" t="inlineStr">
         <is>
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K996" t="inlineStr">
-        <is>
-          <t>ph10_mat_05.png</t>
-        </is>
-      </c>
-      <c r="L996" t="inlineStr">
+      <c r="K946" t="inlineStr"/>
+      <c r="L946" t="inlineStr">
         <is>
           <t>7ano</t>
         </is>
       </c>
     </row>
-    <row r="997">
-      <c r="A997" t="inlineStr">
+    <row r="947">
+      <c r="A947" t="inlineStr">
         <is>
           <t>Observe o triângulo abaixo:
+[img:ph10_mat_06.png]
 A relação que existe entre a medida dos lados deste triângulo é</t>
         </is>
       </c>
-      <c r="B997" t="inlineStr">
+      <c r="B947" t="inlineStr">
         <is>
           <t>[img:ph10_mat_06_a.png]</t>
         </is>
       </c>
-      <c r="C997" t="inlineStr">
+      <c r="C947" t="inlineStr">
         <is>
           <t>[img:ph10_mat_06_b.png]</t>
         </is>
       </c>
-      <c r="D997" t="inlineStr">
+      <c r="D947" t="inlineStr">
         <is>
           <t>[img:ph10_mat_06_c.png]</t>
         </is>
       </c>
-      <c r="E997" t="inlineStr">
+      <c r="E947" t="inlineStr">
         <is>
           <t>[img:ph10_mat_06_d.png]</t>
         </is>
       </c>
-      <c r="F997" t="inlineStr"/>
-      <c r="G997" t="inlineStr">
+      <c r="F947" t="inlineStr"/>
+      <c r="G947" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H997" t="inlineStr">
+      <c r="H947" t="inlineStr">
         <is>
           <t>Em um triângulo, o maior dos lados é oposto ao maior dos ângulos, assim como o menor lado é oposto ao menor ângulo.
 Desta forma, como  então .</t>
         </is>
       </c>
-      <c r="I997" t="inlineStr">
+      <c r="I947" t="inlineStr">
         <is>
           <t>PH10</t>
         </is>
       </c>
-      <c r="J997" t="inlineStr">
+      <c r="J947" t="inlineStr">
         <is>
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K997" t="inlineStr">
-        <is>
-          <t>ph10_mat_06.png</t>
-        </is>
-      </c>
-      <c r="L997" t="inlineStr">
+      <c r="K947" t="inlineStr"/>
+      <c r="L947" t="inlineStr">
         <is>
           <t>7ano</t>
         </is>
       </c>
     </row>
-    <row r="998">
-      <c r="A998" t="inlineStr">
-        <is>
-          <t>Na figura abaixo estão marcados 4 ângulos, de forma que a soma da medida do ângulo reto com a medida do ângulo  é 130°..
-Qual é a medida do ângulo ?</t>
-        </is>
-      </c>
-      <c r="B998" t="inlineStr">
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>Na figura abaixo estão marcados 4 ângulos, de forma que a soma da medida do ângulo reto com a medida do ângulo [img:ph10_mat_07.png] é 130°..
+[img:ph10_mat_07_t1.png]
+Qual é a medida do ângulo [img:ph10_mat_07_t2.png]?</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
         <is>
           <t>40°</t>
         </is>
       </c>
-      <c r="C998" t="inlineStr">
+      <c r="C948" t="inlineStr">
         <is>
           <t>45°</t>
         </is>
       </c>
-      <c r="D998" t="inlineStr">
+      <c r="D948" t="inlineStr">
         <is>
           <t>55°</t>
         </is>
       </c>
-      <c r="E998" t="inlineStr">
+      <c r="E948" t="inlineStr">
         <is>
           <t>65°</t>
         </is>
       </c>
-      <c r="F998" t="inlineStr"/>
-      <c r="G998" t="inlineStr">
+      <c r="F948" t="inlineStr"/>
+      <c r="G948" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H998" t="inlineStr">
+      <c r="H948" t="inlineStr">
         <is>
           <t>O ângulo  é externo ao triângulo que contém os ângulos  e 25°, logo ele é dado pela medida desses dois ângulos.
 Como a soma da medida do ângulo reto com a medida do ângulo  é 130° e de 90° para 130° faltam 40°, logo a medida de  = 40° e a medida de  = 40° + 25° ⟹  = 65°.</t>
         </is>
       </c>
-      <c r="I998" t="inlineStr">
+      <c r="I948" t="inlineStr">
         <is>
           <t>PH10</t>
         </is>
       </c>
-      <c r="J998" t="inlineStr">
+      <c r="J948" t="inlineStr">
         <is>
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K998" t="inlineStr">
-        <is>
-          <t>ph10_mat_07.png</t>
-        </is>
-      </c>
-      <c r="L998" t="inlineStr">
+      <c r="K948" t="inlineStr"/>
+      <c r="L948" t="inlineStr">
         <is>
           <t>7ano</t>
         </is>
       </c>
     </row>
-    <row r="999">
-      <c r="A999" t="inlineStr">
+    <row r="949">
+      <c r="A949" t="inlineStr">
         <is>
           <t>Observe a figura abaixo:
-Qual é a medida de ?</t>
-        </is>
-      </c>
-      <c r="B999" t="inlineStr">
+[img:ph10_mat_08.png]
+Qual é a medida de [img:ph10_mat_08_t1.png]?</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
         <is>
           <t>20°</t>
         </is>
       </c>
-      <c r="C999" t="inlineStr">
+      <c r="C949" t="inlineStr">
         <is>
           <t>30°</t>
         </is>
       </c>
-      <c r="D999" t="inlineStr">
+      <c r="D949" t="inlineStr">
         <is>
           <t>40°</t>
         </is>
       </c>
-      <c r="E999" t="inlineStr">
+      <c r="E949" t="inlineStr">
         <is>
           <t>50°</t>
         </is>
       </c>
-      <c r="F999" t="inlineStr"/>
-      <c r="G999" t="inlineStr">
+      <c r="F949" t="inlineStr"/>
+      <c r="G949" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H999" t="inlineStr">
+      <c r="H949" t="inlineStr">
         <is>
           <t>Para descobrir o valor de , basta subtrair de 180° os ângulos internos que sabemos o valor: 180° - 115° - 25° = 40°.</t>
         </is>
       </c>
-      <c r="I999" t="inlineStr">
+      <c r="I949" t="inlineStr">
         <is>
           <t>PH10</t>
         </is>
       </c>
-      <c r="J999" t="inlineStr">
+      <c r="J949" t="inlineStr">
         <is>
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K999" t="inlineStr">
-        <is>
-          <t>ph10_mat_08.png</t>
-        </is>
-      </c>
-      <c r="L999" t="inlineStr">
+      <c r="K949" t="inlineStr"/>
+      <c r="L949" t="inlineStr">
         <is>
           <t>7ano</t>
         </is>
       </c>
     </row>
-    <row r="1000">
-      <c r="A1000" t="inlineStr">
+    <row r="950">
+      <c r="A950" t="inlineStr">
         <is>
           <t>Observe a figura desenhada abaixo, formada por um quadrado e 4 triângulos equiláteros de lados com a mesma medida, além de dois segmentos: FC e FD.
-Qual a medida do ângulo ?</t>
-        </is>
-      </c>
-      <c r="B1000" t="inlineStr">
+[img:ph10_mat_09.png]
+Qual a medida do ângulo [img:ph10_mat_09_t1.png]?</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
         <is>
           <t>15°</t>
         </is>
       </c>
-      <c r="C1000" t="inlineStr">
+      <c r="C950" t="inlineStr">
         <is>
           <t>30°</t>
         </is>
       </c>
-      <c r="D1000" t="inlineStr">
+      <c r="D950" t="inlineStr">
         <is>
           <t>40°</t>
         </is>
       </c>
-      <c r="E1000" t="inlineStr">
+      <c r="E950" t="inlineStr">
         <is>
           <t>45°</t>
         </is>
       </c>
-      <c r="F1000" t="inlineStr"/>
-      <c r="G1000" t="inlineStr">
+      <c r="F950" t="inlineStr"/>
+      <c r="G950" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H1000" t="inlineStr">
+      <c r="H950" t="inlineStr">
         <is>
           <t>O triângulo ADF é isósceles, pois o lado do quadrado e o lado do triângulo equilátero têm a mesma medida.
 Logo, o ângulo A do triângulo ADF será de 60° + 90° = 150°. O que falta para chegar a 180° será dividido em dois ângulos congruentes:</t>
         </is>
       </c>
-      <c r="I1000" t="inlineStr">
+      <c r="I950" t="inlineStr">
         <is>
           <t>PH10</t>
         </is>
       </c>
-      <c r="J1000" t="inlineStr">
+      <c r="J950" t="inlineStr">
         <is>
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K1000" t="inlineStr">
-        <is>
-          <t>ph10_mat_09.png</t>
-        </is>
-      </c>
-      <c r="L1000" t="inlineStr">
+      <c r="K950" t="inlineStr"/>
+      <c r="L950" t="inlineStr">
         <is>
           <t>7ano</t>
         </is>
       </c>
     </row>
-    <row r="1001">
-      <c r="A1001" t="inlineStr">
+    <row r="951">
+      <c r="A951" t="inlineStr">
         <is>
           <t>Observe a figura desenhada abaixo, formada por um quadrado e 4 triângulos equiláteros de lados com a mesma medida, além de dois segmentos: FC e FD.
- ​
-Qual a medida do ângulo ?</t>
-        </is>
-      </c>
-      <c r="B1001" t="inlineStr">
+[img:ph10_mat_10.png]  ​
+Qual a medida do ângulo [img:ph10_mat_10_t1.png]?</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
         <is>
           <t>45°</t>
         </is>
       </c>
-      <c r="C1001" t="inlineStr">
+      <c r="C951" t="inlineStr">
         <is>
           <t>60°</t>
         </is>
       </c>
-      <c r="D1001" t="inlineStr">
+      <c r="D951" t="inlineStr">
         <is>
           <t>75°</t>
         </is>
       </c>
-      <c r="E1001" t="inlineStr">
+      <c r="E951" t="inlineStr">
         <is>
           <t>80°</t>
         </is>
       </c>
-      <c r="F1001" t="inlineStr"/>
-      <c r="G1001" t="inlineStr">
+      <c r="F951" t="inlineStr"/>
+      <c r="G951" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H1001" t="inlineStr">
+      <c r="H951" t="inlineStr">
         <is>
           <t>Como o triângulo ADF é isósceles, e o ângulo DAF mede , então o ângulo D do triângulo ADF será de .
 É possível concluir que:
 A soma de (beta) com a medida do ângulo ADF é 90°, de 15° para 90° faltam 75°. Logo, β = 75°.</t>
         </is>
       </c>
-      <c r="I1001" t="inlineStr">
+      <c r="I951" t="inlineStr">
         <is>
           <t>PH10</t>
         </is>
       </c>
-      <c r="J1001" t="inlineStr">
+      <c r="J951" t="inlineStr">
         <is>
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K1001" t="inlineStr">
-        <is>
-          <t>ph10_mat_10.png</t>
-        </is>
-      </c>
-      <c r="L1001" t="inlineStr">
+      <c r="K951" t="inlineStr"/>
+      <c r="L951" t="inlineStr">
         <is>
           <t>7ano</t>
         </is>

--- a/questoes.xlsx
+++ b/questoes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L951"/>
+  <dimension ref="A1:L1051"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51342,7 +51342,6 @@
           <t>São fotossintetizantes.</t>
         </is>
       </c>
-      <c r="F902" t="inlineStr"/>
       <c r="G902" t="inlineStr">
         <is>
           <t>C</t>
@@ -51363,7 +51362,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K902" t="inlineStr"/>
       <c r="L902" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -51397,7 +51395,6 @@
           <t>transformar oxigênio em gás carbônico.</t>
         </is>
       </c>
-      <c r="F903" t="inlineStr"/>
       <c r="G903" t="inlineStr">
         <is>
           <t>C</t>
@@ -51418,7 +51415,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K903" t="inlineStr"/>
       <c r="L903" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -51452,7 +51448,6 @@
           <t>temperatura ideal para crescimento.</t>
         </is>
       </c>
-      <c r="F904" t="inlineStr"/>
       <c r="G904" t="inlineStr">
         <is>
           <t>B</t>
@@ -51473,7 +51468,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K904" t="inlineStr"/>
       <c r="L904" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -51507,7 +51501,6 @@
           <t>Parasitismo de outros organismos.</t>
         </is>
       </c>
-      <c r="F905" t="inlineStr"/>
       <c r="G905" t="inlineStr">
         <is>
           <t>B</t>
@@ -51528,7 +51521,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K905" t="inlineStr"/>
       <c r="L905" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -51562,7 +51554,6 @@
           <t>Paramécios e bactérias.</t>
         </is>
       </c>
-      <c r="F906" t="inlineStr"/>
       <c r="G906" t="inlineStr">
         <is>
           <t>A</t>
@@ -51583,7 +51574,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K906" t="inlineStr"/>
       <c r="L906" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -51618,7 +51608,6 @@
           <t>Possui metabolismo e possui nadadeiras.</t>
         </is>
       </c>
-      <c r="F907" t="inlineStr"/>
       <c r="G907" t="inlineStr">
         <is>
           <t>C</t>
@@ -51639,7 +51628,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K907" t="inlineStr"/>
       <c r="L907" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -51674,7 +51662,6 @@
           <t>A árvore é autotrófica e não produz seu próprio alimento.</t>
         </is>
       </c>
-      <c r="F908" t="inlineStr"/>
       <c r="G908" t="inlineStr">
         <is>
           <t>A</t>
@@ -51695,7 +51682,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K908" t="inlineStr"/>
       <c r="L908" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -51728,7 +51714,6 @@
           <t>Acelular.</t>
         </is>
       </c>
-      <c r="F909" t="inlineStr"/>
       <c r="G909" t="inlineStr">
         <is>
           <t>A</t>
@@ -51749,7 +51734,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K909" t="inlineStr"/>
       <c r="L909" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -51785,7 +51769,6 @@
           <t>vírus.</t>
         </is>
       </c>
-      <c r="F910" t="inlineStr"/>
       <c r="G910" t="inlineStr">
         <is>
           <t>D</t>
@@ -51806,7 +51789,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K910" t="inlineStr"/>
       <c r="L910" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -51839,7 +51821,6 @@
           <t>capsídeo e núcleo.</t>
         </is>
       </c>
-      <c r="F911" t="inlineStr"/>
       <c r="G911" t="inlineStr">
         <is>
           <t>B</t>
@@ -51860,7 +51841,6 @@
           <t>Ciências</t>
         </is>
       </c>
-      <c r="K911" t="inlineStr"/>
       <c r="L911" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -51893,7 +51873,6 @@
           <t>A diversidade sociocultural do Brasil não está ligada ao território, mas sim à economia global.</t>
         </is>
       </c>
-      <c r="F912" t="inlineStr"/>
       <c r="G912" t="inlineStr">
         <is>
           <t>B</t>
@@ -51914,7 +51893,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K912" t="inlineStr"/>
       <c r="L912" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -51948,7 +51926,6 @@
           <t>A noção de território não tem impacto na organização política do Brasil, já que todas as regiões seguem as mesmas políticas públicas.</t>
         </is>
       </c>
-      <c r="F913" t="inlineStr"/>
       <c r="G913" t="inlineStr">
         <is>
           <t>C</t>
@@ -51969,7 +51946,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K913" t="inlineStr"/>
       <c r="L913" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -52003,7 +51979,6 @@
           <t>Pela exclusão de influências externas.</t>
         </is>
       </c>
-      <c r="F914" t="inlineStr"/>
       <c r="G914" t="inlineStr">
         <is>
           <t>B</t>
@@ -52024,7 +51999,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K914" t="inlineStr"/>
       <c r="L914" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -52058,7 +52032,6 @@
           <t>competição entre o uso agrícola e a preservação ambiental.</t>
         </is>
       </c>
-      <c r="F915" t="inlineStr"/>
       <c r="G915" t="inlineStr">
         <is>
           <t>A</t>
@@ -52079,7 +52052,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K915" t="inlineStr"/>
       <c r="L915" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -52113,7 +52085,6 @@
           <t>O Poder Executivo julga casos de violação de leis, o Poder Legislativo executa as políticas públicas, e o Poder Judiciário cria as leis.</t>
         </is>
       </c>
-      <c r="F916" t="inlineStr"/>
       <c r="G916" t="inlineStr">
         <is>
           <t>C</t>
@@ -52134,7 +52105,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K916" t="inlineStr"/>
       <c r="L916" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -52175,7 +52145,6 @@
           <t>Estados Unidos, Canadá, África do Sul e Indonésia.</t>
         </is>
       </c>
-      <c r="F917" t="inlineStr"/>
       <c r="G917" t="inlineStr">
         <is>
           <t>C</t>
@@ -52196,7 +52165,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K917" t="inlineStr"/>
       <c r="L917" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -52230,7 +52198,6 @@
           <t>Bolívia e Venezuela.</t>
         </is>
       </c>
-      <c r="F918" t="inlineStr"/>
       <c r="G918" t="inlineStr">
         <is>
           <t>B</t>
@@ -52251,7 +52218,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K918" t="inlineStr"/>
       <c r="L918" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -52287,7 +52253,6 @@
           <t>Arroio Chuí.</t>
         </is>
       </c>
-      <c r="F919" t="inlineStr"/>
       <c r="G919" t="inlineStr">
         <is>
           <t>D</t>
@@ -52308,7 +52273,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K919" t="inlineStr"/>
       <c r="L919" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -52348,7 +52312,6 @@
           <t>Apenas I, II, e III são verdadeiras.</t>
         </is>
       </c>
-      <c r="F920" t="inlineStr"/>
       <c r="G920" t="inlineStr">
         <is>
           <t>C</t>
@@ -52370,7 +52333,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K920" t="inlineStr"/>
       <c r="L920" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -52406,7 +52368,6 @@
           <t>o espaço controlado pelas instituições políticas e militares de um país.</t>
         </is>
       </c>
-      <c r="F921" t="inlineStr"/>
       <c r="G921" t="inlineStr">
         <is>
           <t>D</t>
@@ -52427,7 +52388,6 @@
           <t>Geografia</t>
         </is>
       </c>
-      <c r="K921" t="inlineStr"/>
       <c r="L921" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -52462,7 +52422,6 @@
           <t>A construção de grandes monumentos.</t>
         </is>
       </c>
-      <c r="F922" t="inlineStr"/>
       <c r="G922" t="inlineStr">
         <is>
           <t>B</t>
@@ -52483,7 +52442,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K922" t="inlineStr"/>
       <c r="L922" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -52519,7 +52477,6 @@
           <t>impedir o avanço do Império Bizantino no Oriente Médio.</t>
         </is>
       </c>
-      <c r="F923" t="inlineStr"/>
       <c r="G923" t="inlineStr">
         <is>
           <t>C</t>
@@ -52540,7 +52497,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K923" t="inlineStr"/>
       <c r="L923" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -52574,7 +52530,6 @@
           <t>Assembleias comerciais.</t>
         </is>
       </c>
-      <c r="F924" t="inlineStr"/>
       <c r="G924" t="inlineStr">
         <is>
           <t>A</t>
@@ -52595,7 +52550,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K924" t="inlineStr"/>
       <c r="L924" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -52630,7 +52584,6 @@
           <t>corporações de ofício.</t>
         </is>
       </c>
-      <c r="F925" t="inlineStr"/>
       <c r="G925" t="inlineStr">
         <is>
           <t>D</t>
@@ -52651,7 +52604,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K925" t="inlineStr"/>
       <c r="L925" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -52686,7 +52638,6 @@
           <t>descoberta de novas terras.</t>
         </is>
       </c>
-      <c r="F926" t="inlineStr"/>
       <c r="G926" t="inlineStr">
         <is>
           <t>C</t>
@@ -52707,7 +52658,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K926" t="inlineStr"/>
       <c r="L926" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -52742,7 +52692,6 @@
           <t>a descoberta de novas vacinas, o que permitiu aos europeus superar doenças fatais como a peste negra.</t>
         </is>
       </c>
-      <c r="F927" t="inlineStr"/>
       <c r="G927" t="inlineStr">
         <is>
           <t>C</t>
@@ -52763,7 +52712,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K927" t="inlineStr"/>
       <c r="L927" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -52798,7 +52746,6 @@
           <t>iniciou-se no século XIII e não provocou significativas mudanças no sistema e nas relações feudais vigentes.</t>
         </is>
       </c>
-      <c r="F928" t="inlineStr"/>
       <c r="G928" t="inlineStr">
         <is>
           <t>A</t>
@@ -52819,7 +52766,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K928" t="inlineStr"/>
       <c r="L928" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -52858,7 +52804,6 @@
           <t>forma de convencer os fiéis a participarem das expedições.</t>
         </is>
       </c>
-      <c r="F929" t="inlineStr"/>
       <c r="G929" t="inlineStr">
         <is>
           <t>D</t>
@@ -52879,7 +52824,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K929" t="inlineStr"/>
       <c r="L929" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -52915,7 +52859,6 @@
           <t>o processo de migração de comerciantes que viviam nos feudos para os burgos.</t>
         </is>
       </c>
-      <c r="F930" t="inlineStr"/>
       <c r="G930" t="inlineStr">
         <is>
           <t>D</t>
@@ -52936,7 +52879,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K930" t="inlineStr"/>
       <c r="L930" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -52972,7 +52914,6 @@
           <t>monopólio de determinadas atividades econômicas.</t>
         </is>
       </c>
-      <c r="F931" t="inlineStr"/>
       <c r="G931" t="inlineStr">
         <is>
           <t>D</t>
@@ -52993,7 +52934,6 @@
           <t>História</t>
         </is>
       </c>
-      <c r="K931" t="inlineStr"/>
       <c r="L931" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -53028,7 +52968,6 @@
           <t>Frágil</t>
         </is>
       </c>
-      <c r="F932" t="inlineStr"/>
       <c r="G932" t="inlineStr">
         <is>
           <t>C</t>
@@ -53049,7 +52988,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K932" t="inlineStr"/>
       <c r="L932" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -53084,7 +53022,6 @@
           <t>Nomear Poseidon.</t>
         </is>
       </c>
-      <c r="F933" t="inlineStr"/>
       <c r="G933" t="inlineStr">
         <is>
           <t>B</t>
@@ -53105,7 +53042,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K933" t="inlineStr"/>
       <c r="L933" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -53145,7 +53081,6 @@
           <t>Rapazinhos.</t>
         </is>
       </c>
-      <c r="F934" t="inlineStr"/>
       <c r="G934" t="inlineStr">
         <is>
           <t>B</t>
@@ -53166,7 +53101,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K934" t="inlineStr"/>
       <c r="L934" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -53201,7 +53135,6 @@
           <t>Substantivo comum, concreto.</t>
         </is>
       </c>
-      <c r="F935" t="inlineStr"/>
       <c r="G935" t="inlineStr">
         <is>
           <t>B</t>
@@ -53222,7 +53155,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K935" t="inlineStr"/>
       <c r="L935" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -53258,7 +53190,6 @@
           <t>Brilhantes</t>
         </is>
       </c>
-      <c r="F936" t="inlineStr"/>
       <c r="G936" t="inlineStr">
         <is>
           <t>D</t>
@@ -53279,7 +53210,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K936" t="inlineStr"/>
       <c r="L936" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -53329,7 +53259,6 @@
           <t>um substantivo concreto, pois indica o ser denominado.</t>
         </is>
       </c>
-      <c r="F937" t="inlineStr"/>
       <c r="G937" t="inlineStr">
         <is>
           <t>A</t>
@@ -53350,7 +53279,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K937" t="inlineStr"/>
       <c r="L937" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -53400,7 +53328,6 @@
           <t>sintagma verbal, por se referir à relação de posse entre a caneca e a água.</t>
         </is>
       </c>
-      <c r="F938" t="inlineStr"/>
       <c r="G938" t="inlineStr">
         <is>
           <t>B</t>
@@ -53421,7 +53348,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K938" t="inlineStr"/>
       <c r="L938" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -53457,7 +53383,6 @@
           <t>“interminável”, “prazerosas” e “diferentes”.</t>
         </is>
       </c>
-      <c r="F939" t="inlineStr"/>
       <c r="G939" t="inlineStr">
         <is>
           <t>D</t>
@@ -53478,7 +53403,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K939" t="inlineStr"/>
       <c r="L939" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -53516,7 +53440,6 @@
           <t>é parte integral do substantivo e não se refere necessariamente à sua dimensão.</t>
         </is>
       </c>
-      <c r="F940" t="inlineStr"/>
       <c r="G940" t="inlineStr">
         <is>
           <t>D</t>
@@ -53537,7 +53460,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K940" t="inlineStr"/>
       <c r="L940" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -53573,7 +53495,6 @@
           <t>de definição e concretização.</t>
         </is>
       </c>
-      <c r="F941" t="inlineStr"/>
       <c r="G941" t="inlineStr">
         <is>
           <t>C</t>
@@ -53594,7 +53515,6 @@
           <t>Português</t>
         </is>
       </c>
-      <c r="K941" t="inlineStr"/>
       <c r="L941" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -53628,7 +53548,6 @@
           <t>48</t>
         </is>
       </c>
-      <c r="F942" t="inlineStr"/>
       <c r="G942" t="inlineStr">
         <is>
           <t>B</t>
@@ -53652,7 +53571,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K942" t="inlineStr"/>
       <c r="L942" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -53688,7 +53606,6 @@
           <t>Apenas o participante 2, uma vez que a soma deve ser feita da direita para a esquerda.</t>
         </is>
       </c>
-      <c r="F943" t="inlineStr"/>
       <c r="G943" t="inlineStr">
         <is>
           <t>A</t>
@@ -53709,7 +53626,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K943" t="inlineStr"/>
       <c r="L943" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -53743,7 +53659,6 @@
           <t>0 e 1</t>
         </is>
       </c>
-      <c r="F944" t="inlineStr"/>
       <c r="G944" t="inlineStr">
         <is>
           <t>A</t>
@@ -53768,7 +53683,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K944" t="inlineStr"/>
       <c r="L944" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -53802,7 +53716,6 @@
           <t>Elemento Neutro.</t>
         </is>
       </c>
-      <c r="F945" t="inlineStr"/>
       <c r="G945" t="inlineStr">
         <is>
           <t>C</t>
@@ -53823,7 +53736,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K945" t="inlineStr"/>
       <c r="L945" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -53857,7 +53769,6 @@
           <t>60</t>
         </is>
       </c>
-      <c r="F946" t="inlineStr"/>
       <c r="G946" t="inlineStr">
         <is>
           <t>D</t>
@@ -53889,7 +53800,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K946" t="inlineStr"/>
       <c r="L946" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -53922,7 +53832,6 @@
           <t>420 figurinhas</t>
         </is>
       </c>
-      <c r="F947" t="inlineStr"/>
       <c r="G947" t="inlineStr">
         <is>
           <t>C</t>
@@ -53943,7 +53852,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K947" t="inlineStr"/>
       <c r="L947" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -53976,7 +53884,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="F948" t="inlineStr"/>
       <c r="G948" t="inlineStr">
         <is>
           <t>A</t>
@@ -53997,7 +53904,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K948" t="inlineStr"/>
       <c r="L948" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -54030,7 +53936,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="F949" t="inlineStr"/>
       <c r="G949" t="inlineStr">
         <is>
           <t>B</t>
@@ -54053,7 +53958,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K949" t="inlineStr"/>
       <c r="L949" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -54086,7 +53990,6 @@
           <t>R$ 60,00</t>
         </is>
       </c>
-      <c r="F950" t="inlineStr"/>
       <c r="G950" t="inlineStr">
         <is>
           <t>C</t>
@@ -54108,7 +54011,6 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K950" t="inlineStr"/>
       <c r="L950" t="inlineStr">
         <is>
           <t>7ano</t>
@@ -54141,7 +54043,6 @@
           <t>4 + (5+2) + 3x1 + 3x7</t>
         </is>
       </c>
-      <c r="F951" t="inlineStr"/>
       <c r="G951" t="inlineStr">
         <is>
           <t>D</t>
@@ -54162,8 +54063,5633 @@
           <t>Matemática</t>
         </is>
       </c>
-      <c r="K951" t="inlineStr"/>
       <c r="L951" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>As esponjas marinhas são animais aquáticos simples, pertencentes ao filo Porifera, conhecidos por seu corpo cheio de poros. Qual é a função principal desses poros?
+[img:ph02_cie_01.png]
+Disponível em: https://www.shutterstock.com/image-photo/yellow-tube-sea-sponge-aplysina-aerophoba-2340752989.</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>Permitir a entrada de nutrientes e oxigênio, além de expelir água.</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>Permitir a locomoção da esponja em busca de alimento.</t>
+        </is>
+      </c>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>Proteger a esponja contra predadores, fechando-se quando ameaçada.</t>
+        </is>
+      </c>
+      <c r="E952" t="inlineStr">
+        <is>
+          <t>Liberar toxinas na água para afastar outras espécies competidoras.</t>
+        </is>
+      </c>
+      <c r="G952" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H952" t="inlineStr">
+        <is>
+          <t>As esponjas marinhas, pertencentes ao filo Porifera, possuem um corpo cheio de poros, por onde entra a água rica em nutrientes e oxigênio. Dentro do corpo da esponja, a água circula e, posteriormente, é expelida pelo ósculo, após a retirada do que é necessário para a sua sobrevivência.</t>
+        </is>
+      </c>
+      <c r="I952" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J952" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="L952" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>Os platelmintos são vermes de corpo achatado que possuem um sistema digestório incompleto, com apenas uma abertura que serve tanto para a entrada de alimentos quanto para a eliminação de resíduos. Eles também possuem um sistema nervoso simples, com gânglios cerebrais e cordões nervosos.
+Que característica está presente nos platelmintos que não é encontrada nos nematelmintos?</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>Presença de ânus.</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>Corpo segmentado.</t>
+        </is>
+      </c>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>Sistema digestório incompleto.</t>
+        </is>
+      </c>
+      <c r="E953" t="inlineStr">
+        <is>
+          <t>Sistema circulatório fechado.</t>
+        </is>
+      </c>
+      <c r="G953" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H953" t="inlineStr">
+        <is>
+          <t>Os platelmintos possuem um sistema digestório incompleto, com apenas uma abertura, ao contrário dos nematódeos que têm um sistema digestório completo.</t>
+        </is>
+      </c>
+      <c r="I953" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J953" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="L953" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>São o grupo mais diverso do reino Animalia, incluindo insetos, aracnídeos e crustáceos. Uma característica marcante é a presença de um exoesqueleto quitinoso, que oferece proteção e suporte, mas precisa ser trocado periodicamente para permitir o crescimento do animal.
+O grupo descrito no trecho acima se trato dos</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>moluscos.</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>anelídeos</t>
+        </is>
+      </c>
+      <c r="D954" t="inlineStr">
+        <is>
+          <t>artrópodes.</t>
+        </is>
+      </c>
+      <c r="E954" t="inlineStr">
+        <is>
+          <t>equinodermos.</t>
+        </is>
+      </c>
+      <c r="G954" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H954" t="inlineStr">
+        <is>
+          <t>O grupo descrito são os artrópodes, que incluem insetos, aracnídeos e crustáceos. Eles possuem um exoesqueleto de quitina, que precisa ser trocado periodicamente durante o processo de muda para permitir o crescimento.</t>
+        </is>
+      </c>
+      <c r="I954" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J954" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="L954" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>As aves são animais que possuem diversas adaptações que as ajudam a sobreviver e a realizar atividades essenciais, como voar. O voo é uma habilidade que exige uma combinação de características físicas e fisiológicas especiais. Entre essas características, algumas são essenciais para que as aves possam se deslocar pelo ar de forma eficiente e rápida.
+Que característica das aves facilita o voo?</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>Ossos pneumáticos.</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>Garras finas.</t>
+        </is>
+      </c>
+      <c r="D955" t="inlineStr">
+        <is>
+          <t>Asas longas.</t>
+        </is>
+      </c>
+      <c r="E955" t="inlineStr">
+        <is>
+          <t>Penas impermeáveis.</t>
+        </is>
+      </c>
+      <c r="G955" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H955" t="inlineStr">
+        <is>
+          <t>As aves possuem ossos pneumáticos, que são ossos ocos e leves, mas ainda assim muito resistentes. Essa característica ajuda a reduzir o peso do corpo, facilitando o voo e permitindo que as aves utilizem menos energia para se manterem no ar.</t>
+        </is>
+      </c>
+      <c r="I955" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J955" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="L955" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>Com base na forma como regulam a temperatura de seus corpos, os animais podem ser classificados em dois grupos: ectotérmicos e endotérmicos.
+Qual é a principal diferença entre animais ectotérmicos e endotérmicos?</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>Os endotérmicos regulam a temperatura corporal internamente, enquanto os ectotérmicos dependem da temperatura do ambiente.</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>Os ectotérmicos têm pelos e penas para se aquecer, enquanto os endotérmicos não possuem tais estruturas.</t>
+        </is>
+      </c>
+      <c r="D956" t="inlineStr">
+        <is>
+          <t>Os endotérmicos só vivem em ambientes quentes, enquanto os ectotérmicos podem viver em qualquer ambiente.</t>
+        </is>
+      </c>
+      <c r="E956" t="inlineStr">
+        <is>
+          <t>Os ectotérmicos precisam se alimentar constantemente para manter sua temperatura, enquanto os endotérmicos se alimentam menos frequentemente.</t>
+        </is>
+      </c>
+      <c r="G956" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H956" t="inlineStr">
+        <is>
+          <t>Os animais endotérmicos mantêm uma temperatura corporal estável independentemente das condições ambientais, usando energia de seu metabolismo. Os animais ectotérmicos, por outro lado, ajustam sua temperatura de acordo com o ambiente em que estão.</t>
+        </is>
+      </c>
+      <c r="I956" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J956" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="L956" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>O Corpo de Bombeiros registrou 93.577 ocorrências de ferimentos com água-viva nesta temporada no litoral gaúcho. Na comparação com o verão passado, houve queda de 11,6%, quando 105.911 pessoas relataram queimaduras aos guarda-vidas. Segundo o major Isandré Antunes, chefe de assessoria de operações e Defesa Civil do Corpo de Bombeiros, as líderes no ranking de registros são as praias de Torres, Capão da Canoa e Tramandaí.
+Retirado de https://gauchazh.clicrbs.com.br/comportamento/verao/noticia/2020/02/ferimentos-com-agua-viva-caem-11-no-litoral-gaucho-ck72m08k80m6j01qd4l45zr78.html
+Os cnidários podem apresentar em seus tentáculos células urticantes conhecidas como:</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>cnidócitos, sendo que cada cnidócito possui uma medusa que abriga substâncias tóxicas.</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>cnidócitos, sendo que cada cnidócito possui um nematocisto que abriga substâncias tóxicas.</t>
+        </is>
+      </c>
+      <c r="D957" t="inlineStr">
+        <is>
+          <t>nematocisto, no qual cada nematocisto possui um cnidócito que abriga substâncias tóxicas.</t>
+        </is>
+      </c>
+      <c r="E957" t="inlineStr">
+        <is>
+          <t>nematocisto, no qual cada nematocisto possui um pólipo que abriga substâncias tóxicas.</t>
+        </is>
+      </c>
+      <c r="G957" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H957" t="inlineStr">
+        <is>
+          <t>As células urticantes dos cnidários são os cnidócitos. Cada cnidócito contém uma cápsula, o nematocisto. Dentro dessa cápsula, há um tubo enrolado com substâncias tóxicas que podem causar lesões na pele.</t>
+        </is>
+      </c>
+      <c r="I957" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J957" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="L957" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>A imagem a seguir é uma fotografia de um cnidário pertencente ao gênero Crossota e encontrado a grandes profundidades no oceano.
+[img:ph02_cie_07.jpg]
+Disponível em: &lt;http://mesosyn.com/Hydrozoa-05.jpg&gt;. Acesso em: 22 mai 2018.
+Sobre o animal da foto é correto afirmar que:</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>Ele está na fase assexuada.</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>Ele está na fase de medusa.</t>
+        </is>
+      </c>
+      <c r="D958" t="inlineStr">
+        <is>
+          <t>Ele está na fase de pólipo.</t>
+        </is>
+      </c>
+      <c r="E958" t="inlineStr">
+        <is>
+          <t>Ele está na forma de vida séssil.</t>
+        </is>
+      </c>
+      <c r="G958" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H958" t="inlineStr">
+        <is>
+          <t>Pela imagem é possível notar que o animal está na fase livre natante, então é uma medusa.</t>
+        </is>
+      </c>
+      <c r="I958" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J958" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="L958" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>Polvos, lulas, caracóis e bivalves são exemplos de moluscos que compartilham algumas características, porém apresentam diferenças como o hábitat em que vivem.
+Qual das seguintes características é comum a todos os animais citados?</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>Rádula.</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>Concha.</t>
+        </is>
+      </c>
+      <c r="D959" t="inlineStr">
+        <is>
+          <t>Tentáculos.</t>
+        </is>
+      </c>
+      <c r="E959" t="inlineStr">
+        <is>
+          <t>Corpo mole.</t>
+        </is>
+      </c>
+      <c r="G959" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H959" t="inlineStr">
+        <is>
+          <t>Os bivalves não possuem rádula, pois se alimentam por filtração. Polvos não têm concha externa nem interna. Caracóis e bivalves não possuem tentáculos, que são exclusivos dos cefalópodes (lulas, polvos e náutilos). Portanto, a única característica compartilhada por todos os animais citados é o corpo mole.</t>
+        </is>
+      </c>
+      <c r="I959" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J959" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="L959" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>Um biólogo encontra uma nova espécie de animal de aspecto vermiforme. A princípio, fica em dúvida se este é um representante do Filo Annelida ou Nematoda.
+Para decidir entre as duas opções, você recomendaria que ele examinasse a presença de:</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>simetria bilateral.</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>segmentação corporal.</t>
+        </is>
+      </c>
+      <c r="D960" t="inlineStr">
+        <is>
+          <t>sistema circulatório aberto.</t>
+        </is>
+      </c>
+      <c r="E960" t="inlineStr">
+        <is>
+          <t>sistema digestivo completo.</t>
+        </is>
+      </c>
+      <c r="G960" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H960" t="inlineStr">
+        <is>
+          <t>A segmentação corporal é uma característica importante para distinguir os dois grupos, uma vez que nematódeos não apresentam corpo formado por segmentos como os anelídeos.</t>
+        </is>
+      </c>
+      <c r="I960" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J960" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="L960" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>Os animais da imagem a seguir são invertebrados que compartilham de algumas características como a presença de exoesqueleto e membros articulados.
+[img:ph02_cie_10.jpg]
+Disponível em: &lt;https://alunosonline.uol.com.br/upload/conteudo_legenda/622cc0b84c7e1e197decb69c78e19985.jpg&gt;. Acesso em: 27 jul. 2018.
+Qual é o nome do grupo que compreende todos esses animais?</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>Insetos.</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>Anelídeos.</t>
+        </is>
+      </c>
+      <c r="D961" t="inlineStr">
+        <is>
+          <t>Crustáceos.</t>
+        </is>
+      </c>
+      <c r="E961" t="inlineStr">
+        <is>
+          <t>Artrópodes.</t>
+        </is>
+      </c>
+      <c r="G961" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H961" t="inlineStr">
+        <is>
+          <t>Os animais da imagem são todos artrópodes, invertebrados que possuem corpo segmentado, membros (apêndices) articulados e exoesqueleto de quitina.</t>
+        </is>
+      </c>
+      <c r="I961" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J961" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="L961" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>No século XVI, a chegada dos portugueses ao Brasil marcou o início de um processo de colonização que envolveu a exploração de recursos naturais e a ocupação de terras indígenas. Esse período foi caracterizado por intensos conflitos com os povos nativos, que resistiam à invasão de suas terras.
+Qual foi um dos primeiros produtos naturais explorados pelos portugueses no Brasil?</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>Ouro</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>Pau-brasil</t>
+        </is>
+      </c>
+      <c r="D962" t="inlineStr">
+        <is>
+          <t>Café</t>
+        </is>
+      </c>
+      <c r="E962" t="inlineStr">
+        <is>
+          <t>Algodão</t>
+        </is>
+      </c>
+      <c r="G962" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H962" t="inlineStr">
+        <is>
+          <t>O pau-brasil foi um dos primeiros recursos naturais explorados pelos portugueses após sua chegada ao Brasil. A madeira era valiosa para a produção de corantes e foi intensamente extraída no início da colonização.</t>
+        </is>
+      </c>
+      <c r="I962" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J962" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="L962" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>Durante o século XIX, a economia brasileira foi fortemente influenciada pelo cultivo do café. Esse período também foi marcado pelo uso intensivo de mão de obra escrava, que era fundamental para a produção e exportação do café.
+Em qual região do Brasil se concentrava a maior parte da economia cafeeira no século XIX?</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>Nordeste</t>
+        </is>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="D963" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="E963" t="inlineStr">
+        <is>
+          <t>Centro-Oeste</t>
+        </is>
+      </c>
+      <c r="G963" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H963" t="inlineStr">
+        <is>
+          <t>Os estados de São Paulo e Rio de Janeiro, localizados nessa região, foram os principais produtores de café durante o século XIX, impulsionando a economia local.</t>
+        </is>
+      </c>
+      <c r="I963" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J963" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="L963" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>A descoberta de novas fontes de exploração no interior do Brasil, no final do século XVII, provocou uma grande migração de pessoas do litoral para o interior. Esse movimento foi fundamental para a expansão territorial do Brasil, levando à criação de novas vilas e cidades nas regiões em questão.
+Qual atividade econômica incentivou a interiorização da colonização portuguesa no Brasil?</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>Agricultura</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>Pecuária</t>
+        </is>
+      </c>
+      <c r="D964" t="inlineStr">
+        <is>
+          <t>Comércio</t>
+        </is>
+      </c>
+      <c r="E964" t="inlineStr">
+        <is>
+          <t>Mineração</t>
+        </is>
+      </c>
+      <c r="G964" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H964" t="inlineStr">
+        <is>
+          <t>A descoberta de ouro no interior do Brasil levou à migração de pessoas e ao desenvolvimento de novas áreas, promovendo a interiorização da colonização portuguesa.</t>
+        </is>
+      </c>
+      <c r="I964" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J964" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="L964" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>A relação entre os povos indígenas e os colonizadores portugueses foi marcada por conflitos e resistência. Os indígenas lutaram para proteger suas terras e culturas, mas muitos foram dizimados. Esse processo de colonização teve um impacto devastador nas populações nativas.
+Qual foi um dos principais fatores que contribuíram para a dizimação dos povos indígenas após a chegada dos portugueses?</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>As doenças trazidas pelos europeus.</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>A aliança com outros povos indígenas.</t>
+        </is>
+      </c>
+      <c r="D965" t="inlineStr">
+        <is>
+          <t>A resistência militar indígena</t>
+        </is>
+      </c>
+      <c r="E965" t="inlineStr">
+        <is>
+          <t>A migração para o interior.</t>
+        </is>
+      </c>
+      <c r="G965" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H965" t="inlineStr">
+        <is>
+          <t>Os indígenas não tinham imunidade contra as doenças trazidas pelos colonizadores, como varíola e sarampo, o que resultou em um elevado número de mortes.</t>
+        </is>
+      </c>
+      <c r="I965" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J965" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="L965" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>A criação das capitanias hereditárias foi uma estratégia utilizada pela Coroa portuguesa  no vasto território brasileiro. As capitanias foram distribuídas entre nobres que tinham a responsabilidade de desenvolver a região e garantir a posse das terras. No entanto, muitas capitanias enfrentaram dificuldades e não prosperaram como esperado.
+O principal objetivo da criação das capitanias hereditárias no Brasil foi</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>administrar e colonizar o território.</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>promover o comércio com a África.</t>
+        </is>
+      </c>
+      <c r="D966" t="inlineStr">
+        <is>
+          <t>estabelecer missões religiosas.</t>
+        </is>
+      </c>
+      <c r="E966" t="inlineStr">
+        <is>
+          <t>desenvolver a mineração de ouro.</t>
+        </is>
+      </c>
+      <c r="G966" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H966" t="inlineStr">
+        <is>
+          <t>As capitanias hereditárias foram criadas para facilitar a administração e a colonização do Brasil, distribuindo terras entre nobres que deveriam desenvolvê-las.</t>
+        </is>
+      </c>
+      <c r="I966" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J966" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="L966" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>O Tratado de Tordesilhas, firmado em 1494 na América, dividiu as terras recém-descobertas entre</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>Inglaterra e França.</t>
+        </is>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>Espanha e Portugal.</t>
+        </is>
+      </c>
+      <c r="D967" t="inlineStr">
+        <is>
+          <t>Alemanha e Itália.</t>
+        </is>
+      </c>
+      <c r="E967" t="inlineStr">
+        <is>
+          <t>Espanha e Rússia.</t>
+        </is>
+      </c>
+      <c r="G967" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H967" t="inlineStr">
+        <is>
+          <t>O Tratado de Tordesilhas marca a divisão do mundo entre Portugal e Espanha, sendo que a porção leste do território ficou com Portugal e a porção oeste pertenceu à Espanha.</t>
+        </is>
+      </c>
+      <c r="I967" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J967" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="L967" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>Leia as afirmativas:
+I. Expedições armadas de colonos e de indígenas já integrados aos conquistadores, conhecidas como bandeiras, partiam da Vila de São Paulo em direção ao interior do território.
+II. O objetivo das bandeiras era aprisionar indígenas e encontrar pedras preciosas.
+III. As bandeiras foram as responsáveis pela interiorização do território no início da colonização.
+IV. Os jesuítas fundaram importantes povoados no território recém-colonizado.
+Assinale a alternativa que contenha as afirmativas corretas:</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>Apenas a I e a II estão corretas.</t>
+        </is>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>Apenas a I e a III estão corretas.</t>
+        </is>
+      </c>
+      <c r="D968" t="inlineStr">
+        <is>
+          <t>Apenas a II e a IV estão corretas.</t>
+        </is>
+      </c>
+      <c r="E968" t="inlineStr">
+        <is>
+          <t>Todas estão corretas.</t>
+        </is>
+      </c>
+      <c r="G968" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H968" t="inlineStr">
+        <is>
+          <t>As bandeiras, também conhecido como bandeirismo, marcam as expedições realizadas pelos bandeirantes com o objetivo de aprisionar indígenas e encontrar pedras preciosas no interior do Brasil. Os jesuítas foram responsáveis por fundar importantes povoados no território colonial.</t>
+        </is>
+      </c>
+      <c r="I968" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J968" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="L968" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>Sobre a formação do território brasileiro, é correto afirmar que</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>a formação do território brasileiro, da conquista europeia até nossos dias, expressa uma história de concentração fundiária.</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>as monoculturas predominaram no Brasil, como as culturas de cana, soja e feijão.</t>
+        </is>
+      </c>
+      <c r="D969" t="inlineStr">
+        <is>
+          <t>o processo de formação do território brasileiro atingiu somente o século XVI.</t>
+        </is>
+      </c>
+      <c r="E969" t="inlineStr">
+        <is>
+          <t>as legislações sobre o acesso à terra no Brasil tiveram um caráter essencialmente popular, buscando melhorar a condição de vida do trabalhador.</t>
+        </is>
+      </c>
+      <c r="G969" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H969" t="inlineStr">
+        <is>
+          <t>A formação do território brasileiro expressa uma história de concentração fundiária desde a sua origem.</t>
+        </is>
+      </c>
+      <c r="I969" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J969" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="L969" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>Assinale a alternativa correta acerca do processo de formação do território brasileiro.</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>Os bandeirantes formavam grupos que ocupavam o sertão nordestino no período colonial.</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>Os metais preciosos foram a primeira forma de exploração econômica no Brasil, sendo feita no litoral.</t>
+        </is>
+      </c>
+      <c r="D970" t="inlineStr">
+        <is>
+          <t>No século XIX, a produção de café foi utilizada para a ocupação de terras inexploradas, como o oeste paulista.</t>
+        </is>
+      </c>
+      <c r="E970" t="inlineStr">
+        <is>
+          <t>No século XVIII aconteceu a produção de cana-de-açúcar, junto com a exploração do pau-brasil.</t>
+        </is>
+      </c>
+      <c r="G970" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H970" t="inlineStr">
+        <is>
+          <t>O café constituiu um dos vários ciclos econômicos brasileiros que contribuíram na ocupação do território por não-nativos. O cultivo do café foi utilizado para a expansão da agricultura no oeste paulista que no século XIX ainda era densamente ocupados por indígenas e coberto de Mata Atlântica e Cerrado. Sempre lembrando que a ocupação do território de fez em detrimento da expulsão de indígenas de suas terras.</t>
+        </is>
+      </c>
+      <c r="I970" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J970" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="L970" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>“[...] O consumo de derivados de ___________ – rapadura, mel de engenho, melado e açúcar mascavo – é fortemente influenciado por hábitos regionais no Brasil e vem se ampliando na medida em que aumenta o consumo de produtos orgânicos e oriundos da agricultura familiar.”
+Qual produto brasileiro completa adequadamente a lacuna?</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>Café.</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>Fumo.</t>
+        </is>
+      </c>
+      <c r="D971" t="inlineStr">
+        <is>
+          <t>Cacau.</t>
+        </is>
+      </c>
+      <c r="E971" t="inlineStr">
+        <is>
+          <t>Cana de açúcar.</t>
+        </is>
+      </c>
+      <c r="G971" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H971" t="inlineStr">
+        <is>
+          <t>O produto que completa a lacuna é a cana de açúcar, plantada nos estados de São Paulo e Rio de Janeiro.</t>
+        </is>
+      </c>
+      <c r="I971" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J971" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="L971" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>Leia o texto a seguir.
+O conflito começou em 1337, quando o rei francês Felipe VI invadiu uma região no atual sul da França que na época pertencia à Inglaterra. A resposta do monarca britânico, Eduardo III, foi a invasão do país rival, dando início à disputa quase sem fim. As duas monarquias queriam expandir sua área de influência sobre feudos que até então tinham uma boa autonomia. Ou seja, por trás da guerra estava rolando o processo de centralização do poder na mão dos reis e a própria formação dos dois países. Isso influenciou na longa duração da disputa, pois guerras muito longas só são possíveis de ser mantidas com Estados bem organizados. 
+Disponível em: https://super.abril.com.br/mundo-estranho/qual-foi-a-guerra-mais-longa-da-historia. Acesso em: 23 out. 2024.
+Qual foi uma das principais consequências da Guerra dos Cem Anos para a organização política europeia?</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>A centralização do poder nas mãos dos monarcas.</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>A manutenção do poder dos senhores feudais.</t>
+        </is>
+      </c>
+      <c r="D972" t="inlineStr">
+        <is>
+          <t>O aumento da produção agrícola.</t>
+        </is>
+      </c>
+      <c r="E972" t="inlineStr">
+        <is>
+          <t>A estabilidade política e social.</t>
+        </is>
+      </c>
+      <c r="G972" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H972" t="inlineStr">
+        <is>
+          <t>As crises do século XIV, como a peste bubônica, a fome e sobretudo a Guerra dos Cem Anos, enfraqueceram o sistema feudal e contribuíram para a centralização do poder nas mãos dos monarcas.</t>
+        </is>
+      </c>
+      <c r="I972" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J972" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="L972" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>Leia o texto a seguir.
+No fim da Idade Média, uma pandemia matou dezenas de milhões de pessoas. A doença da vez era a peste bubônica, uma febre infecciosa causada pela bactéria Yersinia pestis e transmitida de roedores para humanos pela picada de pulgas infectadas. Foi um estrago e tanto: dizimou de 30% a 50% da população da Eurásia. 
+Disponível em: https://super.abril.com.br/ciencia/como-a-peste-bubonica-pode-influenciar-na-saude-dos-europeus-hoje/. Acesso em: 23 out. 2024.
+Um dos fatores que facilitou a rápida disseminação da peste bubônica na Europa foi a(o)</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>desenvolvimento de novas técnicas agrícolas.</t>
+        </is>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>alta densidade populacional nas cidades.</t>
+        </is>
+      </c>
+      <c r="D973" t="inlineStr">
+        <is>
+          <t>estabilidade política.</t>
+        </is>
+      </c>
+      <c r="E973" t="inlineStr">
+        <is>
+          <t>ausência de ratos nas áreas urbanas.</t>
+        </is>
+      </c>
+      <c r="G973" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H973" t="inlineStr">
+        <is>
+          <t>A alta densidade populacional nas cidades, juntamente com as más condições de higiene, facilitou a rápida disseminação da peste bubônica.</t>
+        </is>
+      </c>
+      <c r="I973" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J973" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="L973" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>Leia o texto a seguir.
+“A Guerra dos Cem Anos foi a última guerra feudal e também a primeira moderna. Ela foi dirigida por membros da aristocracia feudal no início do conflito e terminou como uma disputa entre Estados que já tinham exércitos nacionais”, diz Yone. Por isso, ela foi um grande marco no desenvolvimento europeu (principalmente na França) da ideia de nação, que unificou países antes divididos em territórios controlados por nobres. 
+NAVARRO, Roberto. O que foi a Guerra dos Cem Anos?. Disponível em: https://super.abril.com.br/mundo-estranho/o-que-foi-a-guerra-dos-cem-anos. Acesso em: 23 out. 2024.
+Qual impacto a Guerra dos Cem Anos na França?</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>A descentralização do poder.</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>O fortalecimento do sistema feudal.</t>
+        </is>
+      </c>
+      <c r="D974" t="inlineStr">
+        <is>
+          <t>O surgimento de um sentimento nacionalista.</t>
+        </is>
+      </c>
+      <c r="E974" t="inlineStr">
+        <is>
+          <t>A estabilidade econômica.</t>
+        </is>
+      </c>
+      <c r="G974" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H974" t="inlineStr">
+        <is>
+          <t>A Guerra dos Cem Anos contribuiu para o surgimento de um sentimento nacionalista entre os franceses, tendo lançado as bases para o surgimento do Estado moderno francês.</t>
+        </is>
+      </c>
+      <c r="I974" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J974" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="L974" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>Leia o texto a seguir.
+Mais de 100 juízes e especialistas participaram do julgamento de Joana por feitiçaria. Entre eles, apenas sete ingleses – todos os demais eram franceses. O interrogatório durou um mês. Dois pontos (discutíveis) condenaram a ré: as vozes, que viriam do diabo na interpretação dos magistrados; e o uso teimoso de vestes masculinas, inadmissível para uma dama da época. Condenada, Joana foi queimada viva aos 19 anos, em 30 de maio de 1431 
+SAYURI, Juliana. Quem foi Joana D'Arc?. Disponível em: https://super.abril.com.br/mundo-estranho/quem-foi-joana-darc. Acesso em: 23 out. 2024.
+Por que Joana D’Arc foi condenada e queimada na fogueira?</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>Por heresia e bruxaria.</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>Por roubo e assassinato.</t>
+        </is>
+      </c>
+      <c r="D975" t="inlineStr">
+        <is>
+          <t>Por traição ao rei da França.</t>
+        </is>
+      </c>
+      <c r="E975" t="inlineStr">
+        <is>
+          <t>Por deserção do exército francês.</t>
+        </is>
+      </c>
+      <c r="G975" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H975" t="inlineStr">
+        <is>
+          <t>Por conta de suas alegações de que ouvia "vozes", entendido pelos magistrados com uma prova da influência diabólica sobre ela, Joana D’Arc foi condenada e queimada na fogueira por heresia e bruxaria.</t>
+        </is>
+      </c>
+      <c r="I975" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J975" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="L975" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>Leia o texto a seguir.
+Em outros locais a situação camponesa não se alterou, ou até piorou, devido às crescentes exigências senhoriais resultantes das dificuldades daquela camada. Daí a eclosão de revoltas campesinas, algumas exigindo respeito aos velhos costumes, outras objetivando maiores direitos sobre as terras comunais.
+FRANCO JR, Hilário. A Idade Média, nascimento do Ocidente. São Paulo: Brasiliense, 2001, p. 129.
+O que motivou as revoltas camponesas no século XIV?</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>A melhoria das condições de vida no campo.</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>A superexploração e os altos tributos.</t>
+        </is>
+      </c>
+      <c r="D976" t="inlineStr">
+        <is>
+          <t>A paz e estabilidade política.</t>
+        </is>
+      </c>
+      <c r="E976" t="inlineStr">
+        <is>
+          <t>A abundância de alimentos.</t>
+        </is>
+      </c>
+      <c r="G976" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H976" t="inlineStr">
+        <is>
+          <t>As revoltas camponesas foram motivadas pela superexploração dos trabalhadores rurais e pela imposição de altos tributos pelos senhores feudais, que visavam garantir a continuidade da produção agrícola em meio às crises do século XIV.</t>
+        </is>
+      </c>
+      <c r="I976" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J976" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="L976" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>Ao longo do século XIV, a Europa passou por profundas transformações que levaram à crise do feudalismo. O texto a seguir retrata a “Grande Fome” que afetou as ilhas britânicas e a maior parte da Europa ocidental.
+Já no início do século, através de uma conjunção de fatores climáticos, como uma queda anormal de temperatura na Europa e grandes inundações ocorridas entre os anos de 1315 a 1317, as colheitas são perdidas. Com isso, ocorre na Cristandade o fenômeno conhecido como a ‘grande fome’. Nas Ilhas Britânicas, as consequências também são desastrosas e, por isso, alguns historiadores consideram-na a maior crise da agricultura inglesa desde a invasão normanda. O cronista dos Anais de Bermondsey “conta que os pobres comiam cachorros e gatos, o excremento das pombas e inclusive seus próprios filhos”
+SELVATICI, Monica. Igreja Católica e sentimento religioso na Inglaterra do século XIV. Pelotas. 2007.
+Uma causa para a fome no início do século XIV</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>foi a expansão muçulmana pela Europa.</t>
+        </is>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>foram as invasões bárbaras na Europa ocidental.</t>
+        </is>
+      </c>
+      <c r="D977" t="inlineStr">
+        <is>
+          <t>foi o deslocamento de camponeses para as cidades.</t>
+        </is>
+      </c>
+      <c r="E977" t="inlineStr">
+        <is>
+          <t>foi o intenso cultivo de soja pelos francos.</t>
+        </is>
+      </c>
+      <c r="G977" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H977" t="inlineStr">
+        <is>
+          <t>A partir do Renascimento Urbano, muitos trabalhadores rurais migraram para as cidades. Com pouca mão-de-obra e chuvas intensas que devastavam as plantações, o cultivo não era suficiente para atender à crescente população, gerando o que ficou conhecido como Grande Fome.</t>
+        </is>
+      </c>
+      <c r="I977" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J977" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="L977" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>Leia o texto a seguir.
+“Eu, Agnolo di Tura, conhecido por il Grasso, enterrei meus cinco filhinhos com minhas mãos (…); e não havia quem chorasse algum morto, uma vez que cada um esperava a [própria] morte”
+In: LISINI, A. e IACOMETTI, F. (org.). Rerum Italicarum sciptores. Cronache senesi, XV, 6,1, 1931-37, p. 555.
+O texto revela um aspecto trágico da disseminação da peste negra pela Europa que foi a alta mortalidade da população europeia em consequência da disseminação da doença. A peste negra</t>
+        </is>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>demorou para se espalhar pela Europa, pois o contato entre os habitantes dos diferentes feudos e reinos era raro.</t>
+        </is>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>chegou na Europa por conta do comércio com o Oriente e se disseminou rapidamente, em parte, por conta das movimentadas rotas comerciais.</t>
+        </is>
+      </c>
+      <c r="D978" t="inlineStr">
+        <is>
+          <t>espalhou-se pelo continente europeu a partir das invasões bárbaras e de muçulmanos após as derrotas dos cristãos nas Cruzadas.</t>
+        </is>
+      </c>
+      <c r="E978" t="inlineStr">
+        <is>
+          <t>afetou apenas a região da atual Itália, não afetando as demais áreas da Europa que seguiram se desenvolvendo.</t>
+        </is>
+      </c>
+      <c r="G978" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H978" t="inlineStr">
+        <is>
+          <t>O alto fluxo de pessoas viajando para fins comerciais, neste período, contribuiu para a disseminação da peste em uma vasta área territorial.</t>
+        </is>
+      </c>
+      <c r="I978" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J978" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="L978" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>Leia o texto a seguir.
+Muitos acreditavam que a Peste Negra veio aos homens por justa 'cólera divina', isto é, um sentimento de justiça que se atribui a Deus quando castiga as culpas dos homens. Já outros, com registros da época acusavam os judeus, os leprosos e os estrangeiros de terem disseminado os horrores causados pela peste negra. 
+ALVES, Gabriel e FERNANDES, Fabiana. IMPACTO DA PESTE NEGRA NA EUROPA. 2015.
+Conforme a peste matava cada vez mais pessoas na Europa, muitas teorias surgiram sobre as causas e origem da doença. Uma consequência dessas teorias na sociedade europeia do século XIV foi a</t>
+        </is>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>perseguição aos judeus, acusados de transmitirem a doença.</t>
+        </is>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>execução imediata dos contaminados e a cremação de seus corpos.</t>
+        </is>
+      </c>
+      <c r="D979" t="inlineStr">
+        <is>
+          <t>imigração de portugueses para a América para escapar da doença.</t>
+        </is>
+      </c>
+      <c r="E979" t="inlineStr">
+        <is>
+          <t>revolução camponesa que eliminou a aristocracia francesa.</t>
+        </is>
+      </c>
+      <c r="G979" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H979" t="inlineStr">
+        <is>
+          <t>O texto menciona os judeus como grupo perseguido após a epidemia de Peste Negra, já que a população católica buscava em Deus uma explicação para seu sofrimento.</t>
+        </is>
+      </c>
+      <c r="I979" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J979" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="L979" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>Leia o texto a seguir.
+Na França, os levantes camponeses ficaram conhecidos como jacqueries, devido ao fato de os camponeses serem chamados pejorativamente naquele país de “Jacques Bonhomme”, termo similar ao que hoje conhecemos como “João-ninguém” ou “Zé-povinho.
+SANTOS, Lenalda. e ALVARO. Bruno. A CRISE DA SOCIEDADE FEUDAL: OS SÉCULOS XIV E XV: Aula 8.
+As revoltas camponesas na França de 1358 ficaram conhecidas como “Jacqueries” e tiveram como resultado a</t>
+        </is>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>punição severa a todos os revoltosos e seus familiares.</t>
+        </is>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>conquista do direito ao arrendamento de terras pelos camponeses.</t>
+        </is>
+      </c>
+      <c r="D980" t="inlineStr">
+        <is>
+          <t>tomada de poder de dois feudos por comunas formadas por servos.</t>
+        </is>
+      </c>
+      <c r="E980" t="inlineStr">
+        <is>
+          <t>isenção de impostos para todo o campesinato francês.</t>
+        </is>
+      </c>
+      <c r="G980" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H980" t="inlineStr">
+        <is>
+          <t>As Revoltas Camponesas marcam o início da desarticulação do regime feudal, já que os servos passaram a lutar por direitos e, em muitos casos, conseguiram o pagamento de salário e o arrendamento de terras.</t>
+        </is>
+      </c>
+      <c r="I980" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J980" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="L980" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>Leia o texto a seguir.
+Uma característica da unificação da França foi o fato de que os reis franceses foram obrigados a travar uma dura luta não só contra os seus próprios vassalos, mas também contra inimigos do estrangeiro.
+Estes inimigos, nos séculos XIV e XV, os barões ingleses, que travaram guerras contra a França por um período de mais de cem anos (1337- 1453). No decurso desta guerra, deram-se revoltas camponesas em larga escala tanto em França como em Inglaterra, revoltas a que se podem atribuir as mesmas causas: os tremendos sacrifícios exigidos às massas por causa da guerra.
+MANFRED, A. Z. História do Mundo Volume I - O Mundo Antigo. Lisboa: Edições Sociais, 1977, p. 233. (Adaptado).
+O trecho acima trata da Guerra dos Cem Anos, e nele o autor observa que neste episódio</t>
+        </is>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>os governantes franceses e ingleses contavam com total apoio popular.</t>
+        </is>
+      </c>
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>houve uma aliança entre a França e a Inglaterra contra seus vizinhos europeus.</t>
+        </is>
+      </c>
+      <c r="D981" t="inlineStr">
+        <is>
+          <t>os camponeses, por meio de revoltas, tiveram uma importante influência na Guerra.</t>
+        </is>
+      </c>
+      <c r="E981" t="inlineStr">
+        <is>
+          <t>ocorreu uma descentralização do governo francês, enfraquecido pelos ataques ingleses.</t>
+        </is>
+      </c>
+      <c r="G981" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H981" t="inlineStr">
+        <is>
+          <t>Como pode ser observado no texto, durante a Guerra dos Cem Anos, além do embate entre França e Inglaterra, os governantes tiveram que se preocupar com as rebeliões internas lideradas por camponeses em decorrência, dentre outros motivos, de sua extrema exploração, fato esse que teve uma grande relevância durante o conflito.</t>
+        </is>
+      </c>
+      <c r="I981" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J981" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="L981" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>Leia um trecho do conto a seguir.
+Branca de neve
+Era uma vez Branca de Neve, uma princesinha muito bonita que morava com seu pai. Sua mãe havia morrido e o rei se casou novamente com uma bela moça.
+Entretanto, a nova esposa do rei era também muito vaidosa e má. Ela possuía um espelho mágico e todas as manhãs perguntava para ele: “Espelho, espelho meu, existe uma mulher mais bela do que eu?”
+E o espelho sempre respondia que ela era a mais bela de todas.
+Enquanto isso, Branca de Neve crescia e se tornava cada dia mais formosa, com a pele alva como a neve, os cabelos negros como a noite e a boca vermelha como o sangue.
+Assim, um dia, ao perguntar para o espelho, a madrasta recebeu como resposta: “Minha rainha, a senhora é realmente muito bela, mas agora Branca de Neve é a mais bonita de todas.”
+Disponível em: https://www.culturagenial.com/historias-infantis-contos-para-criancas/. Acesso em: 14 out. 2024. (Fragmento)
+Qual verbo do texto expressa uma ação recorrente no passado, isto é, habitual?</t>
+        </is>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>perguntar</t>
+        </is>
+      </c>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>se casou</t>
+        </is>
+      </c>
+      <c r="D982" t="inlineStr">
+        <is>
+          <t>respondia</t>
+        </is>
+      </c>
+      <c r="E982" t="inlineStr">
+        <is>
+          <t>recebeu</t>
+        </is>
+      </c>
+      <c r="G982" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H982" t="inlineStr">
+        <is>
+          <t>"Respondia" expressa uma ação habitual, pois indica que o espelho respondia a mesma coisa todas as manhãs. Já os verbos "se casou" (pretérito perfeito), "recebeu" (pretérito perfeito) e "perguntar" (infinitivo) não indicam ação habitual no passado.</t>
+        </is>
+      </c>
+      <c r="I982" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J982" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="L982" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>Leia o conto a seguir.
+A princesa e o sapo
+Era uma vez uma princesa que vivia em um reino muito distante. Ela passava as tardes brincando com sua bola de ouro nos jardins do castelo.
+Um dia a bola caiu dentro do lago e a princesa ficou muito triste. Nessa hora, surgiu um sapo que lhe perguntou o porquê de tamanha tristeza. Sabendo do ocorrido, o sapo então prometeu resgatar a bola da jovem, mas havia uma condição: que ela lhe desse um beijo.
+A princesa concordou, pois queria muito a bola. Entretanto, assim que teve o objeto em suas mãos, ela correu para o castelo sem ao menos agradecer.
+O sapo ficou muito frustrado e gritou:
+— Mas princesa, você me prometeu!
+A partir daí, o sapinho passou a acompanhar a princesa em todos os lugares, exigindo sua recompensa.
+Um dia, cansado, o sapo foi até o rei e disse:
+— A princesa me prometeu um beijo, pois resgatei sua bola de ouro. Mas ela não quer cumprir sua promessa.
+O rei chamou a filha e lhe disse que uma promessa real deve sempre ser cumprida. Assim, a princesa tomou coragem e, finalmente, beijou o sapo.
+Para sua surpresa, o sapo asqueroso se transformou em um lindo príncipe e os dois se apaixonaram, vivendo felizes para sempre.
+ Disponível em: https://www.culturagenial.com/historias-infantis-contos-para-criancas/. Acesso em: 14 out. 2024. (Fragmento)
+Qual das frases está correta quanto à concordância nominal e verbal?</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>A princesa e o sapo estava felizes.</t>
+        </is>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>A princesa e o sapo estavam felizes.</t>
+        </is>
+      </c>
+      <c r="D983" t="inlineStr">
+        <is>
+          <t>A princesa e o sapo estava feliz.</t>
+        </is>
+      </c>
+      <c r="E983" t="inlineStr">
+        <is>
+          <t>A princesa e o sapo estavam feliz.</t>
+        </is>
+      </c>
+      <c r="G983" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H983" t="inlineStr">
+        <is>
+          <t>A frase "A princesa e o sapo estavam felizes" está correta quanto à concordância nominal e verbal, pois o sujeito composto "A princesa e o sapo" exige o verbo no plural "estavam" e o adjetivo "felizes" também no plural.</t>
+        </is>
+      </c>
+      <c r="I983" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J983" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="L983" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>Leia o conto a seguir.
+A princesa e o sapo
+Era uma vez uma princesa que vivia em um reino muito distante. Ela passava as tardes brincando com sua bola de ouro nos jardins do castelo.
+Um dia a bola caiu dentro do lago e a princesa ficou muito triste. Nessa hora, surgiu um sapo que lhe perguntou o porquê de tamanha tristeza. Sabendo do ocorrido, o sapo então prometeu resgatar a bola da jovem, mas havia uma condição: que ela lhe desse um beijo.
+A princesa concordou, pois queria muito a bola. Entretanto, assim que teve o objeto em suas mãos, ela correu para o castelo sem ao menos agradecer.
+O sapo ficou muito frustrado e gritou:
+— Mas princesa, você me prometeu!
+A partir daí, o sapinho passou a acompanhar a princesa em todos os lugares, exigindo sua recompensa.
+Um dia, cansado, o sapo foi até o rei e disse:
+— A princesa me prometeu um beijo, pois resgatei sua bola de ouro. Mas ela não quer cumprir sua promessa.
+O rei chamou a filha e lhe disse que uma promessa real deve sempre ser cumprida. Assim, a princesa tomou coragem e, finalmente, beijou o sapo.
+Para sua surpresa, o sapo asqueroso se transformou em um lindo príncipe e os dois se apaixonaram, vivendo felizes para sempre.
+ Disponível em: https://www.culturagenial.com/historias-infantis-contos-para-criancas/. Acesso em: 14 out. 2024. (Fragmento)
+Qual alternativa apresenta corretamente a identificação dos sintagmas nominais e verbais na frase destacada?</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>[A princesa] (sintagma nominal), [concordou] (sintagma verbal), [queria muito] sintagma verbal [a bola] (sintagma nominal).</t>
+        </is>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>[A princesa] (sintagma nominal), [concordou] (sintagma verbal), [queria muito a bola] (sintagma verbal).</t>
+        </is>
+      </c>
+      <c r="D984" t="inlineStr">
+        <is>
+          <t>[A princesa] (sintagma nominal), [concordou] (sintagma verbal), [queria muito a bola] (sintagma nominal).</t>
+        </is>
+      </c>
+      <c r="E984" t="inlineStr">
+        <is>
+          <t>[A princesa] (sintagma nominal), [concordou] (sintagma verbal), [queria] (sintagma verbal), [muito a bola] (sintagma nominal).</t>
+        </is>
+      </c>
+      <c r="G984" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H984" t="inlineStr">
+        <is>
+          <t>Na frase "A princesa concordou, pois queria muito a bola.", "A princesa" é o sintagma nominal que funciona como sujeito, "concordou" é o sintagma verbal, "queria muito'' é um sintagma verbal e ''a bola" é o sintagma nominal que funciona como objeto direto.</t>
+        </is>
+      </c>
+      <c r="I984" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J984" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="L984" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>Leia o conto a seguir.
+O relógio
+O relógio de Nasrudin vivia marcando a hora errada.
+— Mas será que não dá pra fazer alguma coisa? - alguém comentou.
+— Fazer o que? - falou outra pessoa
+— Bem, o relógio nunca marca a hora certa. Qualquer coisa que se faça já será uma melhora.
+Narsudin deu um jeito de quebrar o relógio e ele parou.
+— Você tem toda razão - disse ele. - Agora já dá para sentir uma melhora.
+— Eu não quis dizer “qualquer coisa”, assim literalmente. Como é que agora o relógio pode estar melhor do que antes?
+— Bem, antes ele nunca marcava a hora certa. Agora, pelo menos, duas vezes por dia ele vai estar certo.
+Disponível em: www.culturagenial.com/contos-infantis-que-as-criancas-vao-adorar/. Acesso em: 14 out. 2024.
+A frase que apresenta um verbo no modo subjuntivo é:</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>“O relógio de Nasrudin vivia marcando a hora errada”.</t>
+        </is>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>“Narsudin deu um jeito de quebrar o relógio e ele parou”.</t>
+        </is>
+      </c>
+      <c r="D985" t="inlineStr">
+        <is>
+          <t>“Como é que agora o relógio pode estar melhor do que antes?”.</t>
+        </is>
+      </c>
+      <c r="E985" t="inlineStr">
+        <is>
+          <t>“Qualquer coisa que se faça já será uma melhora”.</t>
+        </is>
+      </c>
+      <c r="G985" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H985" t="inlineStr">
+        <is>
+          <t>Na frase "Qualquer coisa que se faça já será uma melhora.", o verbo "faça" está no modo subjuntivo, expressando uma ação hipotética ou incerta.</t>
+        </is>
+      </c>
+      <c r="I985" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J985" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="L985" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>O menino e o lobo
+Numa colina, acima de um povoado, estava um dia um pastorzinho. Entediado, o menino, para se divertir, começou a gritar para a aldeia lá embaixo:
+O lobo! O lobo! O lobo vem vindo!
+O truque funcionou. Fez isso três vezes ainda e, a cada vez, os moradores do vilarejo subiram correndo, colina acima, para ajudar o menino a salvar as ovelhas. Quando chegavam ao topo, o garoto caía na risada, e os homens ficaram furiosos, sentindo-se enganados.
+Infelizmente para o garoto, num dia cinzento e enevoado o lobo realmente apareceu, e se atirou direto para cima das ovelhas. O menino, a sério desta vez, começou aberrar:
+— O lobo está aqui! Acudam! O lobo está aqui!
+Ninguém atendeu ao chamado, pois os aldeões pensaram que se tratasse apenas de mais uma das brincadeiras do garoto - e o lobo devorou todas as ovelhas.
+Disponível em: https://www.culturagenial.com/contos-comentados-com-grandes-ensinamentos-para-criancas/. Acesso em: 14 out. 2024.
+Qual o tipo do numeral destacado no texto?</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>multiplicativo</t>
+        </is>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>fracionário</t>
+        </is>
+      </c>
+      <c r="D986" t="inlineStr">
+        <is>
+          <t>ordinal</t>
+        </is>
+      </c>
+      <c r="E986" t="inlineStr">
+        <is>
+          <t>cardinal</t>
+        </is>
+      </c>
+      <c r="G986" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H986" t="inlineStr">
+        <is>
+          <t>O numeral "três" é classificado como numeral cardinal, pois indica uma quantidade exata de vezes que o menino gritou "O lobo!" para enganar os aldeões.</t>
+        </is>
+      </c>
+      <c r="I986" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J986" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="L986" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>Indestrutível
+Eu sei que tudo vai ficar bem
+E as minhas lágrimas vão secar
+Eu sei que tudo vai ficar bem
+E essas feridas vão se curar
+O que me impede de sorrir
+É tudo o que eu já perdi
+Eu fechei os olhos e pedi
+Para quando abrir a dor não estar aqui
+Mas sei que não é fácil assim
+Mas vou aprender no fim
+Minhas mãos se unem para que
+Tirem do meu peito o que é de ruim
+E vou dizendo
+Tudo vai ficar bem
+E as minhas lágrimas vão secar
+Tudo vai ficar bem
+E essas feridas vão se curar
+E se eu recebo dor, te devolvo amor
+Se recebo dor, te devolvo amor
+E quanto mais dor recebo
+Mais percebo que eu sou
+Indestrutível
+VITTAR, Pabllo. Disponível em: &lt;https://www.vagalume.com.br/pabllo-vittar/indestrutivel.html&gt;. Acesso em: 17 set. 2017.
+ Nota-se na letra da canção a presença de um eu lírico que diz ser indestrutível diante da própria dor. Além do título, só se sabe dessa característica por meio de um verbo que expressa estado ao fim da letra.
+Tal uso verbal está presente nos versos:</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>“Mas sei que não é fácil assim / Mas vou aprender no fim”.</t>
+        </is>
+      </c>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>“O que me impede de sorrir / É tudo o que eu já perdi”.</t>
+        </is>
+      </c>
+      <c r="D987" t="inlineStr">
+        <is>
+          <t>“Mais percebo que eu sou / Indestrutível”.</t>
+        </is>
+      </c>
+      <c r="E987" t="inlineStr">
+        <is>
+          <t>“Eu fechei os olhos e pedi / Para quando abrir a dor não estar aqui”.</t>
+        </is>
+      </c>
+      <c r="G987" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H987" t="inlineStr">
+        <is>
+          <t>O verbo de ligação “ser” expressa um estado. No caso da canção, demonstra o estado do eu lírico de ser indestrutível perante sua dor.</t>
+        </is>
+      </c>
+      <c r="I987" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J987" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="L987" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>Indestrutível
+Eu sei que tudo vai ficar bem
+E as minhas lágrimas vão secar
+Eu sei que tudo vai ficar bem
+E essas feridas vão se curar
+O que me impede de sorrir
+É tudo o que eu já perdi
+Eu fechei os olhos e pedi
+Para quando abrir a dor não estar aqui
+Mas sei que não é fácil assim
+Mas vou aprender no fim
+Minhas mãos se unem para que
+Tirem do meu peito o que é de ruim
+E vou dizendo
+Tudo vai ficar bem
+E as minhas lágrimas vão secar
+Tudo vai ficar bem
+E essas feridas vão se curar
+E se eu recebo dor, te devolvo amor
+Se recebo dor, te devolvo amor
+E quanto mais dor recebo
+Mais percebo que eu sou
+Indestrutível
+VITTAR, Pabllo. Disponível em: &lt;https://www.vagalume.com.br/pabllo-vittar/indestrutivel.html&gt;. Acesso em: 17 set. 2017.
+ Para dar ao leitor a noção de certeza a respeito de suas decisões, o eu lírico utiliza predominantemente verbos no modo</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>subjuntivo, como “sei”, “vão” e “tirem”.</t>
+        </is>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>indicativo, como “vai”, “tirem” e “recebo”.</t>
+        </is>
+      </c>
+      <c r="D988" t="inlineStr">
+        <is>
+          <t>imperativo, como  “impede”, “pedi” e “devolvo”.</t>
+        </is>
+      </c>
+      <c r="E988" t="inlineStr">
+        <is>
+          <t>indicativo, como “percebo”, “impede” e “é”.</t>
+        </is>
+      </c>
+      <c r="G988" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H988" t="inlineStr">
+        <is>
+          <t>Verbos no modo indicativo, como “percebo”, “impede” e “é”, utilizados na canção, atribuem ideia de certeza, enquanto verbos no subjuntivo expressam incerteza.</t>
+        </is>
+      </c>
+      <c r="I988" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J988" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="L988" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>[img:ph02_por_08.png]
+Disponível em: http://3.bp.blogspot.com/-SqUWJo1K8iM/U_aaK8v2R0I/AAAAAAAABOs/OUOngrORVi8/s1600/images.jpg. Acesso em 15 dez. 2017.​
+ Para adequar a peça publicitária à norma padrão, o modo imperativo deve ser transformado em:</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>“Vens tu pra Caixa também!”</t>
+        </is>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>“Venha para a Caixa tu também!”</t>
+        </is>
+      </c>
+      <c r="D989" t="inlineStr">
+        <is>
+          <t>“Vem tu pra Caixa você também!”</t>
+        </is>
+      </c>
+      <c r="E989" t="inlineStr">
+        <is>
+          <t>“Venha para a Caixa você também!”</t>
+        </is>
+      </c>
+      <c r="G989" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H989" t="inlineStr">
+        <is>
+          <t>O verbo "vir" no modo imperativo deve estar de acordo com o sujeito "você", ou seja, a terceira pessoa do singular. Logo, de acordo com a norma padrão, a frase transforma-se em “Venha para a Caixa você também!”.</t>
+        </is>
+      </c>
+      <c r="I989" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J989" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="L989" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>[img:ph02_por_09.jpg]
+QUINO. Toda Mafalda. São Paulo: Martins Fontes, 2001.
+ O numeral utilizado por Mafalda no segundo quadrinho exprime a ideia de</t>
+        </is>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>multiplicidade (“um patrão”).</t>
+        </is>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>fracionamento (“três mil operários”).</t>
+        </is>
+      </c>
+      <c r="D990" t="inlineStr">
+        <is>
+          <t>posição em sequência (“um patrão”).</t>
+        </is>
+      </c>
+      <c r="E990" t="inlineStr">
+        <is>
+          <t>quantidade (“três mil operários”).</t>
+        </is>
+      </c>
+      <c r="G990" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H990" t="inlineStr">
+        <is>
+          <t>Mafalda utiliza o numeral cardinal com o objetivo de quantificar o número de operários.</t>
+        </is>
+      </c>
+      <c r="I990" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J990" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="L990" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>[img:ph02_por_10.jpg]
+QUINO. Toda Mafalda. São Paulo: Martins Fontes, 2001.
+ No terceiro quadrinho, Mafalda faz uso de uma interjeição após descobrir a possível utilidade do dedo indicador. Ao analisar o contexto da tirinha, compreende-se que a interjeição possui valor semântico de</t>
+        </is>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>decepção/tristeza.</t>
+        </is>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>alegria/felicidade.</t>
+        </is>
+      </c>
+      <c r="D991" t="inlineStr">
+        <is>
+          <t>espanto/surpresa.</t>
+        </is>
+      </c>
+      <c r="E991" t="inlineStr">
+        <is>
+          <t>terror/medo.</t>
+        </is>
+      </c>
+      <c r="G991" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H991" t="inlineStr">
+        <is>
+          <t>Mafalda fica surpresa/espantada ao perceber qual seria o uso do dedo indicador em relação ao desemprego.</t>
+        </is>
+      </c>
+      <c r="I991" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J991" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="L991" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>Um elevador de um shopping está no andar 0 (térreo). Ele desce até o andar oposto de 4 e depois sobe 7 andares. Qual é o andar onde ele está agora?</t>
+        </is>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>-7</t>
+        </is>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D992" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E992" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G992" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H992" t="inlineStr">
+        <is>
+          <t>O oposto de 4 é – 4, portanto, do térreo o elevador desce para o andar – 4 e sobe 7 andares, ou seja, – 4 + 7 = 3. Logo o elevador se encontra no andar 3.</t>
+        </is>
+      </c>
+      <c r="I992" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J992" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="L992" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>Um mergulhador está a – 15 metros de profundidade em um lago. Ele nada – 8 metros. Qual é a profundidade final, em metros, em que ele se encontra?</t>
+        </is>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>– 23</t>
+        </is>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>– 7</t>
+        </is>
+      </c>
+      <c r="D993" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E993" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G993" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H993" t="inlineStr">
+        <is>
+          <t>O mergulhador nada -8 metros a partir de – 15 metros: – 15 – 8 = – 23 metros.</t>
+        </is>
+      </c>
+      <c r="I993" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J993" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="L993" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>Paula estava jogando um jogo em que cada jogador começava no ponto 0 de uma reta numérica. Em sua primeira jogada, ela avançou 5 casas, depois recuou 8 casas e, por fim, avançou 4 casas.
+Em que ponto da reta numérica Paula terminou?</t>
+        </is>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>[img:ph02_mat_03_a.png]</t>
+        </is>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>[img:ph02_mat_03_b.png]</t>
+        </is>
+      </c>
+      <c r="D994" t="inlineStr">
+        <is>
+          <t>[img:ph02_mat_03_c.png]</t>
+        </is>
+      </c>
+      <c r="E994" t="inlineStr">
+        <is>
+          <t>[img:ph02_mat_03_d.png]</t>
+        </is>
+      </c>
+      <c r="G994" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H994" t="inlineStr">
+        <is>
+          <t>Paula começou no 0, avançou 5, recuou 8 e depois avançou 4: 0 + 5 – 8 + 4 = 1. Portanto, ela terminou no ponto 1.</t>
+        </is>
+      </c>
+      <c r="I994" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J994" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="L994" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>Uma cidade registrou as seguintes temperaturas ao longo de quatro dias de inverno: – 7 °C, – 2 °C, – 5 °C, 0 °C, – 3 °C.
+A alternativa que apresenta essas temperaturas ordenadas, respectivamente, da mais fria para a mais quente é:</t>
+        </is>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>– 7 °C, – 5 °C, – 3 °C, – 2 °C, 0 °C</t>
+        </is>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>0 °C, – 7 °C, – 5 °C, – 3 °C, – 2 °C</t>
+        </is>
+      </c>
+      <c r="D995" t="inlineStr">
+        <is>
+          <t>– 2 °C, – 3 °C, – 5 °C, – 7 °C, 0 °C</t>
+        </is>
+      </c>
+      <c r="E995" t="inlineStr">
+        <is>
+          <t>0 °C, – 2 °C, – 3 °C, – 5 °C, – 7 °C</t>
+        </is>
+      </c>
+      <c r="G995" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H995" t="inlineStr">
+        <is>
+          <t>A ordenação do menor para o maior deve respeitar a posição dos números negativos na reta numérica. Assim, a ordem é: – 7 °C, – 5 °C, – 3 °C, – 2 °C, 0 °C.</t>
+        </is>
+      </c>
+      <c r="I995" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J995" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="L995" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>Carlos tinha um saldo devedor de R$ 700 em sua conta bancária. Ele recebeu um pagamento de R$ 1000 e decidiu quitar toda a sua dívida. Após o pagamento, ele fez um saque de R$ 150.
+Qual é o saldo final da conta de Carlos?</t>
+        </is>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>R$ – 450,00</t>
+        </is>
+      </c>
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>R$ 150,00</t>
+        </is>
+      </c>
+      <c r="D996" t="inlineStr">
+        <is>
+          <t>R$ 450,00</t>
+        </is>
+      </c>
+      <c r="E996" t="inlineStr">
+        <is>
+          <t>R$ 1550,00</t>
+        </is>
+      </c>
+      <c r="G996" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H996" t="inlineStr">
+        <is>
+          <t>Carlos tinha uma dívida de setecentos reais, logo – 700. Recebendo R$ 1000 (+1000), e quitando sua dívida, ele fica com um saldo positivo de R$ 300 (– 700 + 1000 = 300). Após o saque de R$ 150, o saldo final é R$ 150 (300 – 150 = 150).</t>
+        </is>
+      </c>
+      <c r="I996" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J996" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="L996" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>Os números inteiros abaixo estão organizados em ordem crescente, com uma lacuna no lugar do terceiro número:
+– 20 ; – 11 ; ___ ; – 3 ; 0
+Dentre as alternativas abaixo, a única opção que contém um possível valor para a lacuna é:</t>
+        </is>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D997" t="inlineStr">
+        <is>
+          <t>– 7</t>
+        </is>
+      </c>
+      <c r="E997" t="inlineStr">
+        <is>
+          <t>– 12</t>
+        </is>
+      </c>
+      <c r="G997" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H997" t="inlineStr">
+        <is>
+          <t>O número da lacuna está entre – 11 e – 3, então ele deve ser um número inteiro negativo menor que – 3 e maior que – 11. As possíveis opções são: – 4, – 5, – 6, – 7, – 8, – 9 e – 10. Logo, entre as alternativas, a única que está entre – 11 e – 3 é: – 7</t>
+        </is>
+      </c>
+      <c r="I997" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J997" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="L997" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>Considere as afirmações de um aluno sobre os números inteiros:
+I. o simétrico de – 5 é igual ao módulo de 5.
+II. o módulo de – 3 é igual ao simétrico de 3.
+III. o módulo de 15 é igual ao oposto de – 15.
+IV. o oposto de – 9 é igual ao simétrico de 9.
+Quantas afirmativas estão corretas?</t>
+        </is>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D998" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E998" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G998" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H998" t="inlineStr">
+        <is>
+          <t>I. O simétrico de – 5 é 5 e o módulo de 5 também é, portanto, a afirmativa é verdadeira.
+II. O módulo de – 3 é 3 e o simétrico de 3 é – 3, portanto, a afirmativa é falsa.
+III. O módulo de 15 é 15 e o oposto de – 15 é 15, portanto, a afirmativa é verdadeira.
+IV. O oposto de – 9 é 9, e o simétrico de 9 é – 9, portanto, a afirmativa é falsa.
+Logo, 2 afirmações estão corretas.</t>
+        </is>
+      </c>
+      <c r="I998" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J998" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="L998" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>Ana está jogando dois dados diferentes alternadamente e anotando os números encontrados em um papel. Um dos dados ela modificou para serem números negativos. Ela obteve os seguintes números: 4; – 1; – 5; 1; 2; – 2; 5; – 6. A partir dessa sequência, Ana concluiu as seguintes afirmações:
+I. – 6 &gt; 5
+II. | –1 | = | 1 |
+III. – 2 &gt; – 1
+IV. | 4 | &lt; | – 5 |
+Quantas afirmações estão certas?</t>
+        </is>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C999" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D999" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E999" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G999" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H999" t="inlineStr">
+        <is>
+          <t>I. – 6 &gt; 5 está errado, pois nenhum número negativo será maior que um número positivo.
+II. | – 1 | = | 1 | está certo, pois o módulo de 1 e de – 1 é igual a 1 para os dois.
+III. – 2 &gt; – 1 está errado, pois o – 2 está mais a esquerda que o – 1 na reta numérica e, portanto, – 2 é menor que – 1.
+IV. | 4 | &lt; | – 5 | está certo, pois o módulo de 4 é 4 e o módulo de – 5 é 5, assim, 4 é menor que 5.</t>
+        </is>
+      </c>
+      <c r="I999" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J999" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="L999" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>Um prédio possui 15 andares: 12 acima do solo (incluindo o térreo) e 3 abaixo. No painel do elevador, todos os andares são identificados por números inteiros e sequenciais. O térreo é identificado pelo número zero, os andares abaixo do solo são identificados por números negativos, e os demais andares acima do solo, por números positivos.
+O andar mais alto e o mais baixo desse prédio são representados no painel do elevador, respectivamente, por</t>
+        </is>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>15 e 0.</t>
+        </is>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>12 e 0.</t>
+        </is>
+      </c>
+      <c r="D1000" t="inlineStr">
+        <is>
+          <t>12 e – 3.</t>
+        </is>
+      </c>
+      <c r="E1000" t="inlineStr">
+        <is>
+          <t>11 e – 3.</t>
+        </is>
+      </c>
+      <c r="G1000" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H1000" t="inlineStr">
+        <is>
+          <t>Como existem 12 andares acima do solo, incluindo o térreo, a numeração vai de 0 a 11 positivo. Já para os 3 andares abaixo do solo, a numeração vai de – 1 a – 3. Desta forma, o andar mais alto é representado por + 11 no elevador e o mais baixo por – 3.</t>
+        </is>
+      </c>
+      <c r="I1000" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J1000" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="L1000" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>Um cliente verificou seu saldo bancário ao final de cada mês do segundo semestre de um ano. Veja o balanço bancário:
+Julho: R$ 150,00
+Agosto: R$ 80,00
+Setembro: R$ 40,00
+Outubro: – R$ 2,00
+Novembro: – R$ 75,00
+Dezembro: – R$ 200,00
+Qual foi o mês com o maior saldo, em módulo, do extrato deste cliente?</t>
+        </is>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>Julho</t>
+        </is>
+      </c>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="D1001" t="inlineStr">
+        <is>
+          <t>Outubro</t>
+        </is>
+      </c>
+      <c r="E1001" t="inlineStr">
+        <is>
+          <t>Dezembro</t>
+        </is>
+      </c>
+      <c r="G1001" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H1001" t="inlineStr">
+        <is>
+          <t>Organizando os módulos dos saldos de cada mês tem-se:
+|–2| &lt; |40| &lt; |–75| &lt; |80| &lt; |150| &lt; |–200|
+Portanto, dezembro foi o mês com o maior saldo, em módulo.</t>
+        </is>
+      </c>
+      <c r="I1001" t="inlineStr">
+        <is>
+          <t>PH02</t>
+        </is>
+      </c>
+      <c r="J1001" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="L1001" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>As plantas são seres autotróficos, o que significa que elas conseguem produzir o próprio alimento através da fotossíntese. Qual das opções abaixo apresenta as condições necessárias para que a planta realize esse processo?</t>
+        </is>
+      </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>Luz, água e gás carbônico.</t>
+        </is>
+      </c>
+      <c r="C1002" t="inlineStr">
+        <is>
+          <t>Água, minerais e oxigênio.</t>
+        </is>
+      </c>
+      <c r="D1002" t="inlineStr">
+        <is>
+          <t>Oxigênio, luz e gás carbônico.</t>
+        </is>
+      </c>
+      <c r="E1002" t="inlineStr">
+        <is>
+          <t>Minerais, gás carbônico e temperatura baixa.</t>
+        </is>
+      </c>
+      <c r="F1002" t="inlineStr"/>
+      <c r="G1002" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H1002" t="inlineStr">
+        <is>
+          <t>As plantas necessitam de luz solar, água e gás carbônico para realizar a fotossíntese, o processo pelo qual produzem seu alimento. Esse processo libera oxigênio como subproduto.</t>
+        </is>
+      </c>
+      <c r="I1002" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J1002" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K1002" t="inlineStr"/>
+      <c r="L1002" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>As briófitas são um grupo de plantas que vivem em locais úmidos. Por que essas plantas dependem de água para a reprodução?</t>
+        </is>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>Porque a água ajuda na dispersão das sementes.</t>
+        </is>
+      </c>
+      <c r="C1003" t="inlineStr">
+        <is>
+          <t>Porque o esporo depende da água para germinar.</t>
+        </is>
+      </c>
+      <c r="D1003" t="inlineStr">
+        <is>
+          <t>Porque precisam absorver nutrientes diretamente do ambiente.</t>
+        </is>
+      </c>
+      <c r="E1003" t="inlineStr">
+        <is>
+          <t>Porque essas plantas dependem da água para se reproduzirem.</t>
+        </is>
+      </c>
+      <c r="F1003" t="inlineStr"/>
+      <c r="G1003" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H1003" t="inlineStr">
+        <is>
+          <t>As briófitas dependem da água para que seus gametas masculinos possam nadar até os gametas femininos para a fecundação.</t>
+        </is>
+      </c>
+      <c r="I1003" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J1003" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K1003" t="inlineStr"/>
+      <c r="L1003" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>A principal característica que diferencia as gimnospermas de outros grupos de plantas é a</t>
+        </is>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>ausência de sementes.</t>
+        </is>
+      </c>
+      <c r="C1004" t="inlineStr">
+        <is>
+          <t>presença de flores coloridas.</t>
+        </is>
+      </c>
+      <c r="D1004" t="inlineStr">
+        <is>
+          <t>presença de sementes nuas.</t>
+        </is>
+      </c>
+      <c r="E1004" t="inlineStr">
+        <is>
+          <t>presença de vasos condutores.</t>
+        </is>
+      </c>
+      <c r="F1004" t="inlineStr"/>
+      <c r="G1004" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H1004" t="inlineStr">
+        <is>
+          <t>As gimnospermas são plantas que possuem sementes expostas, ao contrário das angiospermas, cujas sementes são envolvidas por frutos.</t>
+        </is>
+      </c>
+      <c r="I1004" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J1004" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K1004" t="inlineStr"/>
+      <c r="L1004" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>As angiospermas são plantas que se destacam por apresentar frutos. Qual é a função principal dos frutos para essas plantas?</t>
+        </is>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>Absorver água e nutrientes do solo.</t>
+        </is>
+      </c>
+      <c r="C1005" t="inlineStr">
+        <is>
+          <t>Facilitar a polinização pelos insetos.</t>
+        </is>
+      </c>
+      <c r="D1005" t="inlineStr">
+        <is>
+          <t>Proteger as sementes e auxiliar na sua dispersão.</t>
+        </is>
+      </c>
+      <c r="E1005" t="inlineStr">
+        <is>
+          <t>Realizar a fotossíntese para gerar energia para a planta.</t>
+        </is>
+      </c>
+      <c r="F1005" t="inlineStr"/>
+      <c r="G1005" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H1005" t="inlineStr">
+        <is>
+          <t>Os frutos protegem as sementes e, em muitos casos, ajudam na dispersão, garantindo que as sementes alcancem locais favoráveis para germinar.</t>
+        </is>
+      </c>
+      <c r="I1005" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J1005" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K1005" t="inlineStr"/>
+      <c r="L1005" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>Qual das seguintes estruturas das plantas é responsável pela absorção de água e nutrientes do solo?</t>
+        </is>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>As flores.</t>
+        </is>
+      </c>
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>As raízes.</t>
+        </is>
+      </c>
+      <c r="D1006" t="inlineStr">
+        <is>
+          <t>As folhas.</t>
+        </is>
+      </c>
+      <c r="E1006" t="inlineStr">
+        <is>
+          <t>Os estômatos.</t>
+        </is>
+      </c>
+      <c r="F1006" t="inlineStr"/>
+      <c r="G1006" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H1006" t="inlineStr">
+        <is>
+          <t>As raízes são estruturas essenciais das plantas, pois são responsáveis por absorver água e nutrientes do solo, fornecendo os recursos necessários para a sobrevivência e o crescimento da planta.</t>
+        </is>
+      </c>
+      <c r="I1006" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J1006" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K1006" t="inlineStr"/>
+      <c r="L1006" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>A laranjeira é um vegetal pertencente ao grupo das ___________. A laranja é o (a) _______ dessa árvore, sendo uma estrutura ligada à ___________ dessa planta.
+Marque a alternativa correta que completa a frase acima.</t>
+        </is>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>angiospermas, flor, respiração.</t>
+        </is>
+      </c>
+      <c r="C1007" t="inlineStr">
+        <is>
+          <t>angiospermas, fruto, reprodução.</t>
+        </is>
+      </c>
+      <c r="D1007" t="inlineStr">
+        <is>
+          <t>gimnospermas, flor, reprodução.</t>
+        </is>
+      </c>
+      <c r="E1007" t="inlineStr">
+        <is>
+          <t>gimnospermas, fruto, fotossíntese.</t>
+        </is>
+      </c>
+      <c r="F1007" t="inlineStr"/>
+      <c r="G1007" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H1007" t="inlineStr">
+        <is>
+          <t>A laranjeira é uma planta representante das angiospermas e apresenta flores e frutos. A laranja é o fruto dessa planta, sendo uma estrutura ligada à reprodução.</t>
+        </is>
+      </c>
+      <c r="I1007" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J1007" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K1007" t="inlineStr"/>
+      <c r="L1007" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>[img:ph03_cie_07.png]
+De acordo com a imagem acima é correto afirmar que a seiva</t>
+        </is>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>bruta é constituída de água e sais minerais absorvidos pela raiz e é transportada através do xilema para as folhas.</t>
+        </is>
+      </c>
+      <c r="C1008" t="inlineStr">
+        <is>
+          <t>elaborada é constituída de água e sais minerais absorvidos pela folha e é transportada através do xilema para a raiz.</t>
+        </is>
+      </c>
+      <c r="D1008" t="inlineStr">
+        <is>
+          <t>bruta é constituída de substâncias orgânicas e água e é transportada da raiz até a folha através do floema.</t>
+        </is>
+      </c>
+      <c r="E1008" t="inlineStr">
+        <is>
+          <t>elaborada é constituída de substâncias orgânicas e água, produzidas pelas folhas e é transportada até a raiz através do xilema.</t>
+        </is>
+      </c>
+      <c r="F1008" t="inlineStr"/>
+      <c r="G1008" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H1008" t="inlineStr">
+        <is>
+          <t>A seiva bruta é constituída de água e sais minerais absorvidos do solo pela raiz e é transportada através do xilema para as folhas. Já a seiva elaborada é constituída de substâncias orgânicas dissolvidas na água e é transportada das folhas até a raiz através do floema.</t>
+        </is>
+      </c>
+      <c r="I1008" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J1008" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K1008" t="inlineStr"/>
+      <c r="L1008" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>As pteridófitas, como as samambaias, são plantas que possuem vasos condutores. Qual dessas características diferencia as pteridófitas das briófitas?</t>
+        </is>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>As pteridófitas possuem flores para reprodução.</t>
+        </is>
+      </c>
+      <c r="C1009" t="inlineStr">
+        <is>
+          <t>As pteridófitas dependem de fungos para sobreviver.</t>
+        </is>
+      </c>
+      <c r="D1009" t="inlineStr">
+        <is>
+          <t>As pteridófitas vivem apenas em ambientes aquáticos.</t>
+        </is>
+      </c>
+      <c r="E1009" t="inlineStr">
+        <is>
+          <t>As pteridófitas têm vasos condutores para transportar água e nutrientes.</t>
+        </is>
+      </c>
+      <c r="F1009" t="inlineStr"/>
+      <c r="G1009" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H1009" t="inlineStr">
+        <is>
+          <t>Diferente das briófitas, que não possuem vasos condutores, as pteridófitas conseguem transportar água e nutrientes pelo corpo da planta usando vasos especializados (xilema e floema).</t>
+        </is>
+      </c>
+      <c r="I1009" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J1009" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K1009" t="inlineStr"/>
+      <c r="L1009" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>As flores que são polinizadas por animais apresentam pétalas vistosas, perfume e néctar. O beija-flor possui o bico alongado, o que facilita sua alimentação de néctar. Ele pode ser considerado um agente polinizador pois</t>
+        </is>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>transporta grãos de pólen da antera até o estigma de outra flor.</t>
+        </is>
+      </c>
+      <c r="C1010" t="inlineStr">
+        <is>
+          <t>transporta gametas masculinos até a antera de outra flor.</t>
+        </is>
+      </c>
+      <c r="D1010" t="inlineStr">
+        <is>
+          <t>transporta núcleo vegetativo até o filete de outra flor.</t>
+        </is>
+      </c>
+      <c r="E1010" t="inlineStr">
+        <is>
+          <t>transporta estames até a oosfera de outra flor.</t>
+        </is>
+      </c>
+      <c r="F1010" t="inlineStr"/>
+      <c r="G1010" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H1010" t="inlineStr">
+        <is>
+          <t>O grão de pólen é produzido na flor masculina e nele contém o gameta masculino (núcleo espermático) e o núcleo vegetativo. O beija-flor leva essa estrutura até o estigma de uma flor feminina, onde o tubo polínico é formado e ocorre o encontro dos gametas (fecundação).</t>
+        </is>
+      </c>
+      <c r="I1010" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J1010" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K1010" t="inlineStr"/>
+      <c r="L1010" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>Os frutos contribuem para a dispersão das sementes na natureza, favorecendo a conquista de novos territórios pelas angiospermas.
+Sobre a dispersão das sementes das angiospermas, marque a alternativa correta.</t>
+        </is>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>Os frutos, que carregam as sementes, são opacos, secos e duros, o que desfavorece a dispersão das sementes pelos animais.</t>
+        </is>
+      </c>
+      <c r="C1011" t="inlineStr">
+        <is>
+          <t>As angiospermas são dispersas, principalmente, pelos animais e vento.</t>
+        </is>
+      </c>
+      <c r="D1011" t="inlineStr">
+        <is>
+          <t>As sementes que são dispersas pelo vento são pesadas e podem possuir espinhos.</t>
+        </is>
+      </c>
+      <c r="E1011" t="inlineStr">
+        <is>
+          <t>Algumas sementes são dispersas a partir da adesão aos pelos de alguns animais, como acontece com os dentes-de-leão.</t>
+        </is>
+      </c>
+      <c r="F1011" t="inlineStr"/>
+      <c r="G1011" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H1011" t="inlineStr">
+        <is>
+          <t>As sementes das angiospermas são dispersas principalmente pelos animais e pelo vento. A dispersão feita pelo vento ocorre com sementes leves; a dispersão por animais ocorre geralmente com os frutos comestíveis, suculentos, coloridos e com odor agradável.</t>
+        </is>
+      </c>
+      <c r="I1011" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J1011" t="inlineStr">
+        <is>
+          <t>Ciências</t>
+        </is>
+      </c>
+      <c r="K1011" t="inlineStr"/>
+      <c r="L1011" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>A exploração mineral ilegal no Brasil é um problema grave que envolve agentes armados, garimpeiros e até políticos. Entre 2016 e 2021, o avanço do garimpo ilegal em terras indígenas cresceu significativamente.
+Quais são os principais impactos da exploração mineral ilegal em terras indígenas no Brasil?</t>
+        </is>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>Aumento da biodiversidade e melhoria das condições de vida.</t>
+        </is>
+      </c>
+      <c r="C1012" t="inlineStr">
+        <is>
+          <t>Redução da pobreza e melhoria na infraestrutura.</t>
+        </is>
+      </c>
+      <c r="D1012" t="inlineStr">
+        <is>
+          <t>Desenvolvimento sustentável e preservação cultural.</t>
+        </is>
+      </c>
+      <c r="E1012" t="inlineStr">
+        <is>
+          <t>Conflitos violentos e danos ambientais severos.</t>
+        </is>
+      </c>
+      <c r="F1012" t="inlineStr"/>
+      <c r="G1012" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H1012" t="inlineStr">
+        <is>
+          <t>A exploração mineral ilegal em terras indígenas no Brasil causa conflitos violentos e danos ambientais severos, afetando negativamente as comunidades locais.</t>
+        </is>
+      </c>
+      <c r="I1012" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J1012" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K1012" t="inlineStr"/>
+      <c r="L1012" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>Os escudos cristalinos brasileiros são estruturas geológicas antigas formadas por rochas cristalinas e metamórficas. Essas estruturas ocupam cerca de um terço do território brasileiro e contêm alumínio, manganês, ferro, ouro, nióbio e cobre.
+Quais tipos de minerais são comumente encontrados nos escudos cristalinos brasileiros?</t>
+        </is>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>Minerais não metálicos.</t>
+        </is>
+      </c>
+      <c r="C1013" t="inlineStr">
+        <is>
+          <t>Combustíveis fósseis.</t>
+        </is>
+      </c>
+      <c r="D1013" t="inlineStr">
+        <is>
+          <t>Minerais metálicos.</t>
+        </is>
+      </c>
+      <c r="E1013" t="inlineStr">
+        <is>
+          <t>Minerais radioativos.</t>
+        </is>
+      </c>
+      <c r="F1013" t="inlineStr"/>
+      <c r="G1013" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H1013" t="inlineStr">
+        <is>
+          <t>Os escudos cristalinos brasileiros contêm principalmente minerais metálicos, como alumínio, manganês, ferro, ouro, nióbio e cobre.</t>
+        </is>
+      </c>
+      <c r="I1013" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J1013" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K1013" t="inlineStr"/>
+      <c r="L1013" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>A atualização cartográfica do Quadrilátero Ferrífero em Minas Gerais favorece a descoberta de novas jazidas de ouro. A correção das distorções nos mapas permite uma pesquisa geológica mais precisa, aumentando a segurança para os investidores na atividade mineradora.
+Por que a atualização cartográfica do Quadrilátero Ferrífero é importante para a mineração?</t>
+        </is>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>Facilita a descoberta de novas jazidas minerais.</t>
+        </is>
+      </c>
+      <c r="C1014" t="inlineStr">
+        <is>
+          <t>Reduz o custo da mineração.</t>
+        </is>
+      </c>
+      <c r="D1014" t="inlineStr">
+        <is>
+          <t>Aumenta a quantidade de minério extraído.</t>
+        </is>
+      </c>
+      <c r="E1014" t="inlineStr">
+        <is>
+          <t>Elimina a necessidade de pesquisas geológicas.</t>
+        </is>
+      </c>
+      <c r="F1014" t="inlineStr"/>
+      <c r="G1014" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H1014" t="inlineStr">
+        <is>
+          <t>A atualização cartográfica corrige distorções nos mapas, facilitando a descoberta de novas jazidas minerais e aumentando a segurança para os investidores.</t>
+        </is>
+      </c>
+      <c r="I1014" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J1014" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K1014" t="inlineStr"/>
+      <c r="L1014" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>As tragédias socioambientais em Mariana e Brumadinho, ambas em Minas Gerais, envolveram rejeitos de mineração. Esses eventos resultaram em grandes danos ambientais e sociais, incluindo mortes, desalojamentos e contaminação de rios e solos.
+Qual foi a causa comum das tragédias em Mariana e Brumadinho?</t>
+        </is>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>Terremotos.</t>
+        </is>
+      </c>
+      <c r="C1015" t="inlineStr">
+        <is>
+          <t>Rompimento de barragens.</t>
+        </is>
+      </c>
+      <c r="D1015" t="inlineStr">
+        <is>
+          <t>Erupções vulcânicas.</t>
+        </is>
+      </c>
+      <c r="E1015" t="inlineStr">
+        <is>
+          <t>Inundações naturais.</t>
+        </is>
+      </c>
+      <c r="F1015" t="inlineStr"/>
+      <c r="G1015" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H1015" t="inlineStr">
+        <is>
+          <t>Ambas as tragédias foram causadas pelo rompimento de barragens de rejeitos de mineração, resultando em graves danos ambientais e sociais.</t>
+        </is>
+      </c>
+      <c r="I1015" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J1015" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K1015" t="inlineStr"/>
+      <c r="L1015" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>A mineração é uma atividade fundamental para o Brasil, que possui uma grande diversidade de rochas ricas em minérios, como ouro, ferro, petróleo, cobre e alumínio. Esses recursos são essenciais para diversas indústrias e têm um valor econômico significativo. No entanto, a exploração mineral também pode causar graves problemas socioambientais.
+Um dos principais problemas socioambientais causados pela exploração mineral no Brasil é o(a):</t>
+        </is>
+      </c>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>Aumento da biodiversidade.</t>
+        </is>
+      </c>
+      <c r="C1016" t="inlineStr">
+        <is>
+          <t>Desmatamento.</t>
+        </is>
+      </c>
+      <c r="D1016" t="inlineStr">
+        <is>
+          <t>Melhoria na qualidade do ar.</t>
+        </is>
+      </c>
+      <c r="E1016" t="inlineStr">
+        <is>
+          <t>Crescimento da população indígena.</t>
+        </is>
+      </c>
+      <c r="F1016" t="inlineStr"/>
+      <c r="G1016" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H1016" t="inlineStr">
+        <is>
+          <t>A exploração mineral pode causar desmatamento, que é um dos principais problemas socioambientais associados a essa atividade.</t>
+        </is>
+      </c>
+      <c r="I1016" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J1016" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K1016" t="inlineStr"/>
+      <c r="L1016" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>Texto I
+O Ministério Público de Minas Gerais (MPMG) denunciou, nesta terça-feira (21), Fabio Schvartsman, ex-presidente da Vale, mais 15 pessoas pelo crime de homicídio doloso, aquele em que há a intenção de matar. Elas também vão responder por crime ambiental, assim como as empresas Vale e TÜV SÜD
+[...]
+A barragem I da Mina do Córrego do Feijão se rompeu quase um ano atrás, no dia 25 de janeiro de 2019, deixando 270 vítimas. Destas, 259 foram identificadas pela Polícia Civil de Minas Gerais. Os bombeiros procuram 11 desaparecidos, na maior operação de buscas do país.
+[...]
+RAGAZZI, Lucas. ZUBA, Fernando. Portal G1. Disponível em:&lt;
+https://g1.globo.com/mg/minas-gerais/noticia/2020/01/21/mp-denuncia-ex-presidente-da-vale-mais-15-pessoas-e-duas-empresas-porhomicidio-doloso.ghtml&gt;. Acesso em: 22 jan.2020.
+Texto II​
+Viver em um território que tenha em seu subsolo grandes reservas de ouro pode parecer uma benção e um sinônimo de riqueza. Infelizmente, para os Yanomami, esta situação tem sido a sua maior maldição. Um estudo recente conduzido pela Fundação Oswaldo Cruz (Fiocruz), em parceria com o Instituto Socioambiental (ISA), mostra que a contínua invasão ilegal de garimpeiros em seu território tem trazido graves consequências: algumas aldeias chegam a ter 92% das pessoas examinadas contaminadas por mercúrio.
+[...]
+Disponível em:&lt; https://www.socioambiental.org/pt-br/noticias-socioambientais/o-povo-yanomami-esta-contaminado-por-mercurio-dogarimpo&gt;. Acesso em: 22 jan.2020.
+Considerando as notícias trazidas, percebe-se</t>
+        </is>
+      </c>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>os ganhos sociais absolutos da mineração.</t>
+        </is>
+      </c>
+      <c r="C1017" t="inlineStr">
+        <is>
+          <t>a perda de espaço econômico do setor mineral.</t>
+        </is>
+      </c>
+      <c r="D1017" t="inlineStr">
+        <is>
+          <t>os raros impactos ambientais da atividade minerária.</t>
+        </is>
+      </c>
+      <c r="E1017" t="inlineStr">
+        <is>
+          <t>a necessidade de regulamentação social da mineração.</t>
+        </is>
+      </c>
+      <c r="F1017" t="inlineStr"/>
+      <c r="G1017" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H1017" t="inlineStr">
+        <is>
+          <t>A ocorrência de vários eventos negativos envolvendo o setor minerário nos últimos anos, trouxe à tona uma discussão em torno da necessidade de aperfeiçoar o controle sobre tais atividades, de modo a evitar desastres gerados pela falta de fiscalização e regulamentação efetiva sobre o setor.</t>
+        </is>
+      </c>
+      <c r="I1017" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J1017" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K1017" t="inlineStr"/>
+      <c r="L1017" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>Alumínio é um mineral metálico encontrado em escudos cristalinos, isso ocorre porque</t>
+        </is>
+      </c>
+      <c r="B1018" t="inlineStr">
+        <is>
+          <t>os escudos cristalinos acumulam o material retirado pela erosão, acumulando também os metais.</t>
+        </is>
+      </c>
+      <c r="C1018" t="inlineStr">
+        <is>
+          <t>esses materiais metálicos se acumulam nos escudos, que constituem estruturas geológicas rebaixadas.</t>
+        </is>
+      </c>
+      <c r="D1018" t="inlineStr">
+        <is>
+          <t>a antiguidade dos escudos cristalinos favorece a formação do alumínio, fruto da alteração local de outros minerais.</t>
+        </is>
+      </c>
+      <c r="E1018" t="inlineStr">
+        <is>
+          <t>os escudos cristalinos se formam a partir de material magmático, material primordial de origem de minerais metálicos.</t>
+        </is>
+      </c>
+      <c r="F1018" t="inlineStr"/>
+      <c r="G1018" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H1018" t="inlineStr">
+        <is>
+          <t>O alumínio é obtido através da exploração da bauxita, formada pela alteração química in situ de rochas ricas em feldspatos, que ocorre na escala geológica de milhões de anos.</t>
+        </is>
+      </c>
+      <c r="I1018" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J1018" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K1018" t="inlineStr"/>
+      <c r="L1018" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>A exploração mineral é capaz de gerar benefícios para a economia de um país ao mesmo tempo que pode impactar negativamente o meio ambiente e a sociedade. Dessa forma, entre os possíveis impactos negativos dessa atividade, é possível citar:</t>
+        </is>
+      </c>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t>A contaminação das águas.</t>
+        </is>
+      </c>
+      <c r="C1019" t="inlineStr">
+        <is>
+          <t>A implantação de infraestrutura.</t>
+        </is>
+      </c>
+      <c r="D1019" t="inlineStr">
+        <is>
+          <t>A escassez de água.</t>
+        </is>
+      </c>
+      <c r="E1019" t="inlineStr">
+        <is>
+          <t>A desvalorização imobiliária.</t>
+        </is>
+      </c>
+      <c r="F1019" t="inlineStr"/>
+      <c r="G1019" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H1019" t="inlineStr">
+        <is>
+          <t>A contaminação das águas é um dos possíveis impactos negativos da exploração mineral no meio ambiente, devido aos produtos químicos utilizados durante o processo de extração dos minérios, comumente utilizados junto com água, gerando componentes tóxicos que precisam ficar, muitas vezes, armazenados em represas.</t>
+        </is>
+      </c>
+      <c r="I1019" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J1019" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K1019" t="inlineStr"/>
+      <c r="L1019" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>“Devido a simplicidade do trabalho no que diz respeito a técnicas e conhecimentos necessários para a realização da extração de minérios que continua a ser ainda na atualidade em muitos casos feita de forma rudimentar...”.
+Fonte: RODRIGUES, C. C; GARCÍA, M. F. Disponível em: http://www.proceedings.scielo.br/pdf/jtrab/n1/22.pdf. Acesso em: 20 fev. 2019.
+O trecho acima destaca características da</t>
+        </is>
+      </c>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t>extração mineral intensiva.</t>
+        </is>
+      </c>
+      <c r="C1020" t="inlineStr">
+        <is>
+          <t>extração mineral básica.</t>
+        </is>
+      </c>
+      <c r="D1020" t="inlineStr">
+        <is>
+          <t>extração mineral popular.</t>
+        </is>
+      </c>
+      <c r="E1020" t="inlineStr">
+        <is>
+          <t>extração mineral garimpeira.</t>
+        </is>
+      </c>
+      <c r="F1020" t="inlineStr"/>
+      <c r="G1020" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H1020" t="inlineStr">
+        <is>
+          <t>O garimpo é uma forma de exploração mineral precária, com a utilização de técnicas e equipamentos mais rudimentares e baratos.</t>
+        </is>
+      </c>
+      <c r="I1020" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J1020" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K1020" t="inlineStr"/>
+      <c r="L1020" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>Uma importante jazida mineral brasileira encontrada no estado do Pará, é:</t>
+        </is>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>Bacia do Litoral Norte.</t>
+        </is>
+      </c>
+      <c r="C1021" t="inlineStr">
+        <is>
+          <t>Quadrilátero Ferrífero.</t>
+        </is>
+      </c>
+      <c r="D1021" t="inlineStr">
+        <is>
+          <t>Província Mineral de Carajás.</t>
+        </is>
+      </c>
+      <c r="E1021" t="inlineStr">
+        <is>
+          <t>Bacia de Campos.</t>
+        </is>
+      </c>
+      <c r="F1021" t="inlineStr"/>
+      <c r="G1021" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H1021" t="inlineStr">
+        <is>
+          <t>Considerando as principais jazidas minerais brasileiras, no estado do Pará, é possível encontrar a Província Mineral de Carajás, onde é possível encontrar ferro, manganês, ouro e entre outros minerais.</t>
+        </is>
+      </c>
+      <c r="I1021" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J1021" t="inlineStr">
+        <is>
+          <t>Geografia</t>
+        </is>
+      </c>
+      <c r="K1021" t="inlineStr"/>
+      <c r="L1021" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>Mas foi o filósofo inglês Thomas Hobbes que ajudou a construir as bases teóricas do Estado moderno. Na obra Leviatã, do século XVII, diz que os humanos são egoístas por natureza e têm a tendência natural de guerrear uns contra os outros. A única maneira de evitar uma situação de caos é por meio de um “contrato social”, em que os homens reconhecem a autoridade, personificada em um governante ou um regime político.
+Estado. Disponível em: https://super.abril.com.br/historia/estado. Acesso em: 22 out. 2024.
+De acordo com o texto, qual a principal ideia defendida por Thomas Hobbes em sua obra Leviatã?</t>
+        </is>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>A separação dos poderes.</t>
+        </is>
+      </c>
+      <c r="C1022" t="inlineStr">
+        <is>
+          <t>O governo com participação popular.</t>
+        </is>
+      </c>
+      <c r="D1022" t="inlineStr">
+        <is>
+          <t>O contrato social para evitar o caos.</t>
+        </is>
+      </c>
+      <c r="E1022" t="inlineStr">
+        <is>
+          <t>A anarquia como forma ideal de governo.</t>
+        </is>
+      </c>
+      <c r="F1022" t="inlineStr"/>
+      <c r="G1022" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H1022" t="inlineStr">
+        <is>
+          <t>Hobbes argumenta que, para evitar o estado de guerra e caos, os homens devem firmar um contrato social em que reconhecem a autoridade de um governante ou regime político centralizado, estabelecendo assim a paz e a ordem.</t>
+        </is>
+      </c>
+      <c r="I1022" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J1022" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K1022" t="inlineStr"/>
+      <c r="L1022" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>Maquiavel usou sua própria experiência como diplomata e conselheiro político para construir o tratado enxuto, de cerca de cem páginas, em que o pragmatismo impera sobre a moral. O texto de O Príncipe é tão preto no branco que a sinceridade de Maquiavel causa calafrios até hoje. Também é uma das obras mais citadas em ciência política. Maquiavélico virou um adjetivo como sinônimo de crueldade e frieza. Os admiradores da obra lamentam a leitura negativa do filósofo. Maquiavel foi preciso na sua análise realista do mundo político, onde nada é o que parece, e foi o primeiro a colocar a discussão ética em termos práticos, com exemplos da vida real.
+SANTI, Alexandre de. Maquiavel: os fins justificam os meios. Disponível em: https://super.abril.com.br/cultura/os-fins-justificam-os-meios. Acesso em: 22 out. 2024.
+Qual é a principal característica da obra "O Príncipe", de Maquiavel, conforme descrita no texto base?</t>
+        </is>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>A promoção de um governo ideal baseado na igualdade e justiça social, destacando-se como uma referência para ideais democráticos no contexto político da época.</t>
+        </is>
+      </c>
+      <c r="C1023" t="inlineStr">
+        <is>
+          <t>A elaboração de uma análise puramente teórica, desligada da realidade prática, focando em conceitos abstratos sem dialogar concretamente com a política da época.</t>
+        </is>
+      </c>
+      <c r="D1023" t="inlineStr">
+        <is>
+          <t>A ênfase no pragmatismo político, destacando que a eficácia e o realismo são mais importantes do que a moralidade, e utilizando exemplos práticos para suas ideias.</t>
+        </is>
+      </c>
+      <c r="E1023" t="inlineStr">
+        <is>
+          <t>A proposta de uma visão utópica da política, onde os governantes agem sempre de forma justa, idealizando um mundo onde os princípios éticos suprem a realidade prática.</t>
+        </is>
+      </c>
+      <c r="F1023" t="inlineStr"/>
+      <c r="G1023" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H1023" t="inlineStr">
+        <is>
+          <t>Maquiavel, em "O Príncipe", foca sua análise no pragmatismo e realismo político, priorizando a eficácia das ações governamentais sobre a moralidade, defendendo a realização de qualquer ação necessária para a manutenção do poder do príncipe. Para tanto, como indica o texto, Maquiavel relaciona seus escritos com exemplos e acontecimentos políticos do período em que escrevia.</t>
+        </is>
+      </c>
+      <c r="I1023" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J1023" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K1023" t="inlineStr"/>
+      <c r="L1023" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>Durante a Idade Moderna, a base do poder absoluto do rei foi formada pelas duas classes sociais de elite - a nobreza e a burguesia - e pela igreja. No entanto, neste mesmo período, percebemos grandes transformações na organização religiosa do cristianismo, com o movimento reformista e a formação de novas doutrinas, iniciados por Lutero.
+Apesar da quebra da unidade do cristianismo, dividido a partir de então em doutrinas diferentes, a religião continuou a ter um papel importante na formação cultural do homem europeu e, consequentemente, foi utilizada para apoiar e/ou justificar o poder real.
+RECCO, Claudio B. O absolutismo e a reforma religiosa. Disponível em: https://www1.folha.uol.com.br/folha/educacao/ult305u13408.shtml. Acesso em: 22 out. 2024.
+Como o conceito de direito divino dos reis foi utilizado na Idade Moderna para legitimar o poder absoluto?</t>
+        </is>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>Afirmando que o poder real se originava exclusivamente da vontade popular e dos conselhos de cidadãos.</t>
+        </is>
+      </c>
+      <c r="C1024" t="inlineStr">
+        <is>
+          <t>Alegando que o poder dos reis era delegado pelo Papa e consistia em manter a igreja subjugada.</t>
+        </is>
+      </c>
+      <c r="D1024" t="inlineStr">
+        <is>
+          <t>Justificando que o poder dos reis era concedido por Deus, tornando sua autoridade incontestável e sagrada.</t>
+        </is>
+      </c>
+      <c r="E1024" t="inlineStr">
+        <is>
+          <t>Defendendo que o poder dos reis era adquirido apenas através da conquista militar e expansão territorial, sem qualquer vínculo religioso.</t>
+        </is>
+      </c>
+      <c r="F1024" t="inlineStr"/>
+      <c r="G1024" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H1024" t="inlineStr">
+        <is>
+          <t>O conceito do direito divino dos reis defendia que o poder do monarca era de origem divina, legitimando assim sua autoridade absoluta e sem contestação, pois qualquer ato contra o rei ou qualquer forma de contestação ao seu governo seria visto como uma ofensa a Deus.</t>
+        </is>
+      </c>
+      <c r="I1024" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J1024" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K1024" t="inlineStr"/>
+      <c r="L1024" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>Tanto a prática como a teoria partiam do princípio de que não há ganho para um Estado sem prejuízo de outro, Como alcançar o ganho? Atraindo para si a maior quantidade possível do estoque mundial de metais preciosos e tratando de retê-lo. Isso deveria ser alcançado por uma política de proteção dos produtos do país mediante uma série de medidas: reduzir pela tributação elevada, ou proibir a entrada de bens manufaturados estrangeiros e facilitar o ingresso de matérias-primas; inversamente, proibir a saída de matérias-primas produzidas no país e estimular a exportação de manufaturados [...].
+[...] Não se tratava de uma política absurda, como poderia parecer por sua obsessão pelos metais preciosos. Pelo contrário, era coerente com as possibilidades de ação dos Estados nacionais em vias de criação e crescimento, em um período no qual a moeda metálica tinha uma grande importância para consolidar o Estado.
+glossário:
+tributação: aplicação de impostos;
+manufaturados: produtos feitos de forma manual, padronizados, e normalmente em uma grande quantidade.
+FAUSTO, Boris. História do Brasil. São Paulo: Edusp, 2019, 14ª edição, p, 50.
+Qual é o objetivo principal da política econômica mercantilista descrita no texto?</t>
+        </is>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>Garantir o livre comércio internacional sem restrições, promovendo a igualdade entre os Estados.</t>
+        </is>
+      </c>
+      <c r="C1025" t="inlineStr">
+        <is>
+          <t>Proibir a exportação, focando na importação de produtos independentemente dos impactos na balança comercial.</t>
+        </is>
+      </c>
+      <c r="D1025" t="inlineStr">
+        <is>
+          <t>Aumentar o estoque de metais preciosos, protegendo a economia através de políticas restritivas e incentivadoras do comércio favorável.</t>
+        </is>
+      </c>
+      <c r="E1025" t="inlineStr">
+        <is>
+          <t>Sustentar a economia por meio da dependência exclusiva de colheitas agrícolas, ignorando a necessidade de acumular riquezas metálicas.</t>
+        </is>
+      </c>
+      <c r="F1025" t="inlineStr"/>
+      <c r="G1025" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H1025" t="inlineStr">
+        <is>
+          <t>O mercantilismo visava acumular metais preciosos e fortalecer a economia nacional através de uma série de medidas protecionistas, como restrições à importação de manufaturados e promoção da exportação de produtos acabados, fortalecendo o Estado frente aos demais ao garantir uma balança comercial favorável.</t>
+        </is>
+      </c>
+      <c r="I1025" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J1025" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K1025" t="inlineStr"/>
+      <c r="L1025" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>Enquanto regime, o absolutismo resulta de um longo processo histórico de centralização do poder e da autoridade na figura do monarca; que se foi cumprindo entre o final da Idade Médio e o princípio da Era Moderna. O país onde primeiro surgiu um regime absolutista de uma forma acabada [...] foi o reino da França, no século XVI.
+Disponível em: https://repositorio-aberto.up.pt/bitstream/10216/118246/2/306625.pdf. Acesso em: 22 out. 2024. (Adaptado).
+O longo processo mencionado no texto foi caracterizado pela(o)</t>
+        </is>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>formação de alianças entre o rei e os senhores feudais para manter a descentralização dos poderes político e territorial.</t>
+        </is>
+      </c>
+      <c r="C1026" t="inlineStr">
+        <is>
+          <t>fortalecimento do poder real pela construção de um sistema centralizado de autoridade, aliado à reorganização da nobreza e da igreja.</t>
+        </is>
+      </c>
+      <c r="D1026" t="inlineStr">
+        <is>
+          <t>consolidação do poder dos artesãos e comerciantes, que passaram a controlar os impostos e a administração local.</t>
+        </is>
+      </c>
+      <c r="E1026" t="inlineStr">
+        <is>
+          <t>desenvolvimento de uma estrutura política baseada na cooperação entre diversas cidades-estado independentes, sem a figura central do monarca.</t>
+        </is>
+      </c>
+      <c r="F1026" t="inlineStr"/>
+      <c r="G1026" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H1026" t="inlineStr">
+        <is>
+          <t>O processo de absolutismo envolveu a centralização do poder na figura do rei, que unificou o controle político e territorial, com o apoio da nobreza e da igreja, elementos essenciais para consolidar e manter seu poder.</t>
+        </is>
+      </c>
+      <c r="I1026" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J1026" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K1026" t="inlineStr"/>
+      <c r="L1026" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>Entre o final da Idade Média e o início dos tempos modernos, a lenta desestruturação do feudalismo e o reaquecimento do comércio, assim como a conquista da América, trouxeram mudanças para o modo de pensar e viver de muitas pessoas de diversas cidades e regiões europeias.
+ALMEIDA, Andréia e SILVEIRA, Adinan. Uma releitura do poder no Estado Absolutista. Rio de Janeiro. 2013
+ No contexto de crise do sistema feudal, começa a se formar em algumas áreas da Europa uma nova forma de organização: os Estados modernos. Para a nobreza europeia, o Estado moderno representou</t>
+        </is>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>o fim de todos os privilégios que esta classe possuía durante a idade média.</t>
+        </is>
+      </c>
+      <c r="C1027" t="inlineStr">
+        <is>
+          <t>a coletivização de suas terras e a retirada dos seus títulos e posses.</t>
+        </is>
+      </c>
+      <c r="D1027" t="inlineStr">
+        <is>
+          <t>a ascensão social, uma vez que passaria a ser uma classe de grandes comerciantes.</t>
+        </is>
+      </c>
+      <c r="E1027" t="inlineStr">
+        <is>
+          <t>uma nova forma de se manter como classe dominante, participando da burocracia estatal.</t>
+        </is>
+      </c>
+      <c r="F1027" t="inlineStr"/>
+      <c r="G1027" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H1027" t="inlineStr">
+        <is>
+          <t>No processo de formação dos Estados Modernos a nobreza percebeu uma oportunidade de se reorganizar e manter seu poder tornando-se parte da burocracia estatal, ou seja, integrando a administração do Estado.</t>
+        </is>
+      </c>
+      <c r="I1027" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J1027" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K1027" t="inlineStr"/>
+      <c r="L1027" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>Burocracia, polícia, exército regular, clero e magistratura, tudo teve seu nascimento nos dias da monarquia absoluta. O poder centralizado do Estado tinha, naquele tempo, de servir à nascente sociedade de classe média como uma poderosa arma em suas lutas para emancipar-se do feudalismo​.
+ANDERSON, Perry. Passagens da Antiguidade ao Feudalismo. São Paulo: Unesp, 2013, p.170.
+ A formação dos Estados modernos trouxe, além da centralização política, outras vantagens para os monarcas. Entre elas está:</t>
+        </is>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>a formação de um exército regular sob as ordens do rei.</t>
+        </is>
+      </c>
+      <c r="C1028" t="inlineStr">
+        <is>
+          <t>a tripartição do poder em executivo, legislativo e judiciário.</t>
+        </is>
+      </c>
+      <c r="D1028" t="inlineStr">
+        <is>
+          <t>o crescimento do número de servos leais ao rei e senhores feudais.</t>
+        </is>
+      </c>
+      <c r="E1028" t="inlineStr">
+        <is>
+          <t>a separação do poder político e do poder religioso.</t>
+        </is>
+      </c>
+      <c r="F1028" t="inlineStr"/>
+      <c r="G1028" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H1028" t="inlineStr">
+        <is>
+          <t>Para garantir as decisões do governo soberano do novo Estado, foi preciso a formação de exércitos regulares controlados pelos reis.</t>
+        </is>
+      </c>
+      <c r="I1028" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J1028" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K1028" t="inlineStr"/>
+      <c r="L1028" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>Na tentativa de solucionar todos esses problemas, a burguesia buscou um aliado que, por mais contraditório que possa parecer, era o mais alto dos nobres: o rei. Seu poder havia sido corroído por uma cadeia de acordos político-militares firmados com a nobreza (as chamadas relações de suserania e vassalagem ou relações feudo-vassálicas), desde a divisão do Império de Carlos Magno, em 843.
+NAZARO, Newton. Disponível em: https://educacao.uol.com.br/disciplinas/historia/estados-nacionais-burguesia-se-une-ao-rei-e-forma-o-estado-nacao.htm
+ O texto acima atenta ao fato de que a burguesia se aliou aos reis porque tinha interesses no processo de centralização política durante a formação dos Estados modernos. Um interesse da burguesia nesse processo foi</t>
+        </is>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>o fim de todos os impostos, visto que os monarcas não mais iriam taxar as trocas comerciais.</t>
+        </is>
+      </c>
+      <c r="C1029" t="inlineStr">
+        <is>
+          <t>a unificação das moedas e dos sistemas de pesos e medidas, facilitando a atividade comercial.</t>
+        </is>
+      </c>
+      <c r="D1029" t="inlineStr">
+        <is>
+          <t>o estabelecimento do escambo como única maneira de se realizar o comércio, eliminando as moedas.</t>
+        </is>
+      </c>
+      <c r="E1029" t="inlineStr">
+        <is>
+          <t>a tomada de terras dos senhores feudais que seriam repassadas aos burgueses.</t>
+        </is>
+      </c>
+      <c r="F1029" t="inlineStr"/>
+      <c r="G1029" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H1029" t="inlineStr">
+        <is>
+          <t>Através da centralização do poder e da unificação do território, o rei garantia o desenvolvimento do comércio, favorecendo, assim, a expansão dos negócios da burguesia. Além disso, a unificação de pesos, medidas e da moeda, também facilitava a atividade comercial.</t>
+        </is>
+      </c>
+      <c r="I1029" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J1029" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K1029" t="inlineStr"/>
+      <c r="L1029" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>O texto a seguir trata do papel da Igreja durante a Idade Média, caracterizado pela forte influência que os papas exerciam na política interna dos vários reis. Observe:
+A Igreja não só tinha alguns dos atributos do Estado, como instituições duradouras e uma teoria do “poder supremo” papal, mas, além disso, influenciava diretamente a política secular, pelo envolvimento do clero nos negócios públicos e pela atribuição, aos governantes, da obrigação de garantir a paz e a justiça entre os súditos.
+(KRITSCH, Raquel. RUMO AO ESTADO MODERNO: AS RAÍZES MEDIEVAIS DE ALGUNS DE SEUS ELEMENTOS FORMADORES. Curitiba. 2004)
+ Contudo, essa situação vai se modificando durante o processo de formação das monarquias modernas. As relações entre reis e Igreja no contexto de formação dos Estados modernos foram marcadas</t>
+        </is>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>pela autoridade do papa sobre os reis e os nobres possuidores de terras.</t>
+        </is>
+      </c>
+      <c r="C1030" t="inlineStr">
+        <is>
+          <t>pela ausência de influência da Igreja nas decisões políticas de cada reino.</t>
+        </is>
+      </c>
+      <c r="D1030" t="inlineStr">
+        <is>
+          <t>por um conflito de interesses entre reis e papas pelo exercício do poder político.</t>
+        </is>
+      </c>
+      <c r="E1030" t="inlineStr">
+        <is>
+          <t>pelo financiamento da Igreja a revoltas de senhores feudais contra os monarcas.</t>
+        </is>
+      </c>
+      <c r="F1030" t="inlineStr"/>
+      <c r="G1030" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H1030" t="inlineStr">
+        <is>
+          <t>A Igreja, durante a formação do Estado moderno, sofreu com a diminuição da sua influência, tendo em vista que funcionava como a única instituição com força centralizadora durante o período medieval.</t>
+        </is>
+      </c>
+      <c r="I1030" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J1030" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K1030" t="inlineStr"/>
+      <c r="L1030" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>Leia o trecho abaixo, extraído das Memórias de Luís XIV para o ano de 1661:
+Em todos os lugares havia calma. Nenhum movimento, nem temor ou aparência de movimento no Reino havia que pudessem interromper ou se opor aos meus projetos.
+ O regime político caracterizado acima é a:</t>
+        </is>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>monarquia parlamentarista.</t>
+        </is>
+      </c>
+      <c r="C1031" t="inlineStr">
+        <is>
+          <t>monarquia absolutista.</t>
+        </is>
+      </c>
+      <c r="D1031" t="inlineStr">
+        <is>
+          <t>monarquia feudal.</t>
+        </is>
+      </c>
+      <c r="E1031" t="inlineStr">
+        <is>
+          <t>ditadura.</t>
+        </is>
+      </c>
+      <c r="F1031" t="inlineStr"/>
+      <c r="G1031" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H1031" t="inlineStr">
+        <is>
+          <t>A monarquia absolutista é marcada pelo poder do monarca, que estava acima de todos os outros poderes, centralizando o Estado em sua figura.</t>
+        </is>
+      </c>
+      <c r="I1031" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J1031" t="inlineStr">
+        <is>
+          <t>História</t>
+        </is>
+      </c>
+      <c r="K1031" t="inlineStr"/>
+      <c r="L1031" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>Leia o texto a seguir.
+Agora, por que os recifes de coral são tão importantes? Primeiro, porque eles apresentam uma grande biodiversidade, servindo de local para reprodução e alimentação de muitas espécies. A depender da localização, peixes, esponjas, lagostas, caranguejos, ouriços, estrelas-do-mar e tartarugas vivem em torno dos recifes. Fora isso, são estruturas resistentes, que suportam a energia das ondas e das correntes marítimas, diminuindo os impactos da água do mar no litoral.
+Disponível em: https://chc.org.br/artigo/recifes-de-coral/. Acesso em 16 out. 2024
+O advérbio "em torno" pode ser substituído sem alteração de significado por</t>
+        </is>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>"perto".</t>
+        </is>
+      </c>
+      <c r="C1032" t="inlineStr">
+        <is>
+          <t>"ao lado".</t>
+        </is>
+      </c>
+      <c r="D1032" t="inlineStr">
+        <is>
+          <t>"ao redor".</t>
+        </is>
+      </c>
+      <c r="E1032" t="inlineStr">
+        <is>
+          <t>"à frente".</t>
+        </is>
+      </c>
+      <c r="F1032" t="inlineStr"/>
+      <c r="G1032" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H1032" t="inlineStr">
+        <is>
+          <t>A expressão "ao redor" é sinônima de "em torno", pois ambas indicam algo que circunda ou está em volta de um ponto ou objeto. No contexto da frase, ela mantém o mesmo sentido de "algo que vive ao redor dos recifes", ou seja, no entorno dos recifes.</t>
+        </is>
+      </c>
+      <c r="I1032" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J1032" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K1032" t="inlineStr"/>
+      <c r="L1032" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>Leia o texto a seguir:
+Atlético-MG passa apuros, suporta pressão com paciência e recorre a Hulk para vencer
+Disponível em:https://ge.globo.com/futebol/times/atletico-mg/noticia/2024/07/29/analise-atletico-mg-passa-apuros-suporta-pressao-com-paciencia-e-recorre-a-hulk-para-vencer.ghtml Acesso em: 28 out. 2024. 
+O trecho em destaque é uma locução adverbial. Indique qual das frases também contém uma locução adverbial.</t>
+        </is>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>O cientista conduziu o experimento cuidadosamente, anotando cada detalhe.</t>
+        </is>
+      </c>
+      <c r="C1033" t="inlineStr">
+        <is>
+          <t>Os alunos resolveram a equação corretamente, sem cometer erros.</t>
+        </is>
+      </c>
+      <c r="D1033" t="inlineStr">
+        <is>
+          <t>Eles caminhavam em silêncio pelos corredores da biblioteca.</t>
+        </is>
+      </c>
+      <c r="E1033" t="inlineStr">
+        <is>
+          <t>A garota percebeu que o dia estava mais quente.</t>
+        </is>
+      </c>
+      <c r="F1033" t="inlineStr"/>
+      <c r="G1033" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H1033" t="inlineStr">
+        <is>
+          <t>A frase contém a locução adverbial "em silêncio", que indica a maneira como os alunos caminhavam. Locuções adverbiais são formadas por mais de uma palavra e descrevem como a ação é realizada. Neste caso, "em silêncio" descreve a ação de forma mais detalhada.</t>
+        </is>
+      </c>
+      <c r="I1033" t="inlineStr">
+        <is>
+          <t>PH03</t>
+        </is>
+      </c>
+      <c r="J1033" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="K1033" t="inlineStr"/>
+      <c r="L1033" t="inlineStr">
+        <is>
+          <t>7ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>[img:ph03_por_03.jpg]
+Hagar, o Horrível, vol 1, 2014
+Considerando o uso de advérbios, qual das alternativas interpreta corretamente o uso dessa classe gramatical na tirinha?</t>
+        </is>
+      </c>
+      <c r="B1034" t="inlineStr">
+      